--- a/jogos_2026-11-01.xlsx
+++ b/jogos_2026-11-01.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tokyo Verdy</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="G6">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Tokyo Verdy</t>
         </is>
       </c>
       <c r="G7">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G33">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Atlético Central</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G50">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Atlético Central</t>
         </is>
       </c>
       <c r="G51">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Gamo Chencha</t>
         </is>
       </c>
       <c r="G65">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gamo Chencha</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G66">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G76">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G77">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G81">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G82">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="G114">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G115">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G117">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G118">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Birmingham City Women</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G129">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Crystal Palace Ladies</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Birmingham City Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Crystal Palace Ladies</t>
         </is>
       </c>
       <c r="G131">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G134">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G136">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G137">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G138">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G146">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>AD Nogueirense</t>
         </is>
       </c>
       <c r="G147">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>AD Nogueirense</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G148">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Fazendense</t>
         </is>
       </c>
       <c r="G149">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Gd Nazarenos</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Sertanense</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G150">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Gd Nazarenos</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Sertanense</t>
         </is>
       </c>
       <c r="G151">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Fazendense</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G152">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Portel</t>
         </is>
       </c>
       <c r="G154">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Portel</t>
+          <t>Imortal Albufeira</t>
         </is>
       </c>
       <c r="G155">
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Imortal Albufeira</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="G156">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Guarda</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G161">
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Ovarense</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G162">
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Ovarense</t>
+          <t>Estrela Calheta</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="G163">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Castro Daire</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Guarda</t>
         </is>
       </c>
       <c r="G164">
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Sousense</t>
+          <t>Castro Daire</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G165">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Estrela Calheta</t>
+          <t>Sousense</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="G166">
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G168">
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G169">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G170">
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Montalegre</t>
+          <t>Ponte da Barca</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Maria da Fonte</t>
+          <t>Vinhais</t>
         </is>
       </c>
       <c r="G175">
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Ponte da Barca</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vinhais</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G176">
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G177">
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G178">
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Montalegre</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Maria da Fonte</t>
         </is>
       </c>
       <c r="G180">
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G181">
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="G187">
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G188">
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G189">
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G190">
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G198">
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G199">
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>De Graafschap W</t>
         </is>
       </c>
       <c r="G200">
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>De Graafschap W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="G201">
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G202">
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Calvo Sotelo</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="G215">
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G216">
@@ -35648,12 +35648,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G217">
@@ -35811,12 +35811,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Calvo Sotelo</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G218">
@@ -42657,12 +42657,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>CD Badajoz</t>
+          <t>Ciudad de Lucena</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G260">
@@ -42820,12 +42820,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Ciudad de Lucena</t>
+          <t>CD Badajoz</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G261">
@@ -44287,12 +44287,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G270">
@@ -44450,12 +44450,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G271">
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Humble Lions</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G289">
@@ -47547,12 +47547,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G290">
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G291">
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tru-Juice</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G292">
@@ -48036,12 +48036,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Tru-Juice</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Humble Lions</t>
         </is>
       </c>
       <c r="G293">
@@ -49177,12 +49177,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G300">
@@ -49340,12 +49340,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G301">
@@ -49503,12 +49503,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G302">
@@ -49666,12 +49666,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G303">
@@ -49829,12 +49829,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G304">
@@ -49992,12 +49992,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G305">
@@ -50155,12 +50155,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G306">
@@ -50318,12 +50318,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G307">

--- a/jogos_2026-11-01.xlsx
+++ b/jogos_2026-11-01.xlsx
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Adhyaksa</t>
         </is>
       </c>
       <c r="G12">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Adhyaksa</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G13">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G81">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G82">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G134">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G136">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G138">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G146">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>AD Nogueirense</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G147">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>AD Nogueirense</t>
         </is>
       </c>
       <c r="G148">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Fazendense</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G149">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Fazendense</t>
         </is>
       </c>
       <c r="G150">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Gd Nazarenos</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Sertanense</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G151">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Gd Nazarenos</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Sertanense</t>
         </is>
       </c>
       <c r="G152">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Vitória Setúbal</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="G153">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Vitória Setúbal</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Portel</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G154">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Imortal Albufeira</t>
+          <t>Portel</t>
         </is>
       </c>
       <c r="G155">
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Imortal Albufeira</t>
         </is>
       </c>
       <c r="G156">
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G168">
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G169">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G170">
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Ponte da Barca</t>
+          <t>Montalegre</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Vinhais</t>
+          <t>Maria da Fonte</t>
         </is>
       </c>
       <c r="G175">
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Ponte da Barca</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Vinhais</t>
         </is>
       </c>
       <c r="G176">
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G177">
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G178">
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Maia Lidador</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G179">
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Montalegre</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Maria da Fonte</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G180">
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Maia Lidador</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="G181">
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G189">
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G190">
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G202">
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G203">
@@ -42657,12 +42657,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Ciudad de Lucena</t>
+          <t>CD Badajoz</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G260">
@@ -42820,12 +42820,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>CD Badajoz</t>
+          <t>Ciudad de Lucena</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G261">
@@ -43635,12 +43635,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G266">
@@ -43798,12 +43798,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G267">
@@ -44287,12 +44287,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G270">
@@ -44450,12 +44450,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G271">
@@ -47547,12 +47547,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Tru-Juice</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G290">
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G291">
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Tru-Juice</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G292">

--- a/jogos_2026-11-01.xlsx
+++ b/jogos_2026-11-01.xlsx
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G102">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G103">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G117">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G118">
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Ovarense</t>
+          <t>Estrela Calheta</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="G162">
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Estrela Calheta</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Guarda</t>
         </is>
       </c>
       <c r="G163">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Castro Daire</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Guarda</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G164">
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Castro Daire</t>
+          <t>Sousense</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="G165">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Sousense</t>
+          <t>Ovarense</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G166">
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G168">
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G169">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G170">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G192">
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G193">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G194">
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G202">
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G203">
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G216">
@@ -35648,12 +35648,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Calvo Sotelo</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G217">
@@ -35811,12 +35811,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Calvo Sotelo</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G218">
@@ -35974,12 +35974,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G219">
@@ -43635,12 +43635,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G266">
@@ -43798,12 +43798,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G267">
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Tru-Juice</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G289">
@@ -47547,12 +47547,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Tru-Juice</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G290">
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Humble Lions</t>
         </is>
       </c>
       <c r="G291">
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G292">
@@ -48036,12 +48036,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Humble Lions</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G293">

--- a/jogos_2026-11-01.xlsx
+++ b/jogos_2026-11-01.xlsx
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -21499,13 +21499,13 @@
         </is>
       </c>
       <c r="N130">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="O130">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="P130">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q130">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G137">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G138">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G192">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G194">
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G230">
@@ -37930,12 +37930,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G231">
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G232">
@@ -39560,12 +39560,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Cieza</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G241">
@@ -39723,12 +39723,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Cieza</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G242">
@@ -43635,12 +43635,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G266">
@@ -43798,12 +43798,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G267">
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Tru-Juice</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G289">
@@ -47547,12 +47547,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Humble Lions</t>
         </is>
       </c>
       <c r="G290">
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Humble Lions</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G291">
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G292">
@@ -48036,12 +48036,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Tru-Juice</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G293">

--- a/jogos_2026-11-01.xlsx
+++ b/jogos_2026-11-01.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC5">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1326,10 +1326,10 @@
         <v>0</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC6">
         <v>0</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1489,10 +1489,10 @@
         <v>0</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC7">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1815,10 +1815,10 @@
         <v>0</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC9">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -1978,10 +1978,10 @@
         <v>0</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC10">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Adhyaksa</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G12">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Adhyaksa</t>
         </is>
       </c>
       <c r="G13">
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mijas Las Lagunas</t>
+          <t>CD Don Benito</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CD Don Benito</t>
+          <t>Mijas Las Lagunas</t>
         </is>
       </c>
       <c r="G40">
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gamo Chencha</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G65">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Gamo Chencha</t>
         </is>
       </c>
       <c r="G66">
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O73">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P73">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q73">
         <v>0</v>
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O75">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P75">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -12579,10 +12579,10 @@
         <v>0</v>
       </c>
       <c r="AC75">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD75">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE75">
         <v>0</v>
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O76">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -12742,10 +12742,10 @@
         <v>0</v>
       </c>
       <c r="AC76">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD76">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE76">
         <v>0</v>
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O77">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P77">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -12899,10 +12899,10 @@
         <v>0</v>
       </c>
       <c r="AA77">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB77">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC77">
         <v>0</v>
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="O84">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q90">
         <v>0</v>
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O91">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q91">
         <v>0</v>
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O94">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q94">
         <v>0</v>
@@ -20032,13 +20032,13 @@
         </is>
       </c>
       <c r="N121">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O121">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="P121">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q121">
         <v>0</v>
@@ -27530,13 +27530,13 @@
         </is>
       </c>
       <c r="N167">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O167">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="P167">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="Q167">
         <v>0</v>
@@ -27575,10 +27575,10 @@
         <v>0</v>
       </c>
       <c r="AC167">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD167">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AE167">
         <v>0</v>
@@ -28345,13 +28345,13 @@
         </is>
       </c>
       <c r="N172">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="O172">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="P172">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Q172">
         <v>0</v>
@@ -30138,13 +30138,13 @@
         </is>
       </c>
       <c r="N183">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O183">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="P183">
-        <v>0</v>
+        <v>5.02</v>
       </c>
       <c r="Q183">
         <v>0</v>
@@ -30177,10 +30177,10 @@
         <v>0</v>
       </c>
       <c r="AA183">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB183">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC183">
         <v>0</v>
@@ -31605,13 +31605,13 @@
         </is>
       </c>
       <c r="N192">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O192">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P192">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Q192">
         <v>0</v>
@@ -31931,13 +31931,13 @@
         </is>
       </c>
       <c r="N194">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O194">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P194">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q194">
         <v>0</v>
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Manresa</t>
         </is>
       </c>
       <c r="G208">
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Manresa</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G209">
@@ -35648,12 +35648,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Calvo Sotelo</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G217">
@@ -35811,12 +35811,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G218">
@@ -35974,12 +35974,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Calvo Sotelo</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G219">
@@ -37310,13 +37310,13 @@
         </is>
       </c>
       <c r="N227">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O227">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="P227">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q227">
         <v>0</v>
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G228">
@@ -37473,13 +37473,13 @@
         </is>
       </c>
       <c r="N228">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="O228">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P228">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q228">
         <v>0</v>
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G229">
@@ -37636,13 +37636,13 @@
         </is>
       </c>
       <c r="N229">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O229">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="P229">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Q229">
         <v>0</v>
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G230">
@@ -37799,13 +37799,13 @@
         </is>
       </c>
       <c r="N230">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="O230">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="P230">
-        <v>0</v>
+        <v>8.56</v>
       </c>
       <c r="Q230">
         <v>0</v>
@@ -37930,12 +37930,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G231">
@@ -37962,13 +37962,13 @@
         </is>
       </c>
       <c r="N231">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O231">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="P231">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="Q231">
         <v>0</v>
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G232">
@@ -38125,13 +38125,13 @@
         </is>
       </c>
       <c r="N232">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="O232">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="P232">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q232">
         <v>0</v>

--- a/jogos_2026-11-01.xlsx
+++ b/jogos_2026-11-01.xlsx
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G81">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G82">
@@ -31116,13 +31116,13 @@
         </is>
       </c>
       <c r="N189">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O189">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P189">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q189">
         <v>0</v>
@@ -31279,13 +31279,13 @@
         </is>
       </c>
       <c r="N190">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O190">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P190">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q190">
         <v>0</v>
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G227">
@@ -37310,13 +37310,13 @@
         </is>
       </c>
       <c r="N227">
-        <v>1.46</v>
+        <v>4.04</v>
       </c>
       <c r="O227">
-        <v>4.89</v>
+        <v>3.84</v>
       </c>
       <c r="P227">
-        <v>5.2</v>
+        <v>1.76</v>
       </c>
       <c r="Q227">
         <v>0</v>
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G228">
@@ -37473,13 +37473,13 @@
         </is>
       </c>
       <c r="N228">
-        <v>4.04</v>
+        <v>2.03</v>
       </c>
       <c r="O228">
-        <v>3.84</v>
+        <v>3.79</v>
       </c>
       <c r="P228">
-        <v>1.76</v>
+        <v>3.14</v>
       </c>
       <c r="Q228">
         <v>0</v>
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G229">
@@ -37636,13 +37636,13 @@
         </is>
       </c>
       <c r="N229">
-        <v>2.03</v>
+        <v>1.48</v>
       </c>
       <c r="O229">
-        <v>3.79</v>
+        <v>4.85</v>
       </c>
       <c r="P229">
-        <v>3.14</v>
+        <v>4.99</v>
       </c>
       <c r="Q229">
         <v>0</v>
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G230">
@@ -37799,13 +37799,13 @@
         </is>
       </c>
       <c r="N230">
-        <v>1.22</v>
+        <v>5.39</v>
       </c>
       <c r="O230">
-        <v>6.75</v>
+        <v>5.23</v>
       </c>
       <c r="P230">
-        <v>8.56</v>
+        <v>1.42</v>
       </c>
       <c r="Q230">
         <v>0</v>
@@ -37930,12 +37930,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G231">
@@ -37962,13 +37962,13 @@
         </is>
       </c>
       <c r="N231">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="O231">
-        <v>4.85</v>
+        <v>4.89</v>
       </c>
       <c r="P231">
-        <v>4.99</v>
+        <v>5.2</v>
       </c>
       <c r="Q231">
         <v>0</v>
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G232">
@@ -38125,13 +38125,13 @@
         </is>
       </c>
       <c r="N232">
-        <v>5.39</v>
+        <v>1.22</v>
       </c>
       <c r="O232">
-        <v>5.23</v>
+        <v>6.75</v>
       </c>
       <c r="P232">
-        <v>1.42</v>
+        <v>8.56</v>
       </c>
       <c r="Q232">
         <v>0</v>
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Tru-Juice</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G292">
@@ -48036,12 +48036,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Tru-Juice</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G293">

--- a/jogos_2026-11-01.xlsx
+++ b/jogos_2026-11-01.xlsx
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.15</v>
+        <v>2.74</v>
       </c>
       <c r="O9">
-        <v>3.22</v>
+        <v>3.26</v>
       </c>
       <c r="P9">
-        <v>3.02</v>
+        <v>2.3</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1815,10 +1815,10 @@
         <v>0</v>
       </c>
       <c r="AA9">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AB9">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AC9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.74</v>
+        <v>2.15</v>
       </c>
       <c r="O10">
-        <v>3.26</v>
+        <v>3.22</v>
       </c>
       <c r="P10">
-        <v>2.3</v>
+        <v>3.02</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -1978,10 +1978,10 @@
         <v>0</v>
       </c>
       <c r="AA10">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AB10">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AC10">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.06</v>
+        <v>3.29</v>
       </c>
       <c r="O64">
-        <v>11</v>
+        <v>3.62</v>
       </c>
       <c r="P64">
-        <v>26</v>
+        <v>1.9</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -13186,13 +13186,13 @@
         </is>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O79">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Q79">
         <v>0</v>
@@ -13225,10 +13225,10 @@
         <v>0</v>
       </c>
       <c r="AA79">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC79">
         <v>0</v>
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="O86">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q86">
         <v>0</v>
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O87">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O98">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>6.12</v>
       </c>
       <c r="Q98">
         <v>0</v>
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O99">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P99">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O112">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q112">
         <v>0</v>
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="O116">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P116">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q116">
         <v>0</v>
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O117">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P117">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q117">
         <v>0</v>
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O118">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P118">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q118">
         <v>0</v>
@@ -23129,13 +23129,13 @@
         </is>
       </c>
       <c r="N140">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O140">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="P140">
-        <v>0</v>
+        <v>7.15</v>
       </c>
       <c r="Q140">
         <v>0</v>
@@ -23168,10 +23168,10 @@
         <v>0</v>
       </c>
       <c r="AA140">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB140">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC140">
         <v>0</v>
@@ -23292,13 +23292,13 @@
         </is>
       </c>
       <c r="N141">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O141">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="P141">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="Q141">
         <v>0</v>
@@ -28508,13 +28508,13 @@
         </is>
       </c>
       <c r="N173">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O173">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="P173">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q173">
         <v>0</v>
@@ -31768,13 +31768,13 @@
         </is>
       </c>
       <c r="N193">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="O193">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P193">
-        <v>0</v>
+        <v>7.03</v>
       </c>
       <c r="Q193">
         <v>0</v>
@@ -32257,13 +32257,13 @@
         </is>
       </c>
       <c r="N196">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O196">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="P196">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="Q196">
         <v>0</v>
@@ -32296,10 +32296,10 @@
         <v>0</v>
       </c>
       <c r="AA196">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB196">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC196">
         <v>0</v>
@@ -38288,13 +38288,13 @@
         </is>
       </c>
       <c r="N233">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O233">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P233">
-        <v>0</v>
+        <v>5.86</v>
       </c>
       <c r="Q233">
         <v>0</v>
@@ -41874,13 +41874,13 @@
         </is>
       </c>
       <c r="N255">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O255">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P255">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q255">
         <v>0</v>
@@ -42200,13 +42200,13 @@
         </is>
       </c>
       <c r="N257">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O257">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P257">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q257">
         <v>0</v>
@@ -42363,13 +42363,13 @@
         </is>
       </c>
       <c r="N258">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O258">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="P258">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q258">
         <v>0</v>
@@ -43015,13 +43015,13 @@
         </is>
       </c>
       <c r="N262">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O262">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="P262">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q262">
         <v>0</v>
@@ -43054,10 +43054,10 @@
         <v>0</v>
       </c>
       <c r="AA262">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB262">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC262">
         <v>0</v>
@@ -44319,13 +44319,13 @@
         </is>
       </c>
       <c r="N270">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="O270">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="P270">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q270">
         <v>0</v>
@@ -44482,13 +44482,13 @@
         </is>
       </c>
       <c r="N271">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O271">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="P271">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="Q271">
         <v>0</v>
@@ -44521,10 +44521,10 @@
         <v>0</v>
       </c>
       <c r="AA271">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB271">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC271">
         <v>0</v>
@@ -44808,13 +44808,13 @@
         </is>
       </c>
       <c r="N273">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O273">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P273">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="Q273">
         <v>0</v>
@@ -44971,13 +44971,13 @@
         </is>
       </c>
       <c r="N274">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O274">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="P274">
-        <v>0</v>
+        <v>6.51</v>
       </c>
       <c r="Q274">
         <v>0</v>
@@ -45010,10 +45010,10 @@
         <v>0</v>
       </c>
       <c r="AA274">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB274">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC274">
         <v>0</v>
@@ -45022,7 +45022,7 @@
         <v>0</v>
       </c>
       <c r="AE274">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF274">
         <v>0</v>
@@ -45134,13 +45134,13 @@
         </is>
       </c>
       <c r="N275">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O275">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P275">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="Q275">
         <v>0</v>
@@ -46112,13 +46112,13 @@
         </is>
       </c>
       <c r="N281">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O281">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="P281">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q281">
         <v>0</v>
@@ -46151,10 +46151,10 @@
         <v>0</v>
       </c>
       <c r="AA281">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB281">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC281">
         <v>0</v>
@@ -46438,13 +46438,13 @@
         </is>
       </c>
       <c r="N283">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O283">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P283">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q283">
         <v>0</v>
@@ -47253,13 +47253,13 @@
         </is>
       </c>
       <c r="N288">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O288">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P288">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="Q288">
         <v>0</v>
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Tru-Juice</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G291">
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Tru-Juice</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G292">
@@ -48036,12 +48036,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G293">
@@ -49046,13 +49046,13 @@
         </is>
       </c>
       <c r="N299">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O299">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P299">
-        <v>0</v>
+        <v>6.12</v>
       </c>
       <c r="Q299">
         <v>0</v>
@@ -49085,10 +49085,10 @@
         <v>0</v>
       </c>
       <c r="AA299">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB299">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC299">
         <v>0</v>
@@ -49209,13 +49209,13 @@
         </is>
       </c>
       <c r="N300">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O300">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P300">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="Q300">
         <v>0</v>
@@ -49372,13 +49372,13 @@
         </is>
       </c>
       <c r="N301">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="O301">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="P301">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q301">
         <v>0</v>
@@ -49503,12 +49503,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G302">
@@ -49535,13 +49535,13 @@
         </is>
       </c>
       <c r="N302">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="O302">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="P302">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q302">
         <v>0</v>
@@ -49666,12 +49666,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G303">
@@ -49698,13 +49698,13 @@
         </is>
       </c>
       <c r="N303">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="O303">
-        <v>0</v>
+        <v>7.45</v>
       </c>
       <c r="P303">
-        <v>0</v>
+        <v>10.53</v>
       </c>
       <c r="Q303">
         <v>0</v>
@@ -49743,10 +49743,10 @@
         <v>0</v>
       </c>
       <c r="AC303">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD303">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE303">
         <v>0</v>
@@ -49829,12 +49829,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G304">
@@ -49861,13 +49861,13 @@
         </is>
       </c>
       <c r="N304">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O304">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P304">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q304">
         <v>0</v>
@@ -49992,12 +49992,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G305">
@@ -50024,13 +50024,13 @@
         </is>
       </c>
       <c r="N305">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O305">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P305">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q305">
         <v>0</v>
@@ -50155,12 +50155,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G306">
@@ -50187,13 +50187,13 @@
         </is>
       </c>
       <c r="N306">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O306">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="P306">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q306">
         <v>0</v>
@@ -50318,12 +50318,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G307">
@@ -50350,13 +50350,13 @@
         </is>
       </c>
       <c r="N307">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O307">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="P307">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="Q307">
         <v>0</v>

--- a/jogos_2026-11-01.xlsx
+++ b/jogos_2026-11-01.xlsx
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.74</v>
+        <v>2.15</v>
       </c>
       <c r="O9">
-        <v>3.26</v>
+        <v>3.22</v>
       </c>
       <c r="P9">
-        <v>2.3</v>
+        <v>3.02</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1815,10 +1815,10 @@
         <v>0</v>
       </c>
       <c r="AA9">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AB9">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AC9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.15</v>
+        <v>2.74</v>
       </c>
       <c r="O10">
-        <v>3.22</v>
+        <v>3.26</v>
       </c>
       <c r="P10">
-        <v>3.02</v>
+        <v>2.3</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -1978,10 +1978,10 @@
         <v>0</v>
       </c>
       <c r="AA10">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AB10">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AC10">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>La Nucía</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Mallorca II</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>La Nucía</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mallorca II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G45">
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O106">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="P106">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -17632,10 +17632,10 @@
         <v>0</v>
       </c>
       <c r="AC106">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD106">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE106">
         <v>0</v>
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Birmingham City Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,13 +21336,13 @@
         </is>
       </c>
       <c r="N129">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="O129">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="P129">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q129">
         <v>0</v>
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Crystal Palace Ladies</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,13 +21499,13 @@
         </is>
       </c>
       <c r="N130">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="O130">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="P130">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Q130">
         <v>0</v>
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Birmingham City Women</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Crystal Palace Ladies</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G131">
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G189">
@@ -31116,13 +31116,13 @@
         </is>
       </c>
       <c r="N189">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="O189">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="P189">
-        <v>5</v>
+        <v>2.45</v>
       </c>
       <c r="Q189">
         <v>0</v>
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G190">
@@ -31279,13 +31279,13 @@
         </is>
       </c>
       <c r="N190">
-        <v>2.45</v>
+        <v>1.53</v>
       </c>
       <c r="O190">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="P190">
-        <v>2.45</v>
+        <v>5</v>
       </c>
       <c r="Q190">
         <v>0</v>
@@ -34539,13 +34539,13 @@
         </is>
       </c>
       <c r="N210">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O210">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="P210">
-        <v>0</v>
+        <v>5.54</v>
       </c>
       <c r="Q210">
         <v>0</v>
@@ -34702,13 +34702,13 @@
         </is>
       </c>
       <c r="N211">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O211">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P211">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q211">
         <v>0</v>
@@ -34865,13 +34865,13 @@
         </is>
       </c>
       <c r="N212">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O212">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="P212">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="Q212">
         <v>0</v>
@@ -44645,13 +44645,13 @@
         </is>
       </c>
       <c r="N272">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O272">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="P272">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q272">
         <v>0</v>
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Tru-Juice</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G291">
@@ -48036,12 +48036,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Tru-Juice</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G293">
@@ -49340,12 +49340,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G301">
@@ -49372,13 +49372,13 @@
         </is>
       </c>
       <c r="N301">
-        <v>3.49</v>
+        <v>4.46</v>
       </c>
       <c r="O301">
-        <v>3.64</v>
+        <v>4.23</v>
       </c>
       <c r="P301">
-        <v>1.81</v>
+        <v>1.53</v>
       </c>
       <c r="Q301">
         <v>0</v>
@@ -49503,12 +49503,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G302">
@@ -49535,13 +49535,13 @@
         </is>
       </c>
       <c r="N302">
-        <v>4.46</v>
+        <v>1.13</v>
       </c>
       <c r="O302">
-        <v>4.23</v>
+        <v>7.45</v>
       </c>
       <c r="P302">
-        <v>1.53</v>
+        <v>10.53</v>
       </c>
       <c r="Q302">
         <v>0</v>
@@ -49580,10 +49580,10 @@
         <v>0</v>
       </c>
       <c r="AC302">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD302">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE302">
         <v>0</v>
@@ -49666,12 +49666,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G303">
@@ -49698,13 +49698,13 @@
         </is>
       </c>
       <c r="N303">
-        <v>1.13</v>
+        <v>2.13</v>
       </c>
       <c r="O303">
-        <v>7.45</v>
+        <v>3.36</v>
       </c>
       <c r="P303">
-        <v>10.53</v>
+        <v>2.9</v>
       </c>
       <c r="Q303">
         <v>0</v>
@@ -49743,10 +49743,10 @@
         <v>0</v>
       </c>
       <c r="AC303">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD303">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE303">
         <v>0</v>
@@ -49829,12 +49829,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G304">
@@ -49861,13 +49861,13 @@
         </is>
       </c>
       <c r="N304">
-        <v>2.13</v>
+        <v>2.4</v>
       </c>
       <c r="O304">
-        <v>3.36</v>
+        <v>3.44</v>
       </c>
       <c r="P304">
-        <v>2.9</v>
+        <v>2.47</v>
       </c>
       <c r="Q304">
         <v>0</v>
@@ -49992,12 +49992,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G305">
@@ -50024,13 +50024,13 @@
         </is>
       </c>
       <c r="N305">
-        <v>2.4</v>
+        <v>1.69</v>
       </c>
       <c r="O305">
-        <v>3.44</v>
+        <v>3.79</v>
       </c>
       <c r="P305">
-        <v>2.47</v>
+        <v>3.89</v>
       </c>
       <c r="Q305">
         <v>0</v>
@@ -50155,12 +50155,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G306">
@@ -50187,13 +50187,13 @@
         </is>
       </c>
       <c r="N306">
-        <v>3.57</v>
+        <v>3.49</v>
       </c>
       <c r="O306">
-        <v>3.67</v>
+        <v>3.64</v>
       </c>
       <c r="P306">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="Q306">
         <v>0</v>
@@ -50318,12 +50318,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G307">
@@ -50350,13 +50350,13 @@
         </is>
       </c>
       <c r="N307">
-        <v>1.69</v>
+        <v>3.57</v>
       </c>
       <c r="O307">
-        <v>3.79</v>
+        <v>3.67</v>
       </c>
       <c r="P307">
-        <v>3.89</v>
+        <v>1.79</v>
       </c>
       <c r="Q307">
         <v>0</v>

--- a/jogos_2026-11-01.xlsx
+++ b/jogos_2026-11-01.xlsx
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.06</v>
+        <v>3.29</v>
       </c>
       <c r="O63">
-        <v>11</v>
+        <v>3.62</v>
       </c>
       <c r="P63">
-        <v>26</v>
+        <v>1.9</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>3.29</v>
+        <v>1.06</v>
       </c>
       <c r="O64">
-        <v>3.62</v>
+        <v>11</v>
       </c>
       <c r="P64">
-        <v>1.9</v>
+        <v>26</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G235">
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="G236">
@@ -38908,12 +38908,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G237">

--- a/jogos_2026-11-01.xlsx
+++ b/jogos_2026-11-01.xlsx
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.15</v>
+        <v>2.74</v>
       </c>
       <c r="O9">
-        <v>3.22</v>
+        <v>3.26</v>
       </c>
       <c r="P9">
-        <v>3.02</v>
+        <v>2.3</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1815,10 +1815,10 @@
         <v>0</v>
       </c>
       <c r="AA9">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AB9">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AC9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.74</v>
+        <v>2.15</v>
       </c>
       <c r="O10">
-        <v>3.26</v>
+        <v>3.22</v>
       </c>
       <c r="P10">
-        <v>2.3</v>
+        <v>3.02</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -1978,10 +1978,10 @@
         <v>0</v>
       </c>
       <c r="AA10">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AB10">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AC10">
         <v>0</v>
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G236">
@@ -38908,12 +38908,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="G237">
@@ -39560,12 +39560,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Cieza</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G241">
@@ -39723,12 +39723,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Cieza</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G242">
@@ -40864,12 +40864,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G249">
@@ -40896,13 +40896,13 @@
         </is>
       </c>
       <c r="N249">
-        <v>2.47</v>
+        <v>1.28</v>
       </c>
       <c r="O249">
-        <v>3.24</v>
+        <v>5.35</v>
       </c>
       <c r="P249">
-        <v>2.76</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q249">
         <v>0</v>
@@ -41027,12 +41027,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G250">
@@ -41059,13 +41059,13 @@
         </is>
       </c>
       <c r="N250">
-        <v>1.28</v>
+        <v>2.47</v>
       </c>
       <c r="O250">
-        <v>5.35</v>
+        <v>3.24</v>
       </c>
       <c r="P250">
-        <v>9.800000000000001</v>
+        <v>2.76</v>
       </c>
       <c r="Q250">
         <v>0</v>
@@ -49177,12 +49177,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G300">
@@ -49209,13 +49209,13 @@
         </is>
       </c>
       <c r="N300">
-        <v>1.64</v>
+        <v>4.46</v>
       </c>
       <c r="O300">
-        <v>3.74</v>
+        <v>4.23</v>
       </c>
       <c r="P300">
-        <v>4.27</v>
+        <v>1.53</v>
       </c>
       <c r="Q300">
         <v>0</v>
@@ -49340,12 +49340,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G301">
@@ -49372,13 +49372,13 @@
         </is>
       </c>
       <c r="N301">
-        <v>4.46</v>
+        <v>1.13</v>
       </c>
       <c r="O301">
-        <v>4.23</v>
+        <v>7.45</v>
       </c>
       <c r="P301">
-        <v>1.53</v>
+        <v>10.53</v>
       </c>
       <c r="Q301">
         <v>0</v>
@@ -49417,10 +49417,10 @@
         <v>0</v>
       </c>
       <c r="AC301">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD301">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE301">
         <v>0</v>
@@ -49503,12 +49503,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G302">
@@ -49535,13 +49535,13 @@
         </is>
       </c>
       <c r="N302">
-        <v>1.13</v>
+        <v>2.13</v>
       </c>
       <c r="O302">
-        <v>7.45</v>
+        <v>3.36</v>
       </c>
       <c r="P302">
-        <v>10.53</v>
+        <v>2.9</v>
       </c>
       <c r="Q302">
         <v>0</v>
@@ -49580,10 +49580,10 @@
         <v>0</v>
       </c>
       <c r="AC302">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD302">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE302">
         <v>0</v>
@@ -49666,12 +49666,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G303">
@@ -49698,13 +49698,13 @@
         </is>
       </c>
       <c r="N303">
-        <v>2.13</v>
+        <v>1.69</v>
       </c>
       <c r="O303">
-        <v>3.36</v>
+        <v>3.79</v>
       </c>
       <c r="P303">
-        <v>2.9</v>
+        <v>3.89</v>
       </c>
       <c r="Q303">
         <v>0</v>
@@ -49829,12 +49829,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G304">
@@ -49861,13 +49861,13 @@
         </is>
       </c>
       <c r="N304">
-        <v>2.4</v>
+        <v>3.49</v>
       </c>
       <c r="O304">
-        <v>3.44</v>
+        <v>3.64</v>
       </c>
       <c r="P304">
-        <v>2.47</v>
+        <v>1.81</v>
       </c>
       <c r="Q304">
         <v>0</v>
@@ -49992,12 +49992,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G305">
@@ -50024,13 +50024,13 @@
         </is>
       </c>
       <c r="N305">
-        <v>1.69</v>
+        <v>3.57</v>
       </c>
       <c r="O305">
-        <v>3.79</v>
+        <v>3.67</v>
       </c>
       <c r="P305">
-        <v>3.89</v>
+        <v>1.79</v>
       </c>
       <c r="Q305">
         <v>0</v>
@@ -50155,12 +50155,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G306">
@@ -50187,13 +50187,13 @@
         </is>
       </c>
       <c r="N306">
-        <v>3.49</v>
+        <v>1.64</v>
       </c>
       <c r="O306">
-        <v>3.64</v>
+        <v>3.74</v>
       </c>
       <c r="P306">
-        <v>1.81</v>
+        <v>4.27</v>
       </c>
       <c r="Q306">
         <v>0</v>
@@ -50318,12 +50318,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G307">
@@ -50350,13 +50350,13 @@
         </is>
       </c>
       <c r="N307">
-        <v>3.57</v>
+        <v>2.4</v>
       </c>
       <c r="O307">
-        <v>3.67</v>
+        <v>3.44</v>
       </c>
       <c r="P307">
-        <v>1.79</v>
+        <v>2.47</v>
       </c>
       <c r="Q307">
         <v>0</v>

--- a/jogos_2026-11-01.xlsx
+++ b/jogos_2026-11-01.xlsx
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.74</v>
+        <v>2.15</v>
       </c>
       <c r="O9">
-        <v>3.26</v>
+        <v>3.22</v>
       </c>
       <c r="P9">
-        <v>2.3</v>
+        <v>3.02</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1815,10 +1815,10 @@
         <v>0</v>
       </c>
       <c r="AA9">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AB9">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AC9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.15</v>
+        <v>2.74</v>
       </c>
       <c r="O10">
-        <v>3.22</v>
+        <v>3.26</v>
       </c>
       <c r="P10">
-        <v>3.02</v>
+        <v>2.3</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -1978,10 +1978,10 @@
         <v>0</v>
       </c>
       <c r="AA10">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AB10">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AC10">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.3</v>
+        <v>3.9</v>
       </c>
       <c r="O90">
-        <v>5.4</v>
+        <v>3.9</v>
       </c>
       <c r="P90">
-        <v>8.550000000000001</v>
+        <v>1.78</v>
       </c>
       <c r="Q90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>3.9</v>
+        <v>1.3</v>
       </c>
       <c r="O91">
-        <v>3.9</v>
+        <v>5.4</v>
       </c>
       <c r="P91">
-        <v>1.78</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q91">
         <v>0</v>
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Tru-Juice</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G292">
@@ -48036,12 +48036,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Tru-Juice</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G293">

--- a/jogos_2026-11-01.xlsx
+++ b/jogos_2026-11-01.xlsx
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.15</v>
+        <v>2.74</v>
       </c>
       <c r="O9">
-        <v>3.22</v>
+        <v>3.26</v>
       </c>
       <c r="P9">
-        <v>3.02</v>
+        <v>2.3</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1815,10 +1815,10 @@
         <v>0</v>
       </c>
       <c r="AA9">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AB9">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AC9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.74</v>
+        <v>2.15</v>
       </c>
       <c r="O10">
-        <v>3.26</v>
+        <v>3.22</v>
       </c>
       <c r="P10">
-        <v>2.3</v>
+        <v>3.02</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -1978,10 +1978,10 @@
         <v>0</v>
       </c>
       <c r="AA10">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AB10">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AC10">
         <v>0</v>
@@ -40864,12 +40864,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G249">
@@ -40896,13 +40896,13 @@
         </is>
       </c>
       <c r="N249">
-        <v>1.28</v>
+        <v>2.47</v>
       </c>
       <c r="O249">
-        <v>5.35</v>
+        <v>3.24</v>
       </c>
       <c r="P249">
-        <v>9.800000000000001</v>
+        <v>2.76</v>
       </c>
       <c r="Q249">
         <v>0</v>
@@ -41027,12 +41027,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G250">
@@ -41059,13 +41059,13 @@
         </is>
       </c>
       <c r="N250">
-        <v>2.47</v>
+        <v>1.28</v>
       </c>
       <c r="O250">
-        <v>3.24</v>
+        <v>5.35</v>
       </c>
       <c r="P250">
-        <v>2.76</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q250">
         <v>0</v>
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Tru-Juice</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G292">
@@ -48036,12 +48036,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Tru-Juice</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G293">

--- a/jogos_2026-11-01.xlsx
+++ b/jogos_2026-11-01.xlsx
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G114">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="G115">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Birmingham City Women</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,13 +21336,13 @@
         </is>
       </c>
       <c r="N129">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="O129">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="P129">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Q129">
         <v>0</v>
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Crystal Palace Ladies</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,13 +21499,13 @@
         </is>
       </c>
       <c r="N130">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="O130">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="P130">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q130">
         <v>0</v>
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Birmingham City Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Crystal Palace Ladies</t>
         </is>
       </c>
       <c r="G131">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G134">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G136">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G137">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G138">
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Montalegre</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Maria da Fonte</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G175">
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Ponte da Barca</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vinhais</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G176">
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G177">
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Montalegre</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Maria da Fonte</t>
         </is>
       </c>
       <c r="G178">
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Maia Lidador</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="G179">
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Ponte da Barca</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Vinhais</t>
         </is>
       </c>
       <c r="G180">
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Maia Lidador</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G181">

--- a/jogos_2026-11-01.xlsx
+++ b/jogos_2026-11-01.xlsx
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>La Nucía</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mallorca II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>La Nucía</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Mallorca II</t>
         </is>
       </c>
       <c r="G45">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="G95">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G96">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G102">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G103">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>3.07</v>
+        <v>2.7</v>
       </c>
       <c r="O116">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P116">
-        <v>2.29</v>
+        <v>2.55</v>
       </c>
       <c r="Q116">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>2.36</v>
+        <v>3.07</v>
       </c>
       <c r="O117">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P117">
-        <v>2.92</v>
+        <v>2.29</v>
       </c>
       <c r="Q117">
         <v>0</v>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>2.7</v>
+        <v>2.36</v>
       </c>
       <c r="O118">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="P118">
-        <v>2.55</v>
+        <v>2.92</v>
       </c>
       <c r="Q118">
         <v>0</v>
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Crystal Palace Ladies</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,13 +21499,13 @@
         </is>
       </c>
       <c r="N130">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="O130">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="P130">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Q130">
         <v>0</v>
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Crystal Palace Ladies</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,13 +21662,13 @@
         </is>
       </c>
       <c r="N131">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="O131">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="P131">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Fazendense</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G150">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Gd Nazarenos</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Sertanense</t>
         </is>
       </c>
       <c r="G151">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Gd Nazarenos</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Sertanense</t>
+          <t>Fazendense</t>
         </is>
       </c>
       <c r="G152">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Vitória Setúbal</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Portel</t>
         </is>
       </c>
       <c r="G154">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Portel</t>
+          <t>Imortal Albufeira</t>
         </is>
       </c>
       <c r="G155">
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Vitória Setúbal</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Imortal Albufeira</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G156">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Estrela Calheta</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="G161">
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Estrela Calheta</t>
+          <t>Sousense</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="G162">
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Ovarense</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Guarda</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G163">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Castro Daire</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Guarda</t>
         </is>
       </c>
       <c r="G164">
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Sousense</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G165">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Ovarense</t>
+          <t>Castro Daire</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G166">
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Montalegre</t>
+          <t>Maia Lidador</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Maria da Fonte</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="G178">
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Maia Lidador</t>
+          <t>Ponte da Barca</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Vinhais</t>
         </is>
       </c>
       <c r="G179">
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Ponte da Barca</t>
+          <t>Montalegre</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Vinhais</t>
+          <t>Maria da Fonte</t>
         </is>
       </c>
       <c r="G180">
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G228">
@@ -37473,13 +37473,13 @@
         </is>
       </c>
       <c r="N228">
-        <v>2.03</v>
+        <v>1.48</v>
       </c>
       <c r="O228">
-        <v>3.79</v>
+        <v>4.85</v>
       </c>
       <c r="P228">
-        <v>3.14</v>
+        <v>4.99</v>
       </c>
       <c r="Q228">
         <v>0</v>
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G229">
@@ -37636,13 +37636,13 @@
         </is>
       </c>
       <c r="N229">
-        <v>1.48</v>
+        <v>5.39</v>
       </c>
       <c r="O229">
-        <v>4.85</v>
+        <v>5.23</v>
       </c>
       <c r="P229">
-        <v>4.99</v>
+        <v>1.42</v>
       </c>
       <c r="Q229">
         <v>0</v>
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G230">
@@ -37799,13 +37799,13 @@
         </is>
       </c>
       <c r="N230">
-        <v>5.39</v>
+        <v>1.46</v>
       </c>
       <c r="O230">
-        <v>5.23</v>
+        <v>4.89</v>
       </c>
       <c r="P230">
-        <v>1.42</v>
+        <v>5.2</v>
       </c>
       <c r="Q230">
         <v>0</v>
@@ -37930,12 +37930,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G231">
@@ -37962,13 +37962,13 @@
         </is>
       </c>
       <c r="N231">
-        <v>1.46</v>
+        <v>1.22</v>
       </c>
       <c r="O231">
-        <v>4.89</v>
+        <v>6.75</v>
       </c>
       <c r="P231">
-        <v>5.2</v>
+        <v>8.56</v>
       </c>
       <c r="Q231">
         <v>0</v>
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G232">
@@ -38125,13 +38125,13 @@
         </is>
       </c>
       <c r="N232">
-        <v>1.22</v>
+        <v>2.03</v>
       </c>
       <c r="O232">
-        <v>6.75</v>
+        <v>3.79</v>
       </c>
       <c r="P232">
-        <v>8.56</v>
+        <v>3.14</v>
       </c>
       <c r="Q232">
         <v>0</v>
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Tru-Juice</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G292">
@@ -48036,12 +48036,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Tru-Juice</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G293">

--- a/jogos_2026-11-01.xlsx
+++ b/jogos_2026-11-01.xlsx
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>4.37</v>
+        <v>1.75</v>
       </c>
       <c r="O86">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="P86">
-        <v>1.86</v>
+        <v>5.17</v>
       </c>
       <c r="Q86">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.75</v>
+        <v>4.37</v>
       </c>
       <c r="O87">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="P87">
-        <v>5.17</v>
+        <v>1.86</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="G114">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G115">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Castro Daire</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Guarda</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G164">
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Guarda</t>
         </is>
       </c>
       <c r="G165">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Castro Daire</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G166">
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G201">
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G202">
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="G203">
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Manresa</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G208">
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Manresa</t>
         </is>
       </c>
       <c r="G209">
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G211">
@@ -34702,13 +34702,13 @@
         </is>
       </c>
       <c r="N211">
-        <v>2.46</v>
+        <v>1.97</v>
       </c>
       <c r="O211">
-        <v>3.78</v>
+        <v>3.59</v>
       </c>
       <c r="P211">
-        <v>2.66</v>
+        <v>3.82</v>
       </c>
       <c r="Q211">
         <v>0</v>
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G212">
@@ -34865,13 +34865,13 @@
         </is>
       </c>
       <c r="N212">
-        <v>1.97</v>
+        <v>2.46</v>
       </c>
       <c r="O212">
-        <v>3.59</v>
+        <v>3.78</v>
       </c>
       <c r="P212">
-        <v>3.82</v>
+        <v>2.66</v>
       </c>
       <c r="Q212">
         <v>0</v>
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>SD Compostela</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G222">
@@ -36626,12 +36626,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>SD Compostela</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G223">
@@ -36789,12 +36789,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G224">
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Tru-Juice</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G292">
@@ -48036,12 +48036,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Tru-Juice</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G293">

--- a/jogos_2026-11-01.xlsx
+++ b/jogos_2026-11-01.xlsx
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Guarda</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G165">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Guarda</t>
         </is>
       </c>
       <c r="G166">
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Maia Lidador</t>
+          <t>Ponte da Barca</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Vinhais</t>
         </is>
       </c>
       <c r="G178">
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Ponte da Barca</t>
+          <t>Montalegre</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Vinhais</t>
+          <t>Maria da Fonte</t>
         </is>
       </c>
       <c r="G179">
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Montalegre</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Maria da Fonte</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G180">
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Maia Lidador</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="G181">
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>SD Compostela</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G222">
@@ -36626,12 +36626,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G223">
@@ -36789,12 +36789,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>SD Compostela</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G224">

--- a/jogos_2026-11-01.xlsx
+++ b/jogos_2026-11-01.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.24</v>
+        <v>2.58</v>
       </c>
       <c r="O6">
-        <v>5.45</v>
+        <v>3.16</v>
       </c>
       <c r="P6">
-        <v>8.6</v>
+        <v>2.41</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1326,10 +1326,10 @@
         <v>0</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.58</v>
+        <v>1.24</v>
       </c>
       <c r="O7">
-        <v>3.16</v>
+        <v>5.45</v>
       </c>
       <c r="P7">
-        <v>2.41</v>
+        <v>8.6</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1489,10 +1489,10 @@
         <v>0</v>
       </c>
       <c r="AA7">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB7">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC7">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9639,10 +9639,10 @@
         <v>0</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC57">
         <v>0</v>
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O77">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P77">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O109">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="P109">
-        <v>0</v>
+        <v>6.32</v>
       </c>
       <c r="Q109">
         <v>0</v>
@@ -18115,10 +18115,10 @@
         <v>0</v>
       </c>
       <c r="AA109">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB109">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC109">
         <v>0</v>
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O110">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P110">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="Q110">
         <v>0</v>
@@ -18278,10 +18278,10 @@
         <v>0</v>
       </c>
       <c r="AA110">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB110">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC110">
         <v>0</v>
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O114">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P114">
-        <v>0</v>
+        <v>5.11</v>
       </c>
       <c r="Q114">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>2.76</v>
+        <v>5.21</v>
       </c>
       <c r="O117">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="P117">
-        <v>2.37</v>
+        <v>1.57</v>
       </c>
       <c r="Q117">
         <v>0</v>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>5.21</v>
+        <v>2.76</v>
       </c>
       <c r="O118">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="P118">
-        <v>1.57</v>
+        <v>2.37</v>
       </c>
       <c r="Q118">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,13 +20032,13 @@
         </is>
       </c>
       <c r="N121">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="O121">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P121">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q121">
         <v>0</v>
@@ -20071,10 +20071,10 @@
         <v>0</v>
       </c>
       <c r="AA121">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB121">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC121">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,13 +20195,13 @@
         </is>
       </c>
       <c r="N122">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O122">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P122">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="Q122">
         <v>0</v>
@@ -20234,10 +20234,10 @@
         <v>0</v>
       </c>
       <c r="AA122">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB122">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC122">
         <v>0</v>
@@ -20847,13 +20847,13 @@
         </is>
       </c>
       <c r="N126">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O126">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P126">
-        <v>0</v>
+        <v>7.23</v>
       </c>
       <c r="Q126">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G144">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G145">
@@ -24116,55 +24116,55 @@
         <v>5.75</v>
       </c>
       <c r="Q146">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="R146">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S146">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T146">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U146">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="V146">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W146">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X146">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y146">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z146">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA146">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB146">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC146">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD146">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE146">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF146">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG146">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK146">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>SD Compostela</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G233">
@@ -38419,12 +38419,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>SD Compostela</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G234">
@@ -40244,13 +40244,13 @@
         </is>
       </c>
       <c r="N245">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O245">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P245">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="Q245">
         <v>0</v>
@@ -40407,13 +40407,13 @@
         </is>
       </c>
       <c r="N246">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O246">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P246">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="Q246">
         <v>0</v>
@@ -40570,13 +40570,13 @@
         </is>
       </c>
       <c r="N247">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O247">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P247">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="Q247">
         <v>0</v>
@@ -40609,10 +40609,10 @@
         <v>0</v>
       </c>
       <c r="AA247">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB247">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC247">
         <v>0</v>
@@ -41059,13 +41059,13 @@
         </is>
       </c>
       <c r="N250">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O250">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P250">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="Q250">
         <v>0</v>
@@ -41548,13 +41548,13 @@
         </is>
       </c>
       <c r="N253">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O253">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P253">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q253">
         <v>0</v>
@@ -41587,10 +41587,10 @@
         <v>0</v>
       </c>
       <c r="AA253">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB253">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC253">
         <v>0</v>
@@ -41711,13 +41711,13 @@
         </is>
       </c>
       <c r="N254">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O254">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P254">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q254">
         <v>0</v>

--- a/jogos_2026-11-01.xlsx
+++ b/jogos_2026-11-01.xlsx
@@ -644,55 +644,55 @@
         <v>5.5</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -807,55 +807,55 @@
         <v>2.2</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -970,55 +970,55 @@
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1133,55 +1133,55 @@
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.58</v>
+        <v>1.24</v>
       </c>
       <c r="O6">
-        <v>3.16</v>
+        <v>5.45</v>
       </c>
       <c r="P6">
-        <v>2.41</v>
+        <v>8.6</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA6">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="AB6">
-        <v>1.91</v>
+        <v>2.56</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.24</v>
+        <v>2.58</v>
       </c>
       <c r="O7">
-        <v>5.45</v>
+        <v>3.16</v>
       </c>
       <c r="P7">
-        <v>8.6</v>
+        <v>2.41</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1622,34 +1622,34 @@
         <v>2.44</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA8">
         <v>1.97</v>
@@ -1658,19 +1658,19 @@
         <v>1.83</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1785,34 +1785,34 @@
         <v>3.28</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA9">
         <v>2.02</v>
@@ -1821,19 +1821,19 @@
         <v>1.79</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1948,55 +1948,55 @@
         <v>4.31</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G11">
@@ -2111,55 +2111,55 @@
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G12">
@@ -2274,55 +2274,55 @@
         <v>0</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2437,34 +2437,34 @@
         <v>2.3</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="AA13">
         <v>1.86</v>
@@ -2473,19 +2473,19 @@
         <v>1.91</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2600,34 +2600,34 @@
         <v>3.02</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AA14">
         <v>1.95</v>
@@ -2636,19 +2636,19 @@
         <v>1.81</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2763,55 +2763,55 @@
         <v>2.63</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3578,55 +3578,55 @@
         <v>1.88</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -4230,55 +4230,55 @@
         <v>0</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -5697,55 +5697,55 @@
         <v>3.22</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>12.1</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -8631,55 +8631,55 @@
         <v>2.9</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8824,10 +8824,10 @@
         <v>0</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC52">
         <v>0</v>
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T63">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF63">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK63">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -11402,55 +11402,55 @@
         <v>26</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="T68">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="W68">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X68">
         <v>0</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Z68">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD68">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AE68">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF68">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK68">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O78">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P78">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q78">
         <v>0</v>
@@ -13195,55 +13195,55 @@
         <v>2.94</v>
       </c>
       <c r="Q79">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R79">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S79">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T79">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U79">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="V79">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W79">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X79">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y79">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z79">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AA79">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC79">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="AD79">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF79">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG79">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AK79">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13358,55 +13358,55 @@
         <v>2.8</v>
       </c>
       <c r="Q80">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R80">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S80">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T80">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U80">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V80">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W80">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X80">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y80">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z80">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA80">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB80">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC80">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD80">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE80">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF80">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG80">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK80">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13521,55 +13521,55 @@
         <v>0</v>
       </c>
       <c r="Q81">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S81">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T81">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U81">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="V81">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W81">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X81">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y81">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z81">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA81">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB81">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC81">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD81">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG81">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK81">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13684,40 +13684,40 @@
         <v>2.55</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S82">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T82">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U82">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V82">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W82">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X82">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y82">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z82">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA82">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB82">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC82">
         <v>2.05</v>
@@ -13726,13 +13726,13 @@
         <v>1.66</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG82">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AK82">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13847,40 +13847,40 @@
         <v>3.6</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S83">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T83">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="U83">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V83">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W83">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X83">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y83">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z83">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA83">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB83">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AC83">
         <v>2</v>
@@ -13889,13 +13889,13 @@
         <v>1.7</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG83">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK83">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14010,34 +14010,34 @@
         <v>3</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S84">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T84">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U84">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V84">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W84">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X84">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y84">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z84">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA84">
         <v>1.57</v>
@@ -14046,19 +14046,19 @@
         <v>2.25</v>
       </c>
       <c r="AC84">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD84">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE84">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF84">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG84">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK84">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O85">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="Q85">
         <v>0</v>
@@ -14336,34 +14336,34 @@
         <v>3.65</v>
       </c>
       <c r="Q86">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S86">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T86">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U86">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V86">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W86">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y86">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z86">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA86">
         <v>1.53</v>
@@ -14372,19 +14372,19 @@
         <v>2.3</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD86">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG86">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK86">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O88">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q88">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R88">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S88">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T88">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U88">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V88">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W88">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y88">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z88">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="AA88">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB88">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AC88">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD88">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE88">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF88">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG88">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK88">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O89">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="Q89">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R89">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S89">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T89">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U89">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V89">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W89">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y89">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z89">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA89">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB89">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC89">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD89">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE89">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF89">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG89">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK89">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -15151,55 +15151,55 @@
         <v>9</v>
       </c>
       <c r="Q91">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R91">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="S91">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="T91">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U91">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V91">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="W91">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y91">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Z91">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AA91">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB91">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AC91">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AD91">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AE91">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AF91">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG91">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK91">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15314,55 +15314,55 @@
         <v>3.1</v>
       </c>
       <c r="Q92">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R92">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S92">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T92">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U92">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V92">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W92">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X92">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y92">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z92">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AA92">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB92">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC92">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD92">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE92">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF92">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG92">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK92">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15477,55 +15477,55 @@
         <v>5.17</v>
       </c>
       <c r="Q93">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="R93">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S93">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T93">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U93">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V93">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W93">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X93">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y93">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z93">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA93">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB93">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC93">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AD93">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE93">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF93">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG93">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK93">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15640,55 +15640,55 @@
         <v>1.86</v>
       </c>
       <c r="Q94">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="R94">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S94">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T94">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U94">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="V94">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W94">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y94">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z94">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA94">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB94">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC94">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="AD94">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE94">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF94">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG94">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AK94">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15803,34 +15803,34 @@
         <v>3.16</v>
       </c>
       <c r="Q95">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R95">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S95">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T95">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U95">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V95">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W95">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y95">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z95">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA95">
         <v>1.82</v>
@@ -15839,19 +15839,19 @@
         <v>1.87</v>
       </c>
       <c r="AC95">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD95">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE95">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF95">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG95">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK95">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O96">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="P96">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q96">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="R96">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="S96">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T96">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U96">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V96">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W96">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X96">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y96">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z96">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AA96">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB96">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC96">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD96">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE96">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF96">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG96">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK96">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16618,40 +16618,40 @@
         <v>1.32</v>
       </c>
       <c r="Q100">
-        <v>0</v>
+        <v>6.44</v>
       </c>
       <c r="R100">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="S100">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T100">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="U100">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V100">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W100">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X100">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y100">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z100">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA100">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB100">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AC100">
         <v>1.9</v>
@@ -16660,13 +16660,13 @@
         <v>1.78</v>
       </c>
       <c r="AE100">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF100">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG100">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK100">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16781,55 +16781,55 @@
         <v>1.78</v>
       </c>
       <c r="Q101">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R101">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S101">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T101">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="U101">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V101">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W101">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X101">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y101">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z101">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA101">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB101">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC101">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD101">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE101">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF101">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG101">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK101">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16944,55 +16944,55 @@
         <v>0</v>
       </c>
       <c r="Q102">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R102">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S102">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T102">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U102">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="V102">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W102">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X102">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y102">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z102">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA102">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB102">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC102">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD102">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE102">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF102">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG102">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK102">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17107,55 +17107,55 @@
         <v>0</v>
       </c>
       <c r="Q103">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="R103">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S103">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T103">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U103">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V103">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W103">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X103">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y103">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z103">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA103">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB103">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC103">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD103">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE103">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF103">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG103">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK103">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17270,55 +17270,55 @@
         <v>3.07</v>
       </c>
       <c r="Q104">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R104">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S104">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T104">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U104">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V104">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W104">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X104">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y104">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z104">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA104">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB104">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC104">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD104">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE104">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF104">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG104">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK104">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17433,55 +17433,55 @@
         <v>6.12</v>
       </c>
       <c r="Q105">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R105">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S105">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T105">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U105">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V105">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W105">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X105">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y105">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z105">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA105">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB105">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC105">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD105">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE105">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF105">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG105">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK105">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17596,55 +17596,55 @@
         <v>3.69</v>
       </c>
       <c r="Q106">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R106">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S106">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T106">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U106">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V106">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W106">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X106">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y106">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z106">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA106">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB106">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AC106">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD106">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE106">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF106">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG106">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK106">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -18930,10 +18930,10 @@
         <v>0</v>
       </c>
       <c r="AA114">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB114">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC114">
         <v>0</v>
@@ -19063,40 +19063,40 @@
         <v>12.2</v>
       </c>
       <c r="Q115">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="R115">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S115">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="T115">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="U115">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V115">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="W115">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y115">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Z115">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AA115">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB115">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AC115">
         <v>1.83</v>
@@ -19105,13 +19105,13 @@
         <v>1.98</v>
       </c>
       <c r="AE115">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AF115">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG115">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK115">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19226,55 +19226,55 @@
         <v>1.58</v>
       </c>
       <c r="Q116">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R116">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S116">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T116">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="U116">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="V116">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W116">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X116">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y116">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z116">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA116">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB116">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC116">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD116">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE116">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF116">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG116">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK116">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19389,55 +19389,55 @@
         <v>1.57</v>
       </c>
       <c r="Q117">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R117">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S117">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T117">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U117">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V117">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W117">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X117">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y117">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z117">
-        <v>0</v>
+        <v>5.54</v>
       </c>
       <c r="AA117">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB117">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AC117">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD117">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE117">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF117">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG117">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AK117">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19552,55 +19552,55 @@
         <v>2.37</v>
       </c>
       <c r="Q118">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R118">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S118">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T118">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U118">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V118">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W118">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X118">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y118">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z118">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA118">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB118">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AC118">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AD118">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE118">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF118">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG118">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AK118">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19715,55 +19715,55 @@
         <v>3.56</v>
       </c>
       <c r="Q119">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R119">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S119">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T119">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U119">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V119">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="W119">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X119">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y119">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Z119">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AA119">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB119">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AC119">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD119">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AE119">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AF119">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AG119">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK119">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O120">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P120">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q120">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R120">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S120">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T120">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U120">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V120">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W120">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X120">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y120">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z120">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="AA120">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB120">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC120">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AD120">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE120">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF120">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG120">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK120">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
-        <v>2.7</v>
+        <v>3.07</v>
       </c>
       <c r="O123">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P123">
-        <v>2.55</v>
+        <v>2.29</v>
       </c>
       <c r="Q123">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R123">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S123">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T123">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U123">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="V123">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W123">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X123">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y123">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z123">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA123">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB123">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC123">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD123">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE123">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF123">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG123">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK123">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,64 +20521,64 @@
         </is>
       </c>
       <c r="N124">
-        <v>3.07</v>
+        <v>2.36</v>
       </c>
       <c r="O124">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P124">
-        <v>2.29</v>
+        <v>2.92</v>
       </c>
       <c r="Q124">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R124">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S124">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T124">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U124">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V124">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W124">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X124">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y124">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z124">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA124">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB124">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC124">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD124">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE124">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF124">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG124">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK124">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,64 +20684,64 @@
         </is>
       </c>
       <c r="N125">
-        <v>2.36</v>
+        <v>2.7</v>
       </c>
       <c r="O125">
+        <v>3.15</v>
+      </c>
+      <c r="P125">
+        <v>2.55</v>
+      </c>
+      <c r="Q125">
         <v>3.25</v>
       </c>
-      <c r="P125">
-        <v>2.92</v>
-      </c>
-      <c r="Q125">
-        <v>0</v>
-      </c>
       <c r="R125">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S125">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T125">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U125">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V125">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W125">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X125">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y125">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z125">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA125">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB125">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC125">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD125">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE125">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF125">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG125">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK125">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -21019,34 +21019,34 @@
         <v>4.16</v>
       </c>
       <c r="Q127">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R127">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S127">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T127">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U127">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V127">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W127">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X127">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y127">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z127">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA127">
         <v>1.58</v>
@@ -21055,19 +21055,19 @@
         <v>2.25</v>
       </c>
       <c r="AC127">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD127">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE127">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF127">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG127">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK127">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21182,55 +21182,55 @@
         <v>3.9</v>
       </c>
       <c r="Q128">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="R128">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S128">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T128">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U128">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V128">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W128">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X128">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y128">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z128">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA128">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AB128">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC128">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD128">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE128">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF128">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG128">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK128">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21345,55 +21345,55 @@
         <v>1.75</v>
       </c>
       <c r="Q129">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R129">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S129">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T129">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U129">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="V129">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W129">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X129">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y129">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z129">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA129">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB129">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC129">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD129">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE129">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF129">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG129">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK129">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21508,55 +21508,55 @@
         <v>3.85</v>
       </c>
       <c r="Q130">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R130">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S130">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T130">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U130">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V130">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W130">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X130">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y130">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z130">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA130">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB130">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC130">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AD130">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE130">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF130">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG130">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK130">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21662,13 +21662,13 @@
         </is>
       </c>
       <c r="N131">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O131">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P131">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O132">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P132">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q132">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R132">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S132">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T132">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U132">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V132">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W132">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X132">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y132">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z132">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA132">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB132">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AC132">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AD132">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE132">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF132">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG132">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK132">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -22151,13 +22151,13 @@
         </is>
       </c>
       <c r="N134">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O134">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P134">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="Q134">
         <v>0</v>
@@ -22486,55 +22486,55 @@
         <v>0</v>
       </c>
       <c r="Q136">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R136">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S136">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T136">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U136">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V136">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W136">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X136">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y136">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z136">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA136">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AB136">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AC136">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD136">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE136">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF136">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG136">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK136">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22649,55 +22649,55 @@
         <v>0</v>
       </c>
       <c r="Q137">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="R137">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S137">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T137">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U137">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V137">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="W137">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X137">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y137">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z137">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AA137">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AB137">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AC137">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD137">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE137">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AF137">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG137">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK137">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22812,55 +22812,55 @@
         <v>1.58</v>
       </c>
       <c r="Q138">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R138">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S138">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T138">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U138">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V138">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W138">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X138">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y138">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z138">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA138">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB138">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC138">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD138">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE138">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF138">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG138">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK138">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -22975,55 +22975,55 @@
         <v>4.69</v>
       </c>
       <c r="Q139">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R139">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S139">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T139">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U139">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V139">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W139">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X139">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y139">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z139">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA139">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB139">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC139">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD139">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE139">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF139">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG139">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK139">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G144">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G145">
@@ -24279,34 +24279,34 @@
         <v>7.15</v>
       </c>
       <c r="Q147">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R147">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S147">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T147">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U147">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V147">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W147">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X147">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y147">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z147">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AA147">
         <v>1.88</v>
@@ -24315,19 +24315,19 @@
         <v>1.98</v>
       </c>
       <c r="AC147">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AD147">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE147">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF147">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG147">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK147">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -24605,55 +24605,55 @@
         <v>4.51</v>
       </c>
       <c r="Q149">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R149">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S149">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T149">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="U149">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="V149">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W149">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X149">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y149">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z149">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AA149">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB149">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC149">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD149">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE149">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF149">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG149">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH149" t="inlineStr">
         <is>
@@ -24666,10 +24666,10 @@
         </is>
       </c>
       <c r="AJ149">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK149">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AL149">
         <v>0</v>
@@ -25094,34 +25094,34 @@
         <v>2.72</v>
       </c>
       <c r="Q152">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R152">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S152">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T152">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U152">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V152">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W152">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X152">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y152">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z152">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA152">
         <v>1.6</v>
@@ -25130,19 +25130,19 @@
         <v>2.2</v>
       </c>
       <c r="AC152">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AD152">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE152">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF152">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG152">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK152">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -27204,64 +27204,64 @@
         </is>
       </c>
       <c r="N165">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O165">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P165">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q165">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R165">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S165">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T165">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U165">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V165">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W165">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X165">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y165">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z165">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA165">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB165">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC165">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD165">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE165">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF165">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG165">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH165" t="inlineStr">
         <is>
@@ -27274,10 +27274,10 @@
         </is>
       </c>
       <c r="AJ165">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK165">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL165">
         <v>0</v>
@@ -27376,34 +27376,34 @@
         <v>3.4</v>
       </c>
       <c r="Q166">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R166">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S166">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T166">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U166">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V166">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W166">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X166">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y166">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z166">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA166">
         <v>1.95</v>
@@ -27412,19 +27412,19 @@
         <v>1.85</v>
       </c>
       <c r="AC166">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD166">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE166">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF166">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG166">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH166" t="inlineStr">
         <is>
@@ -27437,10 +27437,10 @@
         </is>
       </c>
       <c r="AJ166">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK166">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL166">
         <v>0</v>
@@ -28680,40 +28680,40 @@
         <v>5.05</v>
       </c>
       <c r="Q174">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="R174">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="S174">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T174">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U174">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="V174">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="W174">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X174">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y174">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z174">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="AA174">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB174">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AC174">
         <v>1.8</v>
@@ -28722,13 +28722,13 @@
         <v>1.96</v>
       </c>
       <c r="AE174">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF174">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AG174">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AH174" t="inlineStr">
         <is>
@@ -28741,10 +28741,10 @@
         </is>
       </c>
       <c r="AJ174">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK174">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL174">
         <v>0</v>
@@ -29658,55 +29658,55 @@
         <v>2.9</v>
       </c>
       <c r="Q180">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R180">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S180">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T180">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U180">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V180">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W180">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X180">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y180">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z180">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AA180">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AB180">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AC180">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD180">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE180">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF180">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG180">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH180" t="inlineStr">
         <is>
@@ -29719,10 +29719,10 @@
         </is>
       </c>
       <c r="AJ180">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK180">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL180">
         <v>0</v>
@@ -31451,34 +31451,34 @@
         <v>5.02</v>
       </c>
       <c r="Q191">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R191">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S191">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T191">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U191">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V191">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W191">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X191">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y191">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z191">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA191">
         <v>1.57</v>
@@ -31487,19 +31487,19 @@
         <v>2.25</v>
       </c>
       <c r="AC191">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD191">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE191">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF191">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG191">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH191" t="inlineStr">
         <is>
@@ -31512,10 +31512,10 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK191">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -31768,64 +31768,64 @@
         </is>
       </c>
       <c r="N193">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O193">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="P193">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Q193">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="R193">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S193">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T193">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U193">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V193">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="W193">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X193">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y193">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z193">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA193">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AB193">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AC193">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD193">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AE193">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF193">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG193">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31838,10 +31838,10 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK193">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -32429,55 +32429,55 @@
         <v>2.45</v>
       </c>
       <c r="Q197">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R197">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S197">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T197">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U197">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V197">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W197">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X197">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y197">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z197">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA197">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB197">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AC197">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD197">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE197">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF197">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG197">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32490,10 +32490,10 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK197">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -32592,55 +32592,55 @@
         <v>5</v>
       </c>
       <c r="Q198">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="R198">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="S198">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T198">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U198">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V198">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="W198">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X198">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y198">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z198">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA198">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB198">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC198">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD198">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE198">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF198">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG198">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH198" t="inlineStr">
         <is>
@@ -32653,10 +32653,10 @@
         </is>
       </c>
       <c r="AJ198">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK198">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -35037,55 +35037,55 @@
         <v>4.96</v>
       </c>
       <c r="Q213">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="R213">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S213">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T213">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U213">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V213">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W213">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X213">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y213">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z213">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA213">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB213">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AC213">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD213">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE213">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF213">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG213">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AH213" t="inlineStr">
         <is>
@@ -35098,10 +35098,10 @@
         </is>
       </c>
       <c r="AJ213">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK213">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AL213">
         <v>0</v>
@@ -36667,34 +36667,34 @@
         <v>4.26</v>
       </c>
       <c r="Q223">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R223">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S223">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T223">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U223">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V223">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W223">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X223">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y223">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z223">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="AA223">
         <v>1.88</v>
@@ -36703,19 +36703,19 @@
         <v>1.87</v>
       </c>
       <c r="AC223">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AD223">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE223">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF223">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG223">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH223" t="inlineStr">
         <is>
@@ -36728,10 +36728,10 @@
         </is>
       </c>
       <c r="AJ223">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK223">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL223">
         <v>0</v>
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G227">
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Calvo Sotelo</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G228">
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Calvo Sotelo</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G229">
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G232">
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>SD Compostela</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G233">
@@ -38419,12 +38419,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>SD Compostela</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G234">
@@ -38949,55 +38949,55 @@
         <v>1.76</v>
       </c>
       <c r="Q237">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R237">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S237">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T237">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U237">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V237">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W237">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X237">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y237">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z237">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA237">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB237">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC237">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD237">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE237">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF237">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG237">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH237" t="inlineStr">
         <is>
@@ -39010,10 +39010,10 @@
         </is>
       </c>
       <c r="AJ237">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK237">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL237">
         <v>0</v>
@@ -39071,12 +39071,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G238">
@@ -39103,64 +39103,64 @@
         </is>
       </c>
       <c r="N238">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="O238">
-        <v>4.85</v>
+        <v>4.89</v>
       </c>
       <c r="P238">
-        <v>4.99</v>
+        <v>5.2</v>
       </c>
       <c r="Q238">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R238">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S238">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T238">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="U238">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V238">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W238">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X238">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y238">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z238">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AA238">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AB238">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AC238">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD238">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE238">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF238">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG238">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH238" t="inlineStr">
         <is>
@@ -39173,10 +39173,10 @@
         </is>
       </c>
       <c r="AJ238">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK238">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL238">
         <v>0</v>
@@ -39275,55 +39275,55 @@
         <v>1.42</v>
       </c>
       <c r="Q239">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R239">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S239">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="T239">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="U239">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V239">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="W239">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X239">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y239">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Z239">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA239">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AB239">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AC239">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD239">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AE239">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AF239">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AG239">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH239" t="inlineStr">
         <is>
@@ -39336,10 +39336,10 @@
         </is>
       </c>
       <c r="AJ239">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK239">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AL239">
         <v>0</v>
@@ -39397,12 +39397,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G240">
@@ -39429,64 +39429,64 @@
         </is>
       </c>
       <c r="N240">
-        <v>1.46</v>
+        <v>1.22</v>
       </c>
       <c r="O240">
-        <v>4.89</v>
+        <v>6.75</v>
       </c>
       <c r="P240">
-        <v>5.2</v>
+        <v>8.56</v>
       </c>
       <c r="Q240">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="R240">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="S240">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="T240">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="U240">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V240">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="W240">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X240">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y240">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Z240">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AA240">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB240">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AC240">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD240">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AE240">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF240">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG240">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH240" t="inlineStr">
         <is>
@@ -39499,10 +39499,10 @@
         </is>
       </c>
       <c r="AJ240">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK240">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AL240">
         <v>0</v>
@@ -39560,12 +39560,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G241">
@@ -39592,64 +39592,64 @@
         </is>
       </c>
       <c r="N241">
+        <v>1.48</v>
+      </c>
+      <c r="O241">
+        <v>4.85</v>
+      </c>
+      <c r="P241">
+        <v>4.99</v>
+      </c>
+      <c r="Q241">
+        <v>2.13</v>
+      </c>
+      <c r="R241">
+        <v>2.7</v>
+      </c>
+      <c r="S241">
+        <v>1.17</v>
+      </c>
+      <c r="T241">
+        <v>5.1</v>
+      </c>
+      <c r="U241">
+        <v>1.91</v>
+      </c>
+      <c r="V241">
+        <v>1.86</v>
+      </c>
+      <c r="W241">
         <v>1.22</v>
       </c>
-      <c r="O241">
-        <v>6.75</v>
-      </c>
-      <c r="P241">
-        <v>8.56</v>
-      </c>
-      <c r="Q241">
-        <v>0</v>
-      </c>
-      <c r="R241">
-        <v>0</v>
-      </c>
-      <c r="S241">
-        <v>0</v>
-      </c>
-      <c r="T241">
-        <v>0</v>
-      </c>
-      <c r="U241">
-        <v>0</v>
-      </c>
-      <c r="V241">
-        <v>0</v>
-      </c>
-      <c r="W241">
-        <v>0</v>
-      </c>
       <c r="X241">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y241">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z241">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AA241">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AB241">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AC241">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD241">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE241">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF241">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AG241">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH241" t="inlineStr">
         <is>
@@ -39662,10 +39662,10 @@
         </is>
       </c>
       <c r="AJ241">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK241">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL241">
         <v>0</v>
@@ -39764,55 +39764,55 @@
         <v>3.14</v>
       </c>
       <c r="Q242">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="R242">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="S242">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T242">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U242">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V242">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W242">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X242">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y242">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z242">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA242">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB242">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC242">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD242">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE242">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF242">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG242">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AH242" t="inlineStr">
         <is>
@@ -39825,10 +39825,10 @@
         </is>
       </c>
       <c r="AJ242">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK242">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL242">
         <v>0</v>
@@ -40212,12 +40212,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="G245">
@@ -40244,49 +40244,49 @@
         </is>
       </c>
       <c r="N245">
+        <v>1.71</v>
+      </c>
+      <c r="O245">
+        <v>3.5</v>
+      </c>
+      <c r="P245">
+        <v>4.21</v>
+      </c>
+      <c r="Q245">
+        <v>0</v>
+      </c>
+      <c r="R245">
+        <v>0</v>
+      </c>
+      <c r="S245">
+        <v>0</v>
+      </c>
+      <c r="T245">
+        <v>0</v>
+      </c>
+      <c r="U245">
+        <v>0</v>
+      </c>
+      <c r="V245">
+        <v>0</v>
+      </c>
+      <c r="W245">
+        <v>0</v>
+      </c>
+      <c r="X245">
+        <v>0</v>
+      </c>
+      <c r="Y245">
+        <v>0</v>
+      </c>
+      <c r="Z245">
+        <v>0</v>
+      </c>
+      <c r="AA245">
+        <v>1.85</v>
+      </c>
+      <c r="AB245">
         <v>1.95</v>
-      </c>
-      <c r="O245">
-        <v>3.34</v>
-      </c>
-      <c r="P245">
-        <v>3.37</v>
-      </c>
-      <c r="Q245">
-        <v>0</v>
-      </c>
-      <c r="R245">
-        <v>0</v>
-      </c>
-      <c r="S245">
-        <v>0</v>
-      </c>
-      <c r="T245">
-        <v>0</v>
-      </c>
-      <c r="U245">
-        <v>0</v>
-      </c>
-      <c r="V245">
-        <v>0</v>
-      </c>
-      <c r="W245">
-        <v>0</v>
-      </c>
-      <c r="X245">
-        <v>0</v>
-      </c>
-      <c r="Y245">
-        <v>0</v>
-      </c>
-      <c r="Z245">
-        <v>0</v>
-      </c>
-      <c r="AA245">
-        <v>0</v>
-      </c>
-      <c r="AB245">
-        <v>0</v>
       </c>
       <c r="AC245">
         <v>0</v>
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G246">
@@ -40407,13 +40407,13 @@
         </is>
       </c>
       <c r="N246">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="O246">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="P246">
-        <v>4.63</v>
+        <v>3.37</v>
       </c>
       <c r="Q246">
         <v>0</v>
@@ -40538,12 +40538,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G247">
@@ -40570,13 +40570,13 @@
         </is>
       </c>
       <c r="N247">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="O247">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="P247">
-        <v>4.21</v>
+        <v>4.63</v>
       </c>
       <c r="Q247">
         <v>0</v>
@@ -40609,10 +40609,10 @@
         <v>0</v>
       </c>
       <c r="AA247">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB247">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC247">
         <v>0</v>
@@ -42494,12 +42494,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G259">
@@ -42526,13 +42526,13 @@
         </is>
       </c>
       <c r="N259">
-        <v>2.47</v>
+        <v>1.28</v>
       </c>
       <c r="O259">
-        <v>3.24</v>
+        <v>5.35</v>
       </c>
       <c r="P259">
-        <v>2.76</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q259">
         <v>0</v>
@@ -42657,12 +42657,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G260">
@@ -42689,13 +42689,13 @@
         </is>
       </c>
       <c r="N260">
-        <v>1.28</v>
+        <v>2.47</v>
       </c>
       <c r="O260">
-        <v>5.35</v>
+        <v>3.24</v>
       </c>
       <c r="P260">
-        <v>9.800000000000001</v>
+        <v>2.76</v>
       </c>
       <c r="Q260">
         <v>0</v>
@@ -49503,12 +49503,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Tru-Juice</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G302">
@@ -49666,12 +49666,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G303">
@@ -49829,12 +49829,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Tru-Juice</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G304">

--- a/jogos_2026-11-01.xlsx
+++ b/jogos_2026-11-01.xlsx
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.74</v>
+        <v>12.1</v>
       </c>
       <c r="O39">
-        <v>3.75</v>
+        <v>6.6</v>
       </c>
       <c r="P39">
-        <v>3.95</v>
+        <v>1.17</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>12.1</v>
+        <v>1.65</v>
       </c>
       <c r="O40">
-        <v>6.6</v>
+        <v>3.8</v>
       </c>
       <c r="P40">
-        <v>1.17</v>
+        <v>4.53</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="O41">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P41">
-        <v>4.53</v>
+        <v>3.95</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>La Nucía</t>
+          <t>Peña Deportiva</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G48">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Peña Deportiva</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Mallorca II</t>
         </is>
       </c>
       <c r="G49">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>La Nucía</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mallorca II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G50">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G60">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G61">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="O75">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P75">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -12573,10 +12573,10 @@
         <v>0</v>
       </c>
       <c r="AA75">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB75">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Nagykanizsai TE</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G76">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Nagykanizsai TE</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="O77">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P77">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,13 +20358,13 @@
         </is>
       </c>
       <c r="N123">
-        <v>3.33</v>
+        <v>1.85</v>
       </c>
       <c r="O123">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
       <c r="P123">
-        <v>2.02</v>
+        <v>3.83</v>
       </c>
       <c r="Q123">
         <v>0</v>
@@ -20397,10 +20397,10 @@
         <v>0</v>
       </c>
       <c r="AA123">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AB123">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC123">
         <v>0</v>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,13 +20521,13 @@
         </is>
       </c>
       <c r="N124">
-        <v>1.85</v>
+        <v>3.33</v>
       </c>
       <c r="O124">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="P124">
-        <v>3.83</v>
+        <v>2.02</v>
       </c>
       <c r="Q124">
         <v>0</v>
@@ -20560,10 +20560,10 @@
         <v>0</v>
       </c>
       <c r="AA124">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AB124">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC124">
         <v>0</v>
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Estrela Calheta</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Guarda</t>
         </is>
       </c>
       <c r="G171">
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Sousense</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G172">
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Ovarense</t>
+          <t>Estrela Calheta</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="G173">
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Castro Daire</t>
+          <t>Sousense</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="G174">
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Ovarense</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Guarda</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G175">
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Castro Daire</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G176">
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Maia Lidador</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G189">
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Montalegre</t>
+          <t>Maia Lidador</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Maria da Fonte</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="G190">
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Montalegre</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Maria da Fonte</t>
         </is>
       </c>
       <c r="G191">
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G228">
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="G229">
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G230">
@@ -39266,13 +39266,13 @@
         </is>
       </c>
       <c r="N239">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O239">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P239">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="Q239">
         <v>0</v>
@@ -40701,12 +40701,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="G248">
@@ -40733,49 +40733,49 @@
         </is>
       </c>
       <c r="N248">
+        <v>1.71</v>
+      </c>
+      <c r="O248">
+        <v>3.5</v>
+      </c>
+      <c r="P248">
+        <v>4.21</v>
+      </c>
+      <c r="Q248">
+        <v>0</v>
+      </c>
+      <c r="R248">
+        <v>0</v>
+      </c>
+      <c r="S248">
+        <v>0</v>
+      </c>
+      <c r="T248">
+        <v>0</v>
+      </c>
+      <c r="U248">
+        <v>0</v>
+      </c>
+      <c r="V248">
+        <v>0</v>
+      </c>
+      <c r="W248">
+        <v>0</v>
+      </c>
+      <c r="X248">
+        <v>0</v>
+      </c>
+      <c r="Y248">
+        <v>0</v>
+      </c>
+      <c r="Z248">
+        <v>0</v>
+      </c>
+      <c r="AA248">
+        <v>1.85</v>
+      </c>
+      <c r="AB248">
         <v>1.95</v>
-      </c>
-      <c r="O248">
-        <v>3.34</v>
-      </c>
-      <c r="P248">
-        <v>3.37</v>
-      </c>
-      <c r="Q248">
-        <v>0</v>
-      </c>
-      <c r="R248">
-        <v>0</v>
-      </c>
-      <c r="S248">
-        <v>0</v>
-      </c>
-      <c r="T248">
-        <v>0</v>
-      </c>
-      <c r="U248">
-        <v>0</v>
-      </c>
-      <c r="V248">
-        <v>0</v>
-      </c>
-      <c r="W248">
-        <v>0</v>
-      </c>
-      <c r="X248">
-        <v>0</v>
-      </c>
-      <c r="Y248">
-        <v>0</v>
-      </c>
-      <c r="Z248">
-        <v>0</v>
-      </c>
-      <c r="AA248">
-        <v>0</v>
-      </c>
-      <c r="AB248">
-        <v>0</v>
       </c>
       <c r="AC248">
         <v>0</v>
@@ -40864,12 +40864,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G249">
@@ -40896,13 +40896,13 @@
         </is>
       </c>
       <c r="N249">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="O249">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="P249">
-        <v>4.63</v>
+        <v>3.37</v>
       </c>
       <c r="Q249">
         <v>0</v>
@@ -41027,12 +41027,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G250">
@@ -41059,13 +41059,13 @@
         </is>
       </c>
       <c r="N250">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="O250">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="P250">
-        <v>4.21</v>
+        <v>4.63</v>
       </c>
       <c r="Q250">
         <v>0</v>
@@ -41098,10 +41098,10 @@
         <v>0</v>
       </c>
       <c r="AA250">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB250">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC250">
         <v>0</v>
@@ -49666,12 +49666,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G303">
@@ -49829,12 +49829,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G304">
@@ -50155,12 +50155,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Tru-Juice</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G306">
@@ -50318,12 +50318,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Tru-Juice</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G307">
@@ -52437,12 +52437,12 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G320">
@@ -52469,13 +52469,13 @@
         </is>
       </c>
       <c r="N320">
-        <v>4.46</v>
+        <v>2.4</v>
       </c>
       <c r="O320">
-        <v>4.23</v>
+        <v>3.44</v>
       </c>
       <c r="P320">
-        <v>1.53</v>
+        <v>2.47</v>
       </c>
       <c r="Q320">
         <v>0</v>
@@ -52600,12 +52600,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G321">
@@ -52632,13 +52632,13 @@
         </is>
       </c>
       <c r="N321">
-        <v>1.13</v>
+        <v>4.46</v>
       </c>
       <c r="O321">
-        <v>7.45</v>
+        <v>4.23</v>
       </c>
       <c r="P321">
-        <v>10.53</v>
+        <v>1.53</v>
       </c>
       <c r="Q321">
         <v>0</v>
@@ -52677,10 +52677,10 @@
         <v>0</v>
       </c>
       <c r="AC321">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD321">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE321">
         <v>0</v>
@@ -52763,12 +52763,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G322">
@@ -52795,13 +52795,13 @@
         </is>
       </c>
       <c r="N322">
-        <v>2.13</v>
+        <v>1.13</v>
       </c>
       <c r="O322">
-        <v>3.36</v>
+        <v>7.45</v>
       </c>
       <c r="P322">
-        <v>2.9</v>
+        <v>10.53</v>
       </c>
       <c r="Q322">
         <v>0</v>
@@ -52840,10 +52840,10 @@
         <v>0</v>
       </c>
       <c r="AC322">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD322">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE322">
         <v>0</v>
@@ -52926,12 +52926,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G323">
@@ -52958,13 +52958,13 @@
         </is>
       </c>
       <c r="N323">
-        <v>3.57</v>
+        <v>2.13</v>
       </c>
       <c r="O323">
-        <v>3.67</v>
+        <v>3.36</v>
       </c>
       <c r="P323">
-        <v>1.79</v>
+        <v>2.9</v>
       </c>
       <c r="Q323">
         <v>0</v>
@@ -53578,12 +53578,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G327">
@@ -53610,13 +53610,13 @@
         </is>
       </c>
       <c r="N327">
-        <v>2.4</v>
+        <v>3.57</v>
       </c>
       <c r="O327">
-        <v>3.44</v>
+        <v>3.67</v>
       </c>
       <c r="P327">
-        <v>2.47</v>
+        <v>1.79</v>
       </c>
       <c r="Q327">
         <v>0</v>

--- a/jogos_2026-11-01.xlsx
+++ b/jogos_2026-11-01.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q4">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="R4">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W4">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y4">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z4">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA4">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC4">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD4">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE4">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK4">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G5">
@@ -1133,55 +1133,55 @@
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>3.25</v>
+        <v>2.57</v>
       </c>
       <c r="R5">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="S5">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="T5">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="U5">
-        <v>3.22</v>
+        <v>2.59</v>
       </c>
       <c r="V5">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="W5">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X5">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="Z5">
-        <v>3.07</v>
+        <v>3.5</v>
       </c>
       <c r="AA5">
-        <v>2.14</v>
+        <v>1.85</v>
       </c>
       <c r="AB5">
-        <v>1.66</v>
+        <v>1.82</v>
       </c>
       <c r="AC5">
-        <v>3.68</v>
+        <v>3.3</v>
       </c>
       <c r="AD5">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AE5">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF5">
-        <v>1.84</v>
+        <v>1.69</v>
       </c>
       <c r="AG5">
-        <v>1.86</v>
+        <v>2.05</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AK5">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.24</v>
+        <v>2.58</v>
       </c>
       <c r="O6">
-        <v>5.45</v>
+        <v>3.16</v>
       </c>
       <c r="P6">
-        <v>8.6</v>
+        <v>2.41</v>
       </c>
       <c r="Q6">
+        <v>3.1</v>
+      </c>
+      <c r="R6">
+        <v>2.2</v>
+      </c>
+      <c r="S6">
+        <v>1.35</v>
+      </c>
+      <c r="T6">
+        <v>2.76</v>
+      </c>
+      <c r="U6">
+        <v>2.64</v>
+      </c>
+      <c r="V6">
+        <v>1.38</v>
+      </c>
+      <c r="W6">
+        <v>1.05</v>
+      </c>
+      <c r="X6">
+        <v>1</v>
+      </c>
+      <c r="Y6">
+        <v>1.23</v>
+      </c>
+      <c r="Z6">
+        <v>3.42</v>
+      </c>
+      <c r="AA6">
+        <v>1.85</v>
+      </c>
+      <c r="AB6">
+        <v>1.91</v>
+      </c>
+      <c r="AC6">
+        <v>2.92</v>
+      </c>
+      <c r="AD6">
+        <v>1.31</v>
+      </c>
+      <c r="AE6">
+        <v>1.08</v>
+      </c>
+      <c r="AF6">
         <v>1.64</v>
       </c>
-      <c r="R6">
-        <v>2.75</v>
-      </c>
-      <c r="S6">
-        <v>1.18</v>
-      </c>
-      <c r="T6">
-        <v>3.85</v>
-      </c>
-      <c r="U6">
-        <v>2.08</v>
-      </c>
-      <c r="V6">
-        <v>1.64</v>
-      </c>
-      <c r="W6">
-        <v>1.14</v>
-      </c>
-      <c r="X6">
-        <v>1.01</v>
-      </c>
-      <c r="Y6">
-        <v>1.09</v>
-      </c>
-      <c r="Z6">
-        <v>5.35</v>
-      </c>
-      <c r="AA6">
-        <v>1.4</v>
-      </c>
-      <c r="AB6">
-        <v>2.56</v>
-      </c>
-      <c r="AC6">
-        <v>2.1</v>
-      </c>
-      <c r="AD6">
-        <v>1.63</v>
-      </c>
-      <c r="AE6">
-        <v>1.23</v>
-      </c>
-      <c r="AF6">
-        <v>1.73</v>
-      </c>
       <c r="AG6">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AK6">
-        <v>3.3</v>
+        <v>1.36</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.58</v>
+        <v>1.24</v>
       </c>
       <c r="O7">
-        <v>3.16</v>
+        <v>5.45</v>
       </c>
       <c r="P7">
-        <v>2.41</v>
+        <v>8.6</v>
       </c>
       <c r="Q7">
-        <v>3.1</v>
+        <v>1.64</v>
       </c>
       <c r="R7">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="S7">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="T7">
-        <v>2.76</v>
+        <v>3.85</v>
       </c>
       <c r="U7">
-        <v>2.64</v>
+        <v>2.08</v>
       </c>
       <c r="V7">
-        <v>1.38</v>
+        <v>1.64</v>
       </c>
       <c r="W7">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X7">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
+        <v>1.09</v>
+      </c>
+      <c r="Z7">
+        <v>5.35</v>
+      </c>
+      <c r="AA7">
+        <v>1.4</v>
+      </c>
+      <c r="AB7">
+        <v>2.56</v>
+      </c>
+      <c r="AC7">
+        <v>2.1</v>
+      </c>
+      <c r="AD7">
+        <v>1.63</v>
+      </c>
+      <c r="AE7">
         <v>1.23</v>
       </c>
-      <c r="Z7">
-        <v>3.42</v>
-      </c>
-      <c r="AA7">
-        <v>1.85</v>
-      </c>
-      <c r="AB7">
-        <v>1.91</v>
-      </c>
-      <c r="AC7">
-        <v>2.92</v>
-      </c>
-      <c r="AD7">
-        <v>1.31</v>
-      </c>
-      <c r="AE7">
-        <v>1.08</v>
-      </c>
       <c r="AF7">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AG7">
-        <v>2.07</v>
+        <v>1.92</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="AK7">
-        <v>1.36</v>
+        <v>3.3</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Q12">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R12">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T12">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="V12">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W12">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y12">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z12">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA12">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AB12">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AC12">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD12">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE12">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF12">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG12">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK12">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2926,55 +2926,55 @@
         <v>2.04</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -8957,34 +8957,34 @@
         <v>2.52</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T53">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U53">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V53">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W53">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X53">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z53">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA53">
         <v>2</v>
@@ -8993,19 +8993,19 @@
         <v>1.8</v>
       </c>
       <c r="AC53">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD53">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE53">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF53">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG53">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK53">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9772,34 +9772,34 @@
         <v>1.57</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>6.28</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T58">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U58">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V58">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W58">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y58">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z58">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA58">
         <v>2.03</v>
@@ -9808,19 +9808,19 @@
         <v>1.78</v>
       </c>
       <c r="AC58">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE58">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF58">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG58">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK58">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9935,55 +9935,55 @@
         <v>8.5</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z59">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AF59">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -11432,10 +11432,10 @@
         <v>0</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC68">
         <v>0</v>
@@ -11586,7 +11586,7 @@
         <v>1.33</v>
       </c>
       <c r="X69">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y69">
         <v>1.02</v>
@@ -12543,34 +12543,34 @@
         <v>1.97</v>
       </c>
       <c r="Q75">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="R75">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S75">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T75">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U75">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V75">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W75">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X75">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y75">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z75">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA75">
         <v>1.8</v>
@@ -12579,19 +12579,19 @@
         <v>2</v>
       </c>
       <c r="AC75">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD75">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE75">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF75">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG75">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK75">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12736,10 +12736,10 @@
         <v>0</v>
       </c>
       <c r="AA76">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB76">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC76">
         <v>0</v>
@@ -12869,55 +12869,55 @@
         <v>2.08</v>
       </c>
       <c r="Q77">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R77">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S77">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T77">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U77">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V77">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W77">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y77">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z77">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA77">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB77">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC77">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD77">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE77">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF77">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG77">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK77">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13032,55 +13032,55 @@
         <v>2.69</v>
       </c>
       <c r="Q78">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="R78">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S78">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T78">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U78">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V78">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W78">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y78">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z78">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA78">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB78">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC78">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD78">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE78">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF78">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG78">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK78">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q82">
         <v>2.54</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,65 +13838,65 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="O83">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="P83">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="Q83">
+        <v>2.45</v>
+      </c>
+      <c r="R83">
+        <v>2.38</v>
+      </c>
+      <c r="S83">
+        <v>1.22</v>
+      </c>
+      <c r="T83">
+        <v>3.65</v>
+      </c>
+      <c r="U83">
+        <v>2.12</v>
+      </c>
+      <c r="V83">
+        <v>1.63</v>
+      </c>
+      <c r="W83">
+        <v>1.17</v>
+      </c>
+      <c r="X83">
+        <v>1.02</v>
+      </c>
+      <c r="Y83">
+        <v>1.13</v>
+      </c>
+      <c r="Z83">
+        <v>5.25</v>
+      </c>
+      <c r="AA83">
+        <v>1.53</v>
+      </c>
+      <c r="AB83">
+        <v>2.58</v>
+      </c>
+      <c r="AC83">
+        <v>2</v>
+      </c>
+      <c r="AD83">
+        <v>1.7</v>
+      </c>
+      <c r="AE83">
+        <v>1.22</v>
+      </c>
+      <c r="AF83">
+        <v>1.44</v>
+      </c>
+      <c r="AG83">
         <v>2.6</v>
       </c>
-      <c r="R83">
-        <v>2.25</v>
-      </c>
-      <c r="S83">
-        <v>1.28</v>
-      </c>
-      <c r="T83">
-        <v>3.22</v>
-      </c>
-      <c r="U83">
-        <v>2.25</v>
-      </c>
-      <c r="V83">
-        <v>1.57</v>
-      </c>
-      <c r="W83">
-        <v>1.12</v>
-      </c>
-      <c r="X83">
-        <v>1.03</v>
-      </c>
-      <c r="Y83">
-        <v>1.17</v>
-      </c>
-      <c r="Z83">
-        <v>4.5</v>
-      </c>
-      <c r="AA83">
-        <v>1.57</v>
-      </c>
-      <c r="AB83">
-        <v>2.25</v>
-      </c>
-      <c r="AC83">
-        <v>2.38</v>
-      </c>
-      <c r="AD83">
-        <v>1.46</v>
-      </c>
-      <c r="AE83">
-        <v>1.15</v>
-      </c>
-      <c r="AF83">
-        <v>1.53</v>
-      </c>
-      <c r="AG83">
-        <v>2.4</v>
-      </c>
       <c r="AH83" t="inlineStr">
         <is>
           <t>[]</t>
@@ -13908,7 +13908,7 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK83">
         <v>1.73</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="O85">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="P85">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="Q85">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="R85">
+        <v>2.25</v>
+      </c>
+      <c r="S85">
+        <v>1.28</v>
+      </c>
+      <c r="T85">
+        <v>3.22</v>
+      </c>
+      <c r="U85">
+        <v>2.25</v>
+      </c>
+      <c r="V85">
+        <v>1.57</v>
+      </c>
+      <c r="W85">
+        <v>1.12</v>
+      </c>
+      <c r="X85">
+        <v>1.03</v>
+      </c>
+      <c r="Y85">
+        <v>1.17</v>
+      </c>
+      <c r="Z85">
+        <v>4.5</v>
+      </c>
+      <c r="AA85">
+        <v>1.57</v>
+      </c>
+      <c r="AB85">
+        <v>2.25</v>
+      </c>
+      <c r="AC85">
         <v>2.38</v>
       </c>
-      <c r="S85">
-        <v>1.22</v>
-      </c>
-      <c r="T85">
-        <v>3.65</v>
-      </c>
-      <c r="U85">
-        <v>2.12</v>
-      </c>
-      <c r="V85">
-        <v>1.63</v>
-      </c>
-      <c r="W85">
-        <v>1.17</v>
-      </c>
-      <c r="X85">
-        <v>1.02</v>
-      </c>
-      <c r="Y85">
-        <v>1.13</v>
-      </c>
-      <c r="Z85">
-        <v>5.25</v>
-      </c>
-      <c r="AA85">
+      <c r="AD85">
+        <v>1.46</v>
+      </c>
+      <c r="AE85">
+        <v>1.15</v>
+      </c>
+      <c r="AF85">
         <v>1.53</v>
       </c>
-      <c r="AB85">
-        <v>2.58</v>
-      </c>
-      <c r="AC85">
-        <v>2</v>
-      </c>
-      <c r="AD85">
-        <v>1.7</v>
-      </c>
-      <c r="AE85">
-        <v>1.22</v>
-      </c>
-      <c r="AF85">
-        <v>1.44</v>
-      </c>
       <c r="AG85">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,7 +14234,7 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK85">
         <v>1.73</v>
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O104">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P104">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q104">
         <v>2.61</v>
@@ -18248,34 +18248,34 @@
         <v>6.32</v>
       </c>
       <c r="Q110">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="R110">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S110">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T110">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U110">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="V110">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W110">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X110">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y110">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z110">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA110">
         <v>1.9</v>
@@ -18284,19 +18284,19 @@
         <v>1.9</v>
       </c>
       <c r="AC110">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD110">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE110">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF110">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG110">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK110">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18411,34 +18411,34 @@
         <v>3.66</v>
       </c>
       <c r="Q111">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R111">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S111">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T111">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U111">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V111">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W111">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X111">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y111">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z111">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA111">
         <v>2.05</v>
@@ -18447,19 +18447,19 @@
         <v>1.75</v>
       </c>
       <c r="AC111">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD111">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE111">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF111">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG111">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK111">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -19226,34 +19226,34 @@
         <v>5.11</v>
       </c>
       <c r="Q116">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R116">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S116">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T116">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U116">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V116">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W116">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X116">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y116">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z116">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA116">
         <v>1.75</v>
@@ -19262,19 +19262,19 @@
         <v>2.05</v>
       </c>
       <c r="AC116">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD116">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE116">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF116">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG116">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK116">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -20367,34 +20367,34 @@
         <v>3.83</v>
       </c>
       <c r="Q123">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R123">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S123">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T123">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U123">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V123">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W123">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X123">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y123">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z123">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA123">
         <v>2.1</v>
@@ -20403,19 +20403,19 @@
         <v>1.7</v>
       </c>
       <c r="AC123">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD123">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE123">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF123">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG123">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK123">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20530,34 +20530,34 @@
         <v>2.02</v>
       </c>
       <c r="Q124">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R124">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S124">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T124">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U124">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V124">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W124">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X124">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y124">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z124">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA124">
         <v>2.07</v>
@@ -20566,19 +20566,19 @@
         <v>1.72</v>
       </c>
       <c r="AC124">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD124">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE124">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF124">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG124">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK124">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -21182,55 +21182,55 @@
         <v>7.23</v>
       </c>
       <c r="Q128">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="R128">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S128">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T128">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U128">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V128">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W128">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X128">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y128">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z128">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA128">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB128">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC128">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD128">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE128">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF128">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG128">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK128">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -22516,10 +22516,10 @@
         <v>0</v>
       </c>
       <c r="AA136">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB136">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC136">
         <v>0</v>
@@ -24768,55 +24768,55 @@
         <v>2.91</v>
       </c>
       <c r="Q150">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R150">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S150">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T150">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U150">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V150">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W150">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X150">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y150">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z150">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AA150">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB150">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC150">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD150">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE150">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF150">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG150">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH150" t="inlineStr">
         <is>
@@ -24829,10 +24829,10 @@
         </is>
       </c>
       <c r="AJ150">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK150">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL150">
         <v>0</v>
@@ -25287,10 +25287,10 @@
         <v>0</v>
       </c>
       <c r="AA153">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB153">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC153">
         <v>0</v>
@@ -29821,55 +29821,55 @@
         <v>2.16</v>
       </c>
       <c r="Q181">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R181">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S181">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T181">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U181">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V181">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W181">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X181">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y181">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z181">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA181">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB181">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC181">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD181">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE181">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF181">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG181">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH181" t="inlineStr">
         <is>
@@ -29882,10 +29882,10 @@
         </is>
       </c>
       <c r="AJ181">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK181">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL181">
         <v>0</v>
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Ponte da Barca</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Vinhais</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G188">
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Maia Lidador</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="G189">
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Maia Lidador</t>
+          <t>Montalegre</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Maria da Fonte</t>
         </is>
       </c>
       <c r="G190">
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Montalegre</t>
+          <t>Ponte da Barca</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Maria da Fonte</t>
+          <t>Vinhais</t>
         </is>
       </c>
       <c r="G191">
@@ -31777,55 +31777,55 @@
         <v>2.5</v>
       </c>
       <c r="Q193">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R193">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S193">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T193">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U193">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V193">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W193">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X193">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y193">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z193">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA193">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB193">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC193">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD193">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE193">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF193">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG193">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31838,10 +31838,10 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK193">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -32103,34 +32103,34 @@
         <v>2.56</v>
       </c>
       <c r="Q195">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R195">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S195">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T195">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U195">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V195">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W195">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y195">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z195">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA195">
         <v>1.83</v>
@@ -32139,19 +32139,19 @@
         <v>1.98</v>
       </c>
       <c r="AC195">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD195">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE195">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF195">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG195">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK195">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -33398,64 +33398,64 @@
         </is>
       </c>
       <c r="N203">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O203">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P203">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q203">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R203">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S203">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T203">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U203">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V203">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W203">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X203">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y203">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z203">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA203">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB203">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AC203">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD203">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE203">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF203">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG203">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH203" t="inlineStr">
         <is>
@@ -33468,10 +33468,10 @@
         </is>
       </c>
       <c r="AJ203">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK203">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL203">
         <v>0</v>
@@ -34385,55 +34385,55 @@
         <v>6.85</v>
       </c>
       <c r="Q209">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R209">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S209">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T209">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U209">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V209">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W209">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X209">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y209">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z209">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA209">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB209">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AC209">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AD209">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE209">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF209">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG209">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH209" t="inlineStr">
         <is>
@@ -34446,10 +34446,10 @@
         </is>
       </c>
       <c r="AJ209">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK209">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -35680,64 +35680,64 @@
         </is>
       </c>
       <c r="N217">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O217">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P217">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q217">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R217">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S217">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T217">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U217">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V217">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W217">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X217">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y217">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z217">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA217">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB217">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC217">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD217">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE217">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF217">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG217">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH217" t="inlineStr">
         <is>
@@ -35750,10 +35750,10 @@
         </is>
       </c>
       <c r="AJ217">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK217">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL217">
         <v>0</v>
@@ -36993,55 +36993,55 @@
         <v>2.45</v>
       </c>
       <c r="Q225">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R225">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S225">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T225">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U225">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V225">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W225">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X225">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y225">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z225">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA225">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB225">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC225">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD225">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE225">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF225">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG225">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH225" t="inlineStr">
         <is>
@@ -37054,10 +37054,10 @@
         </is>
       </c>
       <c r="AJ225">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK225">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL225">
         <v>0</v>
@@ -37930,12 +37930,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Calvo Sotelo</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G231">
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Calvo Sotelo</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G232">
@@ -38460,55 +38460,55 @@
         <v>0</v>
       </c>
       <c r="Q234">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="R234">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S234">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T234">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U234">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V234">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W234">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X234">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y234">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z234">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA234">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB234">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC234">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD234">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE234">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF234">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG234">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH234" t="inlineStr">
         <is>
@@ -38521,10 +38521,10 @@
         </is>
       </c>
       <c r="AJ234">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK234">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL234">
         <v>0</v>
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>SD Compostela</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G235">
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>SD Compostela</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G236">
@@ -39275,55 +39275,55 @@
         <v>4.91</v>
       </c>
       <c r="Q239">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="R239">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S239">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T239">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U239">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V239">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W239">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X239">
         <v>0</v>
       </c>
       <c r="Y239">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z239">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA239">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB239">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AC239">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD239">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE239">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF239">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG239">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH239" t="inlineStr">
         <is>
@@ -39336,10 +39336,10 @@
         </is>
       </c>
       <c r="AJ239">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK239">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AL239">
         <v>0</v>
@@ -40416,55 +40416,55 @@
         <v>5.86</v>
       </c>
       <c r="Q246">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R246">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S246">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T246">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U246">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V246">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W246">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X246">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y246">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z246">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA246">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB246">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AC246">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD246">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE246">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF246">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG246">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH246" t="inlineStr">
         <is>
@@ -40477,10 +40477,10 @@
         </is>
       </c>
       <c r="AJ246">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK246">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AL246">
         <v>0</v>
@@ -40742,34 +40742,34 @@
         <v>4.21</v>
       </c>
       <c r="Q248">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R248">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S248">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T248">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U248">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V248">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W248">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X248">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y248">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z248">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA248">
         <v>1.85</v>
@@ -40778,19 +40778,19 @@
         <v>1.95</v>
       </c>
       <c r="AC248">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD248">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE248">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF248">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG248">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH248" t="inlineStr">
         <is>
@@ -40803,10 +40803,10 @@
         </is>
       </c>
       <c r="AJ248">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK248">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL248">
         <v>0</v>
@@ -40864,12 +40864,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G249">
@@ -40896,80 +40896,80 @@
         </is>
       </c>
       <c r="N249">
+        <v>1.72</v>
+      </c>
+      <c r="O249">
+        <v>3.22</v>
+      </c>
+      <c r="P249">
+        <v>4.63</v>
+      </c>
+      <c r="Q249">
+        <v>2.34</v>
+      </c>
+      <c r="R249">
+        <v>1.94</v>
+      </c>
+      <c r="S249">
+        <v>1.43</v>
+      </c>
+      <c r="T249">
+        <v>2.48</v>
+      </c>
+      <c r="U249">
+        <v>3.06</v>
+      </c>
+      <c r="V249">
+        <v>1.29</v>
+      </c>
+      <c r="W249">
+        <v>1.02</v>
+      </c>
+      <c r="X249">
+        <v>1.03</v>
+      </c>
+      <c r="Y249">
+        <v>1.37</v>
+      </c>
+      <c r="Z249">
+        <v>2.66</v>
+      </c>
+      <c r="AA249">
+        <v>2.35</v>
+      </c>
+      <c r="AB249">
+        <v>1.57</v>
+      </c>
+      <c r="AC249">
+        <v>4.25</v>
+      </c>
+      <c r="AD249">
+        <v>1.15</v>
+      </c>
+      <c r="AE249">
+        <v>1.01</v>
+      </c>
+      <c r="AF249">
+        <v>2.09</v>
+      </c>
+      <c r="AG249">
+        <v>1.63</v>
+      </c>
+      <c r="AH249" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI249" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ249">
+        <v>1.09</v>
+      </c>
+      <c r="AK249">
         <v>1.95</v>
-      </c>
-      <c r="O249">
-        <v>3.34</v>
-      </c>
-      <c r="P249">
-        <v>3.37</v>
-      </c>
-      <c r="Q249">
-        <v>0</v>
-      </c>
-      <c r="R249">
-        <v>0</v>
-      </c>
-      <c r="S249">
-        <v>0</v>
-      </c>
-      <c r="T249">
-        <v>0</v>
-      </c>
-      <c r="U249">
-        <v>0</v>
-      </c>
-      <c r="V249">
-        <v>0</v>
-      </c>
-      <c r="W249">
-        <v>0</v>
-      </c>
-      <c r="X249">
-        <v>0</v>
-      </c>
-      <c r="Y249">
-        <v>0</v>
-      </c>
-      <c r="Z249">
-        <v>0</v>
-      </c>
-      <c r="AA249">
-        <v>0</v>
-      </c>
-      <c r="AB249">
-        <v>0</v>
-      </c>
-      <c r="AC249">
-        <v>0</v>
-      </c>
-      <c r="AD249">
-        <v>0</v>
-      </c>
-      <c r="AE249">
-        <v>0</v>
-      </c>
-      <c r="AF249">
-        <v>0</v>
-      </c>
-      <c r="AG249">
-        <v>0</v>
-      </c>
-      <c r="AH249" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI249" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ249">
-        <v>0</v>
-      </c>
-      <c r="AK249">
-        <v>0</v>
       </c>
       <c r="AL249">
         <v>0</v>
@@ -41027,12 +41027,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G250">
@@ -41059,64 +41059,64 @@
         </is>
       </c>
       <c r="N250">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="O250">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="P250">
-        <v>4.63</v>
+        <v>3.37</v>
       </c>
       <c r="Q250">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="R250">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S250">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T250">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U250">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V250">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W250">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X250">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y250">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z250">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA250">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB250">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC250">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD250">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE250">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF250">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG250">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH250" t="inlineStr">
         <is>
@@ -41129,10 +41129,10 @@
         </is>
       </c>
       <c r="AJ250">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK250">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL250">
         <v>0</v>
@@ -41557,55 +41557,55 @@
         <v>4.91</v>
       </c>
       <c r="Q253">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R253">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S253">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T253">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U253">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V253">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W253">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X253">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y253">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z253">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA253">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB253">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC253">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD253">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE253">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF253">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG253">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH253" t="inlineStr">
         <is>
@@ -41618,10 +41618,10 @@
         </is>
       </c>
       <c r="AJ253">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK253">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL253">
         <v>0</v>
@@ -41679,12 +41679,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Cieza</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G254">
@@ -41842,12 +41842,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Cieza</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G255">
@@ -42046,34 +42046,34 @@
         <v>2.45</v>
       </c>
       <c r="Q256">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R256">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S256">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T256">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U256">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V256">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W256">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X256">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y256">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z256">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA256">
         <v>1.85</v>
@@ -42082,19 +42082,19 @@
         <v>1.95</v>
       </c>
       <c r="AC256">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD256">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE256">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF256">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG256">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH256" t="inlineStr">
         <is>
@@ -42107,10 +42107,10 @@
         </is>
       </c>
       <c r="AJ256">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK256">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL256">
         <v>0</v>
@@ -42209,55 +42209,55 @@
         <v>2.46</v>
       </c>
       <c r="Q257">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R257">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S257">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T257">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U257">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V257">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W257">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X257">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y257">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z257">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA257">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB257">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC257">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD257">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE257">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF257">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG257">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH257" t="inlineStr">
         <is>
@@ -42270,10 +42270,10 @@
         </is>
       </c>
       <c r="AJ257">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK257">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL257">
         <v>0</v>
@@ -42372,40 +42372,40 @@
         <v>4.83</v>
       </c>
       <c r="Q258">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R258">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S258">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T258">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U258">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V258">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W258">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X258">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y258">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z258">
-        <v>0</v>
+        <v>5.92</v>
       </c>
       <c r="AA258">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB258">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AC258">
         <v>1.98</v>
@@ -42414,13 +42414,13 @@
         <v>1.75</v>
       </c>
       <c r="AE258">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF258">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG258">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AH258" t="inlineStr">
         <is>
@@ -42433,10 +42433,10 @@
         </is>
       </c>
       <c r="AJ258">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK258">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AL258">
         <v>0</v>
@@ -43024,55 +43024,55 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Q262">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R262">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S262">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T262">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U262">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V262">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W262">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X262">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y262">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z262">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA262">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB262">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AC262">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD262">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE262">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF262">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG262">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH262" t="inlineStr">
         <is>
@@ -43085,10 +43085,10 @@
         </is>
       </c>
       <c r="AJ262">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK262">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AL262">
         <v>0</v>
@@ -43187,55 +43187,55 @@
         <v>2.76</v>
       </c>
       <c r="Q263">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R263">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S263">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T263">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U263">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V263">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W263">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X263">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y263">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z263">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="AA263">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB263">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC263">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD263">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE263">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF263">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG263">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH263" t="inlineStr">
         <is>
@@ -43248,10 +43248,10 @@
         </is>
       </c>
       <c r="AJ263">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK263">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL263">
         <v>0</v>
@@ -43667,64 +43667,64 @@
         </is>
       </c>
       <c r="N266">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O266">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P266">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q266">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R266">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S266">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T266">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U266">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V266">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W266">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X266">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y266">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z266">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA266">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB266">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC266">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AD266">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE266">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF266">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG266">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH266" t="inlineStr">
         <is>
@@ -43737,10 +43737,10 @@
         </is>
       </c>
       <c r="AJ266">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK266">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL266">
         <v>0</v>
@@ -43839,34 +43839,34 @@
         <v>1.7</v>
       </c>
       <c r="Q267">
-        <v>0</v>
+        <v>7.04</v>
       </c>
       <c r="R267">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S267">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T267">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U267">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V267">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W267">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X267">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y267">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z267">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA267">
         <v>1.88</v>
@@ -43875,19 +43875,19 @@
         <v>1.93</v>
       </c>
       <c r="AC267">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD267">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE267">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF267">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG267">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH267" t="inlineStr">
         <is>
@@ -43900,10 +43900,10 @@
         </is>
       </c>
       <c r="AJ267">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AK267">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AL267">
         <v>0</v>
@@ -44002,55 +44002,55 @@
         <v>2.83</v>
       </c>
       <c r="Q268">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R268">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S268">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T268">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U268">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V268">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W268">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X268">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y268">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z268">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AA268">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB268">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC268">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD268">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE268">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF268">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG268">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH268" t="inlineStr">
         <is>
@@ -44063,10 +44063,10 @@
         </is>
       </c>
       <c r="AJ268">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK268">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL268">
         <v>0</v>
@@ -44491,55 +44491,55 @@
         <v>2.07</v>
       </c>
       <c r="Q271">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R271">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S271">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T271">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U271">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V271">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W271">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X271">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y271">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z271">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA271">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB271">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC271">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD271">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE271">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF271">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG271">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH271" t="inlineStr">
         <is>
@@ -44552,10 +44552,10 @@
         </is>
       </c>
       <c r="AJ271">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK271">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL271">
         <v>0</v>
@@ -45143,34 +45143,34 @@
         <v>1.86</v>
       </c>
       <c r="Q275">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R275">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S275">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T275">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U275">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V275">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W275">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X275">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y275">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z275">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA275">
         <v>1.72</v>
@@ -45179,19 +45179,19 @@
         <v>1.98</v>
       </c>
       <c r="AC275">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD275">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE275">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF275">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG275">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH275" t="inlineStr">
         <is>
@@ -45204,10 +45204,10 @@
         </is>
       </c>
       <c r="AJ275">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK275">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL275">
         <v>0</v>
@@ -47099,34 +47099,34 @@
         <v>6.51</v>
       </c>
       <c r="Q287">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R287">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S287">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T287">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U287">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V287">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W287">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X287">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y287">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z287">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA287">
         <v>1.61</v>
@@ -47135,19 +47135,19 @@
         <v>2.15</v>
       </c>
       <c r="AC287">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD287">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE287">
         <v>1.18</v>
       </c>
       <c r="AF287">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG287">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH287" t="inlineStr">
         <is>
@@ -47160,10 +47160,10 @@
         </is>
       </c>
       <c r="AJ287">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK287">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL287">
         <v>0</v>
@@ -47262,55 +47262,55 @@
         <v>4.85</v>
       </c>
       <c r="Q288">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R288">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S288">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T288">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U288">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V288">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W288">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X288">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y288">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z288">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA288">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB288">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC288">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD288">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE288">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF288">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG288">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH288" t="inlineStr">
         <is>
@@ -47323,10 +47323,10 @@
         </is>
       </c>
       <c r="AJ288">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK288">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL288">
         <v>0</v>
@@ -47416,64 +47416,64 @@
         </is>
       </c>
       <c r="N289">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O289">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P289">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q289">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R289">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S289">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T289">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U289">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V289">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W289">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X289">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y289">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z289">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA289">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB289">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC289">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD289">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE289">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF289">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG289">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH289" t="inlineStr">
         <is>
@@ -47486,10 +47486,10 @@
         </is>
       </c>
       <c r="AJ289">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK289">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL289">
         <v>0</v>
@@ -47742,13 +47742,13 @@
         </is>
       </c>
       <c r="N291">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O291">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P291">
-        <v>0</v>
+        <v>5.11</v>
       </c>
       <c r="Q291">
         <v>0</v>
@@ -48729,34 +48729,34 @@
         <v>3.44</v>
       </c>
       <c r="Q297">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R297">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S297">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T297">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U297">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V297">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W297">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X297">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y297">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z297">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AA297">
         <v>1.92</v>
@@ -48765,19 +48765,19 @@
         <v>1.88</v>
       </c>
       <c r="AC297">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD297">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE297">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF297">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG297">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH297" t="inlineStr">
         <is>
@@ -48790,10 +48790,10 @@
         </is>
       </c>
       <c r="AJ297">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK297">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL297">
         <v>0</v>
@@ -49085,10 +49085,10 @@
         <v>0</v>
       </c>
       <c r="AA299">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB299">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC299">
         <v>0</v>

--- a/jogos_2026-11-01.xlsx
+++ b/jogos_2026-11-01.xlsx
@@ -970,55 +970,55 @@
         <v>2.92</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -2274,34 +2274,34 @@
         <v>3.91</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA12">
         <v>1.91</v>
@@ -2310,19 +2310,19 @@
         <v>1.89</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O38">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="P38">
-        <v>5.01</v>
+        <v>0</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>12.1</v>
+        <v>1.57</v>
       </c>
       <c r="O39">
-        <v>6.6</v>
+        <v>3.95</v>
       </c>
       <c r="P39">
-        <v>1.17</v>
+        <v>5.01</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.65</v>
+        <v>12.1</v>
       </c>
       <c r="O40">
-        <v>3.8</v>
+        <v>6.6</v>
       </c>
       <c r="P40">
-        <v>4.53</v>
+        <v>1.17</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="O41">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P41">
-        <v>3.95</v>
+        <v>4.53</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -13195,55 +13195,55 @@
         <v>3.3</v>
       </c>
       <c r="Q79">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R79">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S79">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T79">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U79">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="V79">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W79">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X79">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z79">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA79">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC79">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD79">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE79">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF79">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG79">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK79">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,31 +13838,31 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="O83">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="P83">
-        <v>3.6</v>
+        <v>2.55</v>
       </c>
       <c r="Q83">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="R83">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="S83">
         <v>1.22</v>
       </c>
       <c r="T83">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="U83">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="V83">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W83">
         <v>1.17</v>
@@ -13871,31 +13871,31 @@
         <v>1.02</v>
       </c>
       <c r="Y83">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z83">
-        <v>5.25</v>
+        <v>5.05</v>
       </c>
       <c r="AA83">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB83">
-        <v>2.58</v>
+        <v>2.35</v>
       </c>
       <c r="AC83">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AD83">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AE83">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF83">
         <v>1.44</v>
       </c>
       <c r="AG83">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="AK83">
-        <v>1.73</v>
+        <v>1.49</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,31 +14001,31 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="O84">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="P84">
-        <v>2.55</v>
+        <v>3.6</v>
       </c>
       <c r="Q84">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="R84">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="S84">
         <v>1.22</v>
       </c>
       <c r="T84">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="U84">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="V84">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W84">
         <v>1.17</v>
@@ -14034,31 +14034,31 @@
         <v>1.02</v>
       </c>
       <c r="Y84">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z84">
-        <v>5.05</v>
+        <v>5.25</v>
       </c>
       <c r="AA84">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB84">
-        <v>2.35</v>
+        <v>2.58</v>
       </c>
       <c r="AC84">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AD84">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AE84">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF84">
         <v>1.44</v>
       </c>
       <c r="AG84">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="AK84">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -22649,55 +22649,55 @@
         <v>4.14</v>
       </c>
       <c r="Q137">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R137">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S137">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T137">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U137">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V137">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W137">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X137">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y137">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z137">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA137">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB137">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC137">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD137">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE137">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF137">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG137">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK137">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Maia Lidador</t>
+          <t>Montalegre</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Maria da Fonte</t>
         </is>
       </c>
       <c r="G189">
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Montalegre</t>
+          <t>Maia Lidador</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Maria da Fonte</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="G190">
@@ -34222,34 +34222,34 @@
         <v>4.17</v>
       </c>
       <c r="Q208">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="R208">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S208">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T208">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U208">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V208">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W208">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X208">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y208">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z208">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA208">
         <v>1.85</v>
@@ -34258,19 +34258,19 @@
         <v>1.95</v>
       </c>
       <c r="AC208">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD208">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE208">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF208">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG208">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH208" t="inlineStr">
         <is>
@@ -34283,10 +34283,10 @@
         </is>
       </c>
       <c r="AJ208">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK208">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL208">
         <v>0</v>
@@ -36015,55 +36015,55 @@
         <v>29</v>
       </c>
       <c r="Q219">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R219">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="S219">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T219">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U219">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V219">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W219">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X219">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y219">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z219">
-        <v>0</v>
+        <v>6.97</v>
       </c>
       <c r="AA219">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB219">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AC219">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD219">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE219">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF219">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG219">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH219" t="inlineStr">
         <is>
@@ -36076,10 +36076,10 @@
         </is>
       </c>
       <c r="AJ219">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK219">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AL219">
         <v>0</v>
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G230">
@@ -37930,12 +37930,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G231">
@@ -38297,55 +38297,55 @@
         <v>1.64</v>
       </c>
       <c r="Q233">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R233">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S233">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T233">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U233">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V233">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W233">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X233">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y233">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z233">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA233">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB233">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AC233">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD233">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE233">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF233">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG233">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH233" t="inlineStr">
         <is>
@@ -38358,10 +38358,10 @@
         </is>
       </c>
       <c r="AJ233">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK233">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL233">
         <v>0</v>
@@ -40579,34 +40579,34 @@
         <v>3</v>
       </c>
       <c r="Q247">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="R247">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S247">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T247">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U247">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V247">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W247">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X247">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y247">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z247">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA247">
         <v>1.7</v>
@@ -40615,19 +40615,19 @@
         <v>2.05</v>
       </c>
       <c r="AC247">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AD247">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE247">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF247">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG247">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH247" t="inlineStr">
         <is>
@@ -40640,10 +40640,10 @@
         </is>
       </c>
       <c r="AJ247">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK247">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL247">
         <v>0</v>
@@ -40701,12 +40701,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G248">
@@ -40733,19 +40733,19 @@
         </is>
       </c>
       <c r="N248">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="O248">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="P248">
-        <v>4.21</v>
+        <v>3.37</v>
       </c>
       <c r="Q248">
-        <v>2.27</v>
+        <v>2.41</v>
       </c>
       <c r="R248">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="S248">
         <v>1.31</v>
@@ -40754,13 +40754,13 @@
         <v>2.95</v>
       </c>
       <c r="U248">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="V248">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W248">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X248">
         <v>1</v>
@@ -40772,25 +40772,25 @@
         <v>3.42</v>
       </c>
       <c r="AA248">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AB248">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AC248">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AD248">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE248">
         <v>1.09</v>
       </c>
       <c r="AF248">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AG248">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AH248" t="inlineStr">
         <is>
@@ -40803,10 +40803,10 @@
         </is>
       </c>
       <c r="AJ248">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK248">
-        <v>1.89</v>
+        <v>1.74</v>
       </c>
       <c r="AL248">
         <v>0</v>
@@ -40864,12 +40864,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="G249">
@@ -40896,64 +40896,64 @@
         </is>
       </c>
       <c r="N249">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="O249">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="P249">
-        <v>4.63</v>
+        <v>4.21</v>
       </c>
       <c r="Q249">
-        <v>2.34</v>
+        <v>2.27</v>
       </c>
       <c r="R249">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="S249">
+        <v>1.31</v>
+      </c>
+      <c r="T249">
+        <v>2.95</v>
+      </c>
+      <c r="U249">
+        <v>2.48</v>
+      </c>
+      <c r="V249">
         <v>1.43</v>
       </c>
-      <c r="T249">
-        <v>2.48</v>
-      </c>
-      <c r="U249">
-        <v>3.06</v>
-      </c>
-      <c r="V249">
-        <v>1.29</v>
-      </c>
       <c r="W249">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X249">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y249">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="Z249">
-        <v>2.66</v>
+        <v>3.42</v>
       </c>
       <c r="AA249">
-        <v>2.35</v>
+        <v>1.85</v>
       </c>
       <c r="AB249">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AC249">
-        <v>4.25</v>
+        <v>2.92</v>
       </c>
       <c r="AD249">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="AE249">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AF249">
-        <v>2.09</v>
+        <v>1.73</v>
       </c>
       <c r="AG249">
-        <v>1.63</v>
+        <v>1.95</v>
       </c>
       <c r="AH249" t="inlineStr">
         <is>
@@ -40966,10 +40966,10 @@
         </is>
       </c>
       <c r="AJ249">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AK249">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AL249">
         <v>0</v>
@@ -41027,12 +41027,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G250">
@@ -41059,80 +41059,80 @@
         </is>
       </c>
       <c r="N250">
+        <v>1.72</v>
+      </c>
+      <c r="O250">
+        <v>3.22</v>
+      </c>
+      <c r="P250">
+        <v>4.63</v>
+      </c>
+      <c r="Q250">
+        <v>2.34</v>
+      </c>
+      <c r="R250">
+        <v>1.94</v>
+      </c>
+      <c r="S250">
+        <v>1.43</v>
+      </c>
+      <c r="T250">
+        <v>2.48</v>
+      </c>
+      <c r="U250">
+        <v>3.06</v>
+      </c>
+      <c r="V250">
+        <v>1.29</v>
+      </c>
+      <c r="W250">
+        <v>1.02</v>
+      </c>
+      <c r="X250">
+        <v>1.03</v>
+      </c>
+      <c r="Y250">
+        <v>1.37</v>
+      </c>
+      <c r="Z250">
+        <v>2.66</v>
+      </c>
+      <c r="AA250">
+        <v>2.35</v>
+      </c>
+      <c r="AB250">
+        <v>1.57</v>
+      </c>
+      <c r="AC250">
+        <v>4.25</v>
+      </c>
+      <c r="AD250">
+        <v>1.15</v>
+      </c>
+      <c r="AE250">
+        <v>1.01</v>
+      </c>
+      <c r="AF250">
+        <v>2.09</v>
+      </c>
+      <c r="AG250">
+        <v>1.63</v>
+      </c>
+      <c r="AH250" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI250" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ250">
+        <v>1.09</v>
+      </c>
+      <c r="AK250">
         <v>1.95</v>
-      </c>
-      <c r="O250">
-        <v>3.34</v>
-      </c>
-      <c r="P250">
-        <v>3.37</v>
-      </c>
-      <c r="Q250">
-        <v>2.41</v>
-      </c>
-      <c r="R250">
-        <v>2.13</v>
-      </c>
-      <c r="S250">
-        <v>1.31</v>
-      </c>
-      <c r="T250">
-        <v>2.95</v>
-      </c>
-      <c r="U250">
-        <v>2.45</v>
-      </c>
-      <c r="V250">
-        <v>1.44</v>
-      </c>
-      <c r="W250">
-        <v>1.09</v>
-      </c>
-      <c r="X250">
-        <v>1</v>
-      </c>
-      <c r="Y250">
-        <v>1.23</v>
-      </c>
-      <c r="Z250">
-        <v>3.42</v>
-      </c>
-      <c r="AA250">
-        <v>1.79</v>
-      </c>
-      <c r="AB250">
-        <v>1.88</v>
-      </c>
-      <c r="AC250">
-        <v>2.88</v>
-      </c>
-      <c r="AD250">
-        <v>1.32</v>
-      </c>
-      <c r="AE250">
-        <v>1.09</v>
-      </c>
-      <c r="AF250">
-        <v>1.68</v>
-      </c>
-      <c r="AG250">
-        <v>1.99</v>
-      </c>
-      <c r="AH250" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI250" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ250">
-        <v>1.21</v>
-      </c>
-      <c r="AK250">
-        <v>1.74</v>
       </c>
       <c r="AL250">
         <v>0</v>
@@ -41231,34 +41231,34 @@
         <v>2.22</v>
       </c>
       <c r="Q251">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R251">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S251">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T251">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U251">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="V251">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W251">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X251">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y251">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z251">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA251">
         <v>1.61</v>
@@ -41267,19 +41267,19 @@
         <v>2.2</v>
       </c>
       <c r="AC251">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AD251">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE251">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF251">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG251">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH251" t="inlineStr">
         <is>
@@ -41292,10 +41292,10 @@
         </is>
       </c>
       <c r="AJ251">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK251">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL251">
         <v>0</v>
@@ -41385,13 +41385,13 @@
         </is>
       </c>
       <c r="N252">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O252">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P252">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Q252">
         <v>0</v>
@@ -42535,55 +42535,55 @@
         <v>1.97</v>
       </c>
       <c r="Q259">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="R259">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S259">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T259">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U259">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V259">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W259">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X259">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y259">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z259">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="AA259">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB259">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC259">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AD259">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE259">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF259">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG259">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH259" t="inlineStr">
         <is>
@@ -42596,10 +42596,10 @@
         </is>
       </c>
       <c r="AJ259">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK259">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL259">
         <v>0</v>
@@ -42689,64 +42689,64 @@
         </is>
       </c>
       <c r="N260">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O260">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P260">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q260">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R260">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S260">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T260">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U260">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V260">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W260">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X260">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y260">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z260">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA260">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB260">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC260">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD260">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE260">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF260">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG260">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH260" t="inlineStr">
         <is>
@@ -42759,10 +42759,10 @@
         </is>
       </c>
       <c r="AJ260">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK260">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL260">
         <v>0</v>
@@ -43341,64 +43341,64 @@
         </is>
       </c>
       <c r="N264">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O264">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P264">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q264">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R264">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S264">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T264">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U264">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="V264">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W264">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X264">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y264">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z264">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA264">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB264">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC264">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AD264">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE264">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF264">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG264">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH264" t="inlineStr">
         <is>
@@ -43411,10 +43411,10 @@
         </is>
       </c>
       <c r="AJ264">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK264">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL264">
         <v>0</v>
@@ -44156,64 +44156,64 @@
         </is>
       </c>
       <c r="N269">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O269">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P269">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q269">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R269">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S269">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T269">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U269">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V269">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W269">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X269">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y269">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z269">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="AA269">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB269">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC269">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD269">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE269">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF269">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG269">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH269" t="inlineStr">
         <is>
@@ -44226,10 +44226,10 @@
         </is>
       </c>
       <c r="AJ269">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK269">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL269">
         <v>0</v>
@@ -44328,55 +44328,55 @@
         <v>3.25</v>
       </c>
       <c r="Q270">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R270">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S270">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T270">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U270">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V270">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W270">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X270">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y270">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z270">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA270">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB270">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AC270">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD270">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE270">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF270">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG270">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH270" t="inlineStr">
         <is>
@@ -44389,10 +44389,10 @@
         </is>
       </c>
       <c r="AJ270">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK270">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL270">
         <v>0</v>
@@ -44645,64 +44645,64 @@
         </is>
       </c>
       <c r="N272">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O272">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P272">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q272">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R272">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S272">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T272">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U272">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V272">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W272">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X272">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y272">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z272">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA272">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB272">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC272">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD272">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE272">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF272">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG272">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH272" t="inlineStr">
         <is>
@@ -44715,10 +44715,10 @@
         </is>
       </c>
       <c r="AJ272">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK272">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL272">
         <v>0</v>
@@ -46284,55 +46284,55 @@
         <v>1.44</v>
       </c>
       <c r="Q282">
-        <v>0</v>
+        <v>5.56</v>
       </c>
       <c r="R282">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="S282">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T282">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U282">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V282">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W282">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X282">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y282">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z282">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA282">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB282">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC282">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD282">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE282">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF282">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG282">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH282" t="inlineStr">
         <is>
@@ -46345,10 +46345,10 @@
         </is>
       </c>
       <c r="AJ282">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK282">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL282">
         <v>0</v>
@@ -46447,55 +46447,55 @@
         <v>2.5</v>
       </c>
       <c r="Q283">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R283">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S283">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T283">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U283">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V283">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W283">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X283">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y283">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z283">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AA283">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB283">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC283">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="AD283">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE283">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF283">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG283">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH283" t="inlineStr">
         <is>
@@ -46508,10 +46508,10 @@
         </is>
       </c>
       <c r="AJ283">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK283">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL283">
         <v>0</v>
@@ -46610,34 +46610,34 @@
         <v>3.59</v>
       </c>
       <c r="Q284">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R284">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S284">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T284">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U284">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V284">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W284">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X284">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y284">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z284">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA284">
         <v>1.96</v>
@@ -46646,19 +46646,19 @@
         <v>1.85</v>
       </c>
       <c r="AC284">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD284">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE284">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF284">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG284">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH284" t="inlineStr">
         <is>
@@ -46671,10 +46671,10 @@
         </is>
       </c>
       <c r="AJ284">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK284">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL284">
         <v>0</v>
@@ -46773,55 +46773,55 @@
         <v>2.63</v>
       </c>
       <c r="Q285">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R285">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S285">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T285">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U285">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V285">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W285">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X285">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y285">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z285">
-        <v>0</v>
+        <v>5.07</v>
       </c>
       <c r="AA285">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB285">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC285">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD285">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE285">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF285">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG285">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH285" t="inlineStr">
         <is>
@@ -46834,10 +46834,10 @@
         </is>
       </c>
       <c r="AJ285">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK285">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL285">
         <v>0</v>
@@ -46936,55 +46936,55 @@
         <v>4.63</v>
       </c>
       <c r="Q286">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R286">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S286">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T286">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U286">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V286">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W286">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X286">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y286">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z286">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA286">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB286">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC286">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD286">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE286">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF286">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG286">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH286" t="inlineStr">
         <is>
@@ -46997,10 +46997,10 @@
         </is>
       </c>
       <c r="AJ286">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK286">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AL286">
         <v>0</v>
@@ -47588,34 +47588,34 @@
         <v>3.74</v>
       </c>
       <c r="Q290">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R290">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S290">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T290">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U290">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V290">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W290">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X290">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y290">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z290">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA290">
         <v>1.79</v>
@@ -47624,19 +47624,19 @@
         <v>1.97</v>
       </c>
       <c r="AC290">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AD290">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE290">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF290">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG290">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH290" t="inlineStr">
         <is>
@@ -47649,10 +47649,10 @@
         </is>
       </c>
       <c r="AJ290">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK290">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL290">
         <v>0</v>
@@ -47914,55 +47914,55 @@
         <v>3.28</v>
       </c>
       <c r="Q292">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R292">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S292">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T292">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U292">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V292">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W292">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X292">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y292">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z292">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA292">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB292">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC292">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD292">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE292">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF292">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG292">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH292" t="inlineStr">
         <is>
@@ -47975,10 +47975,10 @@
         </is>
       </c>
       <c r="AJ292">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK292">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL292">
         <v>0</v>
@@ -48270,10 +48270,10 @@
         <v>0</v>
       </c>
       <c r="AA294">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB294">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC294">
         <v>0</v>
@@ -48403,34 +48403,34 @@
         <v>4.11</v>
       </c>
       <c r="Q295">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R295">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S295">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T295">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U295">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V295">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W295">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X295">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y295">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z295">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA295">
         <v>1.94</v>
@@ -48439,19 +48439,19 @@
         <v>1.85</v>
       </c>
       <c r="AC295">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AD295">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE295">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF295">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG295">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH295" t="inlineStr">
         <is>
@@ -48464,10 +48464,10 @@
         </is>
       </c>
       <c r="AJ295">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK295">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL295">
         <v>0</v>
@@ -48566,34 +48566,34 @@
         <v>4.09</v>
       </c>
       <c r="Q296">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="R296">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="S296">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T296">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U296">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V296">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W296">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X296">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y296">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z296">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA296">
         <v>1.61</v>
@@ -48602,19 +48602,19 @@
         <v>2.2</v>
       </c>
       <c r="AC296">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD296">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE296">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF296">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG296">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH296" t="inlineStr">
         <is>
@@ -48627,10 +48627,10 @@
         </is>
       </c>
       <c r="AJ296">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK296">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AL296">
         <v>0</v>
@@ -49372,64 +49372,64 @@
         </is>
       </c>
       <c r="N301">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O301">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P301">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q301">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="R301">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S301">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T301">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="U301">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V301">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W301">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X301">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y301">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z301">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA301">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB301">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC301">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AD301">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE301">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF301">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG301">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH301" t="inlineStr">
         <is>
@@ -49442,10 +49442,10 @@
         </is>
       </c>
       <c r="AJ301">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK301">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL301">
         <v>0</v>
@@ -50513,64 +50513,64 @@
         </is>
       </c>
       <c r="N308">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O308">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P308">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q308">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R308">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S308">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T308">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U308">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V308">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W308">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X308">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y308">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z308">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA308">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB308">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC308">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD308">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE308">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF308">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG308">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH308" t="inlineStr">
         <is>
@@ -50583,10 +50583,10 @@
         </is>
       </c>
       <c r="AJ308">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK308">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL308">
         <v>0</v>
@@ -50685,55 +50685,55 @@
         <v>4.95</v>
       </c>
       <c r="Q309">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R309">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S309">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T309">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U309">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V309">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W309">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X309">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y309">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z309">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA309">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB309">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC309">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD309">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE309">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF309">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG309">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH309" t="inlineStr">
         <is>
@@ -50746,10 +50746,10 @@
         </is>
       </c>
       <c r="AJ309">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK309">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AL309">
         <v>0</v>
@@ -50878,10 +50878,10 @@
         <v>0</v>
       </c>
       <c r="AA310">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB310">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC310">
         <v>0</v>
@@ -51011,34 +51011,34 @@
         <v>3.22</v>
       </c>
       <c r="Q311">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R311">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S311">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T311">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U311">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V311">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W311">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X311">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y311">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z311">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA311">
         <v>1.99</v>
@@ -51047,19 +51047,19 @@
         <v>1.78</v>
       </c>
       <c r="AC311">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="AD311">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE311">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF311">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG311">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH311" t="inlineStr">
         <is>
@@ -51072,10 +51072,10 @@
         </is>
       </c>
       <c r="AJ311">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK311">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL311">
         <v>0</v>
@@ -51459,12 +51459,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G314">
@@ -51622,12 +51622,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G315">
@@ -51948,12 +51948,12 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G317">
@@ -51980,64 +51980,64 @@
         </is>
       </c>
       <c r="N317">
+        <v>1.46</v>
+      </c>
+      <c r="O317">
+        <v>4.33</v>
+      </c>
+      <c r="P317">
+        <v>6.12</v>
+      </c>
+      <c r="Q317">
+        <v>1.91</v>
+      </c>
+      <c r="R317">
+        <v>2.38</v>
+      </c>
+      <c r="S317">
+        <v>1.3</v>
+      </c>
+      <c r="T317">
+        <v>3.3</v>
+      </c>
+      <c r="U317">
+        <v>2.4</v>
+      </c>
+      <c r="V317">
+        <v>1.5</v>
+      </c>
+      <c r="W317">
+        <v>1.11</v>
+      </c>
+      <c r="X317">
+        <v>1.03</v>
+      </c>
+      <c r="Y317">
+        <v>1.23</v>
+      </c>
+      <c r="Z317">
+        <v>3.8</v>
+      </c>
+      <c r="AA317">
+        <v>1.65</v>
+      </c>
+      <c r="AB317">
+        <v>2.1</v>
+      </c>
+      <c r="AC317">
+        <v>2.62</v>
+      </c>
+      <c r="AD317">
+        <v>1.38</v>
+      </c>
+      <c r="AE317">
+        <v>1.12</v>
+      </c>
+      <c r="AF317">
         <v>1.85</v>
       </c>
-      <c r="O317">
-        <v>3.38</v>
-      </c>
-      <c r="P317">
-        <v>4.12</v>
-      </c>
-      <c r="Q317">
-        <v>0</v>
-      </c>
-      <c r="R317">
-        <v>0</v>
-      </c>
-      <c r="S317">
-        <v>0</v>
-      </c>
-      <c r="T317">
-        <v>0</v>
-      </c>
-      <c r="U317">
-        <v>0</v>
-      </c>
-      <c r="V317">
-        <v>0</v>
-      </c>
-      <c r="W317">
-        <v>0</v>
-      </c>
-      <c r="X317">
-        <v>0</v>
-      </c>
-      <c r="Y317">
-        <v>0</v>
-      </c>
-      <c r="Z317">
-        <v>0</v>
-      </c>
-      <c r="AA317">
-        <v>2.05</v>
-      </c>
-      <c r="AB317">
-        <v>1.68</v>
-      </c>
-      <c r="AC317">
-        <v>0</v>
-      </c>
-      <c r="AD317">
-        <v>0</v>
-      </c>
-      <c r="AE317">
-        <v>0</v>
-      </c>
-      <c r="AF317">
-        <v>0</v>
-      </c>
       <c r="AG317">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH317" t="inlineStr">
         <is>
@@ -52050,10 +52050,10 @@
         </is>
       </c>
       <c r="AJ317">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK317">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AL317">
         <v>0</v>
@@ -52111,12 +52111,12 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G318">
@@ -52143,64 +52143,64 @@
         </is>
       </c>
       <c r="N318">
-        <v>1.46</v>
+        <v>1.85</v>
       </c>
       <c r="O318">
-        <v>4.33</v>
+        <v>3.38</v>
       </c>
       <c r="P318">
-        <v>6.12</v>
+        <v>4.12</v>
       </c>
       <c r="Q318">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R318">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S318">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T318">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U318">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V318">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W318">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X318">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y318">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z318">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA318">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AB318">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="AC318">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD318">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE318">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF318">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG318">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH318" t="inlineStr">
         <is>
@@ -52213,10 +52213,10 @@
         </is>
       </c>
       <c r="AJ318">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK318">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL318">
         <v>0</v>
@@ -52478,55 +52478,55 @@
         <v>2.47</v>
       </c>
       <c r="Q320">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R320">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S320">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T320">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U320">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V320">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W320">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X320">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y320">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z320">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA320">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB320">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC320">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD320">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE320">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF320">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG320">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AH320" t="inlineStr">
         <is>
@@ -52539,10 +52539,10 @@
         </is>
       </c>
       <c r="AJ320">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK320">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL320">
         <v>0</v>
@@ -52641,55 +52641,55 @@
         <v>1.53</v>
       </c>
       <c r="Q321">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="R321">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S321">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T321">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="U321">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V321">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W321">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X321">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y321">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z321">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA321">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB321">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AC321">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AD321">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE321">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF321">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG321">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH321" t="inlineStr">
         <is>
@@ -52702,10 +52702,10 @@
         </is>
       </c>
       <c r="AJ321">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK321">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL321">
         <v>0</v>
@@ -52804,40 +52804,40 @@
         <v>10.53</v>
       </c>
       <c r="Q322">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="R322">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S322">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T322">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U322">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V322">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W322">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X322">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y322">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z322">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA322">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB322">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AC322">
         <v>1.95</v>
@@ -52846,13 +52846,13 @@
         <v>1.87</v>
       </c>
       <c r="AE322">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF322">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG322">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH322" t="inlineStr">
         <is>
@@ -52865,10 +52865,10 @@
         </is>
       </c>
       <c r="AJ322">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK322">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AL322">
         <v>0</v>
@@ -52967,55 +52967,55 @@
         <v>2.9</v>
       </c>
       <c r="Q323">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R323">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S323">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T323">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U323">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V323">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W323">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X323">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y323">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z323">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA323">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB323">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC323">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD323">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE323">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF323">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG323">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH323" t="inlineStr">
         <is>
@@ -53028,10 +53028,10 @@
         </is>
       </c>
       <c r="AJ323">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK323">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL323">
         <v>0</v>
@@ -53293,55 +53293,55 @@
         <v>1.81</v>
       </c>
       <c r="Q325">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R325">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S325">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T325">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U325">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V325">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W325">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X325">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y325">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z325">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA325">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AB325">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC325">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD325">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE325">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF325">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG325">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH325" t="inlineStr">
         <is>
@@ -53354,10 +53354,10 @@
         </is>
       </c>
       <c r="AJ325">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK325">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL325">
         <v>0</v>
@@ -53456,55 +53456,55 @@
         <v>4.27</v>
       </c>
       <c r="Q326">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R326">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S326">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T326">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U326">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V326">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W326">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X326">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y326">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z326">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA326">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB326">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC326">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD326">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE326">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF326">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG326">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH326" t="inlineStr">
         <is>
@@ -53517,10 +53517,10 @@
         </is>
       </c>
       <c r="AJ326">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK326">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AL326">
         <v>0</v>
@@ -53619,55 +53619,55 @@
         <v>1.79</v>
       </c>
       <c r="Q327">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R327">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S327">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T327">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U327">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="V327">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W327">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X327">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y327">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z327">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA327">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB327">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC327">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AD327">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE327">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF327">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG327">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH327" t="inlineStr">
         <is>
@@ -53680,10 +53680,10 @@
         </is>
       </c>
       <c r="AJ327">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK327">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL327">
         <v>0</v>
@@ -53782,55 +53782,55 @@
         <v>2.88</v>
       </c>
       <c r="Q328">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="R328">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S328">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T328">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="U328">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V328">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W328">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X328">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y328">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z328">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA328">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB328">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AC328">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD328">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE328">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF328">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG328">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AH328" t="inlineStr">
         <is>
@@ -53843,10 +53843,10 @@
         </is>
       </c>
       <c r="AJ328">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK328">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL328">
         <v>0</v>
@@ -54434,34 +54434,34 @@
         <v>4.96</v>
       </c>
       <c r="Q332">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R332">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S332">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T332">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U332">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V332">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W332">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X332">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y332">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z332">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA332">
         <v>1.91</v>
@@ -54470,19 +54470,19 @@
         <v>1.85</v>
       </c>
       <c r="AC332">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD332">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE332">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF332">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG332">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH332" t="inlineStr">
         <is>
@@ -54495,10 +54495,10 @@
         </is>
       </c>
       <c r="AJ332">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK332">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL332">
         <v>0</v>

--- a/jogos_2026-11-01.xlsx
+++ b/jogos_2026-11-01.xlsx
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>4.88</v>
+        <v>1.18</v>
       </c>
       <c r="O117">
-        <v>4.3</v>
+        <v>7</v>
       </c>
       <c r="P117">
-        <v>1.58</v>
+        <v>12.2</v>
       </c>
       <c r="Q117">
-        <v>4.4</v>
+        <v>1.49</v>
       </c>
       <c r="R117">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="S117">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="T117">
-        <v>3.64</v>
+        <v>5.2</v>
       </c>
       <c r="U117">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="V117">
-        <v>1.64</v>
+        <v>1.98</v>
       </c>
       <c r="W117">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="X117">
+        <v>1</v>
+      </c>
+      <c r="Y117">
         <v>1.02</v>
       </c>
-      <c r="Y117">
-        <v>1.1</v>
-      </c>
       <c r="Z117">
-        <v>5.05</v>
+        <v>7.7</v>
       </c>
       <c r="AA117">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AB117">
-        <v>2.43</v>
+        <v>3.8</v>
       </c>
       <c r="AC117">
-        <v>2.21</v>
+        <v>1.83</v>
       </c>
       <c r="AD117">
+        <v>1.98</v>
+      </c>
+      <c r="AE117">
+        <v>1.46</v>
+      </c>
+      <c r="AF117">
         <v>1.62</v>
       </c>
-      <c r="AE117">
-        <v>1.21</v>
-      </c>
-      <c r="AF117">
-        <v>1.49</v>
-      </c>
       <c r="AG117">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="AK117">
-        <v>1.15</v>
+        <v>4.06</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,64 +19543,64 @@
         </is>
       </c>
       <c r="N118">
-        <v>1.18</v>
+        <v>4.88</v>
       </c>
       <c r="O118">
-        <v>7</v>
+        <v>4.3</v>
       </c>
       <c r="P118">
-        <v>12.2</v>
+        <v>1.58</v>
       </c>
       <c r="Q118">
+        <v>4.4</v>
+      </c>
+      <c r="R118">
+        <v>2.4</v>
+      </c>
+      <c r="S118">
+        <v>1.21</v>
+      </c>
+      <c r="T118">
+        <v>3.64</v>
+      </c>
+      <c r="U118">
+        <v>2.07</v>
+      </c>
+      <c r="V118">
+        <v>1.64</v>
+      </c>
+      <c r="W118">
+        <v>1.15</v>
+      </c>
+      <c r="X118">
+        <v>1.02</v>
+      </c>
+      <c r="Y118">
+        <v>1.1</v>
+      </c>
+      <c r="Z118">
+        <v>5.05</v>
+      </c>
+      <c r="AA118">
+        <v>1.44</v>
+      </c>
+      <c r="AB118">
+        <v>2.43</v>
+      </c>
+      <c r="AC118">
+        <v>2.21</v>
+      </c>
+      <c r="AD118">
+        <v>1.62</v>
+      </c>
+      <c r="AE118">
+        <v>1.21</v>
+      </c>
+      <c r="AF118">
         <v>1.49</v>
       </c>
-      <c r="R118">
-        <v>3.1</v>
-      </c>
-      <c r="S118">
-        <v>1.1</v>
-      </c>
-      <c r="T118">
-        <v>5.2</v>
-      </c>
-      <c r="U118">
-        <v>1.75</v>
-      </c>
-      <c r="V118">
-        <v>1.98</v>
-      </c>
-      <c r="W118">
-        <v>1.29</v>
-      </c>
-      <c r="X118">
-        <v>1</v>
-      </c>
-      <c r="Y118">
-        <v>1.02</v>
-      </c>
-      <c r="Z118">
-        <v>7.7</v>
-      </c>
-      <c r="AA118">
-        <v>1.28</v>
-      </c>
-      <c r="AB118">
-        <v>3.8</v>
-      </c>
-      <c r="AC118">
-        <v>1.83</v>
-      </c>
-      <c r="AD118">
-        <v>1.98</v>
-      </c>
-      <c r="AE118">
-        <v>1.46</v>
-      </c>
-      <c r="AF118">
-        <v>1.62</v>
-      </c>
       <c r="AG118">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="AK118">
-        <v>4.06</v>
+        <v>1.15</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -39886,12 +39886,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G243">
@@ -39918,80 +39918,80 @@
         </is>
       </c>
       <c r="N243">
-        <v>2.39</v>
+        <v>1.28</v>
       </c>
       <c r="O243">
+        <v>5.15</v>
+      </c>
+      <c r="P243">
+        <v>7.4</v>
+      </c>
+      <c r="Q243">
+        <v>1.73</v>
+      </c>
+      <c r="R243">
+        <v>2.6</v>
+      </c>
+      <c r="S243">
+        <v>1.22</v>
+      </c>
+      <c r="T243">
         <v>3.8</v>
       </c>
-      <c r="P243">
+      <c r="U243">
+        <v>2.35</v>
+      </c>
+      <c r="V243">
+        <v>1.59</v>
+      </c>
+      <c r="W243">
+        <v>1.13</v>
+      </c>
+      <c r="X243">
+        <v>1</v>
+      </c>
+      <c r="Y243">
+        <v>1.13</v>
+      </c>
+      <c r="Z243">
+        <v>5.25</v>
+      </c>
+      <c r="AA243">
+        <v>1.56</v>
+      </c>
+      <c r="AB243">
+        <v>2.5</v>
+      </c>
+      <c r="AC243">
+        <v>2.24</v>
+      </c>
+      <c r="AD243">
+        <v>1.56</v>
+      </c>
+      <c r="AE243">
+        <v>1.2</v>
+      </c>
+      <c r="AF243">
+        <v>1.75</v>
+      </c>
+      <c r="AG243">
+        <v>2</v>
+      </c>
+      <c r="AH243" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI243" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ243">
+        <v>1.14</v>
+      </c>
+      <c r="AK243">
         <v>3</v>
-      </c>
-      <c r="Q243">
-        <v>2.66</v>
-      </c>
-      <c r="R243">
-        <v>2.37</v>
-      </c>
-      <c r="S243">
-        <v>1.3</v>
-      </c>
-      <c r="T243">
-        <v>3.2</v>
-      </c>
-      <c r="U243">
-        <v>2.5</v>
-      </c>
-      <c r="V243">
-        <v>1.44</v>
-      </c>
-      <c r="W243">
-        <v>1.11</v>
-      </c>
-      <c r="X243">
-        <v>1.02</v>
-      </c>
-      <c r="Y243">
-        <v>1.24</v>
-      </c>
-      <c r="Z243">
-        <v>3.9</v>
-      </c>
-      <c r="AA243">
-        <v>1.7</v>
-      </c>
-      <c r="AB243">
-        <v>2.05</v>
-      </c>
-      <c r="AC243">
-        <v>2.99</v>
-      </c>
-      <c r="AD243">
-        <v>1.41</v>
-      </c>
-      <c r="AE243">
-        <v>1.11</v>
-      </c>
-      <c r="AF243">
-        <v>1.62</v>
-      </c>
-      <c r="AG243">
-        <v>2.2</v>
-      </c>
-      <c r="AH243" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI243" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ243">
-        <v>1.3</v>
-      </c>
-      <c r="AK243">
-        <v>1.6</v>
       </c>
       <c r="AL243">
         <v>0</v>
@@ -40049,12 +40049,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G244">
@@ -40081,64 +40081,64 @@
         </is>
       </c>
       <c r="N244">
-        <v>1.39</v>
+        <v>2.39</v>
       </c>
       <c r="O244">
-        <v>5.15</v>
+        <v>3.8</v>
       </c>
       <c r="P244">
-        <v>7.4</v>
+        <v>3</v>
       </c>
       <c r="Q244">
-        <v>1.73</v>
+        <v>2.66</v>
       </c>
       <c r="R244">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="S244">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T244">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="U244">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="V244">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="W244">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X244">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y244">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="Z244">
-        <v>5.25</v>
+        <v>3.9</v>
       </c>
       <c r="AA244">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AB244">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="AC244">
-        <v>2.24</v>
+        <v>2.99</v>
       </c>
       <c r="AD244">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="AE244">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AF244">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG244">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH244" t="inlineStr">
         <is>
@@ -40151,10 +40151,10 @@
         </is>
       </c>
       <c r="AJ244">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AK244">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="AL244">
         <v>0</v>

--- a/jogos_2026-11-01.xlsx
+++ b/jogos_2026-11-01.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="O2">
-        <v>4.62</v>
+        <v>4.75</v>
       </c>
       <c r="P2">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="Q2">
         <v>1.92</v>
@@ -665,7 +665,7 @@
         <v>1.12</v>
       </c>
       <c r="X2">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
         <v>1.11</v>
@@ -674,16 +674,16 @@
         <v>4.65</v>
       </c>
       <c r="AA2">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AB2">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="AC2">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AD2">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AE2">
         <v>1.2</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AK2">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -2754,34 +2754,34 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="O15">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="P15">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="Q15">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="R15">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="S15">
         <v>1.29</v>
       </c>
       <c r="T15">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="U15">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="V15">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W15">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X15">
         <v>1.01</v>
@@ -2793,7 +2793,7 @@
         <v>4.54</v>
       </c>
       <c r="AA15">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AB15">
         <v>2.1</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="AK15">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.02</v>
+        <v>2.73</v>
       </c>
       <c r="O16">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="P16">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
       <c r="Q16">
         <v>3.3</v>
@@ -2944,7 +2944,7 @@
         <v>1.44</v>
       </c>
       <c r="W16">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X16">
         <v>1.04</v>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.51</v>
+        <v>1.18</v>
       </c>
       <c r="AK16">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3415,55 +3415,55 @@
         <v>0</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>4.45</v>
+        <v>2.78</v>
       </c>
       <c r="O20">
-        <v>3.88</v>
+        <v>3.72</v>
       </c>
       <c r="P20">
-        <v>1.88</v>
+        <v>2.09</v>
       </c>
       <c r="Q20">
         <v>3.74</v>
@@ -3735,16 +3735,16 @@
         <v>1.28</v>
       </c>
       <c r="O21">
-        <v>5.5</v>
+        <v>5.95</v>
       </c>
       <c r="P21">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q21">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="R21">
-        <v>2.81</v>
+        <v>2.46</v>
       </c>
       <c r="S21">
         <v>1.29</v>
@@ -3765,28 +3765,28 @@
         <v>1</v>
       </c>
       <c r="Y21">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z21">
-        <v>4.54</v>
+        <v>4.66</v>
       </c>
       <c r="AA21">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AB21">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="AC21">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="AD21">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="AE21">
         <v>1.2</v>
       </c>
       <c r="AF21">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AG21">
         <v>1.75</v>
@@ -3805,7 +3805,7 @@
         <v>1.1</v>
       </c>
       <c r="AK21">
-        <v>3.23</v>
+        <v>3.33</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,34 +3895,34 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="O22">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="P22">
-        <v>5.34</v>
+        <v>5</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X22">
         <v>0</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q24">
         <v>2.03</v>
@@ -4248,7 +4248,7 @@
         <v>1.53</v>
       </c>
       <c r="W24">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X24">
         <v>1.02</v>
@@ -4260,10 +4260,10 @@
         <v>3.88</v>
       </c>
       <c r="AA24">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB24">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC24">
         <v>2.59</v>
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X25">
         <v>0</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4749,10 +4749,10 @@
         <v>0</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC27">
         <v>0</v>
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5691,61 +5691,61 @@
         <v>2.2</v>
       </c>
       <c r="O33">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P33">
-        <v>3.22</v>
+        <v>2.87</v>
       </c>
       <c r="Q33">
-        <v>2.87</v>
+        <v>2.99</v>
       </c>
       <c r="R33">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="S33">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="T33">
         <v>2.8</v>
       </c>
       <c r="U33">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="V33">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W33">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y33">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="Z33">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="AA33">
         <v>2.08</v>
       </c>
       <c r="AB33">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AC33">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="AD33">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE33">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF33">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AG33">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK33">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6216,10 +6216,10 @@
         <v>0</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC36">
         <v>0</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Peña Deportiva</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Mallorca II</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -8172,10 +8172,10 @@
         <v>0</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>La Nucía</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mallorca II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8335,10 +8335,10 @@
         <v>0</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>La Nucía</t>
+          <t>Peña Deportiva</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -8785,34 +8785,34 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="O52">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="P52">
         <v>2.9</v>
       </c>
       <c r="Q52">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="R52">
         <v>2.3</v>
       </c>
       <c r="S52">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T52">
-        <v>3.46</v>
+        <v>3.8</v>
       </c>
       <c r="U52">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V52">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W52">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X52">
         <v>1</v>
@@ -8824,22 +8824,22 @@
         <v>4.43</v>
       </c>
       <c r="AA52">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AB52">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="AC52">
-        <v>2.47</v>
+        <v>2.51</v>
       </c>
       <c r="AD52">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AE52">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AF52">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG52">
         <v>2.45</v>
@@ -8858,7 +8858,7 @@
         <v>1.25</v>
       </c>
       <c r="AK52">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O53">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P53">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="Q53">
         <v>3.62</v>
@@ -8987,10 +8987,10 @@
         <v>3.2</v>
       </c>
       <c r="AA53">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AB53">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AC53">
         <v>3.2</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>5.23</v>
+        <v>5.25</v>
       </c>
       <c r="O58">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="P58">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="Q58">
         <v>6.28</v>
@@ -9802,10 +9802,10 @@
         <v>3.08</v>
       </c>
       <c r="AA58">
-        <v>2.03</v>
+        <v>1.94</v>
       </c>
       <c r="AB58">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="AC58">
         <v>3.34</v>
@@ -9929,16 +9929,16 @@
         <v>1.33</v>
       </c>
       <c r="O59">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="P59">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="Q59">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="R59">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="S59">
         <v>1.17</v>
@@ -9947,7 +9947,7 @@
         <v>4.5</v>
       </c>
       <c r="U59">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="V59">
         <v>1.75</v>
@@ -9974,7 +9974,7 @@
         <v>2.06</v>
       </c>
       <c r="AD59">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AE59">
         <v>1.37</v>
@@ -9983,7 +9983,7 @@
         <v>1.62</v>
       </c>
       <c r="AG59">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>1.11</v>
       </c>
       <c r="AK59">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10098,55 +10098,55 @@
         <v>0</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>7.19</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="T60">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="W60">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z60">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE60">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF60">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG60">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK60">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10261,55 +10261,55 @@
         <v>0</v>
       </c>
       <c r="Q61">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T61">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U61">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V61">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="W61">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X61">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z61">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA61">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB61">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD61">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE61">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF61">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG61">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK61">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10741,25 +10741,25 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O64">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="P64">
-        <v>2.97</v>
+        <v>2.75</v>
       </c>
       <c r="Q64">
-        <v>2.79</v>
+        <v>2.71</v>
       </c>
       <c r="R64">
-        <v>2.34</v>
+        <v>2.21</v>
       </c>
       <c r="S64">
         <v>1.3</v>
       </c>
       <c r="T64">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="U64">
         <v>2.5</v>
@@ -10780,22 +10780,22 @@
         <v>4.2</v>
       </c>
       <c r="AA64">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AB64">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="AC64">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="AD64">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AE64">
         <v>1.16</v>
       </c>
       <c r="AF64">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="AG64">
         <v>2.39</v>
@@ -10904,19 +10904,19 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="O65">
-        <v>3.72</v>
+        <v>3.27</v>
       </c>
       <c r="P65">
-        <v>3.87</v>
+        <v>2.78</v>
       </c>
       <c r="Q65">
+        <v>2.55</v>
+      </c>
+      <c r="R65">
         <v>2.34</v>
-      </c>
-      <c r="R65">
-        <v>2.24</v>
       </c>
       <c r="S65">
         <v>1.3</v>
@@ -10928,34 +10928,34 @@
         <v>2.4</v>
       </c>
       <c r="V65">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W65">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X65">
         <v>1.03</v>
       </c>
       <c r="Y65">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z65">
-        <v>4.05</v>
+        <v>4.04</v>
       </c>
       <c r="AA65">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AB65">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AC65">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="AD65">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE65">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF65">
         <v>1.62</v>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK65">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11432,10 +11432,10 @@
         <v>0</v>
       </c>
       <c r="AA68">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AB68">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AC68">
         <v>0</v>
@@ -11571,7 +11571,7 @@
         <v>3.44</v>
       </c>
       <c r="S69">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="T69">
         <v>5.5</v>
@@ -11580,7 +11580,7 @@
         <v>1.67</v>
       </c>
       <c r="V69">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="W69">
         <v>1.33</v>
@@ -11595,19 +11595,19 @@
         <v>9.300000000000001</v>
       </c>
       <c r="AA69">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AB69">
         <v>4.1</v>
       </c>
       <c r="AC69">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AD69">
-        <v>2.21</v>
+        <v>2.42</v>
       </c>
       <c r="AE69">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AF69">
         <v>1.7</v>
@@ -11626,7 +11626,7 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK69">
         <v>5.45</v>
@@ -12543,22 +12543,22 @@
         <v>1.97</v>
       </c>
       <c r="Q75">
-        <v>4.09</v>
+        <v>4.05</v>
       </c>
       <c r="R75">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="S75">
         <v>1.33</v>
       </c>
       <c r="T75">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="U75">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="V75">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W75">
         <v>1.09</v>
@@ -12567,10 +12567,10 @@
         <v>1.01</v>
       </c>
       <c r="Y75">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z75">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AA75">
         <v>1.8</v>
@@ -12579,19 +12579,19 @@
         <v>2</v>
       </c>
       <c r="AC75">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AD75">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE75">
         <v>1.06</v>
       </c>
       <c r="AF75">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AG75">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>1.23</v>
       </c>
       <c r="AK75">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O78">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P78">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
       <c r="Q78">
         <v>2.71</v>
@@ -18085,55 +18085,55 @@
         <v>0</v>
       </c>
       <c r="Q109">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="R109">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S109">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T109">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U109">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V109">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W109">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X109">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y109">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z109">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA109">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB109">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC109">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD109">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE109">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF109">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG109">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK109">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -22477,13 +22477,13 @@
         </is>
       </c>
       <c r="N136">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O136">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P136">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -23618,64 +23618,64 @@
         </is>
       </c>
       <c r="N143">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O143">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P143">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q143">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R143">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S143">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T143">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U143">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V143">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W143">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X143">
         <v>0</v>
       </c>
       <c r="Y143">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z143">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AA143">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB143">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC143">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD143">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE143">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF143">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG143">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23688,10 +23688,10 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK143">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -24605,55 +24605,55 @@
         <v>0</v>
       </c>
       <c r="Q149">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R149">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S149">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T149">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U149">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V149">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W149">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X149">
         <v>0</v>
       </c>
       <c r="Y149">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z149">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA149">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB149">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC149">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD149">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE149">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF149">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG149">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH149" t="inlineStr">
         <is>
@@ -24666,10 +24666,10 @@
         </is>
       </c>
       <c r="AJ149">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK149">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL149">
         <v>0</v>
@@ -31605,13 +31605,13 @@
         </is>
       </c>
       <c r="N192">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O192">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P192">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q192">
         <v>0</v>
@@ -31644,10 +31644,10 @@
         <v>0</v>
       </c>
       <c r="AA192">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB192">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC192">
         <v>0</v>
@@ -31768,13 +31768,13 @@
         </is>
       </c>
       <c r="N193">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O193">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P193">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q193">
         <v>0</v>
@@ -31807,10 +31807,10 @@
         <v>0</v>
       </c>
       <c r="AA193">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB193">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC193">
         <v>0</v>
@@ -35354,13 +35354,13 @@
         </is>
       </c>
       <c r="N215">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O215">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P215">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q215">
         <v>0</v>
@@ -35393,10 +35393,10 @@
         <v>0</v>
       </c>
       <c r="AA215">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB215">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC215">
         <v>0</v>
@@ -35517,13 +35517,13 @@
         </is>
       </c>
       <c r="N216">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O216">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P216">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q216">
         <v>0</v>
@@ -35556,10 +35556,10 @@
         <v>0</v>
       </c>
       <c r="AA216">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB216">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC216">
         <v>0</v>
@@ -37799,64 +37799,64 @@
         </is>
       </c>
       <c r="N230">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O230">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P230">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="Q230">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R230">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S230">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T230">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U230">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V230">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W230">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X230">
         <v>0</v>
       </c>
       <c r="Y230">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z230">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA230">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB230">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC230">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD230">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE230">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF230">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG230">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH230" t="inlineStr">
         <is>
@@ -37869,10 +37869,10 @@
         </is>
       </c>
       <c r="AJ230">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK230">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL230">
         <v>0</v>
@@ -37962,64 +37962,64 @@
         </is>
       </c>
       <c r="N231">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O231">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="P231">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q231">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R231">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S231">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T231">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U231">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V231">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W231">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X231">
         <v>0</v>
       </c>
       <c r="Y231">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z231">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA231">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB231">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC231">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD231">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE231">
         <v>0</v>
       </c>
       <c r="AF231">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG231">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH231" t="inlineStr">
         <is>
@@ -38032,10 +38032,10 @@
         </is>
       </c>
       <c r="AJ231">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK231">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL231">
         <v>0</v>
@@ -38125,64 +38125,64 @@
         </is>
       </c>
       <c r="N232">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O232">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P232">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="Q232">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R232">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S232">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T232">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U232">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V232">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W232">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X232">
         <v>0</v>
       </c>
       <c r="Y232">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z232">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA232">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB232">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC232">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD232">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE232">
         <v>0</v>
       </c>
       <c r="AF232">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG232">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH232" t="inlineStr">
         <is>
@@ -38195,10 +38195,10 @@
         </is>
       </c>
       <c r="AJ232">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK232">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL232">
         <v>0</v>
@@ -38288,13 +38288,13 @@
         </is>
       </c>
       <c r="N233">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O233">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P233">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q233">
         <v>0</v>
@@ -38327,10 +38327,10 @@
         <v>0</v>
       </c>
       <c r="AA233">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB233">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC233">
         <v>0</v>
@@ -41222,13 +41222,13 @@
         </is>
       </c>
       <c r="N251">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O251">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P251">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q251">
         <v>0</v>
@@ -41261,10 +41261,10 @@
         <v>0</v>
       </c>
       <c r="AA251">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB251">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC251">
         <v>0</v>
@@ -41385,13 +41385,13 @@
         </is>
       </c>
       <c r="N252">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O252">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P252">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="Q252">
         <v>0</v>
@@ -41424,10 +41424,10 @@
         <v>0</v>
       </c>
       <c r="AA252">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB252">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC252">
         <v>0</v>
@@ -42363,13 +42363,13 @@
         </is>
       </c>
       <c r="N258">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O258">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P258">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q258">
         <v>0</v>
@@ -42402,10 +42402,10 @@
         <v>0</v>
       </c>
       <c r="AA258">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB258">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC258">
         <v>0</v>
@@ -42852,64 +42852,64 @@
         </is>
       </c>
       <c r="N261">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="O261">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P261">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="Q261">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R261">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S261">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T261">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U261">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V261">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W261">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X261">
         <v>0</v>
       </c>
       <c r="Y261">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z261">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA261">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB261">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC261">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD261">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE261">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF261">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG261">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH261" t="inlineStr">
         <is>
@@ -42922,10 +42922,10 @@
         </is>
       </c>
       <c r="AJ261">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK261">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AL261">
         <v>0</v>
@@ -44971,13 +44971,13 @@
         </is>
       </c>
       <c r="N274">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O274">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P274">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q274">
         <v>0</v>
@@ -45010,10 +45010,10 @@
         <v>0</v>
       </c>
       <c r="AA274">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB274">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC274">
         <v>0</v>
@@ -47292,10 +47292,10 @@
         <v>0</v>
       </c>
       <c r="AA288">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB288">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC288">
         <v>0</v>
@@ -48394,13 +48394,13 @@
         </is>
       </c>
       <c r="N295">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O295">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P295">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q295">
         <v>0</v>
@@ -48433,10 +48433,10 @@
         <v>0</v>
       </c>
       <c r="AA295">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB295">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC295">
         <v>0</v>

--- a/jogos_2026-11-01.xlsx
+++ b/jogos_2026-11-01.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>3.03</v>
+        <v>2.8</v>
       </c>
       <c r="O3">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="P3">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q3">
         <v>3.2</v>
@@ -813,10 +813,10 @@
         <v>2.4</v>
       </c>
       <c r="S3">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T3">
-        <v>3.48</v>
+        <v>3.8</v>
       </c>
       <c r="U3">
         <v>2.25</v>
@@ -837,16 +837,16 @@
         <v>4.68</v>
       </c>
       <c r="AA3">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AB3">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AC3">
-        <v>2.37</v>
+        <v>2.28</v>
       </c>
       <c r="AD3">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AE3">
         <v>1.21</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AK3">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -988,7 +988,7 @@
         <v>1.42</v>
       </c>
       <c r="W4">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X4">
         <v>1.01</v>
@@ -1000,13 +1000,13 @@
         <v>3.5</v>
       </c>
       <c r="AA4">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AB4">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="AC4">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="AD4">
         <v>1.29</v>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AK4">
         <v>1.6</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="O5">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P5">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="Q5">
         <v>3.25</v>
@@ -1287,37 +1287,37 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="O6">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="P6">
-        <v>2.41</v>
+        <v>2.2</v>
       </c>
       <c r="Q6">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="R6">
         <v>2.2</v>
       </c>
       <c r="S6">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T6">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="U6">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="V6">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="W6">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X6">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
         <v>1.23</v>
@@ -1326,25 +1326,25 @@
         <v>3.42</v>
       </c>
       <c r="AA6">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AB6">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AC6">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="AD6">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE6">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF6">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AG6">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK6">
         <v>1.36</v>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="O7">
-        <v>5.45</v>
+        <v>5</v>
       </c>
       <c r="P7">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="Q7">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="R7">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="S7">
+        <v>1.22</v>
+      </c>
+      <c r="T7">
+        <v>3.9</v>
+      </c>
+      <c r="U7">
+        <v>2.1</v>
+      </c>
+      <c r="V7">
+        <v>1.7</v>
+      </c>
+      <c r="W7">
         <v>1.18</v>
       </c>
-      <c r="T7">
-        <v>3.85</v>
-      </c>
-      <c r="U7">
-        <v>2.08</v>
-      </c>
-      <c r="V7">
-        <v>1.64</v>
-      </c>
-      <c r="W7">
-        <v>1.14</v>
-      </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Z7">
-        <v>5.35</v>
+        <v>5.75</v>
       </c>
       <c r="AA7">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AB7">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AC7">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AD7">
         <v>1.63</v>
       </c>
       <c r="AE7">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AF7">
         <v>1.73</v>
       </c>
       <c r="AG7">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>1.07</v>
       </c>
       <c r="AK7">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,16 +1613,16 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
       <c r="O8">
-        <v>3.37</v>
+        <v>3.28</v>
       </c>
       <c r="P8">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="Q8">
-        <v>3.86</v>
+        <v>3.39</v>
       </c>
       <c r="R8">
         <v>1.99</v>
@@ -1634,13 +1634,13 @@
         <v>2.88</v>
       </c>
       <c r="U8">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="V8">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W8">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X8">
         <v>1</v>
@@ -1652,10 +1652,10 @@
         <v>2.97</v>
       </c>
       <c r="AA8">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="AB8">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AC8">
         <v>3.9</v>
@@ -1667,10 +1667,10 @@
         <v>1.05</v>
       </c>
       <c r="AF8">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG8">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1776,16 +1776,16 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.24</v>
+        <v>2.44</v>
       </c>
       <c r="O9">
-        <v>3.39</v>
+        <v>3.23</v>
       </c>
       <c r="P9">
-        <v>3.28</v>
+        <v>2.8</v>
       </c>
       <c r="Q9">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="R9">
         <v>1.99</v>
@@ -1803,7 +1803,7 @@
         <v>1.36</v>
       </c>
       <c r="W9">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X9">
         <v>1.04</v>
@@ -1815,10 +1815,10 @@
         <v>3.14</v>
       </c>
       <c r="AA9">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AB9">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AC9">
         <v>3.89</v>
@@ -1833,7 +1833,7 @@
         <v>1.83</v>
       </c>
       <c r="AG9">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AK9">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,34 +1939,34 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="O10">
-        <v>3.92</v>
+        <v>3.7</v>
       </c>
       <c r="P10">
-        <v>4.31</v>
+        <v>4.1</v>
       </c>
       <c r="Q10">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="R10">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="S10">
         <v>1.34</v>
       </c>
       <c r="T10">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="U10">
         <v>2.6</v>
       </c>
       <c r="V10">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W10">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X10">
         <v>1.02</v>
@@ -1978,25 +1978,25 @@
         <v>3.58</v>
       </c>
       <c r="AA10">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AB10">
         <v>1.98</v>
       </c>
       <c r="AC10">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="AD10">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE10">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF10">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG10">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK10">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q11">
         <v>2.24</v>
@@ -2135,31 +2135,31 @@
         <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z11">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA11">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AB11">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AC11">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AD11">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE11">
         <v>1.07</v>
       </c>
       <c r="AF11">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AG11">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>1.22</v>
       </c>
       <c r="AK11">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="O12">
-        <v>3.62</v>
+        <v>3.25</v>
       </c>
       <c r="P12">
-        <v>3.91</v>
+        <v>3.7</v>
       </c>
       <c r="Q12">
         <v>2.4</v>
@@ -2304,13 +2304,13 @@
         <v>3.5</v>
       </c>
       <c r="AA12">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AB12">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AC12">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AD12">
         <v>1.29</v>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK12">
         <v>1.9</v>
@@ -2437,55 +2437,55 @@
         <v>2.3</v>
       </c>
       <c r="Q13">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R13">
         <v>2.2</v>
       </c>
       <c r="S13">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T13">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="U13">
-        <v>2.51</v>
+        <v>2.58</v>
       </c>
       <c r="V13">
         <v>1.42</v>
       </c>
       <c r="W13">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X13">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y13">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z13">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="AA13">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AB13">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AC13">
-        <v>3.13</v>
+        <v>3.25</v>
       </c>
       <c r="AD13">
         <v>1.3</v>
       </c>
       <c r="AE13">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF13">
         <v>1.66</v>
       </c>
       <c r="AG13">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK13">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2600,16 +2600,16 @@
         <v>3.02</v>
       </c>
       <c r="Q14">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="R14">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="S14">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T14">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="U14">
         <v>2.8</v>
@@ -2618,28 +2618,28 @@
         <v>1.34</v>
       </c>
       <c r="W14">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X14">
         <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z14">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="AA14">
         <v>1.95</v>
       </c>
       <c r="AB14">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AC14">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AD14">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE14">
         <v>1.11</v>
@@ -2648,7 +2648,7 @@
         <v>1.73</v>
       </c>
       <c r="AG14">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK14">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3463,7 +3463,7 @@
         <v>1.47</v>
       </c>
       <c r="AG19">
-        <v>2.39</v>
+        <v>2.44</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="O22">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="P22">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Q22">
         <v>2</v>
@@ -3928,31 +3928,31 @@
         <v>0</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4393,28 +4393,28 @@
         <v>3.5</v>
       </c>
       <c r="Q25">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="R25">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="S25">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T25">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="U25">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="V25">
         <v>1.44</v>
       </c>
       <c r="W25">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y25">
         <v>1.2</v>
@@ -4441,7 +4441,7 @@
         <v>1.64</v>
       </c>
       <c r="AG25">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK25">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4556,55 +4556,55 @@
         <v>0</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X26">
         <v>0</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4719,34 +4719,34 @@
         <v>3.16</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA27">
         <v>2</v>
@@ -4755,19 +4755,19 @@
         <v>1.8</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -6349,55 +6349,55 @@
         <v>3.95</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6675,55 +6675,55 @@
         <v>5.01</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>12.1</v>
+        <v>9</v>
       </c>
       <c r="O40">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="P40">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X40">
         <v>0</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7001,55 +7001,55 @@
         <v>4.53</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="O48">
         <v>3.8</v>
       </c>
       <c r="P48">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X48">
         <v>0</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA48">
+        <v>1.71</v>
+      </c>
+      <c r="AB48">
+        <v>1.98</v>
+      </c>
+      <c r="AC48">
+        <v>2.74</v>
+      </c>
+      <c r="AD48">
+        <v>1.35</v>
+      </c>
+      <c r="AE48">
+        <v>1.1</v>
+      </c>
+      <c r="AF48">
         <v>1.75</v>
       </c>
-      <c r="AB48">
-        <v>2.05</v>
-      </c>
-      <c r="AC48">
-        <v>0</v>
-      </c>
-      <c r="AD48">
-        <v>0</v>
-      </c>
-      <c r="AE48">
-        <v>0</v>
-      </c>
-      <c r="AF48">
-        <v>0</v>
-      </c>
       <c r="AG48">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8305,55 +8305,55 @@
         <v>3.28</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X49">
         <v>0</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA49">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB49">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE49">
         <v>0</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8468,55 +8468,55 @@
         <v>1.8</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8794,10 +8794,10 @@
         <v>2.9</v>
       </c>
       <c r="Q52">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="R52">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S52">
         <v>1.22</v>
@@ -8824,13 +8824,13 @@
         <v>4.43</v>
       </c>
       <c r="AA52">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AB52">
         <v>2.27</v>
       </c>
       <c r="AC52">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="AD52">
         <v>1.53</v>
@@ -8858,7 +8858,7 @@
         <v>1.25</v>
       </c>
       <c r="AK52">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9772,7 +9772,7 @@
         <v>1.55</v>
       </c>
       <c r="Q58">
-        <v>6.28</v>
+        <v>5.95</v>
       </c>
       <c r="R58">
         <v>2.09</v>
@@ -9820,7 +9820,7 @@
         <v>1.96</v>
       </c>
       <c r="AG58">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         <v>1.33</v>
       </c>
       <c r="O59">
-        <v>5.2</v>
+        <v>5.75</v>
       </c>
       <c r="P59">
         <v>7.5</v>
@@ -9971,10 +9971,10 @@
         <v>3</v>
       </c>
       <c r="AC59">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="AD59">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AE59">
         <v>1.37</v>
@@ -9996,7 +9996,7 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK59">
         <v>3.4</v>
@@ -12573,7 +12573,7 @@
         <v>3.42</v>
       </c>
       <c r="AA75">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AB75">
         <v>2</v>
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="O86">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="P86">
-        <v>4.82</v>
+        <v>5</v>
       </c>
       <c r="Q86">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S86">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T86">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U86">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V86">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W86">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X86">
         <v>0</v>
       </c>
       <c r="Y86">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z86">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA86">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AD86">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG86">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK86">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14490,22 +14490,22 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="O87">
-        <v>3.92</v>
+        <v>3.75</v>
       </c>
       <c r="P87">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="Q87">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="R87">
         <v>2.38</v>
       </c>
       <c r="S87">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T87">
         <v>3.4</v>
@@ -14517,7 +14517,7 @@
         <v>1.59</v>
       </c>
       <c r="W87">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X87">
         <v>1</v>
@@ -14529,41 +14529,41 @@
         <v>4.5</v>
       </c>
       <c r="AA87">
+        <v>1.57</v>
+      </c>
+      <c r="AB87">
+        <v>2.35</v>
+      </c>
+      <c r="AC87">
+        <v>2.29</v>
+      </c>
+      <c r="AD87">
         <v>1.53</v>
       </c>
-      <c r="AB87">
-        <v>2.3</v>
-      </c>
-      <c r="AC87">
+      <c r="AE87">
+        <v>1.18</v>
+      </c>
+      <c r="AF87">
+        <v>1.47</v>
+      </c>
+      <c r="AG87">
         <v>2.45</v>
       </c>
-      <c r="AD87">
-        <v>1.56</v>
-      </c>
-      <c r="AE87">
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ87">
         <v>1.22</v>
       </c>
-      <c r="AF87">
-        <v>1.5</v>
-      </c>
-      <c r="AG87">
-        <v>2.38</v>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI87" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ87">
-        <v>1.25</v>
-      </c>
       <c r="AK87">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -15468,34 +15468,34 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="O93">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="P93">
-        <v>3.1</v>
+        <v>2.93</v>
       </c>
       <c r="Q93">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="R93">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S93">
         <v>1.36</v>
       </c>
       <c r="T93">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="U93">
         <v>3</v>
       </c>
       <c r="V93">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="W93">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X93">
         <v>1.01</v>
@@ -15507,10 +15507,10 @@
         <v>3.33</v>
       </c>
       <c r="AA93">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AB93">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AC93">
         <v>3.42</v>
@@ -15525,7 +15525,7 @@
         <v>1.68</v>
       </c>
       <c r="AG93">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK93">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -16772,34 +16772,34 @@
         </is>
       </c>
       <c r="N101">
-        <v>7.75</v>
+        <v>8</v>
       </c>
       <c r="O101">
-        <v>5.45</v>
+        <v>5.25</v>
       </c>
       <c r="P101">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Q101">
-        <v>6.44</v>
+        <v>6.3</v>
       </c>
       <c r="R101">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="S101">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="T101">
         <v>4.25</v>
       </c>
       <c r="U101">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="V101">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="W101">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X101">
         <v>1.01</v>
@@ -16811,25 +16811,25 @@
         <v>5.8</v>
       </c>
       <c r="AA101">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AB101">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="AC101">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AD101">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AE101">
         <v>1.3</v>
       </c>
       <c r="AF101">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG101">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -17424,46 +17424,46 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.34</v>
+        <v>2.12</v>
       </c>
       <c r="O105">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P105">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="Q105">
         <v>3</v>
       </c>
       <c r="R105">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S105">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="T105">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="U105">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="V105">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W105">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X105">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y105">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z105">
         <v>3</v>
       </c>
       <c r="AA105">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AB105">
         <v>1.72</v>
@@ -17472,10 +17472,10 @@
         <v>3.8</v>
       </c>
       <c r="AD105">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE105">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF105">
         <v>1.8</v>
@@ -17497,7 +17497,7 @@
         <v>1.33</v>
       </c>
       <c r="AK105">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -18085,25 +18085,25 @@
         <v>0</v>
       </c>
       <c r="Q109">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="R109">
         <v>2.23</v>
       </c>
       <c r="S109">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T109">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="U109">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="V109">
         <v>1.53</v>
       </c>
       <c r="W109">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X109">
         <v>1.02</v>
@@ -18133,7 +18133,7 @@
         <v>1.53</v>
       </c>
       <c r="AG109">
-        <v>2.24</v>
+        <v>2.29</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -19054,19 +19054,19 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="O115">
-        <v>4.06</v>
+        <v>3.96</v>
       </c>
       <c r="P115">
-        <v>2.4</v>
+        <v>2.19</v>
       </c>
       <c r="Q115">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="R115">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="S115">
         <v>1.18</v>
@@ -19075,13 +19075,13 @@
         <v>4.5</v>
       </c>
       <c r="U115">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="V115">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="W115">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X115">
         <v>1</v>
@@ -19090,28 +19090,28 @@
         <v>1.07</v>
       </c>
       <c r="Z115">
-        <v>7.02</v>
+        <v>7</v>
       </c>
       <c r="AA115">
         <v>1.33</v>
       </c>
       <c r="AB115">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="AC115">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AD115">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AE115">
         <v>1.39</v>
       </c>
       <c r="AF115">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AG115">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.22</v>
+        <v>1.62</v>
       </c>
       <c r="AK115">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19706,13 +19706,13 @@
         </is>
       </c>
       <c r="N119">
-        <v>5.21</v>
+        <v>4.8</v>
       </c>
       <c r="O119">
-        <v>4.7</v>
+        <v>4.52</v>
       </c>
       <c r="P119">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="Q119">
         <v>4.5</v>
@@ -19727,34 +19727,34 @@
         <v>3.9</v>
       </c>
       <c r="U119">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V119">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W119">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X119">
         <v>1</v>
       </c>
       <c r="Y119">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z119">
-        <v>5.54</v>
+        <v>5.59</v>
       </c>
       <c r="AA119">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AB119">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="AC119">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AD119">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AE119">
         <v>1.28</v>
@@ -19763,7 +19763,7 @@
         <v>1.5</v>
       </c>
       <c r="AG119">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,7 +19776,7 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>2.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK119">
         <v>1.14</v>
@@ -19869,22 +19869,22 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="O120">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P120">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="Q120">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="R120">
         <v>2.33</v>
       </c>
       <c r="S120">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T120">
         <v>4</v>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="AK120">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20358,13 +20358,13 @@
         </is>
       </c>
       <c r="N123">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="O123">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="P123">
-        <v>3.83</v>
+        <v>4.2</v>
       </c>
       <c r="Q123">
         <v>2.33</v>
@@ -20373,10 +20373,10 @@
         <v>2.01</v>
       </c>
       <c r="S123">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T123">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="U123">
         <v>2.86</v>
@@ -20385,7 +20385,7 @@
         <v>1.33</v>
       </c>
       <c r="W123">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X123">
         <v>1.01</v>
@@ -20397,10 +20397,10 @@
         <v>2.97</v>
       </c>
       <c r="AA123">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AB123">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC123">
         <v>3.58</v>
@@ -20415,7 +20415,7 @@
         <v>1.92</v>
       </c>
       <c r="AG123">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20521,25 +20521,25 @@
         </is>
       </c>
       <c r="N124">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="O124">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P124">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="Q124">
-        <v>3.98</v>
+        <v>3.75</v>
       </c>
       <c r="R124">
         <v>2.01</v>
       </c>
       <c r="S124">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T124">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="U124">
         <v>2.81</v>
@@ -20548,7 +20548,7 @@
         <v>1.34</v>
       </c>
       <c r="W124">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X124">
         <v>1.01</v>
@@ -20560,10 +20560,10 @@
         <v>2.97</v>
       </c>
       <c r="AA124">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AB124">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AC124">
         <v>3.58</v>
@@ -20578,7 +20578,7 @@
         <v>1.8</v>
       </c>
       <c r="AG124">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -21662,13 +21662,13 @@
         </is>
       </c>
       <c r="N131">
-        <v>4.3</v>
+        <v>4.14</v>
       </c>
       <c r="O131">
-        <v>4.01</v>
+        <v>3.93</v>
       </c>
       <c r="P131">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="Q131">
         <v>4.25</v>
@@ -21695,7 +21695,7 @@
         <v>1.01</v>
       </c>
       <c r="Y131">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z131">
         <v>4.25</v>
@@ -21704,22 +21704,22 @@
         <v>1.57</v>
       </c>
       <c r="AB131">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AC131">
-        <v>2.49</v>
+        <v>2.38</v>
       </c>
       <c r="AD131">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AE131">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF131">
         <v>1.56</v>
       </c>
       <c r="AG131">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>1.18</v>
       </c>
       <c r="AK131">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21988,10 +21988,10 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="O133">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P133">
         <v>2.9</v>
@@ -23627,28 +23627,28 @@
         <v>2.43</v>
       </c>
       <c r="Q143">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="R143">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="S143">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="T143">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="U143">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="V143">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W143">
         <v>1.11</v>
       </c>
       <c r="X143">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y143">
         <v>1.17</v>
@@ -23675,7 +23675,7 @@
         <v>1.52</v>
       </c>
       <c r="AG143">
-        <v>2.27</v>
+        <v>2.32</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23688,10 +23688,10 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK143">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23823,7 +23823,7 @@
         <v>1.72</v>
       </c>
       <c r="AB144">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="AC144">
         <v>2.66</v>
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="O145">
-        <v>4.46</v>
+        <v>4.4</v>
       </c>
       <c r="P145">
-        <v>7.15</v>
+        <v>7</v>
       </c>
       <c r="Q145">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="R145">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S145">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T145">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U145">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="V145">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W145">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X145">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y145">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z145">
-        <v>3.38</v>
+        <v>3.7</v>
       </c>
       <c r="AA145">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AB145">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AC145">
-        <v>3.41</v>
+        <v>3.15</v>
       </c>
       <c r="AD145">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AE145">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF145">
         <v>2.05</v>
       </c>
       <c r="AG145">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AK145">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24107,13 +24107,13 @@
         </is>
       </c>
       <c r="N146">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="O146">
-        <v>3.81</v>
+        <v>3.65</v>
       </c>
       <c r="P146">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="Q146">
         <v>2.63</v>
@@ -24140,25 +24140,25 @@
         <v>1.01</v>
       </c>
       <c r="Y146">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z146">
         <v>4.85</v>
       </c>
       <c r="AA146">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AB146">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AC146">
         <v>2.41</v>
       </c>
       <c r="AD146">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AE146">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AF146">
         <v>1.44</v>
@@ -24180,7 +24180,7 @@
         <v>1.2</v>
       </c>
       <c r="AK146">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24605,28 +24605,28 @@
         <v>0</v>
       </c>
       <c r="Q149">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="R149">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="S149">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T149">
         <v>3</v>
       </c>
       <c r="U149">
-        <v>2.75</v>
+        <v>2.51</v>
       </c>
       <c r="V149">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W149">
         <v>1.08</v>
       </c>
       <c r="X149">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y149">
         <v>1.22</v>
@@ -24653,7 +24653,7 @@
         <v>1.71</v>
       </c>
       <c r="AG149">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH149" t="inlineStr">
         <is>
@@ -24666,10 +24666,10 @@
         </is>
       </c>
       <c r="AJ149">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK149">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AL149">
         <v>0</v>
@@ -24759,19 +24759,19 @@
         </is>
       </c>
       <c r="N150">
-        <v>2.58</v>
+        <v>2.32</v>
       </c>
       <c r="O150">
-        <v>3.84</v>
+        <v>3.7</v>
       </c>
       <c r="P150">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="Q150">
-        <v>3.05</v>
+        <v>3.11</v>
       </c>
       <c r="R150">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="S150">
         <v>1.29</v>
@@ -24792,25 +24792,25 @@
         <v>1</v>
       </c>
       <c r="Y150">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z150">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AA150">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AB150">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AC150">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="AD150">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="AE150">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF150">
         <v>1.55</v>
@@ -27041,13 +27041,13 @@
         </is>
       </c>
       <c r="N164">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="O164">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="P164">
-        <v>3.4</v>
+        <v>3.31</v>
       </c>
       <c r="Q164">
         <v>2.63</v>
@@ -27074,10 +27074,10 @@
         <v>1.01</v>
       </c>
       <c r="Y164">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Z164">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="AA164">
         <v>1.95</v>
@@ -27086,19 +27086,19 @@
         <v>1.85</v>
       </c>
       <c r="AC164">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="AD164">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE164">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF164">
         <v>1.68</v>
       </c>
       <c r="AG164">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="AH164" t="inlineStr">
         <is>
@@ -29036,10 +29036,10 @@
         <v>0</v>
       </c>
       <c r="AA176">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB176">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC176">
         <v>0</v>
@@ -30805,19 +30805,19 @@
         <v>2.2</v>
       </c>
       <c r="S187">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T187">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="U187">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="V187">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="W187">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X187">
         <v>1.01</v>
@@ -30829,7 +30829,7 @@
         <v>3.75</v>
       </c>
       <c r="AA187">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AB187">
         <v>2.01</v>
@@ -30860,10 +30860,10 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK187">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -30953,13 +30953,13 @@
         </is>
       </c>
       <c r="N188">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="O188">
-        <v>4.26</v>
+        <v>4.2</v>
       </c>
       <c r="P188">
-        <v>5.02</v>
+        <v>4.8</v>
       </c>
       <c r="Q188">
         <v>2.08</v>
@@ -30974,13 +30974,13 @@
         <v>3.4</v>
       </c>
       <c r="U188">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="V188">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W188">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X188">
         <v>1</v>
@@ -30995,7 +30995,7 @@
         <v>1.57</v>
       </c>
       <c r="AB188">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AC188">
         <v>2.45</v>
@@ -31004,7 +31004,7 @@
         <v>1.56</v>
       </c>
       <c r="AE188">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF188">
         <v>1.62</v>
@@ -33398,19 +33398,19 @@
         </is>
       </c>
       <c r="N203">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="O203">
-        <v>4.2</v>
+        <v>4.85</v>
       </c>
       <c r="P203">
-        <v>6.85</v>
+        <v>6.5</v>
       </c>
       <c r="Q203">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="R203">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="S203">
         <v>1.3</v>
@@ -33419,13 +33419,13 @@
         <v>3.3</v>
       </c>
       <c r="U203">
-        <v>2.55</v>
+        <v>2.29</v>
       </c>
       <c r="V203">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="W203">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X203">
         <v>1</v>
@@ -33437,10 +33437,10 @@
         <v>4.6</v>
       </c>
       <c r="AA203">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AB203">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AC203">
         <v>2.39</v>
@@ -33449,13 +33449,13 @@
         <v>1.49</v>
       </c>
       <c r="AE203">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF203">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AG203">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AH203" t="inlineStr">
         <is>
@@ -33468,10 +33468,10 @@
         </is>
       </c>
       <c r="AJ203">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AK203">
-        <v>2.51</v>
+        <v>3</v>
       </c>
       <c r="AL203">
         <v>0</v>
@@ -34539,31 +34539,31 @@
         </is>
       </c>
       <c r="N210">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="O210">
-        <v>4.65</v>
+        <v>4.1</v>
       </c>
       <c r="P210">
-        <v>4.96</v>
+        <v>4</v>
       </c>
       <c r="Q210">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="R210">
         <v>2.5</v>
       </c>
       <c r="S210">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T210">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="U210">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="V210">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="W210">
         <v>1.18</v>
@@ -34578,13 +34578,13 @@
         <v>5.2</v>
       </c>
       <c r="AA210">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AB210">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AC210">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="AD210">
         <v>1.68</v>
@@ -34596,7 +34596,7 @@
         <v>1.46</v>
       </c>
       <c r="AG210">
-        <v>2.53</v>
+        <v>2.49</v>
       </c>
       <c r="AH210" t="inlineStr">
         <is>
@@ -34609,10 +34609,10 @@
         </is>
       </c>
       <c r="AJ210">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK210">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AL210">
         <v>0</v>
@@ -35028,25 +35028,25 @@
         </is>
       </c>
       <c r="N213">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="O213">
-        <v>9.699999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="P213">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="Q213">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="R213">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="S213">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T213">
-        <v>3.42</v>
+        <v>3.52</v>
       </c>
       <c r="U213">
         <v>2.02</v>
@@ -35055,7 +35055,7 @@
         <v>1.68</v>
       </c>
       <c r="W213">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X213">
         <v>1.01</v>
@@ -35064,28 +35064,28 @@
         <v>1.09</v>
       </c>
       <c r="Z213">
-        <v>6.97</v>
+        <v>6.88</v>
       </c>
       <c r="AA213">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AB213">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="AC213">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="AD213">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AE213">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AF213">
         <v>2.14</v>
       </c>
       <c r="AG213">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AH213" t="inlineStr">
         <is>
@@ -35101,7 +35101,7 @@
         <v>1.06</v>
       </c>
       <c r="AK213">
-        <v>6.1</v>
+        <v>4.75</v>
       </c>
       <c r="AL213">
         <v>0</v>
@@ -35680,19 +35680,19 @@
         </is>
       </c>
       <c r="N217">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="O217">
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
       <c r="P217">
-        <v>3.82</v>
+        <v>3.25</v>
       </c>
       <c r="Q217">
         <v>2.4</v>
       </c>
       <c r="R217">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S217">
         <v>1.3</v>
@@ -35713,10 +35713,10 @@
         <v>1</v>
       </c>
       <c r="Y217">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z217">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="AA217">
         <v>1.74</v>
@@ -35737,7 +35737,7 @@
         <v>1.61</v>
       </c>
       <c r="AG217">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AH217" t="inlineStr">
         <is>
@@ -35843,19 +35843,19 @@
         </is>
       </c>
       <c r="N218">
-        <v>2.46</v>
+        <v>2.71</v>
       </c>
       <c r="O218">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="P218">
-        <v>2.66</v>
+        <v>2.3</v>
       </c>
       <c r="Q218">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="R218">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S218">
         <v>1.22</v>
@@ -35876,22 +35876,22 @@
         <v>1</v>
       </c>
       <c r="Y218">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z218">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AA218">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AB218">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="AC218">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AD218">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AE218">
         <v>1.2</v>
@@ -35913,7 +35913,7 @@
         </is>
       </c>
       <c r="AJ218">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AK218">
         <v>1.46</v>
@@ -36006,25 +36006,25 @@
         </is>
       </c>
       <c r="N219">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="O219">
-        <v>4.52</v>
+        <v>4.48</v>
       </c>
       <c r="P219">
-        <v>5.54</v>
+        <v>5.6</v>
       </c>
       <c r="Q219">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="R219">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="S219">
         <v>1.22</v>
       </c>
       <c r="T219">
-        <v>3.92</v>
+        <v>4.1</v>
       </c>
       <c r="U219">
         <v>2</v>
@@ -36033,7 +36033,7 @@
         <v>1.69</v>
       </c>
       <c r="W219">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X219">
         <v>1</v>
@@ -36042,7 +36042,7 @@
         <v>1.1</v>
       </c>
       <c r="Z219">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="AA219">
         <v>1.43</v>
@@ -36051,13 +36051,13 @@
         <v>2.75</v>
       </c>
       <c r="AC219">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AD219">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AE219">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AF219">
         <v>1.53</v>
@@ -36076,10 +36076,10 @@
         </is>
       </c>
       <c r="AJ219">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK219">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="AL219">
         <v>0</v>
@@ -37808,28 +37808,28 @@
         <v>3.19</v>
       </c>
       <c r="Q230">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="R230">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S230">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T230">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U230">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="V230">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W230">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X230">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y230">
         <v>1.16</v>
@@ -37841,7 +37841,7 @@
         <v>1.61</v>
       </c>
       <c r="AB230">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AC230">
         <v>2.49</v>
@@ -37856,7 +37856,7 @@
         <v>1.54</v>
       </c>
       <c r="AG230">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AH230" t="inlineStr">
         <is>
@@ -37869,10 +37869,10 @@
         </is>
       </c>
       <c r="AJ230">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK230">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AL230">
         <v>0</v>
@@ -37971,28 +37971,28 @@
         <v>2.39</v>
       </c>
       <c r="Q231">
-        <v>3.5</v>
+        <v>3.78</v>
       </c>
       <c r="R231">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="S231">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T231">
-        <v>2.63</v>
+        <v>2.42</v>
       </c>
       <c r="U231">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="V231">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W231">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X231">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y231">
         <v>1.41</v>
@@ -38013,13 +38013,13 @@
         <v>1.14</v>
       </c>
       <c r="AE231">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF231">
         <v>1.97</v>
       </c>
       <c r="AG231">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AH231" t="inlineStr">
         <is>
@@ -38032,10 +38032,10 @@
         </is>
       </c>
       <c r="AJ231">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK231">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AL231">
         <v>0</v>
@@ -38134,28 +38134,28 @@
         <v>3.52</v>
       </c>
       <c r="Q232">
-        <v>2.4</v>
+        <v>2.51</v>
       </c>
       <c r="R232">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="S232">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T232">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="U232">
-        <v>2.75</v>
+        <v>2.58</v>
       </c>
       <c r="V232">
         <v>1.4</v>
       </c>
       <c r="W232">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X232">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y232">
         <v>1.23</v>
@@ -38176,13 +38176,13 @@
         <v>1.28</v>
       </c>
       <c r="AE232">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF232">
         <v>1.71</v>
       </c>
       <c r="AG232">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH232" t="inlineStr">
         <is>
@@ -38195,10 +38195,10 @@
         </is>
       </c>
       <c r="AJ232">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK232">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AL232">
         <v>0</v>
@@ -38297,55 +38297,55 @@
         <v>6.5</v>
       </c>
       <c r="Q233">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="R233">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S233">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T233">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U233">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V233">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W233">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X233">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y233">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z233">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA233">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB233">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC233">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD233">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE233">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF233">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG233">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH233" t="inlineStr">
         <is>
@@ -38358,10 +38358,10 @@
         </is>
       </c>
       <c r="AJ233">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK233">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL233">
         <v>0</v>
@@ -38460,25 +38460,25 @@
         <v>4.91</v>
       </c>
       <c r="Q234">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="R234">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="S234">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T234">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="U234">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="V234">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W234">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X234">
         <v>0</v>
@@ -38487,28 +38487,28 @@
         <v>1.17</v>
       </c>
       <c r="Z234">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="AA234">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AB234">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AC234">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="AD234">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AE234">
         <v>1.14</v>
       </c>
       <c r="AF234">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AG234">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AH234" t="inlineStr">
         <is>
@@ -38521,10 +38521,10 @@
         </is>
       </c>
       <c r="AJ234">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK234">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AL234">
         <v>0</v>

--- a/jogos_2026-11-01.xlsx
+++ b/jogos_2026-11-01.xlsx
@@ -3445,10 +3445,10 @@
         <v>4.45</v>
       </c>
       <c r="AA19">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AB19">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC19">
         <v>2.42</v>
@@ -3575,13 +3575,13 @@
         <v>3.72</v>
       </c>
       <c r="P20">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="Q20">
         <v>3.74</v>
       </c>
       <c r="R20">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="S20">
         <v>1.31</v>
@@ -3593,7 +3593,7 @@
         <v>2.45</v>
       </c>
       <c r="V20">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W20">
         <v>1.1</v>
@@ -3602,22 +3602,22 @@
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z20">
-        <v>4.15</v>
+        <v>4.25</v>
       </c>
       <c r="AA20">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB20">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AC20">
-        <v>2.55</v>
+        <v>2.73</v>
       </c>
       <c r="AD20">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AE20">
         <v>1.14</v>
@@ -3626,7 +3626,7 @@
         <v>1.56</v>
       </c>
       <c r="AG20">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.29</v>
+        <v>1.77</v>
       </c>
       <c r="AK20">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,7 +3732,7 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="O21">
         <v>5.95</v>
@@ -3741,25 +3741,25 @@
         <v>9</v>
       </c>
       <c r="Q21">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R21">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="S21">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T21">
         <v>3.4</v>
       </c>
       <c r="U21">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V21">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="W21">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X21">
         <v>1</v>
@@ -3774,19 +3774,19 @@
         <v>1.6</v>
       </c>
       <c r="AB21">
-        <v>2.27</v>
+        <v>2.34</v>
       </c>
       <c r="AC21">
         <v>2.53</v>
       </c>
       <c r="AD21">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AE21">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF21">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AG21">
         <v>1.75</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AK21">
-        <v>3.33</v>
+        <v>3.58</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3904,16 +3904,16 @@
         <v>4.8</v>
       </c>
       <c r="Q22">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="R22">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="S22">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T22">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="U22">
         <v>2.25</v>
@@ -3925,7 +3925,7 @@
         <v>1.13</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
         <v>1.14</v>
@@ -3952,7 +3952,7 @@
         <v>1.64</v>
       </c>
       <c r="AG22">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK22">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4067,28 +4067,28 @@
         <v>3.54</v>
       </c>
       <c r="Q23">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="R23">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S23">
         <v>1.33</v>
       </c>
       <c r="T23">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="U23">
-        <v>2.88</v>
+        <v>2.61</v>
       </c>
       <c r="V23">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W23">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
         <v>1.26</v>
@@ -4109,13 +4109,13 @@
         <v>1.27</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF23">
         <v>1.74</v>
       </c>
       <c r="AG23">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK23">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4230,55 +4230,55 @@
         <v>5.25</v>
       </c>
       <c r="Q24">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="R24">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="S24">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="T24">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U24">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="V24">
         <v>1.53</v>
       </c>
       <c r="W24">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X24">
         <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z24">
-        <v>4.1</v>
+        <v>3.88</v>
       </c>
       <c r="AA24">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB24">
         <v>2.05</v>
       </c>
       <c r="AC24">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="AD24">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AE24">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF24">
         <v>1.75</v>
       </c>
       <c r="AG24">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AK24">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4423,10 +4423,10 @@
         <v>3.72</v>
       </c>
       <c r="AA25">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB25">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AC25">
         <v>2.88</v>
@@ -4577,7 +4577,7 @@
         <v>1.11</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
         <v>1.16</v>
@@ -4719,22 +4719,22 @@
         <v>3.16</v>
       </c>
       <c r="Q27">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="R27">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="S27">
+        <v>1.33</v>
+      </c>
+      <c r="T27">
+        <v>2.84</v>
+      </c>
+      <c r="U27">
+        <v>2.73</v>
+      </c>
+      <c r="V27">
         <v>1.36</v>
-      </c>
-      <c r="T27">
-        <v>2.9</v>
-      </c>
-      <c r="U27">
-        <v>2.75</v>
-      </c>
-      <c r="V27">
-        <v>1.38</v>
       </c>
       <c r="W27">
         <v>1.06</v>
@@ -4743,10 +4743,10 @@
         <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z27">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AA27">
         <v>2</v>
@@ -4755,19 +4755,19 @@
         <v>1.8</v>
       </c>
       <c r="AC27">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="AD27">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AE27">
         <v>1.06</v>
       </c>
       <c r="AF27">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AG27">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK27">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5374,19 +5374,19 @@
         <v>2.64</v>
       </c>
       <c r="R31">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="S31">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T31">
-        <v>2.6</v>
+        <v>2.51</v>
       </c>
       <c r="U31">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="V31">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W31">
         <v>1.03</v>
@@ -5401,10 +5401,10 @@
         <v>2.66</v>
       </c>
       <c r="AA31">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AB31">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AC31">
         <v>4.15</v>
@@ -5419,7 +5419,7 @@
         <v>1.97</v>
       </c>
       <c r="AG31">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AK31">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5697,28 +5697,28 @@
         <v>2.85</v>
       </c>
       <c r="Q33">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="R33">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="S33">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T33">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="U33">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="V33">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W33">
+        <v>1.02</v>
+      </c>
+      <c r="X33">
         <v>1.04</v>
-      </c>
-      <c r="X33">
-        <v>1.02</v>
       </c>
       <c r="Y33">
         <v>1.31</v>
@@ -5727,19 +5727,19 @@
         <v>2.92</v>
       </c>
       <c r="AA33">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="AB33">
         <v>1.66</v>
       </c>
       <c r="AC33">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="AD33">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE33">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF33">
         <v>1.8</v>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AK33">
         <v>1.47</v>
@@ -7164,7 +7164,7 @@
         <v>0</v>
       </c>
       <c r="Q42">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R42">
         <v>2.1</v>
@@ -7173,19 +7173,19 @@
         <v>1.33</v>
       </c>
       <c r="T42">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="U42">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="V42">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W42">
         <v>1.06</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
         <v>1.26</v>
@@ -7194,10 +7194,10 @@
         <v>3.2</v>
       </c>
       <c r="AA42">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB42">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AC42">
         <v>3.14</v>
@@ -7206,13 +7206,13 @@
         <v>1.27</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF42">
         <v>1.81</v>
       </c>
       <c r="AG42">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK42">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7327,25 +7327,25 @@
         <v>0</v>
       </c>
       <c r="Q43">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="R43">
         <v>2.3</v>
       </c>
       <c r="S43">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T43">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="U43">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="V43">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W43">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X43">
         <v>0</v>
@@ -7375,7 +7375,7 @@
         <v>1.54</v>
       </c>
       <c r="AG43">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK43">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CD Don Benito</t>
+          <t>Mijas Las Lagunas</t>
         </is>
       </c>
       <c r="G44">
@@ -7490,28 +7490,28 @@
         <v>0</v>
       </c>
       <c r="Q44">
-        <v>2.5</v>
+        <v>2.87</v>
       </c>
       <c r="R44">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S44">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="T44">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="U44">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V44">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W44">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y44">
         <v>1.17</v>
@@ -7520,10 +7520,10 @@
         <v>3.94</v>
       </c>
       <c r="AA44">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AB44">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AC44">
         <v>2.7</v>
@@ -7535,10 +7535,10 @@
         <v>1.1</v>
       </c>
       <c r="AF44">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AG44">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>1.22</v>
       </c>
       <c r="AK44">
-        <v>1.73</v>
+        <v>1.49</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mijas Las Lagunas</t>
+          <t>CD Don Benito</t>
         </is>
       </c>
       <c r="G45">
@@ -7653,28 +7653,28 @@
         <v>0</v>
       </c>
       <c r="Q45">
-        <v>2.88</v>
+        <v>2.44</v>
       </c>
       <c r="R45">
         <v>2.2</v>
       </c>
       <c r="S45">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="T45">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="U45">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="V45">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W45">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y45">
         <v>1.17</v>
@@ -7683,10 +7683,10 @@
         <v>3.94</v>
       </c>
       <c r="AA45">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AB45">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="AC45">
         <v>2.7</v>
@@ -7698,10 +7698,10 @@
         <v>1.1</v>
       </c>
       <c r="AF45">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AG45">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK45">
-        <v>1.53</v>
+        <v>1.74</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>La Nucía</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mallorca II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.53</v>
+        <v>2.08</v>
       </c>
       <c r="O48">
-        <v>3.8</v>
+        <v>3.12</v>
       </c>
       <c r="P48">
-        <v>5.3</v>
+        <v>3.28</v>
       </c>
       <c r="Q48">
-        <v>2</v>
+        <v>2.78</v>
       </c>
       <c r="R48">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="S48">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="T48">
-        <v>3.2</v>
+        <v>2.65</v>
       </c>
       <c r="U48">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="V48">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="W48">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y48">
+        <v>1.32</v>
+      </c>
+      <c r="Z48">
+        <v>2.88</v>
+      </c>
+      <c r="AA48">
+        <v>2.15</v>
+      </c>
+      <c r="AB48">
+        <v>1.66</v>
+      </c>
+      <c r="AC48">
+        <v>3.84</v>
+      </c>
+      <c r="AD48">
         <v>1.18</v>
       </c>
-      <c r="Z48">
-        <v>3.84</v>
-      </c>
-      <c r="AA48">
-        <v>1.71</v>
-      </c>
-      <c r="AB48">
-        <v>1.98</v>
-      </c>
-      <c r="AC48">
-        <v>2.74</v>
-      </c>
-      <c r="AD48">
-        <v>1.35</v>
-      </c>
       <c r="AE48">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AF48">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG48">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AK48">
-        <v>2.3</v>
+        <v>1.59</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>La Nucía</t>
+          <t>Peña Deportiva</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.08</v>
+        <v>3.8</v>
       </c>
       <c r="O49">
-        <v>3.12</v>
+        <v>3.6</v>
       </c>
       <c r="P49">
-        <v>3.28</v>
+        <v>1.8</v>
       </c>
       <c r="Q49">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="R49">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="S49">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="T49">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="U49">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="V49">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="W49">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="Z49">
-        <v>2.88</v>
+        <v>3.42</v>
       </c>
       <c r="AA49">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="AB49">
-        <v>1.63</v>
+        <v>1.88</v>
       </c>
       <c r="AC49">
-        <v>3.84</v>
+        <v>2.92</v>
       </c>
       <c r="AD49">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF49">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AG49">
-        <v>1.81</v>
+        <v>1.98</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AK49">
-        <v>1.67</v>
+        <v>1.17</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Peña Deportiva</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Mallorca II</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
+        <v>1.53</v>
+      </c>
+      <c r="O50">
         <v>3.8</v>
       </c>
-      <c r="O50">
-        <v>3.6</v>
-      </c>
       <c r="P50">
-        <v>1.8</v>
+        <v>5.3</v>
       </c>
       <c r="Q50">
-        <v>4.39</v>
+        <v>2.1</v>
       </c>
       <c r="R50">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="S50">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T50">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U50">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="V50">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W50">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y50">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="Z50">
-        <v>3.5</v>
+        <v>3.84</v>
       </c>
       <c r="AA50">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB50">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AC50">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="AD50">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE50">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF50">
         <v>1.75</v>
       </c>
       <c r="AG50">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AK50">
-        <v>1.21</v>
+        <v>2.2</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8794,10 +8794,10 @@
         <v>2.9</v>
       </c>
       <c r="Q52">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="R52">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="S52">
         <v>1.22</v>
@@ -8836,7 +8836,7 @@
         <v>1.53</v>
       </c>
       <c r="AE52">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AF52">
         <v>1.5</v>
@@ -8858,7 +8858,7 @@
         <v>1.25</v>
       </c>
       <c r="AK52">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9120,55 +9120,55 @@
         <v>4.65</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T54">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U54">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="V54">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA54">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG54">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK54">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9283,34 +9283,34 @@
         <v>2.09</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T55">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U55">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V55">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y55">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z55">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA55">
         <v>2.05</v>
@@ -9319,19 +9319,19 @@
         <v>1.75</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE55">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF55">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG55">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK55">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9455,19 +9455,19 @@
         <v>1.3</v>
       </c>
       <c r="T56">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U56">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="V56">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W56">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y56">
         <v>1.2</v>
@@ -9488,13 +9488,13 @@
         <v>1.36</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF56">
         <v>1.59</v>
       </c>
       <c r="AG56">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK56">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -10913,16 +10913,16 @@
         <v>2.75</v>
       </c>
       <c r="Q65">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="R65">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="S65">
         <v>1.3</v>
       </c>
       <c r="T65">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="U65">
         <v>2.45</v>
@@ -10943,7 +10943,7 @@
         <v>4.47</v>
       </c>
       <c r="AA65">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AB65">
         <v>2.09</v>
@@ -10955,13 +10955,13 @@
         <v>1.45</v>
       </c>
       <c r="AE65">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF65">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AG65">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK65">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="O66">
-        <v>3.6</v>
+        <v>3.23</v>
       </c>
       <c r="P66">
-        <v>3.35</v>
+        <v>2.85</v>
       </c>
       <c r="Q66">
         <v>2.55</v>
@@ -11094,7 +11094,7 @@
         <v>1.47</v>
       </c>
       <c r="W66">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X66">
         <v>1.03</v>
@@ -11239,34 +11239,34 @@
         <v>1.82</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S67">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T67">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U67">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V67">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W67">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y67">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z67">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA67">
         <v>1.95</v>
@@ -11275,19 +11275,19 @@
         <v>1.85</v>
       </c>
       <c r="AC67">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD67">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE67">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF67">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG67">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK67">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11402,55 +11402,55 @@
         <v>0</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T68">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W68">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X68">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z68">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD68">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE68">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF68">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK68">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -12706,37 +12706,37 @@
         <v>1.97</v>
       </c>
       <c r="Q76">
-        <v>4.05</v>
+        <v>4.12</v>
       </c>
       <c r="R76">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="S76">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T76">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="U76">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="V76">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W76">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X76">
         <v>1.01</v>
       </c>
       <c r="Y76">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z76">
         <v>3.42</v>
       </c>
       <c r="AA76">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AB76">
         <v>2</v>
@@ -12751,7 +12751,7 @@
         <v>1.06</v>
       </c>
       <c r="AF76">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AG76">
         <v>1.97</v>
@@ -12770,7 +12770,7 @@
         <v>1.23</v>
       </c>
       <c r="AK76">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -13032,7 +13032,7 @@
         <v>2.08</v>
       </c>
       <c r="Q78">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="R78">
         <v>2.08</v>
@@ -13515,10 +13515,10 @@
         <v>2.85</v>
       </c>
       <c r="O81">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="P81">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="Q81">
         <v>4.05</v>
@@ -13527,7 +13527,7 @@
         <v>1.94</v>
       </c>
       <c r="S81">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="T81">
         <v>2.51</v>
@@ -13545,22 +13545,22 @@
         <v>1.06</v>
       </c>
       <c r="Y81">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Z81">
-        <v>2.52</v>
+        <v>2.76</v>
       </c>
       <c r="AA81">
-        <v>2.49</v>
+        <v>2.58</v>
       </c>
       <c r="AB81">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="AC81">
-        <v>4.7</v>
+        <v>4.82</v>
       </c>
       <c r="AD81">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AE81">
         <v>1</v>
@@ -13569,7 +13569,7 @@
         <v>2.04</v>
       </c>
       <c r="AG81">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.62</v>
+        <v>1.37</v>
       </c>
       <c r="AK81">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13693,13 +13693,13 @@
         <v>1.25</v>
       </c>
       <c r="T82">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U82">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="V82">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W82">
         <v>1.1</v>
@@ -13714,7 +13714,7 @@
         <v>4.55</v>
       </c>
       <c r="AA82">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB82">
         <v>2.35</v>
@@ -13838,19 +13838,19 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O83">
         <v>3.4</v>
       </c>
       <c r="P83">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="Q83">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="R83">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S83">
         <v>1.18</v>
@@ -13871,13 +13871,13 @@
         <v>1.02</v>
       </c>
       <c r="Y83">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z83">
-        <v>3.4</v>
+        <v>4.75</v>
       </c>
       <c r="AA83">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AB83">
         <v>2.04</v>
@@ -13886,10 +13886,10 @@
         <v>1.94</v>
       </c>
       <c r="AD83">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AE83">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AF83">
         <v>1.44</v>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AK83">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="O84">
-        <v>3.72</v>
+        <v>3.4</v>
       </c>
       <c r="P84">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="Q84">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="R84">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S84">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="T84">
-        <v>3.65</v>
+        <v>3.22</v>
       </c>
       <c r="U84">
         <v>2.25</v>
       </c>
       <c r="V84">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="W84">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X84">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y84">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z84">
-        <v>5.25</v>
+        <v>4.6</v>
       </c>
       <c r="AA84">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AB84">
-        <v>2.4</v>
+        <v>2.19</v>
       </c>
       <c r="AC84">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="AD84">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="AE84">
         <v>1.22</v>
       </c>
       <c r="AF84">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AG84">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK84">
         <v>1.73</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="O85">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P85">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="Q85">
-        <v>2.59</v>
+        <v>3.04</v>
       </c>
       <c r="R85">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="S85">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="T85">
-        <v>3.22</v>
+        <v>3.8</v>
       </c>
       <c r="U85">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="V85">
+        <v>1.62</v>
+      </c>
+      <c r="W85">
+        <v>1.17</v>
+      </c>
+      <c r="X85">
+        <v>1.02</v>
+      </c>
+      <c r="Y85">
+        <v>1.11</v>
+      </c>
+      <c r="Z85">
+        <v>4.85</v>
+      </c>
+      <c r="AA85">
         <v>1.57</v>
       </c>
-      <c r="W85">
-        <v>1.12</v>
-      </c>
-      <c r="X85">
-        <v>1.03</v>
-      </c>
-      <c r="Y85">
-        <v>1.15</v>
-      </c>
-      <c r="Z85">
-        <v>5</v>
-      </c>
-      <c r="AA85">
-        <v>1.61</v>
-      </c>
       <c r="AB85">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AC85">
-        <v>2.44</v>
+        <v>2.33</v>
       </c>
       <c r="AD85">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="AE85">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AF85">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AG85">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AK85">
-        <v>1.73</v>
+        <v>1.48</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,28 +14327,28 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.57</v>
+        <v>2.11</v>
       </c>
       <c r="O86">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="P86">
+        <v>3.1</v>
+      </c>
+      <c r="Q86">
         <v>2.55</v>
       </c>
-      <c r="Q86">
-        <v>3.04</v>
-      </c>
       <c r="R86">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="S86">
         <v>1.22</v>
       </c>
       <c r="T86">
-        <v>3.8</v>
+        <v>3.56</v>
       </c>
       <c r="U86">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="V86">
         <v>1.62</v>
@@ -14360,28 +14360,28 @@
         <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z86">
-        <v>4.85</v>
+        <v>5.25</v>
       </c>
       <c r="AA86">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB86">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AC86">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AD86">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="AE86">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AF86">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG86">
         <v>2.5</v>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AK86">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14520,7 +14520,7 @@
         <v>1.17</v>
       </c>
       <c r="X87">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y87">
         <v>1.09</v>
@@ -14563,7 +14563,7 @@
         <v>1.14</v>
       </c>
       <c r="AK87">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14662,10 +14662,10 @@
         <v>3.4</v>
       </c>
       <c r="Q88">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="R88">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="S88">
         <v>1.25</v>
@@ -14680,7 +14680,7 @@
         <v>1.59</v>
       </c>
       <c r="W88">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X88">
         <v>1</v>
@@ -14704,10 +14704,10 @@
         <v>1.53</v>
       </c>
       <c r="AE88">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AF88">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG88">
         <v>2.45</v>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK88">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14988,13 +14988,13 @@
         <v>3.9</v>
       </c>
       <c r="Q90">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="R90">
         <v>2.18</v>
       </c>
       <c r="S90">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T90">
         <v>3.3</v>
@@ -15003,40 +15003,40 @@
         <v>2.4</v>
       </c>
       <c r="V90">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W90">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X90">
         <v>1</v>
       </c>
       <c r="Y90">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z90">
-        <v>4.31</v>
+        <v>4.19</v>
       </c>
       <c r="AA90">
         <v>1.7</v>
       </c>
       <c r="AB90">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="AC90">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AD90">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AE90">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF90">
         <v>1.6</v>
       </c>
       <c r="AG90">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK90">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15151,10 +15151,10 @@
         <v>7.75</v>
       </c>
       <c r="Q91">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="R91">
-        <v>2.73</v>
+        <v>2.95</v>
       </c>
       <c r="S91">
         <v>1.22</v>
@@ -15169,7 +15169,7 @@
         <v>1.7</v>
       </c>
       <c r="W91">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X91">
         <v>1</v>
@@ -15178,7 +15178,7 @@
         <v>1.12</v>
       </c>
       <c r="Z91">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA91">
         <v>1.4</v>
@@ -15193,7 +15193,7 @@
         <v>1.7</v>
       </c>
       <c r="AE91">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AF91">
         <v>1.6</v>
@@ -15215,7 +15215,7 @@
         <v>1.07</v>
       </c>
       <c r="AK91">
-        <v>3.2</v>
+        <v>2.84</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15483,10 +15483,10 @@
         <v>3.44</v>
       </c>
       <c r="S93">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="T93">
-        <v>5.5</v>
+        <v>5.65</v>
       </c>
       <c r="U93">
         <v>1.66</v>
@@ -15495,7 +15495,7 @@
         <v>2.05</v>
       </c>
       <c r="W93">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X93">
         <v>1</v>
@@ -15507,19 +15507,19 @@
         <v>10.5</v>
       </c>
       <c r="AA93">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AB93">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AC93">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AD93">
-        <v>2.26</v>
+        <v>2.43</v>
       </c>
       <c r="AE93">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AF93">
         <v>1.4</v>
@@ -15640,10 +15640,10 @@
         <v>2.93</v>
       </c>
       <c r="Q94">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="R94">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S94">
         <v>1.36</v>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK94">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15990,10 +15990,10 @@
         <v>1</v>
       </c>
       <c r="Y96">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z96">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="AA96">
         <v>2.17</v>
@@ -16165,16 +16165,16 @@
         <v>1.84</v>
       </c>
       <c r="AC97">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="AD97">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE97">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF97">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AG97">
         <v>2.05</v>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AK97">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16292,7 +16292,7 @@
         <v>2.34</v>
       </c>
       <c r="Q98">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="R98">
         <v>1.84</v>
@@ -16356,7 +16356,7 @@
         <v>1.32</v>
       </c>
       <c r="AK98">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16455,25 +16455,25 @@
         <v>1.77</v>
       </c>
       <c r="Q99">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="R99">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="S99">
         <v>1.22</v>
       </c>
       <c r="T99">
-        <v>3.8</v>
+        <v>3.56</v>
       </c>
       <c r="U99">
         <v>2.2</v>
       </c>
       <c r="V99">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W99">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X99">
         <v>1.01</v>
@@ -16612,7 +16612,7 @@
         <v>1.28</v>
       </c>
       <c r="O100">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="P100">
         <v>9</v>
@@ -16627,7 +16627,7 @@
         <v>1.24</v>
       </c>
       <c r="T100">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U100">
         <v>2.23</v>
@@ -16654,19 +16654,19 @@
         <v>2.33</v>
       </c>
       <c r="AC100">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="AD100">
         <v>1.58</v>
       </c>
       <c r="AE100">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF100">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG100">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16944,55 +16944,55 @@
         <v>1.34</v>
       </c>
       <c r="Q102">
-        <v>6.3</v>
+        <v>5.55</v>
       </c>
       <c r="R102">
         <v>2.88</v>
       </c>
       <c r="S102">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T102">
-        <v>4.25</v>
+        <v>4.1</v>
       </c>
       <c r="U102">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="V102">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="W102">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X102">
         <v>1.01</v>
       </c>
       <c r="Y102">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="Z102">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AA102">
         <v>1.4</v>
       </c>
       <c r="AB102">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="AC102">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="AD102">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AE102">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AF102">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG102">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AK102">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17294,7 +17294,7 @@
         <v>1</v>
       </c>
       <c r="Y104">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="Z104">
         <v>3.66</v>
@@ -17303,7 +17303,7 @@
         <v>1.84</v>
       </c>
       <c r="AB104">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="AC104">
         <v>3.05</v>
@@ -17427,16 +17427,16 @@
         <v>2</v>
       </c>
       <c r="O105">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P105">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q105">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="R105">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="S105">
         <v>1.33</v>
@@ -17445,10 +17445,10 @@
         <v>3</v>
       </c>
       <c r="U105">
-        <v>2.85</v>
+        <v>2.62</v>
       </c>
       <c r="V105">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W105">
         <v>1.08</v>
@@ -17457,25 +17457,25 @@
         <v>1.01</v>
       </c>
       <c r="Y105">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="Z105">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="AA105">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="AB105">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AC105">
         <v>3.21</v>
       </c>
       <c r="AD105">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AE105">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF105">
         <v>1.7</v>
@@ -17587,31 +17587,31 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="O106">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="P106">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="Q106">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="R106">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="S106">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="T106">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="U106">
         <v>2.78</v>
       </c>
       <c r="V106">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W106">
         <v>1.07</v>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK106">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -18248,7 +18248,7 @@
         <v>0</v>
       </c>
       <c r="Q110">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="R110">
         <v>2.23</v>
@@ -18278,10 +18278,10 @@
         <v>4.45</v>
       </c>
       <c r="AA110">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AB110">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC110">
         <v>2.42</v>
@@ -18411,7 +18411,7 @@
         <v>5.75</v>
       </c>
       <c r="Q111">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R111">
         <v>2.15</v>
@@ -19226,10 +19226,10 @@
         <v>2.19</v>
       </c>
       <c r="Q116">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="R116">
-        <v>2.55</v>
+        <v>2.49</v>
       </c>
       <c r="S116">
         <v>1.18</v>
@@ -19244,7 +19244,7 @@
         <v>1.88</v>
       </c>
       <c r="W116">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X116">
         <v>1</v>
@@ -19259,7 +19259,7 @@
         <v>1.33</v>
       </c>
       <c r="AB116">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="AC116">
         <v>1.86</v>
@@ -19268,13 +19268,13 @@
         <v>1.96</v>
       </c>
       <c r="AE116">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AF116">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AG116">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AK116">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19555,22 +19555,22 @@
         <v>1.51</v>
       </c>
       <c r="R118">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="S118">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="T118">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="U118">
         <v>1.75</v>
       </c>
       <c r="V118">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="W118">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X118">
         <v>1</v>
@@ -19585,16 +19585,16 @@
         <v>1.22</v>
       </c>
       <c r="AB118">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AC118">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AD118">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AE118">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AF118">
         <v>1.62</v>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AK118">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19712,13 +19712,13 @@
         <v>4</v>
       </c>
       <c r="P119">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="Q119">
         <v>3.85</v>
       </c>
       <c r="R119">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S119">
         <v>1.22</v>
@@ -19739,7 +19739,7 @@
         <v>1.02</v>
       </c>
       <c r="Y119">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z119">
         <v>5.46</v>
@@ -19751,19 +19751,19 @@
         <v>2.5</v>
       </c>
       <c r="AC119">
-        <v>2.27</v>
+        <v>2.21</v>
       </c>
       <c r="AD119">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AE119">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AF119">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AG119">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>2.05</v>
       </c>
       <c r="V120">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="W120">
         <v>1.18</v>
@@ -19926,7 +19926,7 @@
         <v>1.5</v>
       </c>
       <c r="AG120">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -20041,10 +20041,10 @@
         <v>2.35</v>
       </c>
       <c r="Q121">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="R121">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="S121">
         <v>1.2</v>
@@ -20059,7 +20059,7 @@
         <v>1.62</v>
       </c>
       <c r="W121">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="X121">
         <v>1</v>
@@ -20105,7 +20105,7 @@
         <v>1.25</v>
       </c>
       <c r="AK121">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20578,7 +20578,7 @@
         <v>1.92</v>
       </c>
       <c r="AG124">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>1.34</v>
       </c>
       <c r="W125">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X125">
         <v>1.01</v>
@@ -20850,61 +20850,61 @@
         <v>2.9</v>
       </c>
       <c r="O126">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="P126">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="Q126">
-        <v>3.6</v>
+        <v>3.74</v>
       </c>
       <c r="R126">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S126">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T126">
+        <v>2.7</v>
+      </c>
+      <c r="U126">
         <v>2.88</v>
       </c>
-      <c r="U126">
-        <v>3</v>
-      </c>
       <c r="V126">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W126">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X126">
         <v>1</v>
       </c>
       <c r="Y126">
+        <v>1.26</v>
+      </c>
+      <c r="Z126">
+        <v>3.2</v>
+      </c>
+      <c r="AA126">
+        <v>2.08</v>
+      </c>
+      <c r="AB126">
+        <v>1.76</v>
+      </c>
+      <c r="AC126">
+        <v>3.28</v>
+      </c>
+      <c r="AD126">
         <v>1.28</v>
       </c>
-      <c r="Z126">
-        <v>3.05</v>
-      </c>
-      <c r="AA126">
-        <v>2.04</v>
-      </c>
-      <c r="AB126">
+      <c r="AE126">
+        <v>1.05</v>
+      </c>
+      <c r="AF126">
         <v>1.73</v>
       </c>
-      <c r="AC126">
-        <v>3.5</v>
-      </c>
-      <c r="AD126">
-        <v>1.22</v>
-      </c>
-      <c r="AE126">
-        <v>1.03</v>
-      </c>
-      <c r="AF126">
-        <v>1.79</v>
-      </c>
       <c r="AG126">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="O127">
         <v>3.3</v>
       </c>
       <c r="P127">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="Q127">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="R127">
         <v>2.1</v>
       </c>
       <c r="S127">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T127">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="U127">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="V127">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="W127">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X127">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y127">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z127">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="AA127">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AB127">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="AC127">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="AD127">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AE127">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF127">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AG127">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21083,7 +21083,7 @@
         <v>1.3</v>
       </c>
       <c r="AK127">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21173,19 +21173,19 @@
         </is>
       </c>
       <c r="N128">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="O128">
         <v>3.1</v>
       </c>
       <c r="P128">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="Q128">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="R128">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="S128">
         <v>1.36</v>
@@ -21194,43 +21194,43 @@
         <v>2.88</v>
       </c>
       <c r="U128">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="V128">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W128">
         <v>1.05</v>
       </c>
       <c r="X128">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y128">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z128">
-        <v>3.14</v>
+        <v>3.34</v>
       </c>
       <c r="AA128">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="AB128">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AC128">
-        <v>3.34</v>
+        <v>3.08</v>
       </c>
       <c r="AD128">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AE128">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF128">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="AG128">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>1.3</v>
       </c>
       <c r="AK128">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21345,10 +21345,10 @@
         <v>6.5</v>
       </c>
       <c r="Q129">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="R129">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="S129">
         <v>1.3</v>
@@ -21357,10 +21357,10 @@
         <v>3</v>
       </c>
       <c r="U129">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V129">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W129">
         <v>1.08</v>
@@ -21393,7 +21393,7 @@
         <v>1.91</v>
       </c>
       <c r="AG129">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK129">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21665,22 +21665,22 @@
         <v>1.82</v>
       </c>
       <c r="O131">
-        <v>3.72</v>
+        <v>3.9</v>
       </c>
       <c r="P131">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q131">
         <v>2.21</v>
       </c>
       <c r="R131">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="S131">
         <v>1.25</v>
       </c>
       <c r="T131">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U131">
         <v>2.3</v>
@@ -21695,16 +21695,16 @@
         <v>1.01</v>
       </c>
       <c r="Y131">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z131">
         <v>4.6</v>
       </c>
       <c r="AA131">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AB131">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AC131">
         <v>2.4</v>
@@ -21713,10 +21713,10 @@
         <v>1.5</v>
       </c>
       <c r="AE131">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AF131">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AG131">
         <v>2.3</v>
@@ -21834,55 +21834,55 @@
         <v>3.9</v>
       </c>
       <c r="Q132">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="R132">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S132">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="T132">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="U132">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="V132">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W132">
+        <v>1.06</v>
+      </c>
+      <c r="X132">
         <v>1.03</v>
-      </c>
-      <c r="X132">
-        <v>1.04</v>
       </c>
       <c r="Y132">
         <v>1.44</v>
       </c>
       <c r="Z132">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="AA132">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AB132">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AC132">
-        <v>4.75</v>
+        <v>4.2</v>
       </c>
       <c r="AD132">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE132">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF132">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG132">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK132">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -22027,16 +22027,16 @@
         <v>4.25</v>
       </c>
       <c r="AA133">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AB133">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AC133">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
       <c r="AD133">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AE133">
         <v>1.16</v>
@@ -22172,13 +22172,13 @@
         <v>2.65</v>
       </c>
       <c r="U134">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="V134">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W134">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X134">
         <v>1.05</v>
@@ -22314,10 +22314,10 @@
         </is>
       </c>
       <c r="N135">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="O135">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P135">
         <v>2.9</v>
@@ -22477,19 +22477,19 @@
         </is>
       </c>
       <c r="N136">
-        <v>3.39</v>
+        <v>3.2</v>
       </c>
       <c r="O136">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P136">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q136">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="R136">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S136">
         <v>1.29</v>
@@ -22498,10 +22498,10 @@
         <v>3.4</v>
       </c>
       <c r="U136">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="V136">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W136">
         <v>1.12</v>
@@ -22525,16 +22525,16 @@
         <v>2.36</v>
       </c>
       <c r="AD136">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AE136">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF136">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AG136">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22809,19 +22809,19 @@
         <v>3.6</v>
       </c>
       <c r="P138">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="Q138">
         <v>2.2</v>
       </c>
       <c r="R138">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S138">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T138">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="U138">
         <v>2.6</v>
@@ -22848,10 +22848,10 @@
         <v>1.93</v>
       </c>
       <c r="AC138">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="AD138">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE138">
         <v>1.08</v>
@@ -22975,55 +22975,55 @@
         <v>1.65</v>
       </c>
       <c r="Q139">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="R139">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S139">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T139">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U139">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V139">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W139">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X139">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y139">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z139">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA139">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB139">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC139">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD139">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE139">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF139">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG139">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK139">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23627,10 +23627,10 @@
         <v>4.69</v>
       </c>
       <c r="Q143">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R143">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="S143">
         <v>1.25</v>
@@ -23639,13 +23639,13 @@
         <v>3.32</v>
       </c>
       <c r="U143">
-        <v>2.21</v>
+        <v>2.31</v>
       </c>
       <c r="V143">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W143">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X143">
         <v>1.03</v>
@@ -23669,13 +23669,13 @@
         <v>1.52</v>
       </c>
       <c r="AE143">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF143">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG143">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23688,10 +23688,10 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK143">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23820,10 +23820,10 @@
         <v>3.96</v>
       </c>
       <c r="AA144">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AB144">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AC144">
         <v>2.52</v>
@@ -23953,10 +23953,10 @@
         <v>5.75</v>
       </c>
       <c r="Q145">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="R145">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S145">
         <v>1.3</v>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK145">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24439,13 +24439,13 @@
         <v>3.64</v>
       </c>
       <c r="P148">
-        <v>4.8</v>
+        <v>4.55</v>
       </c>
       <c r="Q148">
         <v>2.39</v>
       </c>
       <c r="R148">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S148">
         <v>1.42</v>
@@ -24472,7 +24472,7 @@
         <v>2.93</v>
       </c>
       <c r="AA148">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="AB148">
         <v>1.71</v>
@@ -24490,7 +24490,7 @@
         <v>1.99</v>
       </c>
       <c r="AG148">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
@@ -24780,10 +24780,10 @@
         <v>3</v>
       </c>
       <c r="U150">
-        <v>2.51</v>
+        <v>2.75</v>
       </c>
       <c r="V150">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W150">
         <v>1.08</v>
@@ -27074,25 +27074,25 @@
         <v>1.01</v>
       </c>
       <c r="Y164">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z164">
-        <v>4.25</v>
+        <v>4.64</v>
       </c>
       <c r="AA164">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB164">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="AC164">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="AD164">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AE164">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AF164">
         <v>1.5</v>
@@ -27111,10 +27111,10 @@
         </is>
       </c>
       <c r="AJ164">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK164">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AL164">
         <v>0</v>
@@ -27222,16 +27222,16 @@
         <v>1.33</v>
       </c>
       <c r="T165">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="U165">
         <v>2.88</v>
       </c>
       <c r="V165">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W165">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X165">
         <v>1.01</v>
@@ -27249,13 +27249,13 @@
         <v>1.85</v>
       </c>
       <c r="AC165">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
       <c r="AD165">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE165">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF165">
         <v>1.68</v>
@@ -28345,19 +28345,19 @@
         </is>
       </c>
       <c r="N172">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="O172">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="P172">
-        <v>5.24</v>
+        <v>5.03</v>
       </c>
       <c r="Q172">
         <v>1.9</v>
       </c>
       <c r="R172">
-        <v>2.92</v>
+        <v>2.73</v>
       </c>
       <c r="S172">
         <v>1.17</v>
@@ -28366,13 +28366,13 @@
         <v>4.8</v>
       </c>
       <c r="U172">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="V172">
         <v>1.93</v>
       </c>
       <c r="W172">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="X172">
         <v>1.01</v>
@@ -28381,28 +28381,28 @@
         <v>1.04</v>
       </c>
       <c r="Z172">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AA172">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AB172">
         <v>3.6</v>
       </c>
       <c r="AC172">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AD172">
-        <v>1.96</v>
+        <v>2.07</v>
       </c>
       <c r="AE172">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AF172">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AG172">
-        <v>2.73</v>
+        <v>2.84</v>
       </c>
       <c r="AH172" t="inlineStr">
         <is>
@@ -28418,7 +28418,7 @@
         <v>1.11</v>
       </c>
       <c r="AK172">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G173">
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G174">
@@ -29000,7 +29000,7 @@
         <v>3.4</v>
       </c>
       <c r="O176">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="P176">
         <v>1.95</v>
@@ -29009,28 +29009,28 @@
         <v>3.72</v>
       </c>
       <c r="R176">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="S176">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T176">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="U176">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="V176">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W176">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X176">
         <v>1.02</v>
       </c>
       <c r="Y176">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z176">
         <v>2.92</v>
@@ -29042,7 +29042,7 @@
         <v>1.7</v>
       </c>
       <c r="AC176">
-        <v>3.58</v>
+        <v>3.74</v>
       </c>
       <c r="AD176">
         <v>1.21</v>
@@ -31155,7 +31155,7 @@
         <v>3.75</v>
       </c>
       <c r="AA189">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AB189">
         <v>2.01</v>
@@ -31186,10 +31186,10 @@
         </is>
       </c>
       <c r="AJ189">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK189">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AL189">
         <v>0</v>
@@ -31324,16 +31324,16 @@
         <v>2.35</v>
       </c>
       <c r="AC190">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AD190">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AE190">
         <v>1.15</v>
       </c>
       <c r="AF190">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG190">
         <v>2.16</v>
@@ -31442,7 +31442,7 @@
         </is>
       </c>
       <c r="N191">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="O191">
         <v>3.4</v>
@@ -31451,7 +31451,7 @@
         <v>2.59</v>
       </c>
       <c r="Q191">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="R191">
         <v>2.15</v>
@@ -31463,7 +31463,7 @@
         <v>3.02</v>
       </c>
       <c r="U191">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="V191">
         <v>1.44</v>
@@ -31512,10 +31512,10 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK191">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -31620,16 +31620,16 @@
         <v>3.14</v>
       </c>
       <c r="S192">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="T192">
-        <v>6</v>
+        <v>5.55</v>
       </c>
       <c r="U192">
         <v>1.71</v>
       </c>
       <c r="V192">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="W192">
         <v>1.32</v>
@@ -31678,7 +31678,7 @@
         <v>1.06</v>
       </c>
       <c r="AK192">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AL192">
         <v>0</v>
@@ -31940,22 +31940,22 @@
         <v>2</v>
       </c>
       <c r="Q194">
-        <v>4</v>
+        <v>4.37</v>
       </c>
       <c r="R194">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="S194">
         <v>1.36</v>
       </c>
       <c r="T194">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="U194">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="V194">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W194">
         <v>1.05</v>
@@ -31988,7 +31988,7 @@
         <v>1.83</v>
       </c>
       <c r="AG194">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AH194" t="inlineStr">
         <is>
@@ -32001,10 +32001,10 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK194">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32106,22 +32106,22 @@
         <v>2.1</v>
       </c>
       <c r="R195">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S195">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="T195">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="U195">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="V195">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W195">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X195">
         <v>1.01</v>
@@ -32133,10 +32133,10 @@
         <v>3.94</v>
       </c>
       <c r="AA195">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB195">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC195">
         <v>2.62</v>
@@ -32151,7 +32151,7 @@
         <v>1.65</v>
       </c>
       <c r="AG195">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32266,10 +32266,10 @@
         <v>2.45</v>
       </c>
       <c r="Q196">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="R196">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S196">
         <v>1.25</v>
@@ -32284,7 +32284,7 @@
         <v>1.62</v>
       </c>
       <c r="W196">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X196">
         <v>1.02</v>
@@ -32296,16 +32296,16 @@
         <v>5</v>
       </c>
       <c r="AA196">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AB196">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="AC196">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AD196">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AE196">
         <v>1.2</v>
@@ -32426,7 +32426,7 @@
         <v>4.2</v>
       </c>
       <c r="P197">
-        <v>4.73</v>
+        <v>4.7</v>
       </c>
       <c r="Q197">
         <v>2.02</v>
@@ -32465,7 +32465,7 @@
         <v>2.7</v>
       </c>
       <c r="AC197">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AD197">
         <v>1.66</v>
@@ -32490,7 +32490,7 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AK197">
         <v>2.33</v>
@@ -32607,7 +32607,7 @@
         <v>2.9</v>
       </c>
       <c r="V198">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W198">
         <v>1.04</v>
@@ -32755,16 +32755,16 @@
         <v>1.95</v>
       </c>
       <c r="Q199">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="R199">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="S199">
         <v>1.22</v>
       </c>
       <c r="T199">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="U199">
         <v>2.2</v>
@@ -32782,7 +32782,7 @@
         <v>1.1</v>
       </c>
       <c r="Z199">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="AA199">
         <v>1.43</v>
@@ -32803,7 +32803,7 @@
         <v>1.42</v>
       </c>
       <c r="AG199">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="AH199" t="inlineStr">
         <is>
@@ -32816,7 +32816,7 @@
         </is>
       </c>
       <c r="AJ199">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AK199">
         <v>1.3</v>
@@ -32909,43 +32909,43 @@
         </is>
       </c>
       <c r="N200">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="O200">
         <v>3.8</v>
       </c>
       <c r="P200">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="Q200">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="R200">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S200">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T200">
         <v>3.64</v>
       </c>
       <c r="U200">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="V200">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="W200">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X200">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y200">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z200">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="AA200">
         <v>1.42</v>
@@ -32954,19 +32954,19 @@
         <v>2.49</v>
       </c>
       <c r="AC200">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AD200">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AE200">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AF200">
         <v>1.44</v>
       </c>
       <c r="AG200">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="AH200" t="inlineStr">
         <is>
@@ -32979,10 +32979,10 @@
         </is>
       </c>
       <c r="AJ200">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK200">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AL200">
         <v>0</v>
@@ -33142,7 +33142,7 @@
         </is>
       </c>
       <c r="AJ201">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AK201">
         <v>2.95</v>
@@ -33235,80 +33235,80 @@
         </is>
       </c>
       <c r="N202">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="O202">
-        <v>3.84</v>
+        <v>3.62</v>
       </c>
       <c r="P202">
         <v>3.6</v>
       </c>
       <c r="Q202">
-        <v>2.35</v>
+        <v>2.56</v>
       </c>
       <c r="R202">
-        <v>2.32</v>
+        <v>2.37</v>
       </c>
       <c r="S202">
+        <v>1.3</v>
+      </c>
+      <c r="T202">
+        <v>3.25</v>
+      </c>
+      <c r="U202">
+        <v>2.45</v>
+      </c>
+      <c r="V202">
+        <v>1.46</v>
+      </c>
+      <c r="W202">
+        <v>1.11</v>
+      </c>
+      <c r="X202">
+        <v>1.02</v>
+      </c>
+      <c r="Y202">
+        <v>1.17</v>
+      </c>
+      <c r="Z202">
+        <v>4.15</v>
+      </c>
+      <c r="AA202">
+        <v>1.72</v>
+      </c>
+      <c r="AB202">
+        <v>2.1</v>
+      </c>
+      <c r="AC202">
+        <v>2.66</v>
+      </c>
+      <c r="AD202">
+        <v>1.43</v>
+      </c>
+      <c r="AE202">
+        <v>1.11</v>
+      </c>
+      <c r="AF202">
+        <v>1.59</v>
+      </c>
+      <c r="AG202">
+        <v>2.21</v>
+      </c>
+      <c r="AH202" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI202" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ202">
         <v>1.26</v>
       </c>
-      <c r="T202">
-        <v>3.38</v>
-      </c>
-      <c r="U202">
-        <v>2.32</v>
-      </c>
-      <c r="V202">
-        <v>1.52</v>
-      </c>
-      <c r="W202">
-        <v>1.09</v>
-      </c>
-      <c r="X202">
-        <v>1.01</v>
-      </c>
-      <c r="Y202">
-        <v>1.13</v>
-      </c>
-      <c r="Z202">
-        <v>4.55</v>
-      </c>
-      <c r="AA202">
-        <v>1.58</v>
-      </c>
-      <c r="AB202">
-        <v>2.29</v>
-      </c>
-      <c r="AC202">
-        <v>2.38</v>
-      </c>
-      <c r="AD202">
-        <v>1.46</v>
-      </c>
-      <c r="AE202">
-        <v>1.15</v>
-      </c>
-      <c r="AF202">
-        <v>1.53</v>
-      </c>
-      <c r="AG202">
-        <v>2.35</v>
-      </c>
-      <c r="AH202" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI202" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ202">
-        <v>1.23</v>
-      </c>
       <c r="AK202">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AL202">
         <v>0</v>
@@ -33398,7 +33398,7 @@
         </is>
       </c>
       <c r="N203">
-        <v>4</v>
+        <v>3.64</v>
       </c>
       <c r="O203">
         <v>3.1</v>
@@ -33570,7 +33570,7 @@
         <v>4.2</v>
       </c>
       <c r="Q204">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R204">
         <v>2.12</v>
@@ -33579,7 +33579,7 @@
         <v>1.37</v>
       </c>
       <c r="T204">
-        <v>3.2</v>
+        <v>2.78</v>
       </c>
       <c r="U204">
         <v>2.53</v>
@@ -33591,10 +33591,10 @@
         <v>1.1</v>
       </c>
       <c r="X204">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y204">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="Z204">
         <v>3.58</v>
@@ -33609,7 +33609,7 @@
         <v>3.05</v>
       </c>
       <c r="AD204">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE204">
         <v>1.11</v>
@@ -33724,7 +33724,7 @@
         </is>
       </c>
       <c r="N205">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="O205">
         <v>4.85</v>
@@ -33739,19 +33739,19 @@
         <v>2.27</v>
       </c>
       <c r="S205">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T205">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U205">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="V205">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W205">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X205">
         <v>1</v>
@@ -33760,7 +33760,7 @@
         <v>1.15</v>
       </c>
       <c r="Z205">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="AA205">
         <v>1.54</v>
@@ -33769,19 +33769,19 @@
         <v>2.19</v>
       </c>
       <c r="AC205">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="AD205">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AE205">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF205">
         <v>1.83</v>
       </c>
       <c r="AG205">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH205" t="inlineStr">
         <is>
@@ -33794,10 +33794,10 @@
         </is>
       </c>
       <c r="AJ205">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AK205">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="AL205">
         <v>0</v>
@@ -34865,25 +34865,25 @@
         </is>
       </c>
       <c r="N212">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="O212">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="P212">
         <v>4</v>
       </c>
       <c r="Q212">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="R212">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="S212">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T212">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="U212">
         <v>2.13</v>
@@ -34919,10 +34919,10 @@
         <v>1.29</v>
       </c>
       <c r="AF212">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AG212">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="AH212" t="inlineStr">
         <is>
@@ -35028,25 +35028,25 @@
         </is>
       </c>
       <c r="N213">
-        <v>5.25</v>
+        <v>5.05</v>
       </c>
       <c r="O213">
         <v>4.1</v>
       </c>
       <c r="P213">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q213">
         <v>5</v>
       </c>
       <c r="R213">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S213">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T213">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U213">
         <v>2.4</v>
@@ -35061,22 +35061,22 @@
         <v>1</v>
       </c>
       <c r="Y213">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z213">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
       <c r="AA213">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AB213">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AC213">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AD213">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AE213">
         <v>1.18</v>
@@ -35101,7 +35101,7 @@
         <v>1.18</v>
       </c>
       <c r="AK213">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AL213">
         <v>0</v>
@@ -35357,46 +35357,46 @@
         <v>1.11</v>
       </c>
       <c r="O215">
-        <v>8.65</v>
+        <v>8.85</v>
       </c>
       <c r="P215">
         <v>24</v>
       </c>
       <c r="Q215">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="R215">
-        <v>2.63</v>
+        <v>2.68</v>
       </c>
       <c r="S215">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T215">
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="U215">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="V215">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W215">
         <v>1.16</v>
       </c>
       <c r="X215">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y215">
         <v>1.09</v>
       </c>
       <c r="Z215">
-        <v>6.88</v>
+        <v>6.29</v>
       </c>
       <c r="AA215">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AB215">
-        <v>2.81</v>
+        <v>2.76</v>
       </c>
       <c r="AC215">
         <v>2.02</v>
@@ -35427,7 +35427,7 @@
         <v>1.06</v>
       </c>
       <c r="AK215">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="AL215">
         <v>0</v>
@@ -35648,12 +35648,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Manresa</t>
         </is>
       </c>
       <c r="G217">
@@ -35680,64 +35680,64 @@
         </is>
       </c>
       <c r="N217">
-        <v>2.09</v>
+        <v>1.74</v>
       </c>
       <c r="O217">
-        <v>3.24</v>
+        <v>3.32</v>
       </c>
       <c r="P217">
-        <v>3.02</v>
+        <v>4.3</v>
       </c>
       <c r="Q217">
-        <v>2.82</v>
+        <v>2.4</v>
       </c>
       <c r="R217">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="S217">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T217">
-        <v>2.8</v>
+        <v>2.61</v>
       </c>
       <c r="U217">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="V217">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="W217">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X217">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y217">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Z217">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AA217">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AB217">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC217">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="AD217">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AE217">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF217">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="AG217">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="AH217" t="inlineStr">
         <is>
@@ -35750,10 +35750,10 @@
         </is>
       </c>
       <c r="AJ217">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AK217">
-        <v>1.64</v>
+        <v>1.86</v>
       </c>
       <c r="AL217">
         <v>0</v>
@@ -35811,12 +35811,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Manresa</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G218">
@@ -35843,64 +35843,64 @@
         </is>
       </c>
       <c r="N218">
-        <v>1.74</v>
+        <v>2.09</v>
       </c>
       <c r="O218">
-        <v>3.32</v>
+        <v>3.24</v>
       </c>
       <c r="P218">
-        <v>4.3</v>
+        <v>3.02</v>
       </c>
       <c r="Q218">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="R218">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S218">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T218">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U218">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="V218">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W218">
+        <v>1.06</v>
+      </c>
+      <c r="X218">
+        <v>1.02</v>
+      </c>
+      <c r="Y218">
+        <v>1.29</v>
+      </c>
+      <c r="Z218">
+        <v>3.04</v>
+      </c>
+      <c r="AA218">
+        <v>2.05</v>
+      </c>
+      <c r="AB218">
+        <v>1.75</v>
+      </c>
+      <c r="AC218">
+        <v>3.5</v>
+      </c>
+      <c r="AD218">
+        <v>1.22</v>
+      </c>
+      <c r="AE218">
         <v>1.05</v>
       </c>
-      <c r="X218">
-        <v>0</v>
-      </c>
-      <c r="Y218">
-        <v>1.34</v>
-      </c>
-      <c r="Z218">
-        <v>2.78</v>
-      </c>
-      <c r="AA218">
-        <v>2.13</v>
-      </c>
-      <c r="AB218">
-        <v>1.61</v>
-      </c>
-      <c r="AC218">
-        <v>3.88</v>
-      </c>
-      <c r="AD218">
-        <v>1.18</v>
-      </c>
-      <c r="AE218">
-        <v>0</v>
-      </c>
       <c r="AF218">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="AG218">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AH218" t="inlineStr">
         <is>
@@ -35913,10 +35913,10 @@
         </is>
       </c>
       <c r="AJ218">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK218">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AL218">
         <v>0</v>
@@ -36015,7 +36015,7 @@
         <v>3.25</v>
       </c>
       <c r="Q219">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R219">
         <v>2.15</v>
@@ -36024,7 +36024,7 @@
         <v>1.3</v>
       </c>
       <c r="T219">
-        <v>3.3</v>
+        <v>2.96</v>
       </c>
       <c r="U219">
         <v>2.45</v>
@@ -36051,10 +36051,10 @@
         <v>2.08</v>
       </c>
       <c r="AC219">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AD219">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AE219">
         <v>1.13</v>
@@ -36079,7 +36079,7 @@
         <v>1.22</v>
       </c>
       <c r="AK219">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AL219">
         <v>0</v>
@@ -36169,7 +36169,7 @@
         </is>
       </c>
       <c r="N220">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="O220">
         <v>3.7</v>
@@ -36178,7 +36178,7 @@
         <v>2.3</v>
       </c>
       <c r="Q220">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="R220">
         <v>2.45</v>
@@ -36187,7 +36187,7 @@
         <v>1.22</v>
       </c>
       <c r="T220">
-        <v>3.8</v>
+        <v>3.56</v>
       </c>
       <c r="U220">
         <v>2.18</v>
@@ -36242,7 +36242,7 @@
         <v>1.25</v>
       </c>
       <c r="AK220">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AL220">
         <v>0</v>
@@ -36332,7 +36332,7 @@
         </is>
       </c>
       <c r="N221">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="O221">
         <v>4.48</v>
@@ -36341,10 +36341,10 @@
         <v>5.6</v>
       </c>
       <c r="Q221">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="R221">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="S221">
         <v>1.22</v>
@@ -36356,19 +36356,19 @@
         <v>2</v>
       </c>
       <c r="V221">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="W221">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X221">
         <v>1</v>
       </c>
       <c r="Y221">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z221">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="AA221">
         <v>1.43</v>
@@ -36377,13 +36377,13 @@
         <v>2.75</v>
       </c>
       <c r="AC221">
-        <v>1.99</v>
+        <v>2.07</v>
       </c>
       <c r="AD221">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AE221">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AF221">
         <v>1.53</v>
@@ -36498,7 +36498,7 @@
         <v>2.87</v>
       </c>
       <c r="O222">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P222">
         <v>2.5</v>
@@ -36510,10 +36510,10 @@
         <v>2</v>
       </c>
       <c r="S222">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="T222">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="U222">
         <v>2.9</v>
@@ -36537,7 +36537,7 @@
         <v>2.1</v>
       </c>
       <c r="AB222">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC222">
         <v>3.42</v>
@@ -36568,7 +36568,7 @@
         <v>1.36</v>
       </c>
       <c r="AK222">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AL222">
         <v>0</v>
@@ -36673,10 +36673,10 @@
         <v>2.05</v>
       </c>
       <c r="S223">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T223">
-        <v>2.86</v>
+        <v>2.64</v>
       </c>
       <c r="U223">
         <v>2.85</v>
@@ -36694,7 +36694,7 @@
         <v>1.31</v>
       </c>
       <c r="Z223">
-        <v>3.18</v>
+        <v>3.27</v>
       </c>
       <c r="AA223">
         <v>2.03</v>
@@ -36839,7 +36839,7 @@
         <v>1.5</v>
       </c>
       <c r="T224">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="U224">
         <v>3.4</v>
@@ -36860,10 +36860,10 @@
         <v>2.29</v>
       </c>
       <c r="AA224">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AB224">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AC224">
         <v>5.1</v>
@@ -36878,7 +36878,7 @@
         <v>2.2</v>
       </c>
       <c r="AG224">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AH224" t="inlineStr">
         <is>
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G225">
@@ -36984,64 +36984,64 @@
         </is>
       </c>
       <c r="N225">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O225">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P225">
-        <v>0</v>
+        <v>5.62</v>
       </c>
       <c r="Q225">
-        <v>2.61</v>
+        <v>2.12</v>
       </c>
       <c r="R225">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="S225">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T225">
-        <v>2.86</v>
+        <v>2.69</v>
       </c>
       <c r="U225">
-        <v>2.55</v>
+        <v>2.73</v>
       </c>
       <c r="V225">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="W225">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X225">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y225">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z225">
-        <v>3.28</v>
+        <v>2.97</v>
       </c>
       <c r="AA225">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="AB225">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AC225">
-        <v>3.04</v>
+        <v>3.34</v>
       </c>
       <c r="AD225">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE225">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF225">
-        <v>1.69</v>
+        <v>2.01</v>
       </c>
       <c r="AG225">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AH225" t="inlineStr">
         <is>
@@ -37054,10 +37054,10 @@
         </is>
       </c>
       <c r="AJ225">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK225">
-        <v>1.62</v>
+        <v>2.4</v>
       </c>
       <c r="AL225">
         <v>0</v>
@@ -37156,34 +37156,34 @@
         <v>6</v>
       </c>
       <c r="Q226">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="R226">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S226">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T226">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U226">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V226">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W226">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X226">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y226">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z226">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA226">
         <v>1.75</v>
@@ -37192,19 +37192,19 @@
         <v>2.05</v>
       </c>
       <c r="AC226">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AD226">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE226">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF226">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG226">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH226" t="inlineStr">
         <is>
@@ -37217,10 +37217,10 @@
         </is>
       </c>
       <c r="AJ226">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK226">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL226">
         <v>0</v>
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Calvo Sotelo</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G227">
@@ -37310,64 +37310,64 @@
         </is>
       </c>
       <c r="N227">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O227">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P227">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q227">
-        <v>2.77</v>
+        <v>3.98</v>
       </c>
       <c r="R227">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="S227">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="T227">
-        <v>3.18</v>
+        <v>3.46</v>
       </c>
       <c r="U227">
-        <v>2.4</v>
+        <v>2.19</v>
       </c>
       <c r="V227">
+        <v>1.55</v>
+      </c>
+      <c r="W227">
+        <v>1.13</v>
+      </c>
+      <c r="X227">
+        <v>0</v>
+      </c>
+      <c r="Y227">
+        <v>1.14</v>
+      </c>
+      <c r="Z227">
+        <v>4.4</v>
+      </c>
+      <c r="AA227">
+        <v>1.56</v>
+      </c>
+      <c r="AB227">
+        <v>2.22</v>
+      </c>
+      <c r="AC227">
+        <v>2.38</v>
+      </c>
+      <c r="AD227">
         <v>1.46</v>
       </c>
-      <c r="W227">
-        <v>1.07</v>
-      </c>
-      <c r="X227">
-        <v>0</v>
-      </c>
-      <c r="Y227">
-        <v>1.18</v>
-      </c>
-      <c r="Z227">
-        <v>3.86</v>
-      </c>
-      <c r="AA227">
-        <v>1.7</v>
-      </c>
-      <c r="AB227">
-        <v>1.99</v>
-      </c>
-      <c r="AC227">
-        <v>2.74</v>
-      </c>
-      <c r="AD227">
-        <v>1.35</v>
-      </c>
       <c r="AE227">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AF227">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="AG227">
-        <v>2.17</v>
+        <v>2.34</v>
       </c>
       <c r="AH227" t="inlineStr">
         <is>
@@ -37380,10 +37380,10 @@
         </is>
       </c>
       <c r="AJ227">
+        <v>1.19</v>
+      </c>
+      <c r="AK227">
         <v>1.22</v>
-      </c>
-      <c r="AK227">
-        <v>1.53</v>
       </c>
       <c r="AL227">
         <v>0</v>
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G228">
@@ -37473,80 +37473,80 @@
         </is>
       </c>
       <c r="N228">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="O228">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P228">
-        <v>5.62</v>
+        <v>0</v>
       </c>
       <c r="Q228">
-        <v>2</v>
+        <v>2.63</v>
       </c>
       <c r="R228">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S228">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T228">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="U228">
-        <v>2.88</v>
+        <v>2.55</v>
       </c>
       <c r="V228">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="W228">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X228">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y228">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z228">
-        <v>2.97</v>
+        <v>3.28</v>
       </c>
       <c r="AA228">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="AB228">
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="AC228">
-        <v>3.34</v>
+        <v>3.04</v>
       </c>
       <c r="AD228">
+        <v>1.29</v>
+      </c>
+      <c r="AE228">
+        <v>1.08</v>
+      </c>
+      <c r="AF228">
+        <v>1.69</v>
+      </c>
+      <c r="AG228">
+        <v>2.03</v>
+      </c>
+      <c r="AH228" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI228" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ228">
         <v>1.24</v>
       </c>
-      <c r="AE228">
-        <v>0</v>
-      </c>
-      <c r="AF228">
-        <v>2.04</v>
-      </c>
-      <c r="AG228">
-        <v>1.66</v>
-      </c>
-      <c r="AH228" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI228" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ228">
-        <v>1.22</v>
-      </c>
       <c r="AK228">
-        <v>2.4</v>
+        <v>1.62</v>
       </c>
       <c r="AL228">
         <v>0</v>
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Calvo Sotelo</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G229">
@@ -37636,64 +37636,64 @@
         </is>
       </c>
       <c r="N229">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O229">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P229">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q229">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R229">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S229">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T229">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U229">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V229">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W229">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X229">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y229">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z229">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AA229">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AB229">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AC229">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD229">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE229">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF229">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG229">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH229" t="inlineStr">
         <is>
@@ -37706,10 +37706,10 @@
         </is>
       </c>
       <c r="AJ229">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK229">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL229">
         <v>0</v>
@@ -37799,13 +37799,13 @@
         </is>
       </c>
       <c r="N230">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="O230">
         <v>3.8</v>
       </c>
       <c r="P230">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="Q230">
         <v>3.9</v>
@@ -37814,7 +37814,7 @@
         <v>2.4</v>
       </c>
       <c r="S230">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T230">
         <v>3.6</v>
@@ -37844,19 +37844,19 @@
         <v>2.4</v>
       </c>
       <c r="AC230">
-        <v>2.41</v>
+        <v>2.23</v>
       </c>
       <c r="AD230">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AE230">
         <v>1.2</v>
       </c>
       <c r="AF230">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AG230">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="AH230" t="inlineStr">
         <is>
@@ -37869,10 +37869,10 @@
         </is>
       </c>
       <c r="AJ230">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK230">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AL230">
         <v>0</v>
@@ -37989,7 +37989,7 @@
         <v>1.36</v>
       </c>
       <c r="W231">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X231">
         <v>1.02</v>
@@ -38019,7 +38019,7 @@
         <v>1.75</v>
       </c>
       <c r="AG231">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AH231" t="inlineStr">
         <is>
@@ -38318,7 +38318,7 @@
         <v>1.07</v>
       </c>
       <c r="X233">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y233">
         <v>1.23</v>
@@ -38339,7 +38339,7 @@
         <v>1.28</v>
       </c>
       <c r="AE233">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF233">
         <v>1.71</v>
@@ -38623,55 +38623,55 @@
         <v>6.5</v>
       </c>
       <c r="Q235">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="R235">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="S235">
         <v>1.36</v>
       </c>
       <c r="T235">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U235">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="V235">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="W235">
         <v>1.06</v>
       </c>
       <c r="X235">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y235">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z235">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="AA235">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AB235">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC235">
         <v>3.2</v>
       </c>
       <c r="AD235">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE235">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF235">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AG235">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AH235" t="inlineStr">
         <is>
@@ -38684,10 +38684,10 @@
         </is>
       </c>
       <c r="AJ235">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AK235">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AL235">
         <v>0</v>
@@ -38792,7 +38792,7 @@
         <v>2.23</v>
       </c>
       <c r="S236">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T236">
         <v>3.12</v>
@@ -38834,7 +38834,7 @@
         <v>1.65</v>
       </c>
       <c r="AG236">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="AH236" t="inlineStr">
         <is>
@@ -38847,7 +38847,7 @@
         </is>
       </c>
       <c r="AJ236">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK236">
         <v>2.07</v>
@@ -40081,19 +40081,19 @@
         </is>
       </c>
       <c r="N244">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="O244">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="P244">
-        <v>5.86</v>
+        <v>4.8</v>
       </c>
       <c r="Q244">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="R244">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S244">
         <v>1.29</v>
@@ -40102,44 +40102,44 @@
         <v>3.3</v>
       </c>
       <c r="U244">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="V244">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W244">
         <v>1.08</v>
       </c>
       <c r="X244">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y244">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z244">
-        <v>3.85</v>
+        <v>4.24</v>
       </c>
       <c r="AA244">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AB244">
+        <v>2.17</v>
+      </c>
+      <c r="AC244">
+        <v>2.43</v>
+      </c>
+      <c r="AD244">
+        <v>1.45</v>
+      </c>
+      <c r="AE244">
+        <v>1.17</v>
+      </c>
+      <c r="AF244">
+        <v>1.66</v>
+      </c>
+      <c r="AG244">
         <v>2.09</v>
       </c>
-      <c r="AC244">
-        <v>2.59</v>
-      </c>
-      <c r="AD244">
-        <v>1.39</v>
-      </c>
-      <c r="AE244">
-        <v>1.12</v>
-      </c>
-      <c r="AF244">
-        <v>1.82</v>
-      </c>
-      <c r="AG244">
-        <v>1.88</v>
-      </c>
       <c r="AH244" t="inlineStr">
         <is>
           <t>[]</t>
@@ -40151,10 +40151,10 @@
         </is>
       </c>
       <c r="AJ244">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK244">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="AL244">
         <v>0</v>
@@ -40244,16 +40244,16 @@
         </is>
       </c>
       <c r="N245">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="O245">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P245">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Q245">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="R245">
         <v>2.37</v>
@@ -40283,10 +40283,10 @@
         <v>3.9</v>
       </c>
       <c r="AA245">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="AB245">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AC245">
         <v>2.99</v>
@@ -40416,16 +40416,16 @@
         <v>7.4</v>
       </c>
       <c r="Q246">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="R246">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="S246">
         <v>1.22</v>
       </c>
       <c r="T246">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="U246">
         <v>2.35</v>
@@ -40446,13 +40446,13 @@
         <v>5.25</v>
       </c>
       <c r="AA246">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="AB246">
         <v>2.5</v>
       </c>
       <c r="AC246">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="AD246">
         <v>1.56</v>
@@ -40461,7 +40461,7 @@
         <v>1.2</v>
       </c>
       <c r="AF246">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG246">
         <v>2</v>
@@ -40477,10 +40477,10 @@
         </is>
       </c>
       <c r="AJ246">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AK246">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AL246">
         <v>0</v>
@@ -40570,25 +40570,25 @@
         </is>
       </c>
       <c r="N247">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="O247">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="P247">
-        <v>3.37</v>
+        <v>3.5</v>
       </c>
       <c r="Q247">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="R247">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="S247">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T247">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="U247">
         <v>2.45</v>
@@ -40627,7 +40627,7 @@
         <v>1.68</v>
       </c>
       <c r="AG247">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="AH247" t="inlineStr">
         <is>
@@ -40733,13 +40733,13 @@
         </is>
       </c>
       <c r="N248">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="O248">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="P248">
-        <v>4.63</v>
+        <v>4.4</v>
       </c>
       <c r="Q248">
         <v>2.34</v>
@@ -40896,25 +40896,25 @@
         </is>
       </c>
       <c r="N249">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="O249">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P249">
-        <v>4.21</v>
+        <v>4</v>
       </c>
       <c r="Q249">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="R249">
         <v>2.15</v>
       </c>
       <c r="S249">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T249">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="U249">
         <v>2.48</v>
@@ -40953,7 +40953,7 @@
         <v>1.73</v>
       </c>
       <c r="AG249">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AH249" t="inlineStr">
         <is>
@@ -41059,25 +41059,25 @@
         </is>
       </c>
       <c r="N250">
-        <v>3.41</v>
+        <v>3.09</v>
       </c>
       <c r="O250">
-        <v>3.68</v>
+        <v>3.3</v>
       </c>
       <c r="P250">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="Q250">
         <v>3.31</v>
       </c>
       <c r="R250">
-        <v>2.13</v>
+        <v>2.33</v>
       </c>
       <c r="S250">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T250">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="U250">
         <v>2.68</v>
@@ -41089,7 +41089,7 @@
         <v>1.07</v>
       </c>
       <c r="X250">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y250">
         <v>1.26</v>
@@ -41098,25 +41098,25 @@
         <v>3.72</v>
       </c>
       <c r="AA250">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AB250">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AC250">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="AD250">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE250">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF250">
         <v>1.63</v>
       </c>
       <c r="AG250">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AH250" t="inlineStr">
         <is>
@@ -41129,10 +41129,10 @@
         </is>
       </c>
       <c r="AJ250">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK250">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL250">
         <v>0</v>
@@ -41222,13 +41222,13 @@
         </is>
       </c>
       <c r="N251">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="O251">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="P251">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="Q251">
         <v>0</v>
@@ -41557,34 +41557,34 @@
         <v>3.32</v>
       </c>
       <c r="Q253">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R253">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S253">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T253">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U253">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V253">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W253">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X253">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y253">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z253">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA253">
         <v>1.8</v>
@@ -41593,19 +41593,19 @@
         <v>2</v>
       </c>
       <c r="AC253">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD253">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE253">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF253">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG253">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AH253" t="inlineStr">
         <is>
@@ -41618,10 +41618,10 @@
         </is>
       </c>
       <c r="AJ253">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK253">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL253">
         <v>0</v>
@@ -41720,34 +41720,34 @@
         <v>3.09</v>
       </c>
       <c r="Q254">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R254">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S254">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T254">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U254">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V254">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W254">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X254">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y254">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z254">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA254">
         <v>2</v>
@@ -41756,19 +41756,19 @@
         <v>1.8</v>
       </c>
       <c r="AC254">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD254">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE254">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF254">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG254">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH254" t="inlineStr">
         <is>
@@ -41781,10 +41781,10 @@
         </is>
       </c>
       <c r="AJ254">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK254">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL254">
         <v>0</v>
@@ -41904,7 +41904,7 @@
         <v>1.07</v>
       </c>
       <c r="X255">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y255">
         <v>1.24</v>
@@ -41913,10 +41913,10 @@
         <v>3.34</v>
       </c>
       <c r="AA255">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB255">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="AC255">
         <v>3.04</v>
@@ -42037,25 +42037,25 @@
         </is>
       </c>
       <c r="N256">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="O256">
         <v>3.1</v>
       </c>
       <c r="P256">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="Q256">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R256">
         <v>2</v>
       </c>
       <c r="S256">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T256">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="U256">
         <v>2.81</v>
@@ -42107,10 +42107,10 @@
         </is>
       </c>
       <c r="AJ256">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AK256">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AL256">
         <v>0</v>
@@ -42363,13 +42363,13 @@
         </is>
       </c>
       <c r="N258">
-        <v>3.94</v>
+        <v>3.75</v>
       </c>
       <c r="O258">
-        <v>3.94</v>
+        <v>3.68</v>
       </c>
       <c r="P258">
-        <v>1.97</v>
+        <v>1.74</v>
       </c>
       <c r="Q258">
         <v>4.55</v>
@@ -42396,25 +42396,25 @@
         <v>1</v>
       </c>
       <c r="Y258">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z258">
         <v>4.36</v>
       </c>
       <c r="AA258">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AB258">
         <v>2.26</v>
       </c>
       <c r="AC258">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="AD258">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AE258">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AF258">
         <v>1.63</v>
@@ -42526,16 +42526,16 @@
         </is>
       </c>
       <c r="N259">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="O259">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P259">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q259">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="R259">
         <v>2.3</v>
@@ -42544,7 +42544,7 @@
         <v>1.27</v>
       </c>
       <c r="T259">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="U259">
         <v>2.4</v>
@@ -42568,7 +42568,7 @@
         <v>1.68</v>
       </c>
       <c r="AB259">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AC259">
         <v>2.63</v>
@@ -42596,7 +42596,7 @@
         </is>
       </c>
       <c r="AJ259">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK259">
         <v>1.2</v>
@@ -42698,71 +42698,71 @@
         <v>4.2</v>
       </c>
       <c r="Q260">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R260">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S260">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T260">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U260">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V260">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W260">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X260">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y260">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z260">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA260">
+        <v>1.93</v>
+      </c>
+      <c r="AB260">
+        <v>1.75</v>
+      </c>
+      <c r="AC260">
+        <v>3.34</v>
+      </c>
+      <c r="AD260">
+        <v>1.24</v>
+      </c>
+      <c r="AE260">
+        <v>1.1</v>
+      </c>
+      <c r="AF260">
+        <v>1.84</v>
+      </c>
+      <c r="AG260">
+        <v>1.85</v>
+      </c>
+      <c r="AH260" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI260" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ260">
+        <v>1.25</v>
+      </c>
+      <c r="AK260">
         <v>2</v>
-      </c>
-      <c r="AB260">
-        <v>1.8</v>
-      </c>
-      <c r="AC260">
-        <v>0</v>
-      </c>
-      <c r="AD260">
-        <v>0</v>
-      </c>
-      <c r="AE260">
-        <v>0</v>
-      </c>
-      <c r="AF260">
-        <v>0</v>
-      </c>
-      <c r="AG260">
-        <v>0</v>
-      </c>
-      <c r="AH260" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI260" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ260">
-        <v>0</v>
-      </c>
-      <c r="AK260">
-        <v>0</v>
       </c>
       <c r="AL260">
         <v>0</v>
@@ -42855,10 +42855,10 @@
         <v>1.28</v>
       </c>
       <c r="O261">
-        <v>5.35</v>
+        <v>5.5</v>
       </c>
       <c r="P261">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="Q261">
         <v>1.67</v>
@@ -42867,22 +42867,22 @@
         <v>2.46</v>
       </c>
       <c r="S261">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T261">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U261">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="V261">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W261">
         <v>1.1</v>
       </c>
       <c r="X261">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y261">
         <v>1.14</v>
@@ -42891,25 +42891,25 @@
         <v>4.8</v>
       </c>
       <c r="AA261">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AB261">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AC261">
         <v>2.45</v>
       </c>
       <c r="AD261">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AE261">
         <v>1.16</v>
       </c>
       <c r="AF261">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AG261">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AH261" t="inlineStr">
         <is>
@@ -43015,13 +43015,13 @@
         </is>
       </c>
       <c r="N262">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="O262">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P262">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="Q262">
         <v>3.2</v>
@@ -43036,7 +43036,7 @@
         <v>3.1</v>
       </c>
       <c r="U262">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="V262">
         <v>1.44</v>
@@ -43045,16 +43045,16 @@
         <v>1.1</v>
       </c>
       <c r="X262">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y262">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z262">
         <v>3.72</v>
       </c>
       <c r="AA262">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB262">
         <v>2.02</v>
@@ -43066,7 +43066,7 @@
         <v>1.36</v>
       </c>
       <c r="AE262">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF262">
         <v>1.65</v>
@@ -43187,28 +43187,28 @@
         <v>7.9</v>
       </c>
       <c r="Q263">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="R263">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="S263">
         <v>1.25</v>
       </c>
       <c r="T263">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U263">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="V263">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W263">
         <v>1.13</v>
       </c>
       <c r="X263">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y263">
         <v>1.15</v>
@@ -43217,25 +43217,25 @@
         <v>4.25</v>
       </c>
       <c r="AA263">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AB263">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AC263">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="AD263">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AE263">
         <v>1.13</v>
       </c>
       <c r="AF263">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG263">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AH263" t="inlineStr">
         <is>
@@ -43248,10 +43248,10 @@
         </is>
       </c>
       <c r="AJ263">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AK263">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="AL263">
         <v>0</v>
@@ -43513,16 +43513,16 @@
         <v>1.7</v>
       </c>
       <c r="Q265">
-        <v>7.04</v>
+        <v>6.61</v>
       </c>
       <c r="R265">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="S265">
         <v>1.33</v>
       </c>
       <c r="T265">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="U265">
         <v>2.75</v>
@@ -43531,10 +43531,10 @@
         <v>1.4</v>
       </c>
       <c r="W265">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X265">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y265">
         <v>1.22</v>
@@ -43543,10 +43543,10 @@
         <v>3.5</v>
       </c>
       <c r="AA265">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AB265">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AC265">
         <v>2.92</v>
@@ -43558,10 +43558,10 @@
         <v>1.08</v>
       </c>
       <c r="AF265">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="AG265">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AH265" t="inlineStr">
         <is>
@@ -43878,10 +43878,10 @@
         <v>2.38</v>
       </c>
       <c r="AD267">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AE267">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AF267">
         <v>1.5</v>
@@ -43993,19 +43993,19 @@
         </is>
       </c>
       <c r="N268">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="O268">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="P268">
-        <v>3.25</v>
+        <v>3.41</v>
       </c>
       <c r="Q268">
         <v>2.4</v>
       </c>
       <c r="R268">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="S268">
         <v>1.25</v>
@@ -44023,28 +44023,28 @@
         <v>1.15</v>
       </c>
       <c r="X268">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y268">
         <v>1.14</v>
       </c>
       <c r="Z268">
-        <v>4.33</v>
+        <v>4.63</v>
       </c>
       <c r="AA268">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AB268">
-        <v>2.22</v>
+        <v>2.35</v>
       </c>
       <c r="AC268">
-        <v>2.35</v>
+        <v>2.49</v>
       </c>
       <c r="AD268">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="AE268">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AF268">
         <v>1.52</v>
@@ -44156,16 +44156,16 @@
         </is>
       </c>
       <c r="N269">
-        <v>3.63</v>
+        <v>3.2</v>
       </c>
       <c r="O269">
-        <v>3.53</v>
+        <v>3.3</v>
       </c>
       <c r="P269">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="Q269">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="R269">
         <v>2.09</v>
@@ -44174,7 +44174,7 @@
         <v>1.35</v>
       </c>
       <c r="T269">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="U269">
         <v>2.53</v>
@@ -44183,7 +44183,7 @@
         <v>1.44</v>
       </c>
       <c r="W269">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X269">
         <v>1</v>
@@ -44198,16 +44198,16 @@
         <v>1.76</v>
       </c>
       <c r="AB269">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AC269">
-        <v>2.85</v>
+        <v>3.08</v>
       </c>
       <c r="AD269">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE269">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF269">
         <v>1.65</v>
@@ -44319,19 +44319,19 @@
         </is>
       </c>
       <c r="N270">
-        <v>2.47</v>
+        <v>2.06</v>
       </c>
       <c r="O270">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="P270">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="Q270">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="R270">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="S270">
         <v>1.3</v>
@@ -44340,7 +44340,7 @@
         <v>3.2</v>
       </c>
       <c r="U270">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="V270">
         <v>1.45</v>
@@ -44355,25 +44355,25 @@
         <v>1.23</v>
       </c>
       <c r="Z270">
-        <v>4.03</v>
+        <v>4.06</v>
       </c>
       <c r="AA270">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB270">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AC270">
-        <v>2.97</v>
+        <v>2.81</v>
       </c>
       <c r="AD270">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE270">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF270">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG270">
         <v>2.2</v>
@@ -44389,10 +44389,10 @@
         </is>
       </c>
       <c r="AJ270">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AK270">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL270">
         <v>0</v>
@@ -44482,13 +44482,13 @@
         </is>
       </c>
       <c r="N271">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="O271">
         <v>3.4</v>
       </c>
       <c r="P271">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="Q271">
         <v>3.04</v>
@@ -44497,19 +44497,19 @@
         <v>2.08</v>
       </c>
       <c r="S271">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T271">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="U271">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="V271">
         <v>1.4</v>
       </c>
       <c r="W271">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X271">
         <v>1.03</v>
@@ -44521,22 +44521,22 @@
         <v>3.1</v>
       </c>
       <c r="AA271">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AB271">
         <v>1.89</v>
       </c>
       <c r="AC271">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="AD271">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE271">
         <v>1.07</v>
       </c>
       <c r="AF271">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG271">
         <v>2.05</v>
@@ -44552,10 +44552,10 @@
         </is>
       </c>
       <c r="AJ271">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK271">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AL271">
         <v>0</v>
@@ -44645,13 +44645,13 @@
         </is>
       </c>
       <c r="N272">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O272">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P272">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q272">
         <v>0</v>
@@ -44684,10 +44684,10 @@
         <v>0</v>
       </c>
       <c r="AA272">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB272">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC272">
         <v>0</v>
@@ -44817,55 +44817,55 @@
         <v>0</v>
       </c>
       <c r="Q273">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="R273">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S273">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T273">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U273">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="V273">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W273">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X273">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y273">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z273">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA273">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB273">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC273">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD273">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE273">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF273">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG273">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH273" t="inlineStr">
         <is>
@@ -44878,10 +44878,10 @@
         </is>
       </c>
       <c r="AJ273">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK273">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL273">
         <v>0</v>
@@ -44971,13 +44971,13 @@
         </is>
       </c>
       <c r="N274">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="O274">
-        <v>3.82</v>
+        <v>3.52</v>
       </c>
       <c r="P274">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="Q274">
         <v>4.45</v>
@@ -44986,16 +44986,16 @@
         <v>2.23</v>
       </c>
       <c r="S274">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="T274">
-        <v>3.22</v>
+        <v>2.86</v>
       </c>
       <c r="U274">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="V274">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="W274">
         <v>1.11</v>
@@ -45010,10 +45010,10 @@
         <v>3.58</v>
       </c>
       <c r="AA274">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB274">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AC274">
         <v>3</v>
@@ -45044,7 +45044,7 @@
         <v>1.26</v>
       </c>
       <c r="AK274">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AL274">
         <v>0</v>
@@ -45143,55 +45143,55 @@
         <v>0</v>
       </c>
       <c r="Q275">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="R275">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S275">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T275">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U275">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V275">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W275">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X275">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y275">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z275">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA275">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB275">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC275">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD275">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE275">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF275">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG275">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH275" t="inlineStr">
         <is>
@@ -45204,10 +45204,10 @@
         </is>
       </c>
       <c r="AJ275">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK275">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AL275">
         <v>0</v>
@@ -45306,34 +45306,34 @@
         <v>3.3</v>
       </c>
       <c r="Q276">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R276">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S276">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T276">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U276">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V276">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W276">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X276">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y276">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z276">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA276">
         <v>1.95</v>
@@ -45342,19 +45342,19 @@
         <v>1.85</v>
       </c>
       <c r="AC276">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD276">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE276">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF276">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG276">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH276" t="inlineStr">
         <is>
@@ -45367,10 +45367,10 @@
         </is>
       </c>
       <c r="AJ276">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK276">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL276">
         <v>0</v>
@@ -45632,55 +45632,55 @@
         <v>0</v>
       </c>
       <c r="Q278">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R278">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S278">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T278">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U278">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V278">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W278">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X278">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y278">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z278">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA278">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB278">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC278">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AD278">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE278">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF278">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG278">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH278" t="inlineStr">
         <is>
@@ -45693,10 +45693,10 @@
         </is>
       </c>
       <c r="AJ278">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK278">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL278">
         <v>0</v>
@@ -45795,55 +45795,55 @@
         <v>0</v>
       </c>
       <c r="Q279">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R279">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S279">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T279">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U279">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V279">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W279">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X279">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y279">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z279">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA279">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB279">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC279">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AD279">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE279">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF279">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG279">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH279" t="inlineStr">
         <is>
@@ -45856,10 +45856,10 @@
         </is>
       </c>
       <c r="AJ279">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK279">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL279">
         <v>0</v>
@@ -46121,25 +46121,25 @@
         <v>1.44</v>
       </c>
       <c r="Q281">
-        <v>5.56</v>
+        <v>6</v>
       </c>
       <c r="R281">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="S281">
         <v>1.19</v>
       </c>
       <c r="T281">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="U281">
         <v>2.12</v>
       </c>
       <c r="V281">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="W281">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X281">
         <v>1.02</v>
@@ -46154,7 +46154,7 @@
         <v>1.46</v>
       </c>
       <c r="AB281">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="AC281">
         <v>2.25</v>
@@ -46163,7 +46163,7 @@
         <v>1.59</v>
       </c>
       <c r="AE281">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF281">
         <v>1.63</v>
@@ -46182,10 +46182,10 @@
         </is>
       </c>
       <c r="AJ281">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AK281">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AL281">
         <v>0</v>
@@ -46275,13 +46275,13 @@
         </is>
       </c>
       <c r="N282">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="O282">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="P282">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="Q282">
         <v>3.8</v>
@@ -46293,37 +46293,37 @@
         <v>1.44</v>
       </c>
       <c r="T282">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="U282">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="V282">
         <v>1.3</v>
       </c>
       <c r="W282">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X282">
         <v>1.08</v>
       </c>
       <c r="Y282">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="Z282">
-        <v>2.77</v>
+        <v>2.47</v>
       </c>
       <c r="AA282">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AB282">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AC282">
-        <v>4.68</v>
+        <v>4.89</v>
       </c>
       <c r="AD282">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE282">
         <v>1.04</v>
@@ -46345,10 +46345,10 @@
         </is>
       </c>
       <c r="AJ282">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AK282">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AL282">
         <v>0</v>
@@ -46438,80 +46438,80 @@
         </is>
       </c>
       <c r="N283">
-        <v>2.12</v>
+        <v>1.91</v>
       </c>
       <c r="O283">
-        <v>3.57</v>
+        <v>3.55</v>
       </c>
       <c r="P283">
-        <v>3.59</v>
+        <v>3.38</v>
       </c>
       <c r="Q283">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="R283">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="S283">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T283">
-        <v>2.67</v>
+        <v>2.73</v>
       </c>
       <c r="U283">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="V283">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W283">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X283">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y283">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z283">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AA283">
+        <v>1.92</v>
+      </c>
+      <c r="AB283">
         <v>1.96</v>
       </c>
-      <c r="AB283">
-        <v>1.85</v>
-      </c>
       <c r="AC283">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="AD283">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AE283">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF283">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AG283">
+        <v>1.99</v>
+      </c>
+      <c r="AH283" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI283" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ283">
+        <v>1.21</v>
+      </c>
+      <c r="AK283">
         <v>1.93</v>
-      </c>
-      <c r="AH283" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI283" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ283">
-        <v>1.32</v>
-      </c>
-      <c r="AK283">
-        <v>1.79</v>
       </c>
       <c r="AL283">
         <v>0</v>
@@ -46601,13 +46601,13 @@
         </is>
       </c>
       <c r="N284">
-        <v>2.53</v>
+        <v>2.37</v>
       </c>
       <c r="O284">
-        <v>3.53</v>
+        <v>3.76</v>
       </c>
       <c r="P284">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="Q284">
         <v>2.9</v>
@@ -46616,16 +46616,16 @@
         <v>2.33</v>
       </c>
       <c r="S284">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T284">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="U284">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="V284">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W284">
         <v>1.17</v>
@@ -46634,25 +46634,25 @@
         <v>1</v>
       </c>
       <c r="Y284">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z284">
-        <v>5.07</v>
+        <v>4.95</v>
       </c>
       <c r="AA284">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AB284">
         <v>2.38</v>
       </c>
       <c r="AC284">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="AD284">
         <v>1.63</v>
       </c>
       <c r="AE284">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF284">
         <v>1.42</v>
@@ -46671,7 +46671,7 @@
         </is>
       </c>
       <c r="AJ284">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK284">
         <v>1.53</v>
@@ -46764,22 +46764,22 @@
         </is>
       </c>
       <c r="N285">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="O285">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="P285">
-        <v>4.63</v>
+        <v>4.25</v>
       </c>
       <c r="Q285">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="R285">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="S285">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T285">
         <v>3.5</v>
@@ -46791,7 +46791,7 @@
         <v>1.54</v>
       </c>
       <c r="W285">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X285">
         <v>1.01</v>
@@ -46803,10 +46803,10 @@
         <v>4.6</v>
       </c>
       <c r="AA285">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AB285">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="AC285">
         <v>2.5</v>
@@ -46818,7 +46818,7 @@
         <v>1.15</v>
       </c>
       <c r="AF285">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AG285">
         <v>2.15</v>
@@ -46834,7 +46834,7 @@
         </is>
       </c>
       <c r="AJ285">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AK285">
         <v>2.16</v>
@@ -46927,19 +46927,19 @@
         </is>
       </c>
       <c r="N286">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="O286">
-        <v>4.57</v>
+        <v>4.42</v>
       </c>
       <c r="P286">
-        <v>6.51</v>
+        <v>5.8</v>
       </c>
       <c r="Q286">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="R286">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="S286">
         <v>1.3</v>
@@ -46951,7 +46951,7 @@
         <v>2.5</v>
       </c>
       <c r="V286">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W286">
         <v>1.12</v>
@@ -46966,19 +46966,19 @@
         <v>4</v>
       </c>
       <c r="AA286">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="AB286">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AC286">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="AD286">
         <v>1.4</v>
       </c>
       <c r="AE286">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF286">
         <v>1.84</v>
@@ -47000,7 +47000,7 @@
         <v>1.17</v>
       </c>
       <c r="AK286">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AL286">
         <v>0</v>
@@ -47090,49 +47090,49 @@
         </is>
       </c>
       <c r="N287">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="O287">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P287">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="Q287">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="R287">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="S287">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T287">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="U287">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="V287">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="W287">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X287">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y287">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z287">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="AA287">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AB287">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="AC287">
         <v>2.23</v>
@@ -47144,10 +47144,10 @@
         <v>1.21</v>
       </c>
       <c r="AF287">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AG287">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AH287" t="inlineStr">
         <is>
@@ -47160,10 +47160,10 @@
         </is>
       </c>
       <c r="AJ287">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AK287">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AL287">
         <v>0</v>
@@ -47253,16 +47253,16 @@
         </is>
       </c>
       <c r="N288">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="O288">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P288">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="Q288">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="R288">
         <v>2.29</v>
@@ -47274,28 +47274,28 @@
         <v>3.6</v>
       </c>
       <c r="U288">
-        <v>2.17</v>
+        <v>1.92</v>
       </c>
       <c r="V288">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="W288">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X288">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y288">
         <v>1.13</v>
       </c>
       <c r="Z288">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA288">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB288">
-        <v>2.29</v>
+        <v>1.98</v>
       </c>
       <c r="AC288">
         <v>2.28</v>
@@ -47304,13 +47304,13 @@
         <v>1.5</v>
       </c>
       <c r="AE288">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AF288">
         <v>1.5</v>
       </c>
       <c r="AG288">
-        <v>2.32</v>
+        <v>2.05</v>
       </c>
       <c r="AH288" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         </is>
       </c>
       <c r="AJ288">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK288">
         <v>1.8</v>
@@ -47416,22 +47416,22 @@
         </is>
       </c>
       <c r="N289">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="O289">
-        <v>3.61</v>
+        <v>3.5</v>
       </c>
       <c r="P289">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="Q289">
         <v>2.26</v>
       </c>
       <c r="R289">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="S289">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T289">
         <v>3.08</v>
@@ -47449,31 +47449,31 @@
         <v>1.01</v>
       </c>
       <c r="Y289">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z289">
-        <v>3.88</v>
+        <v>3.7</v>
       </c>
       <c r="AA289">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB289">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AC289">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="AD289">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AE289">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF289">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AG289">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AH289" t="inlineStr">
         <is>
@@ -47486,10 +47486,10 @@
         </is>
       </c>
       <c r="AJ289">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK289">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="AL289">
         <v>0</v>
@@ -47579,13 +47579,13 @@
         </is>
       </c>
       <c r="N290">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="O290">
-        <v>3.54</v>
+        <v>3.95</v>
       </c>
       <c r="P290">
-        <v>5.11</v>
+        <v>4.87</v>
       </c>
       <c r="Q290">
         <v>0</v>
@@ -47742,13 +47742,13 @@
         </is>
       </c>
       <c r="N291">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="O291">
-        <v>3.48</v>
+        <v>3.33</v>
       </c>
       <c r="P291">
-        <v>3.28</v>
+        <v>2.75</v>
       </c>
       <c r="Q291">
         <v>2.48</v>
@@ -47760,7 +47760,7 @@
         <v>1.29</v>
       </c>
       <c r="T291">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U291">
         <v>2.32</v>
@@ -47781,7 +47781,7 @@
         <v>4.3</v>
       </c>
       <c r="AA291">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AB291">
         <v>2.15</v>
@@ -47799,7 +47799,7 @@
         <v>1.53</v>
       </c>
       <c r="AG291">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="AH291" t="inlineStr">
         <is>
@@ -47905,13 +47905,13 @@
         </is>
       </c>
       <c r="N292">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="O292">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="P292">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q292">
         <v>0</v>
@@ -48068,13 +48068,13 @@
         </is>
       </c>
       <c r="N293">
-        <v>4.05</v>
+        <v>4.14</v>
       </c>
       <c r="O293">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="P293">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="Q293">
         <v>0</v>
@@ -48231,16 +48231,16 @@
         </is>
       </c>
       <c r="N294">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="O294">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="P294">
-        <v>4.11</v>
+        <v>3.6</v>
       </c>
       <c r="Q294">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R294">
         <v>2.2</v>
@@ -48252,40 +48252,40 @@
         <v>3</v>
       </c>
       <c r="U294">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="V294">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W294">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X294">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y294">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z294">
         <v>3.6</v>
       </c>
       <c r="AA294">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AB294">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC294">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="AD294">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE294">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF294">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AG294">
         <v>2</v>
@@ -48301,7 +48301,7 @@
         </is>
       </c>
       <c r="AJ294">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AK294">
         <v>1.91</v>
@@ -48394,31 +48394,31 @@
         </is>
       </c>
       <c r="N295">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="O295">
-        <v>4.09</v>
+        <v>3.8</v>
       </c>
       <c r="P295">
-        <v>4.09</v>
+        <v>3.6</v>
       </c>
       <c r="Q295">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="R295">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="S295">
         <v>1.23</v>
       </c>
       <c r="T295">
-        <v>3.6</v>
+        <v>3.84</v>
       </c>
       <c r="U295">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="V295">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="W295">
         <v>1.15</v>
@@ -48430,16 +48430,16 @@
         <v>1.15</v>
       </c>
       <c r="Z295">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AA295">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="AB295">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="AC295">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="AD295">
         <v>1.66</v>
@@ -48451,7 +48451,7 @@
         <v>1.55</v>
       </c>
       <c r="AG295">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AH295" t="inlineStr">
         <is>
@@ -48729,34 +48729,34 @@
         <v>4.5</v>
       </c>
       <c r="Q297">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="R297">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S297">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T297">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U297">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V297">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W297">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X297">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y297">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z297">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA297">
         <v>1.85</v>
@@ -48765,19 +48765,19 @@
         <v>1.95</v>
       </c>
       <c r="AC297">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD297">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE297">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF297">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG297">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH297" t="inlineStr">
         <is>
@@ -48790,10 +48790,10 @@
         </is>
       </c>
       <c r="AJ297">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK297">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL297">
         <v>0</v>
@@ -48883,13 +48883,13 @@
         </is>
       </c>
       <c r="N298">
-        <v>2.44</v>
+        <v>2.19</v>
       </c>
       <c r="O298">
-        <v>3.36</v>
+        <v>3.24</v>
       </c>
       <c r="P298">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q298">
         <v>0</v>
@@ -49215,19 +49215,19 @@
         <v>3.68</v>
       </c>
       <c r="P300">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="Q300">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="R300">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="S300">
         <v>1.36</v>
       </c>
       <c r="T300">
-        <v>3.17</v>
+        <v>3.22</v>
       </c>
       <c r="U300">
         <v>2.62</v>
@@ -49236,31 +49236,31 @@
         <v>1.46</v>
       </c>
       <c r="W300">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X300">
         <v>1.01</v>
       </c>
       <c r="Y300">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z300">
-        <v>3.6</v>
+        <v>4.24</v>
       </c>
       <c r="AA300">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AB300">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AC300">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="AD300">
         <v>1.44</v>
       </c>
       <c r="AE300">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF300">
         <v>1.62</v>
@@ -49279,10 +49279,10 @@
         </is>
       </c>
       <c r="AJ300">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AK300">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL300">
         <v>0</v>
@@ -49381,55 +49381,55 @@
         <v>0</v>
       </c>
       <c r="Q301">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R301">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S301">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T301">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U301">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V301">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W301">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X301">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y301">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z301">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AA301">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AB301">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC301">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AD301">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE301">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF301">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG301">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AH301" t="inlineStr">
         <is>
@@ -49442,10 +49442,10 @@
         </is>
       </c>
       <c r="AJ301">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK301">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL301">
         <v>0</v>

--- a/jogos_2026-11-01.xlsx
+++ b/jogos_2026-11-01.xlsx
@@ -641,52 +641,52 @@
         <v>4.75</v>
       </c>
       <c r="P2">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Q2">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="R2">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="S2">
         <v>1.25</v>
       </c>
       <c r="T2">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U2">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="V2">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W2">
         <v>1.12</v>
       </c>
       <c r="X2">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y2">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z2">
         <v>4.65</v>
       </c>
       <c r="AA2">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AB2">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AC2">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AD2">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AE2">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AF2">
         <v>1.67</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AK2">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.8</v>
+        <v>3.01</v>
       </c>
       <c r="O3">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P3">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q3">
         <v>3.2</v>
@@ -813,7 +813,7 @@
         <v>2.4</v>
       </c>
       <c r="S3">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T3">
         <v>3.8</v>
@@ -837,16 +837,16 @@
         <v>4.68</v>
       </c>
       <c r="AA3">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AB3">
         <v>2.35</v>
       </c>
       <c r="AC3">
-        <v>2.28</v>
+        <v>2.43</v>
       </c>
       <c r="AD3">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AE3">
         <v>1.21</v>
@@ -871,7 +871,7 @@
         <v>1.23</v>
       </c>
       <c r="AK3">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q4">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="R4">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W4">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y4">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z4">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA4">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AB4">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AC4">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AD4">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE4">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK4">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1127,10 +1127,10 @@
         <v>2.5</v>
       </c>
       <c r="O5">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P5">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="Q5">
         <v>3.25</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AK5">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="O6">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P6">
         <v>2.3</v>
@@ -1308,10 +1308,10 @@
         <v>2.76</v>
       </c>
       <c r="U6">
-        <v>2.57</v>
+        <v>2.64</v>
       </c>
       <c r="V6">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="W6">
         <v>1.1</v>
@@ -1320,7 +1320,7 @@
         <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="Z6">
         <v>3.42</v>
@@ -1338,10 +1338,10 @@
         <v>1.3</v>
       </c>
       <c r="AE6">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF6">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AG6">
         <v>2.1</v>
@@ -1459,7 +1459,7 @@
         <v>7.5</v>
       </c>
       <c r="Q7">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="R7">
         <v>2.6</v>
@@ -1483,16 +1483,16 @@
         <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Z7">
-        <v>5.75</v>
+        <v>5.3</v>
       </c>
       <c r="AA7">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AB7">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="AC7">
         <v>2.12</v>
@@ -1523,7 +1523,7 @@
         <v>1.09</v>
       </c>
       <c r="AK7">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="O8">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="P8">
         <v>2.25</v>
@@ -1628,10 +1628,10 @@
         <v>1.99</v>
       </c>
       <c r="S8">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T8">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="U8">
         <v>3</v>
@@ -1655,7 +1655,7 @@
         <v>2.08</v>
       </c>
       <c r="AB8">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AC8">
         <v>3.9</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="O9">
-        <v>3.23</v>
+        <v>3</v>
       </c>
       <c r="P9">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="Q9">
         <v>2.9</v>
@@ -1800,13 +1800,13 @@
         <v>2.9</v>
       </c>
       <c r="V9">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W9">
         <v>1.07</v>
       </c>
       <c r="X9">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y9">
         <v>1.36</v>
@@ -1821,7 +1821,7 @@
         <v>1.66</v>
       </c>
       <c r="AC9">
-        <v>3.89</v>
+        <v>3.9</v>
       </c>
       <c r="AD9">
         <v>1.24</v>
@@ -1833,7 +1833,7 @@
         <v>1.83</v>
       </c>
       <c r="AG9">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK9">
         <v>1.57</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="O10">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P10">
-        <v>4.1</v>
+        <v>3.97</v>
       </c>
       <c r="Q10">
         <v>2.22</v>
@@ -1960,7 +1960,7 @@
         <v>3.17</v>
       </c>
       <c r="U10">
-        <v>2.6</v>
+        <v>2.71</v>
       </c>
       <c r="V10">
         <v>1.44</v>
@@ -1975,13 +1975,13 @@
         <v>1.21</v>
       </c>
       <c r="Z10">
-        <v>3.58</v>
+        <v>3.69</v>
       </c>
       <c r="AA10">
         <v>1.85</v>
       </c>
       <c r="AB10">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AC10">
         <v>3.04</v>
@@ -1993,7 +1993,7 @@
         <v>1.08</v>
       </c>
       <c r="AF10">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG10">
         <v>2</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="O11">
         <v>3.4</v>
       </c>
       <c r="P11">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="Q11">
         <v>2.24</v>
@@ -2117,19 +2117,19 @@
         <v>2.09</v>
       </c>
       <c r="S11">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T11">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="U11">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="V11">
         <v>1.4</v>
       </c>
       <c r="W11">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X11">
         <v>1.03</v>
@@ -2144,7 +2144,7 @@
         <v>1.85</v>
       </c>
       <c r="AB11">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AC11">
         <v>3.3</v>
@@ -2156,7 +2156,7 @@
         <v>1.07</v>
       </c>
       <c r="AF11">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AG11">
         <v>1.92</v>
@@ -2175,7 +2175,7 @@
         <v>1.22</v>
       </c>
       <c r="AK11">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="O12">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P12">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="Q12">
         <v>2.4</v>
@@ -2304,13 +2304,13 @@
         <v>3.5</v>
       </c>
       <c r="AA12">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AB12">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="AC12">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="AD12">
         <v>1.29</v>
@@ -2443,13 +2443,13 @@
         <v>2.2</v>
       </c>
       <c r="S13">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="T13">
         <v>3</v>
       </c>
       <c r="U13">
-        <v>2.58</v>
+        <v>2.51</v>
       </c>
       <c r="V13">
         <v>1.42</v>
@@ -2461,10 +2461,10 @@
         <v>1</v>
       </c>
       <c r="Y13">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z13">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="AA13">
         <v>1.88</v>
@@ -2482,7 +2482,7 @@
         <v>1.08</v>
       </c>
       <c r="AF13">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG13">
         <v>2.1</v>
@@ -2612,10 +2612,10 @@
         <v>2.9</v>
       </c>
       <c r="U14">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="V14">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W14">
         <v>1.06</v>
@@ -2636,13 +2636,13 @@
         <v>1.78</v>
       </c>
       <c r="AC14">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AD14">
         <v>1.29</v>
       </c>
       <c r="AE14">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AF14">
         <v>1.73</v>
@@ -2754,7 +2754,7 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="O15">
         <v>3.6</v>
@@ -2763,10 +2763,10 @@
         <v>2.3</v>
       </c>
       <c r="Q15">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="R15">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="S15">
         <v>1.29</v>
@@ -2784,25 +2784,25 @@
         <v>1.12</v>
       </c>
       <c r="X15">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y15">
         <v>1.18</v>
       </c>
       <c r="Z15">
-        <v>4.54</v>
+        <v>4</v>
       </c>
       <c r="AA15">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB15">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AC15">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AD15">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE15">
         <v>1.11</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.55</v>
+        <v>1.29</v>
       </c>
       <c r="AK15">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Adhyaksa</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O16">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P16">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q16">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R16">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S16">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T16">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="V16">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W16">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X16">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y16">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z16">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AA16">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB16">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AC16">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD16">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE16">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF16">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK16">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Adhyaksa</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3427,7 +3427,7 @@
         <v>3.46</v>
       </c>
       <c r="U19">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="V19">
         <v>1.53</v>
@@ -3448,7 +3448,7 @@
         <v>1.61</v>
       </c>
       <c r="AB19">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC19">
         <v>2.42</v>
@@ -3460,10 +3460,10 @@
         <v>1.14</v>
       </c>
       <c r="AF19">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AG19">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3572,10 +3572,10 @@
         <v>2.75</v>
       </c>
       <c r="O20">
-        <v>3.72</v>
+        <v>3.53</v>
       </c>
       <c r="P20">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="Q20">
         <v>3.74</v>
@@ -3735,10 +3735,10 @@
         <v>1.28</v>
       </c>
       <c r="O21">
-        <v>5.95</v>
+        <v>5.5</v>
       </c>
       <c r="P21">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="Q21">
         <v>1.68</v>
@@ -3753,10 +3753,10 @@
         <v>3.4</v>
       </c>
       <c r="U21">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V21">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="W21">
         <v>1.09</v>
@@ -3771,7 +3771,7 @@
         <v>4.66</v>
       </c>
       <c r="AA21">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB21">
         <v>2.34</v>
@@ -4097,10 +4097,10 @@
         <v>3.2</v>
       </c>
       <c r="AA23">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB23">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AC23">
         <v>3.14</v>
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="O24">
         <v>4</v>
@@ -4236,7 +4236,7 @@
         <v>2.32</v>
       </c>
       <c r="S24">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="T24">
         <v>3.4</v>
@@ -4248,10 +4248,10 @@
         <v>1.53</v>
       </c>
       <c r="W24">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y24">
         <v>1.18</v>
@@ -6180,7 +6180,7 @@
         <v>3.82</v>
       </c>
       <c r="O36">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P36">
         <v>1.75</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,80 +6340,80 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.74</v>
+        <v>1.18</v>
       </c>
       <c r="O37">
-        <v>3.75</v>
+        <v>6.5</v>
       </c>
       <c r="P37">
-        <v>3.95</v>
+        <v>10</v>
       </c>
       <c r="Q37">
-        <v>2.32</v>
+        <v>1.51</v>
       </c>
       <c r="R37">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="S37">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="T37">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="U37">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="V37">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="W37">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="X37">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="Z37">
+        <v>6</v>
+      </c>
+      <c r="AA37">
+        <v>1.3</v>
+      </c>
+      <c r="AB37">
+        <v>2.88</v>
+      </c>
+      <c r="AC37">
+        <v>2</v>
+      </c>
+      <c r="AD37">
+        <v>1.73</v>
+      </c>
+      <c r="AE37">
+        <v>1.31</v>
+      </c>
+      <c r="AF37">
+        <v>1.85</v>
+      </c>
+      <c r="AG37">
+        <v>1.87</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ37">
+        <v>1.03</v>
+      </c>
+      <c r="AK37">
         <v>4.5</v>
-      </c>
-      <c r="AA37">
-        <v>1.57</v>
-      </c>
-      <c r="AB37">
-        <v>2.25</v>
-      </c>
-      <c r="AC37">
-        <v>2.63</v>
-      </c>
-      <c r="AD37">
-        <v>1.44</v>
-      </c>
-      <c r="AE37">
-        <v>1.17</v>
-      </c>
-      <c r="AF37">
-        <v>1.57</v>
-      </c>
-      <c r="AG37">
-        <v>2.28</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ37">
-        <v>1.2</v>
-      </c>
-      <c r="AK37">
-        <v>1.91</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="O38">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P38">
-        <v>4.53</v>
+        <v>3.95</v>
       </c>
       <c r="Q38">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="R38">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S38">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T38">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U38">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="V38">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W38">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X38">
         <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z38">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AA38">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AB38">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC38">
-        <v>2.75</v>
+        <v>2.43</v>
       </c>
       <c r="AD38">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE38">
         <v>1.14</v>
       </c>
       <c r="AF38">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG38">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK38">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.17</v>
+        <v>1.65</v>
       </c>
       <c r="O39">
-        <v>7</v>
+        <v>3.8</v>
       </c>
       <c r="P39">
-        <v>11</v>
+        <v>4.53</v>
       </c>
       <c r="Q39">
-        <v>1.51</v>
+        <v>2.12</v>
       </c>
       <c r="R39">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="S39">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="T39">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="U39">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="V39">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="W39">
+        <v>1.11</v>
+      </c>
+      <c r="X39">
+        <v>1.02</v>
+      </c>
+      <c r="Y39">
         <v>1.2</v>
       </c>
-      <c r="X39">
-        <v>1.01</v>
-      </c>
-      <c r="Y39">
-        <v>1.1</v>
-      </c>
       <c r="Z39">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AA39">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AB39">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="AC39">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="AD39">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AE39">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="AF39">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AG39">
-        <v>1.87</v>
+        <v>2.13</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AK39">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6838,16 +6838,16 @@
         <v>5.01</v>
       </c>
       <c r="Q40">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R40">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S40">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T40">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U40">
         <v>2.25</v>
@@ -6856,37 +6856,37 @@
         <v>1.57</v>
       </c>
       <c r="W40">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X40">
         <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z40">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AA40">
+        <v>1.5</v>
+      </c>
+      <c r="AB40">
+        <v>2.5</v>
+      </c>
+      <c r="AC40">
+        <v>2.25</v>
+      </c>
+      <c r="AD40">
         <v>1.57</v>
       </c>
-      <c r="AB40">
-        <v>2.25</v>
-      </c>
-      <c r="AC40">
-        <v>2.5</v>
-      </c>
-      <c r="AD40">
-        <v>1.5</v>
-      </c>
       <c r="AE40">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AF40">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG40">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>1.17</v>
       </c>
       <c r="AK40">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,19 +6992,19 @@
         </is>
       </c>
       <c r="N41">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="O41">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="P41">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="Q41">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="R41">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="S41">
         <v>1.14</v>
@@ -7013,43 +7013,43 @@
         <v>5</v>
       </c>
       <c r="U41">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="V41">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="W41">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X41">
         <v>0</v>
       </c>
       <c r="Y41">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z41">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AA41">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AB41">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AC41">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AD41">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AE41">
         <v>1.37</v>
       </c>
       <c r="AF41">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AG41">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AK41">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Atlético Paso</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G42">
@@ -7164,71 +7164,71 @@
         <v>0</v>
       </c>
       <c r="Q42">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R42">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S42">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="T42">
-        <v>2.84</v>
+        <v>3.38</v>
       </c>
       <c r="U42">
-        <v>2.65</v>
+        <v>2.23</v>
       </c>
       <c r="V42">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="W42">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X42">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y42">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="Z42">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="AA42">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="AB42">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="AC42">
-        <v>3.14</v>
+        <v>2.43</v>
       </c>
       <c r="AD42">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AE42">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AF42">
+        <v>1.54</v>
+      </c>
+      <c r="AG42">
+        <v>2.29</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ42">
+        <v>1.19</v>
+      </c>
+      <c r="AK42">
         <v>1.81</v>
-      </c>
-      <c r="AG42">
-        <v>1.88</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ42">
-        <v>1.21</v>
-      </c>
-      <c r="AK42">
-        <v>1.89</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Atlético Paso</t>
         </is>
       </c>
       <c r="G43">
@@ -7327,55 +7327,55 @@
         <v>0</v>
       </c>
       <c r="Q43">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="R43">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S43">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="T43">
-        <v>3.38</v>
+        <v>2.84</v>
       </c>
       <c r="U43">
-        <v>2.23</v>
+        <v>2.65</v>
       </c>
       <c r="V43">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="W43">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="Z43">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="AA43">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="AB43">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AC43">
-        <v>2.43</v>
+        <v>3.14</v>
       </c>
       <c r="AD43">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="AE43">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AF43">
-        <v>1.54</v>
+        <v>1.81</v>
       </c>
       <c r="AG43">
-        <v>2.29</v>
+        <v>1.88</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AK43">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7973,7 +7973,7 @@
         <v>1.87</v>
       </c>
       <c r="O47">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="P47">
         <v>4.03</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>La Nucía</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Mallorca II</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.08</v>
+        <v>1.53</v>
       </c>
       <c r="O48">
-        <v>3.12</v>
+        <v>3.8</v>
       </c>
       <c r="P48">
-        <v>3.28</v>
+        <v>5.3</v>
       </c>
       <c r="Q48">
-        <v>2.78</v>
+        <v>2.1</v>
       </c>
       <c r="R48">
-        <v>1.97</v>
+        <v>2.22</v>
       </c>
       <c r="S48">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="T48">
-        <v>2.65</v>
+        <v>3.2</v>
       </c>
       <c r="U48">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="V48">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="W48">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X48">
         <v>1.03</v>
       </c>
       <c r="Y48">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="Z48">
-        <v>2.88</v>
+        <v>3.84</v>
       </c>
       <c r="AA48">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AB48">
-        <v>1.66</v>
+        <v>2.05</v>
       </c>
       <c r="AC48">
-        <v>3.84</v>
+        <v>2.74</v>
       </c>
       <c r="AD48">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="AE48">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF48">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG48">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AK48">
-        <v>1.59</v>
+        <v>2.2</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>La Nucía</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mallorca II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.53</v>
+        <v>2.08</v>
       </c>
       <c r="O50">
-        <v>3.8</v>
+        <v>3.12</v>
       </c>
       <c r="P50">
-        <v>5.3</v>
+        <v>3.28</v>
       </c>
       <c r="Q50">
-        <v>2.1</v>
+        <v>2.78</v>
       </c>
       <c r="R50">
-        <v>2.22</v>
+        <v>1.97</v>
       </c>
       <c r="S50">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="T50">
-        <v>3.2</v>
+        <v>2.65</v>
       </c>
       <c r="U50">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="V50">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="W50">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X50">
         <v>1.03</v>
       </c>
       <c r="Y50">
+        <v>1.32</v>
+      </c>
+      <c r="Z50">
+        <v>2.88</v>
+      </c>
+      <c r="AA50">
+        <v>2.15</v>
+      </c>
+      <c r="AB50">
+        <v>1.66</v>
+      </c>
+      <c r="AC50">
+        <v>3.84</v>
+      </c>
+      <c r="AD50">
         <v>1.18</v>
       </c>
-      <c r="Z50">
-        <v>3.84</v>
-      </c>
-      <c r="AA50">
-        <v>1.75</v>
-      </c>
-      <c r="AB50">
-        <v>2.05</v>
-      </c>
-      <c r="AC50">
-        <v>2.74</v>
-      </c>
-      <c r="AD50">
-        <v>1.35</v>
-      </c>
       <c r="AE50">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AF50">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG50">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AK50">
-        <v>2.2</v>
+        <v>1.59</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8824,7 +8824,7 @@
         <v>4.43</v>
       </c>
       <c r="AA52">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AB52">
         <v>2.27</v>
@@ -8957,10 +8957,10 @@
         <v>2.5</v>
       </c>
       <c r="Q53">
-        <v>3.62</v>
+        <v>3.1</v>
       </c>
       <c r="R53">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="S53">
         <v>1.35</v>
@@ -8969,40 +8969,40 @@
         <v>2.77</v>
       </c>
       <c r="U53">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="V53">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W53">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X53">
         <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z53">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AA53">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AB53">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AC53">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AD53">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AE53">
         <v>1.06</v>
       </c>
       <c r="AF53">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AG53">
         <v>1.99</v>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK53">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9126,10 +9126,10 @@
         <v>2.16</v>
       </c>
       <c r="S54">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="T54">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U54">
         <v>2.61</v>
@@ -9138,7 +9138,7 @@
         <v>1.39</v>
       </c>
       <c r="W54">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X54">
         <v>1.01</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Atlético Central</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
+        <v>2.05</v>
+      </c>
+      <c r="O55">
+        <v>3.3</v>
+      </c>
+      <c r="P55">
         <v>3.1</v>
       </c>
-      <c r="O55">
-        <v>3.2</v>
-      </c>
-      <c r="P55">
-        <v>2.09</v>
-      </c>
       <c r="Q55">
-        <v>3.98</v>
+        <v>2.63</v>
       </c>
       <c r="R55">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="S55">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T55">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="U55">
-        <v>2.77</v>
+        <v>2.38</v>
       </c>
       <c r="V55">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="W55">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X55">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y55">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="Z55">
-        <v>3.04</v>
+        <v>3.7</v>
       </c>
       <c r="AA55">
+        <v>1.75</v>
+      </c>
+      <c r="AB55">
         <v>2.05</v>
       </c>
-      <c r="AB55">
-        <v>1.75</v>
-      </c>
       <c r="AC55">
-        <v>3.48</v>
+        <v>2.7</v>
       </c>
       <c r="AD55">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AE55">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF55">
-        <v>1.79</v>
+        <v>1.59</v>
       </c>
       <c r="AG55">
-        <v>1.9</v>
+        <v>2.19</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK55">
-        <v>1.26</v>
+        <v>1.57</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Atlético Central</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
+        <v>3.1</v>
+      </c>
+      <c r="O56">
+        <v>3.2</v>
+      </c>
+      <c r="P56">
+        <v>2.09</v>
+      </c>
+      <c r="Q56">
+        <v>3.98</v>
+      </c>
+      <c r="R56">
+        <v>2.04</v>
+      </c>
+      <c r="S56">
+        <v>1.35</v>
+      </c>
+      <c r="T56">
+        <v>2.77</v>
+      </c>
+      <c r="U56">
+        <v>2.77</v>
+      </c>
+      <c r="V56">
+        <v>1.35</v>
+      </c>
+      <c r="W56">
+        <v>1.06</v>
+      </c>
+      <c r="X56">
+        <v>1.02</v>
+      </c>
+      <c r="Y56">
+        <v>1.29</v>
+      </c>
+      <c r="Z56">
+        <v>3.04</v>
+      </c>
+      <c r="AA56">
         <v>2.05</v>
       </c>
-      <c r="O56">
-        <v>3.3</v>
-      </c>
-      <c r="P56">
-        <v>3.1</v>
-      </c>
-      <c r="Q56">
-        <v>2.63</v>
-      </c>
-      <c r="R56">
-        <v>2.2</v>
-      </c>
-      <c r="S56">
-        <v>1.3</v>
-      </c>
-      <c r="T56">
-        <v>3</v>
-      </c>
-      <c r="U56">
-        <v>2.38</v>
-      </c>
-      <c r="V56">
-        <v>1.47</v>
-      </c>
-      <c r="W56">
-        <v>1.09</v>
-      </c>
-      <c r="X56">
-        <v>1.01</v>
-      </c>
-      <c r="Y56">
-        <v>1.2</v>
-      </c>
-      <c r="Z56">
-        <v>3.7</v>
-      </c>
-      <c r="AA56">
+      <c r="AB56">
         <v>1.75</v>
       </c>
-      <c r="AB56">
-        <v>2.05</v>
-      </c>
       <c r="AC56">
-        <v>2.7</v>
+        <v>3.48</v>
       </c>
       <c r="AD56">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AE56">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF56">
-        <v>1.59</v>
+        <v>1.79</v>
       </c>
       <c r="AG56">
-        <v>2.19</v>
+        <v>1.9</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK56">
-        <v>1.57</v>
+        <v>1.26</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9802,7 +9802,7 @@
         <v>3.08</v>
       </c>
       <c r="AA58">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AB58">
         <v>1.74</v>
@@ -9929,10 +9929,10 @@
         <v>1.29</v>
       </c>
       <c r="O59">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="P59">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="Q59">
         <v>1.62</v>
@@ -9974,10 +9974,10 @@
         <v>1.92</v>
       </c>
       <c r="AD59">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AE59">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AF59">
         <v>1.62</v>
@@ -9999,7 +9999,7 @@
         <v>1.1</v>
       </c>
       <c r="AK59">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10110,7 +10110,7 @@
         <v>4.8</v>
       </c>
       <c r="U60">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="V60">
         <v>1.86</v>
@@ -10128,10 +10128,10 @@
         <v>7.3</v>
       </c>
       <c r="AA60">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AB60">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="AC60">
         <v>1.74</v>
@@ -10143,7 +10143,7 @@
         <v>1.38</v>
       </c>
       <c r="AF60">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AG60">
         <v>2.25</v>
@@ -10159,7 +10159,7 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.06</v>
+        <v>3.9</v>
       </c>
       <c r="AK60">
         <v>1.03</v>
@@ -10261,55 +10261,55 @@
         <v>0</v>
       </c>
       <c r="Q61">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="R61">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="S61">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="T61">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
       <c r="U61">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="V61">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="W61">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="X61">
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z61">
-        <v>6.4</v>
+        <v>6.25</v>
       </c>
       <c r="AA61">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB61">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="AC61">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AD61">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AE61">
         <v>1.31</v>
       </c>
       <c r="AF61">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AG61">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AK61">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10907,7 +10907,7 @@
         <v>2.15</v>
       </c>
       <c r="O65">
-        <v>3.4</v>
+        <v>3.46</v>
       </c>
       <c r="P65">
         <v>2.75</v>
@@ -10919,7 +10919,7 @@
         <v>2.21</v>
       </c>
       <c r="S65">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T65">
         <v>3.26</v>
@@ -11097,7 +11097,7 @@
         <v>1.11</v>
       </c>
       <c r="X66">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y66">
         <v>1.22</v>
@@ -11595,10 +11595,10 @@
         <v>0</v>
       </c>
       <c r="AA69">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AB69">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC69">
         <v>0</v>
@@ -11728,10 +11728,10 @@
         <v>26</v>
       </c>
       <c r="Q70">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="R70">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="S70">
         <v>1.14</v>
@@ -11740,7 +11740,7 @@
         <v>5.5</v>
       </c>
       <c r="U70">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="V70">
         <v>2.1</v>
@@ -11749,7 +11749,7 @@
         <v>1.33</v>
       </c>
       <c r="X70">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y70">
         <v>1.02</v>
@@ -11758,19 +11758,19 @@
         <v>9.300000000000001</v>
       </c>
       <c r="AA70">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AB70">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AC70">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AD70">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="AE70">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AF70">
         <v>1.7</v>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK70">
-        <v>5.45</v>
+        <v>5.5</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -12736,7 +12736,7 @@
         <v>3.42</v>
       </c>
       <c r="AA76">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AB76">
         <v>2</v>
@@ -13195,16 +13195,16 @@
         <v>2.72</v>
       </c>
       <c r="Q79">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="R79">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="S79">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="T79">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="U79">
         <v>2.27</v>
@@ -13213,19 +13213,19 @@
         <v>1.51</v>
       </c>
       <c r="W79">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X79">
         <v>1.02</v>
       </c>
       <c r="Y79">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z79">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="AA79">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AB79">
         <v>2.13</v>
@@ -13349,31 +13349,31 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="O80">
         <v>3.25</v>
       </c>
       <c r="P80">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q80">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="R80">
         <v>2.08</v>
       </c>
       <c r="S80">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T80">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="U80">
-        <v>2.58</v>
+        <v>2.88</v>
       </c>
       <c r="V80">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W80">
         <v>1.07</v>
@@ -13382,31 +13382,31 @@
         <v>1.01</v>
       </c>
       <c r="Y80">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z80">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AA80">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AB80">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AC80">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AD80">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AE80">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF80">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AG80">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK80">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13524,7 +13524,7 @@
         <v>4.05</v>
       </c>
       <c r="R81">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="S81">
         <v>1.51</v>
@@ -13838,7 +13838,7 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O83">
         <v>3.4</v>
@@ -14001,10 +14001,10 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="O84">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P84">
         <v>3</v>
@@ -14016,10 +14016,10 @@
         <v>2.3</v>
       </c>
       <c r="S84">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T84">
-        <v>3.22</v>
+        <v>3.6</v>
       </c>
       <c r="U84">
         <v>2.25</v>
@@ -14058,7 +14058,7 @@
         <v>1.53</v>
       </c>
       <c r="AG84">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14164,10 +14164,10 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="O85">
-        <v>3.7</v>
+        <v>3.71</v>
       </c>
       <c r="P85">
         <v>2.55</v>
@@ -14206,7 +14206,7 @@
         <v>1.57</v>
       </c>
       <c r="AB85">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AC85">
         <v>2.33</v>
@@ -14234,7 +14234,7 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AK85">
         <v>1.48</v>
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="O86">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="P86">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="Q86">
         <v>2.55</v>
@@ -14692,7 +14692,7 @@
         <v>4.5</v>
       </c>
       <c r="AA88">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AB88">
         <v>2.35</v>
@@ -14710,7 +14710,7 @@
         <v>1.5</v>
       </c>
       <c r="AG88">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14979,19 +14979,19 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="O90">
-        <v>3.8</v>
+        <v>3.92</v>
       </c>
       <c r="P90">
-        <v>3.9</v>
+        <v>4.02</v>
       </c>
       <c r="Q90">
         <v>2.34</v>
       </c>
       <c r="R90">
-        <v>2.18</v>
+        <v>2.44</v>
       </c>
       <c r="S90">
         <v>1.3</v>
@@ -15003,7 +15003,7 @@
         <v>2.4</v>
       </c>
       <c r="V90">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W90">
         <v>1.12</v>
@@ -15033,10 +15033,10 @@
         <v>1.13</v>
       </c>
       <c r="AF90">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG90">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15148,7 +15148,7 @@
         <v>5.25</v>
       </c>
       <c r="P91">
-        <v>7.75</v>
+        <v>7.2</v>
       </c>
       <c r="Q91">
         <v>1.73</v>
@@ -15215,7 +15215,7 @@
         <v>1.07</v>
       </c>
       <c r="AK91">
-        <v>2.84</v>
+        <v>3.22</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15471,16 +15471,16 @@
         <v>1.27</v>
       </c>
       <c r="O93">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="P93">
-        <v>7.75</v>
+        <v>7</v>
       </c>
       <c r="Q93">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="R93">
-        <v>3.44</v>
+        <v>3.06</v>
       </c>
       <c r="S93">
         <v>1.08</v>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AK93">
-        <v>3.75</v>
+        <v>3.44</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="O97">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P97">
-        <v>2.95</v>
+        <v>2.71</v>
       </c>
       <c r="Q97">
         <v>2.9</v>
@@ -16159,7 +16159,7 @@
         <v>3.6</v>
       </c>
       <c r="AA97">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AB97">
         <v>1.84</v>
@@ -16190,7 +16190,7 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AK97">
         <v>1.62</v>
@@ -16283,16 +16283,16 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.8</v>
+        <v>3.16</v>
       </c>
       <c r="O98">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="P98">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="Q98">
-        <v>3.62</v>
+        <v>4.1</v>
       </c>
       <c r="R98">
         <v>1.84</v>
@@ -16322,7 +16322,7 @@
         <v>2.29</v>
       </c>
       <c r="AA98">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AB98">
         <v>1.43</v>
@@ -16615,7 +16615,7 @@
         <v>5.4</v>
       </c>
       <c r="P100">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q100">
         <v>1.72</v>
@@ -16624,7 +16624,7 @@
         <v>2.61</v>
       </c>
       <c r="S100">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T100">
         <v>3.6</v>
@@ -16633,10 +16633,10 @@
         <v>2.23</v>
       </c>
       <c r="V100">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="W100">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X100">
         <v>1.01</v>
@@ -16660,7 +16660,7 @@
         <v>1.58</v>
       </c>
       <c r="AE100">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF100">
         <v>1.85</v>
@@ -16935,19 +16935,19 @@
         </is>
       </c>
       <c r="N102">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="O102">
         <v>5.25</v>
       </c>
       <c r="P102">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="Q102">
         <v>5.55</v>
       </c>
       <c r="R102">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="S102">
         <v>1.17</v>
@@ -16968,13 +16968,13 @@
         <v>1.01</v>
       </c>
       <c r="Y102">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z102">
         <v>6</v>
       </c>
       <c r="AA102">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AB102">
         <v>2.75</v>
@@ -17098,19 +17098,19 @@
         </is>
       </c>
       <c r="N103">
-        <v>3.83</v>
+        <v>2.97</v>
       </c>
       <c r="O103">
-        <v>3.87</v>
+        <v>3.55</v>
       </c>
       <c r="P103">
-        <v>1.78</v>
+        <v>1.99</v>
       </c>
       <c r="Q103">
         <v>3.74</v>
       </c>
       <c r="R103">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="S103">
         <v>1.18</v>
@@ -17137,10 +17137,10 @@
         <v>5.2</v>
       </c>
       <c r="AA103">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AB103">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AC103">
         <v>2.18</v>
@@ -17155,7 +17155,7 @@
         <v>1.43</v>
       </c>
       <c r="AG103">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17424,7 +17424,7 @@
         </is>
       </c>
       <c r="N105">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="O105">
         <v>3.3</v>
@@ -17587,7 +17587,7 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="O106">
         <v>3.26</v>
@@ -17608,7 +17608,7 @@
         <v>2.8</v>
       </c>
       <c r="U106">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="V106">
         <v>1.36</v>
@@ -17750,37 +17750,37 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="O107">
-        <v>3.92</v>
+        <v>3.75</v>
       </c>
       <c r="P107">
-        <v>3.69</v>
+        <v>3.4</v>
       </c>
       <c r="Q107">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="R107">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="S107">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T107">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U107">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="V107">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="W107">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X107">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y107">
         <v>1.1</v>
@@ -17789,19 +17789,19 @@
         <v>5</v>
       </c>
       <c r="AA107">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AB107">
         <v>2.46</v>
       </c>
       <c r="AC107">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="AD107">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AE107">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AF107">
         <v>1.5</v>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK107">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17913,28 +17913,28 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="O108">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="P108">
-        <v>6.12</v>
+        <v>5.62</v>
       </c>
       <c r="Q108">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="R108">
-        <v>2.45</v>
+        <v>2.27</v>
       </c>
       <c r="S108">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T108">
         <v>3.4</v>
       </c>
       <c r="U108">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="V108">
         <v>1.57</v>
@@ -17955,7 +17955,7 @@
         <v>1.57</v>
       </c>
       <c r="AB108">
-        <v>2.35</v>
+        <v>2.42</v>
       </c>
       <c r="AC108">
         <v>2.38</v>
@@ -17964,7 +17964,7 @@
         <v>1.54</v>
       </c>
       <c r="AE108">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AF108">
         <v>1.7</v>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AK108">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18248,25 +18248,25 @@
         <v>0</v>
       </c>
       <c r="Q110">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="R110">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="S110">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="T110">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="U110">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="V110">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W110">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X110">
         <v>1.02</v>
@@ -18275,28 +18275,28 @@
         <v>1.14</v>
       </c>
       <c r="Z110">
-        <v>4.45</v>
+        <v>4.33</v>
       </c>
       <c r="AA110">
         <v>1.61</v>
       </c>
       <c r="AB110">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AC110">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AD110">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE110">
         <v>1.14</v>
       </c>
       <c r="AF110">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AG110">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK110">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18408,7 +18408,7 @@
         <v>3.8</v>
       </c>
       <c r="P111">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="Q111">
         <v>2.02</v>
@@ -18444,7 +18444,7 @@
         <v>1.9</v>
       </c>
       <c r="AB111">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AC111">
         <v>3.04</v>
@@ -18565,7 +18565,7 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="O112">
         <v>3.2</v>
@@ -19220,13 +19220,13 @@
         <v>2.8</v>
       </c>
       <c r="O116">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="P116">
         <v>2.19</v>
       </c>
       <c r="Q116">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="R116">
         <v>2.49</v>
@@ -19287,7 +19287,7 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK116">
         <v>1.36</v>
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="O117">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="P117">
-        <v>5.11</v>
+        <v>4.33</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -19398,13 +19398,13 @@
         <v>1.28</v>
       </c>
       <c r="T117">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="U117">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="V117">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W117">
         <v>1.1</v>
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="O118">
         <v>6.5</v>
       </c>
       <c r="P118">
-        <v>9.5</v>
+        <v>12</v>
       </c>
       <c r="Q118">
         <v>1.51</v>
@@ -19706,13 +19706,13 @@
         </is>
       </c>
       <c r="N119">
-        <v>4.33</v>
+        <v>4.29</v>
       </c>
       <c r="O119">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="P119">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="Q119">
         <v>3.85</v>
@@ -19745,10 +19745,10 @@
         <v>5.46</v>
       </c>
       <c r="AA119">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB119">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AC119">
         <v>2.21</v>
@@ -19872,7 +19872,7 @@
         <v>4.8</v>
       </c>
       <c r="O120">
-        <v>4.52</v>
+        <v>4.4</v>
       </c>
       <c r="P120">
         <v>1.6</v>
@@ -20032,13 +20032,13 @@
         </is>
       </c>
       <c r="N121">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="O121">
         <v>3.8</v>
       </c>
       <c r="P121">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Q121">
         <v>3</v>
@@ -20195,37 +20195,37 @@
         </is>
       </c>
       <c r="N122">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="O122">
-        <v>4.31</v>
+        <v>4.15</v>
       </c>
       <c r="P122">
-        <v>3.56</v>
+        <v>3.15</v>
       </c>
       <c r="Q122">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R122">
         <v>2.7</v>
       </c>
       <c r="S122">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="T122">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="U122">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="V122">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="W122">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="X122">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y122">
         <v>1.02</v>
@@ -20234,7 +20234,7 @@
         <v>7.8</v>
       </c>
       <c r="AA122">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AB122">
         <v>3.68</v>
@@ -20243,13 +20243,13 @@
         <v>1.61</v>
       </c>
       <c r="AD122">
-        <v>2.21</v>
+        <v>2.14</v>
       </c>
       <c r="AE122">
         <v>1.51</v>
       </c>
       <c r="AF122">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AG122">
         <v>3.4</v>
@@ -20268,7 +20268,7 @@
         <v>1.22</v>
       </c>
       <c r="AK122">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20358,34 +20358,34 @@
         </is>
       </c>
       <c r="N123">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="O123">
-        <v>4.15</v>
+        <v>3.7</v>
       </c>
       <c r="P123">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q123">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="R123">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="S123">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T123">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="U123">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="V123">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="W123">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X123">
         <v>1.01</v>
@@ -20406,10 +20406,10 @@
         <v>1.89</v>
       </c>
       <c r="AD123">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AE123">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AF123">
         <v>1.36</v>
@@ -20690,7 +20690,7 @@
         <v>3.1</v>
       </c>
       <c r="P125">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q125">
         <v>3.75</v>
@@ -20847,10 +20847,10 @@
         </is>
       </c>
       <c r="N126">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="O126">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P126">
         <v>2.33</v>
@@ -20862,10 +20862,10 @@
         <v>2.1</v>
       </c>
       <c r="S126">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T126">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="U126">
         <v>2.88</v>
@@ -20901,10 +20901,10 @@
         <v>1.05</v>
       </c>
       <c r="AF126">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG126">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -21019,28 +21019,28 @@
         <v>2.62</v>
       </c>
       <c r="Q127">
+        <v>3.26</v>
+      </c>
+      <c r="R127">
+        <v>2.23</v>
+      </c>
+      <c r="S127">
+        <v>1.36</v>
+      </c>
+      <c r="T127">
         <v>3</v>
       </c>
-      <c r="R127">
-        <v>2.1</v>
-      </c>
-      <c r="S127">
-        <v>1.33</v>
-      </c>
-      <c r="T127">
-        <v>2.97</v>
-      </c>
       <c r="U127">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="V127">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W127">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X127">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y127">
         <v>1.22</v>
@@ -21049,25 +21049,25 @@
         <v>3.5</v>
       </c>
       <c r="AA127">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AB127">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AC127">
         <v>3.35</v>
       </c>
       <c r="AD127">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AE127">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF127">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG127">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK127">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21173,34 +21173,34 @@
         </is>
       </c>
       <c r="N128">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="O128">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P128">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q128">
         <v>3.6</v>
       </c>
       <c r="R128">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="S128">
         <v>1.36</v>
       </c>
       <c r="T128">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="U128">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V128">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W128">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X128">
         <v>1.01</v>
@@ -21227,10 +21227,10 @@
         <v>1.11</v>
       </c>
       <c r="AF128">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AG128">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21336,13 +21336,13 @@
         </is>
       </c>
       <c r="N129">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="O129">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="P129">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="Q129">
         <v>1.91</v>
@@ -22169,7 +22169,7 @@
         <v>1.42</v>
       </c>
       <c r="T134">
-        <v>2.65</v>
+        <v>2.83</v>
       </c>
       <c r="U134">
         <v>2.85</v>
@@ -22196,7 +22196,7 @@
         <v>1.75</v>
       </c>
       <c r="AC134">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="AD134">
         <v>1.27</v>
@@ -22492,7 +22492,7 @@
         <v>2.25</v>
       </c>
       <c r="S136">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T136">
         <v>3.4</v>
@@ -22824,10 +22824,10 @@
         <v>3</v>
       </c>
       <c r="U138">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="V138">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W138">
         <v>1.1</v>
@@ -22842,10 +22842,10 @@
         <v>3.58</v>
       </c>
       <c r="AA138">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AB138">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AC138">
         <v>3.1</v>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK138">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -23138,10 +23138,10 @@
         <v>0</v>
       </c>
       <c r="Q140">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="R140">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="S140">
         <v>1.25</v>
@@ -23150,43 +23150,43 @@
         <v>3.7</v>
       </c>
       <c r="U140">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="V140">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W140">
         <v>1.15</v>
       </c>
       <c r="X140">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y140">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z140">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="AA140">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="AB140">
-        <v>2.41</v>
+        <v>2.33</v>
       </c>
       <c r="AC140">
-        <v>2.22</v>
+        <v>2.29</v>
       </c>
       <c r="AD140">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AE140">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AF140">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AG140">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK140">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -23301,55 +23301,55 @@
         <v>0</v>
       </c>
       <c r="Q141">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="R141">
-        <v>2.85</v>
+        <v>2.93</v>
       </c>
       <c r="S141">
         <v>1.17</v>
       </c>
       <c r="T141">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="U141">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="V141">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="W141">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X141">
         <v>1.01</v>
       </c>
       <c r="Y141">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z141">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
       <c r="AA141">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AB141">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="AC141">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AD141">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AE141">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AF141">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AG141">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
@@ -23362,10 +23362,10 @@
         </is>
       </c>
       <c r="AJ141">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AK141">
-        <v>3.36</v>
+        <v>3.82</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23464,28 +23464,28 @@
         <v>1.58</v>
       </c>
       <c r="Q142">
-        <v>4.05</v>
+        <v>4.09</v>
       </c>
       <c r="R142">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S142">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="T142">
-        <v>2.81</v>
+        <v>2.95</v>
       </c>
       <c r="U142">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="V142">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="W142">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X142">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y142">
         <v>1.25</v>
@@ -23494,19 +23494,19 @@
         <v>3.42</v>
       </c>
       <c r="AA142">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB142">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AC142">
         <v>2.92</v>
       </c>
       <c r="AD142">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE142">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF142">
         <v>1.67</v>
@@ -23525,10 +23525,10 @@
         </is>
       </c>
       <c r="AJ142">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK142">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -23627,7 +23627,7 @@
         <v>4.69</v>
       </c>
       <c r="Q143">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="R143">
         <v>2.36</v>
@@ -23660,7 +23660,7 @@
         <v>1.53</v>
       </c>
       <c r="AB143">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AC143">
         <v>2.42</v>
@@ -23796,19 +23796,19 @@
         <v>2.17</v>
       </c>
       <c r="S144">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="T144">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="U144">
-        <v>2.27</v>
+        <v>2.45</v>
       </c>
       <c r="V144">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W144">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X144">
         <v>1.04</v>
@@ -23835,10 +23835,10 @@
         <v>1.13</v>
       </c>
       <c r="AF144">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AG144">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -24110,22 +24110,22 @@
         <v>1.44</v>
       </c>
       <c r="O146">
-        <v>4.4</v>
+        <v>4.46</v>
       </c>
       <c r="P146">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
       <c r="Q146">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="R146">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S146">
         <v>1.33</v>
       </c>
       <c r="T146">
-        <v>3.11</v>
+        <v>3.14</v>
       </c>
       <c r="U146">
         <v>2.6</v>
@@ -24140,7 +24140,7 @@
         <v>1.01</v>
       </c>
       <c r="Y146">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z146">
         <v>3.7</v>
@@ -24149,22 +24149,22 @@
         <v>1.84</v>
       </c>
       <c r="AB146">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AC146">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="AD146">
         <v>1.35</v>
       </c>
       <c r="AE146">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF146">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AG146">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24180,7 +24180,7 @@
         <v>1.06</v>
       </c>
       <c r="AK146">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24273,7 +24273,7 @@
         <v>2.25</v>
       </c>
       <c r="O147">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P147">
         <v>3</v>
@@ -24433,7 +24433,7 @@
         </is>
       </c>
       <c r="N148">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="O148">
         <v>3.64</v>
@@ -24928,7 +24928,7 @@
         <v>3.7</v>
       </c>
       <c r="P151">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q151">
         <v>2.97</v>
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Gd Nazarenos</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Sertanense</t>
         </is>
       </c>
       <c r="G152">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G153">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>AD Nogueirense</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G154">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>AD Nogueirense</t>
         </is>
       </c>
       <c r="G155">
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G156">
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Gd Nazarenos</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Sertanense</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G157">
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Imortal Albufeira</t>
         </is>
       </c>
       <c r="G159">
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Portel</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="G160">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Imortal Albufeira</t>
+          <t>Portel</t>
         </is>
       </c>
       <c r="G161">
@@ -27077,7 +27077,7 @@
         <v>1.19</v>
       </c>
       <c r="Z164">
-        <v>4.64</v>
+        <v>4.4</v>
       </c>
       <c r="AA164">
         <v>1.61</v>
@@ -27243,10 +27243,10 @@
         <v>3.34</v>
       </c>
       <c r="AA165">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AB165">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AC165">
         <v>3.3</v>
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Estrela Calheta</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="G168">
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Estrela Calheta</t>
+          <t>Ovarense</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G169">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Ovarense</t>
+          <t>Castro Daire</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G170">
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Castro Daire</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G171">
@@ -28387,7 +28387,7 @@
         <v>1.25</v>
       </c>
       <c r="AB172">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="AC172">
         <v>1.73</v>
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G173">
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G174">
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G175">
@@ -29000,7 +29000,7 @@
         <v>3.4</v>
       </c>
       <c r="O176">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P176">
         <v>1.95</v>
@@ -29070,7 +29070,7 @@
         <v>1.21</v>
       </c>
       <c r="AK176">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29489,16 +29489,16 @@
         <v>2.16</v>
       </c>
       <c r="O179">
-        <v>3.82</v>
+        <v>3.6</v>
       </c>
       <c r="P179">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="Q179">
-        <v>2.33</v>
+        <v>2.62</v>
       </c>
       <c r="R179">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S179">
         <v>1.2</v>
@@ -29522,13 +29522,13 @@
         <v>1.11</v>
       </c>
       <c r="Z179">
-        <v>5.45</v>
+        <v>5.75</v>
       </c>
       <c r="AA179">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AB179">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="AC179">
         <v>2.08</v>
@@ -29540,10 +29540,10 @@
         <v>1.25</v>
       </c>
       <c r="AF179">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AG179">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AH179" t="inlineStr">
         <is>
@@ -29556,10 +29556,10 @@
         </is>
       </c>
       <c r="AJ179">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AK179">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Montalegre</t>
+          <t>Maia Lidador</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Maria da Fonte</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="G185">
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Maia Lidador</t>
+          <t>Ponte da Barca</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Vinhais</t>
         </is>
       </c>
       <c r="G186">
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Ponte da Barca</t>
+          <t>Montalegre</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Vinhais</t>
+          <t>Maria da Fonte</t>
         </is>
       </c>
       <c r="G187">
@@ -31158,7 +31158,7 @@
         <v>1.75</v>
       </c>
       <c r="AB189">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AC189">
         <v>2.74</v>
@@ -31349,10 +31349,10 @@
         </is>
       </c>
       <c r="AJ190">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK190">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AL190">
         <v>0</v>
@@ -31484,7 +31484,7 @@
         <v>1.74</v>
       </c>
       <c r="AB191">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AC191">
         <v>3.11</v>
@@ -31605,7 +31605,7 @@
         </is>
       </c>
       <c r="N192">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O192">
         <v>7.1</v>
@@ -31617,7 +31617,7 @@
         <v>6.38</v>
       </c>
       <c r="R192">
-        <v>3.14</v>
+        <v>3.52</v>
       </c>
       <c r="S192">
         <v>1.12</v>
@@ -31632,7 +31632,7 @@
         <v>2.06</v>
       </c>
       <c r="W192">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="X192">
         <v>1</v>
@@ -31644,7 +31644,7 @@
         <v>9</v>
       </c>
       <c r="AA192">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AB192">
         <v>4.5</v>
@@ -31659,10 +31659,10 @@
         <v>1.62</v>
       </c>
       <c r="AF192">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG192">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
@@ -31678,7 +31678,7 @@
         <v>1.06</v>
       </c>
       <c r="AK192">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AL192">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,65 +32257,65 @@
         </is>
       </c>
       <c r="N196">
+        <v>1.58</v>
+      </c>
+      <c r="O196">
+        <v>4.2</v>
+      </c>
+      <c r="P196">
+        <v>4.6</v>
+      </c>
+      <c r="Q196">
+        <v>2.02</v>
+      </c>
+      <c r="R196">
+        <v>2.57</v>
+      </c>
+      <c r="S196">
+        <v>1.22</v>
+      </c>
+      <c r="T196">
+        <v>4</v>
+      </c>
+      <c r="U196">
+        <v>2.05</v>
+      </c>
+      <c r="V196">
+        <v>1.69</v>
+      </c>
+      <c r="W196">
+        <v>1.2</v>
+      </c>
+      <c r="X196">
+        <v>1.01</v>
+      </c>
+      <c r="Y196">
+        <v>1.11</v>
+      </c>
+      <c r="Z196">
+        <v>5.5</v>
+      </c>
+      <c r="AA196">
+        <v>1.4</v>
+      </c>
+      <c r="AB196">
+        <v>2.7</v>
+      </c>
+      <c r="AC196">
+        <v>2.15</v>
+      </c>
+      <c r="AD196">
+        <v>1.66</v>
+      </c>
+      <c r="AE196">
+        <v>1.25</v>
+      </c>
+      <c r="AF196">
+        <v>1.53</v>
+      </c>
+      <c r="AG196">
         <v>2.45</v>
       </c>
-      <c r="O196">
-        <v>3.8</v>
-      </c>
-      <c r="P196">
-        <v>2.45</v>
-      </c>
-      <c r="Q196">
-        <v>2.88</v>
-      </c>
-      <c r="R196">
-        <v>2.4</v>
-      </c>
-      <c r="S196">
-        <v>1.25</v>
-      </c>
-      <c r="T196">
-        <v>3.75</v>
-      </c>
-      <c r="U196">
-        <v>2.12</v>
-      </c>
-      <c r="V196">
-        <v>1.62</v>
-      </c>
-      <c r="W196">
-        <v>1.17</v>
-      </c>
-      <c r="X196">
-        <v>1.02</v>
-      </c>
-      <c r="Y196">
-        <v>1.13</v>
-      </c>
-      <c r="Z196">
-        <v>5</v>
-      </c>
-      <c r="AA196">
-        <v>1.51</v>
-      </c>
-      <c r="AB196">
-        <v>2.35</v>
-      </c>
-      <c r="AC196">
-        <v>2.2</v>
-      </c>
-      <c r="AD196">
-        <v>1.57</v>
-      </c>
-      <c r="AE196">
-        <v>1.2</v>
-      </c>
-      <c r="AF196">
-        <v>1.44</v>
-      </c>
-      <c r="AG196">
-        <v>2.6</v>
-      </c>
       <c r="AH196" t="inlineStr">
         <is>
           <t>[]</t>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AK196">
-        <v>1.46</v>
+        <v>2.33</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,64 +32420,64 @@
         </is>
       </c>
       <c r="N197">
-        <v>1.58</v>
+        <v>2.45</v>
       </c>
       <c r="O197">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="P197">
-        <v>4.7</v>
+        <v>2.45</v>
       </c>
       <c r="Q197">
-        <v>2.02</v>
+        <v>2.88</v>
       </c>
       <c r="R197">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="S197">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T197">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="U197">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="V197">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="W197">
+        <v>1.17</v>
+      </c>
+      <c r="X197">
+        <v>1.02</v>
+      </c>
+      <c r="Y197">
+        <v>1.13</v>
+      </c>
+      <c r="Z197">
+        <v>5</v>
+      </c>
+      <c r="AA197">
+        <v>1.51</v>
+      </c>
+      <c r="AB197">
+        <v>2.35</v>
+      </c>
+      <c r="AC197">
+        <v>2.2</v>
+      </c>
+      <c r="AD197">
+        <v>1.57</v>
+      </c>
+      <c r="AE197">
         <v>1.2</v>
       </c>
-      <c r="X197">
-        <v>1.01</v>
-      </c>
-      <c r="Y197">
-        <v>1.11</v>
-      </c>
-      <c r="Z197">
-        <v>5.5</v>
-      </c>
-      <c r="AA197">
-        <v>1.4</v>
-      </c>
-      <c r="AB197">
-        <v>2.7</v>
-      </c>
-      <c r="AC197">
-        <v>2.15</v>
-      </c>
-      <c r="AD197">
-        <v>1.66</v>
-      </c>
-      <c r="AE197">
-        <v>1.25</v>
-      </c>
       <c r="AF197">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AG197">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32490,10 +32490,10 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AK197">
-        <v>2.33</v>
+        <v>1.46</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -32595,10 +32595,10 @@
         <v>3.28</v>
       </c>
       <c r="R198">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S198">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T198">
         <v>2.5</v>
@@ -32616,10 +32616,10 @@
         <v>1.04</v>
       </c>
       <c r="Y198">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z198">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AA198">
         <v>2.07</v>
@@ -32927,7 +32927,7 @@
         <v>1.22</v>
       </c>
       <c r="T200">
-        <v>3.64</v>
+        <v>3.8</v>
       </c>
       <c r="U200">
         <v>2.05</v>
@@ -32936,7 +32936,7 @@
         <v>1.67</v>
       </c>
       <c r="W200">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X200">
         <v>1.02</v>
@@ -33072,10 +33072,10 @@
         </is>
       </c>
       <c r="N201">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="O201">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="P201">
         <v>6.5</v>
@@ -33235,19 +33235,19 @@
         </is>
       </c>
       <c r="N202">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="O202">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="P202">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="Q202">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="R202">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="S202">
         <v>1.3</v>
@@ -33265,7 +33265,7 @@
         <v>1.11</v>
       </c>
       <c r="X202">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y202">
         <v>1.17</v>
@@ -33289,10 +33289,10 @@
         <v>1.11</v>
       </c>
       <c r="AF202">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AG202">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AH202" t="inlineStr">
         <is>
@@ -33305,10 +33305,10 @@
         </is>
       </c>
       <c r="AJ202">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK202">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AL202">
         <v>0</v>
@@ -33398,7 +33398,7 @@
         </is>
       </c>
       <c r="N203">
-        <v>3.64</v>
+        <v>4</v>
       </c>
       <c r="O203">
         <v>3.1</v>
@@ -33564,7 +33564,7 @@
         <v>1.77</v>
       </c>
       <c r="O204">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P204">
         <v>4.2</v>
@@ -33606,7 +33606,7 @@
         <v>1.98</v>
       </c>
       <c r="AC204">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="AD204">
         <v>1.38</v>
@@ -33724,13 +33724,13 @@
         </is>
       </c>
       <c r="N205">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="O205">
-        <v>4.85</v>
+        <v>4.6</v>
       </c>
       <c r="P205">
-        <v>6.5</v>
+        <v>7.55</v>
       </c>
       <c r="Q205">
         <v>1.8</v>
@@ -34865,13 +34865,13 @@
         </is>
       </c>
       <c r="N212">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="O212">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="P212">
-        <v>4</v>
+        <v>4.22</v>
       </c>
       <c r="Q212">
         <v>2.2</v>
@@ -34904,10 +34904,10 @@
         <v>5.2</v>
       </c>
       <c r="AA212">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AB212">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AC212">
         <v>2.02</v>
@@ -34935,7 +34935,7 @@
         </is>
       </c>
       <c r="AJ212">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK212">
         <v>2.1</v>
@@ -35028,13 +35028,13 @@
         </is>
       </c>
       <c r="N213">
-        <v>5.05</v>
+        <v>4.7</v>
       </c>
       <c r="O213">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="P213">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Q213">
         <v>5</v>
@@ -35098,7 +35098,7 @@
         </is>
       </c>
       <c r="AJ213">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AK213">
         <v>1.15</v>
@@ -35357,16 +35357,16 @@
         <v>1.11</v>
       </c>
       <c r="O215">
-        <v>8.85</v>
+        <v>8.65</v>
       </c>
       <c r="P215">
         <v>24</v>
       </c>
       <c r="Q215">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="R215">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="S215">
         <v>1.21</v>
@@ -35375,34 +35375,34 @@
         <v>3.6</v>
       </c>
       <c r="U215">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="V215">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="W215">
         <v>1.16</v>
       </c>
       <c r="X215">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y215">
         <v>1.09</v>
       </c>
       <c r="Z215">
-        <v>6.29</v>
+        <v>6.97</v>
       </c>
       <c r="AA215">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AB215">
-        <v>2.76</v>
+        <v>2.81</v>
       </c>
       <c r="AC215">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AD215">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AE215">
         <v>1.31</v>
@@ -35411,7 +35411,7 @@
         <v>2.14</v>
       </c>
       <c r="AG215">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AH215" t="inlineStr">
         <is>
@@ -35427,7 +35427,7 @@
         <v>1.06</v>
       </c>
       <c r="AK215">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AL215">
         <v>0</v>
@@ -35731,7 +35731,7 @@
         <v>1.18</v>
       </c>
       <c r="AE217">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF217">
         <v>1.98</v>
@@ -35861,19 +35861,19 @@
         <v>1.36</v>
       </c>
       <c r="T218">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="U218">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V218">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W218">
         <v>1.06</v>
       </c>
       <c r="X218">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y218">
         <v>1.29</v>
@@ -35894,7 +35894,7 @@
         <v>1.22</v>
       </c>
       <c r="AE218">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF218">
         <v>1.79</v>
@@ -35913,10 +35913,10 @@
         </is>
       </c>
       <c r="AJ218">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK218">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AL218">
         <v>0</v>
@@ -35974,12 +35974,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G219">
@@ -36006,64 +36006,64 @@
         </is>
       </c>
       <c r="N219">
-        <v>1.95</v>
+        <v>1.51</v>
       </c>
       <c r="O219">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="P219">
-        <v>3.25</v>
+        <v>5.6</v>
       </c>
       <c r="Q219">
-        <v>2.5</v>
+        <v>1.89</v>
       </c>
       <c r="R219">
-        <v>2.15</v>
+        <v>2.44</v>
       </c>
       <c r="S219">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T219">
-        <v>2.96</v>
+        <v>4.1</v>
       </c>
       <c r="U219">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="V219">
-        <v>1.44</v>
+        <v>1.72</v>
       </c>
       <c r="W219">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="X219">
         <v>1</v>
       </c>
       <c r="Y219">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="Z219">
-        <v>3.9</v>
+        <v>6.5</v>
       </c>
       <c r="AA219">
-        <v>1.74</v>
+        <v>1.43</v>
       </c>
       <c r="AB219">
-        <v>2.08</v>
+        <v>2.75</v>
       </c>
       <c r="AC219">
-        <v>2.7</v>
+        <v>2.07</v>
       </c>
       <c r="AD219">
-        <v>1.36</v>
+        <v>1.78</v>
       </c>
       <c r="AE219">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="AF219">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AG219">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AH219" t="inlineStr">
         <is>
@@ -36076,10 +36076,10 @@
         </is>
       </c>
       <c r="AJ219">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AK219">
-        <v>1.73</v>
+        <v>2.42</v>
       </c>
       <c r="AL219">
         <v>0</v>
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G220">
@@ -36169,64 +36169,64 @@
         </is>
       </c>
       <c r="N220">
-        <v>2.6</v>
+        <v>1.98</v>
       </c>
       <c r="O220">
-        <v>3.7</v>
+        <v>3.48</v>
       </c>
       <c r="P220">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q220">
-        <v>3.15</v>
+        <v>2.5</v>
       </c>
       <c r="R220">
+        <v>2.15</v>
+      </c>
+      <c r="S220">
+        <v>1.3</v>
+      </c>
+      <c r="T220">
+        <v>2.96</v>
+      </c>
+      <c r="U220">
         <v>2.45</v>
       </c>
-      <c r="S220">
-        <v>1.22</v>
-      </c>
-      <c r="T220">
-        <v>3.56</v>
-      </c>
-      <c r="U220">
-        <v>2.18</v>
-      </c>
       <c r="V220">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="W220">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X220">
         <v>1</v>
       </c>
       <c r="Y220">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="Z220">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="AA220">
-        <v>1.53</v>
+        <v>1.74</v>
       </c>
       <c r="AB220">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="AC220">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="AD220">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="AE220">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AF220">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="AG220">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="AH220" t="inlineStr">
         <is>
@@ -36242,7 +36242,7 @@
         <v>1.25</v>
       </c>
       <c r="AK220">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AL220">
         <v>0</v>
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G221">
@@ -36332,64 +36332,64 @@
         </is>
       </c>
       <c r="N221">
-        <v>1.51</v>
+        <v>2.5</v>
       </c>
       <c r="O221">
-        <v>4.48</v>
+        <v>3.6</v>
       </c>
       <c r="P221">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="Q221">
-        <v>1.89</v>
+        <v>3.15</v>
       </c>
       <c r="R221">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="S221">
         <v>1.22</v>
       </c>
       <c r="T221">
-        <v>4.1</v>
+        <v>3.56</v>
       </c>
       <c r="U221">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="V221">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="W221">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X221">
         <v>1</v>
       </c>
       <c r="Y221">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z221">
-        <v>6.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA221">
+        <v>1.53</v>
+      </c>
+      <c r="AB221">
+        <v>2.3</v>
+      </c>
+      <c r="AC221">
+        <v>2.25</v>
+      </c>
+      <c r="AD221">
+        <v>1.55</v>
+      </c>
+      <c r="AE221">
+        <v>1.2</v>
+      </c>
+      <c r="AF221">
         <v>1.43</v>
       </c>
-      <c r="AB221">
-        <v>2.75</v>
-      </c>
-      <c r="AC221">
-        <v>2.07</v>
-      </c>
-      <c r="AD221">
-        <v>1.78</v>
-      </c>
-      <c r="AE221">
-        <v>1.31</v>
-      </c>
-      <c r="AF221">
-        <v>1.53</v>
-      </c>
       <c r="AG221">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="AH221" t="inlineStr">
         <is>
@@ -36402,10 +36402,10 @@
         </is>
       </c>
       <c r="AJ221">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AK221">
-        <v>2.42</v>
+        <v>1.44</v>
       </c>
       <c r="AL221">
         <v>0</v>
@@ -36495,10 +36495,10 @@
         </is>
       </c>
       <c r="N222">
-        <v>2.87</v>
+        <v>3.09</v>
       </c>
       <c r="O222">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P222">
         <v>2.5</v>
@@ -36715,7 +36715,7 @@
         <v>1.83</v>
       </c>
       <c r="AG223">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH223" t="inlineStr">
         <is>
@@ -37014,7 +37014,7 @@
         <v>1.05</v>
       </c>
       <c r="X225">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y225">
         <v>1.3</v>
@@ -37035,7 +37035,7 @@
         <v>1.24</v>
       </c>
       <c r="AE225">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF225">
         <v>2.01</v>
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G226">
@@ -37147,31 +37147,31 @@
         </is>
       </c>
       <c r="N226">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O226">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P226">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q226">
-        <v>2.01</v>
+        <v>2.79</v>
       </c>
       <c r="R226">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="S226">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T226">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="U226">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V226">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W226">
         <v>1.09</v>
@@ -37183,7 +37183,7 @@
         <v>1.18</v>
       </c>
       <c r="Z226">
-        <v>3.82</v>
+        <v>3.86</v>
       </c>
       <c r="AA226">
         <v>1.75</v>
@@ -37192,19 +37192,19 @@
         <v>2.05</v>
       </c>
       <c r="AC226">
-        <v>2.69</v>
+        <v>2.74</v>
       </c>
       <c r="AD226">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE226">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF226">
-        <v>1.81</v>
+        <v>1.58</v>
       </c>
       <c r="AG226">
-        <v>1.88</v>
+        <v>2.21</v>
       </c>
       <c r="AH226" t="inlineStr">
         <is>
@@ -37217,10 +37217,10 @@
         </is>
       </c>
       <c r="AJ226">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AK226">
-        <v>2.38</v>
+        <v>1.53</v>
       </c>
       <c r="AL226">
         <v>0</v>
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Calvo Sotelo</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="G227">
@@ -37310,80 +37310,80 @@
         </is>
       </c>
       <c r="N227">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="O227">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="P227">
-        <v>1.85</v>
+        <v>6</v>
       </c>
       <c r="Q227">
-        <v>3.98</v>
+        <v>2.01</v>
       </c>
       <c r="R227">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="S227">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="T227">
-        <v>3.46</v>
+        <v>3.12</v>
       </c>
       <c r="U227">
-        <v>2.19</v>
+        <v>2.38</v>
       </c>
       <c r="V227">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="W227">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X227">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y227">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z227">
-        <v>4.4</v>
+        <v>3.82</v>
       </c>
       <c r="AA227">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AB227">
-        <v>2.22</v>
+        <v>2.05</v>
       </c>
       <c r="AC227">
+        <v>2.69</v>
+      </c>
+      <c r="AD227">
+        <v>1.36</v>
+      </c>
+      <c r="AE227">
+        <v>1.11</v>
+      </c>
+      <c r="AF227">
+        <v>1.81</v>
+      </c>
+      <c r="AG227">
+        <v>1.88</v>
+      </c>
+      <c r="AH227" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI227" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ227">
+        <v>1.15</v>
+      </c>
+      <c r="AK227">
         <v>2.38</v>
-      </c>
-      <c r="AD227">
-        <v>1.46</v>
-      </c>
-      <c r="AE227">
-        <v>1.15</v>
-      </c>
-      <c r="AF227">
-        <v>1.52</v>
-      </c>
-      <c r="AG227">
-        <v>2.34</v>
-      </c>
-      <c r="AH227" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI227" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ227">
-        <v>1.19</v>
-      </c>
-      <c r="AK227">
-        <v>1.22</v>
       </c>
       <c r="AL227">
         <v>0</v>
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Calvo Sotelo</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G228">
@@ -37473,64 +37473,64 @@
         </is>
       </c>
       <c r="N228">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O228">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P228">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q228">
-        <v>2.63</v>
+        <v>3.98</v>
       </c>
       <c r="R228">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="S228">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="T228">
-        <v>2.86</v>
+        <v>3.46</v>
       </c>
       <c r="U228">
-        <v>2.55</v>
+        <v>2.19</v>
       </c>
       <c r="V228">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="W228">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X228">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y228">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="Z228">
-        <v>3.28</v>
+        <v>4.4</v>
       </c>
       <c r="AA228">
-        <v>1.83</v>
+        <v>1.56</v>
       </c>
       <c r="AB228">
-        <v>1.9</v>
+        <v>2.22</v>
       </c>
       <c r="AC228">
-        <v>3.04</v>
+        <v>2.38</v>
       </c>
       <c r="AD228">
-        <v>1.29</v>
+        <v>1.46</v>
       </c>
       <c r="AE228">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF228">
-        <v>1.69</v>
+        <v>1.52</v>
       </c>
       <c r="AG228">
-        <v>2.03</v>
+        <v>2.34</v>
       </c>
       <c r="AH228" t="inlineStr">
         <is>
@@ -37543,10 +37543,10 @@
         </is>
       </c>
       <c r="AJ228">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AK228">
-        <v>1.62</v>
+        <v>1.22</v>
       </c>
       <c r="AL228">
         <v>0</v>
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G229">
@@ -37645,55 +37645,55 @@
         <v>0</v>
       </c>
       <c r="Q229">
-        <v>2.79</v>
+        <v>2.63</v>
       </c>
       <c r="R229">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="S229">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="T229">
-        <v>3.18</v>
+        <v>2.86</v>
       </c>
       <c r="U229">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="V229">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="W229">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X229">
         <v>1.01</v>
       </c>
       <c r="Y229">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z229">
-        <v>3.86</v>
+        <v>3.28</v>
       </c>
       <c r="AA229">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AB229">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AC229">
-        <v>2.74</v>
+        <v>3.04</v>
       </c>
       <c r="AD229">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AE229">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF229">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AG229">
-        <v>2.21</v>
+        <v>2.03</v>
       </c>
       <c r="AH229" t="inlineStr">
         <is>
@@ -37706,10 +37706,10 @@
         </is>
       </c>
       <c r="AJ229">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK229">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AL229">
         <v>0</v>
@@ -37805,7 +37805,7 @@
         <v>3.8</v>
       </c>
       <c r="P230">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q230">
         <v>3.9</v>
@@ -37823,7 +37823,7 @@
         <v>2.15</v>
       </c>
       <c r="V230">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W230">
         <v>1.13</v>
@@ -37841,7 +37841,7 @@
         <v>1.52</v>
       </c>
       <c r="AB230">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="AC230">
         <v>2.23</v>
@@ -38297,10 +38297,10 @@
         <v>3.52</v>
       </c>
       <c r="Q233">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="R233">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="S233">
         <v>1.31</v>
@@ -38318,7 +38318,7 @@
         <v>1.07</v>
       </c>
       <c r="X233">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y233">
         <v>1.23</v>
@@ -38339,7 +38339,7 @@
         <v>1.28</v>
       </c>
       <c r="AE233">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF233">
         <v>1.71</v>
@@ -38358,10 +38358,10 @@
         </is>
       </c>
       <c r="AJ233">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK233">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AL233">
         <v>0</v>
@@ -38623,10 +38623,10 @@
         <v>6.5</v>
       </c>
       <c r="Q235">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="R235">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="S235">
         <v>1.36</v>
@@ -38644,7 +38644,7 @@
         <v>1.06</v>
       </c>
       <c r="X235">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y235">
         <v>1.25</v>
@@ -38665,7 +38665,7 @@
         <v>1.26</v>
       </c>
       <c r="AE235">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF235">
         <v>2.04</v>
@@ -39071,12 +39071,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G238">
@@ -39103,64 +39103,64 @@
         </is>
       </c>
       <c r="N238">
-        <v>4.04</v>
+        <v>1.2</v>
       </c>
       <c r="O238">
-        <v>3.84</v>
+        <v>6.2</v>
       </c>
       <c r="P238">
-        <v>1.76</v>
+        <v>8</v>
       </c>
       <c r="Q238">
-        <v>4</v>
+        <v>1.49</v>
       </c>
       <c r="R238">
-        <v>2.34</v>
+        <v>3.06</v>
       </c>
       <c r="S238">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="T238">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="U238">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="V238">
-        <v>1.57</v>
+        <v>2.16</v>
       </c>
       <c r="W238">
-        <v>1.12</v>
+        <v>1.35</v>
       </c>
       <c r="X238">
+        <v>1</v>
+      </c>
+      <c r="Y238">
         <v>1.01</v>
       </c>
-      <c r="Y238">
-        <v>1.14</v>
-      </c>
       <c r="Z238">
-        <v>4.33</v>
+        <v>8.6</v>
       </c>
       <c r="AA238">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="AB238">
-        <v>2.23</v>
+        <v>4.39</v>
       </c>
       <c r="AC238">
+        <v>1.53</v>
+      </c>
+      <c r="AD238">
         <v>2.38</v>
       </c>
-      <c r="AD238">
-        <v>1.49</v>
-      </c>
       <c r="AE238">
-        <v>1.14</v>
+        <v>1.59</v>
       </c>
       <c r="AF238">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AG238">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="AH238" t="inlineStr">
         <is>
@@ -39173,10 +39173,10 @@
         </is>
       </c>
       <c r="AJ238">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AK238">
-        <v>1.25</v>
+        <v>3.66</v>
       </c>
       <c r="AL238">
         <v>0</v>
@@ -39234,12 +39234,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G239">
@@ -39266,64 +39266,64 @@
         </is>
       </c>
       <c r="N239">
-        <v>1.46</v>
+        <v>1.72</v>
       </c>
       <c r="O239">
-        <v>4.89</v>
+        <v>3.85</v>
       </c>
       <c r="P239">
-        <v>5.2</v>
+        <v>3.6</v>
       </c>
       <c r="Q239">
-        <v>1.73</v>
+        <v>2.07</v>
       </c>
       <c r="R239">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="S239">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T239">
-        <v>3.94</v>
+        <v>4.6</v>
       </c>
       <c r="U239">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="V239">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="W239">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="X239">
         <v>1.01</v>
       </c>
       <c r="Y239">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Z239">
-        <v>5.45</v>
+        <v>7.4</v>
       </c>
       <c r="AA239">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="AB239">
-        <v>2.66</v>
+        <v>3.28</v>
       </c>
       <c r="AC239">
-        <v>2.03</v>
+        <v>1.81</v>
       </c>
       <c r="AD239">
-        <v>1.72</v>
+        <v>1.92</v>
       </c>
       <c r="AE239">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AF239">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AG239">
-        <v>2.16</v>
+        <v>2.98</v>
       </c>
       <c r="AH239" t="inlineStr">
         <is>
@@ -39336,10 +39336,10 @@
         </is>
       </c>
       <c r="AJ239">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AK239">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="AL239">
         <v>0</v>
@@ -39397,12 +39397,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G240">
@@ -39429,64 +39429,64 @@
         </is>
       </c>
       <c r="N240">
-        <v>5.39</v>
+        <v>2.99</v>
       </c>
       <c r="O240">
-        <v>5.23</v>
+        <v>3.4</v>
       </c>
       <c r="P240">
-        <v>1.42</v>
+        <v>2.04</v>
       </c>
       <c r="Q240">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="R240">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="S240">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="T240">
-        <v>5.1</v>
+        <v>3.4</v>
       </c>
       <c r="U240">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="V240">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="W240">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="X240">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y240">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="Z240">
-        <v>8.300000000000001</v>
+        <v>4.25</v>
       </c>
       <c r="AA240">
-        <v>1.19</v>
+        <v>1.62</v>
       </c>
       <c r="AB240">
-        <v>3.74</v>
+        <v>2.25</v>
       </c>
       <c r="AC240">
-        <v>1.62</v>
+        <v>2.46</v>
       </c>
       <c r="AD240">
-        <v>2.19</v>
+        <v>1.43</v>
       </c>
       <c r="AE240">
-        <v>1.49</v>
+        <v>1.18</v>
       </c>
       <c r="AF240">
-        <v>1.37</v>
+        <v>1.55</v>
       </c>
       <c r="AG240">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="AH240" t="inlineStr">
         <is>
@@ -39499,10 +39499,10 @@
         </is>
       </c>
       <c r="AJ240">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AK240">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="AL240">
         <v>0</v>
@@ -39560,12 +39560,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G241">
@@ -39592,64 +39592,64 @@
         </is>
       </c>
       <c r="N241">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="O241">
-        <v>4.85</v>
+        <v>4.45</v>
       </c>
       <c r="P241">
-        <v>4.99</v>
+        <v>6.4</v>
       </c>
       <c r="Q241">
+        <v>1.79</v>
+      </c>
+      <c r="R241">
+        <v>2.72</v>
+      </c>
+      <c r="S241">
+        <v>1.22</v>
+      </c>
+      <c r="T241">
+        <v>3.9</v>
+      </c>
+      <c r="U241">
         <v>2.13</v>
       </c>
-      <c r="R241">
-        <v>2.7</v>
-      </c>
-      <c r="S241">
-        <v>1.17</v>
-      </c>
-      <c r="T241">
-        <v>5.1</v>
-      </c>
-      <c r="U241">
-        <v>1.91</v>
-      </c>
       <c r="V241">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="W241">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X241">
         <v>1.01</v>
       </c>
       <c r="Y241">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Z241">
-        <v>7.4</v>
+        <v>5.45</v>
       </c>
       <c r="AA241">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="AB241">
-        <v>3.4</v>
+        <v>2.66</v>
       </c>
       <c r="AC241">
-        <v>1.82</v>
+        <v>2.03</v>
       </c>
       <c r="AD241">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="AE241">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AF241">
-        <v>1.32</v>
+        <v>1.6</v>
       </c>
       <c r="AG241">
-        <v>2.9</v>
+        <v>2.16</v>
       </c>
       <c r="AH241" t="inlineStr">
         <is>
@@ -39662,10 +39662,10 @@
         </is>
       </c>
       <c r="AJ241">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="AK241">
-        <v>1.91</v>
+        <v>2.83</v>
       </c>
       <c r="AL241">
         <v>0</v>
@@ -39723,12 +39723,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G242">
@@ -39755,64 +39755,64 @@
         </is>
       </c>
       <c r="N242">
-        <v>2.03</v>
+        <v>5.5</v>
       </c>
       <c r="O242">
-        <v>3.79</v>
+        <v>4.8</v>
       </c>
       <c r="P242">
-        <v>3.14</v>
+        <v>1.37</v>
       </c>
       <c r="Q242">
-        <v>2.11</v>
+        <v>4.49</v>
       </c>
       <c r="R242">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="S242">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T242">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="U242">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="V242">
-        <v>1.7</v>
+        <v>2.01</v>
       </c>
       <c r="W242">
+        <v>1.3</v>
+      </c>
+      <c r="X242">
+        <v>1.01</v>
+      </c>
+      <c r="Y242">
+        <v>1.02</v>
+      </c>
+      <c r="Z242">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AA242">
         <v>1.19</v>
       </c>
-      <c r="X242">
-        <v>1.02</v>
-      </c>
-      <c r="Y242">
-        <v>1.09</v>
-      </c>
-      <c r="Z242">
-        <v>5.4</v>
-      </c>
-      <c r="AA242">
-        <v>1.38</v>
-      </c>
       <c r="AB242">
-        <v>2.62</v>
+        <v>3.74</v>
       </c>
       <c r="AC242">
-        <v>2.03</v>
+        <v>1.62</v>
       </c>
       <c r="AD242">
-        <v>1.72</v>
+        <v>2.19</v>
       </c>
       <c r="AE242">
-        <v>1.31</v>
+        <v>1.49</v>
       </c>
       <c r="AF242">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="AG242">
-        <v>2.58</v>
+        <v>2.8</v>
       </c>
       <c r="AH242" t="inlineStr">
         <is>
@@ -39825,10 +39825,10 @@
         </is>
       </c>
       <c r="AJ242">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="AK242">
-        <v>2.1</v>
+        <v>1.08</v>
       </c>
       <c r="AL242">
         <v>0</v>
@@ -39886,12 +39886,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G243">
@@ -39918,80 +39918,80 @@
         </is>
       </c>
       <c r="N243">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="O243">
-        <v>6.75</v>
+        <v>3.85</v>
       </c>
       <c r="P243">
-        <v>8.56</v>
+        <v>3.85</v>
       </c>
       <c r="Q243">
-        <v>1.54</v>
+        <v>2.11</v>
       </c>
       <c r="R243">
-        <v>3.28</v>
+        <v>2.71</v>
       </c>
       <c r="S243">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="T243">
-        <v>5.95</v>
+        <v>4.1</v>
       </c>
       <c r="U243">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="V243">
+        <v>1.7</v>
+      </c>
+      <c r="W243">
+        <v>1.19</v>
+      </c>
+      <c r="X243">
+        <v>1.02</v>
+      </c>
+      <c r="Y243">
+        <v>1.09</v>
+      </c>
+      <c r="Z243">
+        <v>5.4</v>
+      </c>
+      <c r="AA243">
+        <v>1.38</v>
+      </c>
+      <c r="AB243">
+        <v>2.62</v>
+      </c>
+      <c r="AC243">
+        <v>2.03</v>
+      </c>
+      <c r="AD243">
+        <v>1.72</v>
+      </c>
+      <c r="AE243">
+        <v>1.27</v>
+      </c>
+      <c r="AF243">
+        <v>1.43</v>
+      </c>
+      <c r="AG243">
+        <v>2.58</v>
+      </c>
+      <c r="AH243" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI243" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ243">
+        <v>1.18</v>
+      </c>
+      <c r="AK243">
         <v>2.1</v>
-      </c>
-      <c r="W243">
-        <v>1.35</v>
-      </c>
-      <c r="X243">
-        <v>1</v>
-      </c>
-      <c r="Y243">
-        <v>1.01</v>
-      </c>
-      <c r="Z243">
-        <v>8.6</v>
-      </c>
-      <c r="AA243">
-        <v>1.16</v>
-      </c>
-      <c r="AB243">
-        <v>4.05</v>
-      </c>
-      <c r="AC243">
-        <v>1.53</v>
-      </c>
-      <c r="AD243">
-        <v>2.45</v>
-      </c>
-      <c r="AE243">
-        <v>1.6</v>
-      </c>
-      <c r="AF243">
-        <v>1.44</v>
-      </c>
-      <c r="AG243">
-        <v>2.5</v>
-      </c>
-      <c r="AH243" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI243" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ243">
-        <v>1.11</v>
-      </c>
-      <c r="AK243">
-        <v>3.9</v>
       </c>
       <c r="AL243">
         <v>0</v>
@@ -40081,7 +40081,7 @@
         </is>
       </c>
       <c r="N244">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="O244">
         <v>3.8</v>
@@ -40096,19 +40096,19 @@
         <v>2.3</v>
       </c>
       <c r="S244">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T244">
         <v>3.3</v>
       </c>
       <c r="U244">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="V244">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W244">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X244">
         <v>1.03</v>
@@ -40117,28 +40117,28 @@
         <v>1.16</v>
       </c>
       <c r="Z244">
-        <v>4.24</v>
+        <v>4.18</v>
       </c>
       <c r="AA244">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AB244">
         <v>2.17</v>
       </c>
       <c r="AC244">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="AD244">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AE244">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF244">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AG244">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AH244" t="inlineStr">
         <is>
@@ -40154,7 +40154,7 @@
         <v>1.22</v>
       </c>
       <c r="AK244">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AL244">
         <v>0</v>
@@ -40244,13 +40244,13 @@
         </is>
       </c>
       <c r="N245">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="O245">
         <v>3.5</v>
       </c>
       <c r="P245">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="Q245">
         <v>2.68</v>
@@ -40407,7 +40407,7 @@
         </is>
       </c>
       <c r="N246">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="O246">
         <v>5.15</v>
@@ -40477,7 +40477,7 @@
         </is>
       </c>
       <c r="AJ246">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AK246">
         <v>2.9</v>
@@ -41062,7 +41062,7 @@
         <v>3.09</v>
       </c>
       <c r="O250">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P250">
         <v>2.27</v>
@@ -41098,7 +41098,7 @@
         <v>3.72</v>
       </c>
       <c r="AA250">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB250">
         <v>2</v>
@@ -41132,7 +41132,7 @@
         <v>1.25</v>
       </c>
       <c r="AK250">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AL250">
         <v>0</v>
@@ -41385,16 +41385,16 @@
         </is>
       </c>
       <c r="N252">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="O252">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="P252">
-        <v>4.91</v>
+        <v>5.75</v>
       </c>
       <c r="Q252">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="R252">
         <v>2.19</v>
@@ -41427,7 +41427,7 @@
         <v>1.69</v>
       </c>
       <c r="AB252">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="AC252">
         <v>2.66</v>
@@ -41442,7 +41442,7 @@
         <v>1.81</v>
       </c>
       <c r="AG252">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AH252" t="inlineStr">
         <is>
@@ -41741,7 +41741,7 @@
         <v>1.06</v>
       </c>
       <c r="X254">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y254">
         <v>1.28</v>
@@ -41762,7 +41762,7 @@
         <v>1.25</v>
       </c>
       <c r="AE254">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF254">
         <v>1.75</v>
@@ -41904,7 +41904,7 @@
         <v>1.07</v>
       </c>
       <c r="X255">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y255">
         <v>1.24</v>
@@ -42076,7 +42076,7 @@
         <v>2.88</v>
       </c>
       <c r="AA256">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AB256">
         <v>1.67</v>
@@ -42203,16 +42203,16 @@
         <v>1.61</v>
       </c>
       <c r="O257">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="P257">
-        <v>4.64</v>
+        <v>4.6</v>
       </c>
       <c r="Q257">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="R257">
-        <v>2.39</v>
+        <v>2.74</v>
       </c>
       <c r="S257">
         <v>1.21</v>
@@ -42369,7 +42369,7 @@
         <v>3.68</v>
       </c>
       <c r="P258">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q258">
         <v>4.55</v>
@@ -42529,10 +42529,10 @@
         <v>4.2</v>
       </c>
       <c r="O259">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="P259">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q259">
         <v>4.5</v>
@@ -42580,10 +42580,10 @@
         <v>1.14</v>
       </c>
       <c r="AF259">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG259">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH259" t="inlineStr">
         <is>
@@ -42599,7 +42599,7 @@
         <v>1.22</v>
       </c>
       <c r="AK259">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AL259">
         <v>0</v>
@@ -42855,16 +42855,16 @@
         <v>1.28</v>
       </c>
       <c r="O261">
-        <v>5.5</v>
+        <v>4.85</v>
       </c>
       <c r="P261">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q261">
         <v>1.67</v>
       </c>
       <c r="R261">
-        <v>2.46</v>
+        <v>2.53</v>
       </c>
       <c r="S261">
         <v>1.25</v>
@@ -42882,7 +42882,7 @@
         <v>1.1</v>
       </c>
       <c r="X261">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y261">
         <v>1.14</v>
@@ -42894,7 +42894,7 @@
         <v>1.6</v>
       </c>
       <c r="AB261">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AC261">
         <v>2.45</v>
@@ -42925,7 +42925,7 @@
         <v>1.13</v>
       </c>
       <c r="AK261">
-        <v>2.99</v>
+        <v>3.6</v>
       </c>
       <c r="AL261">
         <v>0</v>
@@ -43018,10 +43018,10 @@
         <v>2.65</v>
       </c>
       <c r="O262">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P262">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="Q262">
         <v>3.2</v>
@@ -43054,7 +43054,7 @@
         <v>3.72</v>
       </c>
       <c r="AA262">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AB262">
         <v>2.02</v>
@@ -43187,10 +43187,10 @@
         <v>7.9</v>
       </c>
       <c r="Q263">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="R263">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="S263">
         <v>1.25</v>
@@ -43199,10 +43199,10 @@
         <v>3.3</v>
       </c>
       <c r="U263">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="V263">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W263">
         <v>1.13</v>
@@ -43217,25 +43217,25 @@
         <v>4.25</v>
       </c>
       <c r="AA263">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AB263">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AC263">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="AD263">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AE263">
         <v>1.13</v>
       </c>
       <c r="AF263">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AG263">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AH263" t="inlineStr">
         <is>
@@ -43251,7 +43251,7 @@
         <v>1.12</v>
       </c>
       <c r="AK263">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="AL263">
         <v>0</v>
@@ -43368,7 +43368,7 @@
         <v>1.6</v>
       </c>
       <c r="W264">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X264">
         <v>1.01</v>
@@ -43386,19 +43386,19 @@
         <v>2.5</v>
       </c>
       <c r="AC264">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="AD264">
         <v>1.58</v>
       </c>
       <c r="AE264">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF264">
         <v>1.44</v>
       </c>
       <c r="AG264">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AH264" t="inlineStr">
         <is>
@@ -43522,7 +43522,7 @@
         <v>1.33</v>
       </c>
       <c r="T265">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="U265">
         <v>2.75</v>
@@ -43534,7 +43534,7 @@
         <v>1.09</v>
       </c>
       <c r="X265">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y265">
         <v>1.22</v>
@@ -43546,7 +43546,7 @@
         <v>1.85</v>
       </c>
       <c r="AB265">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC265">
         <v>2.92</v>
@@ -43577,7 +43577,7 @@
         <v>2.6</v>
       </c>
       <c r="AK265">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AL265">
         <v>0</v>
@@ -43667,55 +43667,55 @@
         </is>
       </c>
       <c r="N266">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="O266">
         <v>3.1</v>
       </c>
       <c r="P266">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="Q266">
-        <v>3.18</v>
+        <v>3.34</v>
       </c>
       <c r="R266">
         <v>1.92</v>
       </c>
       <c r="S266">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="T266">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="U266">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="V266">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W266">
         <v>1.06</v>
       </c>
       <c r="X266">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y266">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z266">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="AA266">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="AB266">
         <v>1.57</v>
       </c>
       <c r="AC266">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="AD266">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE266">
         <v>1.01</v>
@@ -43737,10 +43737,10 @@
         </is>
       </c>
       <c r="AJ266">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AK266">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AL266">
         <v>0</v>
@@ -44032,10 +44032,10 @@
         <v>4.63</v>
       </c>
       <c r="AA268">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AB268">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="AC268">
         <v>2.49</v>
@@ -44162,7 +44162,7 @@
         <v>3.3</v>
       </c>
       <c r="P269">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="Q269">
         <v>3.75</v>
@@ -44177,7 +44177,7 @@
         <v>3.15</v>
       </c>
       <c r="U269">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="V269">
         <v>1.44</v>
@@ -44319,7 +44319,7 @@
         </is>
       </c>
       <c r="N270">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="O270">
         <v>3.2</v>
@@ -44334,10 +44334,10 @@
         <v>2.2</v>
       </c>
       <c r="S270">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T270">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="U270">
         <v>2.64</v>
@@ -44645,13 +44645,13 @@
         </is>
       </c>
       <c r="N272">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="O272">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="P272">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
       <c r="Q272">
         <v>0</v>
@@ -44971,13 +44971,13 @@
         </is>
       </c>
       <c r="N274">
-        <v>4</v>
+        <v>4.06</v>
       </c>
       <c r="O274">
-        <v>3.52</v>
+        <v>3.8</v>
       </c>
       <c r="P274">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="Q274">
         <v>4.45</v>
@@ -45102,12 +45102,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="G275">
@@ -45134,64 +45134,64 @@
         </is>
       </c>
       <c r="N275">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O275">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P275">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q275">
-        <v>2.06</v>
+        <v>2.63</v>
       </c>
       <c r="R275">
-        <v>2.23</v>
+        <v>2.08</v>
       </c>
       <c r="S275">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T275">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="U275">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="V275">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W275">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X275">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y275">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z275">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AA275">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AB275">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC275">
-        <v>2.83</v>
+        <v>3.28</v>
       </c>
       <c r="AD275">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AE275">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF275">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AG275">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="AH275" t="inlineStr">
         <is>
@@ -45204,10 +45204,10 @@
         </is>
       </c>
       <c r="AJ275">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AK275">
-        <v>2.29</v>
+        <v>1.6</v>
       </c>
       <c r="AL275">
         <v>0</v>
@@ -45265,12 +45265,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G276">
@@ -45297,64 +45297,64 @@
         </is>
       </c>
       <c r="N276">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O276">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P276">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q276">
-        <v>2.63</v>
+        <v>2.06</v>
       </c>
       <c r="R276">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
       <c r="S276">
+        <v>1.31</v>
+      </c>
+      <c r="T276">
+        <v>2.95</v>
+      </c>
+      <c r="U276">
+        <v>2.45</v>
+      </c>
+      <c r="V276">
+        <v>1.44</v>
+      </c>
+      <c r="W276">
+        <v>1.09</v>
+      </c>
+      <c r="X276">
+        <v>1</v>
+      </c>
+      <c r="Y276">
+        <v>1.22</v>
+      </c>
+      <c r="Z276">
+        <v>3.5</v>
+      </c>
+      <c r="AA276">
+        <v>1.77</v>
+      </c>
+      <c r="AB276">
+        <v>1.9</v>
+      </c>
+      <c r="AC276">
+        <v>2.83</v>
+      </c>
+      <c r="AD276">
         <v>1.33</v>
       </c>
-      <c r="T276">
-        <v>2.86</v>
-      </c>
-      <c r="U276">
-        <v>2.65</v>
-      </c>
-      <c r="V276">
-        <v>1.38</v>
-      </c>
-      <c r="W276">
-        <v>1.06</v>
-      </c>
-      <c r="X276">
-        <v>1.01</v>
-      </c>
-      <c r="Y276">
-        <v>1.25</v>
-      </c>
-      <c r="Z276">
-        <v>3.28</v>
-      </c>
-      <c r="AA276">
-        <v>1.95</v>
-      </c>
-      <c r="AB276">
+      <c r="AE276">
+        <v>1.1</v>
+      </c>
+      <c r="AF276">
         <v>1.85</v>
       </c>
-      <c r="AC276">
-        <v>3.28</v>
-      </c>
-      <c r="AD276">
-        <v>1.25</v>
-      </c>
-      <c r="AE276">
-        <v>1.05</v>
-      </c>
-      <c r="AF276">
-        <v>1.72</v>
-      </c>
       <c r="AG276">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="AH276" t="inlineStr">
         <is>
@@ -45367,10 +45367,10 @@
         </is>
       </c>
       <c r="AJ276">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AK276">
-        <v>1.6</v>
+        <v>2.29</v>
       </c>
       <c r="AL276">
         <v>0</v>
@@ -46243,12 +46243,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G282">
@@ -46275,64 +46275,64 @@
         </is>
       </c>
       <c r="N282">
-        <v>3.3</v>
+        <v>1.91</v>
       </c>
       <c r="O282">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="P282">
-        <v>2.2</v>
+        <v>3.38</v>
       </c>
       <c r="Q282">
-        <v>3.8</v>
+        <v>2.48</v>
       </c>
       <c r="R282">
-        <v>1.89</v>
+        <v>2.15</v>
       </c>
       <c r="S282">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="T282">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="U282">
-        <v>3.25</v>
+        <v>2.59</v>
       </c>
       <c r="V282">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="W282">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X282">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y282">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="Z282">
-        <v>2.47</v>
+        <v>3.5</v>
       </c>
       <c r="AA282">
-        <v>2.4</v>
+        <v>1.92</v>
       </c>
       <c r="AB282">
-        <v>1.53</v>
+        <v>1.96</v>
       </c>
       <c r="AC282">
-        <v>4.89</v>
+        <v>3.05</v>
       </c>
       <c r="AD282">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AE282">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF282">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AG282">
-        <v>1.73</v>
+        <v>1.99</v>
       </c>
       <c r="AH282" t="inlineStr">
         <is>
@@ -46345,10 +46345,10 @@
         </is>
       </c>
       <c r="AJ282">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="AK282">
-        <v>1.34</v>
+        <v>1.93</v>
       </c>
       <c r="AL282">
         <v>0</v>
@@ -46406,12 +46406,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G283">
@@ -46438,64 +46438,64 @@
         </is>
       </c>
       <c r="N283">
-        <v>1.91</v>
+        <v>3.3</v>
       </c>
       <c r="O283">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="P283">
-        <v>3.38</v>
+        <v>2.2</v>
       </c>
       <c r="Q283">
-        <v>2.48</v>
+        <v>3.8</v>
       </c>
       <c r="R283">
-        <v>2.15</v>
+        <v>1.89</v>
       </c>
       <c r="S283">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="T283">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="U283">
-        <v>2.59</v>
+        <v>3.25</v>
       </c>
       <c r="V283">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="W283">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X283">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y283">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="Z283">
-        <v>3.5</v>
+        <v>2.47</v>
       </c>
       <c r="AA283">
-        <v>1.92</v>
+        <v>2.4</v>
       </c>
       <c r="AB283">
-        <v>1.96</v>
+        <v>1.53</v>
       </c>
       <c r="AC283">
-        <v>3.05</v>
+        <v>4.89</v>
       </c>
       <c r="AD283">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AE283">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF283">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AG283">
-        <v>1.99</v>
+        <v>1.73</v>
       </c>
       <c r="AH283" t="inlineStr">
         <is>
@@ -46508,10 +46508,10 @@
         </is>
       </c>
       <c r="AJ283">
-        <v>1.21</v>
+        <v>1.55</v>
       </c>
       <c r="AK283">
-        <v>1.93</v>
+        <v>1.34</v>
       </c>
       <c r="AL283">
         <v>0</v>
@@ -46834,7 +46834,7 @@
         </is>
       </c>
       <c r="AJ285">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AK285">
         <v>2.16</v>
@@ -46966,7 +46966,7 @@
         <v>4</v>
       </c>
       <c r="AA286">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB286">
         <v>2.08</v>
@@ -47108,13 +47108,13 @@
         <v>1.21</v>
       </c>
       <c r="T287">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="U287">
         <v>2.12</v>
       </c>
       <c r="V287">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="W287">
         <v>1.15</v>
@@ -47256,10 +47256,10 @@
         <v>1.85</v>
       </c>
       <c r="O288">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P288">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="Q288">
         <v>2.23</v>
@@ -47268,7 +47268,7 @@
         <v>2.29</v>
       </c>
       <c r="S288">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T288">
         <v>3.6</v>
@@ -47283,7 +47283,7 @@
         <v>1.15</v>
       </c>
       <c r="X288">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y288">
         <v>1.13</v>
@@ -47416,7 +47416,7 @@
         </is>
       </c>
       <c r="N289">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="O289">
         <v>3.5</v>
@@ -47449,10 +47449,10 @@
         <v>1.01</v>
       </c>
       <c r="Y289">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z289">
-        <v>3.7</v>
+        <v>3.88</v>
       </c>
       <c r="AA289">
         <v>1.8</v>
@@ -47461,10 +47461,10 @@
         <v>2</v>
       </c>
       <c r="AC289">
-        <v>2.84</v>
+        <v>2.89</v>
       </c>
       <c r="AD289">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AE289">
         <v>1.13</v>
@@ -47579,13 +47579,13 @@
         </is>
       </c>
       <c r="N290">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="O290">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="P290">
-        <v>4.87</v>
+        <v>4.5</v>
       </c>
       <c r="Q290">
         <v>0</v>
@@ -47745,7 +47745,7 @@
         <v>1.94</v>
       </c>
       <c r="O291">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="P291">
         <v>2.75</v>
@@ -47763,13 +47763,13 @@
         <v>3.3</v>
       </c>
       <c r="U291">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V291">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="W291">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X291">
         <v>1.03</v>
@@ -47796,7 +47796,7 @@
         <v>1.18</v>
       </c>
       <c r="AF291">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AG291">
         <v>2.28</v>
@@ -47812,7 +47812,7 @@
         </is>
       </c>
       <c r="AJ291">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK291">
         <v>1.75</v>
@@ -47914,55 +47914,55 @@
         <v>10</v>
       </c>
       <c r="Q292">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="R292">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S292">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T292">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="U292">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="V292">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W292">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X292">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y292">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z292">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="AA292">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB292">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AC292">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD292">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE292">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF292">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG292">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH292" t="inlineStr">
         <is>
@@ -47975,10 +47975,10 @@
         </is>
       </c>
       <c r="AJ292">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK292">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AL292">
         <v>0</v>
@@ -48068,7 +48068,7 @@
         </is>
       </c>
       <c r="N293">
-        <v>4.14</v>
+        <v>4.05</v>
       </c>
       <c r="O293">
         <v>4</v>
@@ -48231,7 +48231,7 @@
         </is>
       </c>
       <c r="N294">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="O294">
         <v>3.4</v>
@@ -48270,10 +48270,10 @@
         <v>3.6</v>
       </c>
       <c r="AA294">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB294">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AC294">
         <v>3.1</v>
@@ -48285,7 +48285,7 @@
         <v>1.09</v>
       </c>
       <c r="AF294">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AG294">
         <v>2</v>
@@ -48394,13 +48394,13 @@
         </is>
       </c>
       <c r="N295">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="O295">
         <v>3.8</v>
       </c>
       <c r="P295">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="Q295">
         <v>2.3</v>
@@ -48557,28 +48557,28 @@
         </is>
       </c>
       <c r="N296">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="O296">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="P296">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="Q296">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="R296">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S296">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T296">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="U296">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="V296">
         <v>1.4</v>
@@ -48587,7 +48587,7 @@
         <v>1.05</v>
       </c>
       <c r="X296">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y296">
         <v>1.31</v>
@@ -48596,10 +48596,10 @@
         <v>3.32</v>
       </c>
       <c r="AA296">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AB296">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AC296">
         <v>3.41</v>
@@ -48611,10 +48611,10 @@
         <v>1.07</v>
       </c>
       <c r="AF296">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG296">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH296" t="inlineStr">
         <is>
@@ -48627,10 +48627,10 @@
         </is>
       </c>
       <c r="AJ296">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK296">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AL296">
         <v>0</v>
@@ -49215,7 +49215,7 @@
         <v>3.68</v>
       </c>
       <c r="P300">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="Q300">
         <v>2.48</v>
@@ -49227,7 +49227,7 @@
         <v>1.36</v>
       </c>
       <c r="T300">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="U300">
         <v>2.62</v>
@@ -49279,7 +49279,7 @@
         </is>
       </c>
       <c r="AJ300">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AK300">
         <v>1.73</v>
@@ -50350,64 +50350,64 @@
         </is>
       </c>
       <c r="N307">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="O307">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="P307">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="Q307">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="R307">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="S307">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T307">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U307">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="V307">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="W307">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X307">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y307">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="Z307">
-        <v>3.42</v>
+        <v>4</v>
       </c>
       <c r="AA307">
         <v>1.85</v>
       </c>
       <c r="AB307">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="AC307">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="AD307">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AE307">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AF307">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG307">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH307" t="inlineStr">
         <is>
@@ -50420,10 +50420,10 @@
         </is>
       </c>
       <c r="AJ307">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK307">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AL307">
         <v>0</v>
@@ -50513,13 +50513,13 @@
         </is>
       </c>
       <c r="N308">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="O308">
-        <v>3.78</v>
+        <v>3.6</v>
       </c>
       <c r="P308">
-        <v>4.95</v>
+        <v>4.8</v>
       </c>
       <c r="Q308">
         <v>2.3</v>
@@ -50531,7 +50531,7 @@
         <v>1.43</v>
       </c>
       <c r="T308">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="U308">
         <v>2.77</v>
@@ -50549,28 +50549,28 @@
         <v>1.35</v>
       </c>
       <c r="Z308">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="AA308">
         <v>2.09</v>
       </c>
       <c r="AB308">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AC308">
-        <v>3.42</v>
+        <v>3.75</v>
       </c>
       <c r="AD308">
         <v>1.27</v>
       </c>
       <c r="AE308">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF308">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG308">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AH308" t="inlineStr">
         <is>
@@ -50583,10 +50583,10 @@
         </is>
       </c>
       <c r="AJ308">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AK308">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="AL308">
         <v>0</v>
@@ -50676,13 +50676,13 @@
         </is>
       </c>
       <c r="N309">
-        <v>4.04</v>
+        <v>4.1</v>
       </c>
       <c r="O309">
-        <v>3.86</v>
+        <v>3.95</v>
       </c>
       <c r="P309">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="Q309">
         <v>0</v>
@@ -50839,28 +50839,28 @@
         </is>
       </c>
       <c r="N310">
-        <v>2.21</v>
+        <v>1.91</v>
       </c>
       <c r="O310">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="P310">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="Q310">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="R310">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="S310">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T310">
-        <v>2.77</v>
+        <v>3.02</v>
       </c>
       <c r="U310">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="V310">
         <v>1.38</v>
@@ -50872,28 +50872,28 @@
         <v>1.01</v>
       </c>
       <c r="Y310">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z310">
         <v>3.2</v>
       </c>
       <c r="AA310">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AB310">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AC310">
-        <v>3.21</v>
+        <v>3.14</v>
       </c>
       <c r="AD310">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AE310">
         <v>1.07</v>
       </c>
       <c r="AF310">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG310">
         <v>1.95</v>
@@ -50909,10 +50909,10 @@
         </is>
       </c>
       <c r="AJ310">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK310">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AL310">
         <v>0</v>
@@ -51011,55 +51011,55 @@
         <v>0</v>
       </c>
       <c r="Q311">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="R311">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S311">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T311">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U311">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V311">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W311">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X311">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y311">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z311">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA311">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AB311">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AC311">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD311">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE311">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF311">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG311">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH311" t="inlineStr">
         <is>
@@ -51072,10 +51072,10 @@
         </is>
       </c>
       <c r="AJ311">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK311">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL311">
         <v>0</v>
@@ -51165,43 +51165,43 @@
         </is>
       </c>
       <c r="N312">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="O312">
         <v>2.85</v>
       </c>
       <c r="P312">
-        <v>3.53</v>
+        <v>3.2</v>
       </c>
       <c r="Q312">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R312">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S312">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="T312">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U312">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V312">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W312">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X312">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y312">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Z312">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AA312">
         <v>3.1</v>
@@ -51210,19 +51210,19 @@
         <v>1.36</v>
       </c>
       <c r="AC312">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD312">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE312">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF312">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AG312">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AH312" t="inlineStr">
         <is>
@@ -51235,10 +51235,10 @@
         </is>
       </c>
       <c r="AJ312">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK312">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL312">
         <v>0</v>
@@ -51491,64 +51491,64 @@
         </is>
       </c>
       <c r="N314">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O314">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P314">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q314">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="R314">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S314">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T314">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U314">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V314">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W314">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X314">
         <v>0</v>
       </c>
       <c r="Y314">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z314">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA314">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB314">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC314">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AD314">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE314">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF314">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG314">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH314" t="inlineStr">
         <is>
@@ -51561,10 +51561,10 @@
         </is>
       </c>
       <c r="AJ314">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK314">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL314">
         <v>0</v>
@@ -51654,13 +51654,13 @@
         </is>
       </c>
       <c r="N315">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O315">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="P315">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="Q315">
         <v>0</v>
@@ -51817,16 +51817,16 @@
         </is>
       </c>
       <c r="N316">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="O316">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="P316">
-        <v>4.12</v>
+        <v>4.33</v>
       </c>
       <c r="Q316">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R316">
         <v>2.15</v>
@@ -51838,7 +51838,7 @@
         <v>2.9</v>
       </c>
       <c r="U316">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="V316">
         <v>1.4</v>
@@ -51856,19 +51856,19 @@
         <v>3.25</v>
       </c>
       <c r="AA316">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB316">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="AC316">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AD316">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE316">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF316">
         <v>1.95</v>
@@ -51887,7 +51887,7 @@
         </is>
       </c>
       <c r="AJ316">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AK316">
         <v>2.05</v>
@@ -51983,16 +51983,16 @@
         <v>1.46</v>
       </c>
       <c r="O317">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="P317">
-        <v>6.12</v>
+        <v>5.75</v>
       </c>
       <c r="Q317">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="R317">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="S317">
         <v>1.3</v>
@@ -52001,43 +52001,43 @@
         <v>3.3</v>
       </c>
       <c r="U317">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="V317">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W317">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X317">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y317">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z317">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AA317">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AB317">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC317">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AD317">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AE317">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF317">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG317">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AH317" t="inlineStr">
         <is>
@@ -52050,10 +52050,10 @@
         </is>
       </c>
       <c r="AJ317">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK317">
-        <v>2.75</v>
+        <v>2.46</v>
       </c>
       <c r="AL317">
         <v>0</v>
@@ -52143,64 +52143,64 @@
         </is>
       </c>
       <c r="N318">
-        <v>2.6</v>
+        <v>2.06</v>
       </c>
       <c r="O318">
-        <v>2.75</v>
+        <v>2.96</v>
       </c>
       <c r="P318">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="Q318">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R318">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S318">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T318">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U318">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="V318">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W318">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X318">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y318">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z318">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA318">
-        <v>2.87</v>
+        <v>2.52</v>
       </c>
       <c r="AB318">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AC318">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AD318">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE318">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF318">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG318">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH318" t="inlineStr">
         <is>
@@ -52213,10 +52213,10 @@
         </is>
       </c>
       <c r="AJ318">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK318">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL318">
         <v>0</v>
@@ -53610,34 +53610,34 @@
         </is>
       </c>
       <c r="N327">
-        <v>2.08</v>
+        <v>1.78</v>
       </c>
       <c r="O327">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P327">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="Q327">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="R327">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="S327">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="T327">
-        <v>3.74</v>
+        <v>3.85</v>
       </c>
       <c r="U327">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="V327">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="W327">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X327">
         <v>1.01</v>
@@ -53646,28 +53646,28 @@
         <v>1.1</v>
       </c>
       <c r="Z327">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AA327">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AB327">
-        <v>2.46</v>
+        <v>2.59</v>
       </c>
       <c r="AC327">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AD327">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AE327">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AF327">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AG327">
-        <v>2.66</v>
+        <v>2.57</v>
       </c>
       <c r="AH327" t="inlineStr">
         <is>
@@ -53680,10 +53680,10 @@
         </is>
       </c>
       <c r="AJ327">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK327">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="AL327">
         <v>0</v>
@@ -53782,55 +53782,55 @@
         <v>0</v>
       </c>
       <c r="Q328">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="R328">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S328">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T328">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U328">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V328">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W328">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X328">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y328">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z328">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA328">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB328">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC328">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AD328">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE328">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF328">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG328">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH328" t="inlineStr">
         <is>
@@ -53843,10 +53843,10 @@
         </is>
       </c>
       <c r="AJ328">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK328">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AL328">
         <v>0</v>
@@ -53936,13 +53936,13 @@
         </is>
       </c>
       <c r="N329">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O329">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P329">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q329">
         <v>0</v>
@@ -54099,13 +54099,13 @@
         </is>
       </c>
       <c r="N330">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O330">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P330">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q330">
         <v>0</v>
@@ -54144,10 +54144,10 @@
         <v>0</v>
       </c>
       <c r="AC330">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD330">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE330">
         <v>0</v>

--- a/jogos_2026-11-01.xlsx
+++ b/jogos_2026-11-01.xlsx
@@ -970,34 +970,34 @@
         <v>3.07</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA4">
         <v>1.85</v>
@@ -1006,19 +1006,19 @@
         <v>1.83</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Tokyo Verdy</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,16 +1613,16 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="O8">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P8">
-        <v>2.25</v>
+        <v>2.68</v>
       </c>
       <c r="Q8">
-        <v>3.39</v>
+        <v>2.9</v>
       </c>
       <c r="R8">
         <v>1.99</v>
@@ -1631,40 +1631,40 @@
         <v>1.4</v>
       </c>
       <c r="T8">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="U8">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="V8">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W8">
         <v>1.07</v>
       </c>
       <c r="X8">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y8">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z8">
-        <v>2.97</v>
+        <v>3.14</v>
       </c>
       <c r="AA8">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AB8">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AC8">
         <v>3.9</v>
       </c>
       <c r="AD8">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE8">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF8">
         <v>1.83</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AK8">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tokyo Verdy</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,16 +1776,16 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="O9">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P9">
-        <v>2.68</v>
+        <v>2.25</v>
       </c>
       <c r="Q9">
-        <v>2.9</v>
+        <v>3.39</v>
       </c>
       <c r="R9">
         <v>1.99</v>
@@ -1794,40 +1794,40 @@
         <v>1.4</v>
       </c>
       <c r="T9">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="U9">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="V9">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W9">
         <v>1.07</v>
       </c>
       <c r="X9">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y9">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z9">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="AA9">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AB9">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC9">
         <v>3.9</v>
       </c>
       <c r="AD9">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE9">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF9">
         <v>1.83</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AK9">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.75</v>
+        <v>3.26</v>
       </c>
       <c r="O20">
-        <v>3.53</v>
+        <v>3.55</v>
       </c>
       <c r="P20">
         <v>2.08</v>
@@ -3738,7 +3738,7 @@
         <v>5.5</v>
       </c>
       <c r="P21">
-        <v>10.5</v>
+        <v>9.75</v>
       </c>
       <c r="Q21">
         <v>1.68</v>
@@ -3750,7 +3750,7 @@
         <v>1.29</v>
       </c>
       <c r="T21">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="U21">
         <v>2.3</v>
@@ -4097,10 +4097,10 @@
         <v>3.2</v>
       </c>
       <c r="AA23">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AB23">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AC23">
         <v>3.14</v>
@@ -4749,10 +4749,10 @@
         <v>3.14</v>
       </c>
       <c r="AA27">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AB27">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC27">
         <v>3.34</v>
@@ -4882,55 +4882,55 @@
         <v>0</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5401,7 +5401,7 @@
         <v>2.66</v>
       </c>
       <c r="AA31">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="AB31">
         <v>1.6</v>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="N36">
-        <v>3.82</v>
+        <v>3.91</v>
       </c>
       <c r="O36">
         <v>3.5</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="O39">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="P39">
-        <v>4.53</v>
+        <v>5.01</v>
       </c>
       <c r="Q39">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="R39">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S39">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T39">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="U39">
+        <v>2.25</v>
+      </c>
+      <c r="V39">
+        <v>1.57</v>
+      </c>
+      <c r="W39">
+        <v>1.14</v>
+      </c>
+      <c r="X39">
+        <v>1.01</v>
+      </c>
+      <c r="Y39">
+        <v>1.14</v>
+      </c>
+      <c r="Z39">
+        <v>5</v>
+      </c>
+      <c r="AA39">
+        <v>1.5</v>
+      </c>
+      <c r="AB39">
         <v>2.5</v>
       </c>
-      <c r="V39">
-        <v>1.5</v>
-      </c>
-      <c r="W39">
-        <v>1.11</v>
-      </c>
-      <c r="X39">
-        <v>1.02</v>
-      </c>
-      <c r="Y39">
-        <v>1.2</v>
-      </c>
-      <c r="Z39">
-        <v>4</v>
-      </c>
-      <c r="AA39">
-        <v>1.67</v>
-      </c>
-      <c r="AB39">
-        <v>2.1</v>
-      </c>
       <c r="AC39">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="AD39">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AE39">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AF39">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AG39">
-        <v>2.13</v>
+        <v>2.28</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK39">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,80 +6829,80 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.57</v>
+        <v>12</v>
       </c>
       <c r="O40">
-        <v>3.95</v>
+        <v>8</v>
       </c>
       <c r="P40">
-        <v>5.01</v>
+        <v>1.12</v>
       </c>
       <c r="Q40">
+        <v>10</v>
+      </c>
+      <c r="R40">
+        <v>3.4</v>
+      </c>
+      <c r="S40">
+        <v>1.14</v>
+      </c>
+      <c r="T40">
+        <v>5</v>
+      </c>
+      <c r="U40">
+        <v>1.73</v>
+      </c>
+      <c r="V40">
         <v>2</v>
       </c>
-      <c r="R40">
-        <v>2.5</v>
-      </c>
-      <c r="S40">
-        <v>1.22</v>
-      </c>
-      <c r="T40">
-        <v>3.75</v>
-      </c>
-      <c r="U40">
-        <v>2.25</v>
-      </c>
-      <c r="V40">
-        <v>1.57</v>
-      </c>
       <c r="W40">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="X40">
+        <v>0</v>
+      </c>
+      <c r="Y40">
+        <v>1.06</v>
+      </c>
+      <c r="Z40">
+        <v>7.5</v>
+      </c>
+      <c r="AA40">
+        <v>1.25</v>
+      </c>
+      <c r="AB40">
+        <v>3.5</v>
+      </c>
+      <c r="AC40">
+        <v>1.67</v>
+      </c>
+      <c r="AD40">
+        <v>2.1</v>
+      </c>
+      <c r="AE40">
+        <v>1.37</v>
+      </c>
+      <c r="AF40">
+        <v>1.85</v>
+      </c>
+      <c r="AG40">
+        <v>1.87</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ40">
+        <v>1.05</v>
+      </c>
+      <c r="AK40">
         <v>1.01</v>
-      </c>
-      <c r="Y40">
-        <v>1.14</v>
-      </c>
-      <c r="Z40">
-        <v>5</v>
-      </c>
-      <c r="AA40">
-        <v>1.5</v>
-      </c>
-      <c r="AB40">
-        <v>2.5</v>
-      </c>
-      <c r="AC40">
-        <v>2.25</v>
-      </c>
-      <c r="AD40">
-        <v>1.57</v>
-      </c>
-      <c r="AE40">
-        <v>1.22</v>
-      </c>
-      <c r="AF40">
-        <v>1.57</v>
-      </c>
-      <c r="AG40">
-        <v>2.28</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ40">
-        <v>1.17</v>
-      </c>
-      <c r="AK40">
-        <v>2.4</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,80 +6992,80 @@
         </is>
       </c>
       <c r="N41">
-        <v>12</v>
+        <v>1.65</v>
       </c>
       <c r="O41">
-        <v>8</v>
+        <v>3.8</v>
       </c>
       <c r="P41">
-        <v>1.12</v>
+        <v>4.53</v>
       </c>
       <c r="Q41">
-        <v>10</v>
+        <v>2.12</v>
       </c>
       <c r="R41">
-        <v>3.4</v>
+        <v>2.38</v>
       </c>
       <c r="S41">
+        <v>1.29</v>
+      </c>
+      <c r="T41">
+        <v>3.25</v>
+      </c>
+      <c r="U41">
+        <v>2.5</v>
+      </c>
+      <c r="V41">
+        <v>1.5</v>
+      </c>
+      <c r="W41">
+        <v>1.11</v>
+      </c>
+      <c r="X41">
+        <v>1.02</v>
+      </c>
+      <c r="Y41">
+        <v>1.2</v>
+      </c>
+      <c r="Z41">
+        <v>4</v>
+      </c>
+      <c r="AA41">
+        <v>1.67</v>
+      </c>
+      <c r="AB41">
+        <v>2.1</v>
+      </c>
+      <c r="AC41">
+        <v>2.75</v>
+      </c>
+      <c r="AD41">
+        <v>1.4</v>
+      </c>
+      <c r="AE41">
         <v>1.14</v>
       </c>
-      <c r="T41">
-        <v>5</v>
-      </c>
-      <c r="U41">
-        <v>1.73</v>
-      </c>
-      <c r="V41">
-        <v>2</v>
-      </c>
-      <c r="W41">
-        <v>1.25</v>
-      </c>
-      <c r="X41">
-        <v>0</v>
-      </c>
-      <c r="Y41">
-        <v>1.06</v>
-      </c>
-      <c r="Z41">
-        <v>7.5</v>
-      </c>
-      <c r="AA41">
-        <v>1.25</v>
-      </c>
-      <c r="AB41">
-        <v>3.5</v>
-      </c>
-      <c r="AC41">
-        <v>1.67</v>
-      </c>
-      <c r="AD41">
+      <c r="AF41">
+        <v>1.65</v>
+      </c>
+      <c r="AG41">
+        <v>2.13</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41">
+        <v>1.2</v>
+      </c>
+      <c r="AK41">
         <v>2.1</v>
-      </c>
-      <c r="AE41">
-        <v>1.37</v>
-      </c>
-      <c r="AF41">
-        <v>1.85</v>
-      </c>
-      <c r="AG41">
-        <v>1.87</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ41">
-        <v>1.05</v>
-      </c>
-      <c r="AK41">
-        <v>1.01</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mijas Las Lagunas</t>
+          <t>CD Don Benito</t>
         </is>
       </c>
       <c r="G44">
@@ -7490,7 +7490,7 @@
         <v>0</v>
       </c>
       <c r="Q44">
-        <v>2.87</v>
+        <v>2.44</v>
       </c>
       <c r="R44">
         <v>2.2</v>
@@ -7520,10 +7520,10 @@
         <v>3.94</v>
       </c>
       <c r="AA44">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AB44">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="AC44">
         <v>2.7</v>
@@ -7535,10 +7535,10 @@
         <v>1.1</v>
       </c>
       <c r="AF44">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AG44">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK44">
-        <v>1.49</v>
+        <v>1.74</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CD Don Benito</t>
+          <t>Mijas Las Lagunas</t>
         </is>
       </c>
       <c r="G45">
@@ -7653,7 +7653,7 @@
         <v>0</v>
       </c>
       <c r="Q45">
-        <v>2.44</v>
+        <v>2.87</v>
       </c>
       <c r="R45">
         <v>2.2</v>
@@ -7683,10 +7683,10 @@
         <v>3.94</v>
       </c>
       <c r="AA45">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AB45">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AC45">
         <v>2.7</v>
@@ -7698,10 +7698,10 @@
         <v>1.1</v>
       </c>
       <c r="AF45">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AG45">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK45">
-        <v>1.74</v>
+        <v>1.49</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7973,7 +7973,7 @@
         <v>1.87</v>
       </c>
       <c r="O47">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="P47">
         <v>4.03</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Peña Deportiva</t>
+          <t>La Nucía</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>3.8</v>
+        <v>2.08</v>
       </c>
       <c r="O49">
-        <v>3.6</v>
+        <v>3.12</v>
       </c>
       <c r="P49">
-        <v>1.8</v>
+        <v>3.28</v>
       </c>
       <c r="Q49">
-        <v>4.2</v>
+        <v>2.78</v>
       </c>
       <c r="R49">
-        <v>2.17</v>
+        <v>1.97</v>
       </c>
       <c r="S49">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="T49">
-        <v>2.95</v>
+        <v>2.65</v>
       </c>
       <c r="U49">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="V49">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="W49">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X49">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y49">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="Z49">
-        <v>3.42</v>
+        <v>2.88</v>
       </c>
       <c r="AA49">
-        <v>1.79</v>
+        <v>2.15</v>
       </c>
       <c r="AB49">
-        <v>1.88</v>
+        <v>1.66</v>
       </c>
       <c r="AC49">
-        <v>2.92</v>
+        <v>3.84</v>
       </c>
       <c r="AD49">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AE49">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AF49">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AG49">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AK49">
-        <v>1.17</v>
+        <v>1.59</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>La Nucía</t>
+          <t>Peña Deportiva</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.08</v>
+        <v>3.8</v>
       </c>
       <c r="O50">
-        <v>3.12</v>
+        <v>3.6</v>
       </c>
       <c r="P50">
-        <v>3.28</v>
+        <v>1.8</v>
       </c>
       <c r="Q50">
-        <v>2.78</v>
+        <v>4.2</v>
       </c>
       <c r="R50">
-        <v>1.97</v>
+        <v>2.17</v>
       </c>
       <c r="S50">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="T50">
-        <v>2.65</v>
+        <v>2.95</v>
       </c>
       <c r="U50">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="V50">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="W50">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X50">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="Z50">
-        <v>2.88</v>
+        <v>3.42</v>
       </c>
       <c r="AA50">
-        <v>2.15</v>
+        <v>1.79</v>
       </c>
       <c r="AB50">
-        <v>1.66</v>
+        <v>1.88</v>
       </c>
       <c r="AC50">
-        <v>3.84</v>
+        <v>2.92</v>
       </c>
       <c r="AD50">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="AE50">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AF50">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AG50">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AK50">
-        <v>1.59</v>
+        <v>1.17</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8791,13 +8791,13 @@
         <v>3.8</v>
       </c>
       <c r="P52">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Q52">
         <v>2.7</v>
       </c>
       <c r="R52">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="S52">
         <v>1.22</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Atlético Central</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
+        <v>3.1</v>
+      </c>
+      <c r="O55">
+        <v>3.2</v>
+      </c>
+      <c r="P55">
+        <v>2.09</v>
+      </c>
+      <c r="Q55">
+        <v>3.98</v>
+      </c>
+      <c r="R55">
+        <v>2.04</v>
+      </c>
+      <c r="S55">
+        <v>1.35</v>
+      </c>
+      <c r="T55">
+        <v>2.77</v>
+      </c>
+      <c r="U55">
+        <v>2.77</v>
+      </c>
+      <c r="V55">
+        <v>1.35</v>
+      </c>
+      <c r="W55">
+        <v>1.06</v>
+      </c>
+      <c r="X55">
+        <v>1.02</v>
+      </c>
+      <c r="Y55">
+        <v>1.29</v>
+      </c>
+      <c r="Z55">
+        <v>3.04</v>
+      </c>
+      <c r="AA55">
         <v>2.05</v>
       </c>
-      <c r="O55">
-        <v>3.3</v>
-      </c>
-      <c r="P55">
-        <v>3.1</v>
-      </c>
-      <c r="Q55">
-        <v>2.63</v>
-      </c>
-      <c r="R55">
-        <v>2.2</v>
-      </c>
-      <c r="S55">
-        <v>1.3</v>
-      </c>
-      <c r="T55">
-        <v>3</v>
-      </c>
-      <c r="U55">
-        <v>2.38</v>
-      </c>
-      <c r="V55">
-        <v>1.47</v>
-      </c>
-      <c r="W55">
-        <v>1.09</v>
-      </c>
-      <c r="X55">
-        <v>1.01</v>
-      </c>
-      <c r="Y55">
-        <v>1.2</v>
-      </c>
-      <c r="Z55">
-        <v>3.7</v>
-      </c>
-      <c r="AA55">
+      <c r="AB55">
         <v>1.75</v>
       </c>
-      <c r="AB55">
-        <v>2.05</v>
-      </c>
       <c r="AC55">
-        <v>2.7</v>
+        <v>3.48</v>
       </c>
       <c r="AD55">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AE55">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF55">
-        <v>1.59</v>
+        <v>1.79</v>
       </c>
       <c r="AG55">
-        <v>2.19</v>
+        <v>1.9</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK55">
-        <v>1.57</v>
+        <v>1.26</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Atlético Central</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
+        <v>2.05</v>
+      </c>
+      <c r="O56">
+        <v>3.3</v>
+      </c>
+      <c r="P56">
         <v>3.1</v>
       </c>
-      <c r="O56">
-        <v>3.2</v>
-      </c>
-      <c r="P56">
-        <v>2.09</v>
-      </c>
       <c r="Q56">
-        <v>3.98</v>
+        <v>2.63</v>
       </c>
       <c r="R56">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="S56">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T56">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="U56">
-        <v>2.77</v>
+        <v>2.38</v>
       </c>
       <c r="V56">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="W56">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X56">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="Z56">
-        <v>3.04</v>
+        <v>3.7</v>
       </c>
       <c r="AA56">
+        <v>1.75</v>
+      </c>
+      <c r="AB56">
         <v>2.05</v>
       </c>
-      <c r="AB56">
-        <v>1.75</v>
-      </c>
       <c r="AC56">
-        <v>3.48</v>
+        <v>2.7</v>
       </c>
       <c r="AD56">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AE56">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF56">
-        <v>1.79</v>
+        <v>1.59</v>
       </c>
       <c r="AG56">
-        <v>1.9</v>
+        <v>2.19</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK56">
-        <v>1.26</v>
+        <v>1.57</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9802,7 +9802,7 @@
         <v>3.08</v>
       </c>
       <c r="AA58">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AB58">
         <v>1.74</v>
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="O59">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="P59">
-        <v>8.1</v>
+        <v>9.1</v>
       </c>
       <c r="Q59">
         <v>1.62</v>
@@ -9974,13 +9974,13 @@
         <v>1.92</v>
       </c>
       <c r="AD59">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AE59">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AF59">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AG59">
         <v>2.06</v>
@@ -10907,7 +10907,7 @@
         <v>2.15</v>
       </c>
       <c r="O65">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="P65">
         <v>2.75</v>
@@ -10925,7 +10925,7 @@
         <v>3.26</v>
       </c>
       <c r="U65">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="V65">
         <v>1.5</v>
@@ -11085,7 +11085,7 @@
         <v>1.3</v>
       </c>
       <c r="T66">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U66">
         <v>2.58</v>
@@ -13512,7 +13512,7 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.85</v>
+        <v>3.18</v>
       </c>
       <c r="O81">
         <v>3.18</v>
@@ -13877,7 +13877,7 @@
         <v>4.75</v>
       </c>
       <c r="AA83">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AB83">
         <v>2.04</v>
@@ -14004,7 +14004,7 @@
         <v>2.07</v>
       </c>
       <c r="O84">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P84">
         <v>3</v>
@@ -14164,10 +14164,10 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.33</v>
+        <v>2.52</v>
       </c>
       <c r="O85">
-        <v>3.71</v>
+        <v>3.62</v>
       </c>
       <c r="P85">
         <v>2.55</v>
@@ -14203,7 +14203,7 @@
         <v>4.85</v>
       </c>
       <c r="AA85">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AB85">
         <v>2.33</v>
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="O86">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="P86">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="Q86">
         <v>2.55</v>
@@ -14351,7 +14351,7 @@
         <v>2.26</v>
       </c>
       <c r="V86">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W86">
         <v>1.17</v>
@@ -14710,7 +14710,7 @@
         <v>1.5</v>
       </c>
       <c r="AG88">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14994,19 +14994,19 @@
         <v>2.44</v>
       </c>
       <c r="S90">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T90">
         <v>3.3</v>
       </c>
       <c r="U90">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V90">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W90">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X90">
         <v>1</v>
@@ -15033,10 +15033,10 @@
         <v>1.13</v>
       </c>
       <c r="AF90">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG90">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="O91">
         <v>5.25</v>
       </c>
       <c r="P91">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="Q91">
         <v>1.73</v>
@@ -15471,7 +15471,7 @@
         <v>1.27</v>
       </c>
       <c r="O93">
-        <v>6.2</v>
+        <v>5.75</v>
       </c>
       <c r="P93">
         <v>7</v>
@@ -15489,7 +15489,7 @@
         <v>5.65</v>
       </c>
       <c r="U93">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="V93">
         <v>2.05</v>
@@ -16123,10 +16123,10 @@
         <v>2.15</v>
       </c>
       <c r="O97">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="P97">
-        <v>2.71</v>
+        <v>2.9</v>
       </c>
       <c r="Q97">
         <v>2.9</v>
@@ -16141,10 +16141,10 @@
         <v>3.02</v>
       </c>
       <c r="U97">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="V97">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W97">
         <v>1.07</v>
@@ -16292,7 +16292,7 @@
         <v>2.5</v>
       </c>
       <c r="Q98">
-        <v>4.1</v>
+        <v>3.62</v>
       </c>
       <c r="R98">
         <v>1.84</v>
@@ -16615,7 +16615,7 @@
         <v>5.4</v>
       </c>
       <c r="P100">
-        <v>8</v>
+        <v>9.1</v>
       </c>
       <c r="Q100">
         <v>1.72</v>
@@ -16666,7 +16666,7 @@
         <v>1.85</v>
       </c>
       <c r="AG100">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16935,7 +16935,7 @@
         </is>
       </c>
       <c r="N102">
-        <v>7.5</v>
+        <v>6.16</v>
       </c>
       <c r="O102">
         <v>5.25</v>
@@ -16965,7 +16965,7 @@
         <v>1.17</v>
       </c>
       <c r="X102">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y102">
         <v>1.15</v>
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="O106">
-        <v>3.26</v>
+        <v>3.32</v>
       </c>
       <c r="P106">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="Q106">
         <v>2.76</v>
@@ -17605,10 +17605,10 @@
         <v>1.36</v>
       </c>
       <c r="T106">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="U106">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="V106">
         <v>1.36</v>
@@ -17623,16 +17623,16 @@
         <v>1.33</v>
       </c>
       <c r="Z106">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AA106">
         <v>1.99</v>
       </c>
       <c r="AB106">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AC106">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AD106">
         <v>1.22</v>
@@ -17641,10 +17641,10 @@
         <v>1.05</v>
       </c>
       <c r="AF106">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AG106">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>1.29</v>
       </c>
       <c r="AK106">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -18402,7 +18402,7 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="O111">
         <v>3.8</v>
@@ -18565,7 +18565,7 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="O112">
         <v>3.2</v>
@@ -18604,7 +18604,7 @@
         <v>3.08</v>
       </c>
       <c r="AA112">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AB112">
         <v>1.75</v>
@@ -19232,7 +19232,7 @@
         <v>2.49</v>
       </c>
       <c r="S116">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="T116">
         <v>4.5</v>
@@ -19259,7 +19259,7 @@
         <v>1.33</v>
       </c>
       <c r="AB116">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AC116">
         <v>1.86</v>
@@ -19546,7 +19546,7 @@
         <v>1.2</v>
       </c>
       <c r="O118">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="P118">
         <v>12</v>
@@ -19558,7 +19558,7 @@
         <v>3.14</v>
       </c>
       <c r="S118">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="T118">
         <v>5.2</v>
@@ -19706,13 +19706,13 @@
         </is>
       </c>
       <c r="N119">
-        <v>4.29</v>
+        <v>3.81</v>
       </c>
       <c r="O119">
         <v>4.15</v>
       </c>
       <c r="P119">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="Q119">
         <v>3.85</v>
@@ -20038,7 +20038,7 @@
         <v>3.8</v>
       </c>
       <c r="P121">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="Q121">
         <v>3</v>
@@ -20521,13 +20521,13 @@
         </is>
       </c>
       <c r="N124">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="O124">
         <v>3.25</v>
       </c>
       <c r="P124">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="Q124">
         <v>2.33</v>
@@ -20560,7 +20560,7 @@
         <v>2.97</v>
       </c>
       <c r="AA124">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AB124">
         <v>1.67</v>
@@ -20690,7 +20690,7 @@
         <v>3.1</v>
       </c>
       <c r="P125">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q125">
         <v>3.75</v>
@@ -20847,13 +20847,13 @@
         </is>
       </c>
       <c r="N126">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="O126">
         <v>3.1</v>
       </c>
       <c r="P126">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="Q126">
         <v>3.74</v>
@@ -21013,7 +21013,7 @@
         <v>2.4</v>
       </c>
       <c r="O127">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="P127">
         <v>2.62</v>
@@ -21028,7 +21028,7 @@
         <v>1.36</v>
       </c>
       <c r="T127">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="U127">
         <v>2.57</v>
@@ -21173,10 +21173,10 @@
         </is>
       </c>
       <c r="N128">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="O128">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P128">
         <v>2.25</v>
@@ -21342,7 +21342,7 @@
         <v>4.1</v>
       </c>
       <c r="P129">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="Q129">
         <v>1.91</v>
@@ -22030,7 +22030,7 @@
         <v>1.63</v>
       </c>
       <c r="AB133">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="AC133">
         <v>2.49</v>
@@ -22477,7 +22477,7 @@
         </is>
       </c>
       <c r="N136">
-        <v>3.2</v>
+        <v>3.39</v>
       </c>
       <c r="O136">
         <v>3.5</v>
@@ -22498,7 +22498,7 @@
         <v>3.4</v>
       </c>
       <c r="U136">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="V136">
         <v>1.53</v>
@@ -23639,10 +23639,10 @@
         <v>3.32</v>
       </c>
       <c r="U143">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="V143">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="W143">
         <v>1.1</v>
@@ -24107,16 +24107,16 @@
         </is>
       </c>
       <c r="N146">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="O146">
         <v>4.46</v>
       </c>
       <c r="P146">
-        <v>7.3</v>
+        <v>7.25</v>
       </c>
       <c r="Q146">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="R146">
         <v>2.4</v>
@@ -24125,7 +24125,7 @@
         <v>1.33</v>
       </c>
       <c r="T146">
-        <v>3.14</v>
+        <v>3.19</v>
       </c>
       <c r="U146">
         <v>2.6</v>
@@ -24140,7 +24140,7 @@
         <v>1.01</v>
       </c>
       <c r="Y146">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z146">
         <v>3.7</v>
@@ -24152,10 +24152,10 @@
         <v>2.02</v>
       </c>
       <c r="AC146">
-        <v>3.1</v>
+        <v>3.17</v>
       </c>
       <c r="AD146">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE146">
         <v>1.1</v>
@@ -24164,7 +24164,7 @@
         <v>1.91</v>
       </c>
       <c r="AG146">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24180,7 +24180,7 @@
         <v>1.06</v>
       </c>
       <c r="AK146">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24270,10 +24270,10 @@
         </is>
       </c>
       <c r="N147">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O147">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P147">
         <v>3</v>
@@ -24297,7 +24297,7 @@
         <v>1.62</v>
       </c>
       <c r="W147">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X147">
         <v>1</v>
@@ -24433,13 +24433,13 @@
         </is>
       </c>
       <c r="N148">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="O148">
         <v>3.64</v>
       </c>
       <c r="P148">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="Q148">
         <v>2.39</v>
@@ -24801,7 +24801,7 @@
         <v>1.79</v>
       </c>
       <c r="AB150">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AC150">
         <v>2.97</v>
@@ -24922,7 +24922,7 @@
         </is>
       </c>
       <c r="N151">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="O151">
         <v>3.7</v>
@@ -27243,7 +27243,7 @@
         <v>3.34</v>
       </c>
       <c r="AA165">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB165">
         <v>1.92</v>
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Castro Daire</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G170">
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Castro Daire</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G171">
@@ -28997,7 +28997,7 @@
         </is>
       </c>
       <c r="N176">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="O176">
         <v>3.4</v>
@@ -31279,10 +31279,10 @@
         </is>
       </c>
       <c r="N190">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="O190">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="P190">
         <v>4.8</v>
@@ -31333,10 +31333,10 @@
         <v>1.15</v>
       </c>
       <c r="AF190">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG190">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AH190" t="inlineStr">
         <is>
@@ -31445,10 +31445,10 @@
         <v>2.45</v>
       </c>
       <c r="O191">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P191">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="Q191">
         <v>3.13</v>
@@ -31484,7 +31484,7 @@
         <v>1.74</v>
       </c>
       <c r="AB191">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AC191">
         <v>3.11</v>
@@ -31605,7 +31605,7 @@
         </is>
       </c>
       <c r="N192">
-        <v>9</v>
+        <v>9.25</v>
       </c>
       <c r="O192">
         <v>7.1</v>
@@ -32260,7 +32260,7 @@
         <v>1.58</v>
       </c>
       <c r="O196">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="P196">
         <v>4.6</v>
@@ -32296,7 +32296,7 @@
         <v>5.5</v>
       </c>
       <c r="AA196">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB196">
         <v>2.7</v>
@@ -32330,7 +32330,7 @@
         <v>1.16</v>
       </c>
       <c r="AK196">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32637,7 +32637,7 @@
         <v>1.04</v>
       </c>
       <c r="AF198">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG198">
         <v>1.85</v>
@@ -32909,13 +32909,13 @@
         </is>
       </c>
       <c r="N200">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="O200">
-        <v>3.8</v>
+        <v>4.15</v>
       </c>
       <c r="P200">
-        <v>3.8</v>
+        <v>4.11</v>
       </c>
       <c r="Q200">
         <v>2.1</v>
@@ -32957,10 +32957,10 @@
         <v>2.17</v>
       </c>
       <c r="AD200">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AE200">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AF200">
         <v>1.44</v>
@@ -33075,7 +33075,7 @@
         <v>1.39</v>
       </c>
       <c r="O201">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="P201">
         <v>6.5</v>
@@ -33238,10 +33238,10 @@
         <v>1.85</v>
       </c>
       <c r="O202">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="P202">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="Q202">
         <v>2.45</v>
@@ -33292,7 +33292,7 @@
         <v>1.62</v>
       </c>
       <c r="AG202">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AH202" t="inlineStr">
         <is>
@@ -33398,7 +33398,7 @@
         </is>
       </c>
       <c r="N203">
-        <v>4</v>
+        <v>3.64</v>
       </c>
       <c r="O203">
         <v>3.1</v>
@@ -33567,7 +33567,7 @@
         <v>3.7</v>
       </c>
       <c r="P204">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="Q204">
         <v>2.3</v>
@@ -33724,7 +33724,7 @@
         </is>
       </c>
       <c r="N205">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="O205">
         <v>4.6</v>
@@ -33736,7 +33736,7 @@
         <v>1.8</v>
       </c>
       <c r="R205">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="S205">
         <v>1.29</v>
@@ -33797,7 +33797,7 @@
         <v>1.14</v>
       </c>
       <c r="AK205">
-        <v>2.81</v>
+        <v>2.95</v>
       </c>
       <c r="AL205">
         <v>0</v>
@@ -34865,7 +34865,7 @@
         </is>
       </c>
       <c r="N212">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="O212">
         <v>4.1</v>
@@ -34877,7 +34877,7 @@
         <v>2.2</v>
       </c>
       <c r="R212">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="S212">
         <v>1.2</v>
@@ -34935,7 +34935,7 @@
         </is>
       </c>
       <c r="AJ212">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK212">
         <v>2.1</v>
@@ -35028,13 +35028,13 @@
         </is>
       </c>
       <c r="N213">
-        <v>4.7</v>
+        <v>5.05</v>
       </c>
       <c r="O213">
         <v>4.2</v>
       </c>
       <c r="P213">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="Q213">
         <v>5</v>
@@ -35061,22 +35061,22 @@
         <v>1</v>
       </c>
       <c r="Y213">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z213">
-        <v>3.98</v>
+        <v>4.33</v>
       </c>
       <c r="AA213">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AB213">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="AC213">
-        <v>2.64</v>
+        <v>2.69</v>
       </c>
       <c r="AD213">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AE213">
         <v>1.18</v>
@@ -35719,10 +35719,10 @@
         <v>2.78</v>
       </c>
       <c r="AA217">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AB217">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AC217">
         <v>3.88</v>
@@ -35731,7 +35731,7 @@
         <v>1.18</v>
       </c>
       <c r="AE217">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF217">
         <v>1.98</v>
@@ -35873,7 +35873,7 @@
         <v>1.06</v>
       </c>
       <c r="X218">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y218">
         <v>1.29</v>
@@ -35894,7 +35894,7 @@
         <v>1.22</v>
       </c>
       <c r="AE218">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF218">
         <v>1.79</v>
@@ -35974,12 +35974,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G219">
@@ -36006,64 +36006,64 @@
         </is>
       </c>
       <c r="N219">
-        <v>1.51</v>
+        <v>1.95</v>
       </c>
       <c r="O219">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="P219">
-        <v>5.6</v>
+        <v>3.25</v>
       </c>
       <c r="Q219">
-        <v>1.89</v>
+        <v>2.5</v>
       </c>
       <c r="R219">
-        <v>2.44</v>
+        <v>2.15</v>
       </c>
       <c r="S219">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T219">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="U219">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="V219">
-        <v>1.72</v>
+        <v>1.44</v>
       </c>
       <c r="W219">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="X219">
         <v>1</v>
       </c>
       <c r="Y219">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="Z219">
-        <v>6.5</v>
+        <v>3.9</v>
       </c>
       <c r="AA219">
-        <v>1.43</v>
+        <v>1.74</v>
       </c>
       <c r="AB219">
-        <v>2.75</v>
+        <v>2.08</v>
       </c>
       <c r="AC219">
-        <v>2.07</v>
+        <v>2.7</v>
       </c>
       <c r="AD219">
-        <v>1.78</v>
+        <v>1.36</v>
       </c>
       <c r="AE219">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="AF219">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AG219">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="AH219" t="inlineStr">
         <is>
@@ -36076,10 +36076,10 @@
         </is>
       </c>
       <c r="AJ219">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AK219">
-        <v>2.42</v>
+        <v>1.8</v>
       </c>
       <c r="AL219">
         <v>0</v>
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G220">
@@ -36169,64 +36169,64 @@
         </is>
       </c>
       <c r="N220">
-        <v>1.98</v>
+        <v>2.5</v>
       </c>
       <c r="O220">
-        <v>3.48</v>
+        <v>3.7</v>
       </c>
       <c r="P220">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q220">
-        <v>2.5</v>
+        <v>3.15</v>
       </c>
       <c r="R220">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="S220">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T220">
-        <v>2.96</v>
+        <v>3.56</v>
       </c>
       <c r="U220">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="V220">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="W220">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X220">
         <v>1</v>
       </c>
       <c r="Y220">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="Z220">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="AA220">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="AB220">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="AC220">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="AD220">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="AE220">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AF220">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AG220">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="AH220" t="inlineStr">
         <is>
@@ -36242,7 +36242,7 @@
         <v>1.25</v>
       </c>
       <c r="AK220">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="AL220">
         <v>0</v>
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G221">
@@ -36332,64 +36332,64 @@
         </is>
       </c>
       <c r="N221">
-        <v>2.5</v>
+        <v>1.51</v>
       </c>
       <c r="O221">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="P221">
-        <v>2.4</v>
+        <v>5.25</v>
       </c>
       <c r="Q221">
-        <v>3.15</v>
+        <v>1.89</v>
       </c>
       <c r="R221">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="S221">
         <v>1.22</v>
       </c>
       <c r="T221">
-        <v>3.56</v>
+        <v>4.1</v>
       </c>
       <c r="U221">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="V221">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="W221">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X221">
         <v>1</v>
       </c>
       <c r="Y221">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z221">
-        <v>4.8</v>
+        <v>6.5</v>
       </c>
       <c r="AA221">
+        <v>1.43</v>
+      </c>
+      <c r="AB221">
+        <v>2.75</v>
+      </c>
+      <c r="AC221">
+        <v>2.07</v>
+      </c>
+      <c r="AD221">
+        <v>1.78</v>
+      </c>
+      <c r="AE221">
+        <v>1.31</v>
+      </c>
+      <c r="AF221">
         <v>1.53</v>
       </c>
-      <c r="AB221">
-        <v>2.3</v>
-      </c>
-      <c r="AC221">
-        <v>2.25</v>
-      </c>
-      <c r="AD221">
-        <v>1.55</v>
-      </c>
-      <c r="AE221">
-        <v>1.2</v>
-      </c>
-      <c r="AF221">
-        <v>1.43</v>
-      </c>
       <c r="AG221">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="AH221" t="inlineStr">
         <is>
@@ -36402,10 +36402,10 @@
         </is>
       </c>
       <c r="AJ221">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK221">
-        <v>1.44</v>
+        <v>2.42</v>
       </c>
       <c r="AL221">
         <v>0</v>
@@ -36658,7 +36658,7 @@
         </is>
       </c>
       <c r="N223">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="O223">
         <v>3.4</v>
@@ -36697,7 +36697,7 @@
         <v>3.27</v>
       </c>
       <c r="AA223">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="AB223">
         <v>1.76</v>
@@ -36878,7 +36878,7 @@
         <v>2.2</v>
       </c>
       <c r="AG224">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AH224" t="inlineStr">
         <is>
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="G226">
@@ -37147,31 +37147,31 @@
         </is>
       </c>
       <c r="N226">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O226">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P226">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q226">
-        <v>2.79</v>
+        <v>2.01</v>
       </c>
       <c r="R226">
-        <v>2.17</v>
+        <v>2.26</v>
       </c>
       <c r="S226">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T226">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="U226">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V226">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W226">
         <v>1.09</v>
@@ -37183,7 +37183,7 @@
         <v>1.18</v>
       </c>
       <c r="Z226">
-        <v>3.86</v>
+        <v>3.82</v>
       </c>
       <c r="AA226">
         <v>1.75</v>
@@ -37192,19 +37192,19 @@
         <v>2.05</v>
       </c>
       <c r="AC226">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="AD226">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE226">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF226">
-        <v>1.58</v>
+        <v>1.81</v>
       </c>
       <c r="AG226">
-        <v>2.21</v>
+        <v>1.88</v>
       </c>
       <c r="AH226" t="inlineStr">
         <is>
@@ -37217,10 +37217,10 @@
         </is>
       </c>
       <c r="AJ226">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AK226">
-        <v>1.53</v>
+        <v>2.38</v>
       </c>
       <c r="AL226">
         <v>0</v>
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Calvo Sotelo</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G227">
@@ -37310,64 +37310,64 @@
         </is>
       </c>
       <c r="N227">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="O227">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="P227">
-        <v>6</v>
+        <v>1.85</v>
       </c>
       <c r="Q227">
-        <v>2.01</v>
+        <v>3.98</v>
       </c>
       <c r="R227">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="S227">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="T227">
-        <v>3.12</v>
+        <v>3.46</v>
       </c>
       <c r="U227">
+        <v>2.19</v>
+      </c>
+      <c r="V227">
+        <v>1.55</v>
+      </c>
+      <c r="W227">
+        <v>1.13</v>
+      </c>
+      <c r="X227">
+        <v>0</v>
+      </c>
+      <c r="Y227">
+        <v>1.14</v>
+      </c>
+      <c r="Z227">
+        <v>4.4</v>
+      </c>
+      <c r="AA227">
+        <v>1.56</v>
+      </c>
+      <c r="AB227">
+        <v>2.22</v>
+      </c>
+      <c r="AC227">
         <v>2.38</v>
       </c>
-      <c r="V227">
-        <v>1.47</v>
-      </c>
-      <c r="W227">
-        <v>1.09</v>
-      </c>
-      <c r="X227">
-        <v>1.01</v>
-      </c>
-      <c r="Y227">
-        <v>1.18</v>
-      </c>
-      <c r="Z227">
-        <v>3.82</v>
-      </c>
-      <c r="AA227">
-        <v>1.75</v>
-      </c>
-      <c r="AB227">
-        <v>2.05</v>
-      </c>
-      <c r="AC227">
-        <v>2.69</v>
-      </c>
       <c r="AD227">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="AE227">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF227">
-        <v>1.81</v>
+        <v>1.52</v>
       </c>
       <c r="AG227">
-        <v>1.88</v>
+        <v>2.34</v>
       </c>
       <c r="AH227" t="inlineStr">
         <is>
@@ -37380,10 +37380,10 @@
         </is>
       </c>
       <c r="AJ227">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AK227">
-        <v>2.38</v>
+        <v>1.22</v>
       </c>
       <c r="AL227">
         <v>0</v>
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Calvo Sotelo</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G228">
@@ -37473,64 +37473,64 @@
         </is>
       </c>
       <c r="N228">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O228">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P228">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q228">
-        <v>3.98</v>
+        <v>2.63</v>
       </c>
       <c r="R228">
-        <v>2.29</v>
+        <v>2.1</v>
       </c>
       <c r="S228">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="T228">
-        <v>3.46</v>
+        <v>2.86</v>
       </c>
       <c r="U228">
-        <v>2.19</v>
+        <v>2.55</v>
       </c>
       <c r="V228">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="W228">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X228">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y228">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="Z228">
-        <v>4.4</v>
+        <v>3.28</v>
       </c>
       <c r="AA228">
-        <v>1.56</v>
+        <v>1.83</v>
       </c>
       <c r="AB228">
-        <v>2.22</v>
+        <v>1.9</v>
       </c>
       <c r="AC228">
-        <v>2.38</v>
+        <v>3.04</v>
       </c>
       <c r="AD228">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="AE228">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF228">
-        <v>1.52</v>
+        <v>1.69</v>
       </c>
       <c r="AG228">
-        <v>2.34</v>
+        <v>2.03</v>
       </c>
       <c r="AH228" t="inlineStr">
         <is>
@@ -37543,10 +37543,10 @@
         </is>
       </c>
       <c r="AJ228">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AK228">
-        <v>1.22</v>
+        <v>1.62</v>
       </c>
       <c r="AL228">
         <v>0</v>
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G229">
@@ -37645,55 +37645,55 @@
         <v>0</v>
       </c>
       <c r="Q229">
-        <v>2.63</v>
+        <v>2.79</v>
       </c>
       <c r="R229">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="S229">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="T229">
-        <v>2.86</v>
+        <v>3.18</v>
       </c>
       <c r="U229">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="V229">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="W229">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X229">
         <v>1.01</v>
       </c>
       <c r="Y229">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z229">
-        <v>3.28</v>
+        <v>3.86</v>
       </c>
       <c r="AA229">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AB229">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AC229">
-        <v>3.04</v>
+        <v>2.74</v>
       </c>
       <c r="AD229">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AE229">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF229">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="AG229">
-        <v>2.03</v>
+        <v>2.21</v>
       </c>
       <c r="AH229" t="inlineStr">
         <is>
@@ -37706,10 +37706,10 @@
         </is>
       </c>
       <c r="AJ229">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK229">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AL229">
         <v>0</v>
@@ -37805,7 +37805,7 @@
         <v>3.8</v>
       </c>
       <c r="P230">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="Q230">
         <v>3.9</v>
@@ -37869,7 +37869,7 @@
         </is>
       </c>
       <c r="AJ230">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK230">
         <v>1.17</v>
@@ -38786,13 +38786,13 @@
         <v>4.91</v>
       </c>
       <c r="Q236">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="R236">
         <v>2.23</v>
       </c>
       <c r="S236">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T236">
         <v>3.12</v>
@@ -38831,10 +38831,10 @@
         <v>1.14</v>
       </c>
       <c r="AF236">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG236">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AH236" t="inlineStr">
         <is>
@@ -38847,10 +38847,10 @@
         </is>
       </c>
       <c r="AJ236">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK236">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AL236">
         <v>0</v>
@@ -39234,12 +39234,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G239">
@@ -39266,64 +39266,64 @@
         </is>
       </c>
       <c r="N239">
-        <v>1.72</v>
+        <v>2.99</v>
       </c>
       <c r="O239">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="P239">
+        <v>2.04</v>
+      </c>
+      <c r="Q239">
         <v>3.6</v>
       </c>
-      <c r="Q239">
-        <v>2.07</v>
-      </c>
       <c r="R239">
-        <v>2.53</v>
+        <v>2.38</v>
       </c>
       <c r="S239">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="T239">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="U239">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="V239">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="W239">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="X239">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y239">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="Z239">
-        <v>7.4</v>
+        <v>4.25</v>
       </c>
       <c r="AA239">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AB239">
-        <v>3.28</v>
+        <v>2.25</v>
       </c>
       <c r="AC239">
-        <v>1.81</v>
+        <v>2.46</v>
       </c>
       <c r="AD239">
-        <v>1.92</v>
+        <v>1.43</v>
       </c>
       <c r="AE239">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AF239">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="AG239">
-        <v>2.98</v>
+        <v>2.35</v>
       </c>
       <c r="AH239" t="inlineStr">
         <is>
@@ -39336,10 +39336,10 @@
         </is>
       </c>
       <c r="AJ239">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AK239">
-        <v>1.95</v>
+        <v>1.29</v>
       </c>
       <c r="AL239">
         <v>0</v>
@@ -39397,12 +39397,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G240">
@@ -39429,80 +39429,80 @@
         </is>
       </c>
       <c r="N240">
-        <v>2.99</v>
+        <v>1.35</v>
       </c>
       <c r="O240">
-        <v>3.4</v>
+        <v>4.45</v>
       </c>
       <c r="P240">
-        <v>2.04</v>
+        <v>6.4</v>
       </c>
       <c r="Q240">
-        <v>3.6</v>
+        <v>1.79</v>
       </c>
       <c r="R240">
-        <v>2.38</v>
+        <v>2.72</v>
       </c>
       <c r="S240">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T240">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="U240">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="V240">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="W240">
+        <v>1.18</v>
+      </c>
+      <c r="X240">
+        <v>1.01</v>
+      </c>
+      <c r="Y240">
+        <v>1.08</v>
+      </c>
+      <c r="Z240">
+        <v>5.45</v>
+      </c>
+      <c r="AA240">
+        <v>1.37</v>
+      </c>
+      <c r="AB240">
+        <v>2.66</v>
+      </c>
+      <c r="AC240">
+        <v>2.03</v>
+      </c>
+      <c r="AD240">
+        <v>1.72</v>
+      </c>
+      <c r="AE240">
+        <v>1.27</v>
+      </c>
+      <c r="AF240">
+        <v>1.6</v>
+      </c>
+      <c r="AG240">
+        <v>2.16</v>
+      </c>
+      <c r="AH240" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI240" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ240">
         <v>1.12</v>
       </c>
-      <c r="X240">
-        <v>1.03</v>
-      </c>
-      <c r="Y240">
-        <v>1.15</v>
-      </c>
-      <c r="Z240">
-        <v>4.25</v>
-      </c>
-      <c r="AA240">
-        <v>1.62</v>
-      </c>
-      <c r="AB240">
-        <v>2.25</v>
-      </c>
-      <c r="AC240">
-        <v>2.46</v>
-      </c>
-      <c r="AD240">
-        <v>1.43</v>
-      </c>
-      <c r="AE240">
-        <v>1.18</v>
-      </c>
-      <c r="AF240">
-        <v>1.55</v>
-      </c>
-      <c r="AG240">
-        <v>2.35</v>
-      </c>
-      <c r="AH240" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI240" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ240">
-        <v>1.24</v>
-      </c>
       <c r="AK240">
-        <v>1.29</v>
+        <v>2.83</v>
       </c>
       <c r="AL240">
         <v>0</v>
@@ -39560,12 +39560,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G241">
@@ -39592,80 +39592,80 @@
         </is>
       </c>
       <c r="N241">
-        <v>1.35</v>
+        <v>5.5</v>
       </c>
       <c r="O241">
-        <v>4.45</v>
+        <v>4.8</v>
       </c>
       <c r="P241">
-        <v>6.4</v>
+        <v>1.37</v>
       </c>
       <c r="Q241">
-        <v>1.79</v>
+        <v>4.49</v>
       </c>
       <c r="R241">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="S241">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="T241">
-        <v>3.9</v>
+        <v>5.4</v>
       </c>
       <c r="U241">
-        <v>2.13</v>
+        <v>1.73</v>
       </c>
       <c r="V241">
-        <v>1.7</v>
+        <v>2.01</v>
       </c>
       <c r="W241">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="X241">
         <v>1.01</v>
       </c>
       <c r="Y241">
+        <v>1.02</v>
+      </c>
+      <c r="Z241">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AA241">
+        <v>1.19</v>
+      </c>
+      <c r="AB241">
+        <v>3.74</v>
+      </c>
+      <c r="AC241">
+        <v>1.62</v>
+      </c>
+      <c r="AD241">
+        <v>2.19</v>
+      </c>
+      <c r="AE241">
+        <v>1.49</v>
+      </c>
+      <c r="AF241">
+        <v>1.37</v>
+      </c>
+      <c r="AG241">
+        <v>2.8</v>
+      </c>
+      <c r="AH241" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI241" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ241">
+        <v>1.1</v>
+      </c>
+      <c r="AK241">
         <v>1.08</v>
-      </c>
-      <c r="Z241">
-        <v>5.45</v>
-      </c>
-      <c r="AA241">
-        <v>1.37</v>
-      </c>
-      <c r="AB241">
-        <v>2.66</v>
-      </c>
-      <c r="AC241">
-        <v>2.03</v>
-      </c>
-      <c r="AD241">
-        <v>1.72</v>
-      </c>
-      <c r="AE241">
-        <v>1.27</v>
-      </c>
-      <c r="AF241">
-        <v>1.6</v>
-      </c>
-      <c r="AG241">
-        <v>2.16</v>
-      </c>
-      <c r="AH241" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI241" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ241">
-        <v>1.12</v>
-      </c>
-      <c r="AK241">
-        <v>2.83</v>
       </c>
       <c r="AL241">
         <v>0</v>
@@ -39723,12 +39723,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G242">
@@ -39755,64 +39755,64 @@
         </is>
       </c>
       <c r="N242">
-        <v>5.5</v>
+        <v>1.67</v>
       </c>
       <c r="O242">
-        <v>4.8</v>
+        <v>3.85</v>
       </c>
       <c r="P242">
-        <v>1.37</v>
+        <v>3.85</v>
       </c>
       <c r="Q242">
-        <v>4.49</v>
+        <v>2.11</v>
       </c>
       <c r="R242">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="S242">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="T242">
+        <v>4.1</v>
+      </c>
+      <c r="U242">
+        <v>2.05</v>
+      </c>
+      <c r="V242">
+        <v>1.7</v>
+      </c>
+      <c r="W242">
+        <v>1.19</v>
+      </c>
+      <c r="X242">
+        <v>1.02</v>
+      </c>
+      <c r="Y242">
+        <v>1.09</v>
+      </c>
+      <c r="Z242">
         <v>5.4</v>
       </c>
-      <c r="U242">
-        <v>1.73</v>
-      </c>
-      <c r="V242">
-        <v>2.01</v>
-      </c>
-      <c r="W242">
-        <v>1.3</v>
-      </c>
-      <c r="X242">
-        <v>1.01</v>
-      </c>
-      <c r="Y242">
-        <v>1.02</v>
-      </c>
-      <c r="Z242">
-        <v>8.300000000000001</v>
-      </c>
       <c r="AA242">
-        <v>1.19</v>
+        <v>1.38</v>
       </c>
       <c r="AB242">
-        <v>3.74</v>
+        <v>2.62</v>
       </c>
       <c r="AC242">
-        <v>1.62</v>
+        <v>2.03</v>
       </c>
       <c r="AD242">
-        <v>2.19</v>
+        <v>1.72</v>
       </c>
       <c r="AE242">
-        <v>1.49</v>
+        <v>1.27</v>
       </c>
       <c r="AF242">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AG242">
-        <v>2.8</v>
+        <v>2.58</v>
       </c>
       <c r="AH242" t="inlineStr">
         <is>
@@ -39825,10 +39825,10 @@
         </is>
       </c>
       <c r="AJ242">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AK242">
-        <v>1.08</v>
+        <v>2.1</v>
       </c>
       <c r="AL242">
         <v>0</v>
@@ -39886,12 +39886,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G243">
@@ -39918,64 +39918,64 @@
         </is>
       </c>
       <c r="N243">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="O243">
         <v>3.85</v>
       </c>
       <c r="P243">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="Q243">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="R243">
-        <v>2.71</v>
+        <v>2.53</v>
       </c>
       <c r="S243">
         <v>1.17</v>
       </c>
       <c r="T243">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="U243">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="V243">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="W243">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="X243">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y243">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="Z243">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="AA243">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AB243">
-        <v>2.62</v>
+        <v>3.28</v>
       </c>
       <c r="AC243">
-        <v>2.03</v>
+        <v>1.81</v>
       </c>
       <c r="AD243">
-        <v>1.72</v>
+        <v>1.92</v>
       </c>
       <c r="AE243">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AF243">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AG243">
-        <v>2.58</v>
+        <v>2.98</v>
       </c>
       <c r="AH243" t="inlineStr">
         <is>
@@ -39988,10 +39988,10 @@
         </is>
       </c>
       <c r="AJ243">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AK243">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AL243">
         <v>0</v>
@@ -40084,10 +40084,10 @@
         <v>1.65</v>
       </c>
       <c r="O244">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="P244">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="Q244">
         <v>2.1</v>
@@ -40244,7 +40244,7 @@
         </is>
       </c>
       <c r="N245">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="O245">
         <v>3.5</v>
@@ -40253,7 +40253,7 @@
         <v>2.97</v>
       </c>
       <c r="Q245">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="R245">
         <v>2.37</v>
@@ -40407,7 +40407,7 @@
         </is>
       </c>
       <c r="N246">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="O246">
         <v>5.15</v>
@@ -40477,7 +40477,7 @@
         </is>
       </c>
       <c r="AJ246">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AK246">
         <v>2.9</v>
@@ -41059,19 +41059,19 @@
         </is>
       </c>
       <c r="N250">
-        <v>3.09</v>
+        <v>2.7</v>
       </c>
       <c r="O250">
         <v>3.4</v>
       </c>
       <c r="P250">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="Q250">
         <v>3.31</v>
       </c>
       <c r="R250">
-        <v>2.33</v>
+        <v>2.13</v>
       </c>
       <c r="S250">
         <v>1.3</v>
@@ -41225,10 +41225,10 @@
         <v>1.44</v>
       </c>
       <c r="O251">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="P251">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="Q251">
         <v>0</v>
@@ -41587,7 +41587,7 @@
         <v>3.72</v>
       </c>
       <c r="AA253">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB253">
         <v>2</v>
@@ -42203,7 +42203,7 @@
         <v>1.61</v>
       </c>
       <c r="O257">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="P257">
         <v>4.6</v>
@@ -42227,7 +42227,7 @@
         <v>1.74</v>
       </c>
       <c r="W257">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X257">
         <v>1</v>
@@ -42363,13 +42363,13 @@
         </is>
       </c>
       <c r="N258">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="O258">
-        <v>3.68</v>
+        <v>3.98</v>
       </c>
       <c r="P258">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="Q258">
         <v>4.55</v>
@@ -42526,10 +42526,10 @@
         </is>
       </c>
       <c r="N259">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="O259">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="P259">
         <v>1.73</v>
@@ -42568,7 +42568,7 @@
         <v>1.68</v>
       </c>
       <c r="AB259">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC259">
         <v>2.63</v>
@@ -42740,7 +42740,7 @@
         <v>1.24</v>
       </c>
       <c r="AE260">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF260">
         <v>1.84</v>
@@ -42855,10 +42855,10 @@
         <v>1.28</v>
       </c>
       <c r="O261">
-        <v>4.85</v>
+        <v>5.35</v>
       </c>
       <c r="P261">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q261">
         <v>1.67</v>
@@ -42891,7 +42891,7 @@
         <v>4.8</v>
       </c>
       <c r="AA261">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AB261">
         <v>2.21</v>
@@ -43217,10 +43217,10 @@
         <v>4.25</v>
       </c>
       <c r="AA263">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AB263">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AC263">
         <v>2.49</v>
@@ -43673,7 +43673,7 @@
         <v>3.1</v>
       </c>
       <c r="P266">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="Q266">
         <v>3.34</v>
@@ -43703,10 +43703,10 @@
         <v>1.41</v>
       </c>
       <c r="Z266">
-        <v>2.81</v>
+        <v>2.87</v>
       </c>
       <c r="AA266">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AB266">
         <v>1.57</v>
@@ -44162,7 +44162,7 @@
         <v>3.3</v>
       </c>
       <c r="P269">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="Q269">
         <v>3.75</v>
@@ -44319,19 +44319,19 @@
         </is>
       </c>
       <c r="N270">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="O270">
         <v>3.2</v>
       </c>
       <c r="P270">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="Q270">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="R270">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="S270">
         <v>1.32</v>
@@ -44482,7 +44482,7 @@
         </is>
       </c>
       <c r="N271">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="O271">
         <v>3.4</v>
@@ -44500,7 +44500,7 @@
         <v>1.36</v>
       </c>
       <c r="T271">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="U271">
         <v>2.66</v>
@@ -44509,7 +44509,7 @@
         <v>1.4</v>
       </c>
       <c r="W271">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X271">
         <v>1.03</v>
@@ -44536,7 +44536,7 @@
         <v>1.07</v>
       </c>
       <c r="AF271">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG271">
         <v>2.05</v>
@@ -44971,10 +44971,10 @@
         </is>
       </c>
       <c r="N274">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="O274">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P274">
         <v>1.8</v>
@@ -45013,7 +45013,7 @@
         <v>1.75</v>
       </c>
       <c r="AB274">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AC274">
         <v>3</v>
@@ -45662,7 +45662,7 @@
         <v>2.7</v>
       </c>
       <c r="AA278">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="AB278">
         <v>1.6</v>
@@ -45828,7 +45828,7 @@
         <v>2.4</v>
       </c>
       <c r="AB279">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AC279">
         <v>4.55</v>
@@ -45837,7 +45837,7 @@
         <v>1.13</v>
       </c>
       <c r="AE279">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF279">
         <v>1.95</v>
@@ -46281,7 +46281,7 @@
         <v>3.35</v>
       </c>
       <c r="P282">
-        <v>3.38</v>
+        <v>3.9</v>
       </c>
       <c r="Q282">
         <v>2.48</v>
@@ -46296,10 +46296,10 @@
         <v>2.73</v>
       </c>
       <c r="U282">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="V282">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W282">
         <v>1.07</v>
@@ -46345,10 +46345,10 @@
         </is>
       </c>
       <c r="AJ282">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="AK282">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AL282">
         <v>0</v>
@@ -46601,7 +46601,7 @@
         </is>
       </c>
       <c r="N284">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="O284">
         <v>3.76</v>
@@ -46619,7 +46619,7 @@
         <v>1.22</v>
       </c>
       <c r="T284">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U284">
         <v>2.13</v>
@@ -46640,7 +46640,7 @@
         <v>4.95</v>
       </c>
       <c r="AA284">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AB284">
         <v>2.38</v>
@@ -46770,7 +46770,7 @@
         <v>3.8</v>
       </c>
       <c r="P285">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="Q285">
         <v>2.17</v>
@@ -46930,10 +46930,10 @@
         <v>1.38</v>
       </c>
       <c r="O286">
-        <v>4.42</v>
+        <v>4.5</v>
       </c>
       <c r="P286">
-        <v>5.8</v>
+        <v>6.25</v>
       </c>
       <c r="Q286">
         <v>1.95</v>
@@ -46966,7 +46966,7 @@
         <v>4</v>
       </c>
       <c r="AA286">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AB286">
         <v>2.08</v>
@@ -46997,7 +46997,7 @@
         </is>
       </c>
       <c r="AJ286">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK286">
         <v>2.53</v>
@@ -47253,19 +47253,19 @@
         </is>
       </c>
       <c r="N288">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="O288">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P288">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="Q288">
-        <v>2.23</v>
+        <v>2.33</v>
       </c>
       <c r="R288">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="S288">
         <v>1.22</v>
@@ -47280,7 +47280,7 @@
         <v>1.47</v>
       </c>
       <c r="W288">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X288">
         <v>1.01</v>
@@ -47416,7 +47416,7 @@
         </is>
       </c>
       <c r="N289">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="O289">
         <v>3.5</v>
@@ -47579,13 +47579,13 @@
         </is>
       </c>
       <c r="N290">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="O290">
         <v>4</v>
       </c>
       <c r="P290">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Q290">
         <v>0</v>
@@ -47799,7 +47799,7 @@
         <v>1.6</v>
       </c>
       <c r="AG291">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AH291" t="inlineStr">
         <is>
@@ -47923,16 +47923,16 @@
         <v>1.15</v>
       </c>
       <c r="T292">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="U292">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="V292">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="W292">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X292">
         <v>1.01</v>
@@ -47959,10 +47959,10 @@
         <v>1.4</v>
       </c>
       <c r="AF292">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG292">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH292" t="inlineStr">
         <is>
@@ -48071,10 +48071,10 @@
         <v>4.05</v>
       </c>
       <c r="O293">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P293">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="Q293">
         <v>0</v>
@@ -48394,7 +48394,7 @@
         </is>
       </c>
       <c r="N295">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="O295">
         <v>3.8</v>
@@ -48403,7 +48403,7 @@
         <v>3.15</v>
       </c>
       <c r="Q295">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="R295">
         <v>2.58</v>
@@ -48412,7 +48412,7 @@
         <v>1.23</v>
       </c>
       <c r="T295">
-        <v>3.84</v>
+        <v>3.7</v>
       </c>
       <c r="U295">
         <v>2.2</v>
@@ -48560,10 +48560,10 @@
         <v>2.1</v>
       </c>
       <c r="O296">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P296">
-        <v>3.4</v>
+        <v>3.56</v>
       </c>
       <c r="Q296">
         <v>2.7</v>
@@ -48578,7 +48578,7 @@
         <v>2.67</v>
       </c>
       <c r="U296">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="V296">
         <v>1.4</v>
@@ -48596,13 +48596,13 @@
         <v>3.32</v>
       </c>
       <c r="AA296">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="AB296">
         <v>1.89</v>
       </c>
       <c r="AC296">
-        <v>3.41</v>
+        <v>3.49</v>
       </c>
       <c r="AD296">
         <v>1.31</v>
@@ -48759,7 +48759,7 @@
         <v>3.5</v>
       </c>
       <c r="AA297">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AB297">
         <v>1.95</v>
@@ -48886,7 +48886,7 @@
         <v>2.19</v>
       </c>
       <c r="O298">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="P298">
         <v>3.1</v>
@@ -49230,13 +49230,13 @@
         <v>3.1</v>
       </c>
       <c r="U300">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="V300">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W300">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X300">
         <v>1.01</v>
@@ -49251,7 +49251,7 @@
         <v>1.76</v>
       </c>
       <c r="AB300">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AC300">
         <v>2.89</v>
@@ -49414,7 +49414,7 @@
         <v>2.52</v>
       </c>
       <c r="AB301">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AC301">
         <v>4.95</v>
@@ -50350,19 +50350,19 @@
         </is>
       </c>
       <c r="N307">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="O307">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="P307">
         <v>2.6</v>
       </c>
       <c r="Q307">
-        <v>2.92</v>
+        <v>2.73</v>
       </c>
       <c r="R307">
-        <v>2.15</v>
+        <v>2.36</v>
       </c>
       <c r="S307">
         <v>1.3</v>
@@ -50386,16 +50386,16 @@
         <v>1.17</v>
       </c>
       <c r="Z307">
-        <v>4</v>
+        <v>4.26</v>
       </c>
       <c r="AA307">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AB307">
         <v>2.08</v>
       </c>
       <c r="AC307">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="AD307">
         <v>1.44</v>
@@ -50531,10 +50531,10 @@
         <v>1.43</v>
       </c>
       <c r="T308">
-        <v>2.57</v>
+        <v>2.84</v>
       </c>
       <c r="U308">
-        <v>2.77</v>
+        <v>3.07</v>
       </c>
       <c r="V308">
         <v>1.37</v>
@@ -50546,19 +50546,19 @@
         <v>1.04</v>
       </c>
       <c r="Y308">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Z308">
-        <v>2.89</v>
+        <v>3.21</v>
       </c>
       <c r="AA308">
-        <v>2.09</v>
+        <v>1.98</v>
       </c>
       <c r="AB308">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="AC308">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AD308">
         <v>1.27</v>
@@ -50586,7 +50586,7 @@
         <v>1.21</v>
       </c>
       <c r="AK308">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AL308">
         <v>0</v>
@@ -50676,10 +50676,10 @@
         </is>
       </c>
       <c r="N309">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="O309">
-        <v>3.95</v>
+        <v>3.74</v>
       </c>
       <c r="P309">
         <v>1.7</v>
@@ -50878,16 +50878,16 @@
         <v>3.2</v>
       </c>
       <c r="AA310">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AB310">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AC310">
-        <v>3.14</v>
+        <v>3.24</v>
       </c>
       <c r="AD310">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE310">
         <v>1.07</v>
@@ -51059,7 +51059,7 @@
         <v>1.36</v>
       </c>
       <c r="AG311">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="AH311" t="inlineStr">
         <is>
@@ -51165,7 +51165,7 @@
         </is>
       </c>
       <c r="N312">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="O312">
         <v>2.85</v>
@@ -51328,64 +51328,64 @@
         </is>
       </c>
       <c r="N313">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O313">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P313">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q313">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="R313">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="S313">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T313">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="U313">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V313">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W313">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X313">
         <v>0</v>
       </c>
       <c r="Y313">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z313">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA313">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AB313">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AC313">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD313">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE313">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF313">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG313">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH313" t="inlineStr">
         <is>
@@ -51398,10 +51398,10 @@
         </is>
       </c>
       <c r="AJ313">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK313">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL313">
         <v>0</v>
@@ -51459,12 +51459,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G314">
@@ -51491,80 +51491,80 @@
         </is>
       </c>
       <c r="N314">
+        <v>1.36</v>
+      </c>
+      <c r="O314">
+        <v>4.6</v>
+      </c>
+      <c r="P314">
+        <v>6.3</v>
+      </c>
+      <c r="Q314">
         <v>1.83</v>
       </c>
-      <c r="O314">
-        <v>3.8</v>
-      </c>
-      <c r="P314">
-        <v>3.25</v>
-      </c>
-      <c r="Q314">
-        <v>2.49</v>
-      </c>
       <c r="R314">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="S314">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T314">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="U314">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="V314">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="W314">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X314">
         <v>0</v>
       </c>
       <c r="Y314">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z314">
-        <v>5.3</v>
+        <v>6.02</v>
       </c>
       <c r="AA314">
         <v>1.4</v>
       </c>
       <c r="AB314">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AC314">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="AD314">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AE314">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AF314">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="AG314">
+        <v>2.38</v>
+      </c>
+      <c r="AH314" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI314" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ314">
+        <v>1.08</v>
+      </c>
+      <c r="AK314">
         <v>2.88</v>
-      </c>
-      <c r="AH314" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI314" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ314">
-        <v>1.22</v>
-      </c>
-      <c r="AK314">
-        <v>1.75</v>
       </c>
       <c r="AL314">
         <v>0</v>
@@ -51622,12 +51622,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G315">
@@ -51654,64 +51654,64 @@
         </is>
       </c>
       <c r="N315">
+        <v>2.01</v>
+      </c>
+      <c r="O315">
+        <v>4</v>
+      </c>
+      <c r="P315">
+        <v>3.2</v>
+      </c>
+      <c r="Q315">
+        <v>2.4</v>
+      </c>
+      <c r="R315">
+        <v>2.45</v>
+      </c>
+      <c r="S315">
+        <v>1.18</v>
+      </c>
+      <c r="T315">
+        <v>4</v>
+      </c>
+      <c r="U315">
+        <v>2.05</v>
+      </c>
+      <c r="V315">
+        <v>1.7</v>
+      </c>
+      <c r="W315">
+        <v>1.2</v>
+      </c>
+      <c r="X315">
+        <v>0</v>
+      </c>
+      <c r="Y315">
+        <v>1.13</v>
+      </c>
+      <c r="Z315">
+        <v>5.3</v>
+      </c>
+      <c r="AA315">
         <v>1.4</v>
       </c>
-      <c r="O315">
-        <v>5.6</v>
-      </c>
-      <c r="P315">
-        <v>6.8</v>
-      </c>
-      <c r="Q315">
-        <v>0</v>
-      </c>
-      <c r="R315">
-        <v>0</v>
-      </c>
-      <c r="S315">
-        <v>0</v>
-      </c>
-      <c r="T315">
-        <v>0</v>
-      </c>
-      <c r="U315">
-        <v>0</v>
-      </c>
-      <c r="V315">
-        <v>0</v>
-      </c>
-      <c r="W315">
-        <v>0</v>
-      </c>
-      <c r="X315">
-        <v>0</v>
-      </c>
-      <c r="Y315">
-        <v>0</v>
-      </c>
-      <c r="Z315">
-        <v>0</v>
-      </c>
-      <c r="AA315">
-        <v>0</v>
-      </c>
       <c r="AB315">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC315">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD315">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE315">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF315">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG315">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH315" t="inlineStr">
         <is>
@@ -51724,10 +51724,10 @@
         </is>
       </c>
       <c r="AJ315">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK315">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL315">
         <v>0</v>
@@ -52321,7 +52321,7 @@
         <v>2.45</v>
       </c>
       <c r="S319">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T319">
         <v>3.7</v>
@@ -52363,7 +52363,7 @@
         <v>1.44</v>
       </c>
       <c r="AG319">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="AH319" t="inlineStr">
         <is>
@@ -52376,7 +52376,7 @@
         </is>
       </c>
       <c r="AJ319">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AK319">
         <v>1.44</v>
@@ -52478,7 +52478,7 @@
         <v>1.53</v>
       </c>
       <c r="Q320">
-        <v>4.88</v>
+        <v>4.6</v>
       </c>
       <c r="R320">
         <v>2.63</v>
@@ -52523,7 +52523,7 @@
         <v>1.3</v>
       </c>
       <c r="AF320">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AG320">
         <v>2.5</v>
@@ -52539,10 +52539,10 @@
         </is>
       </c>
       <c r="AJ320">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AK320">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AL320">
         <v>0</v>
@@ -52677,10 +52677,10 @@
         <v>2.83</v>
       </c>
       <c r="AC321">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AD321">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AE321">
         <v>1.31</v>
@@ -52795,13 +52795,13 @@
         </is>
       </c>
       <c r="N322">
-        <v>1.69</v>
+        <v>1.49</v>
       </c>
       <c r="O322">
-        <v>3.79</v>
+        <v>4.05</v>
       </c>
       <c r="P322">
-        <v>3.89</v>
+        <v>5</v>
       </c>
       <c r="Q322">
         <v>0</v>
@@ -52973,7 +52973,7 @@
         <v>2.3</v>
       </c>
       <c r="S323">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T323">
         <v>3.7</v>
@@ -52985,7 +52985,7 @@
         <v>1.62</v>
       </c>
       <c r="W323">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X323">
         <v>1.02</v>
@@ -53000,22 +53000,22 @@
         <v>1.49</v>
       </c>
       <c r="AB323">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AC323">
-        <v>2.17</v>
+        <v>2.31</v>
       </c>
       <c r="AD323">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="AE323">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AF323">
         <v>1.44</v>
       </c>
       <c r="AG323">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AH323" t="inlineStr">
         <is>
@@ -53028,10 +53028,10 @@
         </is>
       </c>
       <c r="AJ323">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK323">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AL323">
         <v>0</v>
@@ -53136,19 +53136,19 @@
         <v>2.31</v>
       </c>
       <c r="S324">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T324">
         <v>3.08</v>
       </c>
       <c r="U324">
-        <v>2.32</v>
+        <v>2.41</v>
       </c>
       <c r="V324">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W324">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X324">
         <v>1.03</v>
@@ -53191,10 +53191,10 @@
         </is>
       </c>
       <c r="AJ324">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK324">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AL324">
         <v>0</v>
@@ -53323,16 +53323,16 @@
         <v>4.25</v>
       </c>
       <c r="AA325">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AB325">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC325">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="AD325">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AE325">
         <v>1.16</v>
@@ -53354,7 +53354,7 @@
         </is>
       </c>
       <c r="AJ325">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK325">
         <v>1.96</v>
@@ -53456,25 +53456,25 @@
         <v>1.79</v>
       </c>
       <c r="Q326">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="R326">
         <v>2.38</v>
       </c>
       <c r="S326">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T326">
         <v>3.3</v>
       </c>
       <c r="U326">
-        <v>2.21</v>
+        <v>1.88</v>
       </c>
       <c r="V326">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="W326">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X326">
         <v>1.03</v>
@@ -53495,16 +53495,16 @@
         <v>2.24</v>
       </c>
       <c r="AD326">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AE326">
         <v>1.18</v>
       </c>
       <c r="AF326">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="AG326">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH326" t="inlineStr">
         <is>
@@ -53520,7 +53520,7 @@
         <v>1.17</v>
       </c>
       <c r="AK326">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AL326">
         <v>0</v>
@@ -53610,7 +53610,7 @@
         </is>
       </c>
       <c r="N327">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="O327">
         <v>3.75</v>
@@ -53634,7 +53634,7 @@
         <v>2.1</v>
       </c>
       <c r="V327">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="W327">
         <v>1.18</v>
@@ -53683,7 +53683,7 @@
         <v>1.18</v>
       </c>
       <c r="AK327">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AL327">
         <v>0</v>
@@ -53788,7 +53788,7 @@
         <v>2.36</v>
       </c>
       <c r="S328">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T328">
         <v>4</v>
@@ -53797,10 +53797,10 @@
         <v>2.05</v>
       </c>
       <c r="V328">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="W328">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X328">
         <v>1.02</v>
@@ -53936,64 +53936,64 @@
         </is>
       </c>
       <c r="N329">
-        <v>2.63</v>
+        <v>2.79</v>
       </c>
       <c r="O329">
-        <v>4.2</v>
+        <v>4.11</v>
       </c>
       <c r="P329">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="Q329">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R329">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="S329">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T329">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U329">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V329">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W329">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X329">
         <v>0</v>
       </c>
       <c r="Y329">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z329">
-        <v>0</v>
+        <v>7.05</v>
       </c>
       <c r="AA329">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB329">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AC329">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD329">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE329">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF329">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG329">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH329" t="inlineStr">
         <is>
@@ -54006,10 +54006,10 @@
         </is>
       </c>
       <c r="AJ329">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK329">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL329">
         <v>0</v>
@@ -54099,64 +54099,64 @@
         </is>
       </c>
       <c r="N330">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="O330">
-        <v>4.2</v>
+        <v>4.32</v>
       </c>
       <c r="P330">
-        <v>4.6</v>
+        <v>4.47</v>
       </c>
       <c r="Q330">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R330">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="S330">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T330">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U330">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="V330">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W330">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X330">
         <v>0</v>
       </c>
       <c r="Y330">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z330">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="AA330">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB330">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC330">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="AD330">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AE330">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF330">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG330">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH330" t="inlineStr">
         <is>
@@ -54169,10 +54169,10 @@
         </is>
       </c>
       <c r="AJ330">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK330">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AL330">
         <v>0</v>
@@ -54262,13 +54262,13 @@
         </is>
       </c>
       <c r="N331">
-        <v>1.59</v>
+        <v>1.38</v>
       </c>
       <c r="O331">
-        <v>3.64</v>
+        <v>3.83</v>
       </c>
       <c r="P331">
-        <v>4.96</v>
+        <v>5.2</v>
       </c>
       <c r="Q331">
         <v>2.1</v>
@@ -54283,44 +54283,44 @@
         <v>2.9</v>
       </c>
       <c r="U331">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="V331">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W331">
         <v>1.08</v>
       </c>
       <c r="X331">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y331">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z331">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AA331">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AB331">
+        <v>1.84</v>
+      </c>
+      <c r="AC331">
+        <v>3.04</v>
+      </c>
+      <c r="AD331">
+        <v>1.29</v>
+      </c>
+      <c r="AE331">
+        <v>1.08</v>
+      </c>
+      <c r="AF331">
+        <v>1.88</v>
+      </c>
+      <c r="AG331">
         <v>1.85</v>
       </c>
-      <c r="AC331">
-        <v>3.08</v>
-      </c>
-      <c r="AD331">
-        <v>1.28</v>
-      </c>
-      <c r="AE331">
-        <v>1.07</v>
-      </c>
-      <c r="AF331">
-        <v>1.85</v>
-      </c>
-      <c r="AG331">
-        <v>1.83</v>
-      </c>
       <c r="AH331" t="inlineStr">
         <is>
           <t>[]</t>
@@ -54332,10 +54332,10 @@
         </is>
       </c>
       <c r="AJ331">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK331">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AL331">
         <v>0</v>
@@ -54425,64 +54425,64 @@
         </is>
       </c>
       <c r="N332">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O332">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P332">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q332">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R332">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="S332">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T332">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U332">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="V332">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W332">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X332">
         <v>0</v>
       </c>
       <c r="Y332">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z332">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AA332">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB332">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AC332">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD332">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE332">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF332">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG332">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH332" t="inlineStr">
         <is>
@@ -54495,10 +54495,10 @@
         </is>
       </c>
       <c r="AJ332">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK332">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL332">
         <v>0</v>

--- a/jogos_2026-11-01.xlsx
+++ b/jogos_2026-11-01.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="O4">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="P4">
+        <v>2.6</v>
+      </c>
+      <c r="Q4">
+        <v>3.25</v>
+      </c>
+      <c r="R4">
+        <v>2</v>
+      </c>
+      <c r="S4">
+        <v>1.44</v>
+      </c>
+      <c r="T4">
+        <v>2.72</v>
+      </c>
+      <c r="U4">
+        <v>3.22</v>
+      </c>
+      <c r="V4">
+        <v>1.33</v>
+      </c>
+      <c r="W4">
+        <v>1.05</v>
+      </c>
+      <c r="X4">
+        <v>1.04</v>
+      </c>
+      <c r="Y4">
+        <v>1.34</v>
+      </c>
+      <c r="Z4">
         <v>3.07</v>
       </c>
-      <c r="Q4">
-        <v>2.7</v>
-      </c>
-      <c r="R4">
-        <v>2.2</v>
-      </c>
-      <c r="S4">
-        <v>1.38</v>
-      </c>
-      <c r="T4">
-        <v>2.75</v>
-      </c>
-      <c r="U4">
-        <v>2.56</v>
-      </c>
-      <c r="V4">
-        <v>1.43</v>
-      </c>
-      <c r="W4">
-        <v>1.08</v>
-      </c>
-      <c r="X4">
-        <v>1</v>
-      </c>
-      <c r="Y4">
-        <v>1.23</v>
-      </c>
-      <c r="Z4">
-        <v>3.6</v>
-      </c>
       <c r="AA4">
-        <v>1.85</v>
+        <v>2.14</v>
       </c>
       <c r="AB4">
+        <v>1.66</v>
+      </c>
+      <c r="AC4">
+        <v>3.68</v>
+      </c>
+      <c r="AD4">
+        <v>1.2</v>
+      </c>
+      <c r="AE4">
+        <v>1.04</v>
+      </c>
+      <c r="AF4">
         <v>1.83</v>
       </c>
-      <c r="AC4">
-        <v>3.03</v>
-      </c>
-      <c r="AD4">
-        <v>1.38</v>
-      </c>
-      <c r="AE4">
-        <v>1.09</v>
-      </c>
-      <c r="AF4">
-        <v>1.66</v>
-      </c>
       <c r="AG4">
-        <v>2.09</v>
+        <v>1.91</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AK4">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="O5">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="P5">
-        <v>2.6</v>
+        <v>3.07</v>
       </c>
       <c r="Q5">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="R5">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="S5">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="T5">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="U5">
-        <v>3.22</v>
+        <v>2.56</v>
       </c>
       <c r="V5">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="W5">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X5">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="Z5">
-        <v>3.07</v>
+        <v>3.6</v>
       </c>
       <c r="AA5">
-        <v>2.14</v>
+        <v>1.85</v>
       </c>
       <c r="AB5">
+        <v>1.83</v>
+      </c>
+      <c r="AC5">
+        <v>3.03</v>
+      </c>
+      <c r="AD5">
+        <v>1.38</v>
+      </c>
+      <c r="AE5">
+        <v>1.09</v>
+      </c>
+      <c r="AF5">
         <v>1.66</v>
       </c>
-      <c r="AC5">
-        <v>3.68</v>
-      </c>
-      <c r="AD5">
-        <v>1.2</v>
-      </c>
-      <c r="AE5">
-        <v>1.04</v>
-      </c>
-      <c r="AF5">
-        <v>1.83</v>
-      </c>
       <c r="AG5">
-        <v>1.91</v>
+        <v>2.09</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AK5">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -3122,7 +3122,7 @@
         <v>1.72</v>
       </c>
       <c r="AB17">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="AC17">
         <v>2.78</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK17">
         <v>1.36</v>
@@ -3572,10 +3572,10 @@
         <v>3.26</v>
       </c>
       <c r="O20">
-        <v>3.55</v>
+        <v>3.63</v>
       </c>
       <c r="P20">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="Q20">
         <v>3.74</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="O21">
         <v>5.5</v>
       </c>
       <c r="P21">
-        <v>9.75</v>
+        <v>10.5</v>
       </c>
       <c r="Q21">
         <v>1.68</v>
@@ -3750,7 +3750,7 @@
         <v>1.29</v>
       </c>
       <c r="T21">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="U21">
         <v>2.3</v>
@@ -3771,7 +3771,7 @@
         <v>4.66</v>
       </c>
       <c r="AA21">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB21">
         <v>2.34</v>
@@ -4067,71 +4067,71 @@
         <v>3.54</v>
       </c>
       <c r="Q23">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="R23">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S23">
+        <v>1.4</v>
+      </c>
+      <c r="T23">
+        <v>2.7</v>
+      </c>
+      <c r="U23">
+        <v>3</v>
+      </c>
+      <c r="V23">
+        <v>1.35</v>
+      </c>
+      <c r="W23">
+        <v>1.07</v>
+      </c>
+      <c r="X23">
+        <v>1.04</v>
+      </c>
+      <c r="Y23">
+        <v>1.32</v>
+      </c>
+      <c r="Z23">
+        <v>2.88</v>
+      </c>
+      <c r="AA23">
+        <v>2.06</v>
+      </c>
+      <c r="AB23">
+        <v>1.65</v>
+      </c>
+      <c r="AC23">
+        <v>3.68</v>
+      </c>
+      <c r="AD23">
+        <v>1.2</v>
+      </c>
+      <c r="AE23">
+        <v>1.03</v>
+      </c>
+      <c r="AF23">
+        <v>1.91</v>
+      </c>
+      <c r="AG23">
+        <v>1.8</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
         <v>1.33</v>
       </c>
-      <c r="T23">
-        <v>2.84</v>
-      </c>
-      <c r="U23">
-        <v>2.61</v>
-      </c>
-      <c r="V23">
-        <v>1.39</v>
-      </c>
-      <c r="W23">
-        <v>1.06</v>
-      </c>
-      <c r="X23">
-        <v>1.02</v>
-      </c>
-      <c r="Y23">
-        <v>1.26</v>
-      </c>
-      <c r="Z23">
-        <v>3.2</v>
-      </c>
-      <c r="AA23">
-        <v>1.88</v>
-      </c>
-      <c r="AB23">
-        <v>1.79</v>
-      </c>
-      <c r="AC23">
-        <v>3.14</v>
-      </c>
-      <c r="AD23">
-        <v>1.27</v>
-      </c>
-      <c r="AE23">
-        <v>1.07</v>
-      </c>
-      <c r="AF23">
-        <v>1.74</v>
-      </c>
-      <c r="AG23">
-        <v>1.96</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23">
-        <v>1.23</v>
-      </c>
       <c r="AK23">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4251,7 +4251,7 @@
         <v>1.12</v>
       </c>
       <c r="X24">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
         <v>1.18</v>
@@ -4263,7 +4263,7 @@
         <v>1.7</v>
       </c>
       <c r="AB24">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC24">
         <v>2.59</v>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK25">
         <v>1.95</v>
@@ -5371,55 +5371,55 @@
         <v>3.7</v>
       </c>
       <c r="Q31">
-        <v>2.64</v>
+        <v>2.43</v>
       </c>
       <c r="R31">
         <v>2</v>
       </c>
       <c r="S31">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T31">
-        <v>2.51</v>
+        <v>2.75</v>
       </c>
       <c r="U31">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="V31">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W31">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X31">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="Z31">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="AA31">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="AB31">
         <v>1.6</v>
       </c>
       <c r="AC31">
-        <v>4.15</v>
+        <v>3.7</v>
       </c>
       <c r="AD31">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AE31">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF31">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AG31">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK31">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5694,7 +5694,7 @@
         <v>3.2</v>
       </c>
       <c r="P33">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="Q33">
         <v>2.99</v>
@@ -5730,7 +5730,7 @@
         <v>2.13</v>
       </c>
       <c r="AB33">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AC33">
         <v>3.8</v>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AK33">
         <v>1.47</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>3.91</v>
+        <v>4.6</v>
       </c>
       <c r="O36">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="P36">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -7164,55 +7164,55 @@
         <v>0</v>
       </c>
       <c r="Q42">
-        <v>2.34</v>
+        <v>2.45</v>
       </c>
       <c r="R42">
         <v>2.3</v>
       </c>
       <c r="S42">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="T42">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="U42">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="V42">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="W42">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y42">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z42">
-        <v>4.4</v>
+        <v>3.88</v>
       </c>
       <c r="AA42">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AB42">
-        <v>2.18</v>
+        <v>1.99</v>
       </c>
       <c r="AC42">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="AD42">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AE42">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF42">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AG42">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AK42">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7327,34 +7327,34 @@
         <v>0</v>
       </c>
       <c r="Q43">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R43">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S43">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T43">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="U43">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="V43">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W43">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X43">
         <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z43">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AA43">
         <v>1.95</v>
@@ -7363,19 +7363,19 @@
         <v>1.85</v>
       </c>
       <c r="AC43">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="AD43">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE43">
         <v>1.07</v>
       </c>
       <c r="AF43">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AG43">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK43">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7490,34 +7490,34 @@
         <v>0</v>
       </c>
       <c r="Q44">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="R44">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S44">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="T44">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="U44">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="V44">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W44">
         <v>1.1</v>
       </c>
       <c r="X44">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y44">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="Z44">
-        <v>3.94</v>
+        <v>3.58</v>
       </c>
       <c r="AA44">
         <v>1.72</v>
@@ -7526,19 +7526,19 @@
         <v>2.07</v>
       </c>
       <c r="AC44">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="AD44">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AE44">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF44">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AG44">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK44">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7653,55 +7653,55 @@
         <v>0</v>
       </c>
       <c r="Q45">
-        <v>2.87</v>
+        <v>2.3</v>
       </c>
       <c r="R45">
         <v>2.2</v>
       </c>
       <c r="S45">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="T45">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="U45">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="V45">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="W45">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X45">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y45">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z45">
-        <v>3.94</v>
+        <v>3.5</v>
       </c>
       <c r="AA45">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AB45">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="AC45">
-        <v>2.7</v>
+        <v>2.97</v>
       </c>
       <c r="AD45">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE45">
         <v>1.1</v>
       </c>
       <c r="AF45">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="AG45">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK45">
-        <v>1.49</v>
+        <v>1.85</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Peña Deportiva</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mallorca II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,58 +8133,58 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.53</v>
+        <v>3.8</v>
       </c>
       <c r="O48">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P48">
-        <v>5.3</v>
+        <v>1.8</v>
       </c>
       <c r="Q48">
+        <v>4</v>
+      </c>
+      <c r="R48">
         <v>2.1</v>
       </c>
-      <c r="R48">
-        <v>2.25</v>
-      </c>
       <c r="S48">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T48">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="U48">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="V48">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W48">
         <v>1.08</v>
       </c>
       <c r="X48">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="Z48">
-        <v>3.42</v>
+        <v>3.08</v>
       </c>
       <c r="AA48">
+        <v>1.93</v>
+      </c>
+      <c r="AB48">
         <v>1.75</v>
       </c>
-      <c r="AB48">
-        <v>2.05</v>
-      </c>
       <c r="AC48">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AD48">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE48">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF48">
         <v>1.83</v>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="AK48">
-        <v>2.15</v>
+        <v>1.3</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Peña Deportiva</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Mallorca II</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,58 +8459,58 @@
         </is>
       </c>
       <c r="N50">
+        <v>1.53</v>
+      </c>
+      <c r="O50">
         <v>3.8</v>
       </c>
-      <c r="O50">
-        <v>3.6</v>
-      </c>
       <c r="P50">
-        <v>1.8</v>
+        <v>5.3</v>
       </c>
       <c r="Q50">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="R50">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S50">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T50">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="U50">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="V50">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W50">
         <v>1.08</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
+        <v>1.23</v>
+      </c>
+      <c r="Z50">
+        <v>3.42</v>
+      </c>
+      <c r="AA50">
+        <v>1.75</v>
+      </c>
+      <c r="AB50">
+        <v>2.05</v>
+      </c>
+      <c r="AC50">
+        <v>3.05</v>
+      </c>
+      <c r="AD50">
         <v>1.28</v>
       </c>
-      <c r="Z50">
-        <v>3.08</v>
-      </c>
-      <c r="AA50">
-        <v>1.93</v>
-      </c>
-      <c r="AB50">
-        <v>1.75</v>
-      </c>
-      <c r="AC50">
-        <v>3.2</v>
-      </c>
-      <c r="AD50">
-        <v>1.26</v>
-      </c>
       <c r="AE50">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF50">
         <v>1.83</v>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="AK50">
-        <v>1.3</v>
+        <v>2.15</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -9120,22 +9120,22 @@
         <v>4.65</v>
       </c>
       <c r="Q54">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="R54">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="S54">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T54">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U54">
-        <v>2.61</v>
+        <v>2.75</v>
       </c>
       <c r="V54">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W54">
         <v>1.08</v>
@@ -9153,7 +9153,7 @@
         <v>1.85</v>
       </c>
       <c r="AB54">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AC54">
         <v>3.14</v>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK54">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9283,34 +9283,34 @@
         <v>2.09</v>
       </c>
       <c r="Q55">
-        <v>3.98</v>
+        <v>3.5</v>
       </c>
       <c r="R55">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="S55">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T55">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="U55">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="V55">
         <v>1.35</v>
       </c>
       <c r="W55">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X55">
         <v>1.02</v>
       </c>
       <c r="Y55">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z55">
-        <v>3.04</v>
+        <v>2.83</v>
       </c>
       <c r="AA55">
         <v>2.05</v>
@@ -9319,19 +9319,19 @@
         <v>1.75</v>
       </c>
       <c r="AC55">
-        <v>3.48</v>
+        <v>3.75</v>
       </c>
       <c r="AD55">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE55">
         <v>1.06</v>
       </c>
       <c r="AF55">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AG55">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK55">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9446,34 +9446,34 @@
         <v>3.1</v>
       </c>
       <c r="Q56">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="R56">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S56">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T56">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U56">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="V56">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="W56">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X56">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z56">
-        <v>3.7</v>
+        <v>3.28</v>
       </c>
       <c r="AA56">
         <v>1.75</v>
@@ -9482,19 +9482,19 @@
         <v>2.05</v>
       </c>
       <c r="AC56">
-        <v>2.7</v>
+        <v>2.97</v>
       </c>
       <c r="AD56">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE56">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF56">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="AG56">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK56">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9772,40 +9772,40 @@
         <v>1.55</v>
       </c>
       <c r="Q58">
-        <v>5.95</v>
+        <v>6.45</v>
       </c>
       <c r="R58">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="S58">
+        <v>1.39</v>
+      </c>
+      <c r="T58">
+        <v>2.61</v>
+      </c>
+      <c r="U58">
+        <v>2.77</v>
+      </c>
+      <c r="V58">
         <v>1.35</v>
-      </c>
-      <c r="T58">
-        <v>2.77</v>
-      </c>
-      <c r="U58">
-        <v>2.73</v>
-      </c>
-      <c r="V58">
-        <v>1.36</v>
       </c>
       <c r="W58">
         <v>1.06</v>
       </c>
       <c r="X58">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z58">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="AA58">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AB58">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AC58">
         <v>3.34</v>
@@ -9817,10 +9817,10 @@
         <v>1.05</v>
       </c>
       <c r="AF58">
-        <v>1.96</v>
+        <v>2.01</v>
       </c>
       <c r="AG58">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK58">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10098,55 +10098,55 @@
         <v>0</v>
       </c>
       <c r="Q60">
-        <v>7.19</v>
+        <v>9.4</v>
       </c>
       <c r="R60">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="S60">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="T60">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="U60">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="V60">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="W60">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="X60">
         <v>1</v>
       </c>
       <c r="Y60">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Z60">
-        <v>7.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA60">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AB60">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="AC60">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="AD60">
-        <v>1.94</v>
+        <v>2.14</v>
       </c>
       <c r="AE60">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="AF60">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="AG60">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="AK60">
         <v>1.03</v>
@@ -10261,55 +10261,55 @@
         <v>0</v>
       </c>
       <c r="Q61">
-        <v>1.82</v>
+        <v>1.71</v>
       </c>
       <c r="R61">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="S61">
         <v>1.16</v>
       </c>
       <c r="T61">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="U61">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="V61">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="W61">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X61">
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z61">
-        <v>6.25</v>
+        <v>5.9</v>
       </c>
       <c r="AA61">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB61">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="AC61">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="AD61">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="AE61">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AF61">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG61">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK61">
-        <v>2.74</v>
+        <v>3.25</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10925,7 +10925,7 @@
         <v>3.26</v>
       </c>
       <c r="U65">
-        <v>2.26</v>
+        <v>2.45</v>
       </c>
       <c r="V65">
         <v>1.5</v>
@@ -10943,10 +10943,10 @@
         <v>4.47</v>
       </c>
       <c r="AA65">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AB65">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="AC65">
         <v>2.68</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Tamaraceite</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,37 +11230,37 @@
         </is>
       </c>
       <c r="N67">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O67">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P67">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q67">
-        <v>4.57</v>
+        <v>2.62</v>
       </c>
       <c r="R67">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="S67">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="T67">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="U67">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="V67">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W67">
         <v>1.08</v>
       </c>
       <c r="X67">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y67">
         <v>1.25</v>
@@ -11269,25 +11269,25 @@
         <v>3.28</v>
       </c>
       <c r="AA67">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AB67">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AC67">
-        <v>3.28</v>
+        <v>3.08</v>
       </c>
       <c r="AD67">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE67">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF67">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AG67">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AK67">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>Tamaraceite</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,80 +11393,80 @@
         </is>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O68">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q68">
-        <v>2.92</v>
+        <v>4.2</v>
       </c>
       <c r="R68">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="S68">
+        <v>1.44</v>
+      </c>
+      <c r="T68">
+        <v>2.62</v>
+      </c>
+      <c r="U68">
+        <v>3.1</v>
+      </c>
+      <c r="V68">
+        <v>1.33</v>
+      </c>
+      <c r="W68">
+        <v>1.06</v>
+      </c>
+      <c r="X68">
+        <v>1.04</v>
+      </c>
+      <c r="Y68">
+        <v>1.33</v>
+      </c>
+      <c r="Z68">
+        <v>2.83</v>
+      </c>
+      <c r="AA68">
+        <v>1.95</v>
+      </c>
+      <c r="AB68">
+        <v>1.85</v>
+      </c>
+      <c r="AC68">
+        <v>3.92</v>
+      </c>
+      <c r="AD68">
+        <v>1.18</v>
+      </c>
+      <c r="AE68">
+        <v>1.03</v>
+      </c>
+      <c r="AF68">
+        <v>2</v>
+      </c>
+      <c r="AG68">
+        <v>1.75</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ68">
         <v>1.3</v>
       </c>
-      <c r="T68">
-        <v>3</v>
-      </c>
-      <c r="U68">
-        <v>2.48</v>
-      </c>
-      <c r="V68">
-        <v>1.43</v>
-      </c>
-      <c r="W68">
-        <v>1.08</v>
-      </c>
-      <c r="X68">
-        <v>1.01</v>
-      </c>
-      <c r="Y68">
+      <c r="AK68">
         <v>1.22</v>
-      </c>
-      <c r="Z68">
-        <v>3.5</v>
-      </c>
-      <c r="AA68">
-        <v>1.79</v>
-      </c>
-      <c r="AB68">
-        <v>1.88</v>
-      </c>
-      <c r="AC68">
-        <v>2.92</v>
-      </c>
-      <c r="AD68">
-        <v>1.31</v>
-      </c>
-      <c r="AE68">
-        <v>1.09</v>
-      </c>
-      <c r="AF68">
-        <v>1.64</v>
-      </c>
-      <c r="AG68">
-        <v>2.1</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ68">
-        <v>1.23</v>
-      </c>
-      <c r="AK68">
-        <v>1.48</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -13355,7 +13355,7 @@
         <v>3.18</v>
       </c>
       <c r="P80">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="Q80">
         <v>4.05</v>
@@ -13681,7 +13681,7 @@
         <v>3.4</v>
       </c>
       <c r="P82">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Q82">
         <v>2.49</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.07</v>
+        <v>2.4</v>
       </c>
       <c r="O83">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P83">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="Q83">
-        <v>2.59</v>
+        <v>3.04</v>
       </c>
       <c r="R83">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="S83">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T83">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U83">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="V83">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W83">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X83">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y83">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z83">
-        <v>4.6</v>
+        <v>4.85</v>
       </c>
       <c r="AA83">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="AB83">
-        <v>2.19</v>
+        <v>2.33</v>
       </c>
       <c r="AC83">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AD83">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="AE83">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF83">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AG83">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="AK83">
-        <v>1.73</v>
+        <v>1.48</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="O84">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="P84">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Q84">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="R84">
+        <v>2.22</v>
+      </c>
+      <c r="S84">
+        <v>1.25</v>
+      </c>
+      <c r="T84">
+        <v>3.6</v>
+      </c>
+      <c r="U84">
+        <v>2.25</v>
+      </c>
+      <c r="V84">
+        <v>1.57</v>
+      </c>
+      <c r="W84">
+        <v>1.12</v>
+      </c>
+      <c r="X84">
+        <v>1.03</v>
+      </c>
+      <c r="Y84">
+        <v>1.15</v>
+      </c>
+      <c r="Z84">
+        <v>4.6</v>
+      </c>
+      <c r="AA84">
+        <v>1.58</v>
+      </c>
+      <c r="AB84">
+        <v>2.25</v>
+      </c>
+      <c r="AC84">
         <v>2.38</v>
       </c>
-      <c r="S84">
-        <v>1.22</v>
-      </c>
-      <c r="T84">
-        <v>3.56</v>
-      </c>
-      <c r="U84">
-        <v>2.26</v>
-      </c>
-      <c r="V84">
-        <v>1.63</v>
-      </c>
-      <c r="W84">
-        <v>1.17</v>
-      </c>
-      <c r="X84">
-        <v>1.02</v>
-      </c>
-      <c r="Y84">
-        <v>1.13</v>
-      </c>
-      <c r="Z84">
-        <v>5.25</v>
-      </c>
-      <c r="AA84">
-        <v>1.5</v>
-      </c>
-      <c r="AB84">
-        <v>2.5</v>
-      </c>
-      <c r="AC84">
-        <v>2.3</v>
-      </c>
       <c r="AD84">
-        <v>1.64</v>
+        <v>1.46</v>
       </c>
       <c r="AE84">
         <v>1.22</v>
       </c>
       <c r="AF84">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AG84">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK84">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,31 +14164,31 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.52</v>
+        <v>2.11</v>
       </c>
       <c r="O85">
-        <v>3.62</v>
+        <v>3.58</v>
       </c>
       <c r="P85">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="Q85">
-        <v>3.04</v>
+        <v>2.37</v>
       </c>
       <c r="R85">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="S85">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T85">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U85">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="V85">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W85">
         <v>1.17</v>
@@ -14197,28 +14197,28 @@
         <v>1.02</v>
       </c>
       <c r="Y85">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z85">
-        <v>4.85</v>
+        <v>5.25</v>
       </c>
       <c r="AA85">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AB85">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AC85">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AD85">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="AE85">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF85">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG85">
         <v>2.5</v>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AK85">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14816,19 +14816,19 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="O89">
-        <v>3.92</v>
+        <v>3.63</v>
       </c>
       <c r="P89">
-        <v>4.02</v>
+        <v>3.9</v>
       </c>
       <c r="Q89">
         <v>2.34</v>
       </c>
       <c r="R89">
-        <v>2.44</v>
+        <v>2.18</v>
       </c>
       <c r="S89">
         <v>1.28</v>
@@ -14858,7 +14858,7 @@
         <v>1.7</v>
       </c>
       <c r="AB89">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AC89">
         <v>2.6</v>
@@ -14870,10 +14870,10 @@
         <v>1.13</v>
       </c>
       <c r="AF89">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG89">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AK89">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="O90">
-        <v>5.25</v>
+        <v>5.35</v>
       </c>
       <c r="P90">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="Q90">
         <v>1.73</v>
@@ -15027,7 +15027,7 @@
         <v>2.04</v>
       </c>
       <c r="AD90">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AE90">
         <v>1.32</v>
@@ -15311,13 +15311,13 @@
         <v>5.75</v>
       </c>
       <c r="P92">
-        <v>7</v>
+        <v>7.75</v>
       </c>
       <c r="Q92">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="R92">
-        <v>3.06</v>
+        <v>3.44</v>
       </c>
       <c r="S92">
         <v>1.08</v>
@@ -15344,7 +15344,7 @@
         <v>10.5</v>
       </c>
       <c r="AA92">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AB92">
         <v>4.2</v>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AK92">
-        <v>3.44</v>
+        <v>3.75</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15468,16 +15468,16 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.32</v>
+        <v>1.95</v>
       </c>
       <c r="O93">
-        <v>3.54</v>
+        <v>3.59</v>
       </c>
       <c r="P93">
-        <v>2.93</v>
+        <v>3.8</v>
       </c>
       <c r="Q93">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="R93">
         <v>2.1</v>
@@ -15486,46 +15486,46 @@
         <v>1.36</v>
       </c>
       <c r="T93">
-        <v>2.95</v>
+        <v>2.84</v>
       </c>
       <c r="U93">
         <v>3</v>
       </c>
       <c r="V93">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="W93">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X93">
         <v>1.01</v>
       </c>
       <c r="Y93">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z93">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="AA93">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB93">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC93">
-        <v>3.42</v>
+        <v>3.54</v>
       </c>
       <c r="AD93">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE93">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF93">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AG93">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK93">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15963,7 +15963,7 @@
         <v>3.2</v>
       </c>
       <c r="P96">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="Q96">
         <v>2.9</v>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AK96">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16283,34 +16283,34 @@
         </is>
       </c>
       <c r="N98">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="O98">
         <v>3.7</v>
       </c>
       <c r="P98">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="Q98">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="R98">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="S98">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T98">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="U98">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V98">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W98">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X98">
         <v>1.01</v>
@@ -16337,10 +16337,10 @@
         <v>1.18</v>
       </c>
       <c r="AF98">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AG98">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,7 +16353,7 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK98">
         <v>1.22</v>
@@ -16449,10 +16449,10 @@
         <v>1.28</v>
       </c>
       <c r="O99">
-        <v>5.4</v>
+        <v>5.25</v>
       </c>
       <c r="P99">
-        <v>9.1</v>
+        <v>8.5</v>
       </c>
       <c r="Q99">
         <v>1.72</v>
@@ -16802,13 +16802,13 @@
         <v>1.17</v>
       </c>
       <c r="X101">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y101">
         <v>1.15</v>
       </c>
       <c r="Z101">
-        <v>6</v>
+        <v>5.55</v>
       </c>
       <c r="AA101">
         <v>1.38</v>
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="O110">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="P110">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="Q110">
-        <v>2.02</v>
+        <v>1.89</v>
       </c>
       <c r="R110">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S110">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T110">
-        <v>2.84</v>
+        <v>2.95</v>
       </c>
       <c r="U110">
-        <v>2.58</v>
+        <v>2.51</v>
       </c>
       <c r="V110">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W110">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X110">
         <v>1</v>
       </c>
       <c r="Y110">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z110">
-        <v>3.34</v>
+        <v>3.48</v>
       </c>
       <c r="AA110">
         <v>1.9</v>
       </c>
       <c r="AB110">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AC110">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="AD110">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AE110">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF110">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="AG110">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AK110">
-        <v>2.35</v>
+        <v>2.63</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18402,43 +18402,43 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="O111">
         <v>3.2</v>
       </c>
       <c r="P111">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q111">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="R111">
         <v>2.1</v>
       </c>
       <c r="S111">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="T111">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="U111">
-        <v>2.77</v>
+        <v>2.48</v>
       </c>
       <c r="V111">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="W111">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X111">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y111">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="Z111">
-        <v>3.08</v>
+        <v>3.58</v>
       </c>
       <c r="AA111">
         <v>2.05</v>
@@ -18447,19 +18447,19 @@
         <v>1.75</v>
       </c>
       <c r="AC111">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="AD111">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AE111">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF111">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AG111">
-        <v>1.88</v>
+        <v>2.07</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18574,55 +18574,55 @@
         <v>0</v>
       </c>
       <c r="Q112">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R112">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S112">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T112">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U112">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V112">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W112">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X112">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y112">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z112">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA112">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB112">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC112">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AD112">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE112">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF112">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG112">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK112">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>1.2</v>
+        <v>3.81</v>
       </c>
       <c r="O117">
-        <v>7.5</v>
+        <v>3.93</v>
       </c>
       <c r="P117">
-        <v>12</v>
+        <v>1.68</v>
       </c>
       <c r="Q117">
-        <v>1.51</v>
+        <v>3.85</v>
       </c>
       <c r="R117">
-        <v>3.14</v>
+        <v>2.4</v>
       </c>
       <c r="S117">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T117">
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="U117">
-        <v>1.75</v>
+        <v>2.14</v>
       </c>
       <c r="V117">
-        <v>1.95</v>
+        <v>1.64</v>
       </c>
       <c r="W117">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="X117">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y117">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="Z117">
-        <v>7.7</v>
+        <v>5.46</v>
       </c>
       <c r="AA117">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AB117">
-        <v>3.5</v>
+        <v>2.43</v>
       </c>
       <c r="AC117">
-        <v>1.67</v>
+        <v>2.21</v>
       </c>
       <c r="AD117">
-        <v>2.13</v>
+        <v>1.62</v>
       </c>
       <c r="AE117">
-        <v>1.46</v>
+        <v>1.21</v>
       </c>
       <c r="AF117">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AG117">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="AK117">
-        <v>5</v>
+        <v>1.15</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,64 +19543,64 @@
         </is>
       </c>
       <c r="N118">
-        <v>3.81</v>
+        <v>1.2</v>
       </c>
       <c r="O118">
-        <v>4.15</v>
+        <v>7.5</v>
       </c>
       <c r="P118">
-        <v>1.66</v>
+        <v>12</v>
       </c>
       <c r="Q118">
-        <v>3.85</v>
+        <v>1.51</v>
       </c>
       <c r="R118">
-        <v>2.4</v>
+        <v>3.14</v>
       </c>
       <c r="S118">
+        <v>1.17</v>
+      </c>
+      <c r="T118">
+        <v>5.2</v>
+      </c>
+      <c r="U118">
+        <v>1.75</v>
+      </c>
+      <c r="V118">
+        <v>1.95</v>
+      </c>
+      <c r="W118">
+        <v>1.29</v>
+      </c>
+      <c r="X118">
+        <v>1</v>
+      </c>
+      <c r="Y118">
+        <v>1.02</v>
+      </c>
+      <c r="Z118">
+        <v>7.7</v>
+      </c>
+      <c r="AA118">
         <v>1.22</v>
       </c>
-      <c r="T118">
-        <v>3.9</v>
-      </c>
-      <c r="U118">
-        <v>2.14</v>
-      </c>
-      <c r="V118">
-        <v>1.64</v>
-      </c>
-      <c r="W118">
-        <v>1.14</v>
-      </c>
-      <c r="X118">
-        <v>1.02</v>
-      </c>
-      <c r="Y118">
-        <v>1.1</v>
-      </c>
-      <c r="Z118">
-        <v>5.46</v>
-      </c>
-      <c r="AA118">
-        <v>1.44</v>
-      </c>
       <c r="AB118">
-        <v>2.43</v>
+        <v>3.5</v>
       </c>
       <c r="AC118">
-        <v>2.21</v>
+        <v>1.67</v>
       </c>
       <c r="AD118">
+        <v>2.13</v>
+      </c>
+      <c r="AE118">
+        <v>1.46</v>
+      </c>
+      <c r="AF118">
         <v>1.62</v>
       </c>
-      <c r="AE118">
-        <v>1.21</v>
-      </c>
-      <c r="AF118">
-        <v>1.49</v>
-      </c>
       <c r="AG118">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="AK118">
-        <v>1.15</v>
+        <v>4.06</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -20367,19 +20367,19 @@
         <v>4.2</v>
       </c>
       <c r="Q123">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="R123">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="S123">
         <v>1.4</v>
       </c>
       <c r="T123">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U123">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="V123">
         <v>1.33</v>
@@ -20397,7 +20397,7 @@
         <v>2.78</v>
       </c>
       <c r="AA123">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB123">
         <v>1.6</v>
@@ -20415,7 +20415,7 @@
         <v>1.91</v>
       </c>
       <c r="AG123">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AK123">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20533,16 +20533,16 @@
         <v>4.2</v>
       </c>
       <c r="R124">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="S124">
         <v>1.4</v>
       </c>
       <c r="T124">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U124">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="V124">
         <v>1.33</v>
@@ -20557,7 +20557,7 @@
         <v>1.32</v>
       </c>
       <c r="Z124">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="AA124">
         <v>2.08</v>
@@ -20578,7 +20578,7 @@
         <v>1.85</v>
       </c>
       <c r="AG124">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
+        <v>1.33</v>
+      </c>
+      <c r="AK124">
         <v>1.25</v>
-      </c>
-      <c r="AK124">
-        <v>1.19</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20684,13 +20684,13 @@
         </is>
       </c>
       <c r="N125">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="O125">
         <v>3.1</v>
       </c>
       <c r="P125">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="Q125">
         <v>3.74</v>
@@ -20847,16 +20847,16 @@
         </is>
       </c>
       <c r="N126">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="O126">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="P126">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="Q126">
-        <v>3.26</v>
+        <v>3.38</v>
       </c>
       <c r="R126">
         <v>2.23</v>
@@ -20865,10 +20865,10 @@
         <v>1.36</v>
       </c>
       <c r="T126">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="U126">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="V126">
         <v>1.4</v>
@@ -20877,7 +20877,7 @@
         <v>1.08</v>
       </c>
       <c r="X126">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y126">
         <v>1.22</v>
@@ -20901,10 +20901,10 @@
         <v>1.08</v>
       </c>
       <c r="AF126">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AG126">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,7 +20917,7 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK126">
         <v>1.44</v>
@@ -21010,10 +21010,10 @@
         </is>
       </c>
       <c r="N127">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="O127">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P127">
         <v>2.25</v>
@@ -21043,16 +21043,16 @@
         <v>1.01</v>
       </c>
       <c r="Y127">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z127">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AA127">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AB127">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AC127">
         <v>3.08</v>
@@ -21061,7 +21061,7 @@
         <v>1.28</v>
       </c>
       <c r="AE127">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF127">
         <v>1.73</v>
@@ -21080,7 +21080,7 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK127">
         <v>1.36</v>
@@ -21173,10 +21173,10 @@
         </is>
       </c>
       <c r="N128">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="O128">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P128">
         <v>6.5</v>
@@ -21185,13 +21185,13 @@
         <v>1.91</v>
       </c>
       <c r="R128">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="S128">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T128">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="U128">
         <v>2.4</v>
@@ -21203,34 +21203,34 @@
         <v>1.08</v>
       </c>
       <c r="X128">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y128">
         <v>1.18</v>
       </c>
       <c r="Z128">
-        <v>3.88</v>
+        <v>3.84</v>
       </c>
       <c r="AA128">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AB128">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="AC128">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AD128">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE128">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF128">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AG128">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AK128">
-        <v>2.67</v>
+        <v>2.56</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21505,7 +21505,7 @@
         <v>3.9</v>
       </c>
       <c r="P130">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q130">
         <v>2.21</v>
@@ -21541,7 +21541,7 @@
         <v>1.57</v>
       </c>
       <c r="AB130">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="AC130">
         <v>2.4</v>
@@ -21662,16 +21662,16 @@
         </is>
       </c>
       <c r="N131">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="O131">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P131">
         <v>3.9</v>
       </c>
       <c r="Q131">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
       <c r="R131">
         <v>1.95</v>
@@ -21701,7 +21701,7 @@
         <v>2.53</v>
       </c>
       <c r="AA131">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AB131">
         <v>1.5</v>
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
-        <v>4.14</v>
+        <v>3.76</v>
       </c>
       <c r="O132">
-        <v>3.93</v>
+        <v>3.82</v>
       </c>
       <c r="P132">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="Q132">
-        <v>4.25</v>
+        <v>4.05</v>
       </c>
       <c r="R132">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="S132">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T132">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="U132">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="V132">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="W132">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X132">
         <v>1.01</v>
       </c>
       <c r="Y132">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z132">
-        <v>4.25</v>
+        <v>4.6</v>
       </c>
       <c r="AA132">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AB132">
         <v>2.15</v>
       </c>
       <c r="AC132">
-        <v>2.49</v>
+        <v>2.27</v>
       </c>
       <c r="AD132">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AE132">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AF132">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="AG132">
-        <v>2.21</v>
+        <v>2.38</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK132">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -22151,7 +22151,7 @@
         </is>
       </c>
       <c r="N134">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="O134">
         <v>3.15</v>
@@ -22160,55 +22160,55 @@
         <v>2.9</v>
       </c>
       <c r="Q134">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R134">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S134">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T134">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U134">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="V134">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W134">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X134">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y134">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z134">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA134">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB134">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC134">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD134">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE134">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF134">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG134">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK134">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22353,13 +22353,13 @@
         <v>4.6</v>
       </c>
       <c r="AA135">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AB135">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AC135">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="AD135">
         <v>1.47</v>
@@ -22812,37 +22812,37 @@
         <v>1.65</v>
       </c>
       <c r="Q138">
-        <v>5.27</v>
+        <v>5.22</v>
       </c>
       <c r="R138">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="S138">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="T138">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="U138">
-        <v>2.86</v>
+        <v>3.15</v>
       </c>
       <c r="V138">
         <v>1.33</v>
       </c>
       <c r="W138">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X138">
         <v>1</v>
       </c>
       <c r="Y138">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="Z138">
-        <v>2.92</v>
+        <v>3.04</v>
       </c>
       <c r="AA138">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AB138">
         <v>1.65</v>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK138">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -23790,22 +23790,22 @@
         <v>5.75</v>
       </c>
       <c r="Q144">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="R144">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="S144">
         <v>1.3</v>
       </c>
       <c r="T144">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="U144">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="V144">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W144">
         <v>1.11</v>
@@ -23814,31 +23814,31 @@
         <v>1.01</v>
       </c>
       <c r="Y144">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z144">
-        <v>3.75</v>
+        <v>3.68</v>
       </c>
       <c r="AA144">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AB144">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="AC144">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AD144">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE144">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF144">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG144">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK144">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -24270,13 +24270,13 @@
         </is>
       </c>
       <c r="N147">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="O147">
         <v>3.64</v>
       </c>
       <c r="P147">
-        <v>4.35</v>
+        <v>4.85</v>
       </c>
       <c r="Q147">
         <v>2.39</v>
@@ -24759,13 +24759,13 @@
         </is>
       </c>
       <c r="N150">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="O150">
-        <v>3.73</v>
+        <v>3.7</v>
       </c>
       <c r="P150">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="Q150">
         <v>2.97</v>
@@ -26914,10 +26914,10 @@
         <v>1.19</v>
       </c>
       <c r="Z163">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AA163">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AB163">
         <v>2.27</v>
@@ -27041,64 +27041,64 @@
         </is>
       </c>
       <c r="N164">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="O164">
-        <v>3.48</v>
+        <v>3.66</v>
       </c>
       <c r="P164">
-        <v>3.31</v>
+        <v>3.92</v>
       </c>
       <c r="Q164">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="R164">
         <v>2.1</v>
       </c>
       <c r="S164">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T164">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="U164">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V164">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="W164">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X164">
         <v>1.01</v>
       </c>
       <c r="Y164">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="Z164">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="AA164">
         <v>1.95</v>
       </c>
       <c r="AB164">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AC164">
-        <v>3.3</v>
+        <v>3.06</v>
       </c>
       <c r="AD164">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE164">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF164">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG164">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="AH164" t="inlineStr">
         <is>
@@ -27111,10 +27111,10 @@
         </is>
       </c>
       <c r="AJ164">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK164">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AL164">
         <v>0</v>
@@ -28255,7 +28255,7 @@
         <v>1.11</v>
       </c>
       <c r="AK171">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AL171">
         <v>0</v>
@@ -28834,7 +28834,7 @@
         </is>
       </c>
       <c r="N175">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="O175">
         <v>3.4</v>
@@ -28843,7 +28843,7 @@
         <v>1.95</v>
       </c>
       <c r="Q175">
-        <v>3.72</v>
+        <v>3.91</v>
       </c>
       <c r="R175">
         <v>2.1</v>
@@ -31125,7 +31125,7 @@
         <v>2.5</v>
       </c>
       <c r="Q189">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="R189">
         <v>2.25</v>
@@ -31158,7 +31158,7 @@
         <v>1.75</v>
       </c>
       <c r="AB189">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AC189">
         <v>2.83</v>
@@ -31512,7 +31512,7 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AK191">
         <v>1.49</v>
@@ -31605,13 +31605,13 @@
         </is>
       </c>
       <c r="N192">
-        <v>9.25</v>
+        <v>9</v>
       </c>
       <c r="O192">
         <v>7.1</v>
       </c>
       <c r="P192">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Q192">
         <v>6.38</v>
@@ -31623,7 +31623,7 @@
         <v>1.12</v>
       </c>
       <c r="T192">
-        <v>5.55</v>
+        <v>5</v>
       </c>
       <c r="U192">
         <v>1.71</v>
@@ -31644,7 +31644,7 @@
         <v>9</v>
       </c>
       <c r="AA192">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AB192">
         <v>4.5</v>
@@ -31940,40 +31940,40 @@
         <v>2</v>
       </c>
       <c r="Q194">
-        <v>4.37</v>
+        <v>4.6</v>
       </c>
       <c r="R194">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="S194">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T194">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="U194">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="V194">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W194">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X194">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y194">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z194">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AA194">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AB194">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AC194">
         <v>3.58</v>
@@ -31982,13 +31982,13 @@
         <v>1.21</v>
       </c>
       <c r="AE194">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF194">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AG194">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AH194" t="inlineStr">
         <is>
@@ -32001,10 +32001,10 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK194">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32103,34 +32103,34 @@
         <v>4.1</v>
       </c>
       <c r="Q195">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="R195">
         <v>2.25</v>
       </c>
       <c r="S195">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="T195">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="U195">
-        <v>2.34</v>
+        <v>2.55</v>
       </c>
       <c r="V195">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W195">
         <v>1.1</v>
       </c>
       <c r="X195">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y195">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z195">
-        <v>3.94</v>
+        <v>4.1</v>
       </c>
       <c r="AA195">
         <v>1.7</v>
@@ -32139,19 +32139,19 @@
         <v>2.1</v>
       </c>
       <c r="AC195">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AD195">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AE195">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF195">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG195">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK195">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32260,16 +32260,16 @@
         <v>1.58</v>
       </c>
       <c r="O196">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="P196">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Q196">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R196">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="S196">
         <v>1.22</v>
@@ -32296,7 +32296,7 @@
         <v>5.5</v>
       </c>
       <c r="AA196">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB196">
         <v>2.7</v>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AK196">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32450,7 +32450,7 @@
         <v>1.17</v>
       </c>
       <c r="X197">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y197">
         <v>1.13</v>
@@ -32459,10 +32459,10 @@
         <v>5</v>
       </c>
       <c r="AA197">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AB197">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AC197">
         <v>2.2</v>
@@ -32803,7 +32803,7 @@
         <v>1.42</v>
       </c>
       <c r="AG199">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AH199" t="inlineStr">
         <is>
@@ -32909,19 +32909,19 @@
         </is>
       </c>
       <c r="N200">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="O200">
-        <v>4.15</v>
+        <v>3.8</v>
       </c>
       <c r="P200">
-        <v>4.11</v>
+        <v>3.8</v>
       </c>
       <c r="Q200">
         <v>2.1</v>
       </c>
       <c r="R200">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="S200">
         <v>1.22</v>
@@ -32957,13 +32957,13 @@
         <v>2.17</v>
       </c>
       <c r="AD200">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AE200">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AF200">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AG200">
         <v>2.5</v>
@@ -33075,7 +33075,7 @@
         <v>1.39</v>
       </c>
       <c r="O201">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="P201">
         <v>6.5</v>
@@ -33084,52 +33084,52 @@
         <v>1.84</v>
       </c>
       <c r="R201">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="S201">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T201">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="U201">
-        <v>2.31</v>
+        <v>2.23</v>
       </c>
       <c r="V201">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="W201">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X201">
         <v>1.01</v>
       </c>
       <c r="Y201">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z201">
-        <v>4.55</v>
+        <v>4.8</v>
       </c>
       <c r="AA201">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AB201">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AC201">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AD201">
-        <v>1.49</v>
+        <v>1.59</v>
       </c>
       <c r="AE201">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF201">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AG201">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="AH201" t="inlineStr">
         <is>
@@ -33145,7 +33145,7 @@
         <v>1.16</v>
       </c>
       <c r="AK201">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="AL201">
         <v>0</v>
@@ -33235,13 +33235,13 @@
         </is>
       </c>
       <c r="N202">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="O202">
         <v>3.62</v>
       </c>
       <c r="P202">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="Q202">
         <v>2.45</v>
@@ -33289,10 +33289,10 @@
         <v>1.11</v>
       </c>
       <c r="AF202">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AG202">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AH202" t="inlineStr">
         <is>
@@ -33398,13 +33398,13 @@
         </is>
       </c>
       <c r="N203">
-        <v>3.64</v>
+        <v>4.35</v>
       </c>
       <c r="O203">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P203">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="Q203">
         <v>0</v>
@@ -33561,13 +33561,13 @@
         </is>
       </c>
       <c r="N204">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="O204">
         <v>3.7</v>
       </c>
       <c r="P204">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="Q204">
         <v>2.3</v>
@@ -33606,10 +33606,10 @@
         <v>1.98</v>
       </c>
       <c r="AC204">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="AD204">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AE204">
         <v>1.11</v>
@@ -35028,7 +35028,7 @@
         </is>
       </c>
       <c r="N213">
-        <v>5.05</v>
+        <v>4.85</v>
       </c>
       <c r="O213">
         <v>4.2</v>
@@ -35067,10 +35067,10 @@
         <v>4.33</v>
       </c>
       <c r="AA213">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AB213">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AC213">
         <v>2.69</v>
@@ -35357,61 +35357,61 @@
         <v>1.11</v>
       </c>
       <c r="O215">
-        <v>8.65</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="P215">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="Q215">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="R215">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="S215">
+        <v>1.14</v>
+      </c>
+      <c r="T215">
+        <v>4.33</v>
+      </c>
+      <c r="U215">
+        <v>1.87</v>
+      </c>
+      <c r="V215">
+        <v>1.8</v>
+      </c>
+      <c r="W215">
         <v>1.21</v>
-      </c>
-      <c r="T215">
-        <v>3.6</v>
-      </c>
-      <c r="U215">
-        <v>2.02</v>
-      </c>
-      <c r="V215">
-        <v>1.68</v>
-      </c>
-      <c r="W215">
-        <v>1.16</v>
       </c>
       <c r="X215">
         <v>1.01</v>
       </c>
       <c r="Y215">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="Z215">
-        <v>6.97</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA215">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AB215">
-        <v>2.81</v>
+        <v>3.42</v>
       </c>
       <c r="AC215">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="AD215">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="AE215">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AF215">
-        <v>2.14</v>
+        <v>1.87</v>
       </c>
       <c r="AG215">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="AH215" t="inlineStr">
         <is>
@@ -35424,10 +35424,10 @@
         </is>
       </c>
       <c r="AJ215">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AK215">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="AL215">
         <v>0</v>
@@ -35692,52 +35692,52 @@
         <v>2.4</v>
       </c>
       <c r="R217">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="S217">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="T217">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="U217">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="V217">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W217">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X217">
         <v>1.04</v>
       </c>
       <c r="Y217">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="Z217">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="AA217">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AB217">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC217">
-        <v>3.88</v>
+        <v>4.1</v>
       </c>
       <c r="AD217">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AE217">
         <v>1.03</v>
       </c>
       <c r="AF217">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AG217">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AH217" t="inlineStr">
         <is>
@@ -35750,10 +35750,10 @@
         </is>
       </c>
       <c r="AJ217">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AK217">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AL217">
         <v>0</v>
@@ -35852,34 +35852,34 @@
         <v>3.02</v>
       </c>
       <c r="Q218">
+        <v>2.7</v>
+      </c>
+      <c r="R218">
+        <v>2</v>
+      </c>
+      <c r="S218">
+        <v>1.4</v>
+      </c>
+      <c r="T218">
         <v>2.75</v>
-      </c>
-      <c r="R218">
-        <v>2.05</v>
-      </c>
-      <c r="S218">
-        <v>1.36</v>
-      </c>
-      <c r="T218">
-        <v>2.73</v>
       </c>
       <c r="U218">
         <v>3</v>
       </c>
       <c r="V218">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W218">
         <v>1.06</v>
       </c>
       <c r="X218">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y218">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z218">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AA218">
         <v>2.05</v>
@@ -35897,10 +35897,10 @@
         <v>1.05</v>
       </c>
       <c r="AF218">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AG218">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AH218" t="inlineStr">
         <is>
@@ -35913,10 +35913,10 @@
         </is>
       </c>
       <c r="AJ218">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK218">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL218">
         <v>0</v>
@@ -36658,7 +36658,7 @@
         </is>
       </c>
       <c r="N223">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="O223">
         <v>3.4</v>
@@ -36703,7 +36703,7 @@
         <v>1.76</v>
       </c>
       <c r="AC223">
-        <v>3.52</v>
+        <v>3.47</v>
       </c>
       <c r="AD223">
         <v>1.26</v>
@@ -36993,55 +36993,55 @@
         <v>5.62</v>
       </c>
       <c r="Q225">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="R225">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="S225">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T225">
-        <v>2.69</v>
+        <v>2.61</v>
       </c>
       <c r="U225">
-        <v>2.73</v>
+        <v>2.81</v>
       </c>
       <c r="V225">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W225">
         <v>1.05</v>
       </c>
       <c r="X225">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y225">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z225">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="AA225">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="AB225">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AC225">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="AD225">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AE225">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF225">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AG225">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AH225" t="inlineStr">
         <is>
@@ -37054,10 +37054,10 @@
         </is>
       </c>
       <c r="AJ225">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK225">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AL225">
         <v>0</v>
@@ -37156,34 +37156,34 @@
         <v>6</v>
       </c>
       <c r="Q226">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="R226">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="S226">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="T226">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="U226">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="V226">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="W226">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X226">
         <v>1.01</v>
       </c>
       <c r="Y226">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z226">
-        <v>3.82</v>
+        <v>3.48</v>
       </c>
       <c r="AA226">
         <v>1.75</v>
@@ -37192,19 +37192,19 @@
         <v>2.05</v>
       </c>
       <c r="AC226">
-        <v>2.69</v>
+        <v>2.92</v>
       </c>
       <c r="AD226">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AE226">
         <v>1.11</v>
       </c>
       <c r="AF226">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AG226">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AH226" t="inlineStr">
         <is>
@@ -37217,10 +37217,10 @@
         </is>
       </c>
       <c r="AJ226">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AK226">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="AL226">
         <v>0</v>
@@ -37319,55 +37319,55 @@
         <v>1.85</v>
       </c>
       <c r="Q227">
-        <v>3.98</v>
+        <v>3.3</v>
       </c>
       <c r="R227">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="S227">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="T227">
-        <v>3.46</v>
+        <v>3.1</v>
       </c>
       <c r="U227">
-        <v>2.19</v>
+        <v>2.5</v>
       </c>
       <c r="V227">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="W227">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X227">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y227">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="Z227">
-        <v>4.4</v>
+        <v>3.58</v>
       </c>
       <c r="AA227">
-        <v>1.56</v>
+        <v>1.74</v>
       </c>
       <c r="AB227">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AC227">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="AD227">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="AE227">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AF227">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="AG227">
-        <v>2.34</v>
+        <v>2.1</v>
       </c>
       <c r="AH227" t="inlineStr">
         <is>
@@ -37380,10 +37380,10 @@
         </is>
       </c>
       <c r="AJ227">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AK227">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AL227">
         <v>0</v>
@@ -37482,55 +37482,55 @@
         <v>0</v>
       </c>
       <c r="Q228">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="R228">
         <v>2.1</v>
       </c>
       <c r="S228">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T228">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="U228">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="V228">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="W228">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X228">
         <v>1.01</v>
       </c>
       <c r="Y228">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z228">
-        <v>3.28</v>
+        <v>3.04</v>
       </c>
       <c r="AA228">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AB228">
         <v>1.9</v>
       </c>
       <c r="AC228">
-        <v>3.04</v>
+        <v>3.28</v>
       </c>
       <c r="AD228">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE228">
         <v>1.08</v>
       </c>
       <c r="AF228">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="AG228">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="AH228" t="inlineStr">
         <is>
@@ -37543,10 +37543,10 @@
         </is>
       </c>
       <c r="AJ228">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AK228">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL228">
         <v>0</v>
@@ -37645,34 +37645,34 @@
         <v>0</v>
       </c>
       <c r="Q229">
-        <v>2.79</v>
+        <v>2.62</v>
       </c>
       <c r="R229">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="S229">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="T229">
-        <v>3.18</v>
+        <v>2.9</v>
       </c>
       <c r="U229">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="V229">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="W229">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X229">
         <v>1.01</v>
       </c>
       <c r="Y229">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="Z229">
-        <v>3.86</v>
+        <v>3.34</v>
       </c>
       <c r="AA229">
         <v>1.75</v>
@@ -37681,19 +37681,19 @@
         <v>2.05</v>
       </c>
       <c r="AC229">
-        <v>2.74</v>
+        <v>3.08</v>
       </c>
       <c r="AD229">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AE229">
         <v>1.09</v>
       </c>
       <c r="AF229">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="AG229">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="AH229" t="inlineStr">
         <is>
@@ -37706,10 +37706,10 @@
         </is>
       </c>
       <c r="AJ229">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK229">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AL229">
         <v>0</v>
@@ -37805,7 +37805,7 @@
         <v>3.8</v>
       </c>
       <c r="P230">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="Q230">
         <v>3.9</v>
@@ -40117,7 +40117,7 @@
         <v>1.16</v>
       </c>
       <c r="Z244">
-        <v>4.18</v>
+        <v>4.25</v>
       </c>
       <c r="AA244">
         <v>1.64</v>
@@ -40132,7 +40132,7 @@
         <v>1.43</v>
       </c>
       <c r="AE244">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF244">
         <v>1.7</v>
@@ -40250,7 +40250,7 @@
         <v>3.5</v>
       </c>
       <c r="P245">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="Q245">
         <v>2.7</v>
@@ -40422,7 +40422,7 @@
         <v>2.46</v>
       </c>
       <c r="S246">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T246">
         <v>3.5</v>
@@ -40434,7 +40434,7 @@
         <v>1.59</v>
       </c>
       <c r="W246">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X246">
         <v>1</v>
@@ -40570,16 +40570,16 @@
         </is>
       </c>
       <c r="N247">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="O247">
         <v>3.3</v>
       </c>
       <c r="P247">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q247">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="R247">
         <v>2.2</v>
@@ -40591,43 +40591,43 @@
         <v>3</v>
       </c>
       <c r="U247">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="V247">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W247">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X247">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y247">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="Z247">
-        <v>3.42</v>
+        <v>3.82</v>
       </c>
       <c r="AA247">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="AB247">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="AC247">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="AD247">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AE247">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF247">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="AG247">
-        <v>2.02</v>
+        <v>2.17</v>
       </c>
       <c r="AH247" t="inlineStr">
         <is>
@@ -40640,10 +40640,10 @@
         </is>
       </c>
       <c r="AJ247">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK247">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AL247">
         <v>0</v>
@@ -40739,37 +40739,37 @@
         <v>3.25</v>
       </c>
       <c r="P248">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q248">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="R248">
         <v>1.94</v>
       </c>
       <c r="S248">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T248">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="U248">
-        <v>3.06</v>
+        <v>2.95</v>
       </c>
       <c r="V248">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W248">
+        <v>1.03</v>
+      </c>
+      <c r="X248">
         <v>1.02</v>
       </c>
-      <c r="X248">
-        <v>1.03</v>
-      </c>
       <c r="Y248">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="Z248">
-        <v>2.66</v>
+        <v>2.81</v>
       </c>
       <c r="AA248">
         <v>2.35</v>
@@ -40778,19 +40778,19 @@
         <v>1.57</v>
       </c>
       <c r="AC248">
-        <v>4.25</v>
+        <v>3.9</v>
       </c>
       <c r="AD248">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AE248">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF248">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="AG248">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="AH248" t="inlineStr">
         <is>
@@ -40803,10 +40803,10 @@
         </is>
       </c>
       <c r="AJ248">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AK248">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AL248">
         <v>0</v>
@@ -40896,43 +40896,43 @@
         </is>
       </c>
       <c r="N249">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="O249">
         <v>3.4</v>
       </c>
       <c r="P249">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="Q249">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="R249">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="S249">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T249">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U249">
-        <v>2.48</v>
+        <v>2.34</v>
       </c>
       <c r="V249">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="W249">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X249">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y249">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="Z249">
-        <v>3.42</v>
+        <v>3.76</v>
       </c>
       <c r="AA249">
         <v>1.85</v>
@@ -40941,19 +40941,19 @@
         <v>1.95</v>
       </c>
       <c r="AC249">
-        <v>2.92</v>
+        <v>2.66</v>
       </c>
       <c r="AD249">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AE249">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF249">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AG249">
-        <v>1.92</v>
+        <v>2.09</v>
       </c>
       <c r="AH249" t="inlineStr">
         <is>
@@ -40966,10 +40966,10 @@
         </is>
       </c>
       <c r="AJ249">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK249">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="AL249">
         <v>0</v>
@@ -41059,13 +41059,13 @@
         </is>
       </c>
       <c r="N250">
-        <v>2.7</v>
+        <v>3.09</v>
       </c>
       <c r="O250">
         <v>3.4</v>
       </c>
       <c r="P250">
-        <v>2.18</v>
+        <v>2.27</v>
       </c>
       <c r="Q250">
         <v>3.31</v>
@@ -41228,58 +41228,58 @@
         <v>4.33</v>
       </c>
       <c r="P251">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="Q251">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="R251">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S251">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T251">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U251">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V251">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W251">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X251">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y251">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z251">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA251">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB251">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC251">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD251">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE251">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF251">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG251">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH251" t="inlineStr">
         <is>
@@ -41292,10 +41292,10 @@
         </is>
       </c>
       <c r="AJ251">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK251">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AL251">
         <v>0</v>
@@ -41516,12 +41516,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Cieza</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G253">
@@ -41548,31 +41548,31 @@
         </is>
       </c>
       <c r="N253">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="O253">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="P253">
-        <v>3.32</v>
+        <v>3.09</v>
       </c>
       <c r="Q253">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="R253">
         <v>2.1</v>
       </c>
       <c r="S253">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T253">
-        <v>2.88</v>
+        <v>2.61</v>
       </c>
       <c r="U253">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V253">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W253">
         <v>1.06</v>
@@ -41581,31 +41581,31 @@
         <v>1.02</v>
       </c>
       <c r="Y253">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Z253">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="AA253">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AB253">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AC253">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AD253">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE253">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF253">
         <v>1.83</v>
       </c>
       <c r="AG253">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AH253" t="inlineStr">
         <is>
@@ -41618,10 +41618,10 @@
         </is>
       </c>
       <c r="AJ253">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK253">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL253">
         <v>0</v>
@@ -41679,12 +41679,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Cieza</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G254">
@@ -41711,31 +41711,31 @@
         </is>
       </c>
       <c r="N254">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="O254">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="P254">
-        <v>3.09</v>
+        <v>3.32</v>
       </c>
       <c r="Q254">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="R254">
         <v>2.1</v>
       </c>
       <c r="S254">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T254">
-        <v>2.61</v>
+        <v>2.88</v>
       </c>
       <c r="U254">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="V254">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W254">
         <v>1.06</v>
@@ -41744,31 +41744,31 @@
         <v>1.02</v>
       </c>
       <c r="Y254">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z254">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="AA254">
+        <v>1.96</v>
+      </c>
+      <c r="AB254">
         <v>2</v>
       </c>
-      <c r="AB254">
-        <v>1.8</v>
-      </c>
       <c r="AC254">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AD254">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE254">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF254">
         <v>1.83</v>
       </c>
       <c r="AG254">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AH254" t="inlineStr">
         <is>
@@ -41781,10 +41781,10 @@
         </is>
       </c>
       <c r="AJ254">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK254">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AL254">
         <v>0</v>
@@ -41883,28 +41883,28 @@
         <v>2.45</v>
       </c>
       <c r="Q255">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="R255">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="S255">
         <v>1.33</v>
       </c>
       <c r="T255">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="U255">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="V255">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W255">
         <v>1.07</v>
       </c>
       <c r="X255">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y255">
         <v>1.24</v>
@@ -41916,22 +41916,22 @@
         <v>1.83</v>
       </c>
       <c r="AB255">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AC255">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="AD255">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE255">
         <v>1.07</v>
       </c>
       <c r="AF255">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AG255">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AH255" t="inlineStr">
         <is>
@@ -41944,10 +41944,10 @@
         </is>
       </c>
       <c r="AJ255">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK255">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AL255">
         <v>0</v>
@@ -42200,7 +42200,7 @@
         </is>
       </c>
       <c r="N257">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="O257">
         <v>4.5</v>
@@ -42270,7 +42270,7 @@
         </is>
       </c>
       <c r="AJ257">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AK257">
         <v>2.32</v>
@@ -42366,7 +42366,7 @@
         <v>4</v>
       </c>
       <c r="O258">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="P258">
         <v>1.6</v>
@@ -42562,7 +42562,7 @@
         <v>1.18</v>
       </c>
       <c r="Z259">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AA259">
         <v>1.68</v>
@@ -42571,19 +42571,19 @@
         <v>2.2</v>
       </c>
       <c r="AC259">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AD259">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE259">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF259">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG259">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH259" t="inlineStr">
         <is>
@@ -42704,49 +42704,49 @@
         <v>2.1</v>
       </c>
       <c r="S260">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="T260">
-        <v>2.84</v>
+        <v>2.61</v>
       </c>
       <c r="U260">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="V260">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="W260">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X260">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y260">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="Z260">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="AA260">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB260">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AC260">
-        <v>3.34</v>
+        <v>3.75</v>
       </c>
       <c r="AD260">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AE260">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF260">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AG260">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AH260" t="inlineStr">
         <is>
@@ -42759,10 +42759,10 @@
         </is>
       </c>
       <c r="AJ260">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK260">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AL260">
         <v>0</v>
@@ -42855,10 +42855,10 @@
         <v>1.28</v>
       </c>
       <c r="O261">
-        <v>5.35</v>
+        <v>5.5</v>
       </c>
       <c r="P261">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="Q261">
         <v>1.67</v>
@@ -43030,19 +43030,19 @@
         <v>2.2</v>
       </c>
       <c r="S262">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T262">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U262">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="V262">
         <v>1.44</v>
       </c>
       <c r="W262">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X262">
         <v>1.01</v>
@@ -43513,16 +43513,16 @@
         <v>1.7</v>
       </c>
       <c r="Q265">
-        <v>6.35</v>
+        <v>5.13</v>
       </c>
       <c r="R265">
-        <v>2.16</v>
+        <v>2.07</v>
       </c>
       <c r="S265">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T265">
-        <v>2.96</v>
+        <v>2.83</v>
       </c>
       <c r="U265">
         <v>2.75</v>
@@ -43531,37 +43531,37 @@
         <v>1.4</v>
       </c>
       <c r="W265">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X265">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y265">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z265">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AA265">
         <v>1.85</v>
       </c>
       <c r="AB265">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AC265">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="AD265">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AE265">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF265">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AG265">
-        <v>1.77</v>
+        <v>1.88</v>
       </c>
       <c r="AH265" t="inlineStr">
         <is>
@@ -43574,10 +43574,10 @@
         </is>
       </c>
       <c r="AJ265">
-        <v>2.38</v>
+        <v>1.91</v>
       </c>
       <c r="AK265">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="AL265">
         <v>0</v>
@@ -44023,7 +44023,7 @@
         <v>1.15</v>
       </c>
       <c r="X268">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y268">
         <v>1.14</v>
@@ -44162,10 +44162,10 @@
         <v>3.3</v>
       </c>
       <c r="P269">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="Q269">
-        <v>3.75</v>
+        <v>3.44</v>
       </c>
       <c r="R269">
         <v>2.09</v>
@@ -44198,7 +44198,7 @@
         <v>1.76</v>
       </c>
       <c r="AB269">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AC269">
         <v>3.08</v>
@@ -44325,13 +44325,13 @@
         <v>3.2</v>
       </c>
       <c r="P270">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="Q270">
         <v>2.62</v>
       </c>
       <c r="R270">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="S270">
         <v>1.32</v>
@@ -44389,7 +44389,7 @@
         </is>
       </c>
       <c r="AJ270">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AK270">
         <v>1.62</v>
@@ -44527,7 +44527,7 @@
         <v>1.89</v>
       </c>
       <c r="AC271">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="AD271">
         <v>1.33</v>
@@ -44536,7 +44536,7 @@
         <v>1.07</v>
       </c>
       <c r="AF271">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG271">
         <v>2.05</v>
@@ -44555,7 +44555,7 @@
         <v>1.29</v>
       </c>
       <c r="AK271">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AL271">
         <v>0</v>
@@ -44645,7 +44645,7 @@
         </is>
       </c>
       <c r="N272">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="O272">
         <v>3.48</v>
@@ -44817,34 +44817,34 @@
         <v>0</v>
       </c>
       <c r="Q273">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="R273">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="S273">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T273">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="U273">
-        <v>2.51</v>
+        <v>2.9</v>
       </c>
       <c r="V273">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W273">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X273">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y273">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Z273">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="AA273">
         <v>1.85</v>
@@ -44853,35 +44853,35 @@
         <v>1.95</v>
       </c>
       <c r="AC273">
-        <v>2.97</v>
+        <v>3.5</v>
       </c>
       <c r="AD273">
+        <v>1.22</v>
+      </c>
+      <c r="AE273">
+        <v>1.05</v>
+      </c>
+      <c r="AF273">
+        <v>1.85</v>
+      </c>
+      <c r="AG273">
+        <v>1.85</v>
+      </c>
+      <c r="AH273" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI273" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ273">
         <v>1.3</v>
       </c>
-      <c r="AE273">
-        <v>1.07</v>
-      </c>
-      <c r="AF273">
-        <v>1.67</v>
-      </c>
-      <c r="AG273">
-        <v>2.06</v>
-      </c>
-      <c r="AH273" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI273" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ273">
-        <v>1.22</v>
-      </c>
       <c r="AK273">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AL273">
         <v>0</v>
@@ -45143,34 +45143,34 @@
         <v>3.3</v>
       </c>
       <c r="Q275">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="R275">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S275">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T275">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="U275">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="V275">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W275">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X275">
         <v>1.01</v>
       </c>
       <c r="Y275">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z275">
-        <v>3.28</v>
+        <v>3.05</v>
       </c>
       <c r="AA275">
         <v>1.95</v>
@@ -45179,19 +45179,19 @@
         <v>1.85</v>
       </c>
       <c r="AC275">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AD275">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE275">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF275">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AG275">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AH275" t="inlineStr">
         <is>
@@ -45204,10 +45204,10 @@
         </is>
       </c>
       <c r="AJ275">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AK275">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL275">
         <v>0</v>
@@ -45306,55 +45306,55 @@
         <v>0</v>
       </c>
       <c r="Q276">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="R276">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S276">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T276">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U276">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="V276">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W276">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X276">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y276">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z276">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA276">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB276">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC276">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AD276">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE276">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF276">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG276">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AH276" t="inlineStr">
         <is>
@@ -45367,10 +45367,10 @@
         </is>
       </c>
       <c r="AJ276">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK276">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AL276">
         <v>0</v>
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G278">
@@ -45632,71 +45632,71 @@
         <v>0</v>
       </c>
       <c r="Q278">
-        <v>4.75</v>
+        <v>2.8</v>
       </c>
       <c r="R278">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="S278">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="T278">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="U278">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="V278">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="W278">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X278">
+        <v>1.05</v>
+      </c>
+      <c r="Y278">
+        <v>1.47</v>
+      </c>
+      <c r="Z278">
+        <v>2.53</v>
+      </c>
+      <c r="AA278">
+        <v>2.4</v>
+      </c>
+      <c r="AB278">
+        <v>1.53</v>
+      </c>
+      <c r="AC278">
+        <v>4.7</v>
+      </c>
+      <c r="AD278">
+        <v>1.12</v>
+      </c>
+      <c r="AE278">
         <v>1.03</v>
       </c>
-      <c r="Y278">
+      <c r="AF278">
+        <v>1.95</v>
+      </c>
+      <c r="AG278">
+        <v>1.73</v>
+      </c>
+      <c r="AH278" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI278" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ278">
         <v>1.36</v>
       </c>
-      <c r="Z278">
-        <v>2.7</v>
-      </c>
-      <c r="AA278">
-        <v>2.3</v>
-      </c>
-      <c r="AB278">
-        <v>1.6</v>
-      </c>
-      <c r="AC278">
-        <v>3.98</v>
-      </c>
-      <c r="AD278">
-        <v>1.17</v>
-      </c>
-      <c r="AE278">
-        <v>1.02</v>
-      </c>
-      <c r="AF278">
-        <v>2.01</v>
-      </c>
-      <c r="AG278">
-        <v>1.7</v>
-      </c>
-      <c r="AH278" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI278" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ278">
-        <v>1.3</v>
-      </c>
       <c r="AK278">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
       <c r="AL278">
         <v>0</v>
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G279">
@@ -45795,22 +45795,22 @@
         <v>0</v>
       </c>
       <c r="Q279">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="R279">
         <v>1.95</v>
       </c>
       <c r="S279">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="T279">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="U279">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="V279">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W279">
         <v>1.03</v>
@@ -45819,31 +45819,31 @@
         <v>1.04</v>
       </c>
       <c r="Y279">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Z279">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="AA279">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AB279">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AC279">
-        <v>4.55</v>
+        <v>4.25</v>
       </c>
       <c r="AD279">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AE279">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF279">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AG279">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AH279" t="inlineStr">
         <is>
@@ -45856,10 +45856,10 @@
         </is>
       </c>
       <c r="AJ279">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="AK279">
-        <v>1.57</v>
+        <v>1.2</v>
       </c>
       <c r="AL279">
         <v>0</v>
@@ -46278,13 +46278,13 @@
         <v>1.91</v>
       </c>
       <c r="O282">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="P282">
         <v>3.9</v>
       </c>
       <c r="Q282">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="R282">
         <v>2.15</v>
@@ -46296,7 +46296,7 @@
         <v>2.73</v>
       </c>
       <c r="U282">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="V282">
         <v>1.4</v>
@@ -46317,7 +46317,7 @@
         <v>1.92</v>
       </c>
       <c r="AB282">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AC282">
         <v>3.05</v>
@@ -46773,10 +46773,10 @@
         <v>4.33</v>
       </c>
       <c r="Q285">
-        <v>2.17</v>
+        <v>2.02</v>
       </c>
       <c r="R285">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="S285">
         <v>1.25</v>
@@ -46806,7 +46806,7 @@
         <v>1.57</v>
       </c>
       <c r="AB285">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="AC285">
         <v>2.5</v>
@@ -46837,7 +46837,7 @@
         <v>1.14</v>
       </c>
       <c r="AK285">
-        <v>2.16</v>
+        <v>2.07</v>
       </c>
       <c r="AL285">
         <v>0</v>
@@ -47090,7 +47090,7 @@
         </is>
       </c>
       <c r="N287">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="O287">
         <v>4</v>
@@ -47099,22 +47099,22 @@
         <v>4.8</v>
       </c>
       <c r="Q287">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="R287">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
       <c r="S287">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="T287">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U287">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V287">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W287">
         <v>1.15</v>
@@ -47123,25 +47123,25 @@
         <v>1.02</v>
       </c>
       <c r="Y287">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z287">
-        <v>4.95</v>
+        <v>4.8</v>
       </c>
       <c r="AA287">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AB287">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="AC287">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="AD287">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AE287">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AF287">
         <v>1.62</v>
@@ -47163,7 +47163,7 @@
         <v>1.2</v>
       </c>
       <c r="AK287">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AL287">
         <v>0</v>
@@ -47428,7 +47428,7 @@
         <v>2.26</v>
       </c>
       <c r="R289">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="S289">
         <v>1.3</v>
@@ -47914,10 +47914,10 @@
         <v>10</v>
       </c>
       <c r="Q292">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="R292">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="S292">
         <v>1.15</v>
@@ -47962,7 +47962,7 @@
         <v>1.6</v>
       </c>
       <c r="AG292">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AH292" t="inlineStr">
         <is>
@@ -47978,7 +47978,7 @@
         <v>1.08</v>
       </c>
       <c r="AK292">
-        <v>3.44</v>
+        <v>4</v>
       </c>
       <c r="AL292">
         <v>0</v>
@@ -48068,13 +48068,13 @@
         </is>
       </c>
       <c r="N293">
-        <v>4.05</v>
+        <v>3.72</v>
       </c>
       <c r="O293">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P293">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="Q293">
         <v>0</v>
@@ -48394,7 +48394,7 @@
         </is>
       </c>
       <c r="N295">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="O295">
         <v>3.8</v>
@@ -48448,7 +48448,7 @@
         <v>1.25</v>
       </c>
       <c r="AF295">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AG295">
         <v>2.4</v>
@@ -48729,55 +48729,55 @@
         <v>4.5</v>
       </c>
       <c r="Q297">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="R297">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="S297">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T297">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="U297">
-        <v>2.48</v>
+        <v>2.84</v>
       </c>
       <c r="V297">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W297">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X297">
         <v>1.01</v>
       </c>
       <c r="Y297">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z297">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA297">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AB297">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AC297">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="AD297">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AE297">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF297">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG297">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH297" t="inlineStr">
         <is>
@@ -48793,7 +48793,7 @@
         <v>1.25</v>
       </c>
       <c r="AK297">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="AL297">
         <v>0</v>
@@ -48886,7 +48886,7 @@
         <v>2.19</v>
       </c>
       <c r="O298">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="P298">
         <v>3.1</v>
@@ -49212,19 +49212,19 @@
         <v>2.04</v>
       </c>
       <c r="O300">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="P300">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q300">
         <v>2.48</v>
       </c>
       <c r="R300">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="S300">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T300">
         <v>3.1</v>
@@ -49251,10 +49251,10 @@
         <v>1.76</v>
       </c>
       <c r="AB300">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AC300">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="AD300">
         <v>1.44</v>
@@ -50395,7 +50395,7 @@
         <v>2.08</v>
       </c>
       <c r="AC307">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="AD307">
         <v>1.44</v>
@@ -50531,10 +50531,10 @@
         <v>1.43</v>
       </c>
       <c r="T308">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="U308">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="V308">
         <v>1.37</v>
@@ -50549,7 +50549,7 @@
         <v>1.34</v>
       </c>
       <c r="Z308">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="AA308">
         <v>1.98</v>
@@ -50558,7 +50558,7 @@
         <v>1.71</v>
       </c>
       <c r="AC308">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="AD308">
         <v>1.27</v>
@@ -50676,13 +50676,13 @@
         </is>
       </c>
       <c r="N309">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="O309">
-        <v>3.74</v>
+        <v>3.6</v>
       </c>
       <c r="P309">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="Q309">
         <v>0</v>
@@ -51011,22 +51011,22 @@
         <v>0</v>
       </c>
       <c r="Q311">
-        <v>3.87</v>
+        <v>3.4</v>
       </c>
       <c r="R311">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="S311">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T311">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="U311">
         <v>1.85</v>
       </c>
       <c r="V311">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="W311">
         <v>1.25</v>
@@ -51041,10 +51041,10 @@
         <v>6.4</v>
       </c>
       <c r="AA311">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AB311">
-        <v>2.92</v>
+        <v>3.4</v>
       </c>
       <c r="AC311">
         <v>1.83</v>
@@ -51072,7 +51072,7 @@
         </is>
       </c>
       <c r="AJ311">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AK311">
         <v>1.2</v>
@@ -51328,64 +51328,64 @@
         </is>
       </c>
       <c r="N313">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="O313">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="P313">
         <v>6.3</v>
       </c>
       <c r="Q313">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="R313">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="S313">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T313">
         <v>4.5</v>
       </c>
       <c r="U313">
+        <v>2.08</v>
+      </c>
+      <c r="V313">
+        <v>1.75</v>
+      </c>
+      <c r="W313">
+        <v>1.18</v>
+      </c>
+      <c r="X313">
+        <v>0</v>
+      </c>
+      <c r="Y313">
+        <v>1.13</v>
+      </c>
+      <c r="Z313">
+        <v>5.87</v>
+      </c>
+      <c r="AA313">
+        <v>1.42</v>
+      </c>
+      <c r="AB313">
+        <v>2.83</v>
+      </c>
+      <c r="AC313">
         <v>2.07</v>
       </c>
-      <c r="V313">
-        <v>1.8</v>
-      </c>
-      <c r="W313">
-        <v>1.2</v>
-      </c>
-      <c r="X313">
-        <v>0</v>
-      </c>
-      <c r="Y313">
-        <v>1.12</v>
-      </c>
-      <c r="Z313">
-        <v>6.02</v>
-      </c>
-      <c r="AA313">
-        <v>1.4</v>
-      </c>
-      <c r="AB313">
-        <v>2.88</v>
-      </c>
-      <c r="AC313">
-        <v>2.04</v>
-      </c>
       <c r="AD313">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AE313">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AF313">
         <v>1.55</v>
       </c>
       <c r="AG313">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AH313" t="inlineStr">
         <is>
@@ -51398,10 +51398,10 @@
         </is>
       </c>
       <c r="AJ313">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AK313">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="AL313">
         <v>0</v>
@@ -51491,25 +51491,25 @@
         </is>
       </c>
       <c r="N314">
-        <v>2.01</v>
+        <v>2.08</v>
       </c>
       <c r="O314">
-        <v>4</v>
+        <v>4.02</v>
       </c>
       <c r="P314">
-        <v>3.2</v>
+        <v>3.29</v>
       </c>
       <c r="Q314">
+        <v>2.57</v>
+      </c>
+      <c r="R314">
         <v>2.4</v>
       </c>
-      <c r="R314">
-        <v>2.45</v>
-      </c>
       <c r="S314">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T314">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="U314">
         <v>2.05</v>
@@ -51527,19 +51527,19 @@
         <v>1.13</v>
       </c>
       <c r="Z314">
-        <v>5.3</v>
+        <v>5.77</v>
       </c>
       <c r="AA314">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AB314">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="AC314">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="AD314">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AE314">
         <v>1.3</v>
@@ -51548,7 +51548,7 @@
         <v>1.4</v>
       </c>
       <c r="AG314">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="AH314" t="inlineStr">
         <is>
@@ -51561,7 +51561,7 @@
         </is>
       </c>
       <c r="AJ314">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK314">
         <v>1.75</v>
@@ -51654,25 +51654,25 @@
         </is>
       </c>
       <c r="N315">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="O315">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="P315">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Q315">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="R315">
-        <v>2.57</v>
+        <v>2.67</v>
       </c>
       <c r="S315">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T315">
-        <v>4.35</v>
+        <v>3.9</v>
       </c>
       <c r="U315">
         <v>1.99</v>
@@ -51687,10 +51687,10 @@
         <v>0</v>
       </c>
       <c r="Y315">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z315">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AA315">
         <v>1.37</v>
@@ -51699,10 +51699,10 @@
         <v>2.66</v>
       </c>
       <c r="AC315">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="AD315">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AE315">
         <v>1.25</v>
@@ -51724,10 +51724,10 @@
         </is>
       </c>
       <c r="AJ315">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AK315">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AL315">
         <v>0</v>
@@ -53613,10 +53613,10 @@
         <v>1.88</v>
       </c>
       <c r="O327">
-        <v>3.75</v>
+        <v>3.51</v>
       </c>
       <c r="P327">
-        <v>3.4</v>
+        <v>2.78</v>
       </c>
       <c r="Q327">
         <v>2.3</v>
@@ -53667,7 +53667,7 @@
         <v>1.42</v>
       </c>
       <c r="AG327">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="AH327" t="inlineStr">
         <is>
@@ -53782,16 +53782,16 @@
         <v>0</v>
       </c>
       <c r="Q328">
-        <v>4.77</v>
+        <v>4</v>
       </c>
       <c r="R328">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="S328">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T328">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U328">
         <v>2.05</v>
@@ -53843,10 +53843,10 @@
         </is>
       </c>
       <c r="AJ328">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AK328">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AL328">
         <v>0</v>
@@ -53945,13 +53945,13 @@
         <v>2.32</v>
       </c>
       <c r="Q329">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="R329">
         <v>2.72</v>
       </c>
       <c r="S329">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="T329">
         <v>4.5</v>
@@ -53984,7 +53984,7 @@
         <v>1.87</v>
       </c>
       <c r="AD329">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AE329">
         <v>1.41</v>
@@ -53993,7 +53993,7 @@
         <v>1.3</v>
       </c>
       <c r="AG329">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AH329" t="inlineStr">
         <is>
@@ -54108,16 +54108,16 @@
         <v>4.47</v>
       </c>
       <c r="Q330">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="R330">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="S330">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T330">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U330">
         <v>2.24</v>
@@ -54126,7 +54126,7 @@
         <v>1.61</v>
       </c>
       <c r="W330">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X330">
         <v>0</v>
@@ -54138,16 +54138,16 @@
         <v>5.12</v>
       </c>
       <c r="AA330">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB330">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AC330">
-        <v>2.31</v>
+        <v>2.19</v>
       </c>
       <c r="AD330">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AE330">
         <v>1.24</v>
@@ -54169,10 +54169,10 @@
         </is>
       </c>
       <c r="AJ330">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK330">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AL330">
         <v>0</v>
@@ -54262,13 +54262,13 @@
         </is>
       </c>
       <c r="N331">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="O331">
-        <v>3.83</v>
+        <v>3.85</v>
       </c>
       <c r="P331">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="Q331">
         <v>2.1</v>
@@ -54425,28 +54425,28 @@
         </is>
       </c>
       <c r="N332">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="O332">
         <v>3.8</v>
       </c>
       <c r="P332">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="Q332">
+        <v>2.33</v>
+      </c>
+      <c r="R332">
         <v>2.38</v>
-      </c>
-      <c r="R332">
-        <v>2.54</v>
       </c>
       <c r="S332">
         <v>1.25</v>
       </c>
       <c r="T332">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="U332">
-        <v>2.24</v>
+        <v>2.13</v>
       </c>
       <c r="V332">
         <v>1.62</v>
@@ -54458,25 +54458,25 @@
         <v>0</v>
       </c>
       <c r="Y332">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z332">
-        <v>5.15</v>
+        <v>5.22</v>
       </c>
       <c r="AA332">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AB332">
-        <v>2.36</v>
+        <v>2.55</v>
       </c>
       <c r="AC332">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="AD332">
         <v>1.61</v>
       </c>
       <c r="AE332">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AF332">
         <v>1.44</v>
@@ -54495,10 +54495,10 @@
         </is>
       </c>
       <c r="AJ332">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK332">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AL332">
         <v>0</v>

--- a/jogos_2026-11-01.xlsx
+++ b/jogos_2026-11-01.xlsx
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,19 +2102,19 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="O11">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P11">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q11">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="R11">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="S11">
         <v>1.35</v>
@@ -2123,7 +2123,7 @@
         <v>3</v>
       </c>
       <c r="U11">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="V11">
         <v>1.44</v>
@@ -2132,34 +2132,34 @@
         <v>1.1</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z11">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA11">
         <v>1.94</v>
       </c>
       <c r="AB11">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AC11">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AD11">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE11">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF11">
         <v>1.75</v>
       </c>
       <c r="AG11">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>1.22</v>
       </c>
       <c r="AK11">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,19 +2265,19 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="O12">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P12">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q12">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="R12">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="S12">
         <v>1.35</v>
@@ -2286,7 +2286,7 @@
         <v>3</v>
       </c>
       <c r="U12">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="V12">
         <v>1.44</v>
@@ -2295,34 +2295,34 @@
         <v>1.1</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y12">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z12">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA12">
         <v>1.94</v>
       </c>
       <c r="AB12">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AC12">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AD12">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE12">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF12">
         <v>1.75</v>
       </c>
       <c r="AG12">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>1.22</v>
       </c>
       <c r="AK12">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -3415,7 +3415,7 @@
         <v>2.11</v>
       </c>
       <c r="Q19">
-        <v>3.48</v>
+        <v>3.1</v>
       </c>
       <c r="R19">
         <v>2.3</v>
@@ -3569,31 +3569,31 @@
         </is>
       </c>
       <c r="N20">
-        <v>3.26</v>
+        <v>3.09</v>
       </c>
       <c r="O20">
-        <v>3.72</v>
+        <v>3.68</v>
       </c>
       <c r="P20">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="Q20">
-        <v>3.74</v>
+        <v>3.65</v>
       </c>
       <c r="R20">
-        <v>2.39</v>
+        <v>2.28</v>
       </c>
       <c r="S20">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T20">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="U20">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="V20">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W20">
         <v>1.1</v>
@@ -3602,31 +3602,31 @@
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z20">
-        <v>4.25</v>
+        <v>4.05</v>
       </c>
       <c r="AA20">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AB20">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AC20">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="AD20">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AE20">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF20">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG20">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.77</v>
+        <v>1.3</v>
       </c>
       <c r="AK20">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,7 +3732,7 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="O21">
         <v>5.5</v>
@@ -3774,7 +3774,7 @@
         <v>1.6</v>
       </c>
       <c r="AB21">
-        <v>2.34</v>
+        <v>2.19</v>
       </c>
       <c r="AC21">
         <v>2.53</v>
@@ -3789,7 +3789,7 @@
         <v>2.01</v>
       </c>
       <c r="AG21">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>1.06</v>
       </c>
       <c r="AK21">
-        <v>3.33</v>
+        <v>3.6</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4230,10 +4230,10 @@
         <v>5</v>
       </c>
       <c r="Q24">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="R24">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="S24">
         <v>1.29</v>
@@ -4294,7 +4294,7 @@
         <v>1.22</v>
       </c>
       <c r="AK24">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4399,19 +4399,19 @@
         <v>2.16</v>
       </c>
       <c r="S25">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T25">
-        <v>3.1</v>
+        <v>3.03</v>
       </c>
       <c r="U25">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="V25">
         <v>1.44</v>
       </c>
       <c r="W25">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X25">
         <v>1.03</v>
@@ -4429,7 +4429,7 @@
         <v>2</v>
       </c>
       <c r="AC25">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="AD25">
         <v>1.37</v>
@@ -4556,55 +4556,55 @@
         <v>0</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4719,55 +4719,55 @@
         <v>3.16</v>
       </c>
       <c r="Q27">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="R27">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S27">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="T27">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="U27">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="V27">
         <v>1.33</v>
       </c>
       <c r="W27">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X27">
+        <v>1.03</v>
+      </c>
+      <c r="Y27">
+        <v>1.33</v>
+      </c>
+      <c r="Z27">
+        <v>2.97</v>
+      </c>
+      <c r="AA27">
+        <v>2.04</v>
+      </c>
+      <c r="AB27">
+        <v>1.7</v>
+      </c>
+      <c r="AC27">
+        <v>3.58</v>
+      </c>
+      <c r="AD27">
+        <v>1.21</v>
+      </c>
+      <c r="AE27">
         <v>1.05</v>
       </c>
-      <c r="Y27">
-        <v>1.34</v>
-      </c>
-      <c r="Z27">
-        <v>2.78</v>
-      </c>
-      <c r="AA27">
-        <v>2.15</v>
-      </c>
-      <c r="AB27">
-        <v>1.6</v>
-      </c>
-      <c r="AC27">
-        <v>3.96</v>
-      </c>
-      <c r="AD27">
-        <v>1.17</v>
-      </c>
-      <c r="AE27">
-        <v>1.03</v>
-      </c>
       <c r="AF27">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AG27">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>1.25</v>
       </c>
       <c r="AK27">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5374,7 +5374,7 @@
         <v>2.43</v>
       </c>
       <c r="R31">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S31">
         <v>1.36</v>
@@ -5401,10 +5401,10 @@
         <v>2.88</v>
       </c>
       <c r="AA31">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AB31">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AC31">
         <v>3.7</v>
@@ -5691,7 +5691,7 @@
         <v>2.2</v>
       </c>
       <c r="O33">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P33">
         <v>2.85</v>
@@ -5742,10 +5742,10 @@
         <v>1.03</v>
       </c>
       <c r="AF33">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG33">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -7164,55 +7164,55 @@
         <v>0</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7327,55 +7327,55 @@
         <v>0</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7490,55 +7490,55 @@
         <v>0</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7653,55 +7653,55 @@
         <v>0</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -8172,10 +8172,10 @@
         <v>2.88</v>
       </c>
       <c r="AA48">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB48">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AC48">
         <v>3.84</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Atlético Central</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,80 +9274,80 @@
         </is>
       </c>
       <c r="N55">
+        <v>2.05</v>
+      </c>
+      <c r="O55">
+        <v>3.3</v>
+      </c>
+      <c r="P55">
         <v>3.1</v>
       </c>
-      <c r="O55">
-        <v>3.2</v>
-      </c>
-      <c r="P55">
-        <v>2.09</v>
-      </c>
       <c r="Q55">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="R55">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="S55">
+        <v>1.35</v>
+      </c>
+      <c r="T55">
+        <v>2.9</v>
+      </c>
+      <c r="U55">
+        <v>2.7</v>
+      </c>
+      <c r="V55">
         <v>1.4</v>
       </c>
-      <c r="T55">
-        <v>2.7</v>
-      </c>
-      <c r="U55">
-        <v>3</v>
-      </c>
-      <c r="V55">
-        <v>1.35</v>
-      </c>
       <c r="W55">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X55">
         <v>1.02</v>
       </c>
       <c r="Y55">
+        <v>1.25</v>
+      </c>
+      <c r="Z55">
+        <v>3.28</v>
+      </c>
+      <c r="AA55">
+        <v>1.75</v>
+      </c>
+      <c r="AB55">
+        <v>2.05</v>
+      </c>
+      <c r="AC55">
+        <v>2.97</v>
+      </c>
+      <c r="AD55">
+        <v>1.3</v>
+      </c>
+      <c r="AE55">
+        <v>1.08</v>
+      </c>
+      <c r="AF55">
+        <v>1.7</v>
+      </c>
+      <c r="AG55">
+        <v>2.05</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ55">
         <v>1.33</v>
       </c>
-      <c r="Z55">
-        <v>2.83</v>
-      </c>
-      <c r="AA55">
-        <v>2.05</v>
-      </c>
-      <c r="AB55">
-        <v>1.75</v>
-      </c>
-      <c r="AC55">
-        <v>3.75</v>
-      </c>
-      <c r="AD55">
-        <v>1.19</v>
-      </c>
-      <c r="AE55">
-        <v>1.06</v>
-      </c>
-      <c r="AF55">
-        <v>1.83</v>
-      </c>
-      <c r="AG55">
-        <v>1.83</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ55">
-        <v>1.36</v>
-      </c>
       <c r="AK55">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Atlético Central</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
+        <v>3.1</v>
+      </c>
+      <c r="O56">
+        <v>3.2</v>
+      </c>
+      <c r="P56">
+        <v>2.09</v>
+      </c>
+      <c r="Q56">
+        <v>3.5</v>
+      </c>
+      <c r="R56">
         <v>2.05</v>
       </c>
-      <c r="O56">
-        <v>3.3</v>
-      </c>
-      <c r="P56">
-        <v>3.1</v>
-      </c>
-      <c r="Q56">
+      <c r="S56">
+        <v>1.4</v>
+      </c>
+      <c r="T56">
         <v>2.7</v>
       </c>
-      <c r="R56">
-        <v>2.15</v>
-      </c>
-      <c r="S56">
+      <c r="U56">
+        <v>3</v>
+      </c>
+      <c r="V56">
         <v>1.35</v>
       </c>
-      <c r="T56">
-        <v>2.9</v>
-      </c>
-      <c r="U56">
-        <v>2.7</v>
-      </c>
-      <c r="V56">
-        <v>1.4</v>
-      </c>
       <c r="W56">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X56">
         <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="Z56">
-        <v>3.28</v>
+        <v>2.83</v>
       </c>
       <c r="AA56">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AB56">
-        <v>2.05</v>
+        <v>1.63</v>
       </c>
       <c r="AC56">
-        <v>2.97</v>
+        <v>3.75</v>
       </c>
       <c r="AD56">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AE56">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF56">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AG56">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
+        <v>1.36</v>
+      </c>
+      <c r="AK56">
         <v>1.33</v>
-      </c>
-      <c r="AK56">
-        <v>1.6</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9763,31 +9763,31 @@
         </is>
       </c>
       <c r="N58">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="O58">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P58">
         <v>1.55</v>
       </c>
       <c r="Q58">
-        <v>6.45</v>
+        <v>6.3</v>
       </c>
       <c r="R58">
         <v>2.03</v>
       </c>
       <c r="S58">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T58">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
       <c r="U58">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="V58">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W58">
         <v>1.06</v>
@@ -9796,16 +9796,16 @@
         <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z58">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="AA58">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AB58">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AC58">
         <v>3.34</v>
@@ -9817,10 +9817,10 @@
         <v>1.05</v>
       </c>
       <c r="AF58">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="AG58">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9929,10 +9929,10 @@
         <v>1.32</v>
       </c>
       <c r="O59">
-        <v>5.85</v>
+        <v>5.75</v>
       </c>
       <c r="P59">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="Q59">
         <v>1.62</v>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AK59">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10424,55 +10424,55 @@
         <v>1.83</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T62">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U62">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V62">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W62">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X62">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y62">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z62">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE62">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF62">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG62">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK62">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10919,7 +10919,7 @@
         <v>2.21</v>
       </c>
       <c r="S65">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T65">
         <v>3.26</v>
@@ -11073,7 +11073,7 @@
         <v>3.5</v>
       </c>
       <c r="P66">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q66">
         <v>2.55</v>
@@ -11097,7 +11097,7 @@
         <v>1.08</v>
       </c>
       <c r="X66">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y66">
         <v>1.22</v>
@@ -11239,55 +11239,55 @@
         <v>0</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S67">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T67">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U67">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V67">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W67">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X67">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z67">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA67">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC67">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD67">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE67">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF67">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG67">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK67">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -12576,7 +12576,7 @@
         <v>1.84</v>
       </c>
       <c r="AB75">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AC75">
         <v>3.08</v>
@@ -12869,10 +12869,10 @@
         <v>2.08</v>
       </c>
       <c r="Q77">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R77">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="S77">
         <v>1.31</v>
@@ -12899,10 +12899,10 @@
         <v>3.58</v>
       </c>
       <c r="AA77">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AB77">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="AC77">
         <v>2.92</v>
@@ -13352,7 +13352,7 @@
         <v>3.18</v>
       </c>
       <c r="O80">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="P80">
         <v>2.25</v>
@@ -13515,7 +13515,7 @@
         <v>2.15</v>
       </c>
       <c r="O81">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P81">
         <v>2.81</v>
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O82">
         <v>3.4</v>
       </c>
       <c r="P82">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="Q82">
         <v>2.49</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,31 +13838,31 @@
         </is>
       </c>
       <c r="N83">
+        <v>2.1</v>
+      </c>
+      <c r="O83">
+        <v>3.58</v>
+      </c>
+      <c r="P83">
+        <v>2.9</v>
+      </c>
+      <c r="Q83">
+        <v>2.6</v>
+      </c>
+      <c r="R83">
         <v>2.4</v>
       </c>
-      <c r="O83">
-        <v>3.7</v>
-      </c>
-      <c r="P83">
-        <v>2.55</v>
-      </c>
-      <c r="Q83">
-        <v>3.04</v>
-      </c>
-      <c r="R83">
-        <v>2.32</v>
-      </c>
       <c r="S83">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T83">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U83">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="V83">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W83">
         <v>1.17</v>
@@ -13871,28 +13871,28 @@
         <v>1.02</v>
       </c>
       <c r="Y83">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z83">
-        <v>4.85</v>
+        <v>5.25</v>
       </c>
       <c r="AA83">
         <v>1.5</v>
       </c>
       <c r="AB83">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="AC83">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="AD83">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="AE83">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF83">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG83">
         <v>2.5</v>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AK83">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,31 +14001,31 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="O84">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="P84">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="Q84">
-        <v>2.37</v>
+        <v>2.75</v>
       </c>
       <c r="R84">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="S84">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T84">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U84">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="V84">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W84">
         <v>1.17</v>
@@ -14034,28 +14034,28 @@
         <v>1.02</v>
       </c>
       <c r="Y84">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z84">
-        <v>5.25</v>
+        <v>4.85</v>
       </c>
       <c r="AA84">
         <v>1.5</v>
       </c>
       <c r="AB84">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AC84">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="AD84">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AE84">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AF84">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG84">
         <v>2.5</v>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AK84">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14164,7 +14164,7 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="O85">
         <v>3.63</v>
@@ -14234,7 +14234,7 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AK85">
         <v>1.73</v>
@@ -14327,58 +14327,58 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="O86">
         <v>4.8</v>
       </c>
       <c r="P86">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Q86">
         <v>1.67</v>
       </c>
       <c r="R86">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="S86">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="T86">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="U86">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="V86">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="W86">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X86">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z86">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AA86">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AB86">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AC86">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="AD86">
         <v>1.72</v>
       </c>
       <c r="AE86">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AF86">
         <v>1.6</v>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AK86">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14490,7 +14490,7 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="O87">
         <v>3.75</v>
@@ -14822,13 +14822,13 @@
         <v>3.63</v>
       </c>
       <c r="P89">
-        <v>4</v>
+        <v>4.02</v>
       </c>
       <c r="Q89">
         <v>2.34</v>
       </c>
       <c r="R89">
-        <v>2.18</v>
+        <v>2.44</v>
       </c>
       <c r="S89">
         <v>1.28</v>
@@ -14855,10 +14855,10 @@
         <v>4.19</v>
       </c>
       <c r="AA89">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB89">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC89">
         <v>2.6</v>
@@ -14886,7 +14886,7 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK89">
         <v>2</v>
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="O90">
         <v>5.35</v>
       </c>
       <c r="P90">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="Q90">
         <v>1.73</v>
@@ -15344,7 +15344,7 @@
         <v>10.5</v>
       </c>
       <c r="AA92">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AB92">
         <v>4.2</v>
@@ -15353,7 +15353,7 @@
         <v>1.5</v>
       </c>
       <c r="AD92">
-        <v>2.43</v>
+        <v>2.28</v>
       </c>
       <c r="AE92">
         <v>1.61</v>
@@ -15375,7 +15375,7 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AK92">
         <v>3.75</v>
@@ -15631,19 +15631,19 @@
         </is>
       </c>
       <c r="N94">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="O94">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P94">
         <v>3.65</v>
       </c>
       <c r="Q94">
-        <v>2.42</v>
+        <v>2.47</v>
       </c>
       <c r="R94">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="S94">
         <v>1.43</v>
@@ -15664,25 +15664,25 @@
         <v>1.04</v>
       </c>
       <c r="Y94">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z94">
-        <v>3.04</v>
+        <v>2.84</v>
       </c>
       <c r="AA94">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="AB94">
         <v>1.68</v>
       </c>
       <c r="AC94">
-        <v>3.84</v>
+        <v>4.01</v>
       </c>
       <c r="AD94">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE94">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF94">
         <v>1.97</v>
@@ -15794,7 +15794,7 @@
         </is>
       </c>
       <c r="N95">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O95">
         <v>3.3</v>
@@ -15803,55 +15803,55 @@
         <v>1.95</v>
       </c>
       <c r="Q95">
-        <v>4.35</v>
+        <v>4.25</v>
       </c>
       <c r="R95">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="S95">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="T95">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="U95">
-        <v>3.11</v>
+        <v>3.15</v>
       </c>
       <c r="V95">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W95">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X95">
         <v>1</v>
       </c>
       <c r="Y95">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="Z95">
-        <v>3.11</v>
+        <v>3.14</v>
       </c>
       <c r="AA95">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AB95">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AC95">
-        <v>3.7</v>
+        <v>3.76</v>
       </c>
       <c r="AD95">
         <v>1.25</v>
       </c>
       <c r="AE95">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF95">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AG95">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK95">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15969,7 +15969,7 @@
         <v>2.89</v>
       </c>
       <c r="R96">
-        <v>2.26</v>
+        <v>2.05</v>
       </c>
       <c r="S96">
         <v>1.36</v>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AK96">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16123,7 +16123,7 @@
         <v>3.1</v>
       </c>
       <c r="O97">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="P97">
         <v>2.42</v>
@@ -16132,7 +16132,7 @@
         <v>3.59</v>
       </c>
       <c r="R97">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="S97">
         <v>1.53</v>
@@ -16171,7 +16171,7 @@
         <v>1.11</v>
       </c>
       <c r="AE97">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF97">
         <v>2.15</v>
@@ -16193,7 +16193,7 @@
         <v>1.32</v>
       </c>
       <c r="AK97">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16289,7 +16289,7 @@
         <v>3.7</v>
       </c>
       <c r="P98">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="Q98">
         <v>4</v>
@@ -16488,7 +16488,7 @@
         <v>1.44</v>
       </c>
       <c r="AB99">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AC99">
         <v>2.36</v>
@@ -16775,7 +16775,7 @@
         <v>6.16</v>
       </c>
       <c r="O101">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="P101">
         <v>1.43</v>
@@ -16796,19 +16796,19 @@
         <v>2.02</v>
       </c>
       <c r="V101">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="W101">
         <v>1.17</v>
       </c>
       <c r="X101">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y101">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z101">
-        <v>5.55</v>
+        <v>6.5</v>
       </c>
       <c r="AA101">
         <v>1.38</v>
@@ -16817,13 +16817,13 @@
         <v>2.75</v>
       </c>
       <c r="AC101">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AD101">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AE101">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF101">
         <v>1.6</v>
@@ -17107,10 +17107,10 @@
         <v>0</v>
       </c>
       <c r="Q103">
-        <v>4</v>
+        <v>3.78</v>
       </c>
       <c r="R103">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S103">
         <v>1.33</v>
@@ -17270,10 +17270,10 @@
         <v>3.2</v>
       </c>
       <c r="Q104">
-        <v>2.61</v>
+        <v>2.47</v>
       </c>
       <c r="R104">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="S104">
         <v>1.33</v>
@@ -17303,7 +17303,7 @@
         <v>1.9</v>
       </c>
       <c r="AB104">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AC104">
         <v>3.21</v>
@@ -17430,7 +17430,7 @@
         <v>3.32</v>
       </c>
       <c r="P105">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q105">
         <v>2.75</v>
@@ -17439,7 +17439,7 @@
         <v>2.05</v>
       </c>
       <c r="S105">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T105">
         <v>2.56</v>
@@ -17463,7 +17463,7 @@
         <v>3.1</v>
       </c>
       <c r="AA105">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="AB105">
         <v>1.74</v>
@@ -17497,7 +17497,7 @@
         <v>1.3</v>
       </c>
       <c r="AK105">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -18076,10 +18076,10 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="O109">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P109">
         <v>3.4</v>
@@ -18091,7 +18091,7 @@
         <v>2.17</v>
       </c>
       <c r="S109">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="T109">
         <v>3.3</v>
@@ -18115,10 +18115,10 @@
         <v>4.33</v>
       </c>
       <c r="AA109">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AB109">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="AC109">
         <v>2.46</v>
@@ -18242,16 +18242,16 @@
         <v>1.44</v>
       </c>
       <c r="O110">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P110">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="Q110">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="R110">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S110">
         <v>1.31</v>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AK110">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18411,10 +18411,10 @@
         <v>3.5</v>
       </c>
       <c r="Q111">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="R111">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S111">
         <v>1.32</v>
@@ -18441,10 +18441,10 @@
         <v>3.58</v>
       </c>
       <c r="AA111">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AB111">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AC111">
         <v>2.88</v>
@@ -18604,10 +18604,10 @@
         <v>2.7</v>
       </c>
       <c r="AA112">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB112">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AC112">
         <v>3.98</v>
@@ -19093,10 +19093,10 @@
         <v>7</v>
       </c>
       <c r="AA115">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AB115">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AC115">
         <v>1.81</v>
@@ -19124,7 +19124,7 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AK115">
         <v>1.36</v>
@@ -19386,13 +19386,13 @@
         <v>3.95</v>
       </c>
       <c r="P117">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="Q117">
         <v>3.85</v>
       </c>
       <c r="R117">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S117">
         <v>1.22</v>
@@ -19419,10 +19419,10 @@
         <v>5.46</v>
       </c>
       <c r="AA117">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB117">
-        <v>2.43</v>
+        <v>2.63</v>
       </c>
       <c r="AC117">
         <v>2.21</v>
@@ -19564,7 +19564,7 @@
         <v>5.2</v>
       </c>
       <c r="U118">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="V118">
         <v>1.95</v>
@@ -19573,7 +19573,7 @@
         <v>1.29</v>
       </c>
       <c r="X118">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y118">
         <v>1.02</v>
@@ -19582,10 +19582,10 @@
         <v>7.7</v>
       </c>
       <c r="AA118">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AB118">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AC118">
         <v>1.67</v>
@@ -19597,7 +19597,7 @@
         <v>1.46</v>
       </c>
       <c r="AF118">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG118">
         <v>2.15</v>
@@ -19616,7 +19616,7 @@
         <v>1.08</v>
       </c>
       <c r="AK118">
-        <v>4.06</v>
+        <v>3.98</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19745,10 +19745,10 @@
         <v>5.62</v>
       </c>
       <c r="AA119">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB119">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="AC119">
         <v>2.18</v>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
+        <v>1.2</v>
+      </c>
+      <c r="AK119">
         <v>1.17</v>
-      </c>
-      <c r="AK119">
-        <v>1.14</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19875,7 +19875,7 @@
         <v>3.8</v>
       </c>
       <c r="P120">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q120">
         <v>3.1</v>
@@ -19911,7 +19911,7 @@
         <v>1.5</v>
       </c>
       <c r="AB120">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="AC120">
         <v>2.27</v>
@@ -20397,10 +20397,10 @@
         <v>2.96</v>
       </c>
       <c r="AA123">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AB123">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AC123">
         <v>3.7</v>
@@ -20521,13 +20521,13 @@
         </is>
       </c>
       <c r="N124">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="O124">
         <v>3.1</v>
       </c>
       <c r="P124">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="Q124">
         <v>2.45</v>
@@ -20539,10 +20539,10 @@
         <v>1.4</v>
       </c>
       <c r="T124">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="U124">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="V124">
         <v>1.33</v>
@@ -20563,7 +20563,7 @@
         <v>2.2</v>
       </c>
       <c r="AB124">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC124">
         <v>3.92</v>
@@ -20684,7 +20684,7 @@
         </is>
       </c>
       <c r="N125">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="O125">
         <v>3.1</v>
@@ -20723,10 +20723,10 @@
         <v>3.2</v>
       </c>
       <c r="AA125">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AB125">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AC125">
         <v>3.28</v>
@@ -20850,7 +20850,7 @@
         <v>2.73</v>
       </c>
       <c r="O126">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="P126">
         <v>2.57</v>
@@ -20886,10 +20886,10 @@
         <v>3.5</v>
       </c>
       <c r="AA126">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AB126">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC126">
         <v>3.35</v>
@@ -21013,7 +21013,7 @@
         <v>3.1</v>
       </c>
       <c r="O127">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P127">
         <v>2.15</v>
@@ -21182,10 +21182,10 @@
         <v>6.5</v>
       </c>
       <c r="Q128">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="R128">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="S128">
         <v>1.31</v>
@@ -21212,10 +21212,10 @@
         <v>3.84</v>
       </c>
       <c r="AA128">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AB128">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="AC128">
         <v>2.7</v>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AK128">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21345,55 +21345,55 @@
         <v>3.5</v>
       </c>
       <c r="Q129">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R129">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S129">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T129">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U129">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V129">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W129">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X129">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y129">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z129">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA129">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB129">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC129">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AD129">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE129">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF129">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG129">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK129">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21511,7 +21511,7 @@
         <v>2.3</v>
       </c>
       <c r="R130">
-        <v>2.38</v>
+        <v>2.57</v>
       </c>
       <c r="S130">
         <v>1.25</v>
@@ -21535,19 +21535,19 @@
         <v>1.18</v>
       </c>
       <c r="Z130">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AA130">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AB130">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AC130">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AD130">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AE130">
         <v>1.21</v>
@@ -21692,7 +21692,7 @@
         <v>1.06</v>
       </c>
       <c r="X131">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y131">
         <v>1.44</v>
@@ -21704,16 +21704,16 @@
         <v>2.35</v>
       </c>
       <c r="AB131">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AC131">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AD131">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AE131">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF131">
         <v>2.1</v>
@@ -21840,7 +21840,7 @@
         <v>2.3</v>
       </c>
       <c r="S132">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T132">
         <v>3.42</v>
@@ -21988,13 +21988,13 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="O133">
-        <v>3.25</v>
+        <v>3.13</v>
       </c>
       <c r="P133">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="Q133">
         <v>3.1</v>
@@ -22006,13 +22006,13 @@
         <v>1.4</v>
       </c>
       <c r="T133">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U133">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="V133">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W133">
         <v>1.06</v>
@@ -22033,13 +22033,13 @@
         <v>1.75</v>
       </c>
       <c r="AC133">
-        <v>3.52</v>
+        <v>3.55</v>
       </c>
       <c r="AD133">
         <v>1.27</v>
       </c>
       <c r="AE133">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF133">
         <v>1.82</v>
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="O134">
         <v>3.1</v>
       </c>
       <c r="P134">
-        <v>2.75</v>
+        <v>3.43</v>
       </c>
       <c r="Q134">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="R134">
         <v>2.1</v>
       </c>
       <c r="S134">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T134">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U134">
-        <v>2.65</v>
+        <v>2.77</v>
       </c>
       <c r="V134">
         <v>1.36</v>
       </c>
       <c r="W134">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X134">
         <v>1.01</v>
       </c>
       <c r="Y134">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z134">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="AA134">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="AB134">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AC134">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="AD134">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AE134">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF134">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AG134">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK134">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22661,7 +22661,7 @@
         <v>3</v>
       </c>
       <c r="U137">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="V137">
         <v>1.45</v>
@@ -22682,7 +22682,7 @@
         <v>1.87</v>
       </c>
       <c r="AB137">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AC137">
         <v>3.1</v>
@@ -22845,7 +22845,7 @@
         <v>2.1</v>
       </c>
       <c r="AB138">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC138">
         <v>3.8</v>
@@ -23467,7 +23467,7 @@
         <v>2.16</v>
       </c>
       <c r="R142">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="S142">
         <v>1.25</v>
@@ -23528,7 +23528,7 @@
         <v>1.2</v>
       </c>
       <c r="AK142">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -23618,19 +23618,19 @@
         </is>
       </c>
       <c r="N143">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="O143">
         <v>3.35</v>
       </c>
       <c r="P143">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="Q143">
         <v>2.9</v>
       </c>
       <c r="R143">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="S143">
         <v>1.3</v>
@@ -23657,10 +23657,10 @@
         <v>3.68</v>
       </c>
       <c r="AA143">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AB143">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC143">
         <v>2.7</v>
@@ -23781,13 +23781,13 @@
         </is>
       </c>
       <c r="N144">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="O144">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="P144">
-        <v>5.75</v>
+        <v>4.15</v>
       </c>
       <c r="Q144">
         <v>2.12</v>
@@ -23820,7 +23820,7 @@
         <v>3.68</v>
       </c>
       <c r="AA144">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AB144">
         <v>2.01</v>
@@ -23950,7 +23950,7 @@
         <v>4.5</v>
       </c>
       <c r="P145">
-        <v>7.25</v>
+        <v>6.7</v>
       </c>
       <c r="Q145">
         <v>1.91</v>
@@ -23974,28 +23974,28 @@
         <v>1.08</v>
       </c>
       <c r="X145">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y145">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z145">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AA145">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AB145">
         <v>2</v>
       </c>
       <c r="AC145">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="AD145">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE145">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF145">
         <v>2.05</v>
@@ -24014,7 +24014,7 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AK145">
         <v>2.8</v>
@@ -24107,10 +24107,10 @@
         </is>
       </c>
       <c r="N146">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="O146">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="P146">
         <v>2.8</v>
@@ -24140,22 +24140,22 @@
         <v>1</v>
       </c>
       <c r="Y146">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z146">
-        <v>4.95</v>
+        <v>5.5</v>
       </c>
       <c r="AA146">
         <v>1.53</v>
       </c>
       <c r="AB146">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="AC146">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AD146">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AE146">
         <v>1.22</v>
@@ -24276,7 +24276,7 @@
         <v>3.64</v>
       </c>
       <c r="P147">
-        <v>4.55</v>
+        <v>4.85</v>
       </c>
       <c r="Q147">
         <v>2.37</v>
@@ -24804,7 +24804,7 @@
         <v>2.13</v>
       </c>
       <c r="AC150">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="AD150">
         <v>1.47</v>
@@ -24816,7 +24816,7 @@
         <v>1.55</v>
       </c>
       <c r="AG150">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AH150" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>1.31</v>
       </c>
       <c r="AK150">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AL150">
         <v>0</v>
@@ -26878,13 +26878,13 @@
         </is>
       </c>
       <c r="N163">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O163">
         <v>3.6</v>
       </c>
       <c r="P163">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="Q163">
         <v>2.6</v>
@@ -26926,7 +26926,7 @@
         <v>2.52</v>
       </c>
       <c r="AD163">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AE163">
         <v>1.2</v>
@@ -27053,7 +27053,7 @@
         <v>2.25</v>
       </c>
       <c r="R164">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S164">
         <v>1.3</v>
@@ -27089,10 +27089,10 @@
         <v>3.06</v>
       </c>
       <c r="AD164">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AE164">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF164">
         <v>1.67</v>
@@ -28182,7 +28182,7 @@
         </is>
       </c>
       <c r="N171">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="O171">
         <v>4.55</v>
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G172">
@@ -28357,68 +28357,68 @@
         <v>2.3</v>
       </c>
       <c r="R172">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="S172">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T172">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="U172">
-        <v>2.62</v>
+        <v>2.81</v>
       </c>
       <c r="V172">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="W172">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X172">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y172">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="Z172">
-        <v>3.42</v>
+        <v>2.97</v>
       </c>
       <c r="AA172">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AB172">
+        <v>1.8</v>
+      </c>
+      <c r="AC172">
+        <v>3.5</v>
+      </c>
+      <c r="AD172">
+        <v>1.22</v>
+      </c>
+      <c r="AE172">
+        <v>1.07</v>
+      </c>
+      <c r="AF172">
+        <v>1.92</v>
+      </c>
+      <c r="AG172">
+        <v>1.75</v>
+      </c>
+      <c r="AH172" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI172" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ172">
+        <v>1.22</v>
+      </c>
+      <c r="AK172">
         <v>1.95</v>
-      </c>
-      <c r="AC172">
-        <v>3.05</v>
-      </c>
-      <c r="AD172">
-        <v>1.28</v>
-      </c>
-      <c r="AE172">
-        <v>1.11</v>
-      </c>
-      <c r="AF172">
-        <v>1.75</v>
-      </c>
-      <c r="AG172">
-        <v>1.95</v>
-      </c>
-      <c r="AH172" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI172" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ172">
-        <v>1.21</v>
-      </c>
-      <c r="AK172">
-        <v>2</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G173">
@@ -28508,64 +28508,64 @@
         </is>
       </c>
       <c r="N173">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O173">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P173">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q173">
         <v>2.3</v>
       </c>
       <c r="R173">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="S173">
+        <v>1.35</v>
+      </c>
+      <c r="T173">
+        <v>3</v>
+      </c>
+      <c r="U173">
+        <v>2.62</v>
+      </c>
+      <c r="V173">
         <v>1.4</v>
       </c>
-      <c r="T173">
-        <v>2.65</v>
-      </c>
-      <c r="U173">
-        <v>2.81</v>
-      </c>
-      <c r="V173">
-        <v>1.34</v>
-      </c>
       <c r="W173">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X173">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y173">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="Z173">
-        <v>2.97</v>
+        <v>3.42</v>
       </c>
       <c r="AA173">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AB173">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AC173">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="AD173">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AE173">
         <v>1.07</v>
       </c>
       <c r="AF173">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AG173">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AH173" t="inlineStr">
         <is>
@@ -28578,10 +28578,10 @@
         </is>
       </c>
       <c r="AJ173">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK173">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AL173">
         <v>0</v>
@@ -28710,10 +28710,10 @@
         <v>2.83</v>
       </c>
       <c r="AA174">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB174">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AC174">
         <v>3.75</v>
@@ -28846,7 +28846,7 @@
         <v>3.91</v>
       </c>
       <c r="R175">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="S175">
         <v>1.36</v>
@@ -28867,7 +28867,7 @@
         <v>1.02</v>
       </c>
       <c r="Y175">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z175">
         <v>2.92</v>
@@ -28997,13 +28997,13 @@
         </is>
       </c>
       <c r="N176">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="O176">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="P176">
-        <v>2.59</v>
+        <v>2.42</v>
       </c>
       <c r="Q176">
         <v>0</v>
@@ -31116,13 +31116,13 @@
         </is>
       </c>
       <c r="N189">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="O189">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P189">
-        <v>2.5</v>
+        <v>2.11</v>
       </c>
       <c r="Q189">
         <v>3.48</v>
@@ -31285,7 +31285,7 @@
         <v>4.2</v>
       </c>
       <c r="P190">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="Q190">
         <v>2.08</v>
@@ -31321,7 +31321,7 @@
         <v>1.57</v>
       </c>
       <c r="AB190">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="AC190">
         <v>2.5</v>
@@ -31445,10 +31445,10 @@
         <v>2.45</v>
       </c>
       <c r="O191">
-        <v>3.3</v>
+        <v>3.56</v>
       </c>
       <c r="P191">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="Q191">
         <v>3.13</v>
@@ -31481,10 +31481,10 @@
         <v>3.77</v>
       </c>
       <c r="AA191">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="AB191">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AC191">
         <v>3.11</v>
@@ -31611,13 +31611,13 @@
         <v>7.1</v>
       </c>
       <c r="P192">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Q192">
         <v>6.38</v>
       </c>
       <c r="R192">
-        <v>3.52</v>
+        <v>3.14</v>
       </c>
       <c r="S192">
         <v>1.12</v>
@@ -31629,7 +31629,7 @@
         <v>1.73</v>
       </c>
       <c r="V192">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="W192">
         <v>1.36</v>
@@ -31644,10 +31644,10 @@
         <v>9</v>
       </c>
       <c r="AA192">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AB192">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AC192">
         <v>1.57</v>
@@ -31678,7 +31678,7 @@
         <v>1.06</v>
       </c>
       <c r="AK192">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AL192">
         <v>0</v>
@@ -32148,10 +32148,10 @@
         <v>1.12</v>
       </c>
       <c r="AF195">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AG195">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32260,10 +32260,10 @@
         <v>1.55</v>
       </c>
       <c r="O196">
+        <v>4</v>
+      </c>
+      <c r="P196">
         <v>4.4</v>
-      </c>
-      <c r="P196">
-        <v>4.6</v>
       </c>
       <c r="Q196">
         <v>2</v>
@@ -32272,7 +32272,7 @@
         <v>2.55</v>
       </c>
       <c r="S196">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T196">
         <v>4</v>
@@ -32327,7 +32327,7 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AK196">
         <v>2.33</v>
@@ -32447,7 +32447,7 @@
         <v>1.62</v>
       </c>
       <c r="W197">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X197">
         <v>1.02</v>
@@ -32459,7 +32459,7 @@
         <v>5</v>
       </c>
       <c r="AA197">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB197">
         <v>2.35</v>
@@ -32764,7 +32764,7 @@
         <v>1.22</v>
       </c>
       <c r="T199">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="U199">
         <v>2.2</v>
@@ -32927,7 +32927,7 @@
         <v>1.22</v>
       </c>
       <c r="T200">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="U200">
         <v>2.05</v>
@@ -32936,7 +32936,7 @@
         <v>1.67</v>
       </c>
       <c r="W200">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X200">
         <v>1.02</v>
@@ -33075,7 +33075,7 @@
         <v>1.38</v>
       </c>
       <c r="O201">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="P201">
         <v>6.5</v>
@@ -33235,13 +33235,13 @@
         </is>
       </c>
       <c r="N202">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="O202">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="P202">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q202">
         <v>2.45</v>
@@ -33274,10 +33274,10 @@
         <v>4.15</v>
       </c>
       <c r="AA202">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AB202">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC202">
         <v>2.66</v>
@@ -33404,7 +33404,7 @@
         <v>3.18</v>
       </c>
       <c r="P203">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="Q203">
         <v>0</v>
@@ -33567,10 +33567,10 @@
         <v>3.78</v>
       </c>
       <c r="P204">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="Q204">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R204">
         <v>2.12</v>
@@ -33797,7 +33797,7 @@
         <v>1.14</v>
       </c>
       <c r="AK205">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="AL205">
         <v>0</v>
@@ -34865,7 +34865,7 @@
         </is>
       </c>
       <c r="N212">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="O212">
         <v>4.05</v>
@@ -34880,13 +34880,13 @@
         <v>2.5</v>
       </c>
       <c r="S212">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T212">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U212">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="V212">
         <v>1.67</v>
@@ -35028,13 +35028,13 @@
         </is>
       </c>
       <c r="N213">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="O213">
         <v>4.2</v>
       </c>
       <c r="P213">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q213">
         <v>5</v>
@@ -35098,7 +35098,7 @@
         </is>
       </c>
       <c r="AJ213">
-        <v>1.21</v>
+        <v>2.32</v>
       </c>
       <c r="AK213">
         <v>1.15</v>
@@ -36009,7 +36009,7 @@
         <v>1.96</v>
       </c>
       <c r="O219">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="P219">
         <v>3.25</v>
@@ -36018,7 +36018,7 @@
         <v>2.5</v>
       </c>
       <c r="R219">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S219">
         <v>1.3</v>
@@ -36039,10 +36039,10 @@
         <v>1</v>
       </c>
       <c r="Y219">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z219">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AA219">
         <v>1.74</v>
@@ -36051,7 +36051,7 @@
         <v>2.08</v>
       </c>
       <c r="AC219">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AD219">
         <v>1.36</v>
@@ -36060,7 +36060,7 @@
         <v>1.13</v>
       </c>
       <c r="AF219">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AG219">
         <v>2.15</v>
@@ -36076,10 +36076,10 @@
         </is>
       </c>
       <c r="AJ219">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK219">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AL219">
         <v>0</v>
@@ -36172,7 +36172,7 @@
         <v>2.6</v>
       </c>
       <c r="O220">
-        <v>3.67</v>
+        <v>3.6</v>
       </c>
       <c r="P220">
         <v>2.3</v>
@@ -36377,10 +36377,10 @@
         <v>2.8</v>
       </c>
       <c r="AC221">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AD221">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AE221">
         <v>1.31</v>
@@ -36495,7 +36495,7 @@
         </is>
       </c>
       <c r="N222">
-        <v>3.09</v>
+        <v>2.87</v>
       </c>
       <c r="O222">
         <v>3</v>
@@ -36528,19 +36528,19 @@
         <v>1.05</v>
       </c>
       <c r="Y222">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z222">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AA222">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB222">
         <v>1.68</v>
       </c>
       <c r="AC222">
-        <v>3.42</v>
+        <v>3.9</v>
       </c>
       <c r="AD222">
         <v>1.23</v>
@@ -36568,7 +36568,7 @@
         <v>1.27</v>
       </c>
       <c r="AK222">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AL222">
         <v>0</v>
@@ -36664,7 +36664,7 @@
         <v>3.4</v>
       </c>
       <c r="P223">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="Q223">
         <v>2.36</v>
@@ -36830,55 +36830,55 @@
         <v>0</v>
       </c>
       <c r="Q224">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R224">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S224">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T224">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U224">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V224">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W224">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X224">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y224">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z224">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AA224">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB224">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC224">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AD224">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE224">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF224">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG224">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH224" t="inlineStr">
         <is>
@@ -36891,10 +36891,10 @@
         </is>
       </c>
       <c r="AJ224">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK224">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL224">
         <v>0</v>
@@ -36993,55 +36993,55 @@
         <v>0</v>
       </c>
       <c r="Q225">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R225">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S225">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T225">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U225">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V225">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W225">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X225">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y225">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z225">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA225">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB225">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC225">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD225">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE225">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF225">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG225">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH225" t="inlineStr">
         <is>
@@ -37054,10 +37054,10 @@
         </is>
       </c>
       <c r="AJ225">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK225">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL225">
         <v>0</v>
@@ -37325,10 +37325,10 @@
         <v>2.3</v>
       </c>
       <c r="S227">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T227">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U227">
         <v>2.62</v>
@@ -37364,10 +37364,10 @@
         <v>1.11</v>
       </c>
       <c r="AF227">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AG227">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AH227" t="inlineStr">
         <is>
@@ -37645,55 +37645,55 @@
         <v>0</v>
       </c>
       <c r="Q229">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R229">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S229">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T229">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U229">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V229">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W229">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X229">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y229">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z229">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA229">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB229">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC229">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD229">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE229">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF229">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG229">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH229" t="inlineStr">
         <is>
@@ -37706,10 +37706,10 @@
         </is>
       </c>
       <c r="AJ229">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK229">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL229">
         <v>0</v>
@@ -37853,10 +37853,10 @@
         <v>1.2</v>
       </c>
       <c r="AF230">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AG230">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="AH230" t="inlineStr">
         <is>
@@ -38288,13 +38288,13 @@
         </is>
       </c>
       <c r="N233">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="O233">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="P233">
-        <v>3.52</v>
+        <v>3.45</v>
       </c>
       <c r="Q233">
         <v>2.5</v>
@@ -38804,7 +38804,7 @@
         <v>1.51</v>
       </c>
       <c r="W236">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X236">
         <v>0</v>
@@ -40087,7 +40087,7 @@
         <v>3.95</v>
       </c>
       <c r="P244">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="Q244">
         <v>2.1</v>
@@ -40102,10 +40102,10 @@
         <v>3.3</v>
       </c>
       <c r="U244">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="V244">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W244">
         <v>1.12</v>
@@ -40120,16 +40120,16 @@
         <v>4.25</v>
       </c>
       <c r="AA244">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AB244">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AC244">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="AD244">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE244">
         <v>1.17</v>
@@ -40151,10 +40151,10 @@
         </is>
       </c>
       <c r="AJ244">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK244">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AL244">
         <v>0</v>
@@ -40274,7 +40274,7 @@
         <v>1.11</v>
       </c>
       <c r="X245">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y245">
         <v>1.24</v>
@@ -40413,7 +40413,7 @@
         <v>5.15</v>
       </c>
       <c r="P246">
-        <v>7.4</v>
+        <v>6.75</v>
       </c>
       <c r="Q246">
         <v>1.8</v>
@@ -40449,13 +40449,13 @@
         <v>1.52</v>
       </c>
       <c r="AB246">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="AC246">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AD246">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AE246">
         <v>1.2</v>
@@ -40733,13 +40733,13 @@
         </is>
       </c>
       <c r="N248">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="O248">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P248">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q248">
         <v>2.3</v>
@@ -40760,7 +40760,7 @@
         <v>1.5</v>
       </c>
       <c r="W248">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X248">
         <v>1.01</v>
@@ -40896,19 +40896,19 @@
         </is>
       </c>
       <c r="N249">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="O249">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P249">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Q249">
         <v>2.37</v>
       </c>
       <c r="R249">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="S249">
         <v>1.42</v>
@@ -40923,7 +40923,7 @@
         <v>1.31</v>
       </c>
       <c r="W249">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X249">
         <v>1.02</v>
@@ -40950,10 +40950,10 @@
         <v>1.02</v>
       </c>
       <c r="AF249">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AG249">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AH249" t="inlineStr">
         <is>
@@ -41059,7 +41059,7 @@
         </is>
       </c>
       <c r="N250">
-        <v>3.09</v>
+        <v>2.99</v>
       </c>
       <c r="O250">
         <v>3.4</v>
@@ -41074,49 +41074,49 @@
         <v>2.13</v>
       </c>
       <c r="S250">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="T250">
-        <v>2.77</v>
+        <v>2.91</v>
       </c>
       <c r="U250">
-        <v>2.68</v>
+        <v>2.79</v>
       </c>
       <c r="V250">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="W250">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X250">
         <v>1.03</v>
       </c>
       <c r="Y250">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z250">
-        <v>3.72</v>
+        <v>3.81</v>
       </c>
       <c r="AA250">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AB250">
         <v>2</v>
       </c>
       <c r="AC250">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="AD250">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE250">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF250">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG250">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AH250" t="inlineStr">
         <is>
@@ -41129,7 +41129,7 @@
         </is>
       </c>
       <c r="AJ250">
-        <v>1.25</v>
+        <v>1.59</v>
       </c>
       <c r="AK250">
         <v>1.35</v>
@@ -41228,7 +41228,7 @@
         <v>4.33</v>
       </c>
       <c r="P251">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q251">
         <v>1.9</v>
@@ -41295,7 +41295,7 @@
         <v>1.12</v>
       </c>
       <c r="AK251">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="AL251">
         <v>0</v>
@@ -41711,13 +41711,13 @@
         </is>
       </c>
       <c r="N254">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="O254">
-        <v>3.42</v>
+        <v>3.1</v>
       </c>
       <c r="P254">
-        <v>3.32</v>
+        <v>3.05</v>
       </c>
       <c r="Q254">
         <v>2.8</v>
@@ -41765,10 +41765,10 @@
         <v>1.08</v>
       </c>
       <c r="AF254">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AG254">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AH254" t="inlineStr">
         <is>
@@ -41883,7 +41883,7 @@
         <v>2.45</v>
       </c>
       <c r="Q255">
-        <v>2.83</v>
+        <v>2.76</v>
       </c>
       <c r="R255">
         <v>2.04</v>
@@ -41913,7 +41913,7 @@
         <v>3.34</v>
       </c>
       <c r="AA255">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AB255">
         <v>1.83</v>
@@ -41928,10 +41928,10 @@
         <v>1.07</v>
       </c>
       <c r="AF255">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG255">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AH255" t="inlineStr">
         <is>
@@ -41947,7 +41947,7 @@
         <v>1.25</v>
       </c>
       <c r="AK255">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AL255">
         <v>0</v>
@@ -42046,7 +42046,7 @@
         <v>2.3</v>
       </c>
       <c r="Q256">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R256">
         <v>2</v>
@@ -42110,7 +42110,7 @@
         <v>1.43</v>
       </c>
       <c r="AK256">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AL256">
         <v>0</v>
@@ -42245,10 +42245,10 @@
         <v>2.84</v>
       </c>
       <c r="AC257">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AD257">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AE257">
         <v>1.33</v>
@@ -42366,7 +42366,7 @@
         <v>4</v>
       </c>
       <c r="O258">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="P258">
         <v>1.6</v>
@@ -42535,16 +42535,16 @@
         <v>1.73</v>
       </c>
       <c r="Q259">
-        <v>4.5</v>
+        <v>3.77</v>
       </c>
       <c r="R259">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S259">
         <v>1.27</v>
       </c>
       <c r="T259">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="U259">
         <v>2.4</v>
@@ -42553,7 +42553,7 @@
         <v>1.5</v>
       </c>
       <c r="W259">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X259">
         <v>1.03</v>
@@ -42568,7 +42568,7 @@
         <v>1.68</v>
       </c>
       <c r="AB259">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC259">
         <v>2.7</v>
@@ -42580,10 +42580,10 @@
         <v>1.13</v>
       </c>
       <c r="AF259">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG259">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH259" t="inlineStr">
         <is>
@@ -42870,13 +42870,13 @@
         <v>1.25</v>
       </c>
       <c r="T261">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U261">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="V261">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="W261">
         <v>1.1</v>
@@ -42885,16 +42885,16 @@
         <v>1.01</v>
       </c>
       <c r="Y261">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z261">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AA261">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AB261">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AC261">
         <v>2.45</v>
@@ -43015,13 +43015,13 @@
         </is>
       </c>
       <c r="N262">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="O262">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P262">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="Q262">
         <v>3.2</v>
@@ -43057,7 +43057,7 @@
         <v>1.74</v>
       </c>
       <c r="AB262">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AC262">
         <v>2.69</v>
@@ -43504,25 +43504,25 @@
         </is>
       </c>
       <c r="N265">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="O265">
-        <v>3.7</v>
+        <v>4.05</v>
       </c>
       <c r="P265">
-        <v>1.7</v>
+        <v>1.42</v>
       </c>
       <c r="Q265">
-        <v>5.13</v>
+        <v>6.34</v>
       </c>
       <c r="R265">
-        <v>2.07</v>
+        <v>2.22</v>
       </c>
       <c r="S265">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="T265">
-        <v>2.83</v>
+        <v>3.08</v>
       </c>
       <c r="U265">
         <v>2.75</v>
@@ -43531,53 +43531,53 @@
         <v>1.4</v>
       </c>
       <c r="W265">
+        <v>1.1</v>
+      </c>
+      <c r="X265">
+        <v>1</v>
+      </c>
+      <c r="Y265">
+        <v>1.22</v>
+      </c>
+      <c r="Z265">
+        <v>3.5</v>
+      </c>
+      <c r="AA265">
+        <v>1.95</v>
+      </c>
+      <c r="AB265">
+        <v>1.91</v>
+      </c>
+      <c r="AC265">
+        <v>2.97</v>
+      </c>
+      <c r="AD265">
+        <v>1.3</v>
+      </c>
+      <c r="AE265">
+        <v>1.07</v>
+      </c>
+      <c r="AF265">
+        <v>1.9</v>
+      </c>
+      <c r="AG265">
+        <v>1.78</v>
+      </c>
+      <c r="AH265" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI265" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ265">
+        <v>2.5</v>
+      </c>
+      <c r="AK265">
         <v>1.08</v>
-      </c>
-      <c r="X265">
-        <v>1.02</v>
-      </c>
-      <c r="Y265">
-        <v>1.24</v>
-      </c>
-      <c r="Z265">
-        <v>3.34</v>
-      </c>
-      <c r="AA265">
-        <v>1.85</v>
-      </c>
-      <c r="AB265">
-        <v>1.83</v>
-      </c>
-      <c r="AC265">
-        <v>3.14</v>
-      </c>
-      <c r="AD265">
-        <v>1.27</v>
-      </c>
-      <c r="AE265">
-        <v>1.06</v>
-      </c>
-      <c r="AF265">
-        <v>1.8</v>
-      </c>
-      <c r="AG265">
-        <v>1.88</v>
-      </c>
-      <c r="AH265" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI265" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ265">
-        <v>1.91</v>
-      </c>
-      <c r="AK265">
-        <v>1.16</v>
       </c>
       <c r="AL265">
         <v>0</v>
@@ -43673,7 +43673,7 @@
         <v>3.1</v>
       </c>
       <c r="P266">
-        <v>2.55</v>
+        <v>2.44</v>
       </c>
       <c r="Q266">
         <v>3.41</v>
@@ -43830,10 +43830,10 @@
         </is>
       </c>
       <c r="N267">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O267">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P267">
         <v>2.3</v>
@@ -43881,7 +43881,7 @@
         <v>1.46</v>
       </c>
       <c r="AE267">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AF267">
         <v>1.5</v>
@@ -44017,7 +44017,7 @@
         <v>2.17</v>
       </c>
       <c r="V268">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W268">
         <v>1.15</v>
@@ -44032,7 +44032,7 @@
         <v>4.63</v>
       </c>
       <c r="AA268">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AB268">
         <v>2.32</v>
@@ -44162,10 +44162,10 @@
         <v>3.3</v>
       </c>
       <c r="P269">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q269">
-        <v>3.44</v>
+        <v>3.75</v>
       </c>
       <c r="R269">
         <v>2.09</v>
@@ -44195,7 +44195,7 @@
         <v>3.9</v>
       </c>
       <c r="AA269">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="AB269">
         <v>1.98</v>
@@ -44331,7 +44331,7 @@
         <v>2.62</v>
       </c>
       <c r="R270">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="S270">
         <v>1.32</v>
@@ -44485,7 +44485,7 @@
         <v>2.38</v>
       </c>
       <c r="O271">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="P271">
         <v>2.96</v>
@@ -44503,7 +44503,7 @@
         <v>3</v>
       </c>
       <c r="U271">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="V271">
         <v>1.4</v>
@@ -44552,10 +44552,10 @@
         </is>
       </c>
       <c r="AJ271">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK271">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AL271">
         <v>0</v>
@@ -44817,55 +44817,55 @@
         <v>0</v>
       </c>
       <c r="Q273">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R273">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S273">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T273">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U273">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V273">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W273">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X273">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y273">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z273">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA273">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB273">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC273">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD273">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE273">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF273">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG273">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH273" t="inlineStr">
         <is>
@@ -44878,10 +44878,10 @@
         </is>
       </c>
       <c r="AJ273">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK273">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL273">
         <v>0</v>
@@ -44974,10 +44974,10 @@
         <v>4</v>
       </c>
       <c r="O274">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P274">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="Q274">
         <v>4.45</v>
@@ -45016,7 +45016,7 @@
         <v>1.93</v>
       </c>
       <c r="AC274">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="AD274">
         <v>1.38</v>
@@ -45312,16 +45312,16 @@
         <v>2.1</v>
       </c>
       <c r="S276">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T276">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="U276">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="V276">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W276">
         <v>1.07</v>
@@ -45336,10 +45336,10 @@
         <v>2.97</v>
       </c>
       <c r="AA276">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="AB276">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AC276">
         <v>3.34</v>
@@ -45623,64 +45623,64 @@
         </is>
       </c>
       <c r="N278">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O278">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P278">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q278">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R278">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S278">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T278">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U278">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="V278">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W278">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X278">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y278">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z278">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AA278">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB278">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC278">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AD278">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE278">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF278">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG278">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH278" t="inlineStr">
         <is>
@@ -45693,10 +45693,10 @@
         </is>
       </c>
       <c r="AJ278">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK278">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL278">
         <v>0</v>
@@ -45786,64 +45786,64 @@
         </is>
       </c>
       <c r="N279">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O279">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P279">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q279">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R279">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S279">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T279">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U279">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V279">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W279">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X279">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y279">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z279">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA279">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB279">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC279">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD279">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE279">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF279">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG279">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH279" t="inlineStr">
         <is>
@@ -45856,10 +45856,10 @@
         </is>
       </c>
       <c r="AJ279">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AK279">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL279">
         <v>0</v>
@@ -46169,7 +46169,7 @@
         <v>1.63</v>
       </c>
       <c r="AG281">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AH281" t="inlineStr">
         <is>
@@ -46293,7 +46293,7 @@
         <v>1.38</v>
       </c>
       <c r="T282">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="U282">
         <v>2.59</v>
@@ -46314,16 +46314,16 @@
         <v>3.5</v>
       </c>
       <c r="AA282">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AB282">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC282">
         <v>3.05</v>
       </c>
       <c r="AD282">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AE282">
         <v>1.07</v>
@@ -46447,7 +46447,7 @@
         <v>2.19</v>
       </c>
       <c r="Q283">
-        <v>3.8</v>
+        <v>3.59</v>
       </c>
       <c r="R283">
         <v>1.89</v>
@@ -46511,7 +46511,7 @@
         <v>1.55</v>
       </c>
       <c r="AK283">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AL283">
         <v>0</v>
@@ -46622,10 +46622,10 @@
         <v>3.8</v>
       </c>
       <c r="U284">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="V284">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W284">
         <v>1.17</v>
@@ -46643,7 +46643,7 @@
         <v>1.5</v>
       </c>
       <c r="AB284">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="AC284">
         <v>2.3</v>
@@ -46764,19 +46764,19 @@
         </is>
       </c>
       <c r="N285">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="O285">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P285">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="Q285">
-        <v>2.24</v>
+        <v>2.29</v>
       </c>
       <c r="R285">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="S285">
         <v>1.25</v>
@@ -46785,10 +46785,10 @@
         <v>3.5</v>
       </c>
       <c r="U285">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="V285">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W285">
         <v>1.14</v>
@@ -46800,19 +46800,19 @@
         <v>1.13</v>
       </c>
       <c r="Z285">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="AA285">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AB285">
-        <v>2.35</v>
+        <v>2.22</v>
       </c>
       <c r="AC285">
-        <v>2.53</v>
+        <v>2.43</v>
       </c>
       <c r="AD285">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE285">
         <v>1.14</v>
@@ -46834,10 +46834,10 @@
         </is>
       </c>
       <c r="AJ285">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AK285">
-        <v>2.07</v>
+        <v>1.99</v>
       </c>
       <c r="AL285">
         <v>0</v>
@@ -46930,10 +46930,10 @@
         <v>1.38</v>
       </c>
       <c r="O286">
-        <v>4.35</v>
+        <v>4.42</v>
       </c>
       <c r="P286">
-        <v>5.8</v>
+        <v>6.25</v>
       </c>
       <c r="Q286">
         <v>1.95</v>
@@ -46945,7 +46945,7 @@
         <v>1.3</v>
       </c>
       <c r="T286">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U286">
         <v>2.5</v>
@@ -46966,10 +46966,10 @@
         <v>4</v>
       </c>
       <c r="AA286">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AB286">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AC286">
         <v>2.84</v>
@@ -46981,10 +46981,10 @@
         <v>1.13</v>
       </c>
       <c r="AF286">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AG286">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AH286" t="inlineStr">
         <is>
@@ -47000,7 +47000,7 @@
         <v>1.17</v>
       </c>
       <c r="AK286">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="AL286">
         <v>0</v>
@@ -47099,10 +47099,10 @@
         <v>4.6</v>
       </c>
       <c r="Q287">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="R287">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="S287">
         <v>1.23</v>
@@ -47160,10 +47160,10 @@
         </is>
       </c>
       <c r="AJ287">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK287">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AL287">
         <v>0</v>
@@ -47259,7 +47259,7 @@
         <v>3.75</v>
       </c>
       <c r="P288">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="Q288">
         <v>2.33</v>
@@ -47585,7 +47585,7 @@
         <v>3.95</v>
       </c>
       <c r="P290">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="Q290">
         <v>0</v>
@@ -47784,7 +47784,7 @@
         <v>1.66</v>
       </c>
       <c r="AB291">
-        <v>1.96</v>
+        <v>2.15</v>
       </c>
       <c r="AC291">
         <v>2.78</v>
@@ -47947,7 +47947,7 @@
         <v>1.28</v>
       </c>
       <c r="AB292">
-        <v>3.6</v>
+        <v>3.08</v>
       </c>
       <c r="AC292">
         <v>1.74</v>
@@ -47962,7 +47962,7 @@
         <v>1.6</v>
       </c>
       <c r="AG292">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AH292" t="inlineStr">
         <is>
@@ -48394,7 +48394,7 @@
         </is>
       </c>
       <c r="N295">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="O295">
         <v>3.8</v>
@@ -48439,7 +48439,7 @@
         <v>2.48</v>
       </c>
       <c r="AC295">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="AD295">
         <v>1.66</v>
@@ -48464,7 +48464,7 @@
         </is>
       </c>
       <c r="AJ295">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK295">
         <v>1.94</v>
@@ -48581,7 +48581,7 @@
         <v>2.66</v>
       </c>
       <c r="V296">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W296">
         <v>1.05</v>
@@ -48602,7 +48602,7 @@
         <v>1.89</v>
       </c>
       <c r="AC296">
-        <v>3.52</v>
+        <v>3.36</v>
       </c>
       <c r="AD296">
         <v>1.31</v>
@@ -48611,7 +48611,7 @@
         <v>1.07</v>
       </c>
       <c r="AF296">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG296">
         <v>2.15</v>
@@ -49215,7 +49215,7 @@
         <v>3.68</v>
       </c>
       <c r="P300">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q300">
         <v>2.48</v>
@@ -49224,16 +49224,16 @@
         <v>2.34</v>
       </c>
       <c r="S300">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T300">
         <v>3.1</v>
       </c>
       <c r="U300">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="V300">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W300">
         <v>1.08</v>
@@ -49248,16 +49248,16 @@
         <v>4.24</v>
       </c>
       <c r="AA300">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AB300">
         <v>2.16</v>
       </c>
       <c r="AC300">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="AD300">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE300">
         <v>1.15</v>
@@ -49279,7 +49279,7 @@
         </is>
       </c>
       <c r="AJ300">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK300">
         <v>1.73</v>
@@ -49381,55 +49381,55 @@
         <v>0</v>
       </c>
       <c r="Q301">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R301">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S301">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T301">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U301">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V301">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W301">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X301">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y301">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z301">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AA301">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AB301">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC301">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AD301">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE301">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF301">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG301">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AH301" t="inlineStr">
         <is>
@@ -49442,10 +49442,10 @@
         </is>
       </c>
       <c r="AJ301">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK301">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL301">
         <v>0</v>
@@ -50350,13 +50350,13 @@
         </is>
       </c>
       <c r="N307">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="O307">
         <v>3.3</v>
       </c>
       <c r="P307">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="Q307">
         <v>2.73</v>
@@ -50519,7 +50519,7 @@
         <v>3.5</v>
       </c>
       <c r="P308">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="Q308">
         <v>2.3</v>
@@ -50531,7 +50531,7 @@
         <v>1.45</v>
       </c>
       <c r="T308">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="U308">
         <v>3.29</v>
@@ -50552,13 +50552,13 @@
         <v>2.94</v>
       </c>
       <c r="AA308">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AB308">
         <v>1.63</v>
       </c>
       <c r="AC308">
-        <v>4.13</v>
+        <v>4.12</v>
       </c>
       <c r="AD308">
         <v>1.23</v>
@@ -50854,7 +50854,7 @@
         <v>2.08</v>
       </c>
       <c r="S310">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T310">
         <v>3.02</v>
@@ -50878,7 +50878,7 @@
         <v>3.2</v>
       </c>
       <c r="AA310">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AB310">
         <v>1.88</v>
@@ -50909,7 +50909,7 @@
         </is>
       </c>
       <c r="AJ310">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK310">
         <v>1.83</v>
@@ -51171,58 +51171,58 @@
         <v>2.85</v>
       </c>
       <c r="P312">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q312">
-        <v>3.1</v>
+        <v>3.32</v>
       </c>
       <c r="R312">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="S312">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="T312">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="U312">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="V312">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="W312">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X312">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Y312">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="Z312">
-        <v>2.27</v>
+        <v>2.04</v>
       </c>
       <c r="AA312">
-        <v>3.1</v>
+        <v>3.21</v>
       </c>
       <c r="AB312">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AC312">
-        <v>5.3</v>
+        <v>6.45</v>
       </c>
       <c r="AD312">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AE312">
         <v>1.01</v>
       </c>
       <c r="AF312">
-        <v>2.19</v>
+        <v>2.4</v>
       </c>
       <c r="AG312">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AH312" t="inlineStr">
         <is>
@@ -51235,10 +51235,10 @@
         </is>
       </c>
       <c r="AJ312">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AK312">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AL312">
         <v>0</v>
@@ -51401,7 +51401,7 @@
         <v>1.18</v>
       </c>
       <c r="AK313">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AL313">
         <v>0</v>
@@ -51491,13 +51491,13 @@
         </is>
       </c>
       <c r="N314">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="O314">
-        <v>3.98</v>
+        <v>3.9</v>
       </c>
       <c r="P314">
-        <v>3.01</v>
+        <v>2.75</v>
       </c>
       <c r="Q314">
         <v>2.63</v>
@@ -51527,7 +51527,7 @@
         <v>1.13</v>
       </c>
       <c r="Z314">
-        <v>5.74</v>
+        <v>5.3</v>
       </c>
       <c r="AA314">
         <v>1.39</v>
@@ -51660,7 +51660,7 @@
         <v>4.2</v>
       </c>
       <c r="P315">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="Q315">
         <v>2.05</v>
@@ -52170,7 +52170,7 @@
         <v>1.24</v>
       </c>
       <c r="W318">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X318">
         <v>1.1</v>
@@ -53936,7 +53936,7 @@
         </is>
       </c>
       <c r="N329">
-        <v>2.79</v>
+        <v>2.73</v>
       </c>
       <c r="O329">
         <v>4.02</v>
@@ -54301,7 +54301,7 @@
         <v>3.05</v>
       </c>
       <c r="AA331">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB331">
         <v>1.74</v>
@@ -54461,10 +54461,10 @@
         <v>1.18</v>
       </c>
       <c r="Z332">
-        <v>4.78</v>
+        <v>4.8</v>
       </c>
       <c r="AA332">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AB332">
         <v>2.27</v>
@@ -54479,7 +54479,7 @@
         <v>1.18</v>
       </c>
       <c r="AF332">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG332">
         <v>2.4</v>
@@ -54498,7 +54498,7 @@
         <v>1.25</v>
       </c>
       <c r="AK332">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AL332">
         <v>0</v>

--- a/jogos_2026-11-01.xlsx
+++ b/jogos_2026-11-01.xlsx
@@ -3445,7 +3445,7 @@
         <v>4.1</v>
       </c>
       <c r="AA19">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AB19">
         <v>2.2</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>La Nucía</t>
+          <t>Peña Deportiva</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,65 +8133,65 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.08</v>
+        <v>3.8</v>
       </c>
       <c r="O48">
-        <v>3.12</v>
+        <v>3.6</v>
       </c>
       <c r="P48">
-        <v>3.28</v>
+        <v>1.8</v>
       </c>
       <c r="Q48">
-        <v>2.78</v>
+        <v>4</v>
       </c>
       <c r="R48">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="S48">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T48">
+        <v>2.8</v>
+      </c>
+      <c r="U48">
         <v>2.65</v>
       </c>
-      <c r="U48">
-        <v>2.9</v>
-      </c>
       <c r="V48">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W48">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X48">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z48">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="AA48">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AB48">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AC48">
-        <v>3.84</v>
+        <v>3.2</v>
       </c>
       <c r="AD48">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AE48">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF48">
+        <v>1.83</v>
+      </c>
+      <c r="AG48">
         <v>1.85</v>
       </c>
-      <c r="AG48">
-        <v>1.84</v>
-      </c>
       <c r="AH48" t="inlineStr">
         <is>
           <t>[]</t>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.26</v>
+        <v>1.73</v>
       </c>
       <c r="AK48">
-        <v>1.59</v>
+        <v>1.3</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Peña Deportiva</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Mallorca II</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,58 +8296,58 @@
         </is>
       </c>
       <c r="N49">
+        <v>1.53</v>
+      </c>
+      <c r="O49">
         <v>3.8</v>
       </c>
-      <c r="O49">
-        <v>3.6</v>
-      </c>
       <c r="P49">
-        <v>1.8</v>
+        <v>5.3</v>
       </c>
       <c r="Q49">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="R49">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S49">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T49">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="U49">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="V49">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W49">
         <v>1.08</v>
       </c>
       <c r="X49">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
+        <v>1.23</v>
+      </c>
+      <c r="Z49">
+        <v>3.42</v>
+      </c>
+      <c r="AA49">
+        <v>1.75</v>
+      </c>
+      <c r="AB49">
+        <v>2.05</v>
+      </c>
+      <c r="AC49">
+        <v>3.05</v>
+      </c>
+      <c r="AD49">
         <v>1.28</v>
       </c>
-      <c r="Z49">
-        <v>3.08</v>
-      </c>
-      <c r="AA49">
-        <v>1.93</v>
-      </c>
-      <c r="AB49">
-        <v>1.75</v>
-      </c>
-      <c r="AC49">
-        <v>3.2</v>
-      </c>
-      <c r="AD49">
-        <v>1.26</v>
-      </c>
       <c r="AE49">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF49">
         <v>1.83</v>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="AK49">
-        <v>1.3</v>
+        <v>2.15</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>La Nucía</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mallorca II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.53</v>
+        <v>2.08</v>
       </c>
       <c r="O50">
-        <v>3.8</v>
+        <v>3.12</v>
       </c>
       <c r="P50">
-        <v>5.3</v>
+        <v>3.28</v>
       </c>
       <c r="Q50">
+        <v>2.78</v>
+      </c>
+      <c r="R50">
+        <v>1.97</v>
+      </c>
+      <c r="S50">
+        <v>1.38</v>
+      </c>
+      <c r="T50">
+        <v>2.65</v>
+      </c>
+      <c r="U50">
+        <v>2.9</v>
+      </c>
+      <c r="V50">
+        <v>1.32</v>
+      </c>
+      <c r="W50">
+        <v>1.04</v>
+      </c>
+      <c r="X50">
+        <v>1.03</v>
+      </c>
+      <c r="Y50">
+        <v>1.32</v>
+      </c>
+      <c r="Z50">
+        <v>2.88</v>
+      </c>
+      <c r="AA50">
         <v>2.1</v>
       </c>
-      <c r="R50">
-        <v>2.25</v>
-      </c>
-      <c r="S50">
-        <v>1.3</v>
-      </c>
-      <c r="T50">
-        <v>3.2</v>
-      </c>
-      <c r="U50">
-        <v>2.62</v>
-      </c>
-      <c r="V50">
-        <v>1.4</v>
-      </c>
-      <c r="W50">
-        <v>1.08</v>
-      </c>
-      <c r="X50">
-        <v>1.01</v>
-      </c>
-      <c r="Y50">
-        <v>1.23</v>
-      </c>
-      <c r="Z50">
-        <v>3.42</v>
-      </c>
-      <c r="AA50">
-        <v>1.75</v>
-      </c>
       <c r="AB50">
-        <v>2.05</v>
+        <v>1.63</v>
       </c>
       <c r="AC50">
-        <v>3.05</v>
+        <v>3.84</v>
       </c>
       <c r="AD50">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AE50">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF50">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG50">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK50">
-        <v>2.15</v>
+        <v>1.59</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -9932,7 +9932,7 @@
         <v>5.75</v>
       </c>
       <c r="P59">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="Q59">
         <v>1.62</v>
@@ -14490,7 +14490,7 @@
         </is>
       </c>
       <c r="N87">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="O87">
         <v>3.75</v>
@@ -17430,7 +17430,7 @@
         <v>3.32</v>
       </c>
       <c r="P105">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q105">
         <v>2.75</v>
@@ -17445,7 +17445,7 @@
         <v>2.56</v>
       </c>
       <c r="U105">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="V105">
         <v>1.36</v>
@@ -19066,7 +19066,7 @@
         <v>3</v>
       </c>
       <c r="R115">
-        <v>2.49</v>
+        <v>2.63</v>
       </c>
       <c r="S115">
         <v>1.14</v>
@@ -19718,13 +19718,13 @@
         <v>4.5</v>
       </c>
       <c r="R119">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="S119">
         <v>1.22</v>
       </c>
       <c r="T119">
-        <v>3.9</v>
+        <v>3.76</v>
       </c>
       <c r="U119">
         <v>2.05</v>
@@ -19875,7 +19875,7 @@
         <v>3.8</v>
       </c>
       <c r="P120">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q120">
         <v>3.1</v>
@@ -23956,13 +23956,13 @@
         <v>1.91</v>
       </c>
       <c r="R145">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S145">
         <v>1.33</v>
       </c>
       <c r="T145">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="U145">
         <v>2.6</v>
@@ -23974,16 +23974,16 @@
         <v>1.08</v>
       </c>
       <c r="X145">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y145">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z145">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AA145">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AB145">
         <v>2</v>
@@ -23998,10 +23998,10 @@
         <v>1.13</v>
       </c>
       <c r="AF145">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AG145">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24017,7 +24017,7 @@
         <v>1.06</v>
       </c>
       <c r="AK145">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24107,64 +24107,64 @@
         </is>
       </c>
       <c r="N146">
-        <v>2.31</v>
+        <v>2.13</v>
       </c>
       <c r="O146">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="P146">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="Q146">
-        <v>2.76</v>
+        <v>2.61</v>
       </c>
       <c r="R146">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="S146">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="T146">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U146">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="V146">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="W146">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X146">
         <v>1</v>
       </c>
       <c r="Y146">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z146">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA146">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AB146">
-        <v>2.61</v>
+        <v>3</v>
       </c>
       <c r="AC146">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AD146">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AE146">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AF146">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG146">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK146">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24614,7 +24614,7 @@
         <v>1.36</v>
       </c>
       <c r="T149">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="U149">
         <v>2.92</v>
@@ -24759,7 +24759,7 @@
         </is>
       </c>
       <c r="N150">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="O150">
         <v>3.7</v>
@@ -24768,13 +24768,13 @@
         <v>2.6</v>
       </c>
       <c r="Q150">
-        <v>2.97</v>
+        <v>3.12</v>
       </c>
       <c r="R150">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S150">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T150">
         <v>3.4</v>
@@ -24798,13 +24798,13 @@
         <v>4.6</v>
       </c>
       <c r="AA150">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB150">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="AC150">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="AD150">
         <v>1.47</v>
@@ -24829,7 +24829,7 @@
         </is>
       </c>
       <c r="AJ150">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK150">
         <v>1.45</v>
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G172">
@@ -28345,64 +28345,64 @@
         </is>
       </c>
       <c r="N172">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O172">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P172">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q172">
         <v>2.3</v>
       </c>
       <c r="R172">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="S172">
+        <v>1.35</v>
+      </c>
+      <c r="T172">
+        <v>3</v>
+      </c>
+      <c r="U172">
+        <v>2.62</v>
+      </c>
+      <c r="V172">
         <v>1.4</v>
       </c>
-      <c r="T172">
-        <v>2.65</v>
-      </c>
-      <c r="U172">
-        <v>2.81</v>
-      </c>
-      <c r="V172">
-        <v>1.34</v>
-      </c>
       <c r="W172">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X172">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y172">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="Z172">
-        <v>2.97</v>
+        <v>3.42</v>
       </c>
       <c r="AA172">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AB172">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AC172">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="AD172">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AE172">
         <v>1.07</v>
       </c>
       <c r="AF172">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AG172">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AH172" t="inlineStr">
         <is>
@@ -28415,10 +28415,10 @@
         </is>
       </c>
       <c r="AJ172">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK172">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G173">
@@ -28508,80 +28508,80 @@
         </is>
       </c>
       <c r="N173">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="O173">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P173">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q173">
         <v>2.3</v>
       </c>
       <c r="R173">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="S173">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T173">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="U173">
-        <v>2.62</v>
+        <v>2.81</v>
       </c>
       <c r="V173">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="W173">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X173">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y173">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="Z173">
-        <v>3.42</v>
+        <v>2.97</v>
       </c>
       <c r="AA173">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AB173">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AC173">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="AD173">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AE173">
         <v>1.07</v>
       </c>
       <c r="AF173">
+        <v>1.92</v>
+      </c>
+      <c r="AG173">
         <v>1.75</v>
       </c>
-      <c r="AG173">
+      <c r="AH173" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI173" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ173">
+        <v>1.22</v>
+      </c>
+      <c r="AK173">
         <v>1.95</v>
-      </c>
-      <c r="AH173" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI173" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ173">
-        <v>1.21</v>
-      </c>
-      <c r="AK173">
-        <v>2</v>
       </c>
       <c r="AL173">
         <v>0</v>
@@ -33766,7 +33766,7 @@
         <v>1.51</v>
       </c>
       <c r="AB205">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AC205">
         <v>2.34</v>
@@ -34868,10 +34868,10 @@
         <v>1.75</v>
       </c>
       <c r="O212">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="P212">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="Q212">
         <v>2.2</v>
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G220">
@@ -36169,64 +36169,64 @@
         </is>
       </c>
       <c r="N220">
-        <v>2.6</v>
+        <v>1.51</v>
       </c>
       <c r="O220">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="P220">
-        <v>2.3</v>
+        <v>5.25</v>
       </c>
       <c r="Q220">
-        <v>3.15</v>
+        <v>1.89</v>
       </c>
       <c r="R220">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="S220">
         <v>1.22</v>
       </c>
       <c r="T220">
-        <v>3.56</v>
+        <v>4.1</v>
       </c>
       <c r="U220">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="V220">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="W220">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X220">
         <v>1</v>
       </c>
       <c r="Y220">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z220">
-        <v>4.8</v>
+        <v>6.5</v>
       </c>
       <c r="AA220">
+        <v>1.43</v>
+      </c>
+      <c r="AB220">
+        <v>2.8</v>
+      </c>
+      <c r="AC220">
+        <v>2.05</v>
+      </c>
+      <c r="AD220">
+        <v>1.79</v>
+      </c>
+      <c r="AE220">
+        <v>1.31</v>
+      </c>
+      <c r="AF220">
         <v>1.53</v>
       </c>
-      <c r="AB220">
-        <v>2.3</v>
-      </c>
-      <c r="AC220">
-        <v>2.25</v>
-      </c>
-      <c r="AD220">
-        <v>1.55</v>
-      </c>
-      <c r="AE220">
-        <v>1.2</v>
-      </c>
-      <c r="AF220">
-        <v>1.43</v>
-      </c>
       <c r="AG220">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="AH220" t="inlineStr">
         <is>
@@ -36239,10 +36239,10 @@
         </is>
       </c>
       <c r="AJ220">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK220">
-        <v>1.38</v>
+        <v>2.42</v>
       </c>
       <c r="AL220">
         <v>0</v>
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G221">
@@ -36332,64 +36332,64 @@
         </is>
       </c>
       <c r="N221">
-        <v>1.51</v>
+        <v>2.6</v>
       </c>
       <c r="O221">
-        <v>4.5</v>
+        <v>3.67</v>
       </c>
       <c r="P221">
-        <v>6</v>
+        <v>2.3</v>
       </c>
       <c r="Q221">
-        <v>1.89</v>
+        <v>3.15</v>
       </c>
       <c r="R221">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="S221">
         <v>1.22</v>
       </c>
       <c r="T221">
-        <v>4.1</v>
+        <v>3.56</v>
       </c>
       <c r="U221">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="V221">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="W221">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X221">
         <v>1</v>
       </c>
       <c r="Y221">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z221">
-        <v>6.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA221">
+        <v>1.53</v>
+      </c>
+      <c r="AB221">
+        <v>2.3</v>
+      </c>
+      <c r="AC221">
+        <v>2.25</v>
+      </c>
+      <c r="AD221">
+        <v>1.55</v>
+      </c>
+      <c r="AE221">
+        <v>1.2</v>
+      </c>
+      <c r="AF221">
         <v>1.43</v>
       </c>
-      <c r="AB221">
-        <v>2.8</v>
-      </c>
-      <c r="AC221">
-        <v>2.05</v>
-      </c>
-      <c r="AD221">
-        <v>1.79</v>
-      </c>
-      <c r="AE221">
-        <v>1.31</v>
-      </c>
-      <c r="AF221">
-        <v>1.53</v>
-      </c>
       <c r="AG221">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="AH221" t="inlineStr">
         <is>
@@ -36402,10 +36402,10 @@
         </is>
       </c>
       <c r="AJ221">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AK221">
-        <v>2.42</v>
+        <v>1.38</v>
       </c>
       <c r="AL221">
         <v>0</v>
@@ -41575,7 +41575,7 @@
         <v>1.33</v>
       </c>
       <c r="W253">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X253">
         <v>1.02</v>
@@ -41883,7 +41883,7 @@
         <v>2.45</v>
       </c>
       <c r="Q255">
-        <v>2.76</v>
+        <v>2.81</v>
       </c>
       <c r="R255">
         <v>2.04</v>
@@ -41913,22 +41913,22 @@
         <v>3.34</v>
       </c>
       <c r="AA255">
+        <v>1.83</v>
+      </c>
+      <c r="AB255">
         <v>1.84</v>
       </c>
-      <c r="AB255">
-        <v>1.83</v>
-      </c>
       <c r="AC255">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="AD255">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE255">
         <v>1.07</v>
       </c>
       <c r="AF255">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG255">
         <v>2.01</v>
@@ -41947,7 +41947,7 @@
         <v>1.25</v>
       </c>
       <c r="AK255">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL255">
         <v>0</v>
@@ -42233,16 +42233,16 @@
         <v>1</v>
       </c>
       <c r="Y257">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z257">
-        <v>5.92</v>
+        <v>5.98</v>
       </c>
       <c r="AA257">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AB257">
-        <v>2.84</v>
+        <v>2.89</v>
       </c>
       <c r="AC257">
         <v>2.05</v>
@@ -42254,10 +42254,10 @@
         <v>1.33</v>
       </c>
       <c r="AF257">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AG257">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="AH257" t="inlineStr">
         <is>
@@ -42270,10 +42270,10 @@
         </is>
       </c>
       <c r="AJ257">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK257">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="AL257">
         <v>0</v>
@@ -43543,7 +43543,7 @@
         <v>3.5</v>
       </c>
       <c r="AA265">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AB265">
         <v>1.91</v>
@@ -43558,7 +43558,7 @@
         <v>1.07</v>
       </c>
       <c r="AF265">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG265">
         <v>1.78</v>
@@ -43667,16 +43667,16 @@
         </is>
       </c>
       <c r="N266">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O266">
         <v>3.1</v>
       </c>
       <c r="P266">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="Q266">
-        <v>3.41</v>
+        <v>3.47</v>
       </c>
       <c r="R266">
         <v>1.92</v>
@@ -43700,28 +43700,28 @@
         <v>1.06</v>
       </c>
       <c r="Y266">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="Z266">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="AA266">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="AB266">
         <v>1.57</v>
       </c>
       <c r="AC266">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AD266">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AE266">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF266">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AG266">
         <v>1.75</v>
@@ -43737,10 +43737,10 @@
         </is>
       </c>
       <c r="AJ266">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AK266">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AL266">
         <v>0</v>
@@ -44974,7 +44974,7 @@
         <v>4</v>
       </c>
       <c r="O274">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="P274">
         <v>1.85</v>
@@ -44992,7 +44992,7 @@
         <v>2.86</v>
       </c>
       <c r="U274">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="V274">
         <v>1.46</v>
@@ -45102,12 +45102,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G275">
@@ -45134,16 +45134,16 @@
         </is>
       </c>
       <c r="N275">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O275">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P275">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q275">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="R275">
         <v>2.1</v>
@@ -45152,10 +45152,10 @@
         <v>1.36</v>
       </c>
       <c r="T275">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U275">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="V275">
         <v>1.36</v>
@@ -45164,35 +45164,35 @@
         <v>1.07</v>
       </c>
       <c r="X275">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y275">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z275">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="AA275">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AB275">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AC275">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AD275">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE275">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF275">
+        <v>1.91</v>
+      </c>
+      <c r="AG275">
         <v>1.75</v>
       </c>
-      <c r="AG275">
-        <v>1.91</v>
-      </c>
       <c r="AH275" t="inlineStr">
         <is>
           <t>[]</t>
@@ -45204,10 +45204,10 @@
         </is>
       </c>
       <c r="AJ275">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK275">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AL275">
         <v>0</v>
@@ -45265,12 +45265,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="G276">
@@ -45297,16 +45297,16 @@
         </is>
       </c>
       <c r="N276">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O276">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P276">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q276">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="R276">
         <v>2.1</v>
@@ -45315,10 +45315,10 @@
         <v>1.36</v>
       </c>
       <c r="T276">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U276">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="V276">
         <v>1.36</v>
@@ -45327,35 +45327,35 @@
         <v>1.07</v>
       </c>
       <c r="X276">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y276">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z276">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="AA276">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AB276">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AC276">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AD276">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE276">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF276">
+        <v>1.75</v>
+      </c>
+      <c r="AG276">
         <v>1.91</v>
       </c>
-      <c r="AG276">
-        <v>1.75</v>
-      </c>
       <c r="AH276" t="inlineStr">
         <is>
           <t>[]</t>
@@ -45367,10 +45367,10 @@
         </is>
       </c>
       <c r="AJ276">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK276">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AL276">
         <v>0</v>
@@ -46643,7 +46643,7 @@
         <v>1.5</v>
       </c>
       <c r="AB284">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="AC284">
         <v>2.3</v>
@@ -46966,10 +46966,10 @@
         <v>4</v>
       </c>
       <c r="AA286">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB286">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC286">
         <v>2.84</v>
@@ -48560,7 +48560,7 @@
         <v>2.2</v>
       </c>
       <c r="O296">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P296">
         <v>3.24</v>
@@ -48599,22 +48599,22 @@
         <v>1.97</v>
       </c>
       <c r="AB296">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AC296">
         <v>3.36</v>
       </c>
       <c r="AD296">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AE296">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF296">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG296">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH296" t="inlineStr">
         <is>
@@ -48627,7 +48627,7 @@
         </is>
       </c>
       <c r="AJ296">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK296">
         <v>1.57</v>

--- a/jogos_2026-11-01.xlsx
+++ b/jogos_2026-11-01.xlsx
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.71</v>
+        <v>2.43</v>
       </c>
       <c r="O17">
         <v>3.35</v>
@@ -3732,7 +3732,7 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="O21">
         <v>5.5</v>
@@ -3771,7 +3771,7 @@
         <v>4.66</v>
       </c>
       <c r="AA21">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB21">
         <v>2.19</v>
@@ -4112,7 +4112,7 @@
         <v>1.03</v>
       </c>
       <c r="AF23">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AG23">
         <v>1.8</v>
@@ -4230,10 +4230,10 @@
         <v>5</v>
       </c>
       <c r="Q24">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="R24">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="S24">
         <v>1.29</v>
@@ -4411,7 +4411,7 @@
         <v>1.44</v>
       </c>
       <c r="W25">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X25">
         <v>1.03</v>
@@ -4438,10 +4438,10 @@
         <v>1.09</v>
       </c>
       <c r="AF25">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG25">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4556,10 +4556,10 @@
         <v>0</v>
       </c>
       <c r="Q26">
-        <v>2.46</v>
+        <v>2.51</v>
       </c>
       <c r="R26">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="S26">
         <v>1.3</v>
@@ -4583,7 +4583,7 @@
         <v>1.2</v>
       </c>
       <c r="Z26">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="AA26">
         <v>1.78</v>
@@ -4620,7 +4620,7 @@
         <v>1.22</v>
       </c>
       <c r="AK26">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="O31">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P31">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="Q31">
         <v>2.43</v>
       </c>
       <c r="R31">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="S31">
+        <v>1.46</v>
+      </c>
+      <c r="T31">
+        <v>2.55</v>
+      </c>
+      <c r="U31">
+        <v>3.3</v>
+      </c>
+      <c r="V31">
+        <v>1.31</v>
+      </c>
+      <c r="W31">
+        <v>1.04</v>
+      </c>
+      <c r="X31">
+        <v>1.03</v>
+      </c>
+      <c r="Y31">
         <v>1.36</v>
       </c>
-      <c r="T31">
-        <v>2.75</v>
-      </c>
-      <c r="U31">
-        <v>2.8</v>
-      </c>
-      <c r="V31">
-        <v>1.36</v>
-      </c>
-      <c r="W31">
-        <v>1.07</v>
-      </c>
-      <c r="X31">
+      <c r="Z31">
+        <v>2.7</v>
+      </c>
+      <c r="AA31">
+        <v>2.18</v>
+      </c>
+      <c r="AB31">
+        <v>1.65</v>
+      </c>
+      <c r="AC31">
+        <v>4</v>
+      </c>
+      <c r="AD31">
+        <v>1.17</v>
+      </c>
+      <c r="AE31">
         <v>1.02</v>
       </c>
-      <c r="Y31">
-        <v>1.32</v>
-      </c>
-      <c r="Z31">
-        <v>2.88</v>
-      </c>
-      <c r="AA31">
-        <v>2.07</v>
-      </c>
-      <c r="AB31">
-        <v>1.72</v>
-      </c>
-      <c r="AC31">
-        <v>3.7</v>
-      </c>
-      <c r="AD31">
-        <v>1.2</v>
-      </c>
-      <c r="AE31">
-        <v>1.03</v>
-      </c>
       <c r="AF31">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG31">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AK31">
         <v>1.85</v>
@@ -5691,7 +5691,7 @@
         <v>2.2</v>
       </c>
       <c r="O33">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P33">
         <v>2.85</v>
@@ -5709,10 +5709,10 @@
         <v>2.8</v>
       </c>
       <c r="U33">
-        <v>2.9</v>
+        <v>3.02</v>
       </c>
       <c r="V33">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="W33">
         <v>1.02</v>
@@ -7194,7 +7194,7 @@
         <v>3.88</v>
       </c>
       <c r="AA42">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB42">
         <v>1.99</v>
@@ -7520,10 +7520,10 @@
         <v>3.58</v>
       </c>
       <c r="AA44">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AB44">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="AC44">
         <v>2.92</v>
@@ -7701,7 +7701,7 @@
         <v>1.73</v>
       </c>
       <c r="AG45">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>1.73</v>
       </c>
       <c r="AK48">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>La Nucía</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mallorca II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.53</v>
+        <v>2.08</v>
       </c>
       <c r="O49">
-        <v>3.8</v>
+        <v>3.12</v>
       </c>
       <c r="P49">
-        <v>5.3</v>
+        <v>3.28</v>
       </c>
       <c r="Q49">
+        <v>2.78</v>
+      </c>
+      <c r="R49">
+        <v>1.97</v>
+      </c>
+      <c r="S49">
+        <v>1.38</v>
+      </c>
+      <c r="T49">
+        <v>2.65</v>
+      </c>
+      <c r="U49">
+        <v>2.9</v>
+      </c>
+      <c r="V49">
+        <v>1.32</v>
+      </c>
+      <c r="W49">
+        <v>1.04</v>
+      </c>
+      <c r="X49">
+        <v>1.03</v>
+      </c>
+      <c r="Y49">
+        <v>1.32</v>
+      </c>
+      <c r="Z49">
+        <v>2.88</v>
+      </c>
+      <c r="AA49">
         <v>2.1</v>
       </c>
-      <c r="R49">
-        <v>2.25</v>
-      </c>
-      <c r="S49">
-        <v>1.3</v>
-      </c>
-      <c r="T49">
-        <v>3.2</v>
-      </c>
-      <c r="U49">
-        <v>2.62</v>
-      </c>
-      <c r="V49">
-        <v>1.4</v>
-      </c>
-      <c r="W49">
-        <v>1.08</v>
-      </c>
-      <c r="X49">
-        <v>1.01</v>
-      </c>
-      <c r="Y49">
-        <v>1.23</v>
-      </c>
-      <c r="Z49">
-        <v>3.42</v>
-      </c>
-      <c r="AA49">
-        <v>1.75</v>
-      </c>
       <c r="AB49">
-        <v>2.05</v>
+        <v>1.63</v>
       </c>
       <c r="AC49">
-        <v>3.05</v>
+        <v>3.84</v>
       </c>
       <c r="AD49">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AE49">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF49">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG49">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK49">
-        <v>2.15</v>
+        <v>1.59</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>La Nucía</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Mallorca II</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,65 +8459,65 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.08</v>
+        <v>1.53</v>
       </c>
       <c r="O50">
-        <v>3.12</v>
+        <v>3.8</v>
       </c>
       <c r="P50">
-        <v>3.28</v>
+        <v>5.3</v>
       </c>
       <c r="Q50">
-        <v>2.78</v>
+        <v>2.1</v>
       </c>
       <c r="R50">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="S50">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T50">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="U50">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="V50">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="W50">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X50">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="Z50">
-        <v>2.88</v>
+        <v>3.42</v>
       </c>
       <c r="AA50">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AB50">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AC50">
-        <v>3.84</v>
+        <v>3.04</v>
       </c>
       <c r="AD50">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AE50">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF50">
+        <v>1.83</v>
+      </c>
+      <c r="AG50">
         <v>1.85</v>
       </c>
-      <c r="AG50">
-        <v>1.84</v>
-      </c>
       <c r="AH50" t="inlineStr">
         <is>
           <t>[]</t>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK50">
-        <v>1.59</v>
+        <v>2.15</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8827,7 +8827,7 @@
         <v>1.59</v>
       </c>
       <c r="AB52">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="AC52">
         <v>2.52</v>
@@ -9476,7 +9476,7 @@
         <v>2.83</v>
       </c>
       <c r="AA56">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB56">
         <v>1.63</v>
@@ -9953,7 +9953,7 @@
         <v>1.75</v>
       </c>
       <c r="W59">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X59">
         <v>1</v>
@@ -9968,10 +9968,10 @@
         <v>1.36</v>
       </c>
       <c r="AB59">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AC59">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AD59">
         <v>1.84</v>
@@ -9999,7 +9999,7 @@
         <v>1.1</v>
       </c>
       <c r="AK59">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10098,10 +10098,10 @@
         <v>0</v>
       </c>
       <c r="Q60">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="R60">
-        <v>2.89</v>
+        <v>3.3</v>
       </c>
       <c r="S60">
         <v>1.14</v>
@@ -10122,10 +10122,10 @@
         <v>1</v>
       </c>
       <c r="Y60">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Z60">
-        <v>9.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA60">
         <v>1.28</v>
@@ -10134,13 +10134,13 @@
         <v>3.6</v>
       </c>
       <c r="AC60">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AD60">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AE60">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AF60">
         <v>1.63</v>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>4.33</v>
+        <v>1.11</v>
       </c>
       <c r="AK60">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10261,71 +10261,71 @@
         <v>0</v>
       </c>
       <c r="Q61">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="R61">
+        <v>2.5</v>
+      </c>
+      <c r="S61">
+        <v>1.17</v>
+      </c>
+      <c r="T61">
+        <v>3.98</v>
+      </c>
+      <c r="U61">
+        <v>2.13</v>
+      </c>
+      <c r="V61">
+        <v>1.67</v>
+      </c>
+      <c r="W61">
+        <v>1.2</v>
+      </c>
+      <c r="X61">
+        <v>1.02</v>
+      </c>
+      <c r="Y61">
+        <v>1.08</v>
+      </c>
+      <c r="Z61">
+        <v>5.5</v>
+      </c>
+      <c r="AA61">
+        <v>1.4</v>
+      </c>
+      <c r="AB61">
+        <v>2.56</v>
+      </c>
+      <c r="AC61">
+        <v>2.08</v>
+      </c>
+      <c r="AD61">
+        <v>1.64</v>
+      </c>
+      <c r="AE61">
+        <v>1.23</v>
+      </c>
+      <c r="AF61">
+        <v>1.55</v>
+      </c>
+      <c r="AG61">
+        <v>2.25</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ61">
+        <v>1.18</v>
+      </c>
+      <c r="AK61">
         <v>2.62</v>
-      </c>
-      <c r="S61">
-        <v>1.16</v>
-      </c>
-      <c r="T61">
-        <v>4.1</v>
-      </c>
-      <c r="U61">
-        <v>1.95</v>
-      </c>
-      <c r="V61">
-        <v>1.71</v>
-      </c>
-      <c r="W61">
-        <v>1.17</v>
-      </c>
-      <c r="X61">
-        <v>1.01</v>
-      </c>
-      <c r="Y61">
-        <v>1.07</v>
-      </c>
-      <c r="Z61">
-        <v>5.9</v>
-      </c>
-      <c r="AA61">
-        <v>1.36</v>
-      </c>
-      <c r="AB61">
-        <v>2.7</v>
-      </c>
-      <c r="AC61">
-        <v>1.96</v>
-      </c>
-      <c r="AD61">
-        <v>1.72</v>
-      </c>
-      <c r="AE61">
-        <v>1.27</v>
-      </c>
-      <c r="AF61">
-        <v>1.62</v>
-      </c>
-      <c r="AG61">
-        <v>2.15</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ61">
-        <v>1.15</v>
-      </c>
-      <c r="AK61">
-        <v>3.25</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10928,7 +10928,7 @@
         <v>2.45</v>
       </c>
       <c r="V65">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W65">
         <v>1.12</v>
@@ -11067,10 +11067,10 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="O66">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P66">
         <v>3.3</v>
@@ -11094,7 +11094,7 @@
         <v>1.47</v>
       </c>
       <c r="W66">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X66">
         <v>1.03</v>
@@ -11287,7 +11287,7 @@
         <v>1.7</v>
       </c>
       <c r="AG67">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11408,19 +11408,19 @@
         <v>2.05</v>
       </c>
       <c r="S68">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T68">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="U68">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="V68">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W68">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X68">
         <v>1.04</v>
@@ -13355,7 +13355,7 @@
         <v>3.08</v>
       </c>
       <c r="P80">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="Q80">
         <v>4.05</v>
@@ -13512,19 +13512,19 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O81">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P81">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="Q81">
-        <v>2.79</v>
+        <v>2.82</v>
       </c>
       <c r="R81">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="S81">
         <v>1.25</v>
@@ -13536,13 +13536,13 @@
         <v>2.3</v>
       </c>
       <c r="V81">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W81">
         <v>1.1</v>
       </c>
       <c r="X81">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y81">
         <v>1.13</v>
@@ -13563,7 +13563,7 @@
         <v>1.49</v>
       </c>
       <c r="AE81">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF81">
         <v>1.47</v>
@@ -13678,7 +13678,7 @@
         <v>2.1</v>
       </c>
       <c r="O82">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P82">
         <v>2.85</v>
@@ -14058,7 +14058,7 @@
         <v>1.44</v>
       </c>
       <c r="AG84">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="O85">
         <v>3.63</v>
@@ -14188,7 +14188,7 @@
         <v>2.25</v>
       </c>
       <c r="V85">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W85">
         <v>1.12</v>
@@ -14237,7 +14237,7 @@
         <v>1.2</v>
       </c>
       <c r="AK85">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14327,7 +14327,7 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="O86">
         <v>4.8</v>
@@ -14822,7 +14822,7 @@
         <v>3.63</v>
       </c>
       <c r="P89">
-        <v>4.02</v>
+        <v>3.48</v>
       </c>
       <c r="Q89">
         <v>2.34</v>
@@ -14870,10 +14870,10 @@
         <v>1.13</v>
       </c>
       <c r="AF89">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG89">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         <v>1.36</v>
       </c>
       <c r="O90">
-        <v>5.35</v>
+        <v>5.1</v>
       </c>
       <c r="P90">
         <v>7.5</v>
@@ -15963,16 +15963,16 @@
         <v>3.2</v>
       </c>
       <c r="P96">
-        <v>2.9</v>
+        <v>3.12</v>
       </c>
       <c r="Q96">
-        <v>2.89</v>
+        <v>2.96</v>
       </c>
       <c r="R96">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="S96">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T96">
         <v>3.02</v>
@@ -16162,7 +16162,7 @@
         <v>2.5</v>
       </c>
       <c r="AB97">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AC97">
         <v>5.75</v>
@@ -16283,31 +16283,31 @@
         </is>
       </c>
       <c r="N98">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="O98">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="P98">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="Q98">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="R98">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S98">
         <v>1.25</v>
       </c>
       <c r="T98">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U98">
         <v>2.25</v>
       </c>
       <c r="V98">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="W98">
         <v>1.15</v>
@@ -16316,31 +16316,31 @@
         <v>1.01</v>
       </c>
       <c r="Y98">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z98">
-        <v>4.8</v>
+        <v>4.76</v>
       </c>
       <c r="AA98">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AB98">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AC98">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="AD98">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AE98">
         <v>1.18</v>
       </c>
       <c r="AF98">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG98">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK98">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -17107,10 +17107,10 @@
         <v>0</v>
       </c>
       <c r="Q103">
-        <v>3.78</v>
+        <v>4</v>
       </c>
       <c r="R103">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S103">
         <v>1.33</v>
@@ -17122,10 +17122,10 @@
         <v>2.62</v>
       </c>
       <c r="V103">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W103">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X103">
         <v>1</v>
@@ -18423,13 +18423,13 @@
         <v>2.9</v>
       </c>
       <c r="U111">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="V111">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W111">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X111">
         <v>1.01</v>
@@ -19416,7 +19416,7 @@
         <v>1.1</v>
       </c>
       <c r="Z117">
-        <v>5.46</v>
+        <v>5.45</v>
       </c>
       <c r="AA117">
         <v>1.47</v>
@@ -19869,13 +19869,13 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="O120">
         <v>3.8</v>
       </c>
       <c r="P120">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="Q120">
         <v>3.1</v>
@@ -20521,7 +20521,7 @@
         </is>
       </c>
       <c r="N124">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="O124">
         <v>3.1</v>
@@ -20684,7 +20684,7 @@
         </is>
       </c>
       <c r="N125">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="O125">
         <v>3.1</v>
@@ -20741,7 +20741,7 @@
         <v>1.75</v>
       </c>
       <c r="AG125">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20886,10 +20886,10 @@
         <v>3.5</v>
       </c>
       <c r="AA126">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="AB126">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC126">
         <v>3.35</v>
@@ -21019,10 +21019,10 @@
         <v>2.15</v>
       </c>
       <c r="Q127">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="R127">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="S127">
         <v>1.36</v>
@@ -21046,7 +21046,7 @@
         <v>1.23</v>
       </c>
       <c r="Z127">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AA127">
         <v>1.87</v>
@@ -21514,7 +21514,7 @@
         <v>2.57</v>
       </c>
       <c r="S130">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T130">
         <v>3.6</v>
@@ -21698,7 +21698,7 @@
         <v>1.44</v>
       </c>
       <c r="Z131">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="AA131">
         <v>2.35</v>
@@ -21825,10 +21825,10 @@
         </is>
       </c>
       <c r="N132">
-        <v>3.1</v>
+        <v>3.76</v>
       </c>
       <c r="O132">
-        <v>3.45</v>
+        <v>3.82</v>
       </c>
       <c r="P132">
         <v>1.97</v>
@@ -21855,7 +21855,7 @@
         <v>1.14</v>
       </c>
       <c r="X132">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y132">
         <v>1.13</v>
@@ -21864,10 +21864,10 @@
         <v>4.6</v>
       </c>
       <c r="AA132">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="AB132">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AC132">
         <v>2.27</v>
@@ -21997,7 +21997,7 @@
         <v>2.45</v>
       </c>
       <c r="Q133">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R133">
         <v>2.04</v>
@@ -22042,10 +22042,10 @@
         <v>1.06</v>
       </c>
       <c r="AF133">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AG133">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22061,7 +22061,7 @@
         <v>1.34</v>
       </c>
       <c r="AK133">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="O134">
+        <v>3.2</v>
+      </c>
+      <c r="P134">
         <v>3.1</v>
       </c>
-      <c r="P134">
-        <v>3.43</v>
-      </c>
       <c r="Q134">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="R134">
         <v>2.1</v>
       </c>
       <c r="S134">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T134">
         <v>2.88</v>
       </c>
       <c r="U134">
-        <v>2.77</v>
+        <v>2.65</v>
       </c>
       <c r="V134">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W134">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X134">
         <v>1.01</v>
       </c>
       <c r="Y134">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Z134">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="AA134">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="AB134">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AC134">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="AD134">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AE134">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF134">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AG134">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22224,7 +22224,7 @@
         <v>1.3</v>
       </c>
       <c r="AK134">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22371,7 +22371,7 @@
         <v>1.55</v>
       </c>
       <c r="AG135">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22661,7 +22661,7 @@
         <v>3</v>
       </c>
       <c r="U137">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="V137">
         <v>1.45</v>
@@ -23802,7 +23802,7 @@
         <v>3.1</v>
       </c>
       <c r="U144">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="V144">
         <v>1.5</v>
@@ -23947,10 +23947,10 @@
         <v>1.43</v>
       </c>
       <c r="O145">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="P145">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="Q145">
         <v>1.91</v>
@@ -23962,7 +23962,7 @@
         <v>1.33</v>
       </c>
       <c r="T145">
-        <v>3.13</v>
+        <v>3.17</v>
       </c>
       <c r="U145">
         <v>2.6</v>
@@ -24107,7 +24107,7 @@
         </is>
       </c>
       <c r="N146">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="O146">
         <v>3.9</v>
@@ -24119,7 +24119,7 @@
         <v>2.61</v>
       </c>
       <c r="R146">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="S146">
         <v>1.19</v>
@@ -24152,19 +24152,19 @@
         <v>3</v>
       </c>
       <c r="AC146">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AD146">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AE146">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF146">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AG146">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AK146">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24276,7 +24276,7 @@
         <v>3.64</v>
       </c>
       <c r="P147">
-        <v>4.85</v>
+        <v>4.55</v>
       </c>
       <c r="Q147">
         <v>2.37</v>
@@ -24638,7 +24638,7 @@
         <v>1.85</v>
       </c>
       <c r="AB149">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AC149">
         <v>3.42</v>
@@ -24765,7 +24765,7 @@
         <v>3.7</v>
       </c>
       <c r="P150">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="Q150">
         <v>3.12</v>
@@ -27080,7 +27080,7 @@
         <v>3.58</v>
       </c>
       <c r="AA164">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AB164">
         <v>2</v>
@@ -28185,61 +28185,61 @@
         <v>1.5</v>
       </c>
       <c r="O171">
-        <v>4.55</v>
+        <v>4.2</v>
       </c>
       <c r="P171">
-        <v>4.87</v>
+        <v>4.82</v>
       </c>
       <c r="Q171">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R171">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="S171">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T171">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="U171">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="V171">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="W171">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X171">
         <v>1.01</v>
       </c>
       <c r="Y171">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Z171">
-        <v>7</v>
+        <v>6.65</v>
       </c>
       <c r="AA171">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AB171">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="AC171">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AD171">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="AE171">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AF171">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AG171">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="AH171" t="inlineStr">
         <is>
@@ -28517,7 +28517,7 @@
         <v>0</v>
       </c>
       <c r="Q173">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="R173">
         <v>2.02</v>
@@ -28562,10 +28562,10 @@
         <v>1.07</v>
       </c>
       <c r="AF173">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AG173">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AH173" t="inlineStr">
         <is>
@@ -28581,7 +28581,7 @@
         <v>1.22</v>
       </c>
       <c r="AK173">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AL173">
         <v>0</v>
@@ -28680,10 +28680,10 @@
         <v>0</v>
       </c>
       <c r="Q174">
-        <v>3.01</v>
+        <v>3.06</v>
       </c>
       <c r="R174">
-        <v>1.94</v>
+        <v>2.07</v>
       </c>
       <c r="S174">
         <v>1.4</v>
@@ -28722,7 +28722,7 @@
         <v>1.19</v>
       </c>
       <c r="AE174">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF174">
         <v>1.85</v>
@@ -28834,7 +28834,7 @@
         </is>
       </c>
       <c r="N175">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="O175">
         <v>3.4</v>
@@ -28907,7 +28907,7 @@
         <v>1.21</v>
       </c>
       <c r="AK175">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -28997,13 +28997,13 @@
         </is>
       </c>
       <c r="N176">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="O176">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="P176">
-        <v>2.42</v>
+        <v>2.59</v>
       </c>
       <c r="Q176">
         <v>0</v>
@@ -31155,7 +31155,7 @@
         <v>3.58</v>
       </c>
       <c r="AA189">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB189">
         <v>1.98</v>
@@ -31478,7 +31478,7 @@
         <v>1.25</v>
       </c>
       <c r="Z191">
-        <v>3.77</v>
+        <v>3.79</v>
       </c>
       <c r="AA191">
         <v>1.84</v>
@@ -31487,7 +31487,7 @@
         <v>1.98</v>
       </c>
       <c r="AC191">
-        <v>3.11</v>
+        <v>2.7</v>
       </c>
       <c r="AD191">
         <v>1.36</v>
@@ -31512,7 +31512,7 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AK191">
         <v>1.49</v>
@@ -31611,7 +31611,7 @@
         <v>7.1</v>
       </c>
       <c r="P192">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Q192">
         <v>6.38</v>
@@ -31970,10 +31970,10 @@
         <v>2.88</v>
       </c>
       <c r="AA194">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AB194">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AC194">
         <v>3.58</v>
@@ -32124,7 +32124,7 @@
         <v>1.1</v>
       </c>
       <c r="X195">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y195">
         <v>1.17</v>
@@ -32136,7 +32136,7 @@
         <v>1.64</v>
       </c>
       <c r="AB195">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AC195">
         <v>2.59</v>
@@ -32444,7 +32444,7 @@
         <v>2.2</v>
       </c>
       <c r="V197">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W197">
         <v>1.11</v>
@@ -32589,7 +32589,7 @@
         <v>3.1</v>
       </c>
       <c r="P198">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="Q198">
         <v>3.06</v>
@@ -32819,7 +32819,7 @@
         <v>1.08</v>
       </c>
       <c r="AK199">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL199">
         <v>0</v>
@@ -32909,7 +32909,7 @@
         </is>
       </c>
       <c r="N200">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="O200">
         <v>3.8</v>
@@ -33072,19 +33072,19 @@
         </is>
       </c>
       <c r="N201">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="O201">
-        <v>4.5</v>
+        <v>5.15</v>
       </c>
       <c r="P201">
         <v>6.5</v>
       </c>
       <c r="Q201">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="R201">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="S201">
         <v>1.22</v>
@@ -33235,13 +33235,13 @@
         </is>
       </c>
       <c r="N202">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="O202">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P202">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="Q202">
         <v>2.45</v>
@@ -33567,7 +33567,7 @@
         <v>3.78</v>
       </c>
       <c r="P204">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="Q204">
         <v>2.3</v>
@@ -34868,7 +34868,7 @@
         <v>1.75</v>
       </c>
       <c r="O212">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="P212">
         <v>3.65</v>
@@ -35061,22 +35061,22 @@
         <v>1</v>
       </c>
       <c r="Y213">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z213">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="AA213">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB213">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC213">
         <v>2.69</v>
       </c>
       <c r="AD213">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AE213">
         <v>1.18</v>
@@ -35710,7 +35710,7 @@
         <v>1.06</v>
       </c>
       <c r="X217">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y217">
         <v>1.3</v>
@@ -35731,7 +35731,7 @@
         <v>1.22</v>
       </c>
       <c r="AE217">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF217">
         <v>1.82</v>
@@ -35974,12 +35974,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G219">
@@ -36006,64 +36006,64 @@
         </is>
       </c>
       <c r="N219">
-        <v>1.96</v>
+        <v>1.51</v>
       </c>
       <c r="O219">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="P219">
-        <v>3.25</v>
+        <v>5.25</v>
       </c>
       <c r="Q219">
-        <v>2.5</v>
+        <v>1.89</v>
       </c>
       <c r="R219">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="S219">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T219">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="U219">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="V219">
-        <v>1.44</v>
+        <v>1.72</v>
       </c>
       <c r="W219">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="X219">
         <v>1</v>
       </c>
       <c r="Y219">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="Z219">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="AA219">
-        <v>1.74</v>
+        <v>1.43</v>
       </c>
       <c r="AB219">
-        <v>2.08</v>
+        <v>2.8</v>
       </c>
       <c r="AC219">
-        <v>2.88</v>
+        <v>2.05</v>
       </c>
       <c r="AD219">
-        <v>1.36</v>
+        <v>1.79</v>
       </c>
       <c r="AE219">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="AF219">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AG219">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AH219" t="inlineStr">
         <is>
@@ -36076,10 +36076,10 @@
         </is>
       </c>
       <c r="AJ219">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK219">
-        <v>1.73</v>
+        <v>2.42</v>
       </c>
       <c r="AL219">
         <v>0</v>
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G220">
@@ -36169,64 +36169,64 @@
         </is>
       </c>
       <c r="N220">
-        <v>1.51</v>
+        <v>1.96</v>
       </c>
       <c r="O220">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="P220">
-        <v>5.25</v>
+        <v>3.25</v>
       </c>
       <c r="Q220">
-        <v>1.89</v>
+        <v>2.5</v>
       </c>
       <c r="R220">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="S220">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T220">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="U220">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="V220">
-        <v>1.72</v>
+        <v>1.44</v>
       </c>
       <c r="W220">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="X220">
         <v>1</v>
       </c>
       <c r="Y220">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="Z220">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="AA220">
-        <v>1.43</v>
+        <v>1.74</v>
       </c>
       <c r="AB220">
-        <v>2.8</v>
+        <v>2.08</v>
       </c>
       <c r="AC220">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="AD220">
-        <v>1.79</v>
+        <v>1.36</v>
       </c>
       <c r="AE220">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="AF220">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AG220">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="AH220" t="inlineStr">
         <is>
@@ -36239,10 +36239,10 @@
         </is>
       </c>
       <c r="AJ220">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AK220">
-        <v>2.42</v>
+        <v>1.73</v>
       </c>
       <c r="AL220">
         <v>0</v>
@@ -36495,10 +36495,10 @@
         </is>
       </c>
       <c r="N222">
-        <v>2.87</v>
+        <v>3.09</v>
       </c>
       <c r="O222">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="P222">
         <v>2.5</v>
@@ -36830,16 +36830,16 @@
         <v>0</v>
       </c>
       <c r="Q224">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="R224">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="S224">
         <v>1.5</v>
       </c>
       <c r="T224">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="U224">
         <v>3.4</v>
@@ -36854,19 +36854,19 @@
         <v>1.08</v>
       </c>
       <c r="Y224">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="Z224">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="AA224">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="AB224">
         <v>1.44</v>
       </c>
       <c r="AC224">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AD224">
         <v>1.1</v>
@@ -36894,7 +36894,7 @@
         <v>1.36</v>
       </c>
       <c r="AK224">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AL224">
         <v>0</v>
@@ -36996,13 +36996,13 @@
         <v>2.62</v>
       </c>
       <c r="R225">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S225">
         <v>1.35</v>
       </c>
       <c r="T225">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="U225">
         <v>2.7</v>
@@ -37023,10 +37023,10 @@
         <v>3.34</v>
       </c>
       <c r="AA225">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB225">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC225">
         <v>3.08</v>
@@ -37319,19 +37319,19 @@
         <v>6</v>
       </c>
       <c r="Q227">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="R227">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S227">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T227">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U227">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="V227">
         <v>1.4</v>
@@ -37343,10 +37343,10 @@
         <v>1.01</v>
       </c>
       <c r="Y227">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z227">
-        <v>3.48</v>
+        <v>3.34</v>
       </c>
       <c r="AA227">
         <v>1.75</v>
@@ -37355,19 +37355,19 @@
         <v>2.05</v>
       </c>
       <c r="AC227">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="AD227">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AE227">
         <v>1.11</v>
       </c>
       <c r="AF227">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AG227">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AH227" t="inlineStr">
         <is>
@@ -37380,10 +37380,10 @@
         </is>
       </c>
       <c r="AJ227">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK227">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="AL227">
         <v>0</v>
@@ -38001,10 +38001,10 @@
         <v>3.04</v>
       </c>
       <c r="AA231">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB231">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC231">
         <v>3.34</v>
@@ -38179,7 +38179,7 @@
         <v>1.04</v>
       </c>
       <c r="AF232">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AG232">
         <v>1.69</v>
@@ -38493,7 +38493,7 @@
         <v>1.7</v>
       </c>
       <c r="AB234">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AC234">
         <v>2.66</v>
@@ -40081,19 +40081,19 @@
         </is>
       </c>
       <c r="N244">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="O244">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="P244">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="Q244">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="R244">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S244">
         <v>1.3</v>
@@ -40102,10 +40102,10 @@
         <v>3.3</v>
       </c>
       <c r="U244">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="V244">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="W244">
         <v>1.12</v>
@@ -40114,10 +40114,10 @@
         <v>1.03</v>
       </c>
       <c r="Y244">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z244">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="AA244">
         <v>1.7</v>
@@ -40126,10 +40126,10 @@
         <v>2.1</v>
       </c>
       <c r="AC244">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="AD244">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE244">
         <v>1.17</v>
@@ -40151,10 +40151,10 @@
         </is>
       </c>
       <c r="AJ244">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK244">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AL244">
         <v>0</v>
@@ -40253,10 +40253,10 @@
         <v>2.89</v>
       </c>
       <c r="Q245">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="R245">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="S245">
         <v>1.3</v>
@@ -40280,7 +40280,7 @@
         <v>1.24</v>
       </c>
       <c r="Z245">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="AA245">
         <v>1.84</v>
@@ -40295,7 +40295,7 @@
         <v>1.41</v>
       </c>
       <c r="AE245">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF245">
         <v>1.62</v>
@@ -40407,13 +40407,13 @@
         </is>
       </c>
       <c r="N246">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="O246">
-        <v>5.15</v>
+        <v>4.85</v>
       </c>
       <c r="P246">
-        <v>6.75</v>
+        <v>7.4</v>
       </c>
       <c r="Q246">
         <v>1.8</v>
@@ -40609,10 +40609,10 @@
         <v>3.76</v>
       </c>
       <c r="AA247">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB247">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC247">
         <v>2.66</v>
@@ -40917,10 +40917,10 @@
         <v>2.51</v>
       </c>
       <c r="U249">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="V249">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W249">
         <v>1.06</v>
@@ -40950,10 +40950,10 @@
         <v>1.02</v>
       </c>
       <c r="AF249">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AG249">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AH249" t="inlineStr">
         <is>
@@ -41068,10 +41068,10 @@
         <v>2.3</v>
       </c>
       <c r="Q250">
-        <v>3.31</v>
+        <v>3.26</v>
       </c>
       <c r="R250">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="S250">
         <v>1.39</v>
@@ -41098,7 +41098,7 @@
         <v>3.81</v>
       </c>
       <c r="AA250">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AB250">
         <v>2</v>
@@ -41228,7 +41228,7 @@
         <v>4.33</v>
       </c>
       <c r="P251">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="Q251">
         <v>1.9</v>
@@ -41276,10 +41276,10 @@
         <v>1.21</v>
       </c>
       <c r="AF251">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AG251">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AH251" t="inlineStr">
         <is>
@@ -41292,7 +41292,7 @@
         </is>
       </c>
       <c r="AJ251">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK251">
         <v>2.6</v>
@@ -42218,7 +42218,7 @@
         <v>1.21</v>
       </c>
       <c r="T257">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="U257">
         <v>2</v>
@@ -42532,7 +42532,7 @@
         <v>3.9</v>
       </c>
       <c r="P259">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="Q259">
         <v>3.77</v>
@@ -42855,7 +42855,7 @@
         <v>1.28</v>
       </c>
       <c r="O261">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="P261">
         <v>8</v>
@@ -42897,13 +42897,13 @@
         <v>2.3</v>
       </c>
       <c r="AC261">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="AD261">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AE261">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF261">
         <v>2</v>
@@ -43024,10 +43024,10 @@
         <v>2.37</v>
       </c>
       <c r="Q262">
-        <v>3.2</v>
+        <v>3.11</v>
       </c>
       <c r="R262">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S262">
         <v>1.3</v>
@@ -43036,22 +43036,22 @@
         <v>3.2</v>
       </c>
       <c r="U262">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V262">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W262">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X262">
         <v>1.01</v>
       </c>
       <c r="Y262">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z262">
-        <v>3.72</v>
+        <v>3.74</v>
       </c>
       <c r="AA262">
         <v>1.74</v>
@@ -43060,10 +43060,10 @@
         <v>2.02</v>
       </c>
       <c r="AC262">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="AD262">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE262">
         <v>1.11</v>
@@ -43085,10 +43085,10 @@
         </is>
       </c>
       <c r="AJ262">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AK262">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL262">
         <v>0</v>
@@ -43199,10 +43199,10 @@
         <v>2.95</v>
       </c>
       <c r="U263">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="V263">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W263">
         <v>1.1</v>
@@ -43211,31 +43211,31 @@
         <v>1</v>
       </c>
       <c r="Y263">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z263">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="AA263">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AB263">
+        <v>1.93</v>
+      </c>
+      <c r="AC263">
+        <v>2.88</v>
+      </c>
+      <c r="AD263">
+        <v>1.32</v>
+      </c>
+      <c r="AE263">
+        <v>1.1</v>
+      </c>
+      <c r="AF263">
+        <v>1.8</v>
+      </c>
+      <c r="AG263">
         <v>1.89</v>
-      </c>
-      <c r="AC263">
-        <v>2.92</v>
-      </c>
-      <c r="AD263">
-        <v>1.31</v>
-      </c>
-      <c r="AE263">
-        <v>1.09</v>
-      </c>
-      <c r="AF263">
-        <v>1.81</v>
-      </c>
-      <c r="AG263">
-        <v>1.88</v>
       </c>
       <c r="AH263" t="inlineStr">
         <is>
@@ -43251,7 +43251,7 @@
         <v>1.18</v>
       </c>
       <c r="AK263">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AL263">
         <v>0</v>
@@ -43531,7 +43531,7 @@
         <v>1.4</v>
       </c>
       <c r="W265">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X265">
         <v>1</v>
@@ -43676,22 +43676,22 @@
         <v>2.45</v>
       </c>
       <c r="Q266">
-        <v>3.47</v>
+        <v>3.54</v>
       </c>
       <c r="R266">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="S266">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="T266">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="U266">
         <v>3.42</v>
       </c>
       <c r="V266">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W266">
         <v>1.06</v>
@@ -43703,7 +43703,7 @@
         <v>1.44</v>
       </c>
       <c r="Z266">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AA266">
         <v>2.44</v>
@@ -43721,7 +43721,7 @@
         <v>1.05</v>
       </c>
       <c r="AF266">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AG266">
         <v>1.75</v>
@@ -43836,7 +43836,7 @@
         <v>3.4</v>
       </c>
       <c r="P267">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q267">
         <v>3.25</v>
@@ -43866,13 +43866,13 @@
         <v>1.18</v>
       </c>
       <c r="Z267">
-        <v>4.69</v>
+        <v>4.67</v>
       </c>
       <c r="AA267">
         <v>1.6</v>
       </c>
       <c r="AB267">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AC267">
         <v>2.38</v>
@@ -43999,7 +43999,7 @@
         <v>3.6</v>
       </c>
       <c r="P268">
-        <v>3.41</v>
+        <v>3.3</v>
       </c>
       <c r="Q268">
         <v>2.4</v>
@@ -44156,13 +44156,13 @@
         </is>
       </c>
       <c r="N269">
+        <v>3.25</v>
+      </c>
+      <c r="O269">
         <v>3.2</v>
       </c>
-      <c r="O269">
-        <v>3.3</v>
-      </c>
       <c r="P269">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="Q269">
         <v>3.75</v>
@@ -44174,7 +44174,7 @@
         <v>1.35</v>
       </c>
       <c r="T269">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="U269">
         <v>2.62</v>
@@ -44195,19 +44195,19 @@
         <v>3.9</v>
       </c>
       <c r="AA269">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AB269">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AC269">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="AD269">
         <v>1.35</v>
       </c>
       <c r="AE269">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF269">
         <v>1.65</v>
@@ -44319,13 +44319,13 @@
         </is>
       </c>
       <c r="N270">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="O270">
         <v>3.4</v>
       </c>
       <c r="P270">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="Q270">
         <v>2.62</v>
@@ -44349,13 +44349,13 @@
         <v>1.07</v>
       </c>
       <c r="X270">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y270">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z270">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AA270">
         <v>1.8</v>
@@ -44364,7 +44364,7 @@
         <v>2</v>
       </c>
       <c r="AC270">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="AD270">
         <v>1.33</v>
@@ -44485,13 +44485,13 @@
         <v>2.38</v>
       </c>
       <c r="O271">
-        <v>3.36</v>
+        <v>3.4</v>
       </c>
       <c r="P271">
         <v>2.96</v>
       </c>
       <c r="Q271">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="R271">
         <v>2.1</v>
@@ -44515,25 +44515,25 @@
         <v>1.03</v>
       </c>
       <c r="Y271">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z271">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AA271">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AB271">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AC271">
-        <v>3.47</v>
+        <v>3.4</v>
       </c>
       <c r="AD271">
         <v>1.34</v>
       </c>
       <c r="AE271">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF271">
         <v>1.73</v>
@@ -44613,12 +44613,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>CD Badajoz</t>
+          <t>Ciudad de Lucena</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G272">
@@ -44645,64 +44645,64 @@
         </is>
       </c>
       <c r="N272">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O272">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P272">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="Q272">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R272">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S272">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T272">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U272">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V272">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W272">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X272">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y272">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z272">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA272">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB272">
+        <v>1.8</v>
+      </c>
+      <c r="AC272">
+        <v>3.5</v>
+      </c>
+      <c r="AD272">
+        <v>1.22</v>
+      </c>
+      <c r="AE272">
+        <v>1.05</v>
+      </c>
+      <c r="AF272">
         <v>1.85</v>
       </c>
-      <c r="AC272">
-        <v>0</v>
-      </c>
-      <c r="AD272">
-        <v>0</v>
-      </c>
-      <c r="AE272">
-        <v>0</v>
-      </c>
-      <c r="AF272">
-        <v>0</v>
-      </c>
       <c r="AG272">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH272" t="inlineStr">
         <is>
@@ -44715,10 +44715,10 @@
         </is>
       </c>
       <c r="AJ272">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK272">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL272">
         <v>0</v>
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Ciudad de Lucena</t>
+          <t>CD Badajoz</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G273">
@@ -44808,64 +44808,64 @@
         </is>
       </c>
       <c r="N273">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O273">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P273">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q273">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R273">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S273">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T273">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U273">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V273">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W273">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X273">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y273">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z273">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA273">
+        <v>1.95</v>
+      </c>
+      <c r="AB273">
         <v>1.85</v>
       </c>
-      <c r="AB273">
-        <v>1.95</v>
-      </c>
       <c r="AC273">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD273">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE273">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF273">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG273">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH273" t="inlineStr">
         <is>
@@ -44878,10 +44878,10 @@
         </is>
       </c>
       <c r="AJ273">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK273">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL273">
         <v>0</v>
@@ -45324,7 +45324,7 @@
         <v>1.36</v>
       </c>
       <c r="W276">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X276">
         <v>1.01</v>
@@ -45674,7 +45674,7 @@
         <v>1.12</v>
       </c>
       <c r="AE278">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF278">
         <v>1.95</v>
@@ -47090,13 +47090,13 @@
         </is>
       </c>
       <c r="N287">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="O287">
         <v>3.8</v>
       </c>
       <c r="P287">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="Q287">
         <v>1.92</v>
@@ -47256,7 +47256,7 @@
         <v>1.85</v>
       </c>
       <c r="O288">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P288">
         <v>3.5</v>
@@ -47781,10 +47781,10 @@
         <v>3.82</v>
       </c>
       <c r="AA291">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AB291">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AC291">
         <v>2.78</v>
@@ -47962,7 +47962,7 @@
         <v>1.6</v>
       </c>
       <c r="AG292">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH292" t="inlineStr">
         <is>
@@ -48572,7 +48572,7 @@
         <v>2.1</v>
       </c>
       <c r="S296">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T296">
         <v>2.66</v>
@@ -48596,7 +48596,7 @@
         <v>3.32</v>
       </c>
       <c r="AA296">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="AB296">
         <v>1.9</v>
@@ -48611,10 +48611,10 @@
         <v>1.06</v>
       </c>
       <c r="AF296">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG296">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH296" t="inlineStr">
         <is>
@@ -48627,7 +48627,7 @@
         </is>
       </c>
       <c r="AJ296">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK296">
         <v>1.57</v>
@@ -48735,10 +48735,10 @@
         <v>2.15</v>
       </c>
       <c r="S297">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T297">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U297">
         <v>2.84</v>
@@ -48777,7 +48777,7 @@
         <v>1.8</v>
       </c>
       <c r="AG297">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AH297" t="inlineStr">
         <is>
@@ -48790,7 +48790,7 @@
         </is>
       </c>
       <c r="AJ297">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK297">
         <v>1.89</v>
@@ -48883,13 +48883,13 @@
         </is>
       </c>
       <c r="N298">
-        <v>2.19</v>
+        <v>2.11</v>
       </c>
       <c r="O298">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="P298">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q298">
         <v>0</v>
@@ -49230,7 +49230,7 @@
         <v>3.1</v>
       </c>
       <c r="U300">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="V300">
         <v>1.48</v>
@@ -49239,7 +49239,7 @@
         <v>1.08</v>
       </c>
       <c r="X300">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y300">
         <v>1.21</v>
@@ -49263,10 +49263,10 @@
         <v>1.15</v>
       </c>
       <c r="AF300">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG300">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AH300" t="inlineStr">
         <is>
@@ -49381,55 +49381,55 @@
         <v>0</v>
       </c>
       <c r="Q301">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="R301">
         <v>1.91</v>
       </c>
       <c r="S301">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="T301">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="U301">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="V301">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W301">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X301">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y301">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="Z301">
         <v>2.31</v>
       </c>
       <c r="AA301">
-        <v>2.52</v>
+        <v>2.79</v>
       </c>
       <c r="AB301">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AC301">
-        <v>4.95</v>
+        <v>5.2</v>
       </c>
       <c r="AD301">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AE301">
         <v>1.01</v>
       </c>
       <c r="AF301">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AG301">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="AH301" t="inlineStr">
         <is>
@@ -49445,7 +49445,7 @@
         <v>1.36</v>
       </c>
       <c r="AK301">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AL301">
         <v>0</v>
@@ -50350,7 +50350,7 @@
         </is>
       </c>
       <c r="N307">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="O307">
         <v>3.3</v>
@@ -50359,7 +50359,7 @@
         <v>2.7</v>
       </c>
       <c r="Q307">
-        <v>2.73</v>
+        <v>2.95</v>
       </c>
       <c r="R307">
         <v>2.36</v>
@@ -50389,7 +50389,7 @@
         <v>4.26</v>
       </c>
       <c r="AA307">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AB307">
         <v>2.08</v>
@@ -50513,34 +50513,34 @@
         </is>
       </c>
       <c r="N308">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="O308">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P308">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="Q308">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="R308">
         <v>2</v>
       </c>
       <c r="S308">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T308">
         <v>2.68</v>
       </c>
       <c r="U308">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="V308">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W308">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X308">
         <v>1.05</v>
@@ -50549,16 +50549,16 @@
         <v>1.39</v>
       </c>
       <c r="Z308">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="AA308">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="AB308">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AC308">
-        <v>4.12</v>
+        <v>4.14</v>
       </c>
       <c r="AD308">
         <v>1.23</v>
@@ -50567,10 +50567,10 @@
         <v>1.04</v>
       </c>
       <c r="AF308">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AG308">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH308" t="inlineStr">
         <is>
@@ -50583,10 +50583,10 @@
         </is>
       </c>
       <c r="AJ308">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK308">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AL308">
         <v>0</v>
@@ -50676,7 +50676,7 @@
         </is>
       </c>
       <c r="N309">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="O309">
         <v>3.6</v>
@@ -51075,7 +51075,7 @@
         <v>1.22</v>
       </c>
       <c r="AK311">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AL311">
         <v>0</v>
@@ -51168,16 +51168,16 @@
         <v>2.25</v>
       </c>
       <c r="O312">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="P312">
-        <v>3.25</v>
+        <v>2.64</v>
       </c>
       <c r="Q312">
-        <v>3.32</v>
+        <v>3.72</v>
       </c>
       <c r="R312">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="S312">
         <v>1.62</v>
@@ -51186,43 +51186,43 @@
         <v>2.2</v>
       </c>
       <c r="U312">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="V312">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W312">
         <v>1.02</v>
       </c>
       <c r="X312">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Y312">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="Z312">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="AA312">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="AB312">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AC312">
-        <v>6.45</v>
+        <v>7</v>
       </c>
       <c r="AD312">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AE312">
         <v>1.01</v>
       </c>
       <c r="AF312">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="AG312">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AH312" t="inlineStr">
         <is>
@@ -51235,10 +51235,10 @@
         </is>
       </c>
       <c r="AJ312">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AK312">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="AL312">
         <v>0</v>
@@ -51337,7 +51337,7 @@
         <v>5.1</v>
       </c>
       <c r="Q313">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="R313">
         <v>2.6</v>
@@ -51491,7 +51491,7 @@
         </is>
       </c>
       <c r="N314">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="O314">
         <v>3.9</v>
@@ -52143,10 +52143,10 @@
         </is>
       </c>
       <c r="N318">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="O318">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="P318">
         <v>3.1</v>
@@ -52161,7 +52161,7 @@
         <v>1.53</v>
       </c>
       <c r="T318">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="U318">
         <v>3.35</v>
@@ -52170,7 +52170,7 @@
         <v>1.24</v>
       </c>
       <c r="W318">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X318">
         <v>1.1</v>
@@ -52188,7 +52188,7 @@
         <v>1.41</v>
       </c>
       <c r="AC318">
-        <v>5.1</v>
+        <v>5.02</v>
       </c>
       <c r="AD318">
         <v>1.14</v>
@@ -53782,10 +53782,10 @@
         <v>0</v>
       </c>
       <c r="Q328">
-        <v>4</v>
+        <v>4.77</v>
       </c>
       <c r="R328">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="S328">
         <v>1.21</v>
@@ -54141,7 +54141,7 @@
         <v>1.5</v>
       </c>
       <c r="AB330">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AC330">
         <v>2.19</v>
@@ -54268,7 +54268,7 @@
         <v>3.71</v>
       </c>
       <c r="P331">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Q331">
         <v>2.05</v>

--- a/jogos_2026-11-01.xlsx
+++ b/jogos_2026-11-01.xlsx
@@ -638,7 +638,7 @@
         <v>1.47</v>
       </c>
       <c r="O2">
-        <v>4.55</v>
+        <v>4.8</v>
       </c>
       <c r="P2">
         <v>6.5</v>
@@ -689,10 +689,10 @@
         <v>1.19</v>
       </c>
       <c r="AF2">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG2">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AK2">
         <v>2.75</v>
@@ -837,7 +837,7 @@
         <v>4.68</v>
       </c>
       <c r="AA3">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AB3">
         <v>2.35</v>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK3">
         <v>1.36</v>
@@ -1290,7 +1290,7 @@
         <v>2.48</v>
       </c>
       <c r="O6">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P6">
         <v>2.3</v>
@@ -1305,19 +1305,19 @@
         <v>1.35</v>
       </c>
       <c r="T6">
-        <v>2.76</v>
+        <v>3.05</v>
       </c>
       <c r="U6">
-        <v>2.64</v>
+        <v>2.77</v>
       </c>
       <c r="V6">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W6">
         <v>1.1</v>
       </c>
       <c r="X6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
         <v>1.27</v>
@@ -1329,19 +1329,19 @@
         <v>1.82</v>
       </c>
       <c r="AB6">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AC6">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="AD6">
         <v>1.3</v>
       </c>
       <c r="AE6">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF6">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AG6">
         <v>2.1</v>
@@ -1453,7 +1453,7 @@
         <v>1.3</v>
       </c>
       <c r="O7">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="P7">
         <v>7</v>
@@ -1625,7 +1625,7 @@
         <v>3.39</v>
       </c>
       <c r="R8">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="S8">
         <v>1.4</v>
@@ -1640,7 +1640,7 @@
         <v>1.36</v>
       </c>
       <c r="W8">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X8">
         <v>1</v>
@@ -1652,13 +1652,13 @@
         <v>2.97</v>
       </c>
       <c r="AA8">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB8">
         <v>1.67</v>
       </c>
       <c r="AC8">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AD8">
         <v>1.22</v>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.52</v>
+        <v>1.29</v>
       </c>
       <c r="AK8">
         <v>1.33</v>
@@ -1818,7 +1818,7 @@
         <v>2.15</v>
       </c>
       <c r="AB9">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC9">
         <v>3.9</v>
@@ -1945,16 +1945,16 @@
         <v>3.86</v>
       </c>
       <c r="P10">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Q10">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R10">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="S10">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T10">
         <v>3.14</v>
@@ -1981,7 +1981,7 @@
         <v>1.89</v>
       </c>
       <c r="AB10">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC10">
         <v>3.08</v>
@@ -2012,7 +2012,7 @@
         <v>1.25</v>
       </c>
       <c r="AK10">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="AK13">
         <v>1.36</v>
@@ -2600,7 +2600,7 @@
         <v>3.02</v>
       </c>
       <c r="Q14">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="R14">
         <v>2.1</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK14">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2757,7 +2757,7 @@
         <v>2.7</v>
       </c>
       <c r="O15">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="P15">
         <v>2.35</v>
@@ -2769,10 +2769,10 @@
         <v>2.3</v>
       </c>
       <c r="S15">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T15">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U15">
         <v>2.38</v>
@@ -3418,7 +3418,7 @@
         <v>3.1</v>
       </c>
       <c r="R19">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S19">
         <v>1.26</v>
@@ -4073,10 +4073,10 @@
         <v>2.1</v>
       </c>
       <c r="S23">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T23">
-        <v>2.7</v>
+        <v>2.61</v>
       </c>
       <c r="U23">
         <v>3</v>
@@ -4097,10 +4097,10 @@
         <v>2.88</v>
       </c>
       <c r="AA23">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AB23">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AC23">
         <v>3.68</v>
@@ -4224,7 +4224,7 @@
         <v>1.35</v>
       </c>
       <c r="O24">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P24">
         <v>5</v>
@@ -4894,7 +4894,7 @@
         <v>3.1</v>
       </c>
       <c r="U28">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V28">
         <v>1.44</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="O31">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P31">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="Q31">
         <v>2.43</v>
@@ -5377,10 +5377,10 @@
         <v>1.98</v>
       </c>
       <c r="S31">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="T31">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="U31">
         <v>3.3</v>
@@ -5404,7 +5404,7 @@
         <v>2.18</v>
       </c>
       <c r="AB31">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AC31">
         <v>4</v>
@@ -5694,7 +5694,7 @@
         <v>3.1</v>
       </c>
       <c r="P33">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="Q33">
         <v>2.99</v>
@@ -5727,7 +5727,7 @@
         <v>2.92</v>
       </c>
       <c r="AA33">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AB33">
         <v>1.69</v>
@@ -6183,7 +6183,7 @@
         <v>3.64</v>
       </c>
       <c r="P36">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6349,10 +6349,10 @@
         <v>15</v>
       </c>
       <c r="Q37">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="R37">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="S37">
         <v>1.14</v>
@@ -6376,13 +6376,13 @@
         <v>1.05</v>
       </c>
       <c r="Z37">
-        <v>6.6</v>
+        <v>6.55</v>
       </c>
       <c r="AA37">
         <v>1.28</v>
       </c>
       <c r="AB37">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="AC37">
         <v>1.77</v>
@@ -6397,7 +6397,7 @@
         <v>2.18</v>
       </c>
       <c r="AG37">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>1.01</v>
       </c>
       <c r="AK37">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6666,16 +6666,16 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="O39">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="P39">
         <v>5</v>
       </c>
       <c r="Q39">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="R39">
         <v>2.6</v>
@@ -6687,10 +6687,10 @@
         <v>3.75</v>
       </c>
       <c r="U39">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="V39">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="W39">
         <v>1.17</v>
@@ -6702,28 +6702,28 @@
         <v>1.1</v>
       </c>
       <c r="Z39">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AA39">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AB39">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AC39">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AD39">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AE39">
         <v>1.19</v>
       </c>
       <c r="AF39">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AG39">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>1.14</v>
       </c>
       <c r="AK39">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,7 +6829,7 @@
         </is>
       </c>
       <c r="N40">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="O40">
         <v>10</v>
@@ -8948,7 +8948,7 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O53">
         <v>3.1</v>
@@ -8987,7 +8987,7 @@
         <v>3.14</v>
       </c>
       <c r="AA53">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB53">
         <v>1.75</v>
@@ -9138,7 +9138,7 @@
         <v>1.4</v>
       </c>
       <c r="W54">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X54">
         <v>1.01</v>
@@ -9494,7 +9494,7 @@
         <v>1.83</v>
       </c>
       <c r="AG56">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -10961,7 +10961,7 @@
         <v>1.6</v>
       </c>
       <c r="AG65">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         <v>3.4</v>
       </c>
       <c r="P66">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q66">
         <v>2.55</v>
@@ -11106,10 +11106,10 @@
         <v>4.04</v>
       </c>
       <c r="AA66">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB66">
-        <v>1.99</v>
+        <v>2.07</v>
       </c>
       <c r="AC66">
         <v>2.8</v>
@@ -11432,10 +11432,10 @@
         <v>2.83</v>
       </c>
       <c r="AA68">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AB68">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AC68">
         <v>3.92</v>
@@ -11444,7 +11444,7 @@
         <v>1.18</v>
       </c>
       <c r="AE68">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF68">
         <v>2</v>
@@ -11565,55 +11565,55 @@
         <v>1.9</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S69">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T69">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U69">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V69">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W69">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X69">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y69">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z69">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA69">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AB69">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC69">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD69">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE69">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF69">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG69">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK69">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11743,7 +11743,7 @@
         <v>1.64</v>
       </c>
       <c r="V70">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="W70">
         <v>1.33</v>
@@ -11792,7 +11792,7 @@
         <v>1.02</v>
       </c>
       <c r="AK70">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -13186,7 +13186,7 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="O79">
         <v>3.25</v>
@@ -13207,13 +13207,13 @@
         <v>2.84</v>
       </c>
       <c r="U79">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="V79">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W79">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X79">
         <v>1.02</v>
@@ -13352,7 +13352,7 @@
         <v>3.18</v>
       </c>
       <c r="O80">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="P80">
         <v>2.35</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,31 +13838,31 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="O83">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="P83">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="Q83">
-        <v>2.6</v>
+        <v>3.04</v>
       </c>
       <c r="R83">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="S83">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T83">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U83">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="V83">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W83">
         <v>1.17</v>
@@ -13871,32 +13871,32 @@
         <v>1.02</v>
       </c>
       <c r="Y83">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z83">
-        <v>5.25</v>
+        <v>4.85</v>
       </c>
       <c r="AA83">
         <v>1.5</v>
       </c>
       <c r="AB83">
+        <v>2.33</v>
+      </c>
+      <c r="AC83">
+        <v>2.33</v>
+      </c>
+      <c r="AD83">
+        <v>1.56</v>
+      </c>
+      <c r="AE83">
+        <v>1.18</v>
+      </c>
+      <c r="AF83">
+        <v>1.44</v>
+      </c>
+      <c r="AG83">
         <v>2.55</v>
       </c>
-      <c r="AC83">
-        <v>2.28</v>
-      </c>
-      <c r="AD83">
-        <v>1.63</v>
-      </c>
-      <c r="AE83">
-        <v>1.22</v>
-      </c>
-      <c r="AF83">
-        <v>1.4</v>
-      </c>
-      <c r="AG83">
-        <v>2.5</v>
-      </c>
       <c r="AH83" t="inlineStr">
         <is>
           <t>[]</t>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AK83">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,31 +14001,31 @@
         </is>
       </c>
       <c r="N84">
+        <v>2.1</v>
+      </c>
+      <c r="O84">
+        <v>3.58</v>
+      </c>
+      <c r="P84">
+        <v>2.9</v>
+      </c>
+      <c r="Q84">
+        <v>2.6</v>
+      </c>
+      <c r="R84">
         <v>2.4</v>
       </c>
-      <c r="O84">
-        <v>3.7</v>
-      </c>
-      <c r="P84">
-        <v>2.55</v>
-      </c>
-      <c r="Q84">
-        <v>2.75</v>
-      </c>
-      <c r="R84">
-        <v>2.32</v>
-      </c>
       <c r="S84">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T84">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U84">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="V84">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W84">
         <v>1.17</v>
@@ -14034,31 +14034,31 @@
         <v>1.02</v>
       </c>
       <c r="Y84">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z84">
-        <v>4.85</v>
+        <v>5.25</v>
       </c>
       <c r="AA84">
         <v>1.5</v>
       </c>
       <c r="AB84">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="AC84">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="AD84">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="AE84">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF84">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG84">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AK84">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14234,7 +14234,7 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AK85">
         <v>1.7</v>
@@ -14327,31 +14327,31 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="O86">
-        <v>4.8</v>
+        <v>5.75</v>
       </c>
       <c r="P86">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="Q86">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="R86">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="S86">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T86">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="U86">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="V86">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="W86">
         <v>1.2</v>
@@ -14360,10 +14360,10 @@
         <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z86">
-        <v>6</v>
+        <v>6.55</v>
       </c>
       <c r="AA86">
         <v>1.38</v>
@@ -14372,19 +14372,19 @@
         <v>2.9</v>
       </c>
       <c r="AC86">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AD86">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="AE86">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AF86">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AG86">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AK86">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14816,7 +14816,7 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="O89">
         <v>3.63</v>
@@ -14979,19 +14979,19 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="O90">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="P90">
         <v>7.5</v>
       </c>
       <c r="Q90">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R90">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="S90">
         <v>1.22</v>
@@ -15036,7 +15036,7 @@
         <v>1.6</v>
       </c>
       <c r="AG90">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="O91">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q91">
         <v>0</v>
@@ -15181,10 +15181,10 @@
         <v>0</v>
       </c>
       <c r="AA91">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB91">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC91">
         <v>0</v>
@@ -15320,10 +15320,10 @@
         <v>3.44</v>
       </c>
       <c r="S92">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="T92">
-        <v>5.65</v>
+        <v>5</v>
       </c>
       <c r="U92">
         <v>1.7</v>
@@ -15332,13 +15332,13 @@
         <v>2.05</v>
       </c>
       <c r="W92">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="X92">
         <v>1</v>
       </c>
       <c r="Y92">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Z92">
         <v>10.5</v>
@@ -15375,7 +15375,7 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AK92">
         <v>3.75</v>
@@ -15960,10 +15960,10 @@
         <v>2.15</v>
       </c>
       <c r="O96">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P96">
-        <v>3.12</v>
+        <v>2.65</v>
       </c>
       <c r="Q96">
         <v>2.96</v>
@@ -16129,7 +16129,7 @@
         <v>2.42</v>
       </c>
       <c r="Q97">
-        <v>3.59</v>
+        <v>4.12</v>
       </c>
       <c r="R97">
         <v>1.96</v>
@@ -16162,7 +16162,7 @@
         <v>2.5</v>
       </c>
       <c r="AB97">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AC97">
         <v>5.75</v>
@@ -16292,16 +16292,16 @@
         <v>1.67</v>
       </c>
       <c r="Q98">
-        <v>4.4</v>
+        <v>4.83</v>
       </c>
       <c r="R98">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="S98">
         <v>1.25</v>
       </c>
       <c r="T98">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U98">
         <v>2.25</v>
@@ -16319,7 +16319,7 @@
         <v>1.18</v>
       </c>
       <c r="Z98">
-        <v>4.76</v>
+        <v>4.78</v>
       </c>
       <c r="AA98">
         <v>1.55</v>
@@ -16328,10 +16328,10 @@
         <v>2.25</v>
       </c>
       <c r="AC98">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="AD98">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AE98">
         <v>1.18</v>
@@ -16452,7 +16452,7 @@
         <v>5</v>
       </c>
       <c r="P99">
-        <v>8.5</v>
+        <v>9.25</v>
       </c>
       <c r="Q99">
         <v>1.72</v>
@@ -16461,7 +16461,7 @@
         <v>2.61</v>
       </c>
       <c r="S99">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T99">
         <v>3.6</v>
@@ -16485,7 +16485,7 @@
         <v>4.65</v>
       </c>
       <c r="AA99">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AB99">
         <v>2.55</v>
@@ -16497,7 +16497,7 @@
         <v>1.58</v>
       </c>
       <c r="AE99">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AF99">
         <v>1.85</v>
@@ -16624,10 +16624,10 @@
         <v>2.83</v>
       </c>
       <c r="S100">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="T100">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="U100">
         <v>1.83</v>
@@ -16636,19 +16636,19 @@
         <v>1.84</v>
       </c>
       <c r="W100">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="X100">
         <v>0</v>
       </c>
       <c r="Y100">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Z100">
         <v>6.7</v>
       </c>
       <c r="AA100">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AB100">
         <v>3.4</v>
@@ -16666,7 +16666,7 @@
         <v>1.69</v>
       </c>
       <c r="AG100">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>1.05</v>
       </c>
       <c r="AK100">
-        <v>4.5</v>
+        <v>3.94</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16947,7 +16947,7 @@
         <v>3.74</v>
       </c>
       <c r="R102">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="S102">
         <v>1.18</v>
@@ -16968,28 +16968,28 @@
         <v>1.02</v>
       </c>
       <c r="Y102">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z102">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AA102">
         <v>1.5</v>
       </c>
       <c r="AB102">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AC102">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AD102">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AE102">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF102">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AG102">
         <v>2.5</v>
@@ -17261,7 +17261,7 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="O104">
         <v>3.3</v>
@@ -17306,7 +17306,7 @@
         <v>1.87</v>
       </c>
       <c r="AC104">
-        <v>3.21</v>
+        <v>3.05</v>
       </c>
       <c r="AD104">
         <v>1.28</v>
@@ -17427,7 +17427,7 @@
         <v>2.06</v>
       </c>
       <c r="O105">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="P105">
         <v>3.2</v>
@@ -17445,7 +17445,7 @@
         <v>2.56</v>
       </c>
       <c r="U105">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="V105">
         <v>1.36</v>
@@ -17590,10 +17590,10 @@
         <v>1.83</v>
       </c>
       <c r="O106">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="P106">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="Q106">
         <v>2.3</v>
@@ -17602,49 +17602,49 @@
         <v>2.4</v>
       </c>
       <c r="S106">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T106">
-        <v>3.8</v>
+        <v>3.48</v>
       </c>
       <c r="U106">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="V106">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W106">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X106">
         <v>1.01</v>
       </c>
       <c r="Y106">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z106">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="AA106">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AB106">
-        <v>2.46</v>
+        <v>2.21</v>
       </c>
       <c r="AC106">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="AD106">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AE106">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AF106">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AG106">
-        <v>2.51</v>
+        <v>2.31</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK106">
         <v>1.91</v>
@@ -17762,7 +17762,7 @@
         <v>2.06</v>
       </c>
       <c r="R107">
-        <v>2.63</v>
+        <v>2.27</v>
       </c>
       <c r="S107">
         <v>1.25</v>
@@ -17792,7 +17792,7 @@
         <v>1.57</v>
       </c>
       <c r="AB107">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AC107">
         <v>2.38</v>
@@ -18402,7 +18402,7 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="O111">
         <v>3.25</v>
@@ -18432,7 +18432,7 @@
         <v>1.08</v>
       </c>
       <c r="X111">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y111">
         <v>1.21</v>
@@ -18580,10 +18580,10 @@
         <v>2.05</v>
       </c>
       <c r="S112">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T112">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="U112">
         <v>3</v>
@@ -19217,16 +19217,16 @@
         </is>
       </c>
       <c r="N116">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="O116">
         <v>3.7</v>
       </c>
       <c r="P116">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="Q116">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="R116">
         <v>2.3</v>
@@ -19238,7 +19238,7 @@
         <v>3.2</v>
       </c>
       <c r="U116">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="V116">
         <v>1.44</v>
@@ -19247,7 +19247,7 @@
         <v>1.1</v>
       </c>
       <c r="X116">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y116">
         <v>1.18</v>
@@ -19256,10 +19256,10 @@
         <v>3.84</v>
       </c>
       <c r="AA116">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AB116">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AC116">
         <v>2.74</v>
@@ -19271,7 +19271,7 @@
         <v>1.1</v>
       </c>
       <c r="AF116">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AG116">
         <v>1.94</v>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK116">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19386,7 +19386,7 @@
         <v>3.95</v>
       </c>
       <c r="P117">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="Q117">
         <v>3.85</v>
@@ -20032,10 +20032,10 @@
         </is>
       </c>
       <c r="N121">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="O121">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="P121">
         <v>3.15</v>
@@ -20047,43 +20047,43 @@
         <v>2.63</v>
       </c>
       <c r="S121">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="T121">
         <v>5</v>
       </c>
       <c r="U121">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V121">
         <v>1.95</v>
       </c>
       <c r="W121">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="X121">
         <v>1.01</v>
       </c>
       <c r="Y121">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Z121">
-        <v>7.8</v>
+        <v>7.1</v>
       </c>
       <c r="AA121">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AB121">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="AC121">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="AD121">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="AE121">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AF121">
         <v>1.25</v>
@@ -20105,7 +20105,7 @@
         <v>1.25</v>
       </c>
       <c r="AK121">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20201,7 +20201,7 @@
         <v>3.75</v>
       </c>
       <c r="P122">
-        <v>3.4</v>
+        <v>3.07</v>
       </c>
       <c r="Q122">
         <v>2.1</v>
@@ -20222,7 +20222,7 @@
         <v>1.79</v>
       </c>
       <c r="W122">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="X122">
         <v>1.01</v>
@@ -20234,7 +20234,7 @@
         <v>6.45</v>
       </c>
       <c r="AA122">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AB122">
         <v>3.1</v>
@@ -20690,7 +20690,7 @@
         <v>3.1</v>
       </c>
       <c r="P125">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="Q125">
         <v>3.74</v>
@@ -21043,16 +21043,16 @@
         <v>1.01</v>
       </c>
       <c r="Y127">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z127">
         <v>3.34</v>
       </c>
       <c r="AA127">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="AB127">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AC127">
         <v>3.08</v>
@@ -21080,7 +21080,7 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK127">
         <v>1.33</v>
@@ -21188,10 +21188,10 @@
         <v>2.38</v>
       </c>
       <c r="S128">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T128">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="U128">
         <v>2.4</v>
@@ -21203,7 +21203,7 @@
         <v>1.08</v>
       </c>
       <c r="X128">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y128">
         <v>1.18</v>
@@ -21831,7 +21831,7 @@
         <v>3.82</v>
       </c>
       <c r="P132">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="Q132">
         <v>4.05</v>
@@ -21855,7 +21855,7 @@
         <v>1.14</v>
       </c>
       <c r="X132">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y132">
         <v>1.13</v>
@@ -21864,7 +21864,7 @@
         <v>4.6</v>
       </c>
       <c r="AA132">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AB132">
         <v>2.3</v>
@@ -22175,7 +22175,7 @@
         <v>2.65</v>
       </c>
       <c r="V134">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W134">
         <v>1.08</v>
@@ -22803,28 +22803,28 @@
         </is>
       </c>
       <c r="N138">
-        <v>3.95</v>
+        <v>4.15</v>
       </c>
       <c r="O138">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P138">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="Q138">
-        <v>5.22</v>
+        <v>5.42</v>
       </c>
       <c r="R138">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="S138">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T138">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="U138">
-        <v>3.15</v>
+        <v>3.11</v>
       </c>
       <c r="V138">
         <v>1.33</v>
@@ -22836,10 +22836,10 @@
         <v>1</v>
       </c>
       <c r="Y138">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Z138">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="AA138">
         <v>2.1</v>
@@ -22975,10 +22975,10 @@
         <v>0</v>
       </c>
       <c r="Q139">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="R139">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="S139">
         <v>1.25</v>
@@ -22987,7 +22987,7 @@
         <v>3.7</v>
       </c>
       <c r="U139">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="V139">
         <v>1.62</v>
@@ -22999,25 +22999,25 @@
         <v>1.03</v>
       </c>
       <c r="Y139">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z139">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AA139">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AB139">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AC139">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="AD139">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AE139">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF139">
         <v>1.47</v>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
+        <v>1.22</v>
+      </c>
+      <c r="AK139">
         <v>1.2</v>
-      </c>
-      <c r="AK139">
-        <v>1.24</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23138,10 +23138,10 @@
         <v>0</v>
       </c>
       <c r="Q140">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R140">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="S140">
         <v>1.17</v>
@@ -23168,10 +23168,10 @@
         <v>7.1</v>
       </c>
       <c r="AA140">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AB140">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AC140">
         <v>1.79</v>
@@ -23186,7 +23186,7 @@
         <v>1.75</v>
       </c>
       <c r="AG140">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AK140">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -23618,13 +23618,13 @@
         </is>
       </c>
       <c r="N143">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="O143">
         <v>3.35</v>
       </c>
       <c r="P143">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="Q143">
         <v>2.9</v>
@@ -23672,7 +23672,7 @@
         <v>1.11</v>
       </c>
       <c r="AF143">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG143">
         <v>2.2</v>
@@ -24442,55 +24442,55 @@
         <v>0</v>
       </c>
       <c r="Q148">
-        <v>0</v>
+        <v>13.9</v>
       </c>
       <c r="R148">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="S148">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T148">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U148">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V148">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="W148">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y148">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Z148">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA148">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AB148">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="AC148">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD148">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AE148">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AF148">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG148">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
@@ -24503,10 +24503,10 @@
         </is>
       </c>
       <c r="AJ148">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="AK148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL148">
         <v>0</v>
@@ -26715,13 +26715,13 @@
         </is>
       </c>
       <c r="N162">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="O162">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P162">
-        <v>0</v>
+        <v>13.2</v>
       </c>
       <c r="Q162">
         <v>0</v>
@@ -26754,10 +26754,10 @@
         <v>0</v>
       </c>
       <c r="AA162">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB162">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC162">
         <v>0</v>
@@ -26878,13 +26878,13 @@
         </is>
       </c>
       <c r="N163">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O163">
         <v>3.6</v>
       </c>
       <c r="P163">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="Q163">
         <v>2.6</v>
@@ -26917,7 +26917,7 @@
         <v>4.3</v>
       </c>
       <c r="AA163">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AB163">
         <v>2.27</v>
@@ -27041,13 +27041,13 @@
         </is>
       </c>
       <c r="N164">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="O164">
         <v>3.66</v>
       </c>
       <c r="P164">
-        <v>3.92</v>
+        <v>3.5</v>
       </c>
       <c r="Q164">
         <v>2.25</v>
@@ -27077,7 +27077,7 @@
         <v>1.21</v>
       </c>
       <c r="Z164">
-        <v>3.58</v>
+        <v>3.76</v>
       </c>
       <c r="AA164">
         <v>1.85</v>
@@ -28182,13 +28182,13 @@
         </is>
       </c>
       <c r="N171">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="O171">
         <v>4.2</v>
       </c>
       <c r="P171">
-        <v>4.82</v>
+        <v>4.5</v>
       </c>
       <c r="Q171">
         <v>1.96</v>
@@ -28366,7 +28366,7 @@
         <v>3</v>
       </c>
       <c r="U172">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="V172">
         <v>1.4</v>
@@ -28387,7 +28387,7 @@
         <v>1.82</v>
       </c>
       <c r="AB172">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC172">
         <v>3.05</v>
@@ -28547,10 +28547,10 @@
         <v>2.97</v>
       </c>
       <c r="AA173">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AB173">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AC173">
         <v>3.5</v>
@@ -28671,13 +28671,13 @@
         </is>
       </c>
       <c r="N174">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O174">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P174">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q174">
         <v>3.06</v>
@@ -28710,10 +28710,10 @@
         <v>2.83</v>
       </c>
       <c r="AA174">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AB174">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AC174">
         <v>3.75</v>
@@ -28834,7 +28834,7 @@
         </is>
       </c>
       <c r="N175">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="O175">
         <v>3.4</v>
@@ -28997,13 +28997,13 @@
         </is>
       </c>
       <c r="N176">
-        <v>2.47</v>
+        <v>2.52</v>
       </c>
       <c r="O176">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="P176">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="Q176">
         <v>0</v>
@@ -29323,13 +29323,13 @@
         </is>
       </c>
       <c r="N178">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O178">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P178">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="Q178">
         <v>0</v>
@@ -29486,13 +29486,13 @@
         </is>
       </c>
       <c r="N179">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="O179">
         <v>3.75</v>
       </c>
       <c r="P179">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="Q179">
         <v>2.62</v>
@@ -29556,10 +29556,10 @@
         </is>
       </c>
       <c r="AJ179">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="AK179">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -31285,7 +31285,7 @@
         <v>4.2</v>
       </c>
       <c r="P190">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="Q190">
         <v>2.08</v>
@@ -31457,13 +31457,13 @@
         <v>2.15</v>
       </c>
       <c r="S191">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="T191">
         <v>3.02</v>
       </c>
       <c r="U191">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="V191">
         <v>1.44</v>
@@ -31620,7 +31620,7 @@
         <v>3.14</v>
       </c>
       <c r="S192">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="T192">
         <v>5</v>
@@ -32124,7 +32124,7 @@
         <v>1.1</v>
       </c>
       <c r="X195">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y195">
         <v>1.17</v>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK195">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32589,7 +32589,7 @@
         <v>3.1</v>
       </c>
       <c r="P198">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="Q198">
         <v>3.06</v>
@@ -32764,7 +32764,7 @@
         <v>1.22</v>
       </c>
       <c r="T199">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="U199">
         <v>2.2</v>
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G200">
@@ -32909,64 +32909,64 @@
         </is>
       </c>
       <c r="N200">
-        <v>1.71</v>
+        <v>2.05</v>
       </c>
       <c r="O200">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P200">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="Q200">
-        <v>2.1</v>
+        <v>2.56</v>
       </c>
       <c r="R200">
-        <v>2.61</v>
+        <v>2.37</v>
       </c>
       <c r="S200">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T200">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="U200">
-        <v>2.05</v>
+        <v>2.39</v>
       </c>
       <c r="V200">
+        <v>1.49</v>
+      </c>
+      <c r="W200">
+        <v>1.08</v>
+      </c>
+      <c r="X200">
+        <v>1.03</v>
+      </c>
+      <c r="Y200">
+        <v>1.17</v>
+      </c>
+      <c r="Z200">
+        <v>4.15</v>
+      </c>
+      <c r="AA200">
         <v>1.67</v>
       </c>
-      <c r="W200">
-        <v>1.15</v>
-      </c>
-      <c r="X200">
-        <v>1.02</v>
-      </c>
-      <c r="Y200">
-        <v>1.1</v>
-      </c>
-      <c r="Z200">
-        <v>5.2</v>
-      </c>
-      <c r="AA200">
-        <v>1.47</v>
-      </c>
       <c r="AB200">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="AC200">
-        <v>2.17</v>
+        <v>2.66</v>
       </c>
       <c r="AD200">
-        <v>1.66</v>
+        <v>1.43</v>
       </c>
       <c r="AE200">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="AF200">
-        <v>1.47</v>
+        <v>1.59</v>
       </c>
       <c r="AG200">
-        <v>2.5</v>
+        <v>2.21</v>
       </c>
       <c r="AH200" t="inlineStr">
         <is>
@@ -32979,10 +32979,10 @@
         </is>
       </c>
       <c r="AJ200">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK200">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AL200">
         <v>0</v>
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G201">
@@ -33072,64 +33072,64 @@
         </is>
       </c>
       <c r="N201">
-        <v>1.27</v>
+        <v>1.55</v>
       </c>
       <c r="O201">
-        <v>5.15</v>
+        <v>3.8</v>
       </c>
       <c r="P201">
-        <v>6.5</v>
+        <v>3.8</v>
       </c>
       <c r="Q201">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="R201">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="S201">
         <v>1.22</v>
       </c>
       <c r="T201">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="U201">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="V201">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="W201">
         <v>1.15</v>
       </c>
       <c r="X201">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y201">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z201">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="AA201">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB201">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="AC201">
-        <v>2.07</v>
+        <v>2.17</v>
       </c>
       <c r="AD201">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AE201">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AF201">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="AG201">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AH201" t="inlineStr">
         <is>
@@ -33142,10 +33142,10 @@
         </is>
       </c>
       <c r="AJ201">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AK201">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL201">
         <v>0</v>
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G202">
@@ -33235,64 +33235,64 @@
         </is>
       </c>
       <c r="N202">
-        <v>2.05</v>
+        <v>1.27</v>
       </c>
       <c r="O202">
-        <v>3.55</v>
+        <v>5.15</v>
       </c>
       <c r="P202">
-        <v>3.2</v>
+        <v>6.5</v>
       </c>
       <c r="Q202">
-        <v>2.45</v>
+        <v>1.83</v>
       </c>
       <c r="R202">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="S202">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T202">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="U202">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="V202">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="W202">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X202">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y202">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z202">
-        <v>4.15</v>
+        <v>5.5</v>
       </c>
       <c r="AA202">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AB202">
-        <v>2.15</v>
+        <v>2.46</v>
       </c>
       <c r="AC202">
-        <v>2.66</v>
+        <v>2.07</v>
       </c>
       <c r="AD202">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="AE202">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AF202">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AG202">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH202" t="inlineStr">
         <is>
@@ -33305,10 +33305,10 @@
         </is>
       </c>
       <c r="AJ202">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="AK202">
-        <v>1.83</v>
+        <v>3</v>
       </c>
       <c r="AL202">
         <v>0</v>
@@ -33727,7 +33727,7 @@
         <v>1.36</v>
       </c>
       <c r="O205">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="P205">
         <v>7.27</v>
@@ -35689,10 +35689,10 @@
         <v>3.02</v>
       </c>
       <c r="Q217">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="R217">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S217">
         <v>1.4</v>
@@ -35704,13 +35704,13 @@
         <v>3</v>
       </c>
       <c r="V217">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W217">
         <v>1.06</v>
       </c>
       <c r="X217">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y217">
         <v>1.3</v>
@@ -35731,7 +35731,7 @@
         <v>1.22</v>
       </c>
       <c r="AE217">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF217">
         <v>1.82</v>
@@ -35974,12 +35974,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G219">
@@ -36006,64 +36006,64 @@
         </is>
       </c>
       <c r="N219">
-        <v>1.51</v>
+        <v>1.96</v>
       </c>
       <c r="O219">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="P219">
-        <v>5.25</v>
+        <v>3.25</v>
       </c>
       <c r="Q219">
-        <v>1.89</v>
+        <v>2.5</v>
       </c>
       <c r="R219">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="S219">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T219">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="U219">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="V219">
-        <v>1.72</v>
+        <v>1.44</v>
       </c>
       <c r="W219">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="X219">
         <v>1</v>
       </c>
       <c r="Y219">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="Z219">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="AA219">
-        <v>1.43</v>
+        <v>1.74</v>
       </c>
       <c r="AB219">
-        <v>2.8</v>
+        <v>2.08</v>
       </c>
       <c r="AC219">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="AD219">
-        <v>1.79</v>
+        <v>1.36</v>
       </c>
       <c r="AE219">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="AF219">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AG219">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="AH219" t="inlineStr">
         <is>
@@ -36076,10 +36076,10 @@
         </is>
       </c>
       <c r="AJ219">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AK219">
-        <v>2.42</v>
+        <v>1.73</v>
       </c>
       <c r="AL219">
         <v>0</v>
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G220">
@@ -36169,64 +36169,64 @@
         </is>
       </c>
       <c r="N220">
-        <v>1.96</v>
+        <v>1.51</v>
       </c>
       <c r="O220">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="P220">
-        <v>3.25</v>
+        <v>5.3</v>
       </c>
       <c r="Q220">
-        <v>2.5</v>
+        <v>1.89</v>
       </c>
       <c r="R220">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="S220">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T220">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="U220">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="V220">
-        <v>1.44</v>
+        <v>1.72</v>
       </c>
       <c r="W220">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="X220">
         <v>1</v>
       </c>
       <c r="Y220">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="Z220">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="AA220">
-        <v>1.74</v>
+        <v>1.43</v>
       </c>
       <c r="AB220">
-        <v>2.08</v>
+        <v>2.8</v>
       </c>
       <c r="AC220">
-        <v>2.88</v>
+        <v>2.05</v>
       </c>
       <c r="AD220">
-        <v>1.36</v>
+        <v>1.79</v>
       </c>
       <c r="AE220">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="AF220">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AG220">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AH220" t="inlineStr">
         <is>
@@ -36239,10 +36239,10 @@
         </is>
       </c>
       <c r="AJ220">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK220">
-        <v>1.73</v>
+        <v>2.42</v>
       </c>
       <c r="AL220">
         <v>0</v>
@@ -36335,7 +36335,7 @@
         <v>2.6</v>
       </c>
       <c r="O221">
-        <v>3.67</v>
+        <v>3.4</v>
       </c>
       <c r="P221">
         <v>2.3</v>
@@ -36359,7 +36359,7 @@
         <v>1.62</v>
       </c>
       <c r="W221">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X221">
         <v>1</v>
@@ -36498,7 +36498,7 @@
         <v>3.09</v>
       </c>
       <c r="O222">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="P222">
         <v>2.5</v>
@@ -36664,7 +36664,7 @@
         <v>3.4</v>
       </c>
       <c r="P223">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="Q223">
         <v>2.36</v>
@@ -37349,7 +37349,7 @@
         <v>3.34</v>
       </c>
       <c r="AA227">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AB227">
         <v>2.05</v>
@@ -37503,7 +37503,7 @@
         <v>1.1</v>
       </c>
       <c r="X228">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y228">
         <v>1.21</v>
@@ -37512,10 +37512,10 @@
         <v>3.58</v>
       </c>
       <c r="AA228">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AB228">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AC228">
         <v>2.88</v>
@@ -38641,7 +38641,7 @@
         <v>1.35</v>
       </c>
       <c r="W235">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X235">
         <v>1.02</v>
@@ -38656,7 +38656,7 @@
         <v>1.95</v>
       </c>
       <c r="AB235">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC235">
         <v>3.42</v>
@@ -38668,7 +38668,7 @@
         <v>1.05</v>
       </c>
       <c r="AF235">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AG235">
         <v>1.6</v>
@@ -38786,16 +38786,16 @@
         <v>4.91</v>
       </c>
       <c r="Q236">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="R236">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="S236">
         <v>1.28</v>
       </c>
       <c r="T236">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="U236">
         <v>2.27</v>
@@ -38813,28 +38813,28 @@
         <v>1.17</v>
       </c>
       <c r="Z236">
-        <v>3.98</v>
+        <v>3.94</v>
       </c>
       <c r="AA236">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AB236">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AC236">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="AD236">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AE236">
         <v>1.14</v>
       </c>
       <c r="AF236">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG236">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AH236" t="inlineStr">
         <is>
@@ -38847,10 +38847,10 @@
         </is>
       </c>
       <c r="AJ236">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK236">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="AL236">
         <v>0</v>
@@ -39115,7 +39115,7 @@
         <v>2.07</v>
       </c>
       <c r="R238">
-        <v>2.84</v>
+        <v>2.53</v>
       </c>
       <c r="S238">
         <v>1.17</v>
@@ -39148,10 +39148,10 @@
         <v>3.28</v>
       </c>
       <c r="AC238">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AD238">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AE238">
         <v>1.36</v>
@@ -39173,7 +39173,7 @@
         </is>
       </c>
       <c r="AJ238">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AK238">
         <v>1.95</v>
@@ -39272,7 +39272,7 @@
         <v>6.2</v>
       </c>
       <c r="P239">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="Q239">
         <v>1.49</v>
@@ -39339,7 +39339,7 @@
         <v>1.06</v>
       </c>
       <c r="AK239">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AL239">
         <v>0</v>
@@ -39450,7 +39450,7 @@
         <v>3.4</v>
       </c>
       <c r="U240">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V240">
         <v>1.55</v>
@@ -39471,7 +39471,7 @@
         <v>1.62</v>
       </c>
       <c r="AB240">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AC240">
         <v>2.46</v>
@@ -39607,7 +39607,7 @@
         <v>2.72</v>
       </c>
       <c r="S241">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="T241">
         <v>3.9</v>
@@ -39662,7 +39662,7 @@
         </is>
       </c>
       <c r="AJ241">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK241">
         <v>3</v>
@@ -39785,7 +39785,7 @@
         <v>1.3</v>
       </c>
       <c r="X242">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y242">
         <v>1.02</v>
@@ -39927,10 +39927,10 @@
         <v>3.8</v>
       </c>
       <c r="Q243">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="R243">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="S243">
         <v>1.17</v>
@@ -39954,7 +39954,7 @@
         <v>1.09</v>
       </c>
       <c r="Z243">
-        <v>5.4</v>
+        <v>5.52</v>
       </c>
       <c r="AA243">
         <v>1.38</v>
@@ -39991,7 +39991,7 @@
         <v>1.18</v>
       </c>
       <c r="AK243">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AL243">
         <v>0</v>
@@ -40081,19 +40081,19 @@
         </is>
       </c>
       <c r="N244">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="O244">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="P244">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Q244">
         <v>2</v>
       </c>
       <c r="R244">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="S244">
         <v>1.3</v>
@@ -40120,10 +40120,10 @@
         <v>4.3</v>
       </c>
       <c r="AA244">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB244">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC244">
         <v>2.41</v>
@@ -40244,7 +40244,7 @@
         </is>
       </c>
       <c r="N245">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="O245">
         <v>3.5</v>
@@ -40259,7 +40259,7 @@
         <v>2.36</v>
       </c>
       <c r="S245">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T245">
         <v>3.2</v>
@@ -40271,7 +40271,7 @@
         <v>1.44</v>
       </c>
       <c r="W245">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X245">
         <v>1.03</v>
@@ -40280,7 +40280,7 @@
         <v>1.24</v>
       </c>
       <c r="Z245">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="AA245">
         <v>1.84</v>
@@ -40295,7 +40295,7 @@
         <v>1.41</v>
       </c>
       <c r="AE245">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF245">
         <v>1.62</v>
@@ -40407,13 +40407,13 @@
         </is>
       </c>
       <c r="N246">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="O246">
-        <v>4.85</v>
+        <v>5.05</v>
       </c>
       <c r="P246">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="Q246">
         <v>1.8</v>
@@ -40434,7 +40434,7 @@
         <v>1.59</v>
       </c>
       <c r="W246">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X246">
         <v>1</v>
@@ -40609,10 +40609,10 @@
         <v>3.76</v>
       </c>
       <c r="AA247">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AB247">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AC247">
         <v>2.66</v>
@@ -40935,10 +40935,10 @@
         <v>2.81</v>
       </c>
       <c r="AA249">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AB249">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AC249">
         <v>3.9</v>
@@ -41059,7 +41059,7 @@
         </is>
       </c>
       <c r="N250">
-        <v>2.99</v>
+        <v>2.7</v>
       </c>
       <c r="O250">
         <v>3.4</v>
@@ -41113,10 +41113,10 @@
         <v>1.11</v>
       </c>
       <c r="AF250">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG250">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AH250" t="inlineStr">
         <is>
@@ -41243,10 +41243,10 @@
         <v>3.7</v>
       </c>
       <c r="U251">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="V251">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="W251">
         <v>1.13</v>
@@ -41279,7 +41279,7 @@
         <v>1.59</v>
       </c>
       <c r="AG251">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AH251" t="inlineStr">
         <is>
@@ -41391,7 +41391,7 @@
         <v>3.7</v>
       </c>
       <c r="P252">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="Q252">
         <v>2.05</v>
@@ -41400,7 +41400,7 @@
         <v>2.38</v>
       </c>
       <c r="S252">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="T252">
         <v>3.3</v>
@@ -41424,7 +41424,7 @@
         <v>4.2</v>
       </c>
       <c r="AA252">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AB252">
         <v>2.12</v>
@@ -41442,7 +41442,7 @@
         <v>1.62</v>
       </c>
       <c r="AG252">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AH252" t="inlineStr">
         <is>
@@ -41720,7 +41720,7 @@
         <v>3.05</v>
       </c>
       <c r="Q254">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R254">
         <v>2</v>
@@ -41750,10 +41750,10 @@
         <v>3.04</v>
       </c>
       <c r="AA254">
-        <v>1.9</v>
+        <v>2.07</v>
       </c>
       <c r="AB254">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AC254">
         <v>3.5</v>
@@ -42369,7 +42369,7 @@
         <v>3.85</v>
       </c>
       <c r="P258">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="Q258">
         <v>4.55</v>
@@ -42529,7 +42529,7 @@
         <v>4.2</v>
       </c>
       <c r="O259">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P259">
         <v>1.7</v>
@@ -42716,7 +42716,7 @@
         <v>1.35</v>
       </c>
       <c r="W260">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X260">
         <v>1.02</v>
@@ -42743,10 +42743,10 @@
         <v>1.06</v>
       </c>
       <c r="AF260">
+        <v>1.83</v>
+      </c>
+      <c r="AG260">
         <v>1.85</v>
-      </c>
-      <c r="AG260">
-        <v>1.84</v>
       </c>
       <c r="AH260" t="inlineStr">
         <is>
@@ -43350,7 +43350,7 @@
         <v>2.86</v>
       </c>
       <c r="Q264">
-        <v>2.63</v>
+        <v>2.69</v>
       </c>
       <c r="R264">
         <v>2.32</v>
@@ -43368,7 +43368,7 @@
         <v>1.6</v>
       </c>
       <c r="W264">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X264">
         <v>1.01</v>
@@ -43380,10 +43380,10 @@
         <v>4.9</v>
       </c>
       <c r="AA264">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB264">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AC264">
         <v>2.2</v>
@@ -43836,7 +43836,7 @@
         <v>3.4</v>
       </c>
       <c r="P267">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q267">
         <v>3.25</v>
@@ -43996,7 +43996,7 @@
         <v>1.87</v>
       </c>
       <c r="O268">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P268">
         <v>3.3</v>
@@ -44035,7 +44035,7 @@
         <v>1.57</v>
       </c>
       <c r="AB268">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AC268">
         <v>2.49</v>
@@ -44319,10 +44319,10 @@
         </is>
       </c>
       <c r="N270">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O270">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P270">
         <v>3</v>
@@ -44491,7 +44491,7 @@
         <v>2.96</v>
       </c>
       <c r="Q271">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="R271">
         <v>2.1</v>
@@ -44811,7 +44811,7 @@
         <v>1.7</v>
       </c>
       <c r="O273">
-        <v>3.45</v>
+        <v>3.48</v>
       </c>
       <c r="P273">
         <v>4.33</v>
@@ -44974,7 +44974,7 @@
         <v>4</v>
       </c>
       <c r="O274">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="P274">
         <v>1.85</v>
@@ -45173,10 +45173,10 @@
         <v>2.97</v>
       </c>
       <c r="AA275">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AB275">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AC275">
         <v>3.34</v>
@@ -45336,10 +45336,10 @@
         <v>3.05</v>
       </c>
       <c r="AA276">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AB276">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AC276">
         <v>3.5</v>
@@ -45674,7 +45674,7 @@
         <v>1.12</v>
       </c>
       <c r="AE278">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF278">
         <v>1.95</v>
@@ -45843,7 +45843,7 @@
         <v>2.01</v>
       </c>
       <c r="AG279">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AH279" t="inlineStr">
         <is>
@@ -46275,7 +46275,7 @@
         </is>
       </c>
       <c r="N282">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="O282">
         <v>3.6</v>
@@ -46480,7 +46480,7 @@
         <v>2.5</v>
       </c>
       <c r="AB283">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AC283">
         <v>4.85</v>
@@ -46495,7 +46495,7 @@
         <v>2</v>
       </c>
       <c r="AG283">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH283" t="inlineStr">
         <is>
@@ -46640,7 +46640,7 @@
         <v>4.95</v>
       </c>
       <c r="AA284">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AB284">
         <v>2.39</v>
@@ -46791,7 +46791,7 @@
         <v>1.53</v>
       </c>
       <c r="W285">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X285">
         <v>1.01</v>
@@ -46954,7 +46954,7 @@
         <v>1.45</v>
       </c>
       <c r="W286">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X286">
         <v>1</v>
@@ -47163,7 +47163,7 @@
         <v>1.18</v>
       </c>
       <c r="AK287">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="AL287">
         <v>0</v>
@@ -47256,7 +47256,7 @@
         <v>1.85</v>
       </c>
       <c r="O288">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P288">
         <v>3.5</v>
@@ -47486,10 +47486,10 @@
         </is>
       </c>
       <c r="AJ289">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK289">
-        <v>1.96</v>
+        <v>1.84</v>
       </c>
       <c r="AL289">
         <v>0</v>
@@ -48107,10 +48107,10 @@
         <v>0</v>
       </c>
       <c r="AA293">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AB293">
-        <v>2.37</v>
+        <v>2.15</v>
       </c>
       <c r="AC293">
         <v>0</v>
@@ -48267,13 +48267,13 @@
         <v>1.25</v>
       </c>
       <c r="Z294">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AA294">
         <v>1.9</v>
       </c>
       <c r="AB294">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AC294">
         <v>3.1</v>
@@ -48762,7 +48762,7 @@
         <v>1.9</v>
       </c>
       <c r="AB297">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AC297">
         <v>3.2</v>
@@ -49085,10 +49085,10 @@
         <v>0</v>
       </c>
       <c r="AA299">
+        <v>1.95</v>
+      </c>
+      <c r="AB299">
         <v>1.85</v>
-      </c>
-      <c r="AB299">
-        <v>1.95</v>
       </c>
       <c r="AC299">
         <v>0</v>
@@ -49215,7 +49215,7 @@
         <v>3.68</v>
       </c>
       <c r="P300">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q300">
         <v>2.48</v>
@@ -49230,7 +49230,7 @@
         <v>3.1</v>
       </c>
       <c r="U300">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="V300">
         <v>1.48</v>
@@ -50359,7 +50359,7 @@
         <v>2.7</v>
       </c>
       <c r="Q307">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="R307">
         <v>2.36</v>
@@ -50386,25 +50386,25 @@
         <v>1.17</v>
       </c>
       <c r="Z307">
-        <v>4.26</v>
+        <v>4</v>
       </c>
       <c r="AA307">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AB307">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AC307">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="AD307">
         <v>1.44</v>
       </c>
       <c r="AE307">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF307">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AG307">
         <v>2.2</v>
@@ -50519,7 +50519,7 @@
         <v>3.4</v>
       </c>
       <c r="P308">
-        <v>4.45</v>
+        <v>4.6</v>
       </c>
       <c r="Q308">
         <v>2.4</v>
@@ -50583,10 +50583,10 @@
         </is>
       </c>
       <c r="AJ308">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK308">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AL308">
         <v>0</v>
@@ -50909,7 +50909,7 @@
         </is>
       </c>
       <c r="AJ310">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AK310">
         <v>1.83</v>
@@ -51072,10 +51072,10 @@
         </is>
       </c>
       <c r="AJ311">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK311">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AL311">
         <v>0</v>
@@ -51168,10 +51168,10 @@
         <v>2.25</v>
       </c>
       <c r="O312">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="P312">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="Q312">
         <v>3.72</v>
@@ -51195,7 +51195,7 @@
         <v>1.02</v>
       </c>
       <c r="X312">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Y312">
         <v>1.62</v>
@@ -51210,10 +51210,10 @@
         <v>1.31</v>
       </c>
       <c r="AC312">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AD312">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AE312">
         <v>1.01</v>
@@ -51491,13 +51491,13 @@
         </is>
       </c>
       <c r="N314">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="O314">
         <v>3.9</v>
       </c>
       <c r="P314">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="Q314">
         <v>2.63</v>
@@ -51654,13 +51654,13 @@
         </is>
       </c>
       <c r="N315">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="O315">
         <v>4.2</v>
       </c>
       <c r="P315">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="Q315">
         <v>2.05</v>
@@ -51823,7 +51823,7 @@
         <v>3.5</v>
       </c>
       <c r="P316">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="Q316">
         <v>2.29</v>
@@ -51838,7 +51838,7 @@
         <v>2.9</v>
       </c>
       <c r="U316">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V316">
         <v>1.4</v>
@@ -51983,19 +51983,19 @@
         <v>1.44</v>
       </c>
       <c r="O317">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="P317">
         <v>6</v>
       </c>
       <c r="Q317">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="R317">
         <v>2.2</v>
       </c>
       <c r="S317">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T317">
         <v>3.3</v>
@@ -52022,7 +52022,7 @@
         <v>1.72</v>
       </c>
       <c r="AB317">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC317">
         <v>2.66</v>
@@ -52146,16 +52146,16 @@
         <v>2.3</v>
       </c>
       <c r="O318">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="P318">
         <v>3.1</v>
       </c>
       <c r="Q318">
-        <v>2.94</v>
+        <v>2.67</v>
       </c>
       <c r="R318">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="S318">
         <v>1.53</v>
@@ -52164,10 +52164,10 @@
         <v>2.38</v>
       </c>
       <c r="U318">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="V318">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W318">
         <v>1.04</v>
@@ -52176,19 +52176,19 @@
         <v>1.1</v>
       </c>
       <c r="Y318">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="Z318">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="AA318">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="AB318">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AC318">
-        <v>5.02</v>
+        <v>4.93</v>
       </c>
       <c r="AD318">
         <v>1.14</v>
@@ -52197,10 +52197,10 @@
         <v>1.01</v>
       </c>
       <c r="AF318">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AG318">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AH318" t="inlineStr">
         <is>
@@ -52213,7 +52213,7 @@
         </is>
       </c>
       <c r="AJ318">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AK318">
         <v>1.36</v>
@@ -52306,13 +52306,13 @@
         </is>
       </c>
       <c r="N319">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="O319">
-        <v>3.44</v>
+        <v>3.61</v>
       </c>
       <c r="P319">
-        <v>2.47</v>
+        <v>2.28</v>
       </c>
       <c r="Q319">
         <v>2.75</v>
@@ -52333,7 +52333,7 @@
         <v>1.62</v>
       </c>
       <c r="W319">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X319">
         <v>1.02</v>
@@ -52348,10 +52348,10 @@
         <v>1.46</v>
       </c>
       <c r="AB319">
-        <v>2.38</v>
+        <v>2.02</v>
       </c>
       <c r="AC319">
-        <v>2.22</v>
+        <v>1.96</v>
       </c>
       <c r="AD319">
         <v>1.56</v>
@@ -52379,7 +52379,7 @@
         <v>1.19</v>
       </c>
       <c r="AK319">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL319">
         <v>0</v>
@@ -52478,7 +52478,7 @@
         <v>1.53</v>
       </c>
       <c r="Q320">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="R320">
         <v>2.63</v>
@@ -52490,10 +52490,10 @@
         <v>4.3</v>
       </c>
       <c r="U320">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="V320">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="W320">
         <v>1.2</v>
@@ -52502,31 +52502,31 @@
         <v>1.01</v>
       </c>
       <c r="Y320">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Z320">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AA320">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AB320">
-        <v>2.83</v>
+        <v>2.45</v>
       </c>
       <c r="AC320">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AD320">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="AE320">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AF320">
         <v>1.44</v>
       </c>
       <c r="AG320">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AH320" t="inlineStr">
         <is>
@@ -52539,10 +52539,10 @@
         </is>
       </c>
       <c r="AJ320">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AK320">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AL320">
         <v>0</v>
@@ -52641,10 +52641,10 @@
         <v>10.53</v>
       </c>
       <c r="Q321">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="R321">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="S321">
         <v>1.18</v>
@@ -52653,10 +52653,10 @@
         <v>4.2</v>
       </c>
       <c r="U321">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="V321">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="W321">
         <v>1.23</v>
@@ -52665,16 +52665,16 @@
         <v>1.01</v>
       </c>
       <c r="Y321">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Z321">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AA321">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AB321">
-        <v>2.83</v>
+        <v>2.45</v>
       </c>
       <c r="AC321">
         <v>1.89</v>
@@ -52683,13 +52683,13 @@
         <v>1.78</v>
       </c>
       <c r="AE321">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AF321">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AG321">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AH321" t="inlineStr">
         <is>
@@ -52702,10 +52702,10 @@
         </is>
       </c>
       <c r="AJ321">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AK321">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL321">
         <v>0</v>
@@ -52973,7 +52973,7 @@
         <v>2.3</v>
       </c>
       <c r="S323">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T323">
         <v>3.5</v>
@@ -52991,10 +52991,10 @@
         <v>1.02</v>
       </c>
       <c r="Y323">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z323">
-        <v>5.1</v>
+        <v>3.3</v>
       </c>
       <c r="AA323">
         <v>1.49</v>
@@ -53006,7 +53006,7 @@
         <v>2.31</v>
       </c>
       <c r="AD323">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="AE323">
         <v>1.18</v>
@@ -53133,16 +53133,16 @@
         <v>2.1</v>
       </c>
       <c r="R324">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="S324">
         <v>1.29</v>
       </c>
       <c r="T324">
-        <v>3.08</v>
+        <v>2.63</v>
       </c>
       <c r="U324">
-        <v>2.41</v>
+        <v>2.01</v>
       </c>
       <c r="V324">
         <v>1.5</v>
@@ -53154,10 +53154,10 @@
         <v>1.03</v>
       </c>
       <c r="Y324">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z324">
-        <v>4</v>
+        <v>3.13</v>
       </c>
       <c r="AA324">
         <v>1.63</v>
@@ -53172,7 +53172,7 @@
         <v>1.41</v>
       </c>
       <c r="AE324">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF324">
         <v>1.62</v>
@@ -53191,7 +53191,7 @@
         </is>
       </c>
       <c r="AJ324">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="AK324">
         <v>2.05</v>
@@ -53317,31 +53317,31 @@
         <v>1.03</v>
       </c>
       <c r="Y325">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z325">
-        <v>4.25</v>
+        <v>3.2</v>
       </c>
       <c r="AA325">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AB325">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="AC325">
-        <v>2.41</v>
+        <v>2.06</v>
       </c>
       <c r="AD325">
+        <v>1.4</v>
+      </c>
+      <c r="AE325">
+        <v>1.13</v>
+      </c>
+      <c r="AF325">
         <v>1.45</v>
       </c>
-      <c r="AE325">
-        <v>1.16</v>
-      </c>
-      <c r="AF325">
-        <v>1.55</v>
-      </c>
       <c r="AG325">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AH325" t="inlineStr">
         <is>
@@ -53465,7 +53465,7 @@
         <v>1.22</v>
       </c>
       <c r="T326">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U326">
         <v>1.88</v>
@@ -53610,7 +53610,7 @@
         </is>
       </c>
       <c r="N327">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="O327">
         <v>3.42</v>
@@ -53788,10 +53788,10 @@
         <v>2.36</v>
       </c>
       <c r="S328">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T328">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U328">
         <v>2.05</v>
@@ -53800,7 +53800,7 @@
         <v>1.65</v>
       </c>
       <c r="W328">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X328">
         <v>1.02</v>
@@ -53812,7 +53812,7 @@
         <v>5.1</v>
       </c>
       <c r="AA328">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AB328">
         <v>2.46</v>
@@ -53843,10 +53843,10 @@
         </is>
       </c>
       <c r="AJ328">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK328">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AL328">
         <v>0</v>
@@ -53936,10 +53936,10 @@
         </is>
       </c>
       <c r="N329">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="O329">
-        <v>4.02</v>
+        <v>3.8</v>
       </c>
       <c r="P329">
         <v>2.32</v>
@@ -54126,7 +54126,7 @@
         <v>1.61</v>
       </c>
       <c r="W330">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X330">
         <v>0</v>
@@ -54141,7 +54141,7 @@
         <v>1.5</v>
       </c>
       <c r="AB330">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="AC330">
         <v>2.19</v>
@@ -54262,13 +54262,13 @@
         </is>
       </c>
       <c r="N331">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="O331">
-        <v>3.71</v>
+        <v>3.63</v>
       </c>
       <c r="P331">
-        <v>5.2</v>
+        <v>5.45</v>
       </c>
       <c r="Q331">
         <v>2.05</v>
@@ -54289,7 +54289,7 @@
         <v>1.36</v>
       </c>
       <c r="W331">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X331">
         <v>1.01</v>

--- a/jogos_2026-11-01.xlsx
+++ b/jogos_2026-11-01.xlsx
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O4">
         <v>3</v>
       </c>
       <c r="P4">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="Q4">
         <v>3.25</v>
@@ -1124,28 +1124,28 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="O5">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="P5">
-        <v>3.07</v>
+        <v>3.2</v>
       </c>
       <c r="Q5">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="R5">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S5">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T5">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="U5">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="V5">
         <v>1.43</v>
@@ -2105,10 +2105,10 @@
         <v>1.85</v>
       </c>
       <c r="O11">
-        <v>3.25</v>
+        <v>3.43</v>
       </c>
       <c r="P11">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="Q11">
         <v>2.4</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK11">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2268,7 +2268,7 @@
         <v>1.75</v>
       </c>
       <c r="O12">
-        <v>3.4</v>
+        <v>3.47</v>
       </c>
       <c r="P12">
         <v>4</v>
@@ -3418,7 +3418,7 @@
         <v>3.1</v>
       </c>
       <c r="R19">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S19">
         <v>1.26</v>
@@ -3445,7 +3445,7 @@
         <v>4.1</v>
       </c>
       <c r="AA19">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AB19">
         <v>2.2</v>
@@ -3572,7 +3572,7 @@
         <v>3.09</v>
       </c>
       <c r="O20">
-        <v>3.68</v>
+        <v>3.53</v>
       </c>
       <c r="P20">
         <v>2.11</v>
@@ -3741,10 +3741,10 @@
         <v>10.5</v>
       </c>
       <c r="Q21">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="R21">
-        <v>2.59</v>
+        <v>2.46</v>
       </c>
       <c r="S21">
         <v>1.29</v>
@@ -3771,7 +3771,7 @@
         <v>4.66</v>
       </c>
       <c r="AA21">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB21">
         <v>2.19</v>
@@ -4224,13 +4224,13 @@
         <v>1.35</v>
       </c>
       <c r="O24">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P24">
         <v>5</v>
       </c>
       <c r="Q24">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="R24">
         <v>2.4</v>
@@ -4399,7 +4399,7 @@
         <v>2.16</v>
       </c>
       <c r="S25">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T25">
         <v>3.03</v>
@@ -4411,7 +4411,7 @@
         <v>1.44</v>
       </c>
       <c r="W25">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X25">
         <v>1.03</v>
@@ -4438,10 +4438,10 @@
         <v>1.09</v>
       </c>
       <c r="AF25">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG25">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="O38">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P38">
-        <v>4.6</v>
+        <v>5.25</v>
       </c>
       <c r="Q38">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="R38">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="S38">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="T38">
-        <v>3.46</v>
+        <v>3.38</v>
       </c>
       <c r="U38">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="V38">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W38">
         <v>1.11</v>
       </c>
       <c r="X38">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z38">
-        <v>4.45</v>
+        <v>4.2</v>
       </c>
       <c r="AA38">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB38">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC38">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="AD38">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE38">
         <v>1.14</v>
       </c>
       <c r="AF38">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG38">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK38">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="O39">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P39">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="Q39">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="R39">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="S39">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T39">
-        <v>3.75</v>
+        <v>3.46</v>
       </c>
       <c r="U39">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="V39">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="W39">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X39">
         <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z39">
-        <v>5.1</v>
+        <v>4.45</v>
       </c>
       <c r="AA39">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="AB39">
-        <v>2.41</v>
+        <v>2.2</v>
       </c>
       <c r="AC39">
-        <v>2.2</v>
+        <v>2.43</v>
       </c>
       <c r="AD39">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AE39">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AF39">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AG39">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK39">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>17.5</v>
+        <v>1.47</v>
       </c>
       <c r="O40">
-        <v>10</v>
+        <v>4.2</v>
       </c>
       <c r="P40">
-        <v>1.07</v>
+        <v>5</v>
       </c>
       <c r="Q40">
-        <v>14.5</v>
+        <v>1.91</v>
       </c>
       <c r="R40">
-        <v>3.02</v>
+        <v>2.6</v>
       </c>
       <c r="S40">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="T40">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="U40">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="V40">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="W40">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="Z40">
-        <v>9.300000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="AA40">
-        <v>1.23</v>
+        <v>1.45</v>
       </c>
       <c r="AB40">
-        <v>3.42</v>
+        <v>2.41</v>
       </c>
       <c r="AC40">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="AD40">
-        <v>2.08</v>
+        <v>1.57</v>
       </c>
       <c r="AE40">
-        <v>1.52</v>
+        <v>1.19</v>
       </c>
       <c r="AF40">
-        <v>2.24</v>
+        <v>1.58</v>
       </c>
       <c r="AG40">
-        <v>1.53</v>
+        <v>2.19</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AK40">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.47</v>
+        <v>17.5</v>
       </c>
       <c r="O41">
-        <v>4.1</v>
+        <v>10</v>
       </c>
       <c r="P41">
-        <v>5.25</v>
+        <v>1.07</v>
       </c>
       <c r="Q41">
-        <v>1.94</v>
+        <v>14.5</v>
       </c>
       <c r="R41">
-        <v>2.36</v>
+        <v>3.02</v>
       </c>
       <c r="S41">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="T41">
-        <v>3.38</v>
+        <v>5.5</v>
       </c>
       <c r="U41">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="V41">
+        <v>2.1</v>
+      </c>
+      <c r="W41">
+        <v>1.3</v>
+      </c>
+      <c r="X41">
+        <v>0</v>
+      </c>
+      <c r="Y41">
+        <v>1.02</v>
+      </c>
+      <c r="Z41">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AA41">
+        <v>1.23</v>
+      </c>
+      <c r="AB41">
+        <v>3.42</v>
+      </c>
+      <c r="AC41">
+        <v>1.6</v>
+      </c>
+      <c r="AD41">
+        <v>2.08</v>
+      </c>
+      <c r="AE41">
         <v>1.52</v>
       </c>
-      <c r="W41">
-        <v>1.11</v>
-      </c>
-      <c r="X41">
-        <v>1.02</v>
-      </c>
-      <c r="Y41">
-        <v>1.15</v>
-      </c>
-      <c r="Z41">
-        <v>4.2</v>
-      </c>
-      <c r="AA41">
-        <v>1.6</v>
-      </c>
-      <c r="AB41">
-        <v>2.15</v>
-      </c>
-      <c r="AC41">
-        <v>2.46</v>
-      </c>
-      <c r="AD41">
-        <v>1.43</v>
-      </c>
-      <c r="AE41">
-        <v>1.14</v>
-      </c>
       <c r="AF41">
-        <v>1.7</v>
+        <v>2.24</v>
       </c>
       <c r="AG41">
-        <v>1.96</v>
+        <v>1.53</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AK41">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -9313,10 +9313,10 @@
         <v>3.28</v>
       </c>
       <c r="AA55">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB55">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC55">
         <v>2.97</v>
@@ -9476,7 +9476,7 @@
         <v>2.83</v>
       </c>
       <c r="AA56">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB56">
         <v>1.63</v>
@@ -9999,7 +9999,7 @@
         <v>1.1</v>
       </c>
       <c r="AK59">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10974,7 +10974,7 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK65">
         <v>1.62</v>
@@ -11067,7 +11067,7 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="O66">
         <v>3.4</v>
@@ -11109,7 +11109,7 @@
         <v>1.72</v>
       </c>
       <c r="AB66">
-        <v>2.07</v>
+        <v>1.99</v>
       </c>
       <c r="AC66">
         <v>2.8</v>
@@ -13841,13 +13841,13 @@
         <v>2.4</v>
       </c>
       <c r="O83">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P83">
         <v>2.55</v>
       </c>
       <c r="Q83">
-        <v>3.04</v>
+        <v>2.75</v>
       </c>
       <c r="R83">
         <v>2.32</v>
@@ -14816,7 +14816,7 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="O89">
         <v>3.63</v>
@@ -15151,55 +15151,55 @@
         <v>1.74</v>
       </c>
       <c r="Q91">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="R91">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S91">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T91">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U91">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V91">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W91">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X91">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y91">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z91">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA91">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AB91">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AC91">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD91">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE91">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF91">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG91">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK91">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15311,10 +15311,10 @@
         <v>5.75</v>
       </c>
       <c r="P92">
-        <v>7.75</v>
+        <v>8.6</v>
       </c>
       <c r="Q92">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="R92">
         <v>3.44</v>
@@ -15344,7 +15344,7 @@
         <v>10.5</v>
       </c>
       <c r="AA92">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AB92">
         <v>4.2</v>
@@ -15378,7 +15378,7 @@
         <v>1.07</v>
       </c>
       <c r="AK92">
-        <v>3.75</v>
+        <v>3.44</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15483,7 +15483,7 @@
         <v>2.09</v>
       </c>
       <c r="S93">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T93">
         <v>2.72</v>
@@ -15501,7 +15501,7 @@
         <v>1.01</v>
       </c>
       <c r="Y93">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z93">
         <v>3.14</v>
@@ -15522,10 +15522,10 @@
         <v>1.06</v>
       </c>
       <c r="AF93">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AG93">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15661,7 +15661,7 @@
         <v>1.02</v>
       </c>
       <c r="X94">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y94">
         <v>1.4</v>
@@ -15670,16 +15670,16 @@
         <v>2.84</v>
       </c>
       <c r="AA94">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="AB94">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AC94">
-        <v>4.01</v>
+        <v>3.88</v>
       </c>
       <c r="AD94">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE94">
         <v>1.05</v>
@@ -15803,13 +15803,13 @@
         <v>1.95</v>
       </c>
       <c r="Q95">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="R95">
         <v>2.14</v>
       </c>
       <c r="S95">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="T95">
         <v>2.74</v>
@@ -15824,50 +15824,50 @@
         <v>1.02</v>
       </c>
       <c r="X95">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y95">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Z95">
-        <v>3.14</v>
+        <v>3.06</v>
       </c>
       <c r="AA95">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="AB95">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AC95">
         <v>3.76</v>
       </c>
       <c r="AD95">
+        <v>1.21</v>
+      </c>
+      <c r="AE95">
+        <v>1.03</v>
+      </c>
+      <c r="AF95">
+        <v>1.86</v>
+      </c>
+      <c r="AG95">
+        <v>1.84</v>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ95">
+        <v>1.31</v>
+      </c>
+      <c r="AK95">
         <v>1.25</v>
-      </c>
-      <c r="AE95">
-        <v>1.06</v>
-      </c>
-      <c r="AF95">
-        <v>1.83</v>
-      </c>
-      <c r="AG95">
-        <v>1.87</v>
-      </c>
-      <c r="AH95" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI95" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ95">
-        <v>1.3</v>
-      </c>
-      <c r="AK95">
-        <v>1.28</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -16123,7 +16123,7 @@
         <v>3.1</v>
       </c>
       <c r="O97">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P97">
         <v>2.42</v>
@@ -16289,7 +16289,7 @@
         <v>4.1</v>
       </c>
       <c r="P98">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Q98">
         <v>4.83</v>
@@ -16322,13 +16322,13 @@
         <v>4.78</v>
       </c>
       <c r="AA98">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AB98">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AC98">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="AD98">
         <v>1.53</v>
@@ -17445,7 +17445,7 @@
         <v>2.56</v>
       </c>
       <c r="U105">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="V105">
         <v>1.36</v>
@@ -18402,7 +18402,7 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="O111">
         <v>3.25</v>
@@ -19380,10 +19380,10 @@
         </is>
       </c>
       <c r="N117">
-        <v>3.83</v>
+        <v>3.8</v>
       </c>
       <c r="O117">
-        <v>3.95</v>
+        <v>3.92</v>
       </c>
       <c r="P117">
         <v>1.72</v>
@@ -19779,7 +19779,7 @@
         <v>1.2</v>
       </c>
       <c r="AK119">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19875,7 +19875,7 @@
         <v>3.8</v>
       </c>
       <c r="P120">
-        <v>2.35</v>
+        <v>2.18</v>
       </c>
       <c r="Q120">
         <v>3.1</v>
@@ -20521,7 +20521,7 @@
         </is>
       </c>
       <c r="N124">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="O124">
         <v>3.1</v>
@@ -20542,7 +20542,7 @@
         <v>2.75</v>
       </c>
       <c r="U124">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="V124">
         <v>1.33</v>
@@ -20693,7 +20693,7 @@
         <v>2.33</v>
       </c>
       <c r="Q125">
-        <v>3.74</v>
+        <v>3.28</v>
       </c>
       <c r="R125">
         <v>2</v>
@@ -20732,7 +20732,7 @@
         <v>3.28</v>
       </c>
       <c r="AD125">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE125">
         <v>1.05</v>
@@ -20754,7 +20754,7 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AK125">
         <v>1.36</v>
@@ -20868,7 +20868,7 @@
         <v>2.82</v>
       </c>
       <c r="U126">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="V126">
         <v>1.4</v>
@@ -20892,7 +20892,7 @@
         <v>1.9</v>
       </c>
       <c r="AC126">
-        <v>3.35</v>
+        <v>2.92</v>
       </c>
       <c r="AD126">
         <v>1.31</v>
@@ -21010,13 +21010,13 @@
         </is>
       </c>
       <c r="N127">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O127">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P127">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q127">
         <v>3.75</v>
@@ -21083,7 +21083,7 @@
         <v>1.3</v>
       </c>
       <c r="AK127">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21846,10 +21846,10 @@
         <v>3.42</v>
       </c>
       <c r="U132">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="V132">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="W132">
         <v>1.14</v>
@@ -21864,16 +21864,16 @@
         <v>4.6</v>
       </c>
       <c r="AA132">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AB132">
-        <v>2.3</v>
+        <v>1.99</v>
       </c>
       <c r="AC132">
-        <v>2.27</v>
+        <v>2</v>
       </c>
       <c r="AD132">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AE132">
         <v>1.19</v>
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="O133">
         <v>3.13</v>
       </c>
       <c r="P133">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="Q133">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="R133">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="S133">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T133">
         <v>2.75</v>
       </c>
       <c r="U133">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="V133">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W133">
         <v>1.06</v>
       </c>
       <c r="X133">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y133">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z133">
-        <v>2.95</v>
+        <v>3.06</v>
       </c>
       <c r="AA133">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AB133">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC133">
-        <v>3.55</v>
+        <v>3.42</v>
       </c>
       <c r="AD133">
         <v>1.27</v>
       </c>
       <c r="AE133">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF133">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AG133">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AK133">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22848,19 +22848,19 @@
         <v>1.7</v>
       </c>
       <c r="AC138">
-        <v>3.8</v>
+        <v>3.71</v>
       </c>
       <c r="AD138">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AE138">
         <v>1.02</v>
       </c>
       <c r="AF138">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AG138">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -23497,7 +23497,7 @@
         <v>1.53</v>
       </c>
       <c r="AB142">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="AC142">
         <v>2.42</v>
@@ -23781,7 +23781,7 @@
         </is>
       </c>
       <c r="N144">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="O144">
         <v>3.75</v>
@@ -23962,13 +23962,13 @@
         <v>1.33</v>
       </c>
       <c r="T145">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="U145">
         <v>2.6</v>
       </c>
       <c r="V145">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W145">
         <v>1.08</v>
@@ -24107,19 +24107,19 @@
         </is>
       </c>
       <c r="N146">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="O146">
         <v>3.9</v>
       </c>
       <c r="P146">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="Q146">
-        <v>2.61</v>
+        <v>2.42</v>
       </c>
       <c r="R146">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="S146">
         <v>1.19</v>
@@ -24152,13 +24152,13 @@
         <v>3</v>
       </c>
       <c r="AC146">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AD146">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AE146">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AF146">
         <v>1.38</v>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AK146">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24765,7 +24765,7 @@
         <v>3.7</v>
       </c>
       <c r="P150">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="Q150">
         <v>3.12</v>
@@ -26724,55 +26724,55 @@
         <v>13.2</v>
       </c>
       <c r="Q162">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="R162">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S162">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T162">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U162">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V162">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W162">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X162">
         <v>0</v>
       </c>
       <c r="Y162">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z162">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA162">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AB162">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AC162">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD162">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE162">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF162">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG162">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
@@ -26785,10 +26785,10 @@
         </is>
       </c>
       <c r="AJ162">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK162">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AL162">
         <v>0</v>
@@ -26881,10 +26881,10 @@
         <v>2.25</v>
       </c>
       <c r="O163">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="P163">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="Q163">
         <v>2.6</v>
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Castro Daire</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Guarda</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G166">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Estrela Calheta</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Guarda</t>
         </is>
       </c>
       <c r="G167">
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Ovarense</t>
+          <t>Estrela Calheta</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="G168">
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Ovarense</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G169">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Castro Daire</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G170">
@@ -28185,10 +28185,10 @@
         <v>1.48</v>
       </c>
       <c r="O171">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="P171">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Q171">
         <v>1.96</v>
@@ -28366,7 +28366,7 @@
         <v>3</v>
       </c>
       <c r="U172">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="V172">
         <v>1.4</v>
@@ -28547,10 +28547,10 @@
         <v>2.97</v>
       </c>
       <c r="AA173">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AB173">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AC173">
         <v>3.5</v>
@@ -29036,10 +29036,10 @@
         <v>0</v>
       </c>
       <c r="AA176">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AB176">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC176">
         <v>0</v>
@@ -31137,10 +31137,10 @@
         <v>3.08</v>
       </c>
       <c r="U189">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V189">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W189">
         <v>1.1</v>
@@ -31644,7 +31644,7 @@
         <v>9</v>
       </c>
       <c r="AA192">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AB192">
         <v>4.3</v>
@@ -32094,13 +32094,13 @@
         </is>
       </c>
       <c r="N195">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="O195">
         <v>3.35</v>
       </c>
       <c r="P195">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="Q195">
         <v>2.36</v>
@@ -32136,7 +32136,7 @@
         <v>1.64</v>
       </c>
       <c r="AB195">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AC195">
         <v>2.59</v>
@@ -32257,13 +32257,13 @@
         </is>
       </c>
       <c r="N196">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="O196">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="P196">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="Q196">
         <v>2</v>
@@ -32948,10 +32948,10 @@
         <v>4.15</v>
       </c>
       <c r="AA200">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AB200">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AC200">
         <v>2.66</v>
@@ -32963,7 +32963,7 @@
         <v>1.11</v>
       </c>
       <c r="AF200">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AG200">
         <v>2.21</v>
@@ -33280,7 +33280,7 @@
         <v>2.46</v>
       </c>
       <c r="AC202">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="AD202">
         <v>1.65</v>
@@ -33564,10 +33564,10 @@
         <v>1.83</v>
       </c>
       <c r="O204">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="P204">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="Q204">
         <v>2.3</v>
@@ -33591,7 +33591,7 @@
         <v>1.1</v>
       </c>
       <c r="X204">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y204">
         <v>1.21</v>
@@ -33634,7 +33634,7 @@
         <v>1.22</v>
       </c>
       <c r="AK204">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AL204">
         <v>0</v>
@@ -33724,13 +33724,13 @@
         </is>
       </c>
       <c r="N205">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="O205">
-        <v>4.45</v>
+        <v>4.85</v>
       </c>
       <c r="P205">
-        <v>7.27</v>
+        <v>6.75</v>
       </c>
       <c r="Q205">
         <v>1.8</v>
@@ -34868,7 +34868,7 @@
         <v>1.75</v>
       </c>
       <c r="O212">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="P212">
         <v>3.65</v>
@@ -34922,7 +34922,7 @@
         <v>1.44</v>
       </c>
       <c r="AG212">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AH212" t="inlineStr">
         <is>
@@ -35034,7 +35034,7 @@
         <v>4.2</v>
       </c>
       <c r="P213">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q213">
         <v>5</v>
@@ -35974,12 +35974,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G219">
@@ -36006,64 +36006,64 @@
         </is>
       </c>
       <c r="N219">
-        <v>1.96</v>
+        <v>1.51</v>
       </c>
       <c r="O219">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="P219">
-        <v>3.25</v>
+        <v>5.25</v>
       </c>
       <c r="Q219">
-        <v>2.5</v>
+        <v>1.89</v>
       </c>
       <c r="R219">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="S219">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T219">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="U219">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="V219">
-        <v>1.44</v>
+        <v>1.72</v>
       </c>
       <c r="W219">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="X219">
         <v>1</v>
       </c>
       <c r="Y219">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="Z219">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="AA219">
-        <v>1.74</v>
+        <v>1.43</v>
       </c>
       <c r="AB219">
-        <v>2.08</v>
+        <v>2.8</v>
       </c>
       <c r="AC219">
-        <v>2.88</v>
+        <v>2.05</v>
       </c>
       <c r="AD219">
-        <v>1.36</v>
+        <v>1.79</v>
       </c>
       <c r="AE219">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="AF219">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AG219">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AH219" t="inlineStr">
         <is>
@@ -36076,10 +36076,10 @@
         </is>
       </c>
       <c r="AJ219">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK219">
-        <v>1.73</v>
+        <v>2.42</v>
       </c>
       <c r="AL219">
         <v>0</v>
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G220">
@@ -36169,64 +36169,64 @@
         </is>
       </c>
       <c r="N220">
-        <v>1.51</v>
+        <v>1.96</v>
       </c>
       <c r="O220">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="P220">
-        <v>5.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q220">
-        <v>1.89</v>
+        <v>2.4</v>
       </c>
       <c r="R220">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="S220">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T220">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="U220">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="V220">
-        <v>1.72</v>
+        <v>1.44</v>
       </c>
       <c r="W220">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="X220">
         <v>1</v>
       </c>
       <c r="Y220">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="Z220">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="AA220">
-        <v>1.43</v>
+        <v>1.74</v>
       </c>
       <c r="AB220">
-        <v>2.8</v>
+        <v>2.08</v>
       </c>
       <c r="AC220">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="AD220">
-        <v>1.79</v>
+        <v>1.36</v>
       </c>
       <c r="AE220">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="AF220">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AG220">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="AH220" t="inlineStr">
         <is>
@@ -36239,10 +36239,10 @@
         </is>
       </c>
       <c r="AJ220">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AK220">
-        <v>2.42</v>
+        <v>1.73</v>
       </c>
       <c r="AL220">
         <v>0</v>
@@ -36565,7 +36565,7 @@
         </is>
       </c>
       <c r="AJ222">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AK222">
         <v>1.32</v>
@@ -36691,16 +36691,16 @@
         <v>1.01</v>
       </c>
       <c r="Y223">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z223">
-        <v>3.27</v>
+        <v>3.31</v>
       </c>
       <c r="AA223">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="AB223">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AC223">
         <v>3.47</v>
@@ -37367,7 +37367,7 @@
         <v>1.93</v>
       </c>
       <c r="AG227">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AH227" t="inlineStr">
         <is>
@@ -38789,19 +38789,19 @@
         <v>2.17</v>
       </c>
       <c r="R236">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="S236">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T236">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="U236">
-        <v>2.27</v>
+        <v>2.34</v>
       </c>
       <c r="V236">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="W236">
         <v>1.12</v>
@@ -38810,31 +38810,31 @@
         <v>0</v>
       </c>
       <c r="Y236">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z236">
-        <v>3.94</v>
+        <v>3.78</v>
       </c>
       <c r="AA236">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="AB236">
-        <v>2.08</v>
+        <v>2.01</v>
       </c>
       <c r="AC236">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="AD236">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE236">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF236">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG236">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AH236" t="inlineStr">
         <is>
@@ -38847,10 +38847,10 @@
         </is>
       </c>
       <c r="AJ236">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK236">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="AL236">
         <v>0</v>
@@ -40084,7 +40084,7 @@
         <v>1.57</v>
       </c>
       <c r="O244">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="P244">
         <v>5</v>
@@ -40102,10 +40102,10 @@
         <v>3.3</v>
       </c>
       <c r="U244">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="V244">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="W244">
         <v>1.12</v>
@@ -40434,16 +40434,16 @@
         <v>1.59</v>
       </c>
       <c r="W246">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X246">
         <v>1</v>
       </c>
       <c r="Y246">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z246">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AA246">
         <v>1.52</v>
@@ -40455,7 +40455,7 @@
         <v>2.45</v>
       </c>
       <c r="AD246">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AE246">
         <v>1.2</v>
@@ -40920,7 +40920,7 @@
         <v>3</v>
       </c>
       <c r="V249">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W249">
         <v>1.06</v>
@@ -41113,10 +41113,10 @@
         <v>1.11</v>
       </c>
       <c r="AF250">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG250">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AH250" t="inlineStr">
         <is>
@@ -41129,7 +41129,7 @@
         </is>
       </c>
       <c r="AJ250">
-        <v>1.59</v>
+        <v>1.25</v>
       </c>
       <c r="AK250">
         <v>1.35</v>
@@ -41590,7 +41590,7 @@
         <v>2</v>
       </c>
       <c r="AB253">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AC253">
         <v>3.5</v>
@@ -41750,10 +41750,10 @@
         <v>3.04</v>
       </c>
       <c r="AA254">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="AB254">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AC254">
         <v>3.5</v>
@@ -41913,10 +41913,10 @@
         <v>3.34</v>
       </c>
       <c r="AA255">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB255">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AC255">
         <v>3.04</v>
@@ -42209,10 +42209,10 @@
         <v>4.6</v>
       </c>
       <c r="Q257">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="R257">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="S257">
         <v>1.21</v>
@@ -42239,13 +42239,13 @@
         <v>5.98</v>
       </c>
       <c r="AA257">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AB257">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="AC257">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="AD257">
         <v>1.75</v>
@@ -42565,7 +42565,7 @@
         <v>4.33</v>
       </c>
       <c r="AA259">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB259">
         <v>2.1</v>
@@ -42855,7 +42855,7 @@
         <v>1.28</v>
       </c>
       <c r="O261">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="P261">
         <v>8</v>
@@ -43057,7 +43057,7 @@
         <v>1.74</v>
       </c>
       <c r="AB262">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AC262">
         <v>2.66</v>
@@ -43504,13 +43504,13 @@
         </is>
       </c>
       <c r="N265">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="O265">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="P265">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="Q265">
         <v>6.34</v>
@@ -43676,7 +43676,7 @@
         <v>2.45</v>
       </c>
       <c r="Q266">
-        <v>3.54</v>
+        <v>3.56</v>
       </c>
       <c r="R266">
         <v>1.91</v>
@@ -43740,7 +43740,7 @@
         <v>1.57</v>
       </c>
       <c r="AK266">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AL266">
         <v>0</v>
@@ -43830,10 +43830,10 @@
         </is>
       </c>
       <c r="N267">
-        <v>2.7</v>
+        <v>2.51</v>
       </c>
       <c r="O267">
-        <v>3.4</v>
+        <v>3.63</v>
       </c>
       <c r="P267">
         <v>2.22</v>
@@ -43999,7 +43999,7 @@
         <v>3.5</v>
       </c>
       <c r="P268">
-        <v>3.3</v>
+        <v>3.41</v>
       </c>
       <c r="Q268">
         <v>2.4</v>
@@ -44035,7 +44035,7 @@
         <v>1.57</v>
       </c>
       <c r="AB268">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="AC268">
         <v>2.49</v>
@@ -44319,13 +44319,13 @@
         </is>
       </c>
       <c r="N270">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="O270">
         <v>3.2</v>
       </c>
       <c r="P270">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Q270">
         <v>2.62</v>
@@ -44491,7 +44491,7 @@
         <v>2.96</v>
       </c>
       <c r="Q271">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R271">
         <v>2.1</v>
@@ -44715,7 +44715,7 @@
         </is>
       </c>
       <c r="AJ272">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK272">
         <v>1.75</v>
@@ -44811,7 +44811,7 @@
         <v>1.7</v>
       </c>
       <c r="O273">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="P273">
         <v>4.33</v>
@@ -45025,7 +45025,7 @@
         <v>1.1</v>
       </c>
       <c r="AF274">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AG274">
         <v>2.02</v>
@@ -45176,7 +45176,7 @@
         <v>2.1</v>
       </c>
       <c r="AB275">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AC275">
         <v>3.34</v>
@@ -45315,7 +45315,7 @@
         <v>1.36</v>
       </c>
       <c r="T276">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U276">
         <v>2.88</v>
@@ -46643,7 +46643,7 @@
         <v>1.49</v>
       </c>
       <c r="AB284">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="AC284">
         <v>2.3</v>
@@ -46671,7 +46671,7 @@
         </is>
       </c>
       <c r="AJ284">
-        <v>1.23</v>
+        <v>1.39</v>
       </c>
       <c r="AK284">
         <v>1.53</v>
@@ -46764,7 +46764,7 @@
         </is>
       </c>
       <c r="N285">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="O285">
         <v>3.75</v>
@@ -47090,7 +47090,7 @@
         </is>
       </c>
       <c r="N287">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="O287">
         <v>3.8</v>
@@ -47105,13 +47105,13 @@
         <v>2.34</v>
       </c>
       <c r="S287">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T287">
         <v>3.5</v>
       </c>
       <c r="U287">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="V287">
         <v>1.57</v>
@@ -47256,7 +47256,7 @@
         <v>1.85</v>
       </c>
       <c r="O288">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="P288">
         <v>3.5</v>
@@ -48071,10 +48071,10 @@
         <v>3.72</v>
       </c>
       <c r="O293">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P293">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q293">
         <v>0</v>
@@ -48107,10 +48107,10 @@
         <v>0</v>
       </c>
       <c r="AA293">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB293">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC293">
         <v>0</v>
@@ -48557,7 +48557,7 @@
         </is>
       </c>
       <c r="N296">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="O296">
         <v>3.3</v>
@@ -48572,7 +48572,7 @@
         <v>2.1</v>
       </c>
       <c r="S296">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T296">
         <v>2.66</v>
@@ -48596,10 +48596,10 @@
         <v>3.32</v>
       </c>
       <c r="AA296">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AB296">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AC296">
         <v>3.36</v>
@@ -48611,10 +48611,10 @@
         <v>1.06</v>
       </c>
       <c r="AF296">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG296">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH296" t="inlineStr">
         <is>
@@ -48762,7 +48762,7 @@
         <v>1.9</v>
       </c>
       <c r="AB297">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AC297">
         <v>3.2</v>
@@ -50350,7 +50350,7 @@
         </is>
       </c>
       <c r="N307">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="O307">
         <v>3.3</v>
@@ -50513,7 +50513,7 @@
         </is>
       </c>
       <c r="N308">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="O308">
         <v>3.4</v>
@@ -50909,7 +50909,7 @@
         </is>
       </c>
       <c r="AJ310">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AK310">
         <v>1.83</v>
@@ -51204,7 +51204,7 @@
         <v>2.11</v>
       </c>
       <c r="AA312">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AB312">
         <v>1.31</v>
@@ -51340,7 +51340,7 @@
         <v>1.8</v>
       </c>
       <c r="R313">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="S313">
         <v>1.22</v>
@@ -51382,10 +51382,10 @@
         <v>1.25</v>
       </c>
       <c r="AF313">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG313">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH313" t="inlineStr">
         <is>
@@ -51401,7 +51401,7 @@
         <v>1.18</v>
       </c>
       <c r="AK313">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AL313">
         <v>0</v>
@@ -51564,7 +51564,7 @@
         <v>1.25</v>
       </c>
       <c r="AK314">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AL314">
         <v>0</v>
@@ -51654,7 +51654,7 @@
         </is>
       </c>
       <c r="N315">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="O315">
         <v>4.2</v>
@@ -51696,7 +51696,7 @@
         <v>1.47</v>
       </c>
       <c r="AB315">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="AC315">
         <v>2.18</v>
@@ -51705,7 +51705,7 @@
         <v>1.68</v>
       </c>
       <c r="AE315">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AF315">
         <v>1.53</v>
@@ -53788,10 +53788,10 @@
         <v>2.36</v>
       </c>
       <c r="S328">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T328">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U328">
         <v>2.05</v>
@@ -53800,7 +53800,7 @@
         <v>1.65</v>
       </c>
       <c r="W328">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X328">
         <v>1.02</v>
@@ -53936,19 +53936,19 @@
         </is>
       </c>
       <c r="N329">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="O329">
-        <v>3.8</v>
+        <v>4.02</v>
       </c>
       <c r="P329">
         <v>2.32</v>
       </c>
       <c r="Q329">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="R329">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="S329">
         <v>1.14</v>
@@ -53990,7 +53990,7 @@
         <v>1.41</v>
       </c>
       <c r="AF329">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AG329">
         <v>3.25</v>
@@ -54120,7 +54120,7 @@
         <v>3.6</v>
       </c>
       <c r="U330">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="V330">
         <v>1.61</v>
@@ -54132,16 +54132,16 @@
         <v>0</v>
       </c>
       <c r="Y330">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="Z330">
-        <v>5.12</v>
+        <v>5.25</v>
       </c>
       <c r="AA330">
         <v>1.5</v>
       </c>
       <c r="AB330">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AC330">
         <v>2.19</v>
@@ -54150,10 +54150,10 @@
         <v>1.58</v>
       </c>
       <c r="AE330">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AF330">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AG330">
         <v>2.38</v>
@@ -54268,7 +54268,7 @@
         <v>3.63</v>
       </c>
       <c r="P331">
-        <v>5.45</v>
+        <v>5</v>
       </c>
       <c r="Q331">
         <v>2.05</v>
@@ -54301,7 +54301,7 @@
         <v>3.05</v>
       </c>
       <c r="AA331">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB331">
         <v>1.74</v>
@@ -54446,7 +54446,7 @@
         <v>3.6</v>
       </c>
       <c r="U332">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="V332">
         <v>1.6</v>
@@ -54467,13 +54467,13 @@
         <v>1.51</v>
       </c>
       <c r="AB332">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="AC332">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="AD332">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AE332">
         <v>1.18</v>
@@ -54495,10 +54495,10 @@
         </is>
       </c>
       <c r="AJ332">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK332">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AL332">
         <v>0</v>

--- a/jogos_2026-11-01.xlsx
+++ b/jogos_2026-11-01.xlsx
@@ -656,7 +656,7 @@
         <v>3.6</v>
       </c>
       <c r="U2">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="V2">
         <v>1.6</v>
@@ -692,7 +692,7 @@
         <v>1.65</v>
       </c>
       <c r="AG2">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -2784,13 +2784,13 @@
         <v>1.12</v>
       </c>
       <c r="X15">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
         <v>1.18</v>
       </c>
       <c r="Z15">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="AA15">
         <v>1.66</v>
@@ -3448,7 +3448,7 @@
         <v>1.7</v>
       </c>
       <c r="AB19">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC19">
         <v>2.59</v>
@@ -4384,25 +4384,25 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="O25">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="P25">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="Q25">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="R25">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="S25">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="T25">
-        <v>3.08</v>
+        <v>3.03</v>
       </c>
       <c r="U25">
         <v>2.59</v>
@@ -4411,10 +4411,10 @@
         <v>1.44</v>
       </c>
       <c r="W25">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X25">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y25">
         <v>1.19</v>
@@ -4423,7 +4423,7 @@
         <v>3.74</v>
       </c>
       <c r="AA25">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AB25">
         <v>2</v>
@@ -4457,7 +4457,7 @@
         <v>1.17</v>
       </c>
       <c r="AK25">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4565,7 +4565,7 @@
         <v>1.3</v>
       </c>
       <c r="T26">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U26">
         <v>2.5</v>
@@ -4586,25 +4586,25 @@
         <v>3.7</v>
       </c>
       <c r="AA26">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AB26">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AC26">
-        <v>2.74</v>
+        <v>2.87</v>
       </c>
       <c r="AD26">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AE26">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF26">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AG26">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4710,19 +4710,19 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="O27">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="P27">
-        <v>3.16</v>
+        <v>3.5</v>
       </c>
       <c r="Q27">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="R27">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="S27">
         <v>1.38</v>
@@ -4731,28 +4731,28 @@
         <v>2.8</v>
       </c>
       <c r="U27">
-        <v>2.9</v>
+        <v>2.99</v>
       </c>
       <c r="V27">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W27">
         <v>1.05</v>
       </c>
       <c r="X27">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z27">
-        <v>2.97</v>
+        <v>3.09</v>
       </c>
       <c r="AA27">
         <v>2.04</v>
       </c>
       <c r="AB27">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC27">
         <v>3.58</v>
@@ -4761,7 +4761,7 @@
         <v>1.21</v>
       </c>
       <c r="AE27">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF27">
         <v>1.84</v>
@@ -6180,7 +6180,7 @@
         <v>4.6</v>
       </c>
       <c r="O36">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P36">
         <v>1.63</v>
@@ -6340,19 +6340,19 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="O37">
-        <v>3.38</v>
+        <v>3.2</v>
       </c>
       <c r="P37">
-        <v>3.74</v>
+        <v>3.6</v>
       </c>
       <c r="Q37">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="R37">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S37">
         <v>1.4</v>
@@ -6364,13 +6364,13 @@
         <v>3</v>
       </c>
       <c r="V37">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W37">
         <v>1.06</v>
       </c>
       <c r="X37">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y37">
         <v>1.33</v>
@@ -6379,19 +6379,19 @@
         <v>2.81</v>
       </c>
       <c r="AA37">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB37">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AC37">
-        <v>3.82</v>
+        <v>4</v>
       </c>
       <c r="AD37">
         <v>1.17</v>
       </c>
       <c r="AE37">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF37">
         <v>1.91</v>
@@ -6413,7 +6413,7 @@
         <v>1.24</v>
       </c>
       <c r="AK37">
-        <v>1.86</v>
+        <v>1.68</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
+        <v>1.47</v>
+      </c>
+      <c r="O38">
+        <v>4.1</v>
+      </c>
+      <c r="P38">
+        <v>5.25</v>
+      </c>
+      <c r="Q38">
+        <v>1.94</v>
+      </c>
+      <c r="R38">
+        <v>2.36</v>
+      </c>
+      <c r="S38">
+        <v>1.24</v>
+      </c>
+      <c r="T38">
+        <v>3.38</v>
+      </c>
+      <c r="U38">
+        <v>2.25</v>
+      </c>
+      <c r="V38">
+        <v>1.52</v>
+      </c>
+      <c r="W38">
         <v>1.11</v>
       </c>
-      <c r="O38">
-        <v>8.5</v>
-      </c>
-      <c r="P38">
-        <v>15</v>
-      </c>
-      <c r="Q38">
+      <c r="X38">
+        <v>1.02</v>
+      </c>
+      <c r="Y38">
+        <v>1.15</v>
+      </c>
+      <c r="Z38">
+        <v>4.2</v>
+      </c>
+      <c r="AA38">
+        <v>1.6</v>
+      </c>
+      <c r="AB38">
+        <v>2.15</v>
+      </c>
+      <c r="AC38">
+        <v>2.46</v>
+      </c>
+      <c r="AD38">
         <v>1.43</v>
       </c>
-      <c r="R38">
-        <v>2.88</v>
-      </c>
-      <c r="S38">
+      <c r="AE38">
         <v>1.14</v>
       </c>
-      <c r="T38">
-        <v>5</v>
-      </c>
-      <c r="U38">
-        <v>1.8</v>
-      </c>
-      <c r="V38">
-        <v>1.91</v>
-      </c>
-      <c r="W38">
-        <v>1.25</v>
-      </c>
-      <c r="X38">
-        <v>1.01</v>
-      </c>
-      <c r="Y38">
-        <v>1.05</v>
-      </c>
-      <c r="Z38">
-        <v>6.55</v>
-      </c>
-      <c r="AA38">
-        <v>1.28</v>
-      </c>
-      <c r="AB38">
-        <v>3.05</v>
-      </c>
-      <c r="AC38">
-        <v>1.77</v>
-      </c>
-      <c r="AD38">
-        <v>1.9</v>
-      </c>
-      <c r="AE38">
-        <v>1.38</v>
-      </c>
       <c r="AF38">
-        <v>2.18</v>
+        <v>1.7</v>
       </c>
       <c r="AG38">
-        <v>1.56</v>
+        <v>1.96</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AK38">
-        <v>5.75</v>
+        <v>2.38</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.47</v>
+        <v>1.11</v>
       </c>
       <c r="O39">
-        <v>4.1</v>
+        <v>8.5</v>
       </c>
       <c r="P39">
-        <v>5.25</v>
+        <v>15</v>
       </c>
       <c r="Q39">
-        <v>1.94</v>
+        <v>1.43</v>
       </c>
       <c r="R39">
-        <v>2.36</v>
+        <v>2.88</v>
       </c>
       <c r="S39">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="T39">
-        <v>3.38</v>
+        <v>5</v>
       </c>
       <c r="U39">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="V39">
-        <v>1.52</v>
+        <v>1.91</v>
       </c>
       <c r="W39">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="X39">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="Z39">
-        <v>4.2</v>
+        <v>6.55</v>
       </c>
       <c r="AA39">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="AB39">
-        <v>2.15</v>
+        <v>3.05</v>
       </c>
       <c r="AC39">
-        <v>2.46</v>
+        <v>1.77</v>
       </c>
       <c r="AD39">
-        <v>1.43</v>
+        <v>1.9</v>
       </c>
       <c r="AE39">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AF39">
-        <v>1.7</v>
+        <v>2.18</v>
       </c>
       <c r="AG39">
-        <v>1.96</v>
+        <v>1.56</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="AK39">
-        <v>2.38</v>
+        <v>5.75</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q43">
         <v>2.45</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q44">
         <v>2.3</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mijas Las Lagunas</t>
+          <t>CD Don Benito</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q45">
         <v>2.4</v>
       </c>
       <c r="R45">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="S45">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="T45">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="U45">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="V45">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W45">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X45">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y45">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z45">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AA45">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AB45">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AC45">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="AD45">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AE45">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF45">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG45">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>1.3</v>
       </c>
       <c r="AK45">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CD Don Benito</t>
+          <t>Mijas Las Lagunas</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q46">
         <v>2.4</v>
       </c>
       <c r="R46">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="S46">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="T46">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="U46">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="V46">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W46">
+        <v>1.08</v>
+      </c>
+      <c r="X46">
+        <v>1.01</v>
+      </c>
+      <c r="Y46">
+        <v>1.22</v>
+      </c>
+      <c r="Z46">
+        <v>3.5</v>
+      </c>
+      <c r="AA46">
+        <v>1.9</v>
+      </c>
+      <c r="AB46">
+        <v>1.88</v>
+      </c>
+      <c r="AC46">
+        <v>3.04</v>
+      </c>
+      <c r="AD46">
+        <v>1.29</v>
+      </c>
+      <c r="AE46">
         <v>1.1</v>
       </c>
-      <c r="X46">
-        <v>1</v>
-      </c>
-      <c r="Y46">
-        <v>1.21</v>
-      </c>
-      <c r="Z46">
-        <v>3.58</v>
-      </c>
-      <c r="AA46">
-        <v>1.78</v>
-      </c>
-      <c r="AB46">
-        <v>1.89</v>
-      </c>
-      <c r="AC46">
-        <v>2.92</v>
-      </c>
-      <c r="AD46">
-        <v>1.31</v>
-      </c>
-      <c r="AE46">
-        <v>1.11</v>
-      </c>
       <c r="AF46">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG46">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         <v>1.3</v>
       </c>
       <c r="AK46">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8136,7 +8136,7 @@
         <v>1.8</v>
       </c>
       <c r="O48">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P48">
         <v>4.03</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="O49">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="P49">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="Q49">
         <v>4</v>
@@ -8320,25 +8320,25 @@
         <v>2.65</v>
       </c>
       <c r="V49">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W49">
         <v>1.08</v>
       </c>
       <c r="X49">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Z49">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="AA49">
         <v>1.93</v>
       </c>
       <c r="AB49">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC49">
         <v>3.2</v>
@@ -8347,7 +8347,7 @@
         <v>1.26</v>
       </c>
       <c r="AE49">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF49">
         <v>1.83</v>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="O50">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P50">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="Q50">
         <v>2.1</v>
@@ -8480,7 +8480,7 @@
         <v>3</v>
       </c>
       <c r="U50">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="V50">
         <v>1.4</v>
@@ -8501,7 +8501,7 @@
         <v>1.85</v>
       </c>
       <c r="AB50">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AC50">
         <v>3.04</v>
@@ -8510,7 +8510,7 @@
         <v>1.29</v>
       </c>
       <c r="AE50">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF50">
         <v>1.83</v>
@@ -8622,19 +8622,19 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="O51">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="P51">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="Q51">
         <v>2.7</v>
       </c>
       <c r="R51">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="S51">
         <v>1.38</v>
@@ -8652,7 +8652,7 @@
         <v>1.04</v>
       </c>
       <c r="X51">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y51">
         <v>1.32</v>
@@ -8673,7 +8673,7 @@
         <v>1.18</v>
       </c>
       <c r="AE51">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF51">
         <v>1.85</v>
@@ -8957,10 +8957,10 @@
         <v>2.9</v>
       </c>
       <c r="Q53">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="R53">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S53">
         <v>1.22</v>
@@ -8978,7 +8978,7 @@
         <v>1.11</v>
       </c>
       <c r="X53">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y53">
         <v>1.18</v>
@@ -8990,16 +8990,16 @@
         <v>1.59</v>
       </c>
       <c r="AB53">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AC53">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="AD53">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AE53">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AF53">
         <v>1.5</v>
@@ -9120,10 +9120,10 @@
         <v>2.5</v>
       </c>
       <c r="Q54">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="R54">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="S54">
         <v>1.36</v>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK54">
         <v>1.44</v>
@@ -9926,10 +9926,10 @@
         </is>
       </c>
       <c r="N59">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="O59">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P59">
         <v>1.55</v>
@@ -9983,7 +9983,7 @@
         <v>1.99</v>
       </c>
       <c r="AG59">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -10252,16 +10252,16 @@
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Q61">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="R61">
         <v>3.3</v>
@@ -10270,13 +10270,13 @@
         <v>1.14</v>
       </c>
       <c r="T61">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="U61">
         <v>1.67</v>
       </c>
       <c r="V61">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="W61">
         <v>1.27</v>
@@ -10291,22 +10291,22 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AA61">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AB61">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AC61">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AD61">
-        <v>2.12</v>
+        <v>2.19</v>
       </c>
       <c r="AE61">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AF61">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AG61">
         <v>2.12</v>
@@ -10415,61 +10415,61 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q62">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="R62">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="S62">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T62">
-        <v>3.98</v>
+        <v>3.85</v>
       </c>
       <c r="U62">
         <v>2.13</v>
       </c>
       <c r="V62">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W62">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X62">
         <v>1.02</v>
       </c>
       <c r="Y62">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Z62">
         <v>5.5</v>
       </c>
       <c r="AA62">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AB62">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="AC62">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AD62">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AE62">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AF62">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG62">
         <v>2.25</v>
@@ -10488,7 +10488,7 @@
         <v>1.18</v>
       </c>
       <c r="AK62">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -11728,55 +11728,55 @@
         <v>1.9</v>
       </c>
       <c r="Q70">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R70">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S70">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T70">
         <v>3.5</v>
       </c>
       <c r="U70">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="V70">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W70">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X70">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y70">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z70">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA70">
         <v>1.65</v>
       </c>
       <c r="AB70">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="AC70">
-        <v>2.46</v>
+        <v>2.51</v>
       </c>
       <c r="AD70">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AE70">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AF70">
         <v>1.5</v>
       </c>
       <c r="AG70">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK70">
         <v>1.4</v>
@@ -11891,55 +11891,55 @@
         <v>26</v>
       </c>
       <c r="Q71">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="R71">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="S71">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="T71">
         <v>5.5</v>
       </c>
       <c r="U71">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="V71">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="W71">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="X71">
         <v>1</v>
       </c>
       <c r="Y71">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Z71">
         <v>9.300000000000001</v>
       </c>
       <c r="AA71">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AB71">
         <v>4.1</v>
       </c>
       <c r="AC71">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AD71">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="AE71">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AF71">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG71">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AK71">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12706,22 +12706,22 @@
         <v>1.97</v>
       </c>
       <c r="Q76">
-        <v>4.12</v>
+        <v>3.8</v>
       </c>
       <c r="R76">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="S76">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T76">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U76">
-        <v>2.61</v>
+        <v>2.75</v>
       </c>
       <c r="V76">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W76">
         <v>1.07</v>
@@ -12730,16 +12730,16 @@
         <v>1.01</v>
       </c>
       <c r="Y76">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z76">
         <v>3.5</v>
       </c>
       <c r="AA76">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AB76">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AC76">
         <v>3.04</v>
@@ -12751,10 +12751,10 @@
         <v>1.07</v>
       </c>
       <c r="AF76">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AG76">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK76">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -13065,7 +13065,7 @@
         <v>1.85</v>
       </c>
       <c r="AB78">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AC78">
         <v>2.92</v>
@@ -13192,7 +13192,7 @@
         <v>3.42</v>
       </c>
       <c r="P79">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="Q79">
         <v>2.8</v>
@@ -13231,10 +13231,10 @@
         <v>2.13</v>
       </c>
       <c r="AC79">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="AD79">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE79">
         <v>1.12</v>
@@ -13243,7 +13243,7 @@
         <v>1.51</v>
       </c>
       <c r="AG79">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13259,7 +13259,7 @@
         <v>1.2</v>
       </c>
       <c r="AK79">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,25 +14001,25 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="O84">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="P84">
+        <v>2.9</v>
+      </c>
+      <c r="Q84">
         <v>2.55</v>
       </c>
-      <c r="Q84">
-        <v>2.75</v>
-      </c>
       <c r="R84">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="S84">
         <v>1.22</v>
       </c>
       <c r="T84">
-        <v>3.8</v>
+        <v>3.56</v>
       </c>
       <c r="U84">
         <v>2.15</v>
@@ -14034,31 +14034,31 @@
         <v>1.02</v>
       </c>
       <c r="Y84">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z84">
-        <v>4.85</v>
+        <v>5.25</v>
       </c>
       <c r="AA84">
         <v>1.5</v>
       </c>
       <c r="AB84">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="AC84">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="AD84">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AE84">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF84">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG84">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AK84">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,25 +14164,25 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="O85">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="P85">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="Q85">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="R85">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="S85">
         <v>1.22</v>
       </c>
       <c r="T85">
-        <v>3.56</v>
+        <v>3.8</v>
       </c>
       <c r="U85">
         <v>2.15</v>
@@ -14197,32 +14197,32 @@
         <v>1.02</v>
       </c>
       <c r="Y85">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z85">
-        <v>5.25</v>
+        <v>4.85</v>
       </c>
       <c r="AA85">
         <v>1.5</v>
       </c>
       <c r="AB85">
+        <v>2.35</v>
+      </c>
+      <c r="AC85">
+        <v>2.33</v>
+      </c>
+      <c r="AD85">
+        <v>1.58</v>
+      </c>
+      <c r="AE85">
+        <v>1.18</v>
+      </c>
+      <c r="AF85">
+        <v>1.44</v>
+      </c>
+      <c r="AG85">
         <v>2.55</v>
       </c>
-      <c r="AC85">
-        <v>2.28</v>
-      </c>
-      <c r="AD85">
-        <v>1.63</v>
-      </c>
-      <c r="AE85">
-        <v>1.22</v>
-      </c>
-      <c r="AF85">
-        <v>1.4</v>
-      </c>
-      <c r="AG85">
-        <v>2.5</v>
-      </c>
       <c r="AH85" t="inlineStr">
         <is>
           <t>[]</t>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AK85">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14653,10 +14653,10 @@
         </is>
       </c>
       <c r="N88">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="O88">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P88">
         <v>3.4</v>
@@ -14710,7 +14710,7 @@
         <v>1.5</v>
       </c>
       <c r="AG88">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.81</v>
+        <v>1.31</v>
       </c>
       <c r="O90">
-        <v>3.68</v>
+        <v>5.25</v>
       </c>
       <c r="P90">
-        <v>3.45</v>
+        <v>7.25</v>
       </c>
       <c r="Q90">
-        <v>2.34</v>
+        <v>1.72</v>
       </c>
       <c r="R90">
-        <v>2.44</v>
+        <v>2.96</v>
       </c>
       <c r="S90">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="T90">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="U90">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="V90">
-        <v>1.51</v>
+        <v>1.7</v>
       </c>
       <c r="W90">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="X90">
         <v>1</v>
       </c>
       <c r="Y90">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="Z90">
-        <v>4.19</v>
+        <v>6.5</v>
       </c>
       <c r="AA90">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AB90">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="AC90">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="AD90">
-        <v>1.46</v>
+        <v>1.71</v>
       </c>
       <c r="AE90">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="AF90">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG90">
-        <v>2.26</v>
+        <v>2.06</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="AK90">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.31</v>
+        <v>1.81</v>
       </c>
       <c r="O91">
-        <v>5.25</v>
+        <v>3.68</v>
       </c>
       <c r="P91">
-        <v>7.25</v>
+        <v>3.45</v>
       </c>
       <c r="Q91">
-        <v>1.72</v>
+        <v>2.34</v>
       </c>
       <c r="R91">
-        <v>2.96</v>
+        <v>2.44</v>
       </c>
       <c r="S91">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="T91">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="U91">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="V91">
-        <v>1.7</v>
+        <v>1.51</v>
       </c>
       <c r="W91">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="X91">
         <v>1</v>
       </c>
       <c r="Y91">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="Z91">
-        <v>6.5</v>
+        <v>4.19</v>
       </c>
       <c r="AA91">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AB91">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AC91">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="AD91">
-        <v>1.71</v>
+        <v>1.46</v>
       </c>
       <c r="AE91">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="AF91">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AG91">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AK91">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15344,7 +15344,7 @@
         <v>3.2</v>
       </c>
       <c r="AA92">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AB92">
         <v>1.76</v>
@@ -16938,7 +16938,7 @@
         <v>6.16</v>
       </c>
       <c r="O102">
-        <v>4.75</v>
+        <v>4.55</v>
       </c>
       <c r="P102">
         <v>1.43</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O104">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P104">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q104">
-        <v>4</v>
+        <v>2.61</v>
       </c>
       <c r="R104">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="S104">
         <v>1.33</v>
       </c>
       <c r="T104">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U104">
         <v>2.62</v>
       </c>
       <c r="V104">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W104">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X104">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y104">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z104">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="AA104">
+        <v>1.9</v>
+      </c>
+      <c r="AB104">
         <v>1.87</v>
       </c>
-      <c r="AB104">
-        <v>1.95</v>
-      </c>
       <c r="AC104">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="AD104">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE104">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF104">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG104">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17334,7 +17334,7 @@
         <v>1.3</v>
       </c>
       <c r="AK104">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O105">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P105">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q105">
-        <v>2.61</v>
+        <v>4</v>
       </c>
       <c r="R105">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="S105">
         <v>1.33</v>
       </c>
       <c r="T105">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U105">
         <v>2.62</v>
       </c>
       <c r="V105">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W105">
+        <v>1.1</v>
+      </c>
+      <c r="X105">
+        <v>1</v>
+      </c>
+      <c r="Y105">
+        <v>1.24</v>
+      </c>
+      <c r="Z105">
+        <v>3.6</v>
+      </c>
+      <c r="AA105">
+        <v>1.87</v>
+      </c>
+      <c r="AB105">
+        <v>1.95</v>
+      </c>
+      <c r="AC105">
+        <v>3.2</v>
+      </c>
+      <c r="AD105">
+        <v>1.3</v>
+      </c>
+      <c r="AE105">
         <v>1.08</v>
       </c>
-      <c r="X105">
-        <v>1.01</v>
-      </c>
-      <c r="Y105">
-        <v>1.23</v>
-      </c>
-      <c r="Z105">
-        <v>3.42</v>
-      </c>
-      <c r="AA105">
-        <v>1.9</v>
-      </c>
-      <c r="AB105">
-        <v>1.87</v>
-      </c>
-      <c r="AC105">
-        <v>3.05</v>
-      </c>
-      <c r="AD105">
-        <v>1.28</v>
-      </c>
-      <c r="AE105">
-        <v>1.07</v>
-      </c>
       <c r="AF105">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG105">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17497,7 +17497,7 @@
         <v>1.3</v>
       </c>
       <c r="AK105">
-        <v>1.7</v>
+        <v>1.25</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17608,7 +17608,7 @@
         <v>2.56</v>
       </c>
       <c r="U106">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="V106">
         <v>1.36</v>
@@ -18239,16 +18239,16 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="O110">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P110">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="Q110">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="R110">
         <v>2.3</v>
@@ -18293,7 +18293,7 @@
         <v>1.14</v>
       </c>
       <c r="AF110">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AG110">
         <v>2.2</v>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK110">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18604,10 +18604,10 @@
         <v>3.58</v>
       </c>
       <c r="AA112">
+        <v>1.87</v>
+      </c>
+      <c r="AB112">
         <v>1.9</v>
-      </c>
-      <c r="AB112">
-        <v>1.87</v>
       </c>
       <c r="AC112">
         <v>2.88</v>
@@ -19220,7 +19220,7 @@
         <v>2.8</v>
       </c>
       <c r="O116">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="P116">
         <v>2.19</v>
@@ -19398,7 +19398,7 @@
         <v>1.28</v>
       </c>
       <c r="T117">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U117">
         <v>2.45</v>
@@ -19419,13 +19419,13 @@
         <v>3.84</v>
       </c>
       <c r="AA117">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AB117">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AC117">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="AD117">
         <v>1.35</v>
@@ -19437,7 +19437,7 @@
         <v>1.73</v>
       </c>
       <c r="AG117">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19872,13 +19872,13 @@
         <v>2.76</v>
       </c>
       <c r="O120">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P120">
         <v>2.18</v>
       </c>
       <c r="Q120">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="R120">
         <v>2.38</v>
@@ -19914,7 +19914,7 @@
         <v>2.55</v>
       </c>
       <c r="AC120">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="AD120">
         <v>1.63</v>
@@ -20035,7 +20035,7 @@
         <v>4.8</v>
       </c>
       <c r="O121">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="P121">
         <v>1.6</v>
@@ -20089,7 +20089,7 @@
         <v>1.5</v>
       </c>
       <c r="AG121">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20684,13 +20684,13 @@
         </is>
       </c>
       <c r="N125">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="O125">
         <v>3.1</v>
       </c>
       <c r="P125">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q125">
         <v>2.45</v>
@@ -20757,7 +20757,7 @@
         <v>1.3</v>
       </c>
       <c r="AK125">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -21393,7 +21393,7 @@
         <v>1.87</v>
       </c>
       <c r="AG129">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -23138,7 +23138,7 @@
         <v>0</v>
       </c>
       <c r="Q140">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="R140">
         <v>2.38</v>
@@ -23156,7 +23156,7 @@
         <v>1.62</v>
       </c>
       <c r="W140">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X140">
         <v>1.03</v>
@@ -23301,16 +23301,16 @@
         <v>0</v>
       </c>
       <c r="Q141">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R141">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="S141">
         <v>1.17</v>
       </c>
       <c r="T141">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="U141">
         <v>1.86</v>
@@ -23328,7 +23328,7 @@
         <v>1.05</v>
       </c>
       <c r="Z141">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="AA141">
         <v>1.29</v>
@@ -23464,55 +23464,55 @@
         <v>1.58</v>
       </c>
       <c r="Q142">
-        <v>4.07</v>
+        <v>4.06</v>
       </c>
       <c r="R142">
         <v>2.25</v>
       </c>
       <c r="S142">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T142">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="U142">
-        <v>2.51</v>
+        <v>2.44</v>
       </c>
       <c r="V142">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W142">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X142">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y142">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z142">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AA142">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AB142">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AC142">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="AD142">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE142">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF142">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG142">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
@@ -23781,16 +23781,16 @@
         </is>
       </c>
       <c r="N144">
-        <v>2.24</v>
+        <v>2.39</v>
       </c>
       <c r="O144">
         <v>3.35</v>
       </c>
       <c r="P144">
-        <v>2.67</v>
+        <v>2.49</v>
       </c>
       <c r="Q144">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="R144">
         <v>2.25</v>
@@ -23835,10 +23835,10 @@
         <v>1.11</v>
       </c>
       <c r="AF144">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG144">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23854,7 +23854,7 @@
         <v>1.25</v>
       </c>
       <c r="AK144">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -24001,7 +24001,7 @@
         <v>1.75</v>
       </c>
       <c r="AG145">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24113,16 +24113,16 @@
         <v>4.4</v>
       </c>
       <c r="P146">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="Q146">
         <v>1.91</v>
       </c>
       <c r="R146">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S146">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T146">
         <v>3.21</v>
@@ -24134,7 +24134,7 @@
         <v>1.44</v>
       </c>
       <c r="W146">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X146">
         <v>1.03</v>
@@ -24152,10 +24152,10 @@
         <v>2</v>
       </c>
       <c r="AC146">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AD146">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE146">
         <v>1.13</v>
@@ -24164,7 +24164,7 @@
         <v>1.91</v>
       </c>
       <c r="AG146">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24180,7 +24180,7 @@
         <v>1.06</v>
       </c>
       <c r="AK146">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24276,7 +24276,7 @@
         <v>3.9</v>
       </c>
       <c r="P147">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="Q147">
         <v>2.42</v>
@@ -24605,16 +24605,16 @@
         <v>0</v>
       </c>
       <c r="Q149">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R149">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="S149">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="T149">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="U149">
         <v>1.75</v>
@@ -24626,50 +24626,50 @@
         <v>1.29</v>
       </c>
       <c r="X149">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y149">
+        <v>1.03</v>
+      </c>
+      <c r="Z149">
+        <v>8.1</v>
+      </c>
+      <c r="AA149">
+        <v>1.28</v>
+      </c>
+      <c r="AB149">
+        <v>3.5</v>
+      </c>
+      <c r="AC149">
+        <v>1.68</v>
+      </c>
+      <c r="AD149">
+        <v>2.06</v>
+      </c>
+      <c r="AE149">
+        <v>1.44</v>
+      </c>
+      <c r="AF149">
+        <v>1.91</v>
+      </c>
+      <c r="AG149">
+        <v>1.8</v>
+      </c>
+      <c r="AH149" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI149" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ149">
+        <v>1.05</v>
+      </c>
+      <c r="AK149">
         <v>1.02</v>
-      </c>
-      <c r="Z149">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AA149">
-        <v>1.25</v>
-      </c>
-      <c r="AB149">
-        <v>3.75</v>
-      </c>
-      <c r="AC149">
-        <v>1.58</v>
-      </c>
-      <c r="AD149">
-        <v>2.12</v>
-      </c>
-      <c r="AE149">
-        <v>1.51</v>
-      </c>
-      <c r="AF149">
-        <v>2.3</v>
-      </c>
-      <c r="AG149">
-        <v>1.55</v>
-      </c>
-      <c r="AH149" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI149" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ149">
-        <v>6.95</v>
-      </c>
-      <c r="AK149">
-        <v>1</v>
       </c>
       <c r="AL149">
         <v>0</v>
@@ -24780,13 +24780,13 @@
         <v>2.8</v>
       </c>
       <c r="U150">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="V150">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W150">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X150">
         <v>1.03</v>
@@ -24810,7 +24810,7 @@
         <v>1.23</v>
       </c>
       <c r="AE150">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF150">
         <v>1.76</v>
@@ -24928,7 +24928,7 @@
         <v>3.7</v>
       </c>
       <c r="P151">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="Q151">
         <v>3.12</v>
@@ -26887,10 +26887,10 @@
         <v>13.2</v>
       </c>
       <c r="Q163">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="R163">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="S163">
         <v>1.24</v>
@@ -26902,40 +26902,40 @@
         <v>2.17</v>
       </c>
       <c r="V163">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="W163">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X163">
         <v>0</v>
       </c>
       <c r="Y163">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z163">
-        <v>4.35</v>
+        <v>4.5</v>
       </c>
       <c r="AA163">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AB163">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AC163">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="AD163">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AE163">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF163">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AG163">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
@@ -26948,10 +26948,10 @@
         </is>
       </c>
       <c r="AJ163">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AK163">
-        <v>3.52</v>
+        <v>3.06</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -28680,55 +28680,55 @@
         <v>0</v>
       </c>
       <c r="Q174">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R174">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="S174">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T174">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U174">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V174">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W174">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X174">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y174">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z174">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA174">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB174">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC174">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD174">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE174">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF174">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG174">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AH174" t="inlineStr">
         <is>
@@ -28741,10 +28741,10 @@
         </is>
       </c>
       <c r="AJ174">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK174">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL174">
         <v>0</v>
@@ -29160,10 +29160,10 @@
         </is>
       </c>
       <c r="N177">
-        <v>2.52</v>
+        <v>2.61</v>
       </c>
       <c r="O177">
-        <v>2.99</v>
+        <v>3.08</v>
       </c>
       <c r="P177">
         <v>2.36</v>
@@ -31321,10 +31321,10 @@
         <v>1.85</v>
       </c>
       <c r="AB190">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AC190">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AD190">
         <v>1.33</v>
@@ -31349,7 +31349,7 @@
         </is>
       </c>
       <c r="AJ190">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK190">
         <v>1.33</v>
@@ -33887,19 +33887,19 @@
         </is>
       </c>
       <c r="N206">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="O206">
-        <v>4.45</v>
+        <v>4.55</v>
       </c>
       <c r="P206">
         <v>6.75</v>
       </c>
       <c r="Q206">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="R206">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="S206">
         <v>1.29</v>
@@ -33920,10 +33920,10 @@
         <v>1</v>
       </c>
       <c r="Y206">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z206">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="AA206">
         <v>1.51</v>
@@ -33932,13 +33932,13 @@
         <v>2.33</v>
       </c>
       <c r="AC206">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="AD206">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AE206">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF206">
         <v>1.77</v>
@@ -35028,7 +35028,7 @@
         </is>
       </c>
       <c r="N213">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="O213">
         <v>4.1</v>
@@ -35067,16 +35067,16 @@
         <v>5.2</v>
       </c>
       <c r="AA213">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AB213">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="AC213">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AD213">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AE213">
         <v>1.3</v>
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G220">
@@ -36169,64 +36169,64 @@
         </is>
       </c>
       <c r="N220">
-        <v>1.51</v>
+        <v>1.96</v>
       </c>
       <c r="O220">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="P220">
-        <v>5.05</v>
+        <v>3.25</v>
       </c>
       <c r="Q220">
-        <v>1.89</v>
+        <v>2.4</v>
       </c>
       <c r="R220">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="S220">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T220">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="U220">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="V220">
-        <v>1.72</v>
+        <v>1.44</v>
       </c>
       <c r="W220">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="X220">
         <v>1</v>
       </c>
       <c r="Y220">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="Z220">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="AA220">
-        <v>1.43</v>
+        <v>1.74</v>
       </c>
       <c r="AB220">
-        <v>2.75</v>
+        <v>2.08</v>
       </c>
       <c r="AC220">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="AD220">
-        <v>1.79</v>
+        <v>1.36</v>
       </c>
       <c r="AE220">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="AF220">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AG220">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="AH220" t="inlineStr">
         <is>
@@ -36239,10 +36239,10 @@
         </is>
       </c>
       <c r="AJ220">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AK220">
-        <v>2.42</v>
+        <v>1.83</v>
       </c>
       <c r="AL220">
         <v>0</v>
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G221">
@@ -36332,64 +36332,64 @@
         </is>
       </c>
       <c r="N221">
-        <v>1.96</v>
+        <v>2.6</v>
       </c>
       <c r="O221">
         <v>3.4</v>
       </c>
       <c r="P221">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q221">
-        <v>2.4</v>
+        <v>3.15</v>
       </c>
       <c r="R221">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="S221">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T221">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="U221">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="V221">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="W221">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X221">
         <v>1</v>
       </c>
       <c r="Y221">
+        <v>1.14</v>
+      </c>
+      <c r="Z221">
+        <v>4.8</v>
+      </c>
+      <c r="AA221">
+        <v>1.53</v>
+      </c>
+      <c r="AB221">
+        <v>2.3</v>
+      </c>
+      <c r="AC221">
+        <v>2.25</v>
+      </c>
+      <c r="AD221">
+        <v>1.55</v>
+      </c>
+      <c r="AE221">
         <v>1.2</v>
       </c>
-      <c r="Z221">
-        <v>4</v>
-      </c>
-      <c r="AA221">
-        <v>1.74</v>
-      </c>
-      <c r="AB221">
-        <v>2.08</v>
-      </c>
-      <c r="AC221">
-        <v>2.88</v>
-      </c>
-      <c r="AD221">
-        <v>1.36</v>
-      </c>
-      <c r="AE221">
-        <v>1.13</v>
-      </c>
       <c r="AF221">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AG221">
-        <v>2.15</v>
+        <v>2.58</v>
       </c>
       <c r="AH221" t="inlineStr">
         <is>
@@ -36402,10 +36402,10 @@
         </is>
       </c>
       <c r="AJ221">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AK221">
-        <v>1.83</v>
+        <v>1.38</v>
       </c>
       <c r="AL221">
         <v>0</v>
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G222">
@@ -36495,19 +36495,19 @@
         </is>
       </c>
       <c r="N222">
-        <v>2.6</v>
+        <v>1.52</v>
       </c>
       <c r="O222">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="P222">
-        <v>2.3</v>
+        <v>5.5</v>
       </c>
       <c r="Q222">
-        <v>3.15</v>
+        <v>1.89</v>
       </c>
       <c r="R222">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="S222">
         <v>1.22</v>
@@ -36516,43 +36516,43 @@
         <v>3.8</v>
       </c>
       <c r="U222">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="V222">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="W222">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X222">
         <v>1</v>
       </c>
       <c r="Y222">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z222">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AA222">
+        <v>1.43</v>
+      </c>
+      <c r="AB222">
+        <v>2.85</v>
+      </c>
+      <c r="AC222">
+        <v>2.05</v>
+      </c>
+      <c r="AD222">
+        <v>1.79</v>
+      </c>
+      <c r="AE222">
+        <v>1.31</v>
+      </c>
+      <c r="AF222">
         <v>1.53</v>
       </c>
-      <c r="AB222">
-        <v>2.3</v>
-      </c>
-      <c r="AC222">
-        <v>2.25</v>
-      </c>
-      <c r="AD222">
-        <v>1.55</v>
-      </c>
-      <c r="AE222">
-        <v>1.2</v>
-      </c>
-      <c r="AF222">
-        <v>1.43</v>
-      </c>
       <c r="AG222">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="AH222" t="inlineStr">
         <is>
@@ -36565,10 +36565,10 @@
         </is>
       </c>
       <c r="AJ222">
-        <v>1.53</v>
+        <v>1.15</v>
       </c>
       <c r="AK222">
-        <v>1.38</v>
+        <v>2.42</v>
       </c>
       <c r="AL222">
         <v>0</v>
@@ -38297,13 +38297,13 @@
         <v>3.19</v>
       </c>
       <c r="Q233">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="R233">
         <v>2.15</v>
       </c>
       <c r="S233">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T233">
         <v>3.1</v>
@@ -38315,7 +38315,7 @@
         <v>1.47</v>
       </c>
       <c r="W233">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X233">
         <v>1.01</v>
@@ -38330,16 +38330,16 @@
         <v>1.72</v>
       </c>
       <c r="AB233">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="AC233">
         <v>2.66</v>
       </c>
       <c r="AD233">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AE233">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF233">
         <v>1.62</v>
@@ -38481,16 +38481,16 @@
         <v>1.02</v>
       </c>
       <c r="X234">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Y234">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="Z234">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="AA234">
-        <v>2.41</v>
+        <v>2.37</v>
       </c>
       <c r="AB234">
         <v>1.53</v>
@@ -38505,7 +38505,7 @@
         <v>1.04</v>
       </c>
       <c r="AF234">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AG234">
         <v>1.69</v>
@@ -38524,7 +38524,7 @@
         <v>1.32</v>
       </c>
       <c r="AK234">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AL234">
         <v>0</v>
@@ -38644,13 +38644,13 @@
         <v>1.07</v>
       </c>
       <c r="X235">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y235">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="Z235">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
       <c r="AA235">
         <v>1.94</v>
@@ -38665,7 +38665,7 @@
         <v>1.24</v>
       </c>
       <c r="AE235">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF235">
         <v>1.78</v>
@@ -38684,10 +38684,10 @@
         </is>
       </c>
       <c r="AJ235">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK235">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AL235">
         <v>0</v>
@@ -38807,7 +38807,7 @@
         <v>1.07</v>
       </c>
       <c r="X236">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y236">
         <v>1.28</v>
@@ -38819,7 +38819,7 @@
         <v>1.95</v>
       </c>
       <c r="AB236">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC236">
         <v>3.42</v>
@@ -38828,7 +38828,7 @@
         <v>1.23</v>
       </c>
       <c r="AE236">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF236">
         <v>2.1</v>
@@ -40733,13 +40733,13 @@
         </is>
       </c>
       <c r="N248">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="O248">
         <v>3.4</v>
       </c>
       <c r="P248">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="Q248">
         <v>2.3</v>
@@ -40772,10 +40772,10 @@
         <v>3.76</v>
       </c>
       <c r="AA248">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AB248">
-        <v>2.11</v>
+        <v>2.01</v>
       </c>
       <c r="AC248">
         <v>2.66</v>
@@ -40905,10 +40905,10 @@
         <v>3.4</v>
       </c>
       <c r="Q249">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="R249">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S249">
         <v>1.3</v>
@@ -40923,7 +40923,7 @@
         <v>1.5</v>
       </c>
       <c r="W249">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X249">
         <v>1.01</v>
@@ -40953,7 +40953,7 @@
         <v>1.59</v>
       </c>
       <c r="AG249">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="AH249" t="inlineStr">
         <is>
@@ -41059,13 +41059,13 @@
         </is>
       </c>
       <c r="N250">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="O250">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P250">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Q250">
         <v>2.25</v>
@@ -41548,13 +41548,13 @@
         </is>
       </c>
       <c r="N253">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="O253">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P253">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="Q253">
         <v>2.05</v>
@@ -41618,10 +41618,10 @@
         </is>
       </c>
       <c r="AJ253">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK253">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AL253">
         <v>0</v>
@@ -41720,7 +41720,7 @@
         <v>3.09</v>
       </c>
       <c r="Q254">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="R254">
         <v>2.1</v>
@@ -41735,19 +41735,19 @@
         <v>3</v>
       </c>
       <c r="V254">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W254">
         <v>1.07</v>
       </c>
       <c r="X254">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y254">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="Z254">
-        <v>2.88</v>
+        <v>3.01</v>
       </c>
       <c r="AA254">
         <v>2</v>
@@ -41762,7 +41762,7 @@
         <v>1.22</v>
       </c>
       <c r="AE254">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF254">
         <v>1.83</v>
@@ -41781,10 +41781,10 @@
         </is>
       </c>
       <c r="AJ254">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AK254">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AL254">
         <v>0</v>
@@ -41904,7 +41904,7 @@
         <v>1.07</v>
       </c>
       <c r="X255">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y255">
         <v>1.29</v>
@@ -41913,10 +41913,10 @@
         <v>3.04</v>
       </c>
       <c r="AA255">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="AB255">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AC255">
         <v>3.5</v>
@@ -42094,7 +42094,7 @@
         <v>1.79</v>
       </c>
       <c r="AG256">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AH256" t="inlineStr">
         <is>
@@ -42209,7 +42209,7 @@
         <v>2.45</v>
       </c>
       <c r="Q257">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="R257">
         <v>2.04</v>
@@ -42239,10 +42239,10 @@
         <v>3.34</v>
       </c>
       <c r="AA257">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB257">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="AC257">
         <v>3.04</v>
@@ -42273,7 +42273,7 @@
         <v>1.25</v>
       </c>
       <c r="AK257">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL257">
         <v>0</v>
@@ -42369,7 +42369,7 @@
         <v>4.5</v>
       </c>
       <c r="P258">
-        <v>4.6</v>
+        <v>4.85</v>
       </c>
       <c r="Q258">
         <v>2.11</v>
@@ -42411,7 +42411,7 @@
         <v>2.16</v>
       </c>
       <c r="AD258">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AE258">
         <v>1.33</v>
@@ -43359,7 +43359,7 @@
         <v>1.31</v>
       </c>
       <c r="T264">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="U264">
         <v>2.45</v>
@@ -43380,10 +43380,10 @@
         <v>3.68</v>
       </c>
       <c r="AA264">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AB264">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AC264">
         <v>2.88</v>
@@ -43392,7 +43392,7 @@
         <v>1.32</v>
       </c>
       <c r="AE264">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF264">
         <v>1.8</v>
@@ -43414,7 +43414,7 @@
         <v>1.18</v>
       </c>
       <c r="AK264">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AL264">
         <v>0</v>
@@ -43706,7 +43706,7 @@
         <v>3.5</v>
       </c>
       <c r="AA266">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AB266">
         <v>1.91</v>
@@ -43836,7 +43836,7 @@
         <v>3.1</v>
       </c>
       <c r="P267">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="Q267">
         <v>3.56</v>
@@ -43845,10 +43845,10 @@
         <v>1.91</v>
       </c>
       <c r="S267">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="T267">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U267">
         <v>3.46</v>
@@ -43860,7 +43860,7 @@
         <v>1.06</v>
       </c>
       <c r="X267">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y267">
         <v>1.4</v>
@@ -45134,19 +45134,19 @@
         </is>
       </c>
       <c r="N275">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="O275">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="P275">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="Q275">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="R275">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="S275">
         <v>1.35</v>
@@ -45155,7 +45155,7 @@
         <v>2.86</v>
       </c>
       <c r="U275">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="V275">
         <v>1.46</v>
@@ -45185,13 +45185,13 @@
         <v>1.38</v>
       </c>
       <c r="AE275">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF275">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG275">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH275" t="inlineStr">
         <is>
@@ -45204,7 +45204,7 @@
         </is>
       </c>
       <c r="AJ275">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AK275">
         <v>1.15</v>
@@ -45306,55 +45306,55 @@
         <v>0</v>
       </c>
       <c r="Q276">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="R276">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S276">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T276">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U276">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V276">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W276">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X276">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y276">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z276">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA276">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB276">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC276">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD276">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE276">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF276">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG276">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH276" t="inlineStr">
         <is>
@@ -45367,10 +45367,10 @@
         </is>
       </c>
       <c r="AJ276">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK276">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL276">
         <v>0</v>
@@ -48723,7 +48723,7 @@
         <v>2.3</v>
       </c>
       <c r="O297">
-        <v>3.43</v>
+        <v>3.32</v>
       </c>
       <c r="P297">
         <v>3.24</v>
@@ -48741,7 +48741,7 @@
         <v>2.64</v>
       </c>
       <c r="U297">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="V297">
         <v>1.42</v>
@@ -49248,10 +49248,10 @@
         <v>0</v>
       </c>
       <c r="AA300">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB300">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC300">
         <v>0</v>
@@ -51622,12 +51622,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G315">
@@ -51654,64 +51654,64 @@
         </is>
       </c>
       <c r="N315">
-        <v>1.53</v>
+        <v>2.16</v>
       </c>
       <c r="O315">
-        <v>4.79</v>
+        <v>3.7</v>
       </c>
       <c r="P315">
-        <v>5.1</v>
+        <v>2.75</v>
       </c>
       <c r="Q315">
-        <v>1.8</v>
+        <v>2.57</v>
       </c>
       <c r="R315">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S315">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T315">
         <v>4</v>
       </c>
       <c r="U315">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="V315">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="W315">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X315">
         <v>0</v>
       </c>
       <c r="Y315">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z315">
         <v>5.3</v>
       </c>
       <c r="AA315">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="AB315">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="AC315">
-        <v>2.23</v>
+        <v>2.06</v>
       </c>
       <c r="AD315">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AE315">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF315">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AG315">
-        <v>2.25</v>
+        <v>2.72</v>
       </c>
       <c r="AH315" t="inlineStr">
         <is>
@@ -51724,10 +51724,10 @@
         </is>
       </c>
       <c r="AJ315">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK315">
-        <v>2.6</v>
+        <v>1.67</v>
       </c>
       <c r="AL315">
         <v>0</v>
@@ -51785,12 +51785,12 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G316">
@@ -51817,64 +51817,64 @@
         </is>
       </c>
       <c r="N316">
-        <v>2.16</v>
+        <v>1.53</v>
       </c>
       <c r="O316">
-        <v>3.7</v>
+        <v>4.79</v>
       </c>
       <c r="P316">
-        <v>2.75</v>
+        <v>5.1</v>
       </c>
       <c r="Q316">
-        <v>2.57</v>
+        <v>1.8</v>
       </c>
       <c r="R316">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S316">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T316">
         <v>4</v>
       </c>
       <c r="U316">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="V316">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="W316">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X316">
         <v>0</v>
       </c>
       <c r="Y316">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z316">
         <v>5.3</v>
       </c>
       <c r="AA316">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="AB316">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="AC316">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="AD316">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AE316">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF316">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AG316">
-        <v>2.72</v>
+        <v>2.25</v>
       </c>
       <c r="AH316" t="inlineStr">
         <is>
@@ -51887,10 +51887,10 @@
         </is>
       </c>
       <c r="AJ316">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK316">
-        <v>1.67</v>
+        <v>2.6</v>
       </c>
       <c r="AL316">
         <v>0</v>

--- a/jogos_2026-11-01.xlsx
+++ b/jogos_2026-11-01.xlsx
@@ -638,16 +638,16 @@
         <v>1.47</v>
       </c>
       <c r="O2">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="P2">
         <v>6.5</v>
       </c>
       <c r="Q2">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="R2">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="S2">
         <v>1.25</v>
@@ -656,7 +656,7 @@
         <v>3.6</v>
       </c>
       <c r="U2">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="V2">
         <v>1.6</v>
@@ -689,7 +689,7 @@
         <v>1.19</v>
       </c>
       <c r="AF2">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG2">
         <v>2.2</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AK2">
         <v>2.75</v>
@@ -828,7 +828,7 @@
         <v>1.15</v>
       </c>
       <c r="X3">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
         <v>1.13</v>
@@ -837,7 +837,7 @@
         <v>4.68</v>
       </c>
       <c r="AA3">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AB3">
         <v>2.35</v>
@@ -964,16 +964,16 @@
         <v>2.5</v>
       </c>
       <c r="O4">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="P4">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="Q4">
         <v>3.25</v>
       </c>
       <c r="R4">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="S4">
         <v>1.44</v>
@@ -991,7 +991,7 @@
         <v>1.05</v>
       </c>
       <c r="X4">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y4">
         <v>1.34</v>
@@ -1127,16 +1127,16 @@
         <v>2.11</v>
       </c>
       <c r="O5">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P5">
         <v>3.2</v>
       </c>
       <c r="Q5">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="R5">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S5">
         <v>1.38</v>
@@ -1151,7 +1151,7 @@
         <v>1.43</v>
       </c>
       <c r="W5">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X5">
         <v>1</v>
@@ -1163,13 +1163,13 @@
         <v>3.6</v>
       </c>
       <c r="AA5">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AB5">
-        <v>1.92</v>
+        <v>2.01</v>
       </c>
       <c r="AC5">
-        <v>3.03</v>
+        <v>2.88</v>
       </c>
       <c r="AD5">
         <v>1.38</v>
@@ -1181,7 +1181,7 @@
         <v>1.66</v>
       </c>
       <c r="AG5">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>3.25</v>
       </c>
       <c r="P6">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="Q6">
         <v>3.5</v>
@@ -1320,28 +1320,28 @@
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="Z6">
         <v>3.42</v>
       </c>
       <c r="AA6">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AB6">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AC6">
         <v>3.11</v>
       </c>
       <c r="AD6">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE6">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF6">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AG6">
         <v>2.1</v>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK6">
         <v>1.36</v>
@@ -1456,10 +1456,10 @@
         <v>5.1</v>
       </c>
       <c r="P7">
-        <v>7</v>
+        <v>7.25</v>
       </c>
       <c r="Q7">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="R7">
         <v>2.6</v>
@@ -1471,7 +1471,7 @@
         <v>3.88</v>
       </c>
       <c r="U7">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="V7">
         <v>1.7</v>
@@ -1483,16 +1483,16 @@
         <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Z7">
         <v>5.3</v>
       </c>
       <c r="AA7">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AB7">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="AC7">
         <v>2.12</v>
@@ -1523,7 +1523,7 @@
         <v>1.09</v>
       </c>
       <c r="AK7">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1631,7 +1631,7 @@
         <v>1.4</v>
       </c>
       <c r="T8">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="U8">
         <v>2.9</v>
@@ -1640,7 +1640,7 @@
         <v>1.36</v>
       </c>
       <c r="W8">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X8">
         <v>1</v>
@@ -1652,7 +1652,7 @@
         <v>2.97</v>
       </c>
       <c r="AA8">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB8">
         <v>1.67</v>
@@ -1661,7 +1661,7 @@
         <v>3.8</v>
       </c>
       <c r="AD8">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE8">
         <v>1.05</v>
@@ -1827,7 +1827,7 @@
         <v>1.24</v>
       </c>
       <c r="AE9">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF9">
         <v>1.83</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="O10">
-        <v>3.86</v>
+        <v>3.5</v>
       </c>
       <c r="P10">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Q10">
         <v>2.2</v>
@@ -1957,10 +1957,10 @@
         <v>1.34</v>
       </c>
       <c r="T10">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="U10">
-        <v>2.73</v>
+        <v>2.6</v>
       </c>
       <c r="V10">
         <v>1.44</v>
@@ -1969,7 +1969,7 @@
         <v>1.1</v>
       </c>
       <c r="X10">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
         <v>1.21</v>
@@ -1984,13 +1984,13 @@
         <v>1.9</v>
       </c>
       <c r="AC10">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AD10">
         <v>1.37</v>
       </c>
       <c r="AE10">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF10">
         <v>1.75</v>
@@ -2123,7 +2123,7 @@
         <v>3</v>
       </c>
       <c r="U11">
-        <v>2.74</v>
+        <v>2.56</v>
       </c>
       <c r="V11">
         <v>1.44</v>
@@ -2147,19 +2147,19 @@
         <v>1.88</v>
       </c>
       <c r="AC11">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="AD11">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AE11">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF11">
         <v>1.75</v>
       </c>
       <c r="AG11">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>1.75</v>
       </c>
       <c r="O12">
-        <v>3.47</v>
+        <v>3.4</v>
       </c>
       <c r="P12">
         <v>4</v>
@@ -2289,7 +2289,7 @@
         <v>2.62</v>
       </c>
       <c r="V12">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W12">
         <v>1.1</v>
@@ -2322,7 +2322,7 @@
         <v>1.75</v>
       </c>
       <c r="AG12">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>3</v>
       </c>
       <c r="U13">
-        <v>2.51</v>
+        <v>2.76</v>
       </c>
       <c r="V13">
         <v>1.42</v>
@@ -2482,7 +2482,7 @@
         <v>1.08</v>
       </c>
       <c r="AF13">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG13">
         <v>2.1</v>
@@ -2624,7 +2624,7 @@
         <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z14">
         <v>3.4</v>
@@ -3460,10 +3460,10 @@
         <v>1.12</v>
       </c>
       <c r="AF19">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG19">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3904,10 +3904,10 @@
         <v>5</v>
       </c>
       <c r="Q22">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="R22">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="S22">
         <v>1.25</v>
@@ -3934,16 +3934,16 @@
         <v>4.3</v>
       </c>
       <c r="AA22">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AB22">
         <v>2.35</v>
       </c>
       <c r="AC22">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AD22">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="AE22">
         <v>1.17</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="O23">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P23">
-        <v>3.54</v>
+        <v>3.7</v>
       </c>
       <c r="Q23">
         <v>2.4</v>
@@ -4073,10 +4073,10 @@
         <v>2.1</v>
       </c>
       <c r="S23">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="T23">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="U23">
         <v>3</v>
@@ -4085,22 +4085,22 @@
         <v>1.35</v>
       </c>
       <c r="W23">
+        <v>1.07</v>
+      </c>
+      <c r="X23">
         <v>1.04</v>
       </c>
-      <c r="X23">
-        <v>1.05</v>
-      </c>
       <c r="Y23">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="Z23">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="AA23">
         <v>2.06</v>
       </c>
       <c r="AB23">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="AC23">
         <v>3.68</v>
@@ -4109,10 +4109,10 @@
         <v>1.2</v>
       </c>
       <c r="AE23">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AF23">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AG23">
         <v>1.8</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK23">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4233,7 +4233,7 @@
         <v>2.01</v>
       </c>
       <c r="R24">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="S24">
         <v>1.29</v>
@@ -4254,25 +4254,25 @@
         <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z24">
-        <v>3.88</v>
+        <v>4.33</v>
       </c>
       <c r="AA24">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AB24">
         <v>2.1</v>
       </c>
       <c r="AC24">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AD24">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AE24">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF24">
         <v>1.75</v>
@@ -4882,10 +4882,10 @@
         <v>0</v>
       </c>
       <c r="Q28">
-        <v>5.84</v>
+        <v>5</v>
       </c>
       <c r="R28">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="S28">
         <v>1.33</v>
@@ -4903,7 +4903,7 @@
         <v>1.08</v>
       </c>
       <c r="X28">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y28">
         <v>1.2</v>
@@ -4918,19 +4918,19 @@
         <v>2</v>
       </c>
       <c r="AC28">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="AD28">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE28">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF28">
         <v>1.78</v>
       </c>
       <c r="AG28">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK28">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5694,7 +5694,7 @@
         <v>3.1</v>
       </c>
       <c r="P33">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="Q33">
         <v>2.99</v>
@@ -5721,10 +5721,10 @@
         <v>1.04</v>
       </c>
       <c r="Y33">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z33">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AA33">
         <v>2.15</v>
@@ -6512,7 +6512,7 @@
         <v>5.25</v>
       </c>
       <c r="Q38">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R38">
         <v>2.36</v>
@@ -6672,7 +6672,7 @@
         <v>8.5</v>
       </c>
       <c r="P39">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q39">
         <v>1.43</v>
@@ -6874,13 +6874,13 @@
         <v>2.2</v>
       </c>
       <c r="AC40">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="AD40">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE40">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AF40">
         <v>1.62</v>
@@ -6995,13 +6995,13 @@
         <v>1.47</v>
       </c>
       <c r="O41">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="P41">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Q41">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="R41">
         <v>2.6</v>
@@ -7013,10 +7013,10 @@
         <v>3.75</v>
       </c>
       <c r="U41">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="V41">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="W41">
         <v>1.17</v>
@@ -7034,16 +7034,16 @@
         <v>1.45</v>
       </c>
       <c r="AB41">
-        <v>2.41</v>
+        <v>2.63</v>
       </c>
       <c r="AC41">
         <v>2.2</v>
       </c>
       <c r="AD41">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AE41">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AF41">
         <v>1.58</v>
@@ -7065,7 +7065,7 @@
         <v>1.14</v>
       </c>
       <c r="AK41">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="O42">
         <v>10</v>
       </c>
       <c r="P42">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q42">
         <v>14.5</v>
@@ -7333,22 +7333,22 @@
         <v>2.3</v>
       </c>
       <c r="S43">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T43">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="U43">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="V43">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W43">
         <v>1.11</v>
       </c>
       <c r="X43">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y43">
         <v>1.18</v>
@@ -7360,7 +7360,7 @@
         <v>1.72</v>
       </c>
       <c r="AB43">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="AC43">
         <v>2.7</v>
@@ -7391,7 +7391,7 @@
         <v>1.22</v>
       </c>
       <c r="AK43">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7493,13 +7493,13 @@
         <v>2.3</v>
       </c>
       <c r="R44">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="S44">
         <v>1.36</v>
       </c>
       <c r="T44">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="U44">
         <v>2.8</v>
@@ -7508,10 +7508,10 @@
         <v>1.4</v>
       </c>
       <c r="W44">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X44">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y44">
         <v>1.28</v>
@@ -7532,7 +7532,7 @@
         <v>1.25</v>
       </c>
       <c r="AE44">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF44">
         <v>1.83</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AK44">
         <v>1.91</v>
@@ -7659,16 +7659,16 @@
         <v>2.25</v>
       </c>
       <c r="S45">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="T45">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="U45">
-        <v>2.48</v>
+        <v>2.66</v>
       </c>
       <c r="V45">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W45">
         <v>1.1</v>
@@ -7683,10 +7683,10 @@
         <v>3.58</v>
       </c>
       <c r="AA45">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AB45">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AC45">
         <v>2.92</v>
@@ -7695,7 +7695,7 @@
         <v>1.31</v>
       </c>
       <c r="AE45">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF45">
         <v>1.7</v>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK45">
         <v>1.75</v>
@@ -7816,16 +7816,16 @@
         <v>3.4</v>
       </c>
       <c r="Q46">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="R46">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="S46">
         <v>1.35</v>
       </c>
       <c r="T46">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="U46">
         <v>2.62</v>
@@ -7840,10 +7840,10 @@
         <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z46">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AA46">
         <v>1.9</v>
@@ -7852,10 +7852,10 @@
         <v>1.88</v>
       </c>
       <c r="AC46">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="AD46">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE46">
         <v>1.1</v>
@@ -7864,7 +7864,7 @@
         <v>1.73</v>
       </c>
       <c r="AG46">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         <v>1.3</v>
       </c>
       <c r="AK46">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8172,10 +8172,10 @@
         <v>0</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC48">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>La Nucía</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mallorca II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.6</v>
+        <v>2.05</v>
       </c>
       <c r="O50">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="P50">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="Q50">
+        <v>2.7</v>
+      </c>
+      <c r="R50">
+        <v>1.97</v>
+      </c>
+      <c r="S50">
+        <v>1.38</v>
+      </c>
+      <c r="T50">
+        <v>2.65</v>
+      </c>
+      <c r="U50">
+        <v>2.9</v>
+      </c>
+      <c r="V50">
+        <v>1.32</v>
+      </c>
+      <c r="W50">
+        <v>1.04</v>
+      </c>
+      <c r="X50">
+        <v>1.03</v>
+      </c>
+      <c r="Y50">
+        <v>1.32</v>
+      </c>
+      <c r="Z50">
+        <v>2.88</v>
+      </c>
+      <c r="AA50">
         <v>2.1</v>
       </c>
-      <c r="R50">
-        <v>2.25</v>
-      </c>
-      <c r="S50">
-        <v>1.33</v>
-      </c>
-      <c r="T50">
-        <v>3</v>
-      </c>
-      <c r="U50">
-        <v>2.62</v>
-      </c>
-      <c r="V50">
-        <v>1.4</v>
-      </c>
-      <c r="W50">
-        <v>1.08</v>
-      </c>
-      <c r="X50">
-        <v>1.01</v>
-      </c>
-      <c r="Y50">
-        <v>1.23</v>
-      </c>
-      <c r="Z50">
-        <v>3.42</v>
-      </c>
-      <c r="AA50">
+      <c r="AB50">
+        <v>1.63</v>
+      </c>
+      <c r="AC50">
+        <v>3.84</v>
+      </c>
+      <c r="AD50">
+        <v>1.18</v>
+      </c>
+      <c r="AE50">
+        <v>1.04</v>
+      </c>
+      <c r="AF50">
         <v>1.85</v>
       </c>
-      <c r="AB50">
-        <v>1.88</v>
-      </c>
-      <c r="AC50">
-        <v>3.04</v>
-      </c>
-      <c r="AD50">
-        <v>1.29</v>
-      </c>
-      <c r="AE50">
-        <v>1.08</v>
-      </c>
-      <c r="AF50">
-        <v>1.83</v>
-      </c>
       <c r="AG50">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>1.25</v>
       </c>
       <c r="AK50">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>La Nucía</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Mallorca II</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="O51">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="P51">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="Q51">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="R51">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="S51">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T51">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="U51">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="V51">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="W51">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X51">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="Z51">
-        <v>2.88</v>
+        <v>3.42</v>
       </c>
       <c r="AA51">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AB51">
-        <v>1.63</v>
+        <v>1.88</v>
       </c>
       <c r="AC51">
-        <v>3.84</v>
+        <v>3.04</v>
       </c>
       <c r="AD51">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AE51">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF51">
+        <v>1.83</v>
+      </c>
+      <c r="AG51">
         <v>1.85</v>
-      </c>
-      <c r="AG51">
-        <v>1.84</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>1.25</v>
       </c>
       <c r="AK51">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -9292,7 +9292,7 @@
         <v>1.3</v>
       </c>
       <c r="T55">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U55">
         <v>2.6</v>
@@ -9304,13 +9304,13 @@
         <v>1.07</v>
       </c>
       <c r="X55">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y55">
         <v>1.25</v>
       </c>
       <c r="Z55">
-        <v>3.28</v>
+        <v>3.71</v>
       </c>
       <c r="AA55">
         <v>1.85</v>
@@ -9319,19 +9319,19 @@
         <v>1.95</v>
       </c>
       <c r="AC55">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="AD55">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AE55">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF55">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AG55">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         <v>1.35</v>
       </c>
       <c r="T56">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="U56">
         <v>2.7</v>
@@ -9467,7 +9467,7 @@
         <v>1.08</v>
       </c>
       <c r="X56">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y56">
         <v>1.25</v>
@@ -9476,7 +9476,7 @@
         <v>3.28</v>
       </c>
       <c r="AA56">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AB56">
         <v>1.95</v>
@@ -9488,7 +9488,7 @@
         <v>1.3</v>
       </c>
       <c r="AE56">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF56">
         <v>1.7</v>
@@ -9600,49 +9600,49 @@
         </is>
       </c>
       <c r="N57">
+        <v>2.9</v>
+      </c>
+      <c r="O57">
         <v>3.1</v>
       </c>
-      <c r="O57">
-        <v>3.2</v>
-      </c>
       <c r="P57">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="Q57">
-        <v>3.94</v>
+        <v>3.5</v>
       </c>
       <c r="R57">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="S57">
         <v>1.4</v>
       </c>
       <c r="T57">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="U57">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="V57">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W57">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X57">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z57">
-        <v>2.83</v>
+        <v>2.94</v>
       </c>
       <c r="AA57">
         <v>2.15</v>
       </c>
       <c r="AB57">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AC57">
         <v>3.75</v>
@@ -9651,7 +9651,7 @@
         <v>1.19</v>
       </c>
       <c r="AE57">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF57">
         <v>1.83</v>
@@ -10578,16 +10578,16 @@
         </is>
       </c>
       <c r="N63">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="O63">
         <v>3.3</v>
       </c>
       <c r="P63">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="Q63">
-        <v>5.01</v>
+        <v>4.8</v>
       </c>
       <c r="R63">
         <v>2.01</v>
@@ -11100,7 +11100,7 @@
         <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z66">
         <v>4.47</v>
@@ -11257,10 +11257,10 @@
         <v>1.47</v>
       </c>
       <c r="W67">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X67">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y67">
         <v>1.22</v>
@@ -11272,7 +11272,7 @@
         <v>1.72</v>
       </c>
       <c r="AB67">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC67">
         <v>2.8</v>
@@ -11402,55 +11402,55 @@
         <v>0</v>
       </c>
       <c r="Q68">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="R68">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S68">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T68">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U68">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="V68">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W68">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X68">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y68">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z68">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA68">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB68">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC68">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AD68">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE68">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF68">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG68">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK68">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="O69">
-        <v>3.48</v>
+        <v>3.25</v>
       </c>
       <c r="P69">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q69">
         <v>4.2</v>
@@ -11589,16 +11589,16 @@
         <v>1.04</v>
       </c>
       <c r="Y69">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="Z69">
         <v>2.83</v>
       </c>
       <c r="AA69">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AB69">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC69">
         <v>3.92</v>
@@ -11607,7 +11607,7 @@
         <v>1.18</v>
       </c>
       <c r="AE69">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF69">
         <v>2</v>
@@ -13355,7 +13355,7 @@
         <v>3.25</v>
       </c>
       <c r="P80">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="Q80">
         <v>2.15</v>
@@ -13379,13 +13379,13 @@
         <v>1.08</v>
       </c>
       <c r="X80">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y80">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z80">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA80">
         <v>1.92</v>
@@ -13394,10 +13394,10 @@
         <v>1.76</v>
       </c>
       <c r="AC80">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AD80">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE80">
         <v>1.05</v>
@@ -13406,7 +13406,7 @@
         <v>1.91</v>
       </c>
       <c r="AG80">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13729,10 +13729,10 @@
         <v>1.18</v>
       </c>
       <c r="AF82">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG82">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="O83">
         <v>3.45</v>
@@ -13871,7 +13871,7 @@
         <v>1.02</v>
       </c>
       <c r="Y83">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Z83">
         <v>4.75</v>
@@ -14010,7 +14010,7 @@
         <v>2.9</v>
       </c>
       <c r="Q84">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="R84">
         <v>2.38</v>
@@ -14022,7 +14022,7 @@
         <v>3.56</v>
       </c>
       <c r="U84">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="V84">
         <v>1.62</v>
@@ -14031,19 +14031,19 @@
         <v>1.17</v>
       </c>
       <c r="X84">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y84">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z84">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="AA84">
         <v>1.5</v>
       </c>
       <c r="AB84">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="AC84">
         <v>2.28</v>
@@ -14055,7 +14055,7 @@
         <v>1.22</v>
       </c>
       <c r="AF84">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG84">
         <v>2.5</v>
@@ -14074,7 +14074,7 @@
         <v>1.25</v>
       </c>
       <c r="AK84">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14173,7 +14173,7 @@
         <v>2.55</v>
       </c>
       <c r="Q85">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="R85">
         <v>2.32</v>
@@ -14194,7 +14194,7 @@
         <v>1.17</v>
       </c>
       <c r="X85">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y85">
         <v>1.11</v>
@@ -14212,16 +14212,16 @@
         <v>2.33</v>
       </c>
       <c r="AD85">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AE85">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF85">
         <v>1.44</v>
       </c>
       <c r="AG85">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>1.44</v>
       </c>
       <c r="AK85">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14327,40 +14327,40 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O86">
-        <v>3.63</v>
+        <v>3.65</v>
       </c>
       <c r="P86">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Q86">
-        <v>2.43</v>
+        <v>2.67</v>
       </c>
       <c r="R86">
         <v>2.22</v>
       </c>
       <c r="S86">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T86">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U86">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="V86">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="W86">
         <v>1.12</v>
       </c>
       <c r="X86">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z86">
         <v>4.5</v>
@@ -14372,10 +14372,10 @@
         <v>2.25</v>
       </c>
       <c r="AC86">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="AD86">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AE86">
         <v>1.2</v>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK86">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="O87">
         <v>5.75</v>
       </c>
       <c r="P87">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="Q87">
         <v>1.53</v>
@@ -14523,10 +14523,10 @@
         <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Z87">
-        <v>6.55</v>
+        <v>6.5</v>
       </c>
       <c r="AA87">
         <v>1.38</v>
@@ -15012,7 +15012,7 @@
         <v>1</v>
       </c>
       <c r="Y90">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Z90">
         <v>6.5</v>
@@ -15157,10 +15157,10 @@
         <v>2.44</v>
       </c>
       <c r="S91">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T91">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U91">
         <v>2.3</v>
@@ -15175,16 +15175,16 @@
         <v>1</v>
       </c>
       <c r="Y91">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z91">
-        <v>4.19</v>
+        <v>4.45</v>
       </c>
       <c r="AA91">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AB91">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AC91">
         <v>2.38</v>
@@ -15196,10 +15196,10 @@
         <v>1.16</v>
       </c>
       <c r="AF91">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG91">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK91">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15468,7 +15468,7 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="O93">
         <v>5.75</v>
@@ -15646,7 +15646,7 @@
         <v>2.15</v>
       </c>
       <c r="S94">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T94">
         <v>2.72</v>
@@ -15664,10 +15664,10 @@
         <v>1.01</v>
       </c>
       <c r="Y94">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z94">
-        <v>2.5</v>
+        <v>3.14</v>
       </c>
       <c r="AA94">
         <v>1.96</v>
@@ -15676,10 +15676,10 @@
         <v>1.84</v>
       </c>
       <c r="AC94">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="AD94">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AE94">
         <v>1.07</v>
@@ -15688,7 +15688,7 @@
         <v>1.76</v>
       </c>
       <c r="AG94">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
         <v>2.12</v>
       </c>
       <c r="S95">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T95">
         <v>2.57</v>
@@ -15830,13 +15830,13 @@
         <v>1.4</v>
       </c>
       <c r="Z95">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="AA95">
-        <v>2.27</v>
+        <v>2.16</v>
       </c>
       <c r="AB95">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AC95">
         <v>4.14</v>
@@ -16002,7 +16002,7 @@
         <v>1.74</v>
       </c>
       <c r="AC96">
-        <v>3.76</v>
+        <v>3.58</v>
       </c>
       <c r="AD96">
         <v>1.25</v>
@@ -16030,7 +16030,7 @@
         <v>1.28</v>
       </c>
       <c r="AK96">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16120,10 +16120,10 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O97">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P97">
         <v>2.65</v>
@@ -16135,10 +16135,10 @@
         <v>2.25</v>
       </c>
       <c r="S97">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="T97">
-        <v>3.02</v>
+        <v>2.73</v>
       </c>
       <c r="U97">
         <v>2.7</v>
@@ -16165,7 +16165,7 @@
         <v>1.84</v>
       </c>
       <c r="AC97">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="AD97">
         <v>1.3</v>
@@ -16174,7 +16174,7 @@
         <v>1.07</v>
       </c>
       <c r="AF97">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG97">
         <v>2.05</v>
@@ -16292,10 +16292,10 @@
         <v>2.42</v>
       </c>
       <c r="Q98">
-        <v>4.1</v>
+        <v>4.12</v>
       </c>
       <c r="R98">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="S98">
         <v>1.53</v>
@@ -16307,7 +16307,7 @@
         <v>3.6</v>
       </c>
       <c r="V98">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="W98">
         <v>1.02</v>
@@ -16337,10 +16337,10 @@
         <v>1.02</v>
       </c>
       <c r="AF98">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AG98">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16485,16 +16485,16 @@
         <v>4.78</v>
       </c>
       <c r="AA99">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AB99">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AC99">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="AD99">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AE99">
         <v>1.18</v>
@@ -16612,10 +16612,10 @@
         <v>1.28</v>
       </c>
       <c r="O100">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="P100">
-        <v>8.5</v>
+        <v>8.75</v>
       </c>
       <c r="Q100">
         <v>1.72</v>
@@ -16784,16 +16784,16 @@
         <v>1.58</v>
       </c>
       <c r="R101">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="S101">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="T101">
         <v>4.7</v>
       </c>
       <c r="U101">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V101">
         <v>1.91</v>
@@ -16808,7 +16808,7 @@
         <v>1.04</v>
       </c>
       <c r="Z101">
-        <v>6.7</v>
+        <v>6.55</v>
       </c>
       <c r="AA101">
         <v>1.22</v>
@@ -16826,7 +16826,7 @@
         <v>1.3</v>
       </c>
       <c r="AF101">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AG101">
         <v>1.98</v>
@@ -17143,13 +17143,13 @@
         <v>2.55</v>
       </c>
       <c r="AC103">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AD103">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AE103">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AF103">
         <v>1.43</v>
@@ -17270,10 +17270,10 @@
         <v>3.2</v>
       </c>
       <c r="Q104">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="R104">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="S104">
         <v>1.33</v>
@@ -17306,13 +17306,13 @@
         <v>1.87</v>
       </c>
       <c r="AC104">
-        <v>3.05</v>
+        <v>3.22</v>
       </c>
       <c r="AD104">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AE104">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF104">
         <v>1.7</v>
@@ -17469,13 +17469,13 @@
         <v>1.95</v>
       </c>
       <c r="AC105">
-        <v>3.2</v>
+        <v>3.11</v>
       </c>
       <c r="AD105">
         <v>1.3</v>
       </c>
       <c r="AE105">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF105">
         <v>1.73</v>
@@ -17756,7 +17756,7 @@
         <v>3.75</v>
       </c>
       <c r="P107">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="Q107">
         <v>2.3</v>
@@ -17789,16 +17789,16 @@
         <v>4.4</v>
       </c>
       <c r="AA107">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AB107">
         <v>2.21</v>
       </c>
       <c r="AC107">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="AD107">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AE107">
         <v>1.21</v>
@@ -17934,10 +17934,10 @@
         <v>3.4</v>
       </c>
       <c r="U108">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V108">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W108">
         <v>1.15</v>
@@ -17946,10 +17946,10 @@
         <v>1.02</v>
       </c>
       <c r="Y108">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="Z108">
-        <v>4.65</v>
+        <v>4.8</v>
       </c>
       <c r="AA108">
         <v>1.57</v>
@@ -17967,10 +17967,10 @@
         <v>1.21</v>
       </c>
       <c r="AF108">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG108">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -18782,10 +18782,10 @@
         <v>1.02</v>
       </c>
       <c r="AF113">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AG113">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>3.83</v>
+        <v>3.95</v>
       </c>
       <c r="O118">
-        <v>3.95</v>
+        <v>3.93</v>
       </c>
       <c r="P118">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Q118">
         <v>3.85</v>
@@ -19561,13 +19561,13 @@
         <v>1.22</v>
       </c>
       <c r="T118">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="U118">
         <v>2.14</v>
       </c>
       <c r="V118">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W118">
         <v>1.14</v>
@@ -19706,7 +19706,7 @@
         </is>
       </c>
       <c r="N119">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="O119">
         <v>7.5</v>
@@ -19757,7 +19757,7 @@
         <v>2.13</v>
       </c>
       <c r="AE119">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AF119">
         <v>1.65</v>
@@ -20195,13 +20195,13 @@
         </is>
       </c>
       <c r="N122">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="O122">
         <v>4.1</v>
       </c>
       <c r="P122">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q122">
         <v>2.08</v>
@@ -20216,37 +20216,37 @@
         <v>5</v>
       </c>
       <c r="U122">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="V122">
         <v>1.95</v>
       </c>
       <c r="W122">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X122">
         <v>1.01</v>
       </c>
       <c r="Y122">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Z122">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="AA122">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AB122">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AC122">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="AD122">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="AE122">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AF122">
         <v>1.25</v>
@@ -20268,7 +20268,7 @@
         <v>1.25</v>
       </c>
       <c r="AK122">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20364,10 +20364,10 @@
         <v>3.75</v>
       </c>
       <c r="P123">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="Q123">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R123">
         <v>2.7</v>
@@ -20409,10 +20409,10 @@
         <v>1.83</v>
       </c>
       <c r="AE123">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AF123">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AG123">
         <v>2.9</v>
@@ -20868,13 +20868,13 @@
         <v>2.8</v>
       </c>
       <c r="U126">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="V126">
         <v>1.38</v>
       </c>
       <c r="W126">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X126">
         <v>1</v>
@@ -21031,7 +21031,7 @@
         <v>2.82</v>
       </c>
       <c r="U127">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="V127">
         <v>1.4</v>
@@ -21040,25 +21040,25 @@
         <v>1.08</v>
       </c>
       <c r="X127">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y127">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z127">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA127">
         <v>1.84</v>
       </c>
       <c r="AB127">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AC127">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="AD127">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AE127">
         <v>1.08</v>
@@ -21227,7 +21227,7 @@
         <v>1.06</v>
       </c>
       <c r="AF128">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AG128">
         <v>2</v>
@@ -21508,7 +21508,7 @@
         <v>3.5</v>
       </c>
       <c r="Q130">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="R130">
         <v>1.98</v>
@@ -21825,7 +21825,7 @@
         </is>
       </c>
       <c r="N132">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="O132">
         <v>3.2</v>
@@ -22018,7 +22018,7 @@
         <v>1.14</v>
       </c>
       <c r="X133">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y133">
         <v>1.13</v>
@@ -22033,10 +22033,10 @@
         <v>2.38</v>
       </c>
       <c r="AC133">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AD133">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AE133">
         <v>1.19</v>
@@ -22163,7 +22163,7 @@
         <v>3.21</v>
       </c>
       <c r="R134">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="S134">
         <v>1.4</v>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AK134">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22332,7 +22332,7 @@
         <v>1.37</v>
       </c>
       <c r="T135">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="U135">
         <v>2.77</v>
@@ -22341,34 +22341,34 @@
         <v>1.36</v>
       </c>
       <c r="W135">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X135">
         <v>1.01</v>
       </c>
       <c r="Y135">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z135">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="AA135">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="AB135">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AC135">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="AD135">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AE135">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF135">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AG135">
         <v>1.87</v>
@@ -22498,7 +22498,7 @@
         <v>3.4</v>
       </c>
       <c r="U136">
-        <v>2.23</v>
+        <v>2.44</v>
       </c>
       <c r="V136">
         <v>1.53</v>
@@ -22534,7 +22534,7 @@
         <v>1.55</v>
       </c>
       <c r="AG136">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22966,13 +22966,13 @@
         </is>
       </c>
       <c r="N139">
-        <v>4.65</v>
+        <v>4.8</v>
       </c>
       <c r="O139">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="P139">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="Q139">
         <v>5.83</v>
@@ -22990,7 +22990,7 @@
         <v>3.07</v>
       </c>
       <c r="V139">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W139">
         <v>1.05</v>
@@ -23005,22 +23005,22 @@
         <v>3.13</v>
       </c>
       <c r="AA139">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AB139">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AC139">
         <v>3.63</v>
       </c>
       <c r="AD139">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AE139">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF139">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AG139">
         <v>1.69</v>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK139">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23627,10 +23627,10 @@
         <v>4.69</v>
       </c>
       <c r="Q143">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="R143">
-        <v>2.55</v>
+        <v>2.36</v>
       </c>
       <c r="S143">
         <v>1.25</v>
@@ -23639,25 +23639,25 @@
         <v>3.32</v>
       </c>
       <c r="U143">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="V143">
         <v>1.55</v>
       </c>
       <c r="W143">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X143">
         <v>1.03</v>
       </c>
       <c r="Y143">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z143">
         <v>5</v>
       </c>
       <c r="AA143">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB143">
         <v>2.35</v>
@@ -23672,7 +23672,7 @@
         <v>1.18</v>
       </c>
       <c r="AF143">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AG143">
         <v>2.3</v>
@@ -23832,7 +23832,7 @@
         <v>1.38</v>
       </c>
       <c r="AE144">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF144">
         <v>1.6</v>
@@ -24436,7 +24436,7 @@
         <v>1.58</v>
       </c>
       <c r="O148">
-        <v>3.64</v>
+        <v>3.33</v>
       </c>
       <c r="P148">
         <v>4.5</v>
@@ -24925,7 +24925,7 @@
         <v>2.5</v>
       </c>
       <c r="O151">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P151">
         <v>2.53</v>
@@ -27219,10 +27219,10 @@
         <v>2.2</v>
       </c>
       <c r="S165">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T165">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="U165">
         <v>2.75</v>
@@ -27261,7 +27261,7 @@
         <v>1.67</v>
       </c>
       <c r="AG165">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="AH165" t="inlineStr">
         <is>
@@ -28345,13 +28345,13 @@
         </is>
       </c>
       <c r="N172">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="O172">
         <v>4.2</v>
       </c>
       <c r="P172">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q172">
         <v>1.96</v>
@@ -28559,7 +28559,7 @@
         <v>1.28</v>
       </c>
       <c r="AE173">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF173">
         <v>1.75</v>
@@ -28858,7 +28858,7 @@
         <v>3</v>
       </c>
       <c r="V175">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W175">
         <v>1.07</v>
@@ -28873,7 +28873,7 @@
         <v>2.83</v>
       </c>
       <c r="AA175">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AB175">
         <v>1.63</v>
@@ -29012,16 +29012,16 @@
         <v>1.98</v>
       </c>
       <c r="S176">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T176">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="U176">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="V176">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W176">
         <v>1.05</v>
@@ -29033,7 +29033,7 @@
         <v>1.33</v>
       </c>
       <c r="Z176">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="AA176">
         <v>2.11</v>
@@ -29486,13 +29486,13 @@
         </is>
       </c>
       <c r="N179">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="O179">
-        <v>3.96</v>
+        <v>3.98</v>
       </c>
       <c r="P179">
-        <v>3.59</v>
+        <v>3.49</v>
       </c>
       <c r="Q179">
         <v>0</v>
@@ -29658,10 +29658,10 @@
         <v>2.85</v>
       </c>
       <c r="Q180">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="R180">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="S180">
         <v>1.2</v>
@@ -29676,31 +29676,31 @@
         <v>1.7</v>
       </c>
       <c r="W180">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X180">
         <v>1.02</v>
       </c>
       <c r="Y180">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z180">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AA180">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AB180">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AC180">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="AD180">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AE180">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF180">
         <v>1.4</v>
@@ -29719,7 +29719,7 @@
         </is>
       </c>
       <c r="AJ180">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK180">
         <v>1.63</v>
@@ -31614,7 +31614,7 @@
         <v>2.42</v>
       </c>
       <c r="Q192">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="R192">
         <v>2.15</v>
@@ -31623,16 +31623,16 @@
         <v>1.37</v>
       </c>
       <c r="T192">
-        <v>3.02</v>
+        <v>2.78</v>
       </c>
       <c r="U192">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="V192">
         <v>1.44</v>
       </c>
       <c r="W192">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X192">
         <v>1</v>
@@ -31650,7 +31650,7 @@
         <v>1.98</v>
       </c>
       <c r="AC192">
-        <v>2.81</v>
+        <v>3.1</v>
       </c>
       <c r="AD192">
         <v>1.42</v>
@@ -31675,10 +31675,10 @@
         </is>
       </c>
       <c r="AJ192">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK192">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AL192">
         <v>0</v>
@@ -31768,10 +31768,10 @@
         </is>
       </c>
       <c r="N193">
-        <v>10.5</v>
+        <v>9.25</v>
       </c>
       <c r="O193">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="P193">
         <v>1.21</v>
@@ -31783,10 +31783,10 @@
         <v>3.14</v>
       </c>
       <c r="S193">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="T193">
-        <v>5.55</v>
+        <v>5</v>
       </c>
       <c r="U193">
         <v>1.73</v>
@@ -31807,13 +31807,13 @@
         <v>9</v>
       </c>
       <c r="AA193">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AB193">
         <v>4.6</v>
       </c>
       <c r="AC193">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AD193">
         <v>2.43</v>
@@ -32103,16 +32103,16 @@
         <v>1.79</v>
       </c>
       <c r="Q195">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="R195">
         <v>2.1</v>
       </c>
       <c r="S195">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T195">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="U195">
         <v>2.9</v>
@@ -32287,7 +32287,7 @@
         <v>1.1</v>
       </c>
       <c r="X196">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y196">
         <v>1.17</v>
@@ -32305,7 +32305,7 @@
         <v>2.88</v>
       </c>
       <c r="AD196">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AE196">
         <v>1.12</v>
@@ -32426,7 +32426,7 @@
         <v>4.5</v>
       </c>
       <c r="P197">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="Q197">
         <v>2</v>
@@ -32474,7 +32474,7 @@
         <v>1.25</v>
       </c>
       <c r="AF197">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AG197">
         <v>2.45</v>
@@ -32610,7 +32610,7 @@
         <v>1.61</v>
       </c>
       <c r="W198">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X198">
         <v>1.02</v>
@@ -32619,7 +32619,7 @@
         <v>1.13</v>
       </c>
       <c r="Z198">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AA198">
         <v>1.53</v>
@@ -32752,13 +32752,13 @@
         <v>3.1</v>
       </c>
       <c r="P199">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="Q199">
         <v>3.06</v>
       </c>
       <c r="R199">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S199">
         <v>1.4</v>
@@ -32770,7 +32770,7 @@
         <v>2.9</v>
       </c>
       <c r="V199">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W199">
         <v>1.04</v>
@@ -32927,13 +32927,13 @@
         <v>1.22</v>
       </c>
       <c r="T200">
-        <v>3.74</v>
+        <v>3.6</v>
       </c>
       <c r="U200">
         <v>2.2</v>
       </c>
       <c r="V200">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W200">
         <v>1.14</v>
@@ -32948,16 +32948,16 @@
         <v>3.4</v>
       </c>
       <c r="AA200">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AB200">
-        <v>2.46</v>
+        <v>2.35</v>
       </c>
       <c r="AC200">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AD200">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AE200">
         <v>1.23</v>
@@ -32982,7 +32982,7 @@
         <v>1.08</v>
       </c>
       <c r="AK200">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL200">
         <v>0</v>
@@ -33081,10 +33081,10 @@
         <v>3.3</v>
       </c>
       <c r="Q201">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="R201">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="S201">
         <v>1.3</v>
@@ -33129,7 +33129,7 @@
         <v>1.62</v>
       </c>
       <c r="AG201">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AH201" t="inlineStr">
         <is>
@@ -33244,7 +33244,7 @@
         <v>3.8</v>
       </c>
       <c r="Q202">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R202">
         <v>2.61</v>
@@ -33277,19 +33277,19 @@
         <v>1.42</v>
       </c>
       <c r="AB202">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="AC202">
         <v>2.17</v>
       </c>
       <c r="AD202">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AE202">
         <v>1.22</v>
       </c>
       <c r="AF202">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AG202">
         <v>2.5</v>
@@ -33308,7 +33308,7 @@
         <v>1.22</v>
       </c>
       <c r="AK202">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AL202">
         <v>0</v>
@@ -33398,13 +33398,13 @@
         </is>
       </c>
       <c r="N203">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="O203">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="P203">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="Q203">
         <v>1.73</v>
@@ -33425,7 +33425,7 @@
         <v>1.62</v>
       </c>
       <c r="W203">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X203">
         <v>1.02</v>
@@ -33443,13 +33443,13 @@
         <v>2.46</v>
       </c>
       <c r="AC203">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AD203">
         <v>1.65</v>
       </c>
       <c r="AE203">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AF203">
         <v>1.65</v>
@@ -33730,7 +33730,7 @@
         <v>3.8</v>
       </c>
       <c r="P205">
-        <v>3.73</v>
+        <v>4</v>
       </c>
       <c r="Q205">
         <v>2.3</v>
@@ -33754,7 +33754,7 @@
         <v>1.1</v>
       </c>
       <c r="X205">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y205">
         <v>1.21</v>
@@ -35517,64 +35517,64 @@
         </is>
       </c>
       <c r="N216">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="O216">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P216">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="Q216">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="R216">
-        <v>2.93</v>
+        <v>2.85</v>
       </c>
       <c r="S216">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="T216">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="U216">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="V216">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="W216">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X216">
         <v>1.01</v>
       </c>
       <c r="Y216">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z216">
-        <v>8.550000000000001</v>
+        <v>8</v>
       </c>
       <c r="AA216">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AB216">
-        <v>3.23</v>
+        <v>3.1</v>
       </c>
       <c r="AC216">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AD216">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AE216">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AF216">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="AG216">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AH216" t="inlineStr">
         <is>
@@ -35590,7 +35590,7 @@
         <v>1.08</v>
       </c>
       <c r="AK216">
-        <v>5</v>
+        <v>4.65</v>
       </c>
       <c r="AL216">
         <v>0</v>
@@ -35855,25 +35855,25 @@
         <v>2.63</v>
       </c>
       <c r="R218">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="S218">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T218">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="U218">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="V218">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W218">
         <v>1.08</v>
       </c>
       <c r="X218">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y218">
         <v>1.3</v>
@@ -35894,7 +35894,7 @@
         <v>1.22</v>
       </c>
       <c r="AE218">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF218">
         <v>1.8</v>
@@ -35913,10 +35913,10 @@
         </is>
       </c>
       <c r="AJ218">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK218">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL218">
         <v>0</v>
@@ -36024,7 +36024,7 @@
         <v>1.44</v>
       </c>
       <c r="T219">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="U219">
         <v>3.2</v>
@@ -36033,10 +36033,10 @@
         <v>1.3</v>
       </c>
       <c r="W219">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X219">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y219">
         <v>1.37</v>
@@ -36045,7 +36045,7 @@
         <v>2.66</v>
       </c>
       <c r="AA219">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AB219">
         <v>1.65</v>
@@ -36057,7 +36057,7 @@
         <v>1.16</v>
       </c>
       <c r="AE219">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF219">
         <v>2</v>
@@ -36076,7 +36076,7 @@
         </is>
       </c>
       <c r="AJ219">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK219">
         <v>1.85</v>
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G220">
@@ -36169,64 +36169,64 @@
         </is>
       </c>
       <c r="N220">
-        <v>1.96</v>
+        <v>2.6</v>
       </c>
       <c r="O220">
         <v>3.4</v>
       </c>
       <c r="P220">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q220">
-        <v>2.4</v>
+        <v>3.15</v>
       </c>
       <c r="R220">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="S220">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T220">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="U220">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="V220">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="W220">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X220">
         <v>1</v>
       </c>
       <c r="Y220">
+        <v>1.14</v>
+      </c>
+      <c r="Z220">
+        <v>4.8</v>
+      </c>
+      <c r="AA220">
+        <v>1.53</v>
+      </c>
+      <c r="AB220">
+        <v>2.3</v>
+      </c>
+      <c r="AC220">
+        <v>2.25</v>
+      </c>
+      <c r="AD220">
+        <v>1.55</v>
+      </c>
+      <c r="AE220">
         <v>1.2</v>
       </c>
-      <c r="Z220">
-        <v>4</v>
-      </c>
-      <c r="AA220">
-        <v>1.74</v>
-      </c>
-      <c r="AB220">
-        <v>2.08</v>
-      </c>
-      <c r="AC220">
-        <v>2.88</v>
-      </c>
-      <c r="AD220">
-        <v>1.36</v>
-      </c>
-      <c r="AE220">
-        <v>1.13</v>
-      </c>
       <c r="AF220">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AG220">
-        <v>2.15</v>
+        <v>2.58</v>
       </c>
       <c r="AH220" t="inlineStr">
         <is>
@@ -36239,10 +36239,10 @@
         </is>
       </c>
       <c r="AJ220">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="AK220">
-        <v>1.83</v>
+        <v>1.38</v>
       </c>
       <c r="AL220">
         <v>0</v>
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G221">
@@ -36332,64 +36332,64 @@
         </is>
       </c>
       <c r="N221">
-        <v>2.6</v>
+        <v>1.96</v>
       </c>
       <c r="O221">
         <v>3.4</v>
       </c>
       <c r="P221">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q221">
-        <v>3.15</v>
+        <v>2.4</v>
       </c>
       <c r="R221">
+        <v>2.2</v>
+      </c>
+      <c r="S221">
+        <v>1.3</v>
+      </c>
+      <c r="T221">
+        <v>3.25</v>
+      </c>
+      <c r="U221">
         <v>2.45</v>
       </c>
-      <c r="S221">
-        <v>1.22</v>
-      </c>
-      <c r="T221">
-        <v>3.8</v>
-      </c>
-      <c r="U221">
-        <v>2.18</v>
-      </c>
       <c r="V221">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="W221">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X221">
         <v>1</v>
       </c>
       <c r="Y221">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z221">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="AA221">
-        <v>1.53</v>
+        <v>1.74</v>
       </c>
       <c r="AB221">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="AC221">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="AD221">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="AE221">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AF221">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="AG221">
-        <v>2.58</v>
+        <v>2.15</v>
       </c>
       <c r="AH221" t="inlineStr">
         <is>
@@ -36402,10 +36402,10 @@
         </is>
       </c>
       <c r="AJ221">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AK221">
-        <v>1.38</v>
+        <v>1.83</v>
       </c>
       <c r="AL221">
         <v>0</v>
@@ -36700,7 +36700,7 @@
         <v>2.15</v>
       </c>
       <c r="AB223">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC223">
         <v>3.42</v>
@@ -36715,7 +36715,7 @@
         <v>1.8</v>
       </c>
       <c r="AG223">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH223" t="inlineStr">
         <is>
@@ -36839,13 +36839,13 @@
         <v>1.36</v>
       </c>
       <c r="T224">
-        <v>2.88</v>
+        <v>2.64</v>
       </c>
       <c r="U224">
-        <v>2.98</v>
+        <v>2.85</v>
       </c>
       <c r="V224">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="W224">
         <v>1.06</v>
@@ -36993,55 +36993,55 @@
         <v>0</v>
       </c>
       <c r="Q225">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R225">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S225">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T225">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U225">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="V225">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W225">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X225">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y225">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z225">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AA225">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="AB225">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC225">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD225">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE225">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF225">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG225">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH225" t="inlineStr">
         <is>
@@ -37054,10 +37054,10 @@
         </is>
       </c>
       <c r="AJ225">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK225">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AL225">
         <v>0</v>
@@ -37156,55 +37156,55 @@
         <v>0</v>
       </c>
       <c r="Q226">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="R226">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S226">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T226">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U226">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V226">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W226">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X226">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y226">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z226">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AA226">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB226">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC226">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AD226">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE226">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF226">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG226">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AH226" t="inlineStr">
         <is>
@@ -37217,10 +37217,10 @@
         </is>
       </c>
       <c r="AJ226">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK226">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AL226">
         <v>0</v>
@@ -37325,10 +37325,10 @@
         <v>2.03</v>
       </c>
       <c r="S227">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="T227">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="U227">
         <v>2.81</v>
@@ -37361,7 +37361,7 @@
         <v>1.21</v>
       </c>
       <c r="AE227">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF227">
         <v>2</v>
@@ -37485,37 +37485,37 @@
         <v>2.1</v>
       </c>
       <c r="R228">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="S228">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T228">
         <v>2.84</v>
       </c>
       <c r="U228">
-        <v>2.58</v>
+        <v>2.78</v>
       </c>
       <c r="V228">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W228">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X228">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y228">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z228">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AA228">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AB228">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AC228">
         <v>3.08</v>
@@ -37524,10 +37524,10 @@
         <v>1.28</v>
       </c>
       <c r="AE228">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF228">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AG228">
         <v>1.75</v>
@@ -37546,7 +37546,7 @@
         <v>1.25</v>
       </c>
       <c r="AK228">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="AL228">
         <v>0</v>
@@ -37648,22 +37648,22 @@
         <v>3.3</v>
       </c>
       <c r="R229">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="S229">
         <v>1.3</v>
       </c>
       <c r="T229">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="U229">
         <v>2.5</v>
       </c>
       <c r="V229">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W229">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X229">
         <v>1.04</v>
@@ -37678,7 +37678,7 @@
         <v>1.75</v>
       </c>
       <c r="AB229">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AC229">
         <v>2.88</v>
@@ -37808,55 +37808,55 @@
         <v>0</v>
       </c>
       <c r="Q230">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="R230">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="S230">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="T230">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="U230">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="V230">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W230">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X230">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y230">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z230">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AA230">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB230">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC230">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AD230">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE230">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF230">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG230">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH230" t="inlineStr">
         <is>
@@ -37869,10 +37869,10 @@
         </is>
       </c>
       <c r="AJ230">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK230">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AL230">
         <v>0</v>
@@ -38134,7 +38134,7 @@
         <v>0</v>
       </c>
       <c r="Q232">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="R232">
         <v>2.1</v>
@@ -38155,13 +38155,13 @@
         <v>1.08</v>
       </c>
       <c r="X232">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y232">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z232">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="AA232">
         <v>2</v>
@@ -38170,19 +38170,19 @@
         <v>1.8</v>
       </c>
       <c r="AC232">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AD232">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE232">
         <v>1.06</v>
       </c>
       <c r="AF232">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AG232">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AH232" t="inlineStr">
         <is>
@@ -38195,10 +38195,10 @@
         </is>
       </c>
       <c r="AJ232">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK232">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL232">
         <v>0</v>
@@ -39266,13 +39266,13 @@
         </is>
       </c>
       <c r="N239">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="O239">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="P239">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="Q239">
         <v>2.07</v>
@@ -39435,7 +39435,7 @@
         <v>6.2</v>
       </c>
       <c r="P240">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q240">
         <v>1.49</v>
@@ -39468,10 +39468,10 @@
         <v>8.6</v>
       </c>
       <c r="AA240">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AB240">
-        <v>4.39</v>
+        <v>4.5</v>
       </c>
       <c r="AC240">
         <v>1.53</v>
@@ -39480,7 +39480,7 @@
         <v>2.38</v>
       </c>
       <c r="AE240">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AF240">
         <v>1.47</v>
@@ -39592,13 +39592,13 @@
         </is>
       </c>
       <c r="N241">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="O241">
         <v>3.4</v>
       </c>
       <c r="P241">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q241">
         <v>3.6</v>
@@ -39610,7 +39610,7 @@
         <v>1.29</v>
       </c>
       <c r="T241">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U241">
         <v>2.32</v>
@@ -39634,13 +39634,13 @@
         <v>1.62</v>
       </c>
       <c r="AB241">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AC241">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="AD241">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AE241">
         <v>1.18</v>
@@ -39948,7 +39948,7 @@
         <v>1.3</v>
       </c>
       <c r="X243">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y243">
         <v>1.02</v>
@@ -39972,7 +39972,7 @@
         <v>1.49</v>
       </c>
       <c r="AF243">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AG243">
         <v>2.8</v>
@@ -40283,7 +40283,7 @@
         <v>4.3</v>
       </c>
       <c r="AA245">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB245">
         <v>2.15</v>
@@ -40295,7 +40295,7 @@
         <v>1.45</v>
       </c>
       <c r="AE245">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF245">
         <v>1.7</v>
@@ -40413,7 +40413,7 @@
         <v>3.5</v>
       </c>
       <c r="P246">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="Q246">
         <v>2.68</v>
@@ -40461,7 +40461,7 @@
         <v>1.13</v>
       </c>
       <c r="AF246">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG246">
         <v>2.2</v>
@@ -40573,7 +40573,7 @@
         <v>1.4</v>
       </c>
       <c r="O247">
-        <v>5.05</v>
+        <v>5.15</v>
       </c>
       <c r="P247">
         <v>6.5</v>
@@ -41222,10 +41222,10 @@
         </is>
       </c>
       <c r="N251">
-        <v>2.7</v>
+        <v>2.61</v>
       </c>
       <c r="O251">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P251">
         <v>2.3</v>
@@ -41237,7 +41237,7 @@
         <v>2.15</v>
       </c>
       <c r="S251">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="T251">
         <v>2.73</v>
@@ -41276,10 +41276,10 @@
         <v>1.11</v>
       </c>
       <c r="AF251">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG251">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH251" t="inlineStr">
         <is>
@@ -41406,10 +41406,10 @@
         <v>3.7</v>
       </c>
       <c r="U252">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="V252">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="W252">
         <v>1.13</v>
@@ -41442,7 +41442,7 @@
         <v>1.59</v>
       </c>
       <c r="AG252">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AH252" t="inlineStr">
         <is>
@@ -42366,7 +42366,7 @@
         <v>1.61</v>
       </c>
       <c r="O258">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="P258">
         <v>4.85</v>
@@ -42526,7 +42526,7 @@
         </is>
       </c>
       <c r="N259">
-        <v>3.7</v>
+        <v>3.94</v>
       </c>
       <c r="O259">
         <v>3.8</v>
@@ -42689,7 +42689,7 @@
         </is>
       </c>
       <c r="N260">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="O260">
         <v>3.7</v>
@@ -42731,7 +42731,7 @@
         <v>1.67</v>
       </c>
       <c r="AB260">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC260">
         <v>2.7</v>
@@ -42861,7 +42861,7 @@
         <v>4.2</v>
       </c>
       <c r="Q261">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R261">
         <v>2.02</v>
@@ -42882,7 +42882,7 @@
         <v>1.08</v>
       </c>
       <c r="X261">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y261">
         <v>1.31</v>
@@ -42903,7 +42903,7 @@
         <v>1.23</v>
       </c>
       <c r="AE261">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF261">
         <v>1.83</v>
@@ -42922,10 +42922,10 @@
         </is>
       </c>
       <c r="AJ261">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK261">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AL261">
         <v>0</v>
@@ -43027,7 +43027,7 @@
         <v>1.67</v>
       </c>
       <c r="R262">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="S262">
         <v>1.25</v>
@@ -43051,7 +43051,7 @@
         <v>1.14</v>
       </c>
       <c r="Z262">
-        <v>4.4</v>
+        <v>4.62</v>
       </c>
       <c r="AA262">
         <v>1.6</v>
@@ -43060,16 +43060,16 @@
         <v>2.3</v>
       </c>
       <c r="AC262">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="AD262">
         <v>1.51</v>
       </c>
       <c r="AE262">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF262">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AG262">
         <v>1.8</v>
@@ -43085,10 +43085,10 @@
         </is>
       </c>
       <c r="AJ262">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AK262">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AL262">
         <v>0</v>
@@ -43507,13 +43507,13 @@
         <v>2.15</v>
       </c>
       <c r="O265">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P265">
         <v>2.86</v>
       </c>
       <c r="Q265">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="R265">
         <v>2.32</v>
@@ -43993,16 +43993,16 @@
         </is>
       </c>
       <c r="N268">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="O268">
         <v>3.35</v>
       </c>
       <c r="P268">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q268">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="R268">
         <v>2.3</v>
@@ -44044,7 +44044,7 @@
         <v>1.46</v>
       </c>
       <c r="AE268">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AF268">
         <v>1.5</v>
@@ -44063,10 +44063,10 @@
         </is>
       </c>
       <c r="AJ268">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK268">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL268">
         <v>0</v>
@@ -44165,10 +44165,10 @@
         <v>3.3</v>
       </c>
       <c r="Q269">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="R269">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="S269">
         <v>1.25</v>
@@ -44201,10 +44201,10 @@
         <v>2.38</v>
       </c>
       <c r="AC269">
-        <v>2.35</v>
+        <v>2.49</v>
       </c>
       <c r="AD269">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="AE269">
         <v>1.19</v>
@@ -44319,7 +44319,7 @@
         </is>
       </c>
       <c r="N270">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O270">
         <v>3.2</v>
@@ -44482,13 +44482,13 @@
         </is>
       </c>
       <c r="N271">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="O271">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P271">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="Q271">
         <v>2.62</v>
@@ -44527,7 +44527,7 @@
         <v>2</v>
       </c>
       <c r="AC271">
-        <v>2.81</v>
+        <v>2.96</v>
       </c>
       <c r="AD271">
         <v>1.33</v>
@@ -44678,7 +44678,7 @@
         <v>1.03</v>
       </c>
       <c r="Y272">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z272">
         <v>3.4</v>
@@ -44715,7 +44715,7 @@
         </is>
       </c>
       <c r="AJ272">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK272">
         <v>1.6</v>
@@ -44817,55 +44817,55 @@
         <v>0</v>
       </c>
       <c r="Q273">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R273">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S273">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T273">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U273">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V273">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W273">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X273">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y273">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z273">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA273">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB273">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC273">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD273">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE273">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF273">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG273">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH273" t="inlineStr">
         <is>
@@ -44878,10 +44878,10 @@
         </is>
       </c>
       <c r="AJ273">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK273">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL273">
         <v>0</v>
@@ -45469,7 +45469,7 @@
         <v>3.1</v>
       </c>
       <c r="Q277">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="R277">
         <v>2.1</v>
@@ -45493,16 +45493,16 @@
         <v>1.01</v>
       </c>
       <c r="Y277">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z277">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="AA277">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AB277">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AC277">
         <v>3.5</v>
@@ -45819,10 +45819,10 @@
         <v>1.05</v>
       </c>
       <c r="Y279">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="Z279">
-        <v>2.46</v>
+        <v>2.53</v>
       </c>
       <c r="AA279">
         <v>2.4</v>
@@ -45988,7 +45988,7 @@
         <v>2.56</v>
       </c>
       <c r="AA280">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AB280">
         <v>1.5</v>
@@ -46003,7 +46003,7 @@
         <v>1.01</v>
       </c>
       <c r="AF280">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AG280">
         <v>1.7</v>
@@ -46508,7 +46508,7 @@
         </is>
       </c>
       <c r="AJ283">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK283">
         <v>1.83</v>
@@ -46601,13 +46601,13 @@
         </is>
       </c>
       <c r="N284">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="O284">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P284">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="Q284">
         <v>3.59</v>
@@ -46634,10 +46634,10 @@
         <v>1.08</v>
       </c>
       <c r="Y284">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Z284">
-        <v>2.58</v>
+        <v>2.69</v>
       </c>
       <c r="AA284">
         <v>2.5</v>
@@ -46652,7 +46652,7 @@
         <v>1.18</v>
       </c>
       <c r="AE284">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF284">
         <v>2</v>
@@ -47253,13 +47253,13 @@
         </is>
       </c>
       <c r="N288">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="O288">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P288">
-        <v>4.65</v>
+        <v>4.95</v>
       </c>
       <c r="Q288">
         <v>1.92</v>
@@ -47292,16 +47292,16 @@
         <v>4.8</v>
       </c>
       <c r="AA288">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AB288">
         <v>2.35</v>
       </c>
       <c r="AC288">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AD288">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AE288">
         <v>1.2</v>
@@ -47416,13 +47416,13 @@
         </is>
       </c>
       <c r="N289">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="O289">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P289">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="Q289">
         <v>2.33</v>
@@ -47437,7 +47437,7 @@
         <v>3.6</v>
       </c>
       <c r="U289">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V289">
         <v>1.47</v>
@@ -47464,7 +47464,7 @@
         <v>2.39</v>
       </c>
       <c r="AD289">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AE289">
         <v>1.14</v>
@@ -47473,7 +47473,7 @@
         <v>1.5</v>
       </c>
       <c r="AG289">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH289" t="inlineStr">
         <is>
@@ -47630,7 +47630,7 @@
         <v>1.37</v>
       </c>
       <c r="AE290">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF290">
         <v>1.69</v>
@@ -47932,7 +47932,7 @@
         <v>1.43</v>
       </c>
       <c r="W292">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X292">
         <v>1.04</v>
@@ -47944,10 +47944,10 @@
         <v>3.82</v>
       </c>
       <c r="AA292">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB292">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC292">
         <v>2.78</v>
@@ -48080,7 +48080,7 @@
         <v>1.62</v>
       </c>
       <c r="R293">
-        <v>2.66</v>
+        <v>2.71</v>
       </c>
       <c r="S293">
         <v>1.15</v>
@@ -48101,31 +48101,31 @@
         <v>1.01</v>
       </c>
       <c r="Y293">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Z293">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AA293">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AB293">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AC293">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AD293">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AE293">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AF293">
         <v>1.6</v>
       </c>
       <c r="AG293">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AH293" t="inlineStr">
         <is>
@@ -48234,7 +48234,7 @@
         <v>3.72</v>
       </c>
       <c r="O294">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="P294">
         <v>1.78</v>
@@ -48430,7 +48430,7 @@
         <v>1.25</v>
       </c>
       <c r="Z295">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="AA295">
         <v>1.9</v>
@@ -48439,7 +48439,7 @@
         <v>1.9</v>
       </c>
       <c r="AC295">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="AD295">
         <v>1.33</v>
@@ -48883,13 +48883,13 @@
         </is>
       </c>
       <c r="N298">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="O298">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P298">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="Q298">
         <v>2.25</v>
@@ -48922,7 +48922,7 @@
         <v>3.2</v>
       </c>
       <c r="AA298">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB298">
         <v>1.85</v>
@@ -49393,10 +49393,10 @@
         <v>3.1</v>
       </c>
       <c r="U301">
-        <v>2.43</v>
+        <v>2.39</v>
       </c>
       <c r="V301">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W301">
         <v>1.08</v>
@@ -49423,7 +49423,7 @@
         <v>1.45</v>
       </c>
       <c r="AE301">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF301">
         <v>1.57</v>
@@ -49574,7 +49574,7 @@
         <v>2.31</v>
       </c>
       <c r="AA302">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AB302">
         <v>1.38</v>
@@ -50519,7 +50519,7 @@
         <v>3.3</v>
       </c>
       <c r="P308">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="Q308">
         <v>3</v>
@@ -50561,7 +50561,7 @@
         <v>2.65</v>
       </c>
       <c r="AD308">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE308">
         <v>1.13</v>
@@ -50676,13 +50676,13 @@
         </is>
       </c>
       <c r="N309">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="O309">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="P309">
-        <v>4.94</v>
+        <v>4.6</v>
       </c>
       <c r="Q309">
         <v>2.05</v>
@@ -50697,10 +50697,10 @@
         <v>3.9</v>
       </c>
       <c r="U309">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="V309">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W309">
         <v>1.18</v>
@@ -50715,7 +50715,7 @@
         <v>5.75</v>
       </c>
       <c r="AA309">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB309">
         <v>2.7</v>
@@ -50839,7 +50839,7 @@
         </is>
       </c>
       <c r="N310">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="O310">
         <v>3.4</v>
@@ -50890,7 +50890,7 @@
         <v>1.23</v>
       </c>
       <c r="AE310">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF310">
         <v>2.05</v>
@@ -51171,7 +51171,7 @@
         <v>3.3</v>
       </c>
       <c r="P312">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q312">
         <v>2.35</v>
@@ -51180,7 +51180,7 @@
         <v>2.08</v>
       </c>
       <c r="S312">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T312">
         <v>3.02</v>
@@ -51198,7 +51198,7 @@
         <v>1.01</v>
       </c>
       <c r="Y312">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z312">
         <v>3.2</v>
@@ -51385,7 +51385,7 @@
         <v>1.33</v>
       </c>
       <c r="AG313">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AH313" t="inlineStr">
         <is>
@@ -51494,25 +51494,25 @@
         <v>2.25</v>
       </c>
       <c r="O314">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="P314">
-        <v>2.51</v>
+        <v>2.86</v>
       </c>
       <c r="Q314">
-        <v>3.72</v>
+        <v>3.52</v>
       </c>
       <c r="R314">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="S314">
         <v>1.62</v>
       </c>
       <c r="T314">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="U314">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="V314">
         <v>1.18</v>
@@ -51521,34 +51521,34 @@
         <v>1.04</v>
       </c>
       <c r="X314">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Y314">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Z314">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="AA314">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="AB314">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AC314">
-        <v>6.5</v>
+        <v>6.45</v>
       </c>
       <c r="AD314">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AE314">
         <v>1.02</v>
       </c>
       <c r="AF314">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="AG314">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AH314" t="inlineStr">
         <is>
@@ -51561,10 +51561,10 @@
         </is>
       </c>
       <c r="AJ314">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AK314">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AL314">
         <v>0</v>
@@ -51622,12 +51622,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G315">
@@ -51654,64 +51654,64 @@
         </is>
       </c>
       <c r="N315">
-        <v>2.16</v>
+        <v>1.53</v>
       </c>
       <c r="O315">
-        <v>3.7</v>
+        <v>4.79</v>
       </c>
       <c r="P315">
-        <v>2.75</v>
+        <v>5.1</v>
       </c>
       <c r="Q315">
-        <v>2.57</v>
+        <v>1.91</v>
       </c>
       <c r="R315">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S315">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T315">
         <v>4</v>
       </c>
       <c r="U315">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="V315">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="W315">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X315">
         <v>0</v>
       </c>
       <c r="Y315">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z315">
         <v>5.3</v>
       </c>
       <c r="AA315">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="AB315">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="AC315">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="AD315">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AE315">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF315">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AG315">
-        <v>2.72</v>
+        <v>2.25</v>
       </c>
       <c r="AH315" t="inlineStr">
         <is>
@@ -51724,10 +51724,10 @@
         </is>
       </c>
       <c r="AJ315">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK315">
-        <v>1.67</v>
+        <v>2.6</v>
       </c>
       <c r="AL315">
         <v>0</v>
@@ -51785,12 +51785,12 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G316">
@@ -51817,64 +51817,64 @@
         </is>
       </c>
       <c r="N316">
-        <v>1.53</v>
+        <v>2.16</v>
       </c>
       <c r="O316">
-        <v>4.79</v>
+        <v>3.7</v>
       </c>
       <c r="P316">
-        <v>5.1</v>
+        <v>2.75</v>
       </c>
       <c r="Q316">
-        <v>1.8</v>
+        <v>2.57</v>
       </c>
       <c r="R316">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S316">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T316">
         <v>4</v>
       </c>
       <c r="U316">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="V316">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="W316">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X316">
         <v>0</v>
       </c>
       <c r="Y316">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z316">
         <v>5.3</v>
       </c>
       <c r="AA316">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="AB316">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="AC316">
-        <v>2.23</v>
+        <v>2.06</v>
       </c>
       <c r="AD316">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AE316">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF316">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AG316">
-        <v>2.25</v>
+        <v>2.72</v>
       </c>
       <c r="AH316" t="inlineStr">
         <is>
@@ -51887,10 +51887,10 @@
         </is>
       </c>
       <c r="AJ316">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK316">
-        <v>2.6</v>
+        <v>1.67</v>
       </c>
       <c r="AL316">
         <v>0</v>
@@ -51983,16 +51983,16 @@
         <v>1.67</v>
       </c>
       <c r="O317">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P317">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="Q317">
         <v>2.29</v>
       </c>
       <c r="R317">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="S317">
         <v>1.36</v>
@@ -52001,7 +52001,7 @@
         <v>2.9</v>
       </c>
       <c r="U317">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="V317">
         <v>1.4</v>
@@ -52025,7 +52025,7 @@
         <v>1.82</v>
       </c>
       <c r="AC317">
-        <v>3.59</v>
+        <v>3.5</v>
       </c>
       <c r="AD317">
         <v>1.25</v>
@@ -52050,10 +52050,10 @@
         </is>
       </c>
       <c r="AJ317">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AK317">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AL317">
         <v>0</v>
@@ -52179,10 +52179,10 @@
         <v>1.25</v>
       </c>
       <c r="Z318">
-        <v>3.9</v>
+        <v>3.78</v>
       </c>
       <c r="AA318">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AB318">
         <v>2.1</v>
@@ -52191,10 +52191,10 @@
         <v>2.66</v>
       </c>
       <c r="AD318">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AE318">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF318">
         <v>1.85</v>
@@ -52306,19 +52306,19 @@
         </is>
       </c>
       <c r="N319">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="O319">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P319">
         <v>3.1</v>
       </c>
       <c r="Q319">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="R319">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="S319">
         <v>1.52</v>
@@ -52327,7 +52327,7 @@
         <v>2.37</v>
       </c>
       <c r="U319">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="V319">
         <v>1.25</v>
@@ -52339,7 +52339,7 @@
         <v>1.1</v>
       </c>
       <c r="Y319">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Z319">
         <v>2.47</v>
@@ -52496,7 +52496,7 @@
         <v>1.62</v>
       </c>
       <c r="W320">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X320">
         <v>1.02</v>
@@ -52511,10 +52511,10 @@
         <v>1.46</v>
       </c>
       <c r="AB320">
-        <v>2.02</v>
+        <v>2.38</v>
       </c>
       <c r="AC320">
-        <v>1.96</v>
+        <v>2.22</v>
       </c>
       <c r="AD320">
         <v>1.56</v>
@@ -52523,7 +52523,7 @@
         <v>1.19</v>
       </c>
       <c r="AF320">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AG320">
         <v>2.5</v>
@@ -52542,7 +52542,7 @@
         <v>1.19</v>
       </c>
       <c r="AK320">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL320">
         <v>0</v>
@@ -52641,7 +52641,7 @@
         <v>1.53</v>
       </c>
       <c r="Q321">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="R321">
         <v>2.63</v>
@@ -52653,10 +52653,10 @@
         <v>4.3</v>
       </c>
       <c r="U321">
-        <v>1.73</v>
+        <v>1.99</v>
       </c>
       <c r="V321">
-        <v>1.61</v>
+        <v>1.79</v>
       </c>
       <c r="W321">
         <v>1.2</v>
@@ -52665,31 +52665,31 @@
         <v>1.01</v>
       </c>
       <c r="Y321">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Z321">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AA321">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AB321">
-        <v>2.45</v>
+        <v>2.83</v>
       </c>
       <c r="AC321">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AD321">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AE321">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AF321">
         <v>1.44</v>
       </c>
       <c r="AG321">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AH321" t="inlineStr">
         <is>
@@ -52702,10 +52702,10 @@
         </is>
       </c>
       <c r="AJ321">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AK321">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AL321">
         <v>0</v>
@@ -52804,10 +52804,10 @@
         <v>10.53</v>
       </c>
       <c r="Q322">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="R322">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="S322">
         <v>1.18</v>
@@ -52831,13 +52831,13 @@
         <v>1.05</v>
       </c>
       <c r="Z322">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AA322">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AB322">
-        <v>2.45</v>
+        <v>2.83</v>
       </c>
       <c r="AC322">
         <v>1.89</v>
@@ -52846,13 +52846,13 @@
         <v>1.78</v>
       </c>
       <c r="AE322">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AF322">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AG322">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AH322" t="inlineStr">
         <is>
@@ -53136,7 +53136,7 @@
         <v>2.3</v>
       </c>
       <c r="S324">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T324">
         <v>3.5</v>
@@ -53169,7 +53169,7 @@
         <v>2.31</v>
       </c>
       <c r="AD324">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AE324">
         <v>1.18</v>
@@ -53296,16 +53296,16 @@
         <v>2.1</v>
       </c>
       <c r="R325">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="S325">
         <v>1.29</v>
       </c>
       <c r="T325">
-        <v>2.63</v>
+        <v>3.08</v>
       </c>
       <c r="U325">
-        <v>2.01</v>
+        <v>2.41</v>
       </c>
       <c r="V325">
         <v>1.5</v>
@@ -53317,10 +53317,10 @@
         <v>1.03</v>
       </c>
       <c r="Y325">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z325">
-        <v>3.13</v>
+        <v>4</v>
       </c>
       <c r="AA325">
         <v>1.63</v>
@@ -53335,7 +53335,7 @@
         <v>1.41</v>
       </c>
       <c r="AE325">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF325">
         <v>1.62</v>
@@ -53354,10 +53354,10 @@
         </is>
       </c>
       <c r="AJ325">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AK325">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AL325">
         <v>0</v>
@@ -53480,31 +53480,31 @@
         <v>1.03</v>
       </c>
       <c r="Y326">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z326">
-        <v>3.2</v>
+        <v>4.25</v>
       </c>
       <c r="AA326">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AB326">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="AC326">
-        <v>2.06</v>
+        <v>2.41</v>
       </c>
       <c r="AD326">
         <v>1.4</v>
       </c>
       <c r="AE326">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF326">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="AG326">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AH326" t="inlineStr">
         <is>
@@ -53517,7 +53517,7 @@
         </is>
       </c>
       <c r="AJ326">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK326">
         <v>1.96</v>
@@ -53619,7 +53619,7 @@
         <v>1.79</v>
       </c>
       <c r="Q327">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="R327">
         <v>2.38</v>
@@ -53652,7 +53652,7 @@
         <v>1.46</v>
       </c>
       <c r="AB327">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="AC327">
         <v>2.24</v>
@@ -53661,13 +53661,13 @@
         <v>1.55</v>
       </c>
       <c r="AE327">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF327">
         <v>1.44</v>
       </c>
       <c r="AG327">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="AH327" t="inlineStr">
         <is>
@@ -53782,16 +53782,16 @@
         <v>2.7</v>
       </c>
       <c r="Q328">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="R328">
-        <v>2.32</v>
+        <v>2.49</v>
       </c>
       <c r="S328">
         <v>1.25</v>
       </c>
       <c r="T328">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="U328">
         <v>2.2</v>
@@ -53818,7 +53818,7 @@
         <v>2.35</v>
       </c>
       <c r="AC328">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="AD328">
         <v>1.58</v>
@@ -53945,7 +53945,7 @@
         <v>0</v>
       </c>
       <c r="Q329">
-        <v>4.77</v>
+        <v>4.6</v>
       </c>
       <c r="R329">
         <v>2.36</v>
@@ -53960,7 +53960,7 @@
         <v>2.05</v>
       </c>
       <c r="V329">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="W329">
         <v>1.17</v>
@@ -53975,7 +53975,7 @@
         <v>5.1</v>
       </c>
       <c r="AA329">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AB329">
         <v>2.6</v>
@@ -54108,7 +54108,7 @@
         <v>2.41</v>
       </c>
       <c r="Q330">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="R330">
         <v>2.54</v>
@@ -54147,7 +54147,7 @@
         <v>1.83</v>
       </c>
       <c r="AD330">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AE330">
         <v>1.41</v>
@@ -54172,7 +54172,7 @@
         <v>1.22</v>
       </c>
       <c r="AK330">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL330">
         <v>0</v>
@@ -54591,7 +54591,7 @@
         <v>1.87</v>
       </c>
       <c r="O333">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P333">
         <v>3.7</v>
@@ -54609,10 +54609,10 @@
         <v>3.6</v>
       </c>
       <c r="U333">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="V333">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W333">
         <v>1.15</v>
@@ -54630,7 +54630,7 @@
         <v>1.57</v>
       </c>
       <c r="AB333">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AC333">
         <v>2.43</v>

--- a/jogos_2026-11-01.xlsx
+++ b/jogos_2026-11-01.xlsx
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,19 +2102,19 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="O11">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="P11">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="Q11">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="R11">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="S11">
         <v>1.35</v>
@@ -2123,34 +2123,34 @@
         <v>3</v>
       </c>
       <c r="U11">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="V11">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W11">
         <v>1.1</v>
       </c>
       <c r="X11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z11">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA11">
         <v>1.94</v>
       </c>
       <c r="AB11">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AC11">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="AD11">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE11">
         <v>1.07</v>
@@ -2159,7 +2159,7 @@
         <v>1.75</v>
       </c>
       <c r="AG11">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK11">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,19 +2265,19 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="O12">
-        <v>3.4</v>
+        <v>3.43</v>
       </c>
       <c r="P12">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="Q12">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="R12">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="S12">
         <v>1.35</v>
@@ -2286,34 +2286,34 @@
         <v>3</v>
       </c>
       <c r="U12">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="V12">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W12">
         <v>1.1</v>
       </c>
       <c r="X12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z12">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA12">
         <v>1.94</v>
       </c>
       <c r="AB12">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AC12">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="AD12">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE12">
         <v>1.07</v>
@@ -2322,7 +2322,7 @@
         <v>1.75</v>
       </c>
       <c r="AG12">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK12">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -3898,10 +3898,10 @@
         <v>1.48</v>
       </c>
       <c r="O22">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P22">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="Q22">
         <v>1.92</v>
@@ -3910,10 +3910,10 @@
         <v>2.54</v>
       </c>
       <c r="S22">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T22">
-        <v>3.38</v>
+        <v>3.24</v>
       </c>
       <c r="U22">
         <v>2.25</v>
@@ -3928,10 +3928,10 @@
         <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z22">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AA22">
         <v>1.58</v>
@@ -3946,7 +3946,7 @@
         <v>1.51</v>
       </c>
       <c r="AE22">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF22">
         <v>1.67</v>
@@ -4076,7 +4076,7 @@
         <v>1.45</v>
       </c>
       <c r="T23">
-        <v>2.7</v>
+        <v>2.58</v>
       </c>
       <c r="U23">
         <v>3</v>
@@ -4097,22 +4097,22 @@
         <v>2.89</v>
       </c>
       <c r="AA23">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="AB23">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AC23">
-        <v>3.68</v>
+        <v>3.76</v>
       </c>
       <c r="AD23">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE23">
         <v>1.03</v>
       </c>
       <c r="AF23">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AG23">
         <v>1.8</v>
@@ -4260,7 +4260,7 @@
         <v>4.33</v>
       </c>
       <c r="AA24">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AB24">
         <v>2.1</v>
@@ -4586,7 +4586,7 @@
         <v>3.7</v>
       </c>
       <c r="AA26">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AB26">
         <v>1.99</v>
@@ -4725,16 +4725,16 @@
         <v>2.1</v>
       </c>
       <c r="S27">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T27">
         <v>2.8</v>
       </c>
       <c r="U27">
-        <v>2.99</v>
+        <v>2.9</v>
       </c>
       <c r="V27">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W27">
         <v>1.05</v>
@@ -4764,10 +4764,10 @@
         <v>1.05</v>
       </c>
       <c r="AF27">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AG27">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q28">
         <v>5</v>
@@ -5401,7 +5401,7 @@
         <v>2.7</v>
       </c>
       <c r="AA31">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB31">
         <v>1.58</v>
@@ -5416,7 +5416,7 @@
         <v>1.02</v>
       </c>
       <c r="AF31">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG31">
         <v>1.67</v>
@@ -5727,7 +5727,7 @@
         <v>3.1</v>
       </c>
       <c r="AA33">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AB33">
         <v>1.67</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="O37">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P37">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="Q37">
         <v>2.63</v>
@@ -6397,7 +6397,7 @@
         <v>1.91</v>
       </c>
       <c r="AG37">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -7336,13 +7336,13 @@
         <v>1.32</v>
       </c>
       <c r="T43">
-        <v>3.09</v>
+        <v>3.25</v>
       </c>
       <c r="U43">
         <v>2.45</v>
       </c>
       <c r="V43">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W43">
         <v>1.11</v>
@@ -7357,10 +7357,10 @@
         <v>3.88</v>
       </c>
       <c r="AA43">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AB43">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="AC43">
         <v>2.7</v>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK43">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7493,7 +7493,7 @@
         <v>2.3</v>
       </c>
       <c r="R44">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="S44">
         <v>1.36</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CD Don Benito</t>
+          <t>Mijas Las Lagunas</t>
         </is>
       </c>
       <c r="G45">
@@ -7647,61 +7647,61 @@
         <v>1.91</v>
       </c>
       <c r="O45">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P45">
         <v>3.4</v>
       </c>
       <c r="Q45">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="R45">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="S45">
         <v>1.35</v>
       </c>
       <c r="T45">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="U45">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="V45">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W45">
+        <v>1.08</v>
+      </c>
+      <c r="X45">
+        <v>1.01</v>
+      </c>
+      <c r="Y45">
+        <v>1.23</v>
+      </c>
+      <c r="Z45">
+        <v>3.42</v>
+      </c>
+      <c r="AA45">
+        <v>1.9</v>
+      </c>
+      <c r="AB45">
+        <v>1.88</v>
+      </c>
+      <c r="AC45">
+        <v>3.05</v>
+      </c>
+      <c r="AD45">
+        <v>1.28</v>
+      </c>
+      <c r="AE45">
         <v>1.1</v>
       </c>
-      <c r="X45">
-        <v>1</v>
-      </c>
-      <c r="Y45">
-        <v>1.21</v>
-      </c>
-      <c r="Z45">
-        <v>3.58</v>
-      </c>
-      <c r="AA45">
-        <v>1.86</v>
-      </c>
-      <c r="AB45">
-        <v>1.92</v>
-      </c>
-      <c r="AC45">
-        <v>2.92</v>
-      </c>
-      <c r="AD45">
-        <v>1.31</v>
-      </c>
-      <c r="AE45">
-        <v>1.12</v>
-      </c>
       <c r="AF45">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG45">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK45">
         <v>1.75</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mijas Las Lagunas</t>
+          <t>CD Don Benito</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="O46">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P46">
         <v>3.4</v>
       </c>
       <c r="Q46">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="R46">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="S46">
         <v>1.35</v>
       </c>
       <c r="T46">
-        <v>2.86</v>
+        <v>2.95</v>
       </c>
       <c r="U46">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V46">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W46">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X46">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y46">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z46">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="AA46">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AB46">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AC46">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="AD46">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE46">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF46">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG46">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK46">
         <v>1.75</v>
@@ -8308,7 +8308,7 @@
         <v>4</v>
       </c>
       <c r="R49">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S49">
         <v>1.36</v>
@@ -8369,7 +8369,7 @@
         <v>1.73</v>
       </c>
       <c r="AK49">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8667,10 +8667,10 @@
         <v>1.88</v>
       </c>
       <c r="AC51">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="AD51">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE51">
         <v>1.08</v>
@@ -9313,10 +9313,10 @@
         <v>3.71</v>
       </c>
       <c r="AA55">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AB55">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AC55">
         <v>3</v>
@@ -9328,7 +9328,7 @@
         <v>1.13</v>
       </c>
       <c r="AF55">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AG55">
         <v>1.85</v>
@@ -9458,10 +9458,10 @@
         <v>2.87</v>
       </c>
       <c r="U56">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="V56">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W56">
         <v>1.08</v>
@@ -9476,7 +9476,7 @@
         <v>3.28</v>
       </c>
       <c r="AA56">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AB56">
         <v>1.95</v>
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="O60">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="P60">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="Q60">
         <v>1.62</v>
@@ -10104,16 +10104,16 @@
         <v>2.88</v>
       </c>
       <c r="S60">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T60">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="U60">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="V60">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="W60">
         <v>1.2</v>
@@ -11402,55 +11402,55 @@
         <v>0</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T68">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W68">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X68">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z68">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD68">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE68">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF68">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK68">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -13871,7 +13871,7 @@
         <v>1.02</v>
       </c>
       <c r="Y83">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Z83">
         <v>4.75</v>
@@ -13886,10 +13886,10 @@
         <v>1.94</v>
       </c>
       <c r="AD83">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AE83">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AF83">
         <v>1.44</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,28 +14001,28 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="O84">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="P84">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="Q84">
-        <v>2.57</v>
+        <v>3</v>
       </c>
       <c r="R84">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="S84">
         <v>1.22</v>
       </c>
       <c r="T84">
-        <v>3.56</v>
+        <v>3.8</v>
       </c>
       <c r="U84">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="V84">
         <v>1.62</v>
@@ -14034,22 +14034,22 @@
         <v>1.01</v>
       </c>
       <c r="Y84">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z84">
-        <v>5.5</v>
+        <v>4.85</v>
       </c>
       <c r="AA84">
         <v>1.5</v>
       </c>
       <c r="AB84">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AC84">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="AD84">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AE84">
         <v>1.22</v>
@@ -14058,7 +14058,7 @@
         <v>1.44</v>
       </c>
       <c r="AG84">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AK84">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,28 +14164,28 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="O85">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="P85">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="Q85">
-        <v>3</v>
+        <v>2.57</v>
       </c>
       <c r="R85">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="S85">
         <v>1.22</v>
       </c>
       <c r="T85">
-        <v>3.8</v>
+        <v>3.56</v>
       </c>
       <c r="U85">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="V85">
         <v>1.62</v>
@@ -14197,22 +14197,22 @@
         <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z85">
-        <v>4.85</v>
+        <v>5.5</v>
       </c>
       <c r="AA85">
         <v>1.5</v>
       </c>
       <c r="AB85">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AC85">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="AD85">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="AE85">
         <v>1.22</v>
@@ -14221,7 +14221,7 @@
         <v>1.44</v>
       </c>
       <c r="AG85">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AK85">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14351,7 +14351,7 @@
         <v>2.38</v>
       </c>
       <c r="V86">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W86">
         <v>1.12</v>
@@ -14366,10 +14366,10 @@
         <v>4.5</v>
       </c>
       <c r="AA86">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AB86">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC86">
         <v>2.46</v>
@@ -14490,43 +14490,43 @@
         </is>
       </c>
       <c r="N87">
+        <v>1.2</v>
+      </c>
+      <c r="O87">
+        <v>6.25</v>
+      </c>
+      <c r="P87">
+        <v>9.5</v>
+      </c>
+      <c r="Q87">
+        <v>1.5</v>
+      </c>
+      <c r="R87">
+        <v>3.1</v>
+      </c>
+      <c r="S87">
+        <v>1.14</v>
+      </c>
+      <c r="T87">
+        <v>5</v>
+      </c>
+      <c r="U87">
+        <v>1.83</v>
+      </c>
+      <c r="V87">
+        <v>1.83</v>
+      </c>
+      <c r="W87">
         <v>1.22</v>
-      </c>
-      <c r="O87">
-        <v>5.75</v>
-      </c>
-      <c r="P87">
-        <v>8</v>
-      </c>
-      <c r="Q87">
-        <v>1.53</v>
-      </c>
-      <c r="R87">
-        <v>3</v>
-      </c>
-      <c r="S87">
-        <v>1.17</v>
-      </c>
-      <c r="T87">
-        <v>4.5</v>
-      </c>
-      <c r="U87">
-        <v>1.91</v>
-      </c>
-      <c r="V87">
-        <v>1.8</v>
-      </c>
-      <c r="W87">
-        <v>1.2</v>
       </c>
       <c r="X87">
         <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z87">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="AA87">
         <v>1.38</v>
@@ -14535,13 +14535,13 @@
         <v>2.9</v>
       </c>
       <c r="AC87">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AD87">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="AE87">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AF87">
         <v>1.7</v>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AK87">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="O90">
         <v>5.25</v>
       </c>
       <c r="P90">
-        <v>7.25</v>
+        <v>7.5</v>
       </c>
       <c r="Q90">
         <v>1.72</v>
@@ -14994,10 +14994,10 @@
         <v>2.96</v>
       </c>
       <c r="S90">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T90">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U90">
         <v>2.05</v>
@@ -15021,13 +15021,13 @@
         <v>1.4</v>
       </c>
       <c r="AB90">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AC90">
         <v>2.04</v>
       </c>
       <c r="AD90">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AE90">
         <v>1.32</v>
@@ -15036,7 +15036,7 @@
         <v>1.6</v>
       </c>
       <c r="AG90">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>1.27</v>
       </c>
       <c r="T91">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U91">
         <v>2.3</v>
@@ -15471,7 +15471,7 @@
         <v>1.25</v>
       </c>
       <c r="O93">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="P93">
         <v>8.6</v>
@@ -15480,7 +15480,7 @@
         <v>1.5</v>
       </c>
       <c r="R93">
-        <v>3.44</v>
+        <v>3.2</v>
       </c>
       <c r="S93">
         <v>1.14</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.84</v>
+        <v>3.3</v>
       </c>
       <c r="O95">
         <v>3.3</v>
       </c>
       <c r="P95">
-        <v>3.65</v>
+        <v>1.95</v>
       </c>
       <c r="Q95">
-        <v>2.43</v>
+        <v>4.5</v>
       </c>
       <c r="R95">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="S95">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="T95">
-        <v>2.57</v>
+        <v>2.74</v>
       </c>
       <c r="U95">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="V95">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W95">
         <v>1.02</v>
       </c>
       <c r="X95">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y95">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="Z95">
-        <v>2.84</v>
+        <v>3.06</v>
       </c>
       <c r="AA95">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="AB95">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="AC95">
-        <v>4.14</v>
+        <v>3.58</v>
       </c>
       <c r="AD95">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE95">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF95">
-        <v>1.97</v>
+        <v>1.86</v>
       </c>
       <c r="AG95">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK95">
-        <v>1.92</v>
+        <v>1.22</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>3.3</v>
+        <v>1.84</v>
       </c>
       <c r="O96">
         <v>3.3</v>
       </c>
       <c r="P96">
-        <v>1.95</v>
+        <v>3.65</v>
       </c>
       <c r="Q96">
-        <v>4.5</v>
+        <v>2.43</v>
       </c>
       <c r="R96">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="S96">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="T96">
-        <v>2.74</v>
+        <v>2.57</v>
       </c>
       <c r="U96">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="V96">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W96">
         <v>1.02</v>
       </c>
       <c r="X96">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y96">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="Z96">
-        <v>3.06</v>
+        <v>2.84</v>
       </c>
       <c r="AA96">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="AB96">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="AC96">
-        <v>3.58</v>
+        <v>4.14</v>
       </c>
       <c r="AD96">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE96">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF96">
-        <v>1.86</v>
+        <v>1.97</v>
       </c>
       <c r="AG96">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK96">
-        <v>1.22</v>
+        <v>1.92</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16174,7 +16174,7 @@
         <v>1.07</v>
       </c>
       <c r="AF97">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AG97">
         <v>2.05</v>
@@ -16464,7 +16464,7 @@
         <v>1.25</v>
       </c>
       <c r="T99">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U99">
         <v>2.25</v>
@@ -16488,7 +16488,7 @@
         <v>1.55</v>
       </c>
       <c r="AB99">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="AC99">
         <v>2.31</v>
@@ -16519,7 +16519,7 @@
         <v>1.25</v>
       </c>
       <c r="AK99">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16615,7 +16615,7 @@
         <v>5.7</v>
       </c>
       <c r="P100">
-        <v>8.75</v>
+        <v>9</v>
       </c>
       <c r="Q100">
         <v>1.72</v>
@@ -16938,13 +16938,13 @@
         <v>6.16</v>
       </c>
       <c r="O102">
-        <v>4.55</v>
+        <v>4.8</v>
       </c>
       <c r="P102">
         <v>1.43</v>
       </c>
       <c r="Q102">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="R102">
         <v>2.62</v>
@@ -16959,7 +16959,7 @@
         <v>2.02</v>
       </c>
       <c r="V102">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W102">
         <v>1.17</v>
@@ -16977,7 +16977,7 @@
         <v>1.38</v>
       </c>
       <c r="AB102">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="AC102">
         <v>2.06</v>
@@ -17291,7 +17291,7 @@
         <v>1.08</v>
       </c>
       <c r="X104">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y104">
         <v>1.23</v>
@@ -17424,13 +17424,13 @@
         </is>
       </c>
       <c r="N105">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O105">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P105">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q105">
         <v>4</v>
@@ -17596,7 +17596,7 @@
         <v>3.2</v>
       </c>
       <c r="Q106">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="R106">
         <v>2.05</v>
@@ -17608,7 +17608,7 @@
         <v>2.56</v>
       </c>
       <c r="U106">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="V106">
         <v>1.36</v>
@@ -17750,13 +17750,13 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="O107">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P107">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="Q107">
         <v>2.3</v>
@@ -17913,10 +17913,10 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="O108">
-        <v>4.45</v>
+        <v>4.2</v>
       </c>
       <c r="P108">
         <v>5.62</v>
@@ -18402,10 +18402,10 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="O111">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P111">
         <v>5.75</v>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AK111">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18613,7 +18613,7 @@
         <v>2.88</v>
       </c>
       <c r="AD112">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AE112">
         <v>1.08</v>
@@ -18635,7 +18635,7 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK112">
         <v>1.75</v>
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O118">
-        <v>3.93</v>
+        <v>3.88</v>
       </c>
       <c r="P118">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q118">
         <v>3.85</v>
@@ -19582,10 +19582,10 @@
         <v>5.05</v>
       </c>
       <c r="AA118">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AB118">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AC118">
         <v>2.27</v>
@@ -19709,7 +19709,7 @@
         <v>1.18</v>
       </c>
       <c r="O119">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="P119">
         <v>12</v>
@@ -19757,7 +19757,7 @@
         <v>2.13</v>
       </c>
       <c r="AE119">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AF119">
         <v>1.65</v>
@@ -19878,7 +19878,7 @@
         <v>2.18</v>
       </c>
       <c r="Q120">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="R120">
         <v>2.38</v>
@@ -20062,7 +20062,7 @@
         <v>1.18</v>
       </c>
       <c r="X121">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y121">
         <v>1.14</v>
@@ -20403,7 +20403,7 @@
         <v>3.1</v>
       </c>
       <c r="AC123">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AD123">
         <v>1.83</v>
@@ -20415,7 +20415,7 @@
         <v>1.34</v>
       </c>
       <c r="AG123">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20591,7 +20591,7 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK124">
         <v>1.25</v>
@@ -20690,7 +20690,7 @@
         <v>3.1</v>
       </c>
       <c r="P125">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q125">
         <v>2.45</v>
@@ -21058,7 +21058,7 @@
         <v>2.92</v>
       </c>
       <c r="AD127">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AE127">
         <v>1.08</v>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK127">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21336,10 +21336,10 @@
         </is>
       </c>
       <c r="N129">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="O129">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P129">
         <v>6.5</v>
@@ -21406,7 +21406,7 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK129">
         <v>2.62</v>
@@ -21825,7 +21825,7 @@
         </is>
       </c>
       <c r="N132">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="O132">
         <v>3.2</v>
@@ -21988,25 +21988,25 @@
         </is>
       </c>
       <c r="N133">
-        <v>3.76</v>
+        <v>3.65</v>
       </c>
       <c r="O133">
         <v>3.82</v>
       </c>
       <c r="P133">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="Q133">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="R133">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="S133">
         <v>1.25</v>
       </c>
       <c r="T133">
-        <v>3.42</v>
+        <v>3.52</v>
       </c>
       <c r="U133">
         <v>2.25</v>
@@ -22021,10 +22021,10 @@
         <v>1.01</v>
       </c>
       <c r="Y133">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z133">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="AA133">
         <v>1.6</v>
@@ -22039,13 +22039,13 @@
         <v>1.53</v>
       </c>
       <c r="AE133">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF133">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AG133">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22061,7 +22061,7 @@
         <v>1.19</v>
       </c>
       <c r="AK133">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22317,10 +22317,10 @@
         <v>2.05</v>
       </c>
       <c r="O135">
+        <v>3.2</v>
+      </c>
+      <c r="P135">
         <v>3.1</v>
-      </c>
-      <c r="P135">
-        <v>3.2</v>
       </c>
       <c r="Q135">
         <v>2.7</v>
@@ -23947,10 +23947,10 @@
         <v>1.63</v>
       </c>
       <c r="O145">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P145">
-        <v>4.15</v>
+        <v>4.4</v>
       </c>
       <c r="Q145">
         <v>2.15</v>
@@ -24110,13 +24110,13 @@
         <v>1.43</v>
       </c>
       <c r="O146">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="P146">
         <v>6.7</v>
       </c>
       <c r="Q146">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="R146">
         <v>2.4</v>
@@ -24161,7 +24161,7 @@
         <v>1.13</v>
       </c>
       <c r="AF146">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG146">
         <v>1.71</v>
@@ -24180,7 +24180,7 @@
         <v>1.06</v>
       </c>
       <c r="AK146">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24273,7 +24273,7 @@
         <v>2.08</v>
       </c>
       <c r="O147">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P147">
         <v>3</v>
@@ -24759,13 +24759,13 @@
         </is>
       </c>
       <c r="N150">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O150">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P150">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q150">
         <v>2.82</v>
@@ -26887,22 +26887,22 @@
         <v>13.2</v>
       </c>
       <c r="Q163">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="R163">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="S163">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="T163">
-        <v>3.38</v>
+        <v>3.46</v>
       </c>
       <c r="U163">
         <v>2.17</v>
       </c>
       <c r="V163">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="W163">
         <v>1.13</v>
@@ -26911,31 +26911,31 @@
         <v>0</v>
       </c>
       <c r="Y163">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z163">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA163">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB163">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC163">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="AD163">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AE163">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF163">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG163">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
@@ -26948,10 +26948,10 @@
         </is>
       </c>
       <c r="AJ163">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AK163">
-        <v>3.06</v>
+        <v>2.8</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -27059,7 +27059,7 @@
         <v>1.25</v>
       </c>
       <c r="T164">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="U164">
         <v>2.3</v>
@@ -27071,10 +27071,10 @@
         <v>1.14</v>
       </c>
       <c r="X164">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y164">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z164">
         <v>4.3</v>
@@ -27092,7 +27092,7 @@
         <v>1.48</v>
       </c>
       <c r="AE164">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF164">
         <v>1.5</v>
@@ -28348,7 +28348,7 @@
         <v>1.52</v>
       </c>
       <c r="O172">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="P172">
         <v>4.5</v>
@@ -28547,7 +28547,7 @@
         <v>3.42</v>
       </c>
       <c r="AA173">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AB173">
         <v>1.85</v>
@@ -28671,64 +28671,64 @@
         </is>
       </c>
       <c r="N174">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O174">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P174">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q174">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R174">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S174">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T174">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U174">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V174">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W174">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X174">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y174">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z174">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA174">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB174">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC174">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD174">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE174">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF174">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG174">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH174" t="inlineStr">
         <is>
@@ -28741,10 +28741,10 @@
         </is>
       </c>
       <c r="AJ174">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK174">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL174">
         <v>0</v>
@@ -28858,7 +28858,7 @@
         <v>3</v>
       </c>
       <c r="V175">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W175">
         <v>1.07</v>
@@ -28867,10 +28867,10 @@
         <v>1.05</v>
       </c>
       <c r="Y175">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="Z175">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="AA175">
         <v>2.23</v>
@@ -29169,55 +29169,55 @@
         <v>2.36</v>
       </c>
       <c r="Q177">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R177">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S177">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T177">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U177">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V177">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W177">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X177">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y177">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z177">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA177">
-        <v>2.07</v>
+        <v>1.99</v>
       </c>
       <c r="AB177">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC177">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD177">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE177">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF177">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG177">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK177">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29652,7 +29652,7 @@
         <v>2.2</v>
       </c>
       <c r="O180">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P180">
         <v>2.85</v>
@@ -29685,7 +29685,7 @@
         <v>1.1</v>
       </c>
       <c r="Z180">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AA180">
         <v>1.45</v>
@@ -31330,7 +31330,7 @@
         <v>1.33</v>
       </c>
       <c r="AE190">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF190">
         <v>1.62</v>
@@ -31635,7 +31635,7 @@
         <v>1.07</v>
       </c>
       <c r="X192">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y192">
         <v>1.25</v>
@@ -31653,7 +31653,7 @@
         <v>3.1</v>
       </c>
       <c r="AD192">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AE192">
         <v>1.11</v>
@@ -31771,7 +31771,7 @@
         <v>9.25</v>
       </c>
       <c r="O193">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="P193">
         <v>1.21</v>
@@ -31822,10 +31822,10 @@
         <v>1.63</v>
       </c>
       <c r="AF193">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG193">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -32100,7 +32100,7 @@
         <v>3.4</v>
       </c>
       <c r="P195">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="Q195">
         <v>4.5</v>
@@ -32109,7 +32109,7 @@
         <v>2.1</v>
       </c>
       <c r="S195">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T195">
         <v>2.61</v>
@@ -32145,13 +32145,13 @@
         <v>1.21</v>
       </c>
       <c r="AE195">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF195">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG195">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32257,13 +32257,13 @@
         </is>
       </c>
       <c r="N196">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="O196">
         <v>3.35</v>
       </c>
       <c r="P196">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="Q196">
         <v>2.36</v>
@@ -32299,13 +32299,13 @@
         <v>1.64</v>
       </c>
       <c r="AB196">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AC196">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="AD196">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE196">
         <v>1.12</v>
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,64 +32420,64 @@
         </is>
       </c>
       <c r="N197">
-        <v>1.57</v>
+        <v>2.33</v>
       </c>
       <c r="O197">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="P197">
-        <v>4.7</v>
+        <v>2.37</v>
       </c>
       <c r="Q197">
-        <v>2</v>
+        <v>2.99</v>
       </c>
       <c r="R197">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="S197">
+        <v>1.25</v>
+      </c>
+      <c r="T197">
+        <v>3.75</v>
+      </c>
+      <c r="U197">
+        <v>2.2</v>
+      </c>
+      <c r="V197">
+        <v>1.61</v>
+      </c>
+      <c r="W197">
+        <v>1.11</v>
+      </c>
+      <c r="X197">
+        <v>1.02</v>
+      </c>
+      <c r="Y197">
+        <v>1.13</v>
+      </c>
+      <c r="Z197">
+        <v>5.2</v>
+      </c>
+      <c r="AA197">
+        <v>1.53</v>
+      </c>
+      <c r="AB197">
+        <v>2.45</v>
+      </c>
+      <c r="AC197">
+        <v>2.23</v>
+      </c>
+      <c r="AD197">
+        <v>1.56</v>
+      </c>
+      <c r="AE197">
         <v>1.2</v>
       </c>
-      <c r="T197">
-        <v>4</v>
-      </c>
-      <c r="U197">
-        <v>2.05</v>
-      </c>
-      <c r="V197">
-        <v>1.69</v>
-      </c>
-      <c r="W197">
-        <v>1.2</v>
-      </c>
-      <c r="X197">
-        <v>1.01</v>
-      </c>
-      <c r="Y197">
-        <v>1.11</v>
-      </c>
-      <c r="Z197">
-        <v>5.5</v>
-      </c>
-      <c r="AA197">
-        <v>1.4</v>
-      </c>
-      <c r="AB197">
-        <v>2.7</v>
-      </c>
-      <c r="AC197">
-        <v>2.15</v>
-      </c>
-      <c r="AD197">
-        <v>1.66</v>
-      </c>
-      <c r="AE197">
-        <v>1.25</v>
-      </c>
       <c r="AF197">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG197">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32490,10 +32490,10 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AK197">
-        <v>2.33</v>
+        <v>1.46</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G198">
@@ -32583,65 +32583,65 @@
         </is>
       </c>
       <c r="N198">
+        <v>1.58</v>
+      </c>
+      <c r="O198">
+        <v>4.5</v>
+      </c>
+      <c r="P198">
+        <v>4.75</v>
+      </c>
+      <c r="Q198">
+        <v>2</v>
+      </c>
+      <c r="R198">
+        <v>2.55</v>
+      </c>
+      <c r="S198">
+        <v>1.2</v>
+      </c>
+      <c r="T198">
+        <v>4</v>
+      </c>
+      <c r="U198">
+        <v>2.05</v>
+      </c>
+      <c r="V198">
+        <v>1.69</v>
+      </c>
+      <c r="W198">
+        <v>1.2</v>
+      </c>
+      <c r="X198">
+        <v>1.01</v>
+      </c>
+      <c r="Y198">
+        <v>1.11</v>
+      </c>
+      <c r="Z198">
+        <v>5.5</v>
+      </c>
+      <c r="AA198">
+        <v>1.4</v>
+      </c>
+      <c r="AB198">
+        <v>2.7</v>
+      </c>
+      <c r="AC198">
+        <v>2.15</v>
+      </c>
+      <c r="AD198">
+        <v>1.66</v>
+      </c>
+      <c r="AE198">
+        <v>1.25</v>
+      </c>
+      <c r="AF198">
+        <v>1.47</v>
+      </c>
+      <c r="AG198">
         <v>2.45</v>
       </c>
-      <c r="O198">
-        <v>3.8</v>
-      </c>
-      <c r="P198">
-        <v>2.45</v>
-      </c>
-      <c r="Q198">
-        <v>2.99</v>
-      </c>
-      <c r="R198">
-        <v>2.51</v>
-      </c>
-      <c r="S198">
-        <v>1.25</v>
-      </c>
-      <c r="T198">
-        <v>3.75</v>
-      </c>
-      <c r="U198">
-        <v>2.2</v>
-      </c>
-      <c r="V198">
-        <v>1.61</v>
-      </c>
-      <c r="W198">
-        <v>1.11</v>
-      </c>
-      <c r="X198">
-        <v>1.02</v>
-      </c>
-      <c r="Y198">
-        <v>1.13</v>
-      </c>
-      <c r="Z198">
-        <v>5.2</v>
-      </c>
-      <c r="AA198">
-        <v>1.53</v>
-      </c>
-      <c r="AB198">
-        <v>2.45</v>
-      </c>
-      <c r="AC198">
-        <v>2.23</v>
-      </c>
-      <c r="AD198">
-        <v>1.56</v>
-      </c>
-      <c r="AE198">
-        <v>1.2</v>
-      </c>
-      <c r="AF198">
-        <v>1.44</v>
-      </c>
-      <c r="AG198">
-        <v>2.6</v>
-      </c>
       <c r="AH198" t="inlineStr">
         <is>
           <t>[]</t>
@@ -32653,10 +32653,10 @@
         </is>
       </c>
       <c r="AJ198">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AK198">
-        <v>1.46</v>
+        <v>2.33</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -32770,7 +32770,7 @@
         <v>2.9</v>
       </c>
       <c r="V199">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W199">
         <v>1.04</v>
@@ -32918,7 +32918,7 @@
         <v>1.95</v>
       </c>
       <c r="Q200">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R200">
         <v>2.2</v>
@@ -32982,7 +32982,7 @@
         <v>1.08</v>
       </c>
       <c r="AK200">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AL200">
         <v>0</v>
@@ -33072,7 +33072,7 @@
         </is>
       </c>
       <c r="N201">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="O201">
         <v>3.6</v>
@@ -33105,7 +33105,7 @@
         <v>1.03</v>
       </c>
       <c r="Y201">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z201">
         <v>4.15</v>
@@ -33117,7 +33117,7 @@
         <v>2.07</v>
       </c>
       <c r="AC201">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AD201">
         <v>1.4</v>
@@ -33126,7 +33126,7 @@
         <v>1.11</v>
       </c>
       <c r="AF201">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG201">
         <v>2.2</v>
@@ -33235,7 +33235,7 @@
         </is>
       </c>
       <c r="N202">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="O202">
         <v>3.8</v>
@@ -33289,7 +33289,7 @@
         <v>1.22</v>
       </c>
       <c r="AF202">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AG202">
         <v>2.5</v>
@@ -33745,7 +33745,7 @@
         <v>2.78</v>
       </c>
       <c r="U205">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="V205">
         <v>1.44</v>
@@ -33754,7 +33754,7 @@
         <v>1.1</v>
       </c>
       <c r="X205">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y205">
         <v>1.21</v>
@@ -35034,7 +35034,7 @@
         <v>4.1</v>
       </c>
       <c r="P213">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="Q213">
         <v>2.2</v>
@@ -35085,7 +35085,7 @@
         <v>1.44</v>
       </c>
       <c r="AG213">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AH213" t="inlineStr">
         <is>
@@ -35194,10 +35194,10 @@
         <v>4.75</v>
       </c>
       <c r="O214">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="P214">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="Q214">
         <v>5</v>
@@ -35587,7 +35587,7 @@
         </is>
       </c>
       <c r="AJ216">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AK216">
         <v>4.65</v>
@@ -35843,13 +35843,13 @@
         </is>
       </c>
       <c r="N218">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="O218">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="P218">
-        <v>3.02</v>
+        <v>3.4</v>
       </c>
       <c r="Q218">
         <v>2.63</v>
@@ -36006,13 +36006,13 @@
         </is>
       </c>
       <c r="N219">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="O219">
-        <v>3.32</v>
+        <v>3.1</v>
       </c>
       <c r="P219">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="Q219">
         <v>2.4</v>
@@ -36172,10 +36172,10 @@
         <v>2.6</v>
       </c>
       <c r="O220">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P220">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="Q220">
         <v>3.15</v>
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G221">
@@ -36332,64 +36332,64 @@
         </is>
       </c>
       <c r="N221">
-        <v>1.96</v>
+        <v>1.52</v>
       </c>
       <c r="O221">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="P221">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="Q221">
-        <v>2.4</v>
+        <v>1.89</v>
       </c>
       <c r="R221">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="S221">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T221">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="U221">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="V221">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="W221">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="X221">
         <v>1</v>
       </c>
       <c r="Y221">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="Z221">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="AA221">
-        <v>1.74</v>
+        <v>1.43</v>
       </c>
       <c r="AB221">
-        <v>2.08</v>
+        <v>2.85</v>
       </c>
       <c r="AC221">
-        <v>2.88</v>
+        <v>2.05</v>
       </c>
       <c r="AD221">
-        <v>1.36</v>
+        <v>1.79</v>
       </c>
       <c r="AE221">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="AF221">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AG221">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AH221" t="inlineStr">
         <is>
@@ -36402,10 +36402,10 @@
         </is>
       </c>
       <c r="AJ221">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AK221">
-        <v>1.83</v>
+        <v>2.42</v>
       </c>
       <c r="AL221">
         <v>0</v>
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G222">
@@ -36495,64 +36495,64 @@
         </is>
       </c>
       <c r="N222">
-        <v>1.52</v>
+        <v>1.96</v>
       </c>
       <c r="O222">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="P222">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="Q222">
-        <v>1.89</v>
+        <v>2.4</v>
       </c>
       <c r="R222">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="S222">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T222">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="U222">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="V222">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="W222">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="X222">
         <v>1</v>
       </c>
       <c r="Y222">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="Z222">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="AA222">
-        <v>1.43</v>
+        <v>1.74</v>
       </c>
       <c r="AB222">
-        <v>2.85</v>
+        <v>2.08</v>
       </c>
       <c r="AC222">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="AD222">
-        <v>1.79</v>
+        <v>1.36</v>
       </c>
       <c r="AE222">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="AF222">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AG222">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="AH222" t="inlineStr">
         <is>
@@ -36565,10 +36565,10 @@
         </is>
       </c>
       <c r="AJ222">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AK222">
-        <v>2.42</v>
+        <v>1.83</v>
       </c>
       <c r="AL222">
         <v>0</v>
@@ -36984,64 +36984,64 @@
         </is>
       </c>
       <c r="N225">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O225">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P225">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q225">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R225">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S225">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T225">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U225">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V225">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W225">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X225">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y225">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z225">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AA225">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AB225">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC225">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD225">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE225">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF225">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG225">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH225" t="inlineStr">
         <is>
@@ -37054,10 +37054,10 @@
         </is>
       </c>
       <c r="AJ225">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK225">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL225">
         <v>0</v>
@@ -37147,64 +37147,64 @@
         </is>
       </c>
       <c r="N226">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O226">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P226">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q226">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R226">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S226">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T226">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U226">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V226">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W226">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X226">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y226">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z226">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA226">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB226">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC226">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD226">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE226">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF226">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG226">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH226" t="inlineStr">
         <is>
@@ -37217,10 +37217,10 @@
         </is>
       </c>
       <c r="AJ226">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK226">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL226">
         <v>0</v>
@@ -37310,13 +37310,13 @@
         </is>
       </c>
       <c r="N227">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="O227">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="P227">
-        <v>5.62</v>
+        <v>4.6</v>
       </c>
       <c r="Q227">
         <v>2.26</v>
@@ -37328,7 +37328,7 @@
         <v>1.43</v>
       </c>
       <c r="T227">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="U227">
         <v>2.81</v>
@@ -37473,13 +37473,13 @@
         </is>
       </c>
       <c r="N228">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="O228">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="P228">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="Q228">
         <v>2.1</v>
@@ -37636,13 +37636,13 @@
         </is>
       </c>
       <c r="N229">
+        <v>2.8</v>
+      </c>
+      <c r="O229">
         <v>3.4</v>
       </c>
-      <c r="O229">
-        <v>3.75</v>
-      </c>
       <c r="P229">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="Q229">
         <v>3.3</v>
@@ -37808,55 +37808,55 @@
         <v>0</v>
       </c>
       <c r="Q230">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R230">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S230">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T230">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U230">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V230">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W230">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X230">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y230">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z230">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA230">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB230">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC230">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD230">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE230">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF230">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG230">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH230" t="inlineStr">
         <is>
@@ -37869,10 +37869,10 @@
         </is>
       </c>
       <c r="AJ230">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK230">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL230">
         <v>0</v>
@@ -38125,13 +38125,13 @@
         </is>
       </c>
       <c r="N232">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O232">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P232">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q232">
         <v>2.7</v>
@@ -38164,10 +38164,10 @@
         <v>3.05</v>
       </c>
       <c r="AA232">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB232">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC232">
         <v>3.28</v>
@@ -38288,13 +38288,13 @@
         </is>
       </c>
       <c r="N233">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="O233">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P233">
-        <v>3.19</v>
+        <v>3.4</v>
       </c>
       <c r="Q233">
         <v>2.44</v>
@@ -38451,13 +38451,13 @@
         </is>
       </c>
       <c r="N234">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="O234">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="P234">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="Q234">
         <v>3.8</v>
@@ -38614,13 +38614,13 @@
         </is>
       </c>
       <c r="N235">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="O235">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P235">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="Q235">
         <v>2.5</v>
@@ -38780,7 +38780,7 @@
         <v>1.44</v>
       </c>
       <c r="O236">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P236">
         <v>6.5</v>
@@ -40576,7 +40576,7 @@
         <v>5.15</v>
       </c>
       <c r="P247">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="Q247">
         <v>1.8</v>
@@ -40899,7 +40899,7 @@
         <v>1.85</v>
       </c>
       <c r="O249">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P249">
         <v>3.4</v>
@@ -41059,13 +41059,13 @@
         </is>
       </c>
       <c r="N250">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="O250">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P250">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Q250">
         <v>2.25</v>
@@ -41261,7 +41261,7 @@
         <v>3.56</v>
       </c>
       <c r="AA251">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AB251">
         <v>2</v>
@@ -41711,13 +41711,13 @@
         </is>
       </c>
       <c r="N254">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="O254">
+        <v>3.1</v>
+      </c>
+      <c r="P254">
         <v>3.3</v>
-      </c>
-      <c r="P254">
-        <v>3.09</v>
       </c>
       <c r="Q254">
         <v>2.75</v>
@@ -41874,13 +41874,13 @@
         </is>
       </c>
       <c r="N255">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O255">
         <v>3.1</v>
       </c>
       <c r="P255">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="Q255">
         <v>2.88</v>
@@ -42040,7 +42040,7 @@
         <v>2.7</v>
       </c>
       <c r="O256">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P256">
         <v>2.3</v>
@@ -42689,7 +42689,7 @@
         </is>
       </c>
       <c r="N260">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="O260">
         <v>3.7</v>
@@ -43353,7 +43353,7 @@
         <v>2.1</v>
       </c>
       <c r="R264">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="S264">
         <v>1.31</v>
@@ -43833,10 +43833,10 @@
         <v>3.28</v>
       </c>
       <c r="O267">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P267">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q267">
         <v>3.56</v>
@@ -43863,10 +43863,10 @@
         <v>1.05</v>
       </c>
       <c r="Y267">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Z267">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AA267">
         <v>2.45</v>
@@ -44192,7 +44192,7 @@
         <v>1.14</v>
       </c>
       <c r="Z269">
-        <v>4.63</v>
+        <v>4.33</v>
       </c>
       <c r="AA269">
         <v>1.57</v>
@@ -44678,7 +44678,7 @@
         <v>1.03</v>
       </c>
       <c r="Y272">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z272">
         <v>3.4</v>
@@ -44817,55 +44817,55 @@
         <v>0</v>
       </c>
       <c r="Q273">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R273">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S273">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T273">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U273">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V273">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W273">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X273">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y273">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z273">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA273">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB273">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC273">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD273">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE273">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF273">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG273">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH273" t="inlineStr">
         <is>
@@ -44878,10 +44878,10 @@
         </is>
       </c>
       <c r="AJ273">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK273">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL273">
         <v>0</v>
@@ -45143,7 +45143,7 @@
         <v>1.77</v>
       </c>
       <c r="Q275">
-        <v>4.65</v>
+        <v>4.8</v>
       </c>
       <c r="R275">
         <v>2.24</v>
@@ -45297,64 +45297,64 @@
         </is>
       </c>
       <c r="N276">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O276">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P276">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q276">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R276">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S276">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T276">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U276">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V276">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W276">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X276">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y276">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z276">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA276">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB276">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC276">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD276">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE276">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF276">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG276">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH276" t="inlineStr">
         <is>
@@ -45367,10 +45367,10 @@
         </is>
       </c>
       <c r="AJ276">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK276">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL276">
         <v>0</v>
@@ -45490,7 +45490,7 @@
         <v>1.05</v>
       </c>
       <c r="X277">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y277">
         <v>1.33</v>
@@ -45505,13 +45505,13 @@
         <v>1.71</v>
       </c>
       <c r="AC277">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AD277">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE277">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF277">
         <v>1.75</v>
@@ -46275,13 +46275,13 @@
         </is>
       </c>
       <c r="N282">
-        <v>5.94</v>
+        <v>5.5</v>
       </c>
       <c r="O282">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="P282">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Q282">
         <v>6</v>
@@ -46948,7 +46948,7 @@
         <v>3.5</v>
       </c>
       <c r="U286">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="V286">
         <v>1.53</v>
@@ -46966,10 +46966,10 @@
         <v>4.55</v>
       </c>
       <c r="AA286">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AB286">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="AC286">
         <v>2.43</v>
@@ -46997,10 +46997,10 @@
         </is>
       </c>
       <c r="AJ286">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AK286">
-        <v>1.99</v>
+        <v>2.07</v>
       </c>
       <c r="AL286">
         <v>0</v>
@@ -48077,10 +48077,10 @@
         <v>10</v>
       </c>
       <c r="Q293">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R293">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="S293">
         <v>1.15</v>
@@ -48104,19 +48104,19 @@
         <v>1.04</v>
       </c>
       <c r="Z293">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="AA293">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AB293">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AC293">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AD293">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AE293">
         <v>1.41</v>
@@ -48138,7 +48138,7 @@
         </is>
       </c>
       <c r="AJ293">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AK293">
         <v>4</v>
@@ -48560,7 +48560,7 @@
         <v>1.88</v>
       </c>
       <c r="O296">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P296">
         <v>3.6</v>
@@ -48720,7 +48720,7 @@
         </is>
       </c>
       <c r="N297">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O297">
         <v>3.32</v>
@@ -48729,7 +48729,7 @@
         <v>3.24</v>
       </c>
       <c r="Q297">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="R297">
         <v>2.1</v>
@@ -48898,7 +48898,7 @@
         <v>2.15</v>
       </c>
       <c r="S298">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T298">
         <v>2.88</v>
@@ -48916,31 +48916,31 @@
         <v>1.01</v>
       </c>
       <c r="Y298">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z298">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA298">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AB298">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AC298">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD298">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE298">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF298">
         <v>1.8</v>
       </c>
       <c r="AG298">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AH298" t="inlineStr">
         <is>
@@ -49248,10 +49248,10 @@
         <v>0</v>
       </c>
       <c r="AA300">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB300">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC300">
         <v>0</v>
@@ -50522,10 +50522,10 @@
         <v>2.6</v>
       </c>
       <c r="Q308">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="R308">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S308">
         <v>1.3</v>
@@ -50567,7 +50567,7 @@
         <v>1.13</v>
       </c>
       <c r="AF308">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AG308">
         <v>2.2</v>
@@ -50682,7 +50682,7 @@
         <v>4</v>
       </c>
       <c r="P309">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="Q309">
         <v>2.05</v>
@@ -50839,7 +50839,7 @@
         </is>
       </c>
       <c r="N310">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="O310">
         <v>3.4</v>
@@ -51041,10 +51041,10 @@
         <v>0</v>
       </c>
       <c r="AA311">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB311">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="AC311">
         <v>0</v>
@@ -51171,7 +51171,7 @@
         <v>3.3</v>
       </c>
       <c r="P312">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q312">
         <v>2.35</v>
@@ -51198,7 +51198,7 @@
         <v>1.01</v>
       </c>
       <c r="Y312">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z312">
         <v>3.2</v>
@@ -51343,19 +51343,19 @@
         <v>2.7</v>
       </c>
       <c r="S313">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T313">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="U313">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="V313">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="W313">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X313">
         <v>1.01</v>
@@ -51497,22 +51497,22 @@
         <v>2.85</v>
       </c>
       <c r="P314">
-        <v>2.86</v>
+        <v>2.48</v>
       </c>
       <c r="Q314">
-        <v>3.52</v>
+        <v>3.92</v>
       </c>
       <c r="R314">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="S314">
         <v>1.62</v>
       </c>
       <c r="T314">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="U314">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="V314">
         <v>1.18</v>
@@ -51521,25 +51521,25 @@
         <v>1.04</v>
       </c>
       <c r="X314">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y314">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Z314">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AA314">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
       <c r="AB314">
         <v>1.3</v>
       </c>
       <c r="AC314">
-        <v>6.45</v>
+        <v>6.5</v>
       </c>
       <c r="AD314">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AE314">
         <v>1.02</v>
@@ -51561,10 +51561,10 @@
         </is>
       </c>
       <c r="AJ314">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AK314">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="AL314">
         <v>0</v>
@@ -51681,7 +51681,7 @@
         <v>1.65</v>
       </c>
       <c r="W315">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X315">
         <v>0</v>
@@ -52306,7 +52306,7 @@
         </is>
       </c>
       <c r="N319">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="O319">
         <v>3.1</v>
@@ -52315,16 +52315,16 @@
         <v>3.1</v>
       </c>
       <c r="Q319">
-        <v>2.71</v>
+        <v>2.57</v>
       </c>
       <c r="R319">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="S319">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="T319">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="U319">
         <v>3.3</v>
@@ -52342,19 +52342,19 @@
         <v>1.47</v>
       </c>
       <c r="Z319">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AA319">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="AB319">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AC319">
-        <v>4.93</v>
+        <v>4.87</v>
       </c>
       <c r="AD319">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE319">
         <v>1.01</v>
@@ -53776,16 +53776,16 @@
         <v>1.85</v>
       </c>
       <c r="O328">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="P328">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="Q328">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="R328">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="S328">
         <v>1.25</v>
@@ -53818,13 +53818,13 @@
         <v>2.35</v>
       </c>
       <c r="AC328">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="AD328">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AE328">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AF328">
         <v>1.45</v>
@@ -53945,10 +53945,10 @@
         <v>0</v>
       </c>
       <c r="Q329">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="R329">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="S329">
         <v>1.22</v>
@@ -54108,7 +54108,7 @@
         <v>2.41</v>
       </c>
       <c r="Q330">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="R330">
         <v>2.54</v>
@@ -54286,7 +54286,7 @@
         <v>2.2</v>
       </c>
       <c r="V331">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W331">
         <v>1.15</v>
@@ -54301,22 +54301,22 @@
         <v>5.25</v>
       </c>
       <c r="AA331">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AB331">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AC331">
-        <v>2.19</v>
+        <v>2.31</v>
       </c>
       <c r="AD331">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AE331">
         <v>1.22</v>
       </c>
       <c r="AF331">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG331">
         <v>2.38</v>
@@ -54588,13 +54588,13 @@
         </is>
       </c>
       <c r="N333">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="O333">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P333">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="Q333">
         <v>2.3</v>
@@ -54658,10 +54658,10 @@
         </is>
       </c>
       <c r="AJ333">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK333">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AL333">
         <v>0</v>

--- a/jogos_2026-11-01.xlsx
+++ b/jogos_2026-11-01.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.48</v>
+        <v>1.3</v>
       </c>
       <c r="O6">
-        <v>3.25</v>
+        <v>5.1</v>
       </c>
       <c r="P6">
-        <v>2.22</v>
+        <v>7.25</v>
       </c>
       <c r="Q6">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="R6">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="S6">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="T6">
-        <v>3.05</v>
+        <v>3.88</v>
       </c>
       <c r="U6">
-        <v>2.77</v>
+        <v>2.18</v>
       </c>
       <c r="V6">
-        <v>1.41</v>
+        <v>1.7</v>
       </c>
       <c r="W6">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="Z6">
-        <v>3.42</v>
+        <v>5.3</v>
       </c>
       <c r="AA6">
-        <v>1.79</v>
+        <v>1.45</v>
       </c>
       <c r="AB6">
-        <v>1.88</v>
+        <v>2.6</v>
       </c>
       <c r="AC6">
-        <v>3.11</v>
+        <v>2.12</v>
       </c>
       <c r="AD6">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="AE6">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AF6">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AG6">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="AK6">
-        <v>1.36</v>
+        <v>3.1</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,80 +1450,80 @@
         </is>
       </c>
       <c r="N7">
+        <v>2.48</v>
+      </c>
+      <c r="O7">
+        <v>3.25</v>
+      </c>
+      <c r="P7">
+        <v>2.22</v>
+      </c>
+      <c r="Q7">
+        <v>3.5</v>
+      </c>
+      <c r="R7">
+        <v>2.2</v>
+      </c>
+      <c r="S7">
+        <v>1.35</v>
+      </c>
+      <c r="T7">
+        <v>3.05</v>
+      </c>
+      <c r="U7">
+        <v>2.77</v>
+      </c>
+      <c r="V7">
+        <v>1.41</v>
+      </c>
+      <c r="W7">
+        <v>1.1</v>
+      </c>
+      <c r="X7">
+        <v>1.01</v>
+      </c>
+      <c r="Y7">
+        <v>1.23</v>
+      </c>
+      <c r="Z7">
+        <v>3.42</v>
+      </c>
+      <c r="AA7">
+        <v>1.79</v>
+      </c>
+      <c r="AB7">
+        <v>1.88</v>
+      </c>
+      <c r="AC7">
+        <v>3.11</v>
+      </c>
+      <c r="AD7">
+        <v>1.33</v>
+      </c>
+      <c r="AE7">
+        <v>1.08</v>
+      </c>
+      <c r="AF7">
+        <v>1.64</v>
+      </c>
+      <c r="AG7">
+        <v>2.1</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
         <v>1.3</v>
       </c>
-      <c r="O7">
-        <v>5.1</v>
-      </c>
-      <c r="P7">
-        <v>7.25</v>
-      </c>
-      <c r="Q7">
-        <v>1.7</v>
-      </c>
-      <c r="R7">
-        <v>2.6</v>
-      </c>
-      <c r="S7">
-        <v>1.22</v>
-      </c>
-      <c r="T7">
-        <v>3.88</v>
-      </c>
-      <c r="U7">
-        <v>2.18</v>
-      </c>
-      <c r="V7">
-        <v>1.7</v>
-      </c>
-      <c r="W7">
-        <v>1.13</v>
-      </c>
-      <c r="X7">
-        <v>1.02</v>
-      </c>
-      <c r="Y7">
-        <v>1.11</v>
-      </c>
-      <c r="Z7">
-        <v>5.3</v>
-      </c>
-      <c r="AA7">
-        <v>1.45</v>
-      </c>
-      <c r="AB7">
-        <v>2.6</v>
-      </c>
-      <c r="AC7">
-        <v>2.12</v>
-      </c>
-      <c r="AD7">
-        <v>1.62</v>
-      </c>
-      <c r="AE7">
-        <v>1.22</v>
-      </c>
-      <c r="AF7">
-        <v>1.73</v>
-      </c>
-      <c r="AG7">
-        <v>2</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7">
-        <v>1.09</v>
-      </c>
       <c r="AK7">
-        <v>3.1</v>
+        <v>1.36</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.83</v>
+        <v>2.79</v>
       </c>
       <c r="O19">
         <v>3.4</v>
       </c>
       <c r="P19">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="Q19">
         <v>3.25</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O21">
         <v>5.5</v>
       </c>
       <c r="P21">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="Q21">
         <v>1.64</v>
@@ -3759,34 +3759,34 @@
         <v>1.55</v>
       </c>
       <c r="W21">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X21">
         <v>1</v>
       </c>
       <c r="Y21">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z21">
-        <v>4.66</v>
+        <v>4.75</v>
       </c>
       <c r="AA21">
         <v>1.6</v>
       </c>
       <c r="AB21">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AC21">
-        <v>2.52</v>
+        <v>2.36</v>
       </c>
       <c r="AD21">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AE21">
         <v>1.17</v>
       </c>
       <c r="AF21">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AG21">
         <v>1.7</v>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AK21">
         <v>3.6</v>
@@ -3904,13 +3904,13 @@
         <v>5.25</v>
       </c>
       <c r="Q22">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="R22">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="S22">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T22">
         <v>3.24</v>
@@ -3934,16 +3934,16 @@
         <v>4</v>
       </c>
       <c r="AA22">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AB22">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC22">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="AD22">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="AE22">
         <v>1.14</v>
@@ -4073,10 +4073,10 @@
         <v>2.1</v>
       </c>
       <c r="S23">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T23">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="U23">
         <v>3</v>
@@ -4094,7 +4094,7 @@
         <v>1.37</v>
       </c>
       <c r="Z23">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="AA23">
         <v>2.11</v>
@@ -4402,7 +4402,7 @@
         <v>1.33</v>
       </c>
       <c r="T25">
-        <v>3.03</v>
+        <v>3.2</v>
       </c>
       <c r="U25">
         <v>2.59</v>
@@ -4734,7 +4734,7 @@
         <v>2.9</v>
       </c>
       <c r="V27">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W27">
         <v>1.05</v>
@@ -4746,7 +4746,7 @@
         <v>1.33</v>
       </c>
       <c r="Z27">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="AA27">
         <v>2.04</v>
@@ -4873,19 +4873,19 @@
         </is>
       </c>
       <c r="N28">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="O28">
         <v>3.85</v>
       </c>
       <c r="P28">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Q28">
         <v>5</v>
       </c>
       <c r="R28">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="S28">
         <v>1.33</v>
@@ -4921,7 +4921,7 @@
         <v>3.1</v>
       </c>
       <c r="AD28">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE28">
         <v>1.13</v>
@@ -5416,7 +5416,7 @@
         <v>1.02</v>
       </c>
       <c r="AF31">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG31">
         <v>1.67</v>
@@ -6349,10 +6349,10 @@
         <v>3.4</v>
       </c>
       <c r="Q37">
-        <v>2.63</v>
+        <v>2.54</v>
       </c>
       <c r="R37">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="S37">
         <v>1.4</v>
@@ -6370,22 +6370,22 @@
         <v>1.06</v>
       </c>
       <c r="X37">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y37">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="Z37">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="AA37">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AB37">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC37">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="AD37">
         <v>1.17</v>
@@ -6394,10 +6394,10 @@
         <v>1.03</v>
       </c>
       <c r="AF37">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AG37">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK37">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -7336,13 +7336,13 @@
         <v>1.32</v>
       </c>
       <c r="T43">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U43">
-        <v>2.45</v>
+        <v>2.54</v>
       </c>
       <c r="V43">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W43">
         <v>1.11</v>
@@ -7671,7 +7671,7 @@
         <v>1.41</v>
       </c>
       <c r="W45">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X45">
         <v>1.01</v>
@@ -7683,10 +7683,10 @@
         <v>3.42</v>
       </c>
       <c r="AA45">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AB45">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AC45">
         <v>3.05</v>
@@ -7822,13 +7822,13 @@
         <v>2.25</v>
       </c>
       <c r="S46">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T46">
         <v>2.95</v>
       </c>
       <c r="U46">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="V46">
         <v>1.44</v>
@@ -7846,10 +7846,10 @@
         <v>3.58</v>
       </c>
       <c r="AA46">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AB46">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AC46">
         <v>2.92</v>
@@ -7858,13 +7858,13 @@
         <v>1.31</v>
       </c>
       <c r="AE46">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF46">
         <v>1.67</v>
       </c>
       <c r="AG46">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>1.6</v>
       </c>
       <c r="O51">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P51">
         <v>4.8</v>
@@ -9328,7 +9328,7 @@
         <v>1.13</v>
       </c>
       <c r="AF55">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AG55">
         <v>1.85</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Atlético Central</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
+        <v>2.9</v>
+      </c>
+      <c r="O56">
+        <v>3.1</v>
+      </c>
+      <c r="P56">
+        <v>2.2</v>
+      </c>
+      <c r="Q56">
+        <v>3.5</v>
+      </c>
+      <c r="R56">
         <v>2.05</v>
       </c>
-      <c r="O56">
-        <v>3.3</v>
-      </c>
-      <c r="P56">
-        <v>3.1</v>
-      </c>
-      <c r="Q56">
+      <c r="S56">
+        <v>1.4</v>
+      </c>
+      <c r="T56">
         <v>2.7</v>
       </c>
-      <c r="R56">
-        <v>2.15</v>
-      </c>
-      <c r="S56">
+      <c r="U56">
+        <v>3</v>
+      </c>
+      <c r="V56">
         <v>1.35</v>
       </c>
-      <c r="T56">
-        <v>2.87</v>
-      </c>
-      <c r="U56">
-        <v>2.75</v>
-      </c>
-      <c r="V56">
-        <v>1.41</v>
-      </c>
       <c r="W56">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X56">
         <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="Z56">
-        <v>3.28</v>
+        <v>2.94</v>
       </c>
       <c r="AA56">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AB56">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AC56">
-        <v>2.97</v>
+        <v>3.75</v>
       </c>
       <c r="AD56">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AE56">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF56">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AG56">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
+        <v>1.36</v>
+      </c>
+      <c r="AK56">
         <v>1.33</v>
-      </c>
-      <c r="AK56">
-        <v>1.6</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Atlético Central</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.9</v>
+        <v>2.05</v>
       </c>
       <c r="O57">
+        <v>3.3</v>
+      </c>
+      <c r="P57">
         <v>3.1</v>
       </c>
-      <c r="P57">
-        <v>2.2</v>
-      </c>
       <c r="Q57">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="R57">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="S57">
+        <v>1.33</v>
+      </c>
+      <c r="T57">
+        <v>2.87</v>
+      </c>
+      <c r="U57">
+        <v>2.75</v>
+      </c>
+      <c r="V57">
         <v>1.4</v>
       </c>
-      <c r="T57">
-        <v>2.7</v>
-      </c>
-      <c r="U57">
-        <v>3</v>
-      </c>
-      <c r="V57">
-        <v>1.35</v>
-      </c>
       <c r="W57">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X57">
         <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="Z57">
-        <v>2.94</v>
+        <v>3.28</v>
       </c>
       <c r="AA57">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AB57">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AC57">
-        <v>3.75</v>
+        <v>2.97</v>
       </c>
       <c r="AD57">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AE57">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF57">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AG57">
-        <v>1.86</v>
+        <v>2.05</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK57">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9926,16 +9926,16 @@
         </is>
       </c>
       <c r="N59">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="O59">
         <v>3.5</v>
       </c>
       <c r="P59">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="Q59">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="R59">
         <v>2.03</v>
@@ -9980,10 +9980,10 @@
         <v>1.05</v>
       </c>
       <c r="AF59">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="AG59">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK59">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10608,7 +10608,7 @@
         <v>1.03</v>
       </c>
       <c r="X63">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y63">
         <v>1.35</v>
@@ -10629,7 +10629,7 @@
         <v>1.18</v>
       </c>
       <c r="AE63">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF63">
         <v>1.97</v>
@@ -11079,7 +11079,7 @@
         <v>2.6</v>
       </c>
       <c r="R66">
-        <v>2.21</v>
+        <v>2.38</v>
       </c>
       <c r="S66">
         <v>1.3</v>
@@ -11091,7 +11091,7 @@
         <v>2.45</v>
       </c>
       <c r="V66">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="W66">
         <v>1.12</v>
@@ -11269,7 +11269,7 @@
         <v>4.04</v>
       </c>
       <c r="AA67">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB67">
         <v>2.1</v>
@@ -11408,16 +11408,16 @@
         <v>2.2</v>
       </c>
       <c r="S68">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T68">
         <v>2.85</v>
       </c>
       <c r="U68">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="V68">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W68">
         <v>1.08</v>
@@ -11595,7 +11595,7 @@
         <v>2.83</v>
       </c>
       <c r="AA69">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AB69">
         <v>1.65</v>
@@ -12736,10 +12736,10 @@
         <v>3.5</v>
       </c>
       <c r="AA76">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AB76">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AC76">
         <v>3.04</v>
@@ -13687,10 +13687,10 @@
         <v>2.67</v>
       </c>
       <c r="R82">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="S82">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T82">
         <v>3.5</v>
@@ -13838,7 +13838,7 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="O83">
         <v>3.45</v>
@@ -13871,7 +13871,7 @@
         <v>1.02</v>
       </c>
       <c r="Y83">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z83">
         <v>4.75</v>
@@ -13886,10 +13886,10 @@
         <v>1.94</v>
       </c>
       <c r="AD83">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AE83">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AF83">
         <v>1.44</v>
@@ -14209,10 +14209,10 @@
         <v>2.38</v>
       </c>
       <c r="AC85">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="AD85">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AE85">
         <v>1.22</v>
@@ -14378,7 +14378,7 @@
         <v>1.43</v>
       </c>
       <c r="AE86">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AF86">
         <v>1.53</v>
@@ -14493,16 +14493,16 @@
         <v>1.2</v>
       </c>
       <c r="O87">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="P87">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="Q87">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="R87">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="S87">
         <v>1.14</v>
@@ -14544,10 +14544,10 @@
         <v>1.35</v>
       </c>
       <c r="AF87">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG87">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AK87">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14674,10 +14674,10 @@
         <v>3.7</v>
       </c>
       <c r="U88">
-        <v>2.17</v>
+        <v>2.34</v>
       </c>
       <c r="V88">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W88">
         <v>1.12</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.34</v>
+        <v>1.81</v>
       </c>
       <c r="O90">
-        <v>5.25</v>
+        <v>3.68</v>
       </c>
       <c r="P90">
-        <v>7.5</v>
+        <v>3.45</v>
       </c>
       <c r="Q90">
-        <v>1.72</v>
+        <v>2.34</v>
       </c>
       <c r="R90">
-        <v>2.96</v>
+        <v>2.44</v>
       </c>
       <c r="S90">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="T90">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="U90">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="V90">
-        <v>1.7</v>
+        <v>1.51</v>
       </c>
       <c r="W90">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="X90">
         <v>1</v>
       </c>
       <c r="Y90">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="Z90">
-        <v>6.5</v>
+        <v>4.45</v>
       </c>
       <c r="AA90">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AB90">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="AC90">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="AD90">
-        <v>1.72</v>
+        <v>1.46</v>
       </c>
       <c r="AE90">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="AF90">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AG90">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AK90">
-        <v>2.9</v>
+        <v>1.95</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.81</v>
+        <v>1.31</v>
       </c>
       <c r="O91">
-        <v>3.68</v>
+        <v>5.25</v>
       </c>
       <c r="P91">
-        <v>3.45</v>
+        <v>7.5</v>
       </c>
       <c r="Q91">
-        <v>2.34</v>
+        <v>1.69</v>
       </c>
       <c r="R91">
-        <v>2.44</v>
+        <v>3</v>
       </c>
       <c r="S91">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="T91">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="U91">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="V91">
-        <v>1.51</v>
+        <v>1.7</v>
       </c>
       <c r="W91">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="X91">
         <v>1</v>
       </c>
       <c r="Y91">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="Z91">
-        <v>4.45</v>
+        <v>6.5</v>
       </c>
       <c r="AA91">
+        <v>1.4</v>
+      </c>
+      <c r="AB91">
+        <v>2.8</v>
+      </c>
+      <c r="AC91">
+        <v>2.03</v>
+      </c>
+      <c r="AD91">
+        <v>1.72</v>
+      </c>
+      <c r="AE91">
+        <v>1.33</v>
+      </c>
+      <c r="AF91">
         <v>1.6</v>
       </c>
-      <c r="AB91">
-        <v>2.3</v>
-      </c>
-      <c r="AC91">
-        <v>2.38</v>
-      </c>
-      <c r="AD91">
-        <v>1.46</v>
-      </c>
-      <c r="AE91">
-        <v>1.16</v>
-      </c>
-      <c r="AF91">
-        <v>1.53</v>
-      </c>
       <c r="AG91">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="AK91">
-        <v>1.95</v>
+        <v>2.9</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -16286,7 +16286,7 @@
         <v>3.1</v>
       </c>
       <c r="O98">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P98">
         <v>2.42</v>
@@ -16455,10 +16455,10 @@
         <v>1.65</v>
       </c>
       <c r="Q99">
-        <v>4.83</v>
+        <v>4.7</v>
       </c>
       <c r="R99">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="S99">
         <v>1.25</v>
@@ -16470,10 +16470,10 @@
         <v>2.25</v>
       </c>
       <c r="V99">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W99">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X99">
         <v>1.01</v>
@@ -16482,16 +16482,16 @@
         <v>1.18</v>
       </c>
       <c r="Z99">
-        <v>4.78</v>
+        <v>4.74</v>
       </c>
       <c r="AA99">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AB99">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="AC99">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="AD99">
         <v>1.52</v>
@@ -17128,7 +17128,7 @@
         <v>1.17</v>
       </c>
       <c r="X103">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y103">
         <v>1.1</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="O104">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P104">
-        <v>3.2</v>
+        <v>1.85</v>
       </c>
       <c r="Q104">
-        <v>2.63</v>
+        <v>4.33</v>
       </c>
       <c r="R104">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="S104">
         <v>1.33</v>
       </c>
       <c r="T104">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U104">
         <v>2.62</v>
       </c>
       <c r="V104">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W104">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X104">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y104">
         <v>1.23</v>
       </c>
       <c r="Z104">
-        <v>3.42</v>
+        <v>3.63</v>
       </c>
       <c r="AA104">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB104">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AC104">
-        <v>3.22</v>
+        <v>3.08</v>
       </c>
       <c r="AD104">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AE104">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF104">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG104">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17334,7 +17334,7 @@
         <v>1.3</v>
       </c>
       <c r="AK104">
-        <v>1.7</v>
+        <v>1.25</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>3.45</v>
+        <v>2</v>
       </c>
       <c r="O105">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P105">
-        <v>1.91</v>
+        <v>3.2</v>
       </c>
       <c r="Q105">
-        <v>4</v>
+        <v>2.63</v>
       </c>
       <c r="R105">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S105">
         <v>1.33</v>
       </c>
       <c r="T105">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U105">
         <v>2.62</v>
       </c>
       <c r="V105">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W105">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X105">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y105">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z105">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="AA105">
+        <v>1.9</v>
+      </c>
+      <c r="AB105">
         <v>1.87</v>
       </c>
-      <c r="AB105">
-        <v>1.95</v>
-      </c>
       <c r="AC105">
-        <v>3.11</v>
+        <v>3.22</v>
       </c>
       <c r="AD105">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE105">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF105">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG105">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17497,7 +17497,7 @@
         <v>1.3</v>
       </c>
       <c r="AK105">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17587,19 +17587,19 @@
         </is>
       </c>
       <c r="N106">
+        <v>1.93</v>
+      </c>
+      <c r="O106">
+        <v>3.3</v>
+      </c>
+      <c r="P106">
+        <v>3.37</v>
+      </c>
+      <c r="Q106">
+        <v>2.69</v>
+      </c>
+      <c r="R106">
         <v>2.06</v>
-      </c>
-      <c r="O106">
-        <v>3.25</v>
-      </c>
-      <c r="P106">
-        <v>3.2</v>
-      </c>
-      <c r="Q106">
-        <v>2.8</v>
-      </c>
-      <c r="R106">
-        <v>2.05</v>
       </c>
       <c r="S106">
         <v>1.36</v>
@@ -17629,7 +17629,7 @@
         <v>2.1</v>
       </c>
       <c r="AB106">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AC106">
         <v>3.75</v>
@@ -18257,13 +18257,13 @@
         <v>1.3</v>
       </c>
       <c r="T110">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="U110">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="V110">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W110">
         <v>1.12</v>
@@ -18284,7 +18284,7 @@
         <v>2.3</v>
       </c>
       <c r="AC110">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="AD110">
         <v>1.47</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,31 +18402,31 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.42</v>
+        <v>1.91</v>
       </c>
       <c r="O111">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="P111">
-        <v>5.75</v>
+        <v>3.5</v>
       </c>
       <c r="Q111">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="R111">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S111">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T111">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="U111">
-        <v>2.51</v>
+        <v>2.75</v>
       </c>
       <c r="V111">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W111">
         <v>1.08</v>
@@ -18435,31 +18435,31 @@
         <v>1</v>
       </c>
       <c r="Y111">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z111">
-        <v>3.48</v>
+        <v>3.58</v>
       </c>
       <c r="AA111">
+        <v>1.87</v>
+      </c>
+      <c r="AB111">
         <v>1.9</v>
       </c>
-      <c r="AB111">
-        <v>1.88</v>
-      </c>
       <c r="AC111">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AD111">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE111">
         <v>1.08</v>
       </c>
       <c r="AF111">
-        <v>2.01</v>
+        <v>1.67</v>
       </c>
       <c r="AG111">
-        <v>1.69</v>
+        <v>2.07</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AK111">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,31 +18565,31 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.91</v>
+        <v>1.42</v>
       </c>
       <c r="O112">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="P112">
-        <v>3.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q112">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="R112">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S112">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T112">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="U112">
-        <v>2.75</v>
+        <v>2.51</v>
       </c>
       <c r="V112">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W112">
         <v>1.08</v>
@@ -18598,31 +18598,31 @@
         <v>1</v>
       </c>
       <c r="Y112">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z112">
-        <v>3.58</v>
+        <v>3.48</v>
       </c>
       <c r="AA112">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AB112">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AC112">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AD112">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AE112">
         <v>1.08</v>
       </c>
       <c r="AF112">
-        <v>1.67</v>
+        <v>2.01</v>
       </c>
       <c r="AG112">
-        <v>2.07</v>
+        <v>1.69</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AK112">
-        <v>1.75</v>
+        <v>2.7</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -19543,43 +19543,43 @@
         </is>
       </c>
       <c r="N118">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="O118">
-        <v>3.88</v>
+        <v>3.91</v>
       </c>
       <c r="P118">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q118">
         <v>3.85</v>
       </c>
       <c r="R118">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="S118">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T118">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U118">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="V118">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="W118">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X118">
         <v>1.02</v>
       </c>
       <c r="Y118">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z118">
-        <v>5.05</v>
+        <v>4.75</v>
       </c>
       <c r="AA118">
         <v>1.5</v>
@@ -19588,16 +19588,16 @@
         <v>2.55</v>
       </c>
       <c r="AC118">
-        <v>2.27</v>
+        <v>2.39</v>
       </c>
       <c r="AD118">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AE118">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AF118">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="AG118">
         <v>2.4</v>
@@ -19757,7 +19757,7 @@
         <v>2.13</v>
       </c>
       <c r="AE119">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AF119">
         <v>1.65</v>
@@ -19896,7 +19896,7 @@
         <v>1.62</v>
       </c>
       <c r="W120">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="X120">
         <v>1</v>
@@ -20557,7 +20557,7 @@
         <v>1.32</v>
       </c>
       <c r="Z124">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="AA124">
         <v>2.15</v>
@@ -20871,7 +20871,7 @@
         <v>2.88</v>
       </c>
       <c r="V126">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W126">
         <v>1.05</v>
@@ -20889,7 +20889,7 @@
         <v>2.05</v>
       </c>
       <c r="AB126">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC126">
         <v>3.28</v>
@@ -21016,10 +21016,10 @@
         <v>3.1</v>
       </c>
       <c r="P127">
-        <v>2.57</v>
+        <v>2.33</v>
       </c>
       <c r="Q127">
-        <v>3.38</v>
+        <v>3.39</v>
       </c>
       <c r="R127">
         <v>2.23</v>
@@ -21366,7 +21366,7 @@
         <v>1.08</v>
       </c>
       <c r="X129">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y129">
         <v>1.18</v>
@@ -21529,7 +21529,7 @@
         <v>1.04</v>
       </c>
       <c r="X130">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y130">
         <v>1.32</v>
@@ -21550,7 +21550,7 @@
         <v>1.18</v>
       </c>
       <c r="AE130">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF130">
         <v>1.86</v>
@@ -21674,7 +21674,7 @@
         <v>2.3</v>
       </c>
       <c r="R131">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="S131">
         <v>1.22</v>
@@ -21858,10 +21858,10 @@
         <v>1.07</v>
       </c>
       <c r="Y132">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="Z132">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="AA132">
         <v>2.35</v>
@@ -21879,10 +21879,10 @@
         <v>1.05</v>
       </c>
       <c r="AF132">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG132">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -22033,10 +22033,10 @@
         <v>2.38</v>
       </c>
       <c r="AC133">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AD133">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AE133">
         <v>1.2</v>
@@ -22528,7 +22528,7 @@
         <v>1.47</v>
       </c>
       <c r="AE136">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF136">
         <v>1.55</v>
@@ -22975,19 +22975,19 @@
         <v>1.53</v>
       </c>
       <c r="Q139">
-        <v>5.83</v>
+        <v>6.27</v>
       </c>
       <c r="R139">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="S139">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T139">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="U139">
-        <v>3.07</v>
+        <v>3.02</v>
       </c>
       <c r="V139">
         <v>1.36</v>
@@ -22999,10 +22999,10 @@
         <v>1</v>
       </c>
       <c r="Y139">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z139">
-        <v>3.13</v>
+        <v>3.19</v>
       </c>
       <c r="AA139">
         <v>1.98</v>
@@ -23011,7 +23011,7 @@
         <v>1.71</v>
       </c>
       <c r="AC139">
-        <v>3.63</v>
+        <v>3.54</v>
       </c>
       <c r="AD139">
         <v>1.21</v>
@@ -23645,7 +23645,7 @@
         <v>1.55</v>
       </c>
       <c r="W143">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X143">
         <v>1.03</v>
@@ -23784,7 +23784,7 @@
         <v>2.39</v>
       </c>
       <c r="O144">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P144">
         <v>2.49</v>
@@ -23998,7 +23998,7 @@
         <v>1.11</v>
       </c>
       <c r="AF145">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG145">
         <v>1.94</v>
@@ -24113,7 +24113,7 @@
         <v>4.6</v>
       </c>
       <c r="P146">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="Q146">
         <v>1.83</v>
@@ -24125,10 +24125,10 @@
         <v>1.35</v>
       </c>
       <c r="T146">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="U146">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="V146">
         <v>1.44</v>
@@ -24161,7 +24161,7 @@
         <v>1.13</v>
       </c>
       <c r="AF146">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG146">
         <v>1.71</v>
@@ -24180,7 +24180,7 @@
         <v>1.06</v>
       </c>
       <c r="AK146">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24922,7 +24922,7 @@
         </is>
       </c>
       <c r="N151">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O151">
         <v>3.6</v>
@@ -24931,7 +24931,7 @@
         <v>2.53</v>
       </c>
       <c r="Q151">
-        <v>3.12</v>
+        <v>3.19</v>
       </c>
       <c r="R151">
         <v>2.25</v>
@@ -24992,7 +24992,7 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK151">
         <v>1.45</v>
@@ -26887,22 +26887,22 @@
         <v>13.2</v>
       </c>
       <c r="Q163">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="R163">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="S163">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="T163">
-        <v>3.46</v>
+        <v>3.38</v>
       </c>
       <c r="U163">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="V163">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W163">
         <v>1.13</v>
@@ -26914,7 +26914,7 @@
         <v>1.14</v>
       </c>
       <c r="Z163">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="AA163">
         <v>1.6</v>
@@ -26932,10 +26932,10 @@
         <v>1.17</v>
       </c>
       <c r="AF163">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AG163">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
@@ -26951,7 +26951,7 @@
         <v>1.02</v>
       </c>
       <c r="AK163">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -27044,10 +27044,10 @@
         <v>2.25</v>
       </c>
       <c r="O164">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="P164">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="Q164">
         <v>2.6</v>
@@ -27080,13 +27080,13 @@
         <v>4.3</v>
       </c>
       <c r="AA164">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB164">
         <v>2.2</v>
       </c>
       <c r="AC164">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="AD164">
         <v>1.48</v>
@@ -27219,10 +27219,10 @@
         <v>2.2</v>
       </c>
       <c r="S165">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T165">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="U165">
         <v>2.75</v>
@@ -28381,13 +28381,13 @@
         <v>1.05</v>
       </c>
       <c r="Z172">
-        <v>6.65</v>
+        <v>6.55</v>
       </c>
       <c r="AA172">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AB172">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AC172">
         <v>1.83</v>
@@ -28418,7 +28418,7 @@
         <v>1.14</v>
       </c>
       <c r="AK172">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -28578,10 +28578,10 @@
         </is>
       </c>
       <c r="AJ173">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK173">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AL173">
         <v>0</v>
@@ -28858,7 +28858,7 @@
         <v>3</v>
       </c>
       <c r="V175">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W175">
         <v>1.07</v>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK175">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -29000,10 +29000,10 @@
         <v>3.4</v>
       </c>
       <c r="O176">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P176">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q176">
         <v>3.91</v>
@@ -29012,16 +29012,16 @@
         <v>1.98</v>
       </c>
       <c r="S176">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T176">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="U176">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="V176">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W176">
         <v>1.05</v>
@@ -31605,7 +31605,7 @@
         </is>
       </c>
       <c r="N192">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O192">
         <v>3.56</v>
@@ -31768,13 +31768,13 @@
         </is>
       </c>
       <c r="N193">
-        <v>9.25</v>
+        <v>10.5</v>
       </c>
       <c r="O193">
         <v>6.9</v>
       </c>
       <c r="P193">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="Q193">
         <v>6.38</v>
@@ -31783,16 +31783,16 @@
         <v>3.14</v>
       </c>
       <c r="S193">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="T193">
         <v>5</v>
       </c>
       <c r="U193">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="V193">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="W193">
         <v>1.36</v>
@@ -31819,7 +31819,7 @@
         <v>2.43</v>
       </c>
       <c r="AE193">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AF193">
         <v>1.44</v>
@@ -32109,7 +32109,7 @@
         <v>2.1</v>
       </c>
       <c r="S195">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T195">
         <v>2.61</v>
@@ -32266,10 +32266,10 @@
         <v>3.35</v>
       </c>
       <c r="Q196">
-        <v>2.36</v>
+        <v>2.43</v>
       </c>
       <c r="R196">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="S196">
         <v>1.26</v>
@@ -32278,10 +32278,10 @@
         <v>3.24</v>
       </c>
       <c r="U196">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V196">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W196">
         <v>1.1</v>
@@ -32293,10 +32293,10 @@
         <v>1.17</v>
       </c>
       <c r="Z196">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AA196">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AB196">
         <v>2.15</v>
@@ -32450,7 +32450,7 @@
         <v>1.11</v>
       </c>
       <c r="X197">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y197">
         <v>1.13</v>
@@ -32583,13 +32583,13 @@
         </is>
       </c>
       <c r="N198">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="O198">
         <v>4.5</v>
       </c>
       <c r="P198">
-        <v>4.75</v>
+        <v>4.73</v>
       </c>
       <c r="Q198">
         <v>2</v>
@@ -32604,7 +32604,7 @@
         <v>4</v>
       </c>
       <c r="U198">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="V198">
         <v>1.69</v>
@@ -32613,7 +32613,7 @@
         <v>1.2</v>
       </c>
       <c r="X198">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y198">
         <v>1.11</v>
@@ -32628,7 +32628,7 @@
         <v>2.7</v>
       </c>
       <c r="AC198">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AD198">
         <v>1.66</v>
@@ -32960,7 +32960,7 @@
         <v>1.57</v>
       </c>
       <c r="AE200">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AF200">
         <v>1.44</v>
@@ -33117,16 +33117,16 @@
         <v>2.07</v>
       </c>
       <c r="AC201">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AD201">
         <v>1.4</v>
       </c>
       <c r="AE201">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF201">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG201">
         <v>2.2</v>
@@ -33289,7 +33289,7 @@
         <v>1.22</v>
       </c>
       <c r="AF202">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AG202">
         <v>2.5</v>
@@ -33425,7 +33425,7 @@
         <v>1.62</v>
       </c>
       <c r="W203">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X203">
         <v>1.02</v>
@@ -33745,7 +33745,7 @@
         <v>2.78</v>
       </c>
       <c r="U205">
-        <v>2.53</v>
+        <v>2.73</v>
       </c>
       <c r="V205">
         <v>1.44</v>
@@ -33890,10 +33890,10 @@
         <v>1.34</v>
       </c>
       <c r="O206">
-        <v>4.55</v>
+        <v>4.8</v>
       </c>
       <c r="P206">
-        <v>6.75</v>
+        <v>7.25</v>
       </c>
       <c r="Q206">
         <v>1.75</v>
@@ -33926,25 +33926,25 @@
         <v>4.8</v>
       </c>
       <c r="AA206">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AB206">
-        <v>2.33</v>
+        <v>2.44</v>
       </c>
       <c r="AC206">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="AD206">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AE206">
         <v>1.18</v>
       </c>
       <c r="AF206">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AG206">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AH206" t="inlineStr">
         <is>
@@ -33957,7 +33957,7 @@
         </is>
       </c>
       <c r="AJ206">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AK206">
         <v>2.81</v>
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>De Graafschap W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="G209">
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>De Graafschap W</t>
         </is>
       </c>
       <c r="G210">
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G211">
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G212">
@@ -35034,7 +35034,7 @@
         <v>4.1</v>
       </c>
       <c r="P213">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="Q213">
         <v>2.2</v>
@@ -35870,7 +35870,7 @@
         <v>1.33</v>
       </c>
       <c r="W218">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X218">
         <v>1.03</v>
@@ -36033,7 +36033,7 @@
         <v>1.3</v>
       </c>
       <c r="W219">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X219">
         <v>1.04</v>
@@ -36076,7 +36076,7 @@
         </is>
       </c>
       <c r="AJ219">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK219">
         <v>1.85</v>
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G221">
@@ -36332,64 +36332,64 @@
         </is>
       </c>
       <c r="N221">
-        <v>1.52</v>
+        <v>1.96</v>
       </c>
       <c r="O221">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="P221">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="Q221">
-        <v>1.89</v>
+        <v>2.4</v>
       </c>
       <c r="R221">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="S221">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T221">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="U221">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="V221">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="W221">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="X221">
         <v>1</v>
       </c>
       <c r="Y221">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="Z221">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="AA221">
-        <v>1.43</v>
+        <v>1.74</v>
       </c>
       <c r="AB221">
-        <v>2.85</v>
+        <v>2.08</v>
       </c>
       <c r="AC221">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="AD221">
-        <v>1.79</v>
+        <v>1.36</v>
       </c>
       <c r="AE221">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="AF221">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AG221">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="AH221" t="inlineStr">
         <is>
@@ -36402,10 +36402,10 @@
         </is>
       </c>
       <c r="AJ221">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AK221">
-        <v>2.42</v>
+        <v>1.83</v>
       </c>
       <c r="AL221">
         <v>0</v>
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G222">
@@ -36495,64 +36495,64 @@
         </is>
       </c>
       <c r="N222">
-        <v>1.96</v>
+        <v>1.52</v>
       </c>
       <c r="O222">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="P222">
-        <v>3.25</v>
+        <v>5.3</v>
       </c>
       <c r="Q222">
-        <v>2.4</v>
+        <v>1.89</v>
       </c>
       <c r="R222">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="S222">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T222">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="U222">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="V222">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="W222">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="X222">
         <v>1</v>
       </c>
       <c r="Y222">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="Z222">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="AA222">
-        <v>1.74</v>
+        <v>1.48</v>
       </c>
       <c r="AB222">
-        <v>2.08</v>
+        <v>2.65</v>
       </c>
       <c r="AC222">
-        <v>2.88</v>
+        <v>2.19</v>
       </c>
       <c r="AD222">
-        <v>1.36</v>
+        <v>1.68</v>
       </c>
       <c r="AE222">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="AF222">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AG222">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AH222" t="inlineStr">
         <is>
@@ -36565,10 +36565,10 @@
         </is>
       </c>
       <c r="AJ222">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AK222">
-        <v>1.83</v>
+        <v>2.42</v>
       </c>
       <c r="AL222">
         <v>0</v>
@@ -36661,7 +36661,7 @@
         <v>3.09</v>
       </c>
       <c r="O223">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="P223">
         <v>2.5</v>
@@ -36854,16 +36854,16 @@
         <v>1.05</v>
       </c>
       <c r="Y224">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z224">
         <v>3.14</v>
       </c>
       <c r="AA224">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="AB224">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AC224">
         <v>3.47</v>
@@ -36984,13 +36984,13 @@
         </is>
       </c>
       <c r="N225">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="O225">
-        <v>2.85</v>
+        <v>2.93</v>
       </c>
       <c r="P225">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q225">
         <v>4.4</v>
@@ -37361,7 +37361,7 @@
         <v>1.21</v>
       </c>
       <c r="AE227">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF227">
         <v>2</v>
@@ -37512,7 +37512,7 @@
         <v>3.28</v>
       </c>
       <c r="AA228">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AB228">
         <v>1.82</v>
@@ -37530,7 +37530,7 @@
         <v>1.92</v>
       </c>
       <c r="AG228">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AH228" t="inlineStr">
         <is>
@@ -37814,13 +37814,13 @@
         <v>2.02</v>
       </c>
       <c r="S230">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T230">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="U230">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="V230">
         <v>1.36</v>
@@ -37992,7 +37992,7 @@
         <v>1.13</v>
       </c>
       <c r="X231">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y231">
         <v>1.11</v>
@@ -38291,10 +38291,10 @@
         <v>1.91</v>
       </c>
       <c r="O233">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P233">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q233">
         <v>2.44</v>
@@ -40280,7 +40280,7 @@
         <v>1.15</v>
       </c>
       <c r="Z245">
-        <v>4.3</v>
+        <v>4.31</v>
       </c>
       <c r="AA245">
         <v>1.65</v>
@@ -40419,7 +40419,7 @@
         <v>2.68</v>
       </c>
       <c r="R246">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="S246">
         <v>1.35</v>
@@ -40452,7 +40452,7 @@
         <v>2.06</v>
       </c>
       <c r="AC246">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="AD246">
         <v>1.41</v>
@@ -40609,7 +40609,7 @@
         <v>5.5</v>
       </c>
       <c r="AA247">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AB247">
         <v>2.5</v>
@@ -40803,10 +40803,10 @@
         </is>
       </c>
       <c r="AJ248">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK248">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AL248">
         <v>0</v>
@@ -41059,7 +41059,7 @@
         </is>
       </c>
       <c r="N250">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="O250">
         <v>3.25</v>
@@ -41246,7 +41246,7 @@
         <v>2.79</v>
       </c>
       <c r="V251">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="W251">
         <v>1.06</v>
@@ -41273,7 +41273,7 @@
         <v>1.33</v>
       </c>
       <c r="AE251">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF251">
         <v>1.65</v>
@@ -41714,7 +41714,7 @@
         <v>2.05</v>
       </c>
       <c r="O254">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P254">
         <v>3.3</v>
@@ -41944,10 +41944,10 @@
         </is>
       </c>
       <c r="AJ255">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AK255">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AL255">
         <v>0</v>
@@ -42058,10 +42058,10 @@
         <v>2.75</v>
       </c>
       <c r="U256">
-        <v>2.81</v>
+        <v>2.72</v>
       </c>
       <c r="V256">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W256">
         <v>1.06</v>
@@ -42070,31 +42070,31 @@
         <v>1.02</v>
       </c>
       <c r="Y256">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z256">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="AA256">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AB256">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AC256">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AD256">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE256">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF256">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AG256">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AH256" t="inlineStr">
         <is>
@@ -42107,7 +42107,7 @@
         </is>
       </c>
       <c r="AJ256">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AK256">
         <v>1.36</v>
@@ -42363,16 +42363,16 @@
         </is>
       </c>
       <c r="N258">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="O258">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="P258">
-        <v>4.85</v>
+        <v>4.9</v>
       </c>
       <c r="Q258">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="R258">
         <v>2.61</v>
@@ -42402,10 +42402,10 @@
         <v>6.5</v>
       </c>
       <c r="AA258">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB258">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AC258">
         <v>2.16</v>
@@ -42852,10 +42852,10 @@
         </is>
       </c>
       <c r="N261">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="O261">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="P261">
         <v>4.2</v>
@@ -43018,7 +43018,7 @@
         <v>1.28</v>
       </c>
       <c r="O262">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="P262">
         <v>8</v>
@@ -43051,22 +43051,22 @@
         <v>1.14</v>
       </c>
       <c r="Z262">
-        <v>4.62</v>
+        <v>4.61</v>
       </c>
       <c r="AA262">
         <v>1.6</v>
       </c>
       <c r="AB262">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AC262">
-        <v>2.36</v>
+        <v>2.55</v>
       </c>
       <c r="AD262">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AE262">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF262">
         <v>2</v>
@@ -43208,13 +43208,13 @@
         <v>1.1</v>
       </c>
       <c r="X263">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y263">
         <v>1.22</v>
       </c>
       <c r="Z263">
-        <v>3.74</v>
+        <v>4.1</v>
       </c>
       <c r="AA263">
         <v>1.74</v>
@@ -43223,10 +43223,10 @@
         <v>2.02</v>
       </c>
       <c r="AC263">
-        <v>2.66</v>
+        <v>3.1</v>
       </c>
       <c r="AD263">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE263">
         <v>1.11</v>
@@ -43235,7 +43235,7 @@
         <v>1.65</v>
       </c>
       <c r="AG263">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH263" t="inlineStr">
         <is>
@@ -43341,13 +43341,13 @@
         </is>
       </c>
       <c r="N264">
-        <v>1.32</v>
+        <v>1.55</v>
       </c>
       <c r="O264">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="P264">
-        <v>7.9</v>
+        <v>5</v>
       </c>
       <c r="Q264">
         <v>2.1</v>
@@ -43383,7 +43383,7 @@
         <v>1.84</v>
       </c>
       <c r="AB264">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AC264">
         <v>2.88</v>
@@ -43414,7 +43414,7 @@
         <v>1.18</v>
       </c>
       <c r="AK264">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AL264">
         <v>0</v>
@@ -43667,13 +43667,13 @@
         </is>
       </c>
       <c r="N266">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="O266">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="P266">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Q266">
         <v>6.34</v>
@@ -44008,10 +44008,10 @@
         <v>2.3</v>
       </c>
       <c r="S268">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T268">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="U268">
         <v>2.38</v>
@@ -44482,13 +44482,13 @@
         </is>
       </c>
       <c r="N271">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="O271">
         <v>3.4</v>
       </c>
       <c r="P271">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="Q271">
         <v>2.62</v>
@@ -44509,7 +44509,7 @@
         <v>1.45</v>
       </c>
       <c r="W271">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X271">
         <v>1</v>
@@ -44808,16 +44808,16 @@
         </is>
       </c>
       <c r="N273">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O273">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P273">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q273">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="R273">
         <v>2.1</v>
@@ -44878,10 +44878,10 @@
         </is>
       </c>
       <c r="AJ273">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK273">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AL273">
         <v>0</v>
@@ -45185,7 +45185,7 @@
         <v>1.38</v>
       </c>
       <c r="AE275">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF275">
         <v>1.7</v>
@@ -45297,80 +45297,80 @@
         </is>
       </c>
       <c r="N276">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="O276">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P276">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q276">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="R276">
+        <v>2.2</v>
+      </c>
+      <c r="S276">
+        <v>1.33</v>
+      </c>
+      <c r="T276">
+        <v>3</v>
+      </c>
+      <c r="U276">
+        <v>2.5</v>
+      </c>
+      <c r="V276">
+        <v>1.4</v>
+      </c>
+      <c r="W276">
+        <v>1.08</v>
+      </c>
+      <c r="X276">
+        <v>1.01</v>
+      </c>
+      <c r="Y276">
+        <v>1.24</v>
+      </c>
+      <c r="Z276">
+        <v>3.34</v>
+      </c>
+      <c r="AA276">
+        <v>1.9</v>
+      </c>
+      <c r="AB276">
+        <v>1.87</v>
+      </c>
+      <c r="AC276">
+        <v>2.97</v>
+      </c>
+      <c r="AD276">
+        <v>1.3</v>
+      </c>
+      <c r="AE276">
+        <v>1.08</v>
+      </c>
+      <c r="AF276">
+        <v>1.7</v>
+      </c>
+      <c r="AG276">
+        <v>2</v>
+      </c>
+      <c r="AH276" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI276" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ276">
+        <v>1.29</v>
+      </c>
+      <c r="AK276">
         <v>2.1</v>
-      </c>
-      <c r="S276">
-        <v>1.42</v>
-      </c>
-      <c r="T276">
-        <v>2.75</v>
-      </c>
-      <c r="U276">
-        <v>2.8</v>
-      </c>
-      <c r="V276">
-        <v>1.36</v>
-      </c>
-      <c r="W276">
-        <v>1.07</v>
-      </c>
-      <c r="X276">
-        <v>1.02</v>
-      </c>
-      <c r="Y276">
-        <v>1.35</v>
-      </c>
-      <c r="Z276">
-        <v>2.97</v>
-      </c>
-      <c r="AA276">
-        <v>2.1</v>
-      </c>
-      <c r="AB276">
-        <v>1.73</v>
-      </c>
-      <c r="AC276">
-        <v>3.34</v>
-      </c>
-      <c r="AD276">
-        <v>1.24</v>
-      </c>
-      <c r="AE276">
-        <v>1.05</v>
-      </c>
-      <c r="AF276">
-        <v>1.91</v>
-      </c>
-      <c r="AG276">
-        <v>1.75</v>
-      </c>
-      <c r="AH276" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI276" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ276">
-        <v>1.25</v>
-      </c>
-      <c r="AK276">
-        <v>2</v>
       </c>
       <c r="AL276">
         <v>0</v>
@@ -45460,13 +45460,13 @@
         </is>
       </c>
       <c r="N277">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="O277">
         <v>3.2</v>
       </c>
       <c r="P277">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q277">
         <v>2.7</v>
@@ -45502,7 +45502,7 @@
         <v>2.08</v>
       </c>
       <c r="AB277">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AC277">
         <v>3.8</v>
@@ -45786,13 +45786,13 @@
         </is>
       </c>
       <c r="N279">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O279">
         <v>3</v>
       </c>
       <c r="P279">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q279">
         <v>2.8</v>
@@ -45804,7 +45804,7 @@
         <v>1.44</v>
       </c>
       <c r="T279">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="U279">
         <v>3.28</v>
@@ -45949,13 +45949,13 @@
         </is>
       </c>
       <c r="N280">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="O280">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P280">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="Q280">
         <v>4</v>
@@ -45988,10 +45988,10 @@
         <v>2.56</v>
       </c>
       <c r="AA280">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AB280">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AC280">
         <v>4.25</v>
@@ -46003,7 +46003,7 @@
         <v>1.01</v>
       </c>
       <c r="AF280">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AG280">
         <v>1.7</v>
@@ -46019,10 +46019,10 @@
         </is>
       </c>
       <c r="AJ280">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AK280">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AL280">
         <v>0</v>
@@ -46275,10 +46275,10 @@
         </is>
       </c>
       <c r="N282">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="O282">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="P282">
         <v>1.4</v>
@@ -46444,7 +46444,7 @@
         <v>3.6</v>
       </c>
       <c r="P283">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q283">
         <v>2.4</v>
@@ -46640,7 +46640,7 @@
         <v>2.69</v>
       </c>
       <c r="AA284">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="AB284">
         <v>1.54</v>
@@ -46797,7 +46797,7 @@
         <v>1</v>
       </c>
       <c r="Y285">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z285">
         <v>5.07</v>
@@ -46927,19 +46927,19 @@
         </is>
       </c>
       <c r="N286">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="O286">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P286">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="Q286">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="R286">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S286">
         <v>1.25</v>
@@ -46975,7 +46975,7 @@
         <v>2.43</v>
       </c>
       <c r="AD286">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AE286">
         <v>1.14</v>
@@ -47461,7 +47461,7 @@
         <v>1.98</v>
       </c>
       <c r="AC289">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="AD289">
         <v>1.42</v>
@@ -47742,13 +47742,13 @@
         </is>
       </c>
       <c r="N291">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="O291">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P291">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="Q291">
         <v>0</v>
@@ -48068,19 +48068,19 @@
         </is>
       </c>
       <c r="N293">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="O293">
-        <v>5.2</v>
+        <v>5.75</v>
       </c>
       <c r="P293">
-        <v>10</v>
+        <v>7.75</v>
       </c>
       <c r="Q293">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="R293">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="S293">
         <v>1.15</v>
@@ -48104,13 +48104,13 @@
         <v>1.04</v>
       </c>
       <c r="Z293">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="AA293">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AB293">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AC293">
         <v>1.71</v>
@@ -48122,10 +48122,10 @@
         <v>1.41</v>
       </c>
       <c r="AF293">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AG293">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="AH293" t="inlineStr">
         <is>
@@ -48138,10 +48138,10 @@
         </is>
       </c>
       <c r="AJ293">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AK293">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="AL293">
         <v>0</v>
@@ -48234,7 +48234,7 @@
         <v>3.72</v>
       </c>
       <c r="O294">
-        <v>3.62</v>
+        <v>3.61</v>
       </c>
       <c r="P294">
         <v>1.78</v>
@@ -48602,7 +48602,7 @@
         <v>2.48</v>
       </c>
       <c r="AC296">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="AD296">
         <v>1.62</v>
@@ -48729,7 +48729,7 @@
         <v>3.24</v>
       </c>
       <c r="Q297">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="R297">
         <v>2.1</v>
@@ -48738,13 +48738,13 @@
         <v>1.4</v>
       </c>
       <c r="T297">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="U297">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="V297">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W297">
         <v>1.05</v>
@@ -48774,10 +48774,10 @@
         <v>1.06</v>
       </c>
       <c r="AF297">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG297">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH297" t="inlineStr">
         <is>
@@ -48793,7 +48793,7 @@
         <v>1.28</v>
       </c>
       <c r="AK297">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL297">
         <v>0</v>
@@ -49052,7 +49052,7 @@
         <v>3.3</v>
       </c>
       <c r="P299">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q299">
         <v>0</v>
@@ -49378,7 +49378,7 @@
         <v>3.62</v>
       </c>
       <c r="P301">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q301">
         <v>2.48</v>
@@ -49387,10 +49387,10 @@
         <v>2.36</v>
       </c>
       <c r="S301">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T301">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="U301">
         <v>2.39</v>
@@ -49535,13 +49535,13 @@
         </is>
       </c>
       <c r="N302">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O302">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P302">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q302">
         <v>2.5</v>
@@ -49608,7 +49608,7 @@
         <v>1.36</v>
       </c>
       <c r="AK302">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AL302">
         <v>0</v>
@@ -50519,7 +50519,7 @@
         <v>3.3</v>
       </c>
       <c r="P308">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="Q308">
         <v>2.92</v>
@@ -50718,7 +50718,7 @@
         <v>1.44</v>
       </c>
       <c r="AB309">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AC309">
         <v>2.18</v>
@@ -50845,7 +50845,7 @@
         <v>3.4</v>
       </c>
       <c r="P310">
-        <v>4.58</v>
+        <v>3.93</v>
       </c>
       <c r="Q310">
         <v>2.4</v>
@@ -50857,10 +50857,10 @@
         <v>1.46</v>
       </c>
       <c r="T310">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="U310">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="V310">
         <v>1.33</v>
@@ -50875,16 +50875,16 @@
         <v>1.4</v>
       </c>
       <c r="Z310">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="AA310">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="AB310">
         <v>1.61</v>
       </c>
       <c r="AC310">
-        <v>4.14</v>
+        <v>4.19</v>
       </c>
       <c r="AD310">
         <v>1.23</v>
@@ -50912,7 +50912,7 @@
         <v>1.24</v>
       </c>
       <c r="AK310">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AL310">
         <v>0</v>
@@ -51198,7 +51198,7 @@
         <v>1.01</v>
       </c>
       <c r="Y312">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z312">
         <v>3.2</v>
@@ -51337,55 +51337,55 @@
         <v>0</v>
       </c>
       <c r="Q313">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="R313">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="S313">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T313">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="U313">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="V313">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="W313">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X313">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y313">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z313">
-        <v>6.25</v>
+        <v>5.8</v>
       </c>
       <c r="AA313">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AB313">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="AC313">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AD313">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="AE313">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AF313">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AG313">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AH313" t="inlineStr">
         <is>
@@ -51542,7 +51542,7 @@
         <v>1.11</v>
       </c>
       <c r="AE314">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF314">
         <v>2.34</v>
@@ -52309,28 +52309,28 @@
         <v>2.3</v>
       </c>
       <c r="O319">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P319">
         <v>3.1</v>
       </c>
       <c r="Q319">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="R319">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="S319">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="T319">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="U319">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="V319">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W319">
         <v>1.04</v>
@@ -52339,25 +52339,25 @@
         <v>1.1</v>
       </c>
       <c r="Y319">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Z319">
         <v>2.5</v>
       </c>
       <c r="AA319">
-        <v>2.51</v>
+        <v>2.39</v>
       </c>
       <c r="AB319">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AC319">
-        <v>4.87</v>
+        <v>4.48</v>
       </c>
       <c r="AD319">
         <v>1.15</v>
       </c>
       <c r="AE319">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF319">
         <v>2.2</v>
@@ -53773,25 +53773,25 @@
         </is>
       </c>
       <c r="N328">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="O328">
         <v>3.41</v>
       </c>
       <c r="P328">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q328">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="R328">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="S328">
         <v>1.25</v>
       </c>
       <c r="T328">
-        <v>3.7</v>
+        <v>3.42</v>
       </c>
       <c r="U328">
         <v>2.2</v>
@@ -53800,34 +53800,34 @@
         <v>1.62</v>
       </c>
       <c r="W328">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X328">
         <v>1.01</v>
       </c>
       <c r="Y328">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z328">
-        <v>4.7</v>
+        <v>4.45</v>
       </c>
       <c r="AA328">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="AB328">
-        <v>2.35</v>
+        <v>2.24</v>
       </c>
       <c r="AC328">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AD328">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AE328">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AF328">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AG328">
         <v>2.5</v>
@@ -53843,10 +53843,10 @@
         </is>
       </c>
       <c r="AJ328">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK328">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AL328">
         <v>0</v>
@@ -53945,10 +53945,10 @@
         <v>0</v>
       </c>
       <c r="Q329">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="R329">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="S329">
         <v>1.22</v>
@@ -53975,10 +53975,10 @@
         <v>5.1</v>
       </c>
       <c r="AA329">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AB329">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="AC329">
         <v>2.13</v>
@@ -54009,7 +54009,7 @@
         <v>1.22</v>
       </c>
       <c r="AK329">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AL329">
         <v>0</v>
@@ -54108,7 +54108,7 @@
         <v>2.41</v>
       </c>
       <c r="Q330">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="R330">
         <v>2.54</v>
@@ -54286,7 +54286,7 @@
         <v>2.2</v>
       </c>
       <c r="V331">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W331">
         <v>1.15</v>
@@ -54307,7 +54307,7 @@
         <v>2.6</v>
       </c>
       <c r="AC331">
-        <v>2.31</v>
+        <v>2.26</v>
       </c>
       <c r="AD331">
         <v>1.59</v>
@@ -54624,7 +54624,7 @@
         <v>1.15</v>
       </c>
       <c r="Z333">
-        <v>4.8</v>
+        <v>4.81</v>
       </c>
       <c r="AA333">
         <v>1.57</v>
@@ -54633,7 +54633,7 @@
         <v>2.25</v>
       </c>
       <c r="AC333">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="AD333">
         <v>1.56</v>

--- a/jogos_2026-11-01.xlsx
+++ b/jogos_2026-11-01.xlsx
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,19 +2102,19 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="O11">
-        <v>3.4</v>
+        <v>3.43</v>
       </c>
       <c r="P11">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="Q11">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="R11">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="S11">
         <v>1.35</v>
@@ -2123,34 +2123,34 @@
         <v>3</v>
       </c>
       <c r="U11">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="V11">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W11">
         <v>1.1</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z11">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA11">
         <v>1.94</v>
       </c>
       <c r="AB11">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AC11">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="AD11">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE11">
         <v>1.07</v>
@@ -2159,7 +2159,7 @@
         <v>1.75</v>
       </c>
       <c r="AG11">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK11">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,19 +2265,19 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="O12">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="P12">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="Q12">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="R12">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="S12">
         <v>1.35</v>
@@ -2286,34 +2286,34 @@
         <v>3</v>
       </c>
       <c r="U12">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="V12">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W12">
         <v>1.1</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y12">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z12">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA12">
         <v>1.94</v>
       </c>
       <c r="AB12">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AC12">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="AD12">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE12">
         <v>1.07</v>
@@ -2322,7 +2322,7 @@
         <v>1.75</v>
       </c>
       <c r="AG12">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK12">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.8</v>
+        <v>2.43</v>
       </c>
       <c r="O17">
         <v>3.33</v>
@@ -3098,7 +3098,7 @@
         <v>1.3</v>
       </c>
       <c r="T17">
-        <v>3.23</v>
+        <v>3.3</v>
       </c>
       <c r="U17">
         <v>2.44</v>
@@ -3107,7 +3107,7 @@
         <v>1.44</v>
       </c>
       <c r="W17">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X17">
         <v>1.04</v>
@@ -3412,7 +3412,7 @@
         <v>3.4</v>
       </c>
       <c r="P19">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="Q19">
         <v>3.25</v>
@@ -3436,7 +3436,7 @@
         <v>1.09</v>
       </c>
       <c r="X19">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y19">
         <v>1.16</v>
@@ -3445,7 +3445,7 @@
         <v>4.1</v>
       </c>
       <c r="AA19">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB19">
         <v>2.1</v>
@@ -4076,7 +4076,7 @@
         <v>1.44</v>
       </c>
       <c r="T23">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="U23">
         <v>3</v>
@@ -4091,19 +4091,19 @@
         <v>1.04</v>
       </c>
       <c r="Y23">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="Z23">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="AA23">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="AB23">
         <v>1.72</v>
       </c>
       <c r="AC23">
-        <v>3.76</v>
+        <v>3.74</v>
       </c>
       <c r="AD23">
         <v>1.19</v>
@@ -4112,7 +4112,7 @@
         <v>1.03</v>
       </c>
       <c r="AF23">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AG23">
         <v>1.8</v>
@@ -4131,7 +4131,7 @@
         <v>1.33</v>
       </c>
       <c r="AK23">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4556,10 +4556,10 @@
         <v>0</v>
       </c>
       <c r="Q26">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="R26">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="S26">
         <v>1.3</v>
@@ -4583,13 +4583,13 @@
         <v>1.2</v>
       </c>
       <c r="Z26">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="AA26">
         <v>1.75</v>
       </c>
       <c r="AB26">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AC26">
         <v>2.87</v>
@@ -4620,7 +4620,7 @@
         <v>1.22</v>
       </c>
       <c r="AK26">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4749,7 +4749,7 @@
         <v>3.11</v>
       </c>
       <c r="AA27">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AB27">
         <v>1.7</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>4.6</v>
+        <v>4.39</v>
       </c>
       <c r="O36">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P36">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6349,7 +6349,7 @@
         <v>3.4</v>
       </c>
       <c r="Q37">
-        <v>2.54</v>
+        <v>2.63</v>
       </c>
       <c r="R37">
         <v>2.03</v>
@@ -6364,7 +6364,7 @@
         <v>3</v>
       </c>
       <c r="V37">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W37">
         <v>1.06</v>
@@ -7348,7 +7348,7 @@
         <v>1.11</v>
       </c>
       <c r="X43">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y43">
         <v>1.18</v>
@@ -7357,7 +7357,7 @@
         <v>3.88</v>
       </c>
       <c r="AA43">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AB43">
         <v>2.07</v>
@@ -7511,7 +7511,7 @@
         <v>1.08</v>
       </c>
       <c r="X44">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y44">
         <v>1.28</v>
@@ -7523,7 +7523,7 @@
         <v>1.95</v>
       </c>
       <c r="AB44">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AC44">
         <v>3.28</v>
@@ -7532,7 +7532,7 @@
         <v>1.25</v>
       </c>
       <c r="AE44">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF44">
         <v>1.83</v>
@@ -7650,7 +7650,7 @@
         <v>3.25</v>
       </c>
       <c r="P45">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q45">
         <v>2.46</v>
@@ -7662,7 +7662,7 @@
         <v>1.35</v>
       </c>
       <c r="T45">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="U45">
         <v>2.62</v>
@@ -7671,7 +7671,7 @@
         <v>1.41</v>
       </c>
       <c r="W45">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X45">
         <v>1.01</v>
@@ -7822,13 +7822,13 @@
         <v>2.25</v>
       </c>
       <c r="S46">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T46">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="U46">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="V46">
         <v>1.44</v>
@@ -7861,7 +7861,7 @@
         <v>1.1</v>
       </c>
       <c r="AF46">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG46">
         <v>2.06</v>
@@ -8136,7 +8136,7 @@
         <v>1.8</v>
       </c>
       <c r="O48">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P48">
         <v>4.03</v>
@@ -8326,7 +8326,7 @@
         <v>1.08</v>
       </c>
       <c r="X49">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y49">
         <v>1.31</v>
@@ -8335,10 +8335,10 @@
         <v>3.18</v>
       </c>
       <c r="AA49">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB49">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC49">
         <v>3.2</v>
@@ -8347,7 +8347,7 @@
         <v>1.26</v>
       </c>
       <c r="AE49">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF49">
         <v>1.83</v>
@@ -8471,13 +8471,13 @@
         <v>2.7</v>
       </c>
       <c r="R50">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="S50">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T50">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="U50">
         <v>2.9</v>
@@ -8489,7 +8489,7 @@
         <v>1.04</v>
       </c>
       <c r="X50">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y50">
         <v>1.32</v>
@@ -8498,19 +8498,19 @@
         <v>2.88</v>
       </c>
       <c r="AA50">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB50">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AC50">
-        <v>3.84</v>
+        <v>3.78</v>
       </c>
       <c r="AD50">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE50">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF50">
         <v>1.85</v>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK50">
         <v>1.67</v>
@@ -8664,7 +8664,7 @@
         <v>1.85</v>
       </c>
       <c r="AB51">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AC51">
         <v>3.08</v>
@@ -8673,7 +8673,7 @@
         <v>1.28</v>
       </c>
       <c r="AE51">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF51">
         <v>1.83</v>
@@ -8987,19 +8987,19 @@
         <v>4.43</v>
       </c>
       <c r="AA53">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AB53">
         <v>2.27</v>
       </c>
       <c r="AC53">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="AD53">
         <v>1.5</v>
       </c>
       <c r="AE53">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF53">
         <v>1.5</v>
@@ -9114,46 +9114,46 @@
         <v>2.45</v>
       </c>
       <c r="O54">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P54">
         <v>2.5</v>
       </c>
       <c r="Q54">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="R54">
         <v>2.1</v>
       </c>
       <c r="S54">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T54">
-        <v>2.73</v>
+        <v>2.63</v>
       </c>
       <c r="U54">
-        <v>2.88</v>
+        <v>2.68</v>
       </c>
       <c r="V54">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W54">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X54">
         <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z54">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AA54">
         <v>1.95</v>
       </c>
       <c r="AB54">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC54">
         <v>3.28</v>
@@ -9162,13 +9162,13 @@
         <v>1.25</v>
       </c>
       <c r="AE54">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF54">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AG54">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>1.29</v>
       </c>
       <c r="AK54">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9965,7 +9965,7 @@
         <v>3.05</v>
       </c>
       <c r="AA59">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AB59">
         <v>1.72</v>
@@ -10104,16 +10104,16 @@
         <v>2.88</v>
       </c>
       <c r="S60">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="T60">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="U60">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="V60">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="W60">
         <v>1.2</v>
@@ -10252,7 +10252,7 @@
         </is>
       </c>
       <c r="N61">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="O61">
         <v>6.5</v>
@@ -10261,7 +10261,7 @@
         <v>1.2</v>
       </c>
       <c r="Q61">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="R61">
         <v>3.3</v>
@@ -10297,19 +10297,19 @@
         <v>4.1</v>
       </c>
       <c r="AC61">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AD61">
+        <v>2.17</v>
+      </c>
+      <c r="AE61">
+        <v>1.54</v>
+      </c>
+      <c r="AF61">
+        <v>1.6</v>
+      </c>
+      <c r="AG61">
         <v>2.19</v>
-      </c>
-      <c r="AE61">
-        <v>1.52</v>
-      </c>
-      <c r="AF61">
-        <v>1.57</v>
-      </c>
-      <c r="AG61">
-        <v>2.12</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10418,13 +10418,13 @@
         <v>1.4</v>
       </c>
       <c r="O62">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="P62">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Q62">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="R62">
         <v>2.6</v>
@@ -10436,13 +10436,13 @@
         <v>3.85</v>
       </c>
       <c r="U62">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="V62">
         <v>1.66</v>
       </c>
       <c r="W62">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X62">
         <v>1.02</v>
@@ -10454,19 +10454,19 @@
         <v>5.5</v>
       </c>
       <c r="AA62">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AB62">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="AC62">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AD62">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AE62">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF62">
         <v>1.57</v>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK62">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -11411,10 +11411,10 @@
         <v>1.33</v>
       </c>
       <c r="T68">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="U68">
-        <v>2.75</v>
+        <v>2.61</v>
       </c>
       <c r="V68">
         <v>1.4</v>
@@ -11432,10 +11432,10 @@
         <v>3.28</v>
       </c>
       <c r="AA68">
+        <v>1.85</v>
+      </c>
+      <c r="AB68">
         <v>1.95</v>
-      </c>
-      <c r="AB68">
-        <v>1.84</v>
       </c>
       <c r="AC68">
         <v>3.08</v>
@@ -11737,13 +11737,13 @@
         <v>1.25</v>
       </c>
       <c r="T70">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U70">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="V70">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W70">
         <v>1.11</v>
@@ -11752,22 +11752,22 @@
         <v>1.01</v>
       </c>
       <c r="Y70">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z70">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AA70">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AB70">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="AC70">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="AD70">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AE70">
         <v>1.2</v>
@@ -11776,7 +11776,7 @@
         <v>1.5</v>
       </c>
       <c r="AG70">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>1.25</v>
       </c>
       <c r="AK70">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11897,19 +11897,19 @@
         <v>3.5</v>
       </c>
       <c r="S71">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="T71">
         <v>5.5</v>
       </c>
       <c r="U71">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="V71">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="W71">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X71">
         <v>1</v>
@@ -11927,19 +11927,19 @@
         <v>4.1</v>
       </c>
       <c r="AC71">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AD71">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="AE71">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AF71">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG71">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AK71">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -13198,7 +13198,7 @@
         <v>2.8</v>
       </c>
       <c r="R79">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="S79">
         <v>1.3</v>
@@ -13207,10 +13207,10 @@
         <v>3.3</v>
       </c>
       <c r="U79">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="V79">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W79">
         <v>1.13</v>
@@ -13222,28 +13222,28 @@
         <v>1.2</v>
       </c>
       <c r="Z79">
-        <v>4.25</v>
+        <v>4.29</v>
       </c>
       <c r="AA79">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB79">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="AC79">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="AD79">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AE79">
         <v>1.12</v>
       </c>
       <c r="AF79">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AG79">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13259,7 +13259,7 @@
         <v>1.2</v>
       </c>
       <c r="AK79">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13355,7 +13355,7 @@
         <v>3.25</v>
       </c>
       <c r="P80">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="Q80">
         <v>2.15</v>
@@ -14674,13 +14674,13 @@
         <v>3.7</v>
       </c>
       <c r="U88">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="V88">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W88">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X88">
         <v>1</v>
@@ -14692,7 +14692,7 @@
         <v>4.64</v>
       </c>
       <c r="AA88">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB88">
         <v>2.26</v>
@@ -14710,7 +14710,7 @@
         <v>1.5</v>
       </c>
       <c r="AG88">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Gaziantep FK</t>
         </is>
       </c